--- a/data/Export_Progres_Pendataan_Kabupaten_Kota.xlsx
+++ b/data/Export_Progres_Pendataan_Kabupaten_Kota.xlsx
@@ -18,12 +18,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1363" uniqueCount="655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1363" uniqueCount="671">
   <si>
     <t>PROGRES PENDATAAN - PROGRES PENDATAAN</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 17 Agu 2026, 18.00 | Dicetak: 18 Agu 2026, 06.15</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 18 Agu 2026, 06.00 | Dicetak: 18 Agu 2026, 07.19</t>
   </si>
   <si>
     <t>Kode</t>
@@ -98,10 +98,10 @@
     <t>107,72</t>
   </si>
   <si>
-    <t>64,72</t>
-  </si>
-  <si>
-    <t>5,18</t>
+    <t>65,12</t>
+  </si>
+  <si>
+    <t>4,96</t>
   </si>
   <si>
     <t>1801</t>
@@ -113,10 +113,10 @@
     <t>124,06</t>
   </si>
   <si>
-    <t>84,2</t>
-  </si>
-  <si>
-    <t>1,77</t>
+    <t>84,45</t>
+  </si>
+  <si>
+    <t>1,6</t>
   </si>
   <si>
     <t>1802</t>
@@ -128,10 +128,10 @@
     <t>106,43</t>
   </si>
   <si>
-    <t>66,87</t>
-  </si>
-  <si>
-    <t>7,29</t>
+    <t>67,21</t>
+  </si>
+  <si>
+    <t>7,1</t>
   </si>
   <si>
     <t>1803</t>
@@ -143,10 +143,10 @@
     <t>104,26</t>
   </si>
   <si>
-    <t>58,95</t>
-  </si>
-  <si>
-    <t>6,28</t>
+    <t>59,3</t>
+  </si>
+  <si>
+    <t>6,06</t>
   </si>
   <si>
     <t>1804</t>
@@ -158,10 +158,10 @@
     <t>103,21</t>
   </si>
   <si>
-    <t>63,01</t>
-  </si>
-  <si>
-    <t>4,59</t>
+    <t>63,37</t>
+  </si>
+  <si>
+    <t>4,44</t>
   </si>
   <si>
     <t>1805</t>
@@ -173,471 +173,471 @@
     <t>104</t>
   </si>
   <si>
-    <t>63,39</t>
+    <t>63,79</t>
+  </si>
+  <si>
+    <t>5,42</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>LAMPUNG UTARA</t>
+  </si>
+  <si>
+    <t>110,97</t>
+  </si>
+  <si>
+    <t>63,3</t>
+  </si>
+  <si>
+    <t>2,88</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>WAY KANAN</t>
+  </si>
+  <si>
+    <t>107,97</t>
+  </si>
+  <si>
+    <t>64,74</t>
+  </si>
+  <si>
+    <t>5,16</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG</t>
+  </si>
+  <si>
+    <t>108,85</t>
+  </si>
+  <si>
+    <t>64,65</t>
+  </si>
+  <si>
+    <t>5,72</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>PESAWARAN</t>
+  </si>
+  <si>
+    <t>119,52</t>
+  </si>
+  <si>
+    <t>81,12</t>
+  </si>
+  <si>
+    <t>3,57</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>PRINGSEWU</t>
+  </si>
+  <si>
+    <t>107,3</t>
+  </si>
+  <si>
+    <t>75,83</t>
+  </si>
+  <si>
+    <t>6,93</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>MESUJI</t>
+  </si>
+  <si>
+    <t>131,96</t>
+  </si>
+  <si>
+    <t>86,26</t>
+  </si>
+  <si>
+    <t>0,72</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG BARAT</t>
+  </si>
+  <si>
+    <t>126,06</t>
+  </si>
+  <si>
+    <t>84,82</t>
+  </si>
+  <si>
+    <t>1,93</t>
+  </si>
+  <si>
+    <t>1813</t>
+  </si>
+  <si>
+    <t>PESISIR BARAT</t>
+  </si>
+  <si>
+    <t>129,14</t>
+  </si>
+  <si>
+    <t>93,21</t>
+  </si>
+  <si>
+    <t>0,88</t>
+  </si>
+  <si>
+    <t>1871</t>
+  </si>
+  <si>
+    <t>BANDAR LAMPUNG</t>
+  </si>
+  <si>
+    <t>99,72</t>
+  </si>
+  <si>
+    <t>47,65</t>
+  </si>
+  <si>
+    <t>6,1</t>
+  </si>
+  <si>
+    <t>1872</t>
+  </si>
+  <si>
+    <t>METRO</t>
+  </si>
+  <si>
+    <t>104,01</t>
+  </si>
+  <si>
+    <t>6,31</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Catatan</t>
+  </si>
+  <si>
+    <t>Jumlah assignment (usaha/keluarga/bangunan lain) yang sudah berhasil didata dengan status selain open/draft, dibandingkan dengan jumlah usaha/keluarga dalam prelist berjalan.</t>
+  </si>
+  <si>
+    <t>Responden Didata (Usaha &amp; Keluarga Ditemukan/Baru/Force Submit)</t>
+  </si>
+  <si>
+    <t>Jumlah responden Usaha BKU dan Keluarga dengan status Ditemukan/Baru/Force Submit, dibandingkan dengan jumlah usaha/keluarga dalam prelist berjalan.</t>
+  </si>
+  <si>
+    <t>Jumlah Responden Sedang Didata</t>
+  </si>
+  <si>
+    <t>Jumlah responden dengan status Draft.</t>
+  </si>
+  <si>
+    <t>PROGRES PENDATAAN - USAHA/PERUSAHAAN</t>
+  </si>
+  <si>
+    <t>Jumlah Prelist Usaha</t>
+  </si>
+  <si>
+    <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha BKU (Ditemukan CAWI/UB dan CAPI + Baru)</t>
+  </si>
+  <si>
+    <t>Persentase Usaha BKU (Ditemukan CAWI/UB dan CAPI + Baru)</t>
+  </si>
+  <si>
+    <t>CAWI/UB</t>
+  </si>
+  <si>
+    <t>CAPI</t>
+  </si>
+  <si>
+    <t>Ditemukan/Pindah Dapat Ditelusuri</t>
+  </si>
+  <si>
+    <t>Persentase Ditemukan/Pindah Dapat Ditelusuri</t>
+  </si>
+  <si>
+    <t>Ditemukan Tetapi Bukan Cakupan Survei</t>
+  </si>
+  <si>
+    <t>Persentase Ditemukan Tetapi Bukan Cakupan Survei</t>
+  </si>
+  <si>
+    <t>Pindah Tidak Dapat Ditelusuri</t>
+  </si>
+  <si>
+    <t>Persentase Pindah Tidak Dapat Ditelusuri</t>
+  </si>
+  <si>
+    <t>Tutup</t>
+  </si>
+  <si>
+    <t>Persentase Tutup</t>
+  </si>
+  <si>
+    <t>Duplikat</t>
+  </si>
+  <si>
+    <t>Persentase Duplikat</t>
+  </si>
+  <si>
+    <t>Tidak Ditemukan</t>
+  </si>
+  <si>
+    <t>Persentase Tidak Ditemukan</t>
+  </si>
+  <si>
+    <t>Data Diperoleh dari Kantor Pusat</t>
+  </si>
+  <si>
+    <t>Persentase Data Diperoleh dari Kantor Pusat</t>
+  </si>
+  <si>
+    <t>Nonrespon</t>
+  </si>
+  <si>
+    <t>Persentase Nonrespon</t>
+  </si>
+  <si>
+    <t>Ditemukan</t>
+  </si>
+  <si>
+    <t>Persentase Ditemukan</t>
+  </si>
+  <si>
+    <t>Tutup​</t>
+  </si>
+  <si>
+    <t>Persentase Tutup​</t>
+  </si>
+  <si>
+    <t>Ganda</t>
+  </si>
+  <si>
+    <t>Persentase Ganda</t>
+  </si>
+  <si>
+    <t>Tidak Ditemukan​</t>
+  </si>
+  <si>
+    <t>Persentase Tidak Ditemukan​</t>
+  </si>
+  <si>
+    <t>Persentase Baru</t>
+  </si>
+  <si>
+    <t>Data Diperoleh dari Kantor Pusat​</t>
+  </si>
+  <si>
+    <t>Persentase Data Diperoleh dari Kantor Pusat​</t>
+  </si>
+  <si>
+    <t>Nonrespon​</t>
+  </si>
+  <si>
+    <t>Persentase Nonrespon​</t>
+  </si>
+  <si>
+    <t>Force Submit (Diklaim Sebagai Usaha Keluarga)</t>
+  </si>
+  <si>
+    <t>Persentase Force Submit (Diklaim Sebagai Usaha Keluarga)</t>
+  </si>
+  <si>
+    <t>(11)</t>
+  </si>
+  <si>
+    <t>(12)</t>
+  </si>
+  <si>
+    <t>(13)</t>
+  </si>
+  <si>
+    <t>(14)</t>
+  </si>
+  <si>
+    <t>(15)</t>
+  </si>
+  <si>
+    <t>(16)</t>
+  </si>
+  <si>
+    <t>(17)</t>
+  </si>
+  <si>
+    <t>(18)</t>
+  </si>
+  <si>
+    <t>(19)</t>
+  </si>
+  <si>
+    <t>(20)</t>
+  </si>
+  <si>
+    <t>(21)</t>
+  </si>
+  <si>
+    <t>(22)</t>
+  </si>
+  <si>
+    <t>(23)</t>
+  </si>
+  <si>
+    <t>(24)</t>
+  </si>
+  <si>
+    <t>(25)</t>
+  </si>
+  <si>
+    <t>(26)</t>
+  </si>
+  <si>
+    <t>(27)</t>
+  </si>
+  <si>
+    <t>(28)</t>
+  </si>
+  <si>
+    <t>(29)</t>
+  </si>
+  <si>
+    <t>(30)</t>
+  </si>
+  <si>
+    <t>(31)</t>
+  </si>
+  <si>
+    <t>(32)</t>
+  </si>
+  <si>
+    <t>(33)</t>
+  </si>
+  <si>
+    <t>(34)</t>
+  </si>
+  <si>
+    <t>(35)</t>
+  </si>
+  <si>
+    <t>(36)</t>
+  </si>
+  <si>
+    <t>(37)</t>
+  </si>
+  <si>
+    <t>0,14</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>0,01</t>
+  </si>
+  <si>
+    <t>10,92</t>
+  </si>
+  <si>
+    <t>16,71</t>
+  </si>
+  <si>
+    <t>7,53</t>
+  </si>
+  <si>
+    <t>42,78</t>
+  </si>
+  <si>
+    <t>14,55</t>
+  </si>
+  <si>
+    <t>6,07</t>
+  </si>
+  <si>
+    <t>25,62</t>
+  </si>
+  <si>
+    <t>0,19</t>
+  </si>
+  <si>
+    <t>0,03</t>
+  </si>
+  <si>
+    <t>16,49</t>
+  </si>
+  <si>
+    <t>16,53</t>
+  </si>
+  <si>
+    <t>12,59</t>
+  </si>
+  <si>
+    <t>41,65</t>
+  </si>
+  <si>
+    <t>17,21</t>
+  </si>
+  <si>
+    <t>1,48</t>
+  </si>
+  <si>
+    <t>33,9</t>
+  </si>
+  <si>
+    <t>0,09</t>
+  </si>
+  <si>
+    <t>0,02</t>
+  </si>
+  <si>
+    <t>0,05</t>
+  </si>
+  <si>
+    <t>8,38</t>
+  </si>
+  <si>
+    <t>21,34</t>
+  </si>
+  <si>
+    <t>14,9</t>
+  </si>
+  <si>
+    <t>25,96</t>
+  </si>
+  <si>
+    <t>9,03</t>
+  </si>
+  <si>
+    <t>9,86</t>
+  </si>
+  <si>
+    <t>17,5</t>
+  </si>
+  <si>
+    <t>0,13</t>
   </si>
   <si>
     <t>5,63</t>
   </si>
   <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>LAMPUNG UTARA</t>
-  </si>
-  <si>
-    <t>110,97</t>
-  </si>
-  <si>
-    <t>62,86</t>
-  </si>
-  <si>
-    <t>3,05</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>WAY KANAN</t>
-  </si>
-  <si>
-    <t>107,97</t>
-  </si>
-  <si>
-    <t>64,37</t>
-  </si>
-  <si>
-    <t>5,27</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG</t>
-  </si>
-  <si>
-    <t>108,85</t>
-  </si>
-  <si>
-    <t>63,99</t>
-  </si>
-  <si>
-    <t>6,06</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>PESAWARAN</t>
-  </si>
-  <si>
-    <t>119,52</t>
-  </si>
-  <si>
-    <t>80,72</t>
-  </si>
-  <si>
-    <t>3,81</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>PRINGSEWU</t>
-  </si>
-  <si>
-    <t>107,3</t>
-  </si>
-  <si>
-    <t>75,4</t>
-  </si>
-  <si>
-    <t>7,18</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>MESUJI</t>
-  </si>
-  <si>
-    <t>131,96</t>
-  </si>
-  <si>
-    <t>86</t>
-  </si>
-  <si>
-    <t>0,96</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG BARAT</t>
-  </si>
-  <si>
-    <t>126,06</t>
-  </si>
-  <si>
-    <t>84,41</t>
-  </si>
-  <si>
-    <t>2,16</t>
-  </si>
-  <si>
-    <t>1813</t>
-  </si>
-  <si>
-    <t>PESISIR BARAT</t>
-  </si>
-  <si>
-    <t>129,14</t>
-  </si>
-  <si>
-    <t>92,94</t>
-  </si>
-  <si>
-    <t>0,97</t>
-  </si>
-  <si>
-    <t>1871</t>
-  </si>
-  <si>
-    <t>BANDAR LAMPUNG</t>
-  </si>
-  <si>
-    <t>99,72</t>
-  </si>
-  <si>
-    <t>47,22</t>
-  </si>
-  <si>
-    <t>6,44</t>
-  </si>
-  <si>
-    <t>1872</t>
-  </si>
-  <si>
-    <t>METRO</t>
-  </si>
-  <si>
-    <t>104,01</t>
-  </si>
-  <si>
-    <t>62,9</t>
-  </si>
-  <si>
-    <t>6,71</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Catatan</t>
-  </si>
-  <si>
-    <t>Jumlah assignment (usaha/keluarga/bangunan lain) yang sudah berhasil didata dengan status selain open/draft, dibandingkan dengan jumlah usaha/keluarga dalam prelist berjalan.</t>
-  </si>
-  <si>
-    <t>Responden Didata (Usaha &amp; Keluarga Ditemukan/Baru/Force Submit)</t>
-  </si>
-  <si>
-    <t>Jumlah responden Usaha BKU dan Keluarga dengan status Ditemukan/Baru/Force Submit, dibandingkan dengan jumlah usaha/keluarga dalam prelist berjalan.</t>
-  </si>
-  <si>
-    <t>Jumlah Responden Sedang Didata</t>
-  </si>
-  <si>
-    <t>Jumlah responden dengan status Draft.</t>
-  </si>
-  <si>
-    <t>PROGRES PENDATAAN - USAHA/PERUSAHAAN</t>
-  </si>
-  <si>
-    <t>Jumlah Prelist Usaha</t>
-  </si>
-  <si>
-    <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha BKU (Ditemukan CAWI/UB dan CAPI + Baru)</t>
-  </si>
-  <si>
-    <t>Persentase Usaha BKU (Ditemukan CAWI/UB dan CAPI + Baru)</t>
-  </si>
-  <si>
-    <t>CAWI/UB</t>
-  </si>
-  <si>
-    <t>CAPI</t>
-  </si>
-  <si>
-    <t>Ditemukan/Pindah Dapat Ditelusuri</t>
-  </si>
-  <si>
-    <t>Persentase Ditemukan/Pindah Dapat Ditelusuri</t>
-  </si>
-  <si>
-    <t>Ditemukan Tetapi Bukan Cakupan Survei</t>
-  </si>
-  <si>
-    <t>Persentase Ditemukan Tetapi Bukan Cakupan Survei</t>
-  </si>
-  <si>
-    <t>Pindah Tidak Dapat Ditelusuri</t>
-  </si>
-  <si>
-    <t>Persentase Pindah Tidak Dapat Ditelusuri</t>
-  </si>
-  <si>
-    <t>Tutup</t>
-  </si>
-  <si>
-    <t>Persentase Tutup</t>
-  </si>
-  <si>
-    <t>Duplikat</t>
-  </si>
-  <si>
-    <t>Persentase Duplikat</t>
-  </si>
-  <si>
-    <t>Tidak Ditemukan</t>
-  </si>
-  <si>
-    <t>Persentase Tidak Ditemukan</t>
-  </si>
-  <si>
-    <t>Data Diperoleh dari Kantor Pusat</t>
-  </si>
-  <si>
-    <t>Persentase Data Diperoleh dari Kantor Pusat</t>
-  </si>
-  <si>
-    <t>Nonrespon</t>
-  </si>
-  <si>
-    <t>Persentase Nonrespon</t>
-  </si>
-  <si>
-    <t>Ditemukan</t>
-  </si>
-  <si>
-    <t>Persentase Ditemukan</t>
-  </si>
-  <si>
-    <t>Tutup​</t>
-  </si>
-  <si>
-    <t>Persentase Tutup​</t>
-  </si>
-  <si>
-    <t>Ganda</t>
-  </si>
-  <si>
-    <t>Persentase Ganda</t>
-  </si>
-  <si>
-    <t>Tidak Ditemukan​</t>
-  </si>
-  <si>
-    <t>Persentase Tidak Ditemukan​</t>
-  </si>
-  <si>
-    <t>Persentase Baru</t>
-  </si>
-  <si>
-    <t>Data Diperoleh dari Kantor Pusat​</t>
-  </si>
-  <si>
-    <t>Persentase Data Diperoleh dari Kantor Pusat​</t>
-  </si>
-  <si>
-    <t>Nonrespon​</t>
-  </si>
-  <si>
-    <t>Persentase Nonrespon​</t>
-  </si>
-  <si>
-    <t>Force Submit (Diklaim Sebagai Usaha Keluarga)</t>
-  </si>
-  <si>
-    <t>Persentase Force Submit (Diklaim Sebagai Usaha Keluarga)</t>
-  </si>
-  <si>
-    <t>(11)</t>
-  </si>
-  <si>
-    <t>(12)</t>
-  </si>
-  <si>
-    <t>(13)</t>
-  </si>
-  <si>
-    <t>(14)</t>
-  </si>
-  <si>
-    <t>(15)</t>
-  </si>
-  <si>
-    <t>(16)</t>
-  </si>
-  <si>
-    <t>(17)</t>
-  </si>
-  <si>
-    <t>(18)</t>
-  </si>
-  <si>
-    <t>(19)</t>
-  </si>
-  <si>
-    <t>(20)</t>
-  </si>
-  <si>
-    <t>(21)</t>
-  </si>
-  <si>
-    <t>(22)</t>
-  </si>
-  <si>
-    <t>(23)</t>
-  </si>
-  <si>
-    <t>(24)</t>
-  </si>
-  <si>
-    <t>(25)</t>
-  </si>
-  <si>
-    <t>(26)</t>
-  </si>
-  <si>
-    <t>(27)</t>
-  </si>
-  <si>
-    <t>(28)</t>
-  </si>
-  <si>
-    <t>(29)</t>
-  </si>
-  <si>
-    <t>(30)</t>
-  </si>
-  <si>
-    <t>(31)</t>
-  </si>
-  <si>
-    <t>(32)</t>
-  </si>
-  <si>
-    <t>(33)</t>
-  </si>
-  <si>
-    <t>(34)</t>
-  </si>
-  <si>
-    <t>(35)</t>
-  </si>
-  <si>
-    <t>(36)</t>
-  </si>
-  <si>
-    <t>(37)</t>
-  </si>
-  <si>
-    <t>0,14</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>0,01</t>
-  </si>
-  <si>
-    <t>10,92</t>
-  </si>
-  <si>
-    <t>16,71</t>
-  </si>
-  <si>
-    <t>7,53</t>
-  </si>
-  <si>
-    <t>42,78</t>
-  </si>
-  <si>
-    <t>14,55</t>
-  </si>
-  <si>
-    <t>6,07</t>
-  </si>
-  <si>
-    <t>25,62</t>
-  </si>
-  <si>
-    <t>0,19</t>
-  </si>
-  <si>
-    <t>0,03</t>
-  </si>
-  <si>
-    <t>16,49</t>
-  </si>
-  <si>
-    <t>16,53</t>
-  </si>
-  <si>
-    <t>12,59</t>
-  </si>
-  <si>
-    <t>41,65</t>
-  </si>
-  <si>
-    <t>17,21</t>
-  </si>
-  <si>
-    <t>1,48</t>
-  </si>
-  <si>
-    <t>33,9</t>
-  </si>
-  <si>
-    <t>0,09</t>
-  </si>
-  <si>
-    <t>0,02</t>
-  </si>
-  <si>
-    <t>0,05</t>
-  </si>
-  <si>
-    <t>8,38</t>
-  </si>
-  <si>
-    <t>21,34</t>
-  </si>
-  <si>
-    <t>14,9</t>
-  </si>
-  <si>
-    <t>25,96</t>
-  </si>
-  <si>
-    <t>9,03</t>
-  </si>
-  <si>
-    <t>9,86</t>
-  </si>
-  <si>
-    <t>17,5</t>
-  </si>
-  <si>
-    <t>0,13</t>
-  </si>
-  <si>
     <t>11,03</t>
   </si>
   <si>
@@ -995,7 +995,10 @@
     <t>10,35</t>
   </si>
   <si>
-    <t>25,54</t>
+    <t>25,79</t>
+  </si>
+  <si>
+    <t>25,87</t>
   </si>
   <si>
     <t>126,09</t>
@@ -1004,7 +1007,10 @@
     <t>39,07</t>
   </si>
   <si>
-    <t>33,54</t>
+    <t>33,65</t>
+  </si>
+  <si>
+    <t>34,01</t>
   </si>
   <si>
     <t>51,33</t>
@@ -1013,7 +1019,10 @@
     <t>15,58</t>
   </si>
   <si>
-    <t>17,33</t>
+    <t>17,45</t>
+  </si>
+  <si>
+    <t>17,62</t>
   </si>
   <si>
     <t>103,42</t>
@@ -1022,7 +1031,10 @@
     <t>8,31</t>
   </si>
   <si>
-    <t>19,08</t>
+    <t>19,29</t>
+  </si>
+  <si>
+    <t>19,41</t>
   </si>
   <si>
     <t>121,52</t>
@@ -1031,7 +1043,10 @@
     <t>19,85</t>
   </si>
   <si>
-    <t>22,88</t>
+    <t>23,1</t>
+  </si>
+  <si>
+    <t>23,3</t>
   </si>
   <si>
     <t>104,32</t>
@@ -1040,672 +1055,708 @@
     <t>14,64</t>
   </si>
   <si>
+    <t>26,21</t>
+  </si>
+  <si>
+    <t>26,33</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>15,98</t>
+  </si>
+  <si>
+    <t>18,61</t>
+  </si>
+  <si>
+    <t>18,73</t>
+  </si>
+  <si>
+    <t>125,71</t>
+  </si>
+  <si>
+    <t>11,63</t>
+  </si>
+  <si>
+    <t>18,15</t>
+  </si>
+  <si>
+    <t>18,35</t>
+  </si>
+  <si>
+    <t>94,12</t>
+  </si>
+  <si>
+    <t>4,99</t>
+  </si>
+  <si>
+    <t>42,9</t>
+  </si>
+  <si>
+    <t>42,39</t>
+  </si>
+  <si>
+    <t>96,36</t>
+  </si>
+  <si>
+    <t>36,36</t>
+  </si>
+  <si>
+    <t>62,18</t>
+  </si>
+  <si>
+    <t>62,32</t>
+  </si>
+  <si>
+    <t>128,13</t>
+  </si>
+  <si>
+    <t>133,33</t>
+  </si>
+  <si>
+    <t>58,56</t>
+  </si>
+  <si>
+    <t>59,02</t>
+  </si>
+  <si>
+    <t>111,11</t>
+  </si>
+  <si>
+    <t>31,58</t>
+  </si>
+  <si>
+    <t>62,36</t>
+  </si>
+  <si>
+    <t>62,43</t>
+  </si>
+  <si>
+    <t>113,04</t>
+  </si>
+  <si>
+    <t>31,82</t>
+  </si>
+  <si>
+    <t>86,73</t>
+  </si>
+  <si>
+    <t>86,55</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>54,08</t>
+  </si>
+  <si>
+    <t>54,2</t>
+  </si>
+  <si>
+    <t>59,77</t>
+  </si>
+  <si>
+    <t>17,46</t>
+  </si>
+  <si>
+    <t>17,41</t>
+  </si>
+  <si>
+    <t>117,5</t>
+  </si>
+  <si>
+    <t>32,81</t>
+  </si>
+  <si>
+    <t>39,34</t>
+  </si>
+  <si>
+    <t>39,67</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha (UB/UM/UMK)</t>
+  </si>
+  <si>
+    <t>Jumlah prelist usaha yang berhasil didata (keberadaan ditemukan, baru, pindah dapat ditelusuri) berdasarkan skala usaha, untuk usaha baru didekati dengan omzet sebagai berikut: UB (lebih dari 50 Milyar), UM (15-50 Milyar), UMK - Kecil (2-15 Milyar), UMK - Mikro (0-2 Milyar).</t>
+  </si>
+  <si>
+    <t>Tidak Dapat Diklasifikasikan (Kolom 10)</t>
+  </si>
+  <si>
+    <t>Usaha baru dengan nilai omzet/pendapatan kosong sehingga tidak dapat diklasifikasikan skala usahanya, misalnya usaha unit pembantu/penunjang.</t>
+  </si>
+  <si>
+    <t>Persentase Jumlah UB</t>
+  </si>
+  <si>
+    <t>Persentase hasil bagi jumlah UB yang berhasil didata dengan jumlah prelist UB (kolom 3).</t>
+  </si>
+  <si>
+    <t>Persentase Jumlah UM</t>
+  </si>
+  <si>
+    <t>Persentase hasil bagi jumlah UM yang berhasil didata dengan jumlah prelist UM (kolom 4).</t>
+  </si>
+  <si>
+    <t>Persentase Jumlah UMK</t>
+  </si>
+  <si>
+    <t>Persentase hasil bagi jumlah UMK yang berhasil didata dengan jumlah prelist UMK (kolom 5).</t>
+  </si>
+  <si>
+    <t>Akumulasi umlah UB, UM, UMK, dan usaha tanpa klasifikasi skala usaha yang berhasil didata.</t>
+  </si>
+  <si>
+    <t>PROGRES PENDATAAN - USAHA KELUARGA</t>
+  </si>
+  <si>
+    <t>Jumlah Prelist Usaha Keluarga (ST2023 + UMKM)</t>
+  </si>
+  <si>
+    <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha dalam Keluarga (Ditemukan + Baru)</t>
+  </si>
+  <si>
+    <t>Persentase Usaha dalam Keluarga (Ditemukan + Baru)</t>
+  </si>
+  <si>
+    <t>46,61</t>
+  </si>
+  <si>
+    <t>22,84</t>
+  </si>
+  <si>
+    <t>0,36</t>
+  </si>
+  <si>
+    <t>9,38</t>
+  </si>
+  <si>
+    <t>32,6</t>
+  </si>
+  <si>
+    <t>79,21</t>
+  </si>
+  <si>
+    <t>57,99</t>
+  </si>
+  <si>
+    <t>19,56</t>
+  </si>
+  <si>
+    <t>0,5</t>
+  </si>
+  <si>
+    <t>9,19</t>
+  </si>
+  <si>
+    <t>29,68</t>
+  </si>
+  <si>
+    <t>87,67</t>
+  </si>
+  <si>
+    <t>43,38</t>
+  </si>
+  <si>
+    <t>23,78</t>
+  </si>
+  <si>
+    <t>0,43</t>
+  </si>
+  <si>
+    <t>7,82</t>
+  </si>
+  <si>
+    <t>32,86</t>
+  </si>
+  <si>
+    <t>76,24</t>
+  </si>
+  <si>
+    <t>35,43</t>
+  </si>
+  <si>
+    <t>21,86</t>
+  </si>
+  <si>
+    <t>0,18</t>
+  </si>
+  <si>
+    <t>14,3</t>
+  </si>
+  <si>
+    <t>30,34</t>
+  </si>
+  <si>
+    <t>65,77</t>
+  </si>
+  <si>
+    <t>47,76</t>
+  </si>
+  <si>
+    <t>21,56</t>
+  </si>
+  <si>
+    <t>8,27</t>
+  </si>
+  <si>
+    <t>34,66</t>
+  </si>
+  <si>
+    <t>82,42</t>
+  </si>
+  <si>
+    <t>47,99</t>
+  </si>
+  <si>
+    <t>20,62</t>
+  </si>
+  <si>
+    <t>10,49</t>
+  </si>
+  <si>
+    <t>31,23</t>
+  </si>
+  <si>
+    <t>79,23</t>
+  </si>
+  <si>
+    <t>46,31</t>
+  </si>
+  <si>
+    <t>0,21</t>
+  </si>
+  <si>
+    <t>16,85</t>
+  </si>
+  <si>
+    <t>36,47</t>
+  </si>
+  <si>
+    <t>82,78</t>
+  </si>
+  <si>
+    <t>45,43</t>
+  </si>
+  <si>
+    <t>20,68</t>
+  </si>
+  <si>
+    <t>8,39</t>
+  </si>
+  <si>
+    <t>36,53</t>
+  </si>
+  <si>
+    <t>81,96</t>
+  </si>
+  <si>
+    <t>41,04</t>
+  </si>
+  <si>
+    <t>24,82</t>
+  </si>
+  <si>
+    <t>0,45</t>
+  </si>
+  <si>
+    <t>4,75</t>
+  </si>
+  <si>
+    <t>26,08</t>
+  </si>
+  <si>
+    <t>67,12</t>
+  </si>
+  <si>
+    <t>50,82</t>
+  </si>
+  <si>
+    <t>26,83</t>
+  </si>
+  <si>
+    <t>0,7</t>
+  </si>
+  <si>
+    <t>6,84</t>
+  </si>
+  <si>
+    <t>22,81</t>
+  </si>
+  <si>
+    <t>73,63</t>
+  </si>
+  <si>
+    <t>45,76</t>
+  </si>
+  <si>
+    <t>28,12</t>
+  </si>
+  <si>
+    <t>0,55</t>
+  </si>
+  <si>
+    <t>5,84</t>
+  </si>
+  <si>
+    <t>71,72</t>
+  </si>
+  <si>
+    <t>46,55</t>
+  </si>
+  <si>
+    <t>29,37</t>
+  </si>
+  <si>
+    <t>0,69</t>
+  </si>
+  <si>
+    <t>12,26</t>
+  </si>
+  <si>
+    <t>27,84</t>
+  </si>
+  <si>
+    <t>74,39</t>
+  </si>
+  <si>
+    <t>56,09</t>
+  </si>
+  <si>
+    <t>23,43</t>
+  </si>
+  <si>
+    <t>0,54</t>
+  </si>
+  <si>
+    <t>7,58</t>
+  </si>
+  <si>
+    <t>31,52</t>
+  </si>
+  <si>
+    <t>87,6</t>
+  </si>
+  <si>
+    <t>53,52</t>
+  </si>
+  <si>
+    <t>28,97</t>
+  </si>
+  <si>
+    <t>4,81</t>
+  </si>
+  <si>
+    <t>26,15</t>
+  </si>
+  <si>
+    <t>79,67</t>
+  </si>
+  <si>
+    <t>22,35</t>
+  </si>
+  <si>
+    <t>28,01</t>
+  </si>
+  <si>
+    <t>0,75</t>
+  </si>
+  <si>
+    <t>14,26</t>
+  </si>
+  <si>
+    <t>300,86</t>
+  </si>
+  <si>
+    <t>323,21</t>
+  </si>
+  <si>
+    <t>43,79</t>
+  </si>
+  <si>
+    <t>26,97</t>
+  </si>
+  <si>
+    <t>2,27</t>
+  </si>
+  <si>
+    <t>3,09</t>
+  </si>
+  <si>
+    <t>35,29</t>
+  </si>
+  <si>
+    <t>79,08</t>
+  </si>
+  <si>
+    <t>Persentase Kolom 4 9</t>
+  </si>
+  <si>
+    <t>PROGRES PENDATAAN - KESELURUHAN USAHA</t>
+  </si>
+  <si>
+    <t>Total Prelist Usaha dan Usaha Keluarga</t>
+  </si>
+  <si>
+    <t>USAHA BKU CAWI/UB &amp; CAPI</t>
+  </si>
+  <si>
+    <t>USAHA DALAM KELUARGA</t>
+  </si>
+  <si>
+    <t>Subtotal</t>
+  </si>
+  <si>
+    <t>Persentase Subtotal</t>
+  </si>
+  <si>
+    <t>Ditemukan​</t>
+  </si>
+  <si>
+    <t>Persentase Ditemukan​</t>
+  </si>
+  <si>
+    <t>Baru​</t>
+  </si>
+  <si>
+    <t>Persentase Baru​</t>
+  </si>
+  <si>
+    <t>Subtotal​</t>
+  </si>
+  <si>
+    <t>Persentase Subtotal​</t>
+  </si>
+  <si>
+    <t>11,07</t>
+  </si>
+  <si>
+    <t>65,23</t>
+  </si>
+  <si>
+    <t>16,68</t>
+  </si>
+  <si>
+    <t>82,11</t>
+  </si>
+  <si>
+    <t>8,47</t>
+  </si>
+  <si>
+    <t>61,52</t>
+  </si>
+  <si>
+    <t>5,76</t>
+  </si>
+  <si>
+    <t>51,03</t>
+  </si>
+  <si>
+    <t>11,08</t>
+  </si>
+  <si>
+    <t>66,52</t>
+  </si>
+  <si>
+    <t>10,32</t>
+  </si>
+  <si>
+    <t>66,47</t>
+  </si>
+  <si>
+    <t>7,11</t>
+  </si>
+  <si>
+    <t>61,43</t>
+  </si>
+  <si>
+    <t>5,57</t>
+  </si>
+  <si>
+    <t>66,45</t>
+  </si>
+  <si>
+    <t>18,91</t>
+  </si>
+  <si>
+    <t>63,43</t>
+  </si>
+  <si>
+    <t>29,96</t>
+  </si>
+  <si>
+    <t>72,38</t>
+  </si>
+  <si>
+    <t>32,92</t>
+  </si>
+  <si>
+    <t>69,65</t>
+  </si>
+  <si>
+    <t>27,91</t>
+  </si>
+  <si>
+    <t>72,91</t>
+  </si>
+  <si>
+    <t>42,34</t>
+  </si>
+  <si>
+    <t>87,41</t>
+  </si>
+  <si>
+    <t>22,1</t>
+  </si>
+  <si>
+    <t>77,22</t>
+  </si>
+  <si>
+    <t>6,77</t>
+  </si>
+  <si>
+    <t>44,04</t>
+  </si>
+  <si>
+    <t>21,49</t>
+  </si>
+  <si>
+    <t>62,51</t>
+  </si>
+  <si>
+    <t>Total Prelist Usaha Dan Usaha Keluarga</t>
+  </si>
+  <si>
+    <t>Jumlah Prelist Usaha Ditambah Jumlah Prelist Usaha Keluarga (ST2023 + UMKM) atau Kolom (3) + (4).</t>
+  </si>
+  <si>
+    <t>Persentase Usaha BKU Ditemukan</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha BKU Ditemukan/Pindah Dapat Ditelusuri (CAPI dan CAWI) dibagi dengan Jumlah Prelist Usaha (kolom 3).</t>
+  </si>
+  <si>
+    <t>Persentase Usaha BKU Baru</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha BKU Baru (CAPI) dibagi Jumlah Prelist Usaha (kolom 3).</t>
+  </si>
+  <si>
+    <t>Persentase Usaha Keluarga Ditemukan</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha Keluarga Ditemukan dibagi dengan Jumlah Prelist Usaha Keluarga (ST2023 + UMKM) atau Kolom (4).</t>
+  </si>
+  <si>
+    <t>Persentase Usaha Keluarga Baru</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha Keluarga Baru dibagi dengan Jumlah Prelist Usaha Keluarga (ST2023 + UMKM) atau Kolom (4).</t>
+  </si>
+  <si>
+    <t>PROGRES PENDATAAN - PROPORSI USAHA</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha (Semua Status Keberadaan Usaha)</t>
+  </si>
+  <si>
+    <t>Persentase Usaha BKU</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha dalam Keluarga</t>
+  </si>
+  <si>
+    <t>Persentase Usaha dalam Keluarga</t>
+  </si>
+  <si>
+    <t>6,26</t>
+  </si>
+  <si>
+    <t>54,81</t>
+  </si>
+  <si>
+    <t>3,03</t>
+  </si>
+  <si>
+    <t>67,97</t>
+  </si>
+  <si>
+    <t>56,5</t>
+  </si>
+  <si>
+    <t>6,09</t>
+  </si>
+  <si>
+    <t>45,04</t>
+  </si>
+  <si>
+    <t>5,89</t>
+  </si>
+  <si>
+    <t>57,4</t>
+  </si>
+  <si>
+    <t>5,8</t>
+  </si>
+  <si>
+    <t>56,07</t>
+  </si>
+  <si>
+    <t>5,55</t>
+  </si>
+  <si>
+    <t>49,7</t>
+  </si>
+  <si>
+    <t>4,17</t>
+  </si>
+  <si>
+    <t>58,61</t>
+  </si>
+  <si>
+    <t>6,25</t>
+  </si>
+  <si>
+    <t>58,82</t>
+  </si>
+  <si>
+    <t>60,39</t>
+  </si>
+  <si>
+    <t>8,76</t>
+  </si>
+  <si>
+    <t>57,06</t>
+  </si>
+  <si>
+    <t>6,4</t>
+  </si>
+  <si>
+    <t>55,78</t>
+  </si>
+  <si>
+    <t>6,33</t>
+  </si>
+  <si>
+    <t>66,5</t>
+  </si>
+  <si>
+    <t>4,48</t>
+  </si>
+  <si>
+    <t>63,07</t>
+  </si>
+  <si>
+    <t>14,39</t>
+  </si>
+  <si>
     <t>25,88</t>
   </si>
   <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>15,98</t>
-  </si>
-  <si>
-    <t>18,44</t>
-  </si>
-  <si>
-    <t>125,71</t>
-  </si>
-  <si>
-    <t>11,63</t>
-  </si>
-  <si>
-    <t>17,95</t>
-  </si>
-  <si>
-    <t>94,12</t>
-  </si>
-  <si>
-    <t>4,99</t>
-  </si>
-  <si>
-    <t>42,28</t>
-  </si>
-  <si>
-    <t>96,36</t>
-  </si>
-  <si>
-    <t>36,36</t>
-  </si>
-  <si>
-    <t>61,73</t>
-  </si>
-  <si>
-    <t>128,13</t>
-  </si>
-  <si>
-    <t>133,33</t>
-  </si>
-  <si>
-    <t>58,16</t>
-  </si>
-  <si>
-    <t>111,11</t>
-  </si>
-  <si>
-    <t>31,58</t>
-  </si>
-  <si>
-    <t>62,05</t>
-  </si>
-  <si>
-    <t>113,04</t>
-  </si>
-  <si>
-    <t>31,82</t>
-  </si>
-  <si>
-    <t>85,54</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>53,76</t>
-  </si>
-  <si>
-    <t>59,77</t>
-  </si>
-  <si>
-    <t>17,29</t>
-  </si>
-  <si>
-    <t>117,5</t>
-  </si>
-  <si>
-    <t>32,81</t>
-  </si>
-  <si>
-    <t>38,98</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha (UB/UM/UMK)</t>
-  </si>
-  <si>
-    <t>Jumlah prelist usaha yang berhasil didata (keberadaan ditemukan, baru, pindah dapat ditelusuri) berdasarkan skala usaha, untuk usaha baru didekati dengan omzet sebagai berikut: UB (lebih dari 50 Milyar), UM (15-50 Milyar), UMK - Kecil (2-15 Milyar), UMK - Mikro (0-2 Milyar).</t>
-  </si>
-  <si>
-    <t>Tidak Dapat Diklasifikasikan (Kolom 10)</t>
-  </si>
-  <si>
-    <t>Usaha baru dengan nilai omzet/pendapatan kosong sehingga tidak dapat diklasifikasikan skala usahanya, misalnya usaha unit pembantu/penunjang.</t>
-  </si>
-  <si>
-    <t>Persentase Jumlah UB</t>
-  </si>
-  <si>
-    <t>Persentase hasil bagi jumlah UB yang berhasil didata dengan jumlah prelist UB (kolom 3).</t>
-  </si>
-  <si>
-    <t>Persentase Jumlah UM</t>
-  </si>
-  <si>
-    <t>Persentase hasil bagi jumlah UM yang berhasil didata dengan jumlah prelist UM (kolom 4).</t>
-  </si>
-  <si>
-    <t>Persentase Jumlah UMK</t>
-  </si>
-  <si>
-    <t>Persentase hasil bagi jumlah UMK yang berhasil didata dengan jumlah prelist UMK (kolom 5).</t>
-  </si>
-  <si>
-    <t>Akumulasi umlah UB, UM, UMK, dan usaha tanpa klasifikasi skala usaha yang berhasil didata.</t>
-  </si>
-  <si>
-    <t>PROGRES PENDATAAN - USAHA KELUARGA</t>
-  </si>
-  <si>
-    <t>Jumlah Prelist Usaha Keluarga (ST2023 + UMKM)</t>
-  </si>
-  <si>
-    <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha dalam Keluarga (Ditemukan + Baru)</t>
-  </si>
-  <si>
-    <t>Persentase Usaha dalam Keluarga (Ditemukan + Baru)</t>
-  </si>
-  <si>
-    <t>46,61</t>
-  </si>
-  <si>
-    <t>22,84</t>
-  </si>
-  <si>
-    <t>0,36</t>
-  </si>
-  <si>
-    <t>9,38</t>
-  </si>
-  <si>
-    <t>32,6</t>
-  </si>
-  <si>
-    <t>79,21</t>
-  </si>
-  <si>
-    <t>57,99</t>
-  </si>
-  <si>
-    <t>19,56</t>
-  </si>
-  <si>
-    <t>0,5</t>
-  </si>
-  <si>
-    <t>9,19</t>
-  </si>
-  <si>
-    <t>29,68</t>
-  </si>
-  <si>
-    <t>87,67</t>
-  </si>
-  <si>
-    <t>43,38</t>
-  </si>
-  <si>
-    <t>23,78</t>
-  </si>
-  <si>
-    <t>0,43</t>
-  </si>
-  <si>
-    <t>7,82</t>
-  </si>
-  <si>
-    <t>32,86</t>
-  </si>
-  <si>
-    <t>76,24</t>
-  </si>
-  <si>
-    <t>35,43</t>
-  </si>
-  <si>
-    <t>21,86</t>
-  </si>
-  <si>
-    <t>0,18</t>
-  </si>
-  <si>
-    <t>14,3</t>
-  </si>
-  <si>
-    <t>30,34</t>
-  </si>
-  <si>
-    <t>65,77</t>
-  </si>
-  <si>
-    <t>47,76</t>
-  </si>
-  <si>
-    <t>21,56</t>
-  </si>
-  <si>
-    <t>8,27</t>
-  </si>
-  <si>
-    <t>34,66</t>
-  </si>
-  <si>
-    <t>82,42</t>
-  </si>
-  <si>
-    <t>47,99</t>
-  </si>
-  <si>
-    <t>20,62</t>
-  </si>
-  <si>
-    <t>10,49</t>
-  </si>
-  <si>
-    <t>31,23</t>
-  </si>
-  <si>
-    <t>79,23</t>
-  </si>
-  <si>
-    <t>46,31</t>
-  </si>
-  <si>
-    <t>0,21</t>
-  </si>
-  <si>
-    <t>16,85</t>
-  </si>
-  <si>
-    <t>36,47</t>
-  </si>
-  <si>
-    <t>82,78</t>
-  </si>
-  <si>
-    <t>45,43</t>
-  </si>
-  <si>
-    <t>20,68</t>
-  </si>
-  <si>
-    <t>8,39</t>
-  </si>
-  <si>
-    <t>36,53</t>
-  </si>
-  <si>
-    <t>81,96</t>
-  </si>
-  <si>
-    <t>41,04</t>
-  </si>
-  <si>
-    <t>24,82</t>
-  </si>
-  <si>
-    <t>0,45</t>
-  </si>
-  <si>
-    <t>4,75</t>
-  </si>
-  <si>
-    <t>26,08</t>
-  </si>
-  <si>
-    <t>67,12</t>
-  </si>
-  <si>
-    <t>50,82</t>
-  </si>
-  <si>
-    <t>26,83</t>
-  </si>
-  <si>
-    <t>0,7</t>
-  </si>
-  <si>
-    <t>6,84</t>
-  </si>
-  <si>
-    <t>22,81</t>
-  </si>
-  <si>
-    <t>73,63</t>
-  </si>
-  <si>
-    <t>45,76</t>
-  </si>
-  <si>
-    <t>28,12</t>
-  </si>
-  <si>
-    <t>0,55</t>
-  </si>
-  <si>
-    <t>5,84</t>
-  </si>
-  <si>
-    <t>71,72</t>
-  </si>
-  <si>
-    <t>46,55</t>
-  </si>
-  <si>
-    <t>29,37</t>
-  </si>
-  <si>
-    <t>0,69</t>
-  </si>
-  <si>
-    <t>12,26</t>
-  </si>
-  <si>
-    <t>27,84</t>
-  </si>
-  <si>
-    <t>74,39</t>
-  </si>
-  <si>
-    <t>56,09</t>
-  </si>
-  <si>
-    <t>23,43</t>
-  </si>
-  <si>
-    <t>0,54</t>
-  </si>
-  <si>
-    <t>7,58</t>
-  </si>
-  <si>
-    <t>31,52</t>
-  </si>
-  <si>
-    <t>87,6</t>
-  </si>
-  <si>
-    <t>53,52</t>
-  </si>
-  <si>
-    <t>28,97</t>
-  </si>
-  <si>
-    <t>4,81</t>
-  </si>
-  <si>
-    <t>26,15</t>
-  </si>
-  <si>
-    <t>79,67</t>
-  </si>
-  <si>
-    <t>22,35</t>
-  </si>
-  <si>
-    <t>28,01</t>
-  </si>
-  <si>
-    <t>0,75</t>
-  </si>
-  <si>
-    <t>14,26</t>
-  </si>
-  <si>
-    <t>300,86</t>
-  </si>
-  <si>
-    <t>323,21</t>
-  </si>
-  <si>
-    <t>43,79</t>
-  </si>
-  <si>
-    <t>26,97</t>
-  </si>
-  <si>
-    <t>2,27</t>
-  </si>
-  <si>
-    <t>3,09</t>
-  </si>
-  <si>
-    <t>35,29</t>
-  </si>
-  <si>
-    <t>79,08</t>
-  </si>
-  <si>
-    <t>Persentase Kolom 4 9</t>
-  </si>
-  <si>
-    <t>PROGRES PENDATAAN - KESELURUHAN USAHA</t>
-  </si>
-  <si>
-    <t>Total Prelist Usaha dan Usaha Keluarga</t>
-  </si>
-  <si>
-    <t>USAHA BKU CAWI/UB &amp; CAPI</t>
-  </si>
-  <si>
-    <t>USAHA DALAM KELUARGA</t>
-  </si>
-  <si>
-    <t>Subtotal</t>
-  </si>
-  <si>
-    <t>Persentase Subtotal</t>
-  </si>
-  <si>
-    <t>Ditemukan​</t>
-  </si>
-  <si>
-    <t>Persentase Ditemukan​</t>
-  </si>
-  <si>
-    <t>Baru​</t>
-  </si>
-  <si>
-    <t>Persentase Baru​</t>
-  </si>
-  <si>
-    <t>Subtotal​</t>
-  </si>
-  <si>
-    <t>Persentase Subtotal​</t>
-  </si>
-  <si>
-    <t>11,07</t>
-  </si>
-  <si>
-    <t>65,23</t>
-  </si>
-  <si>
-    <t>16,68</t>
-  </si>
-  <si>
-    <t>82,11</t>
-  </si>
-  <si>
-    <t>8,47</t>
-  </si>
-  <si>
-    <t>61,52</t>
-  </si>
-  <si>
-    <t>5,76</t>
-  </si>
-  <si>
-    <t>51,03</t>
-  </si>
-  <si>
-    <t>11,08</t>
-  </si>
-  <si>
-    <t>66,52</t>
-  </si>
-  <si>
-    <t>10,32</t>
-  </si>
-  <si>
-    <t>66,47</t>
-  </si>
-  <si>
-    <t>7,11</t>
-  </si>
-  <si>
-    <t>61,43</t>
-  </si>
-  <si>
-    <t>5,57</t>
-  </si>
-  <si>
-    <t>66,45</t>
-  </si>
-  <si>
-    <t>18,91</t>
-  </si>
-  <si>
-    <t>63,43</t>
-  </si>
-  <si>
-    <t>29,96</t>
-  </si>
-  <si>
-    <t>72,38</t>
-  </si>
-  <si>
-    <t>32,92</t>
-  </si>
-  <si>
-    <t>69,65</t>
-  </si>
-  <si>
-    <t>27,91</t>
-  </si>
-  <si>
-    <t>72,91</t>
-  </si>
-  <si>
-    <t>42,34</t>
-  </si>
-  <si>
-    <t>87,41</t>
-  </si>
-  <si>
-    <t>22,1</t>
-  </si>
-  <si>
-    <t>77,22</t>
-  </si>
-  <si>
-    <t>6,77</t>
-  </si>
-  <si>
-    <t>44,04</t>
-  </si>
-  <si>
-    <t>21,49</t>
-  </si>
-  <si>
-    <t>62,51</t>
-  </si>
-  <si>
-    <t>Total Prelist Usaha Dan Usaha Keluarga</t>
-  </si>
-  <si>
-    <t>Jumlah Prelist Usaha Ditambah Jumlah Prelist Usaha Keluarga (ST2023 + UMKM) atau Kolom (3) + (4).</t>
-  </si>
-  <si>
-    <t>Persentase Usaha BKU Ditemukan</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha BKU Ditemukan/Pindah Dapat Ditelusuri (CAPI dan CAWI) dibagi dengan Jumlah Prelist Usaha (kolom 3).</t>
-  </si>
-  <si>
-    <t>Persentase Usaha BKU Baru</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha BKU Baru (CAPI) dibagi Jumlah Prelist Usaha (kolom 3).</t>
-  </si>
-  <si>
-    <t>Persentase Usaha Keluarga Ditemukan</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha Keluarga Ditemukan dibagi dengan Jumlah Prelist Usaha Keluarga (ST2023 + UMKM) atau Kolom (4).</t>
-  </si>
-  <si>
-    <t>Persentase Usaha Keluarga Baru</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha Keluarga Baru dibagi dengan Jumlah Prelist Usaha Keluarga (ST2023 + UMKM) atau Kolom (4).</t>
-  </si>
-  <si>
-    <t>PROGRES PENDATAAN - PROPORSI USAHA</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha (Semua Status Keberadaan Usaha)</t>
-  </si>
-  <si>
-    <t>Persentase Usaha BKU</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha dalam Keluarga</t>
-  </si>
-  <si>
-    <t>Persentase Usaha dalam Keluarga</t>
-  </si>
-  <si>
-    <t>6,26</t>
-  </si>
-  <si>
-    <t>54,81</t>
-  </si>
-  <si>
-    <t>3,03</t>
-  </si>
-  <si>
-    <t>67,97</t>
-  </si>
-  <si>
-    <t>56,5</t>
-  </si>
-  <si>
-    <t>6,09</t>
-  </si>
-  <si>
-    <t>45,04</t>
-  </si>
-  <si>
-    <t>5,89</t>
-  </si>
-  <si>
-    <t>57,4</t>
-  </si>
-  <si>
-    <t>5,8</t>
-  </si>
-  <si>
-    <t>56,07</t>
-  </si>
-  <si>
-    <t>5,55</t>
-  </si>
-  <si>
-    <t>49,7</t>
-  </si>
-  <si>
-    <t>4,17</t>
-  </si>
-  <si>
-    <t>58,61</t>
-  </si>
-  <si>
-    <t>6,25</t>
-  </si>
-  <si>
-    <t>58,82</t>
-  </si>
-  <si>
-    <t>60,39</t>
-  </si>
-  <si>
-    <t>8,76</t>
-  </si>
-  <si>
-    <t>57,06</t>
-  </si>
-  <si>
-    <t>6,4</t>
-  </si>
-  <si>
-    <t>55,78</t>
-  </si>
-  <si>
-    <t>6,33</t>
-  </si>
-  <si>
-    <t>66,5</t>
-  </si>
-  <si>
-    <t>4,48</t>
-  </si>
-  <si>
-    <t>63,07</t>
-  </si>
-  <si>
-    <t>14,39</t>
-  </si>
-  <si>
     <t>15,56</t>
   </si>
   <si>
@@ -1799,13 +1850,16 @@
     <t>Non Pertanian​​​</t>
   </si>
   <si>
-    <t>0,76</t>
-  </si>
-  <si>
-    <t>2,38</t>
-  </si>
-  <si>
-    <t>24,48</t>
+    <t>0,77</t>
+  </si>
+  <si>
+    <t>2,41</t>
+  </si>
+  <si>
+    <t>55,17</t>
+  </si>
+  <si>
+    <t>24,62</t>
   </si>
   <si>
     <t>0,47</t>
@@ -1814,151 +1868,145 @@
     <t>3,22</t>
   </si>
   <si>
-    <t>56,97</t>
-  </si>
-  <si>
-    <t>25,82</t>
+    <t>57,15</t>
+  </si>
+  <si>
+    <t>25,91</t>
   </si>
   <si>
     <t>1,21</t>
   </si>
   <si>
+    <t>3,38</t>
+  </si>
+  <si>
+    <t>56,9</t>
+  </si>
+  <si>
+    <t>25,16</t>
+  </si>
+  <si>
+    <t>1,08</t>
+  </si>
+  <si>
+    <t>53,86</t>
+  </si>
+  <si>
+    <t>22,57</t>
+  </si>
+  <si>
+    <t>1,14</t>
+  </si>
+  <si>
+    <t>1,35</t>
+  </si>
+  <si>
+    <t>57,98</t>
+  </si>
+  <si>
+    <t>25,76</t>
+  </si>
+  <si>
+    <t>1,16</t>
+  </si>
+  <si>
+    <t>1,97</t>
+  </si>
+  <si>
+    <t>60,85</t>
+  </si>
+  <si>
+    <t>26,09</t>
+  </si>
+  <si>
+    <t>1,02</t>
+  </si>
+  <si>
+    <t>1,66</t>
+  </si>
+  <si>
+    <t>56,22</t>
+  </si>
+  <si>
+    <t>26,25</t>
+  </si>
+  <si>
+    <t>0,83</t>
+  </si>
+  <si>
+    <t>4,37</t>
+  </si>
+  <si>
+    <t>55,56</t>
+  </si>
+  <si>
+    <t>29,39</t>
+  </si>
+  <si>
     <t>3,35</t>
   </si>
   <si>
-    <t>56,6</t>
-  </si>
-  <si>
-    <t>25,05</t>
-  </si>
-  <si>
-    <t>1,07</t>
-  </si>
-  <si>
-    <t>6,02</t>
-  </si>
-  <si>
-    <t>53,51</t>
-  </si>
-  <si>
-    <t>22,46</t>
-  </si>
-  <si>
-    <t>1,13</t>
-  </si>
-  <si>
-    <t>1,33</t>
-  </si>
-  <si>
-    <t>57,6</t>
-  </si>
-  <si>
-    <t>25,6</t>
-  </si>
-  <si>
-    <t>1,16</t>
-  </si>
-  <si>
-    <t>1,93</t>
-  </si>
-  <si>
-    <t>60,37</t>
-  </si>
-  <si>
-    <t>25,9</t>
-  </si>
-  <si>
-    <t>1,01</t>
-  </si>
-  <si>
-    <t>1,64</t>
-  </si>
-  <si>
-    <t>55,74</t>
-  </si>
-  <si>
-    <t>0,83</t>
-  </si>
-  <si>
-    <t>4,36</t>
-  </si>
-  <si>
-    <t>55,13</t>
-  </si>
-  <si>
-    <t>29,2</t>
-  </si>
-  <si>
-    <t>3,31</t>
-  </si>
-  <si>
-    <t>50,8</t>
-  </si>
-  <si>
-    <t>27,58</t>
+    <t>51,4</t>
+  </si>
+  <si>
+    <t>27,85</t>
   </si>
   <si>
     <t>0,53</t>
   </si>
   <si>
-    <t>1,52</t>
-  </si>
-  <si>
-    <t>55,58</t>
-  </si>
-  <si>
-    <t>19,71</t>
-  </si>
-  <si>
-    <t>49,11</t>
-  </si>
-  <si>
-    <t>20,57</t>
-  </si>
-  <si>
-    <t>0,52</t>
-  </si>
-  <si>
-    <t>54,37</t>
-  </si>
-  <si>
-    <t>27,43</t>
-  </si>
-  <si>
-    <t>55,68</t>
-  </si>
-  <si>
-    <t>27,31</t>
+    <t>1,56</t>
+  </si>
+  <si>
+    <t>55,89</t>
+  </si>
+  <si>
+    <t>19,78</t>
+  </si>
+  <si>
+    <t>49,41</t>
+  </si>
+  <si>
+    <t>20,71</t>
+  </si>
+  <si>
+    <t>6,98</t>
+  </si>
+  <si>
+    <t>54,53</t>
+  </si>
+  <si>
+    <t>27,51</t>
+  </si>
+  <si>
+    <t>55,99</t>
+  </si>
+  <si>
+    <t>27,41</t>
   </si>
   <si>
     <t>0,34</t>
   </si>
   <si>
-    <t>2,17</t>
-  </si>
-  <si>
-    <t>56,87</t>
-  </si>
-  <si>
-    <t>23,87</t>
-  </si>
-  <si>
-    <t>0,2</t>
-  </si>
-  <si>
-    <t>6,55</t>
-  </si>
-  <si>
-    <t>2,46</t>
+    <t>2,21</t>
+  </si>
+  <si>
+    <t>23,93</t>
+  </si>
+  <si>
+    <t>6,62</t>
+  </si>
+  <si>
+    <t>2,48</t>
   </si>
   <si>
     <t>0,39</t>
   </si>
   <si>
-    <t>27,94</t>
-  </si>
-  <si>
-    <t>10,74</t>
+    <t>28,15</t>
+  </si>
+  <si>
+    <t>10,83</t>
   </si>
   <si>
     <t>Persentase Usaha BKU Ditemukan Pertanian</t>
@@ -2623,7 +2671,7 @@
         <v>3491483</v>
       </c>
       <c r="D7" s="6">
-        <v>792269</v>
+        <v>794920</v>
       </c>
       <c r="E7" s="6">
         <v>3760912</v>
@@ -2632,13 +2680,13 @@
         <v>25</v>
       </c>
       <c r="G7" s="6">
-        <v>2259770</v>
+        <v>2273483</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>26</v>
       </c>
       <c r="I7" s="6">
-        <v>181028</v>
+        <v>173296</v>
       </c>
       <c r="J7" s="7" t="s">
         <v>27</v>
@@ -2655,7 +2703,7 @@
         <v>97072</v>
       </c>
       <c r="D8" s="9">
-        <v>24778</v>
+        <v>24803</v>
       </c>
       <c r="E8" s="9">
         <v>120429</v>
@@ -2664,13 +2712,13 @@
         <v>30</v>
       </c>
       <c r="G8" s="9">
-        <v>81738</v>
+        <v>81980</v>
       </c>
       <c r="H8" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="9">
-        <v>1720</v>
+        <v>1550</v>
       </c>
       <c r="J8" s="10" t="s">
         <v>32</v>
@@ -2687,7 +2735,7 @@
         <v>230430</v>
       </c>
       <c r="D9" s="9">
-        <v>55806</v>
+        <v>56018</v>
       </c>
       <c r="E9" s="9">
         <v>245254</v>
@@ -2696,13 +2744,13 @@
         <v>35</v>
       </c>
       <c r="G9" s="9">
-        <v>154079</v>
+        <v>154882</v>
       </c>
       <c r="H9" s="10" t="s">
         <v>36</v>
       </c>
       <c r="I9" s="9">
-        <v>16797</v>
+        <v>16367</v>
       </c>
       <c r="J9" s="10" t="s">
         <v>37</v>
@@ -2719,7 +2767,7 @@
         <v>436273</v>
       </c>
       <c r="D10" s="9">
-        <v>116213</v>
+        <v>116498</v>
       </c>
       <c r="E10" s="9">
         <v>454845</v>
@@ -2728,13 +2776,13 @@
         <v>40</v>
       </c>
       <c r="G10" s="9">
-        <v>257176</v>
+        <v>258689</v>
       </c>
       <c r="H10" s="10" t="s">
         <v>41</v>
       </c>
       <c r="I10" s="9">
-        <v>27386</v>
+        <v>26442</v>
       </c>
       <c r="J10" s="10" t="s">
         <v>42</v>
@@ -2751,7 +2799,7 @@
         <v>489942</v>
       </c>
       <c r="D11" s="9">
-        <v>90362</v>
+        <v>90633</v>
       </c>
       <c r="E11" s="9">
         <v>505683</v>
@@ -2760,13 +2808,13 @@
         <v>45</v>
       </c>
       <c r="G11" s="9">
-        <v>308727</v>
+        <v>310486</v>
       </c>
       <c r="H11" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I11" s="9">
-        <v>22505</v>
+        <v>21743</v>
       </c>
       <c r="J11" s="10" t="s">
         <v>47</v>
@@ -2783,7 +2831,7 @@
         <v>580719</v>
       </c>
       <c r="D12" s="9">
-        <v>110551</v>
+        <v>110934</v>
       </c>
       <c r="E12" s="9">
         <v>603941</v>
@@ -2792,13 +2840,13 @@
         <v>50</v>
       </c>
       <c r="G12" s="9">
-        <v>368104</v>
+        <v>370416</v>
       </c>
       <c r="H12" s="10" t="s">
         <v>51</v>
       </c>
       <c r="I12" s="9">
-        <v>32683</v>
+        <v>31468</v>
       </c>
       <c r="J12" s="10" t="s">
         <v>52</v>
@@ -2815,7 +2863,7 @@
         <v>263315</v>
       </c>
       <c r="D13" s="9">
-        <v>52038</v>
+        <v>52302</v>
       </c>
       <c r="E13" s="9">
         <v>292194</v>
@@ -2824,13 +2872,13 @@
         <v>55</v>
       </c>
       <c r="G13" s="9">
-        <v>165515</v>
+        <v>166677</v>
       </c>
       <c r="H13" s="10" t="s">
         <v>56</v>
       </c>
       <c r="I13" s="9">
-        <v>8037</v>
+        <v>7581</v>
       </c>
       <c r="J13" s="10" t="s">
         <v>57</v>
@@ -2847,7 +2895,7 @@
         <v>187422</v>
       </c>
       <c r="D14" s="9">
-        <v>45177</v>
+        <v>45391</v>
       </c>
       <c r="E14" s="9">
         <v>202368</v>
@@ -2856,13 +2904,13 @@
         <v>60</v>
       </c>
       <c r="G14" s="9">
-        <v>120637</v>
+        <v>121335</v>
       </c>
       <c r="H14" s="10" t="s">
         <v>61</v>
       </c>
       <c r="I14" s="9">
-        <v>9885</v>
+        <v>9666</v>
       </c>
       <c r="J14" s="10" t="s">
         <v>62</v>
@@ -2879,7 +2927,7 @@
         <v>154763</v>
       </c>
       <c r="D15" s="9">
-        <v>38473</v>
+        <v>38719</v>
       </c>
       <c r="E15" s="9">
         <v>168457</v>
@@ -2888,13 +2936,13 @@
         <v>65</v>
       </c>
       <c r="G15" s="9">
-        <v>99034</v>
+        <v>100060</v>
       </c>
       <c r="H15" s="10" t="s">
         <v>66</v>
       </c>
       <c r="I15" s="9">
-        <v>9372</v>
+        <v>8845</v>
       </c>
       <c r="J15" s="10" t="s">
         <v>67</v>
@@ -2911,7 +2959,7 @@
         <v>170543</v>
       </c>
       <c r="D16" s="9">
-        <v>44563</v>
+        <v>44709</v>
       </c>
       <c r="E16" s="9">
         <v>203832</v>
@@ -2920,13 +2968,13 @@
         <v>70</v>
       </c>
       <c r="G16" s="9">
-        <v>137659</v>
+        <v>138342</v>
       </c>
       <c r="H16" s="10" t="s">
         <v>71</v>
       </c>
       <c r="I16" s="9">
-        <v>6505</v>
+        <v>6096</v>
       </c>
       <c r="J16" s="10" t="s">
         <v>72</v>
@@ -2943,7 +2991,7 @@
         <v>157837</v>
       </c>
       <c r="D17" s="9">
-        <v>33443</v>
+        <v>33524</v>
       </c>
       <c r="E17" s="9">
         <v>169353</v>
@@ -2952,13 +3000,13 @@
         <v>75</v>
       </c>
       <c r="G17" s="9">
-        <v>119016</v>
+        <v>119682</v>
       </c>
       <c r="H17" s="10" t="s">
         <v>76</v>
       </c>
       <c r="I17" s="9">
-        <v>11334</v>
+        <v>10940</v>
       </c>
       <c r="J17" s="10" t="s">
         <v>77</v>
@@ -2975,7 +3023,7 @@
         <v>86207</v>
       </c>
       <c r="D18" s="9">
-        <v>26648</v>
+        <v>26691</v>
       </c>
       <c r="E18" s="9">
         <v>113757</v>
@@ -2984,13 +3032,13 @@
         <v>80</v>
       </c>
       <c r="G18" s="9">
-        <v>74141</v>
+        <v>74363</v>
       </c>
       <c r="H18" s="10" t="s">
         <v>81</v>
       </c>
       <c r="I18" s="9">
-        <v>831</v>
+        <v>624</v>
       </c>
       <c r="J18" s="10" t="s">
         <v>82</v>
@@ -3007,7 +3055,7 @@
         <v>109078</v>
       </c>
       <c r="D19" s="9">
-        <v>30049</v>
+        <v>30168</v>
       </c>
       <c r="E19" s="9">
         <v>137505</v>
@@ -3016,13 +3064,13 @@
         <v>85</v>
       </c>
       <c r="G19" s="9">
-        <v>92077</v>
+        <v>92522</v>
       </c>
       <c r="H19" s="10" t="s">
         <v>86</v>
       </c>
       <c r="I19" s="9">
-        <v>2357</v>
+        <v>2100</v>
       </c>
       <c r="J19" s="10" t="s">
         <v>87</v>
@@ -3039,7 +3087,7 @@
         <v>47152</v>
       </c>
       <c r="D20" s="9">
-        <v>13968</v>
+        <v>13993</v>
       </c>
       <c r="E20" s="9">
         <v>60890</v>
@@ -3048,13 +3096,13 @@
         <v>90</v>
       </c>
       <c r="G20" s="9">
-        <v>43821</v>
+        <v>43949</v>
       </c>
       <c r="H20" s="10" t="s">
         <v>91</v>
       </c>
       <c r="I20" s="9">
-        <v>459</v>
+        <v>415</v>
       </c>
       <c r="J20" s="10" t="s">
         <v>92</v>
@@ -3071,7 +3119,7 @@
         <v>410237</v>
       </c>
       <c r="D21" s="9">
-        <v>95672</v>
+        <v>95986</v>
       </c>
       <c r="E21" s="9">
         <v>409083</v>
@@ -3080,13 +3128,13 @@
         <v>95</v>
       </c>
       <c r="G21" s="9">
-        <v>193709</v>
+        <v>195477</v>
       </c>
       <c r="H21" s="10" t="s">
         <v>96</v>
       </c>
       <c r="I21" s="9">
-        <v>26425</v>
+        <v>25012</v>
       </c>
       <c r="J21" s="10" t="s">
         <v>97</v>
@@ -3103,7 +3151,7 @@
         <v>70493</v>
       </c>
       <c r="D22" s="9">
-        <v>14528</v>
+        <v>14551</v>
       </c>
       <c r="E22" s="9">
         <v>73321</v>
@@ -3112,30 +3160,30 @@
         <v>100</v>
       </c>
       <c r="G22" s="9">
-        <v>44337</v>
+        <v>44623</v>
       </c>
       <c r="H22" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I22" s="9">
+        <v>4447</v>
+      </c>
+      <c r="J22" s="10" t="s">
         <v>101</v>
-      </c>
-      <c r="I22" s="9">
-        <v>4732</v>
-      </c>
-      <c r="J22" s="10" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B23" s="11" t="s">
         <v>103</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>104</v>
       </c>
       <c r="C23" s="12">
         <v>3491483</v>
       </c>
       <c r="D23" s="12">
-        <v>792269</v>
+        <v>794920</v>
       </c>
       <c r="E23" s="12">
         <v>3760912</v>
@@ -3144,13 +3192,13 @@
         <v>25</v>
       </c>
       <c r="G23" s="12">
-        <v>2259770</v>
+        <v>2273483</v>
       </c>
       <c r="H23" s="13" t="s">
         <v>26</v>
       </c>
       <c r="I23" s="12">
-        <v>181028</v>
+        <v>173296</v>
       </c>
       <c r="J23" s="13" t="s">
         <v>27</v>
@@ -3158,7 +3206,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B25" s="14"/>
       <c r="C25" s="14"/>
@@ -3175,7 +3223,7 @@
         <v>5</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C26" s="16"/>
       <c r="D26" s="16"/>
@@ -3188,10 +3236,10 @@
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="B27" s="16" t="s">
         <v>107</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>108</v>
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
@@ -3204,10 +3252,10 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="B28" s="16" t="s">
         <v>109</v>
-      </c>
-      <c r="B28" s="16" t="s">
-        <v>110</v>
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="16"/>
@@ -3287,7 +3335,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3375,10 +3423,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>112</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>113</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -3412,10 +3460,10 @@
       <c r="AH4" s="3"/>
       <c r="AI4" s="3"/>
       <c r="AJ4" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AK4" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="AK4" s="3" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
@@ -3423,7 +3471,7 @@
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
@@ -3441,7 +3489,7 @@
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
       <c r="T5" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U5" s="3"/>
       <c r="V5" s="3"/>
@@ -3466,100 +3514,100 @@
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="I6" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="K6" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="L6" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="L6" s="3" t="s">
+      <c r="M6" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="M6" s="3" t="s">
+      <c r="N6" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="N6" s="3" t="s">
+      <c r="O6" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="O6" s="3" t="s">
+      <c r="P6" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="P6" s="3" t="s">
+      <c r="Q6" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="Q6" s="3" t="s">
+      <c r="R6" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="R6" s="3" t="s">
+      <c r="S6" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="S6" s="3" t="s">
+      <c r="T6" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="T6" s="3" t="s">
+      <c r="U6" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="U6" s="3" t="s">
+      <c r="V6" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="V6" s="3" t="s">
+      <c r="W6" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="W6" s="3" t="s">
+      <c r="X6" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="X6" s="3" t="s">
+      <c r="Y6" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="Y6" s="3" t="s">
+      <c r="Z6" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="Z6" s="3" t="s">
+      <c r="AA6" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="AA6" s="3" t="s">
-        <v>141</v>
       </c>
       <c r="AB6" s="3" t="s">
         <v>12</v>
       </c>
       <c r="AC6" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="AD6" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="AD6" s="3" t="s">
+      <c r="AE6" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="AE6" s="3" t="s">
+      <c r="AF6" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="AF6" s="3" t="s">
+      <c r="AG6" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="AG6" s="3" t="s">
+      <c r="AH6" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="AH6" s="3" t="s">
+      <c r="AI6" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="AI6" s="3" t="s">
-        <v>148</v>
       </c>
       <c r="AJ6" s="3"/>
       <c r="AK6" s="3"/>
@@ -3596,85 +3644,85 @@
         <v>22</v>
       </c>
       <c r="K7" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="L7" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="L7" s="4" t="s">
+      <c r="M7" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="M7" s="4" t="s">
+      <c r="N7" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="N7" s="4" t="s">
+      <c r="O7" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="O7" s="4" t="s">
+      <c r="P7" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="P7" s="4" t="s">
+      <c r="Q7" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="Q7" s="4" t="s">
+      <c r="R7" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="R7" s="4" t="s">
+      <c r="S7" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="S7" s="4" t="s">
+      <c r="T7" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="T7" s="4" t="s">
+      <c r="U7" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="U7" s="4" t="s">
+      <c r="V7" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="V7" s="4" t="s">
+      <c r="W7" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="W7" s="4" t="s">
+      <c r="X7" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="X7" s="4" t="s">
+      <c r="Y7" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="Y7" s="4" t="s">
+      <c r="Z7" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="Z7" s="4" t="s">
+      <c r="AA7" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="AA7" s="4" t="s">
+      <c r="AB7" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="AB7" s="4" t="s">
+      <c r="AC7" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="AC7" s="4" t="s">
+      <c r="AD7" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="AD7" s="4" t="s">
+      <c r="AE7" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="AE7" s="4" t="s">
+      <c r="AF7" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="AF7" s="4" t="s">
+      <c r="AG7" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="AG7" s="4" t="s">
+      <c r="AH7" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="AH7" s="4" t="s">
+      <c r="AI7" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="AI7" s="4" t="s">
+      <c r="AJ7" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="AJ7" s="4" t="s">
+      <c r="AK7" s="4" t="s">
         <v>174</v>
-      </c>
-      <c r="AK7" s="4" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
@@ -3691,103 +3739,103 @@
         <v>1096</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F8" s="6">
         <v>5</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H8" s="6">
         <v>6</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J8" s="6">
         <v>105</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L8" s="6">
         <v>88</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N8" s="6">
         <v>59</v>
       </c>
       <c r="O8" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P8" s="6">
         <v>111</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="R8" s="6">
         <v>0</v>
       </c>
       <c r="S8" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="T8" s="6">
         <v>83075</v>
       </c>
       <c r="U8" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="V8" s="6">
         <v>127071</v>
       </c>
       <c r="W8" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="X8" s="6">
         <v>57254</v>
       </c>
       <c r="Y8" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Z8" s="6">
         <v>325329</v>
       </c>
       <c r="AA8" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AB8" s="6">
         <v>110664</v>
       </c>
       <c r="AC8" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AD8" s="6">
         <v>9</v>
       </c>
       <c r="AE8" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AF8" s="6">
         <v>72</v>
       </c>
       <c r="AG8" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AH8" s="6">
         <v>46156</v>
       </c>
       <c r="AI8" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AJ8" s="6">
         <v>194835</v>
       </c>
       <c r="AK8" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
@@ -3804,103 +3852,103 @@
         <v>23</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F9" s="9">
         <v>0</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H9" s="9">
         <v>0</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J9" s="9">
         <v>3</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L9" s="9">
         <v>1</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N9" s="9">
         <v>0</v>
       </c>
       <c r="O9" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P9" s="9">
         <v>0</v>
       </c>
       <c r="Q9" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="R9" s="9">
         <v>0</v>
       </c>
       <c r="S9" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="T9" s="9">
         <v>1967</v>
       </c>
       <c r="U9" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="V9" s="9">
         <v>1971</v>
       </c>
       <c r="W9" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="X9" s="9">
         <v>1502</v>
       </c>
       <c r="Y9" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Z9" s="9">
         <v>4967</v>
       </c>
       <c r="AA9" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AB9" s="9">
         <v>2053</v>
       </c>
       <c r="AC9" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AD9" s="9">
         <v>1</v>
       </c>
       <c r="AE9" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AF9" s="9">
         <v>0</v>
       </c>
       <c r="AG9" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AH9" s="9">
         <v>177</v>
       </c>
       <c r="AI9" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AJ9" s="9">
         <v>4043</v>
       </c>
       <c r="AK9" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
@@ -3917,103 +3965,103 @@
         <v>52</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F10" s="9">
         <v>0</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H10" s="9">
         <v>0</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J10" s="9">
         <v>6</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L10" s="9">
         <v>9</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N10" s="9">
         <v>8</v>
       </c>
       <c r="O10" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P10" s="9">
         <v>30</v>
       </c>
       <c r="Q10" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="R10" s="9">
         <v>0</v>
       </c>
       <c r="S10" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="T10" s="9">
         <v>4815</v>
       </c>
       <c r="U10" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="V10" s="9">
         <v>12267</v>
       </c>
       <c r="W10" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="X10" s="9">
         <v>8563</v>
       </c>
       <c r="Y10" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Z10" s="9">
         <v>14919</v>
       </c>
       <c r="AA10" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AB10" s="9">
         <v>5191</v>
       </c>
       <c r="AC10" s="10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AD10" s="9">
         <v>0</v>
       </c>
       <c r="AE10" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AF10" s="9">
         <v>1</v>
       </c>
       <c r="AG10" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AH10" s="9">
         <v>5669</v>
       </c>
       <c r="AI10" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AJ10" s="9">
         <v>10058</v>
       </c>
       <c r="AK10" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
@@ -4030,55 +4078,55 @@
         <v>126</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F11" s="9">
         <v>0</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H11" s="9">
         <v>0</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J11" s="9">
         <v>13</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L11" s="9">
         <v>2</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N11" s="9">
         <v>1</v>
       </c>
       <c r="O11" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P11" s="9">
         <v>2</v>
       </c>
       <c r="Q11" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="R11" s="9">
         <v>0</v>
       </c>
       <c r="S11" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="T11" s="9">
         <v>5264</v>
       </c>
       <c r="U11" s="10" t="s">
-        <v>52</v>
+        <v>205</v>
       </c>
       <c r="V11" s="9">
         <v>10321</v>
@@ -4108,13 +4156,13 @@
         <v>1</v>
       </c>
       <c r="AE11" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AF11" s="9">
         <v>13</v>
       </c>
       <c r="AG11" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AH11" s="9">
         <v>2426</v>
@@ -4149,43 +4197,43 @@
         <v>0</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H12" s="9">
         <v>0</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J12" s="9">
         <v>5</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L12" s="9">
         <v>4</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N12" s="9">
         <v>0</v>
       </c>
       <c r="O12" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P12" s="9">
         <v>2</v>
       </c>
       <c r="Q12" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="R12" s="9">
         <v>0</v>
       </c>
       <c r="S12" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="T12" s="9">
         <v>14012</v>
@@ -4221,13 +4269,13 @@
         <v>1</v>
       </c>
       <c r="AE12" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AF12" s="9">
         <v>1</v>
       </c>
       <c r="AG12" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AH12" s="9">
         <v>13791</v>
@@ -4256,49 +4304,49 @@
         <v>121</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F13" s="9">
         <v>1</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H13" s="9">
         <v>0</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J13" s="9">
         <v>9</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L13" s="9">
         <v>8</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N13" s="9">
         <v>3</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P13" s="9">
         <v>2</v>
       </c>
       <c r="Q13" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="R13" s="9">
         <v>0</v>
       </c>
       <c r="S13" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="T13" s="9">
         <v>13417</v>
@@ -4334,13 +4382,13 @@
         <v>1</v>
       </c>
       <c r="AE13" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AF13" s="9">
         <v>9</v>
       </c>
       <c r="AG13" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AH13" s="9">
         <v>7635</v>
@@ -4375,43 +4423,43 @@
         <v>0</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H14" s="9">
         <v>0</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J14" s="9">
         <v>12</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L14" s="9">
         <v>10</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N14" s="9">
         <v>4</v>
       </c>
       <c r="O14" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P14" s="9">
         <v>2</v>
       </c>
       <c r="Q14" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="R14" s="9">
         <v>0</v>
       </c>
       <c r="S14" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="T14" s="9">
         <v>4495</v>
@@ -4447,13 +4495,13 @@
         <v>0</v>
       </c>
       <c r="AE14" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AF14" s="9">
         <v>3</v>
       </c>
       <c r="AG14" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AH14" s="9">
         <v>4434</v>
@@ -4482,49 +4530,49 @@
         <v>36</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F15" s="9">
         <v>0</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H15" s="9">
         <v>0</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J15" s="9">
         <v>0</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L15" s="9">
         <v>0</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N15" s="9">
         <v>0</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P15" s="9">
         <v>0</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="R15" s="9">
         <v>0</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="T15" s="9">
         <v>2266</v>
@@ -4554,19 +4602,19 @@
         <v>5202</v>
       </c>
       <c r="AC15" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AD15" s="9">
         <v>0</v>
       </c>
       <c r="AE15" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AF15" s="9">
         <v>1</v>
       </c>
       <c r="AG15" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AH15" s="9">
         <v>3826</v>
@@ -4601,43 +4649,43 @@
         <v>1</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H16" s="9">
         <v>0</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J16" s="9">
         <v>3</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L16" s="9">
         <v>3</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N16" s="9">
         <v>1</v>
       </c>
       <c r="O16" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P16" s="9">
         <v>2</v>
       </c>
       <c r="Q16" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="R16" s="9">
         <v>0</v>
       </c>
       <c r="S16" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="T16" s="9">
         <v>3644</v>
@@ -4673,13 +4721,13 @@
         <v>0</v>
       </c>
       <c r="AE16" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AF16" s="9">
         <v>0</v>
       </c>
       <c r="AG16" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AH16" s="9">
         <v>183</v>
@@ -4714,43 +4762,43 @@
         <v>0</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H17" s="9">
         <v>0</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J17" s="9">
         <v>4</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L17" s="9">
         <v>4</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N17" s="9">
         <v>0</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P17" s="9">
         <v>0</v>
       </c>
       <c r="Q17" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="R17" s="9">
         <v>0</v>
       </c>
       <c r="S17" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="T17" s="9">
         <v>5461</v>
@@ -4786,13 +4834,13 @@
         <v>0</v>
       </c>
       <c r="AE17" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AF17" s="9">
         <v>1</v>
       </c>
       <c r="AG17" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AH17" s="9">
         <v>381</v>
@@ -4821,49 +4869,49 @@
         <v>31</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F18" s="9">
         <v>0</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H18" s="9">
         <v>0</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J18" s="9">
         <v>0</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L18" s="9">
         <v>0</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N18" s="9">
         <v>0</v>
       </c>
       <c r="O18" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P18" s="9">
         <v>1</v>
       </c>
       <c r="Q18" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="R18" s="9">
         <v>0</v>
       </c>
       <c r="S18" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="T18" s="9">
         <v>7243</v>
@@ -4899,13 +4947,13 @@
         <v>0</v>
       </c>
       <c r="AE18" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AF18" s="9">
         <v>0</v>
       </c>
       <c r="AG18" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AH18" s="9">
         <v>346</v>
@@ -4940,43 +4988,43 @@
         <v>0</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H19" s="9">
         <v>0</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J19" s="9">
         <v>1</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L19" s="9">
         <v>0</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N19" s="9">
         <v>0</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P19" s="9">
         <v>1</v>
       </c>
       <c r="Q19" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="R19" s="9">
         <v>0</v>
       </c>
       <c r="S19" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="T19" s="9">
         <v>3069</v>
@@ -5012,13 +5060,13 @@
         <v>0</v>
       </c>
       <c r="AE19" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AF19" s="9">
         <v>1</v>
       </c>
       <c r="AG19" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AH19" s="9">
         <v>96</v>
@@ -5053,43 +5101,43 @@
         <v>0</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H20" s="9">
         <v>0</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J20" s="9">
         <v>0</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L20" s="9">
         <v>0</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N20" s="9">
         <v>0</v>
       </c>
       <c r="O20" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P20" s="9">
         <v>0</v>
       </c>
       <c r="Q20" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="R20" s="9">
         <v>0</v>
       </c>
       <c r="S20" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="T20" s="9">
         <v>4173</v>
@@ -5125,13 +5173,13 @@
         <v>2</v>
       </c>
       <c r="AE20" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AF20" s="9">
         <v>0</v>
       </c>
       <c r="AG20" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AH20" s="9">
         <v>170</v>
@@ -5166,43 +5214,43 @@
         <v>1</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H21" s="9">
         <v>0</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J21" s="9">
         <v>1</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L21" s="9">
         <v>1</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N21" s="9">
         <v>0</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P21" s="9">
         <v>0</v>
       </c>
       <c r="Q21" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="R21" s="9">
         <v>0</v>
       </c>
       <c r="S21" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="T21" s="9">
         <v>1180</v>
@@ -5238,13 +5286,13 @@
         <v>0</v>
       </c>
       <c r="AE21" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AF21" s="9">
         <v>0</v>
       </c>
       <c r="AG21" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AH21" s="9">
         <v>66</v>
@@ -5279,13 +5327,13 @@
         <v>2</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H22" s="9">
         <v>6</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J22" s="9">
         <v>48</v>
@@ -5303,19 +5351,19 @@
         <v>42</v>
       </c>
       <c r="O22" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P22" s="9">
         <v>69</v>
       </c>
       <c r="Q22" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="R22" s="9">
         <v>0</v>
       </c>
       <c r="S22" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="T22" s="9">
         <v>8462</v>
@@ -5351,13 +5399,13 @@
         <v>3</v>
       </c>
       <c r="AE22" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AF22" s="9">
         <v>39</v>
       </c>
       <c r="AG22" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AH22" s="9">
         <v>6675</v>
@@ -5392,43 +5440,43 @@
         <v>0</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H23" s="9">
         <v>0</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J23" s="9">
         <v>0</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L23" s="9">
         <v>0</v>
       </c>
       <c r="M23" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N23" s="9">
         <v>0</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P23" s="9">
         <v>0</v>
       </c>
       <c r="Q23" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="R23" s="9">
         <v>0</v>
       </c>
       <c r="S23" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="T23" s="9">
         <v>3607</v>
@@ -5464,13 +5512,13 @@
         <v>0</v>
       </c>
       <c r="AE23" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AF23" s="9">
         <v>3</v>
       </c>
       <c r="AG23" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AH23" s="9">
         <v>281</v>
@@ -5487,10 +5535,10 @@
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" s="11" t="s">
         <v>103</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>104</v>
       </c>
       <c r="C24" s="12">
         <v>760551</v>
@@ -5499,108 +5547,108 @@
         <v>1096</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F24" s="12">
         <v>5</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H24" s="12">
         <v>6</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J24" s="12">
         <v>105</v>
       </c>
       <c r="K24" s="13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L24" s="12">
         <v>88</v>
       </c>
       <c r="M24" s="13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N24" s="12">
         <v>59</v>
       </c>
       <c r="O24" s="13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P24" s="12">
         <v>111</v>
       </c>
       <c r="Q24" s="13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="R24" s="12">
         <v>0</v>
       </c>
       <c r="S24" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="T24" s="12">
         <v>83075</v>
       </c>
       <c r="U24" s="13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="V24" s="12">
         <v>127071</v>
       </c>
       <c r="W24" s="13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="X24" s="12">
         <v>57254</v>
       </c>
       <c r="Y24" s="13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Z24" s="12">
         <v>325329</v>
       </c>
       <c r="AA24" s="13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AB24" s="12">
         <v>110664</v>
       </c>
       <c r="AC24" s="13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AD24" s="12">
         <v>9</v>
       </c>
       <c r="AE24" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AF24" s="12">
         <v>72</v>
       </c>
       <c r="AG24" s="13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AH24" s="12">
         <v>46156</v>
       </c>
       <c r="AI24" s="13" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AJ24" s="12">
         <v>194835</v>
       </c>
       <c r="AK24" s="13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="26" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -5840,7 +5888,7 @@
         <v>313</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>314</v>
@@ -5902,19 +5950,19 @@
         <v>22</v>
       </c>
       <c r="K6" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="L6" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="M6" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="N6" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="N6" s="4" t="s">
+      <c r="O6" s="4" t="s">
         <v>152</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -5949,7 +5997,7 @@
         <v>324</v>
       </c>
       <c r="K7" s="6">
-        <v>191800</v>
+        <v>193697</v>
       </c>
       <c r="L7" s="7" t="s">
         <v>325</v>
@@ -5958,10 +6006,10 @@
         <v>961</v>
       </c>
       <c r="N7" s="6">
-        <v>194835</v>
+        <v>196732</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>185</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -5987,28 +6035,28 @@
         <v>29</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I8" s="9">
         <v>59</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K8" s="9">
-        <v>3942</v>
+        <v>3955</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M8" s="9">
         <v>13</v>
       </c>
       <c r="N8" s="9">
-        <v>4043</v>
+        <v>4056</v>
       </c>
       <c r="O8" s="10" t="s">
-        <v>194</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6034,28 +6082,28 @@
         <v>58</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="I9" s="9">
         <v>12</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K9" s="9">
-        <v>9927</v>
+        <v>9997</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M9" s="9">
         <v>61</v>
       </c>
       <c r="N9" s="9">
-        <v>10058</v>
+        <v>10128</v>
       </c>
       <c r="O9" s="10" t="s">
-        <v>204</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6081,28 +6129,28 @@
         <v>151</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I10" s="9">
         <v>79</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="K10" s="9">
-        <v>17640</v>
+        <v>17833</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="M10" s="9">
         <v>94</v>
       </c>
       <c r="N10" s="9">
-        <v>17964</v>
+        <v>18157</v>
       </c>
       <c r="O10" s="10" t="s">
-        <v>211</v>
+        <v>338</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6128,28 +6176,28 @@
         <v>96</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="I11" s="9">
         <v>77</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="K11" s="9">
-        <v>28974</v>
+        <v>29252</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="M11" s="9">
         <v>190</v>
       </c>
       <c r="N11" s="9">
-        <v>29337</v>
+        <v>29615</v>
       </c>
       <c r="O11" s="10" t="s">
-        <v>219</v>
+        <v>342</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6175,28 +6223,28 @@
         <v>145</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="I12" s="9">
         <v>125</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="K12" s="9">
-        <v>33685</v>
+        <v>34107</v>
       </c>
       <c r="L12" s="10" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="M12" s="9">
         <v>155</v>
       </c>
       <c r="N12" s="9">
-        <v>34110</v>
+        <v>34532</v>
       </c>
       <c r="O12" s="10" t="s">
-        <v>226</v>
+        <v>346</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6222,28 +6270,28 @@
         <v>60</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="I13" s="9">
         <v>62</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="K13" s="9">
-        <v>11702</v>
+        <v>11812</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="M13" s="9">
         <v>39</v>
       </c>
       <c r="N13" s="9">
-        <v>11863</v>
+        <v>11973</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>234</v>
+        <v>350</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6269,28 +6317,28 @@
         <v>44</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="I14" s="9">
         <v>15</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="K14" s="9">
-        <v>7391</v>
+        <v>7472</v>
       </c>
       <c r="L14" s="10" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="M14" s="9">
         <v>54</v>
       </c>
       <c r="N14" s="9">
-        <v>7504</v>
+        <v>7585</v>
       </c>
       <c r="O14" s="10" t="s">
-        <v>240</v>
+        <v>354</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6316,28 +6364,28 @@
         <v>48</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="I15" s="9">
         <v>18</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="K15" s="9">
-        <v>8073</v>
+        <v>8191</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="M15" s="9">
         <v>12</v>
       </c>
       <c r="N15" s="9">
-        <v>8151</v>
+        <v>8269</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>248</v>
+        <v>358</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6363,28 +6411,28 @@
         <v>53</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="I16" s="9">
         <v>48</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="K16" s="9">
-        <v>11234</v>
+        <v>11316</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="M16" s="9">
         <v>41</v>
       </c>
       <c r="N16" s="9">
-        <v>11376</v>
+        <v>11458</v>
       </c>
       <c r="O16" s="10" t="s">
-        <v>256</v>
+        <v>362</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6410,28 +6458,28 @@
         <v>41</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="I17" s="9">
         <v>12</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="K17" s="9">
-        <v>12827</v>
+        <v>12915</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="M17" s="9">
         <v>72</v>
       </c>
       <c r="N17" s="9">
-        <v>12952</v>
+        <v>13040</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>263</v>
+        <v>366</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6457,28 +6505,28 @@
         <v>30</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="I18" s="9">
         <v>18</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="K18" s="9">
-        <v>6830</v>
+        <v>6865</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="M18" s="9">
         <v>12</v>
       </c>
       <c r="N18" s="9">
-        <v>6890</v>
+        <v>6925</v>
       </c>
       <c r="O18" s="10" t="s">
-        <v>271</v>
+        <v>370</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6504,28 +6552,28 @@
         <v>26</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="I19" s="9">
         <v>21</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="K19" s="9">
-        <v>8400</v>
+        <v>8517</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="M19" s="9">
         <v>12</v>
       </c>
       <c r="N19" s="9">
-        <v>8459</v>
+        <v>8576</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>279</v>
+        <v>374</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6551,28 +6599,28 @@
         <v>10</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="I20" s="9">
         <v>2</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K20" s="9">
-        <v>2887</v>
+        <v>2904</v>
       </c>
       <c r="L20" s="10" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="M20" s="9">
         <v>0</v>
       </c>
       <c r="N20" s="9">
-        <v>2899</v>
+        <v>2916</v>
       </c>
       <c r="O20" s="10" t="s">
-        <v>287</v>
+        <v>377</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6598,7 +6646,7 @@
         <v>407</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="I21" s="9">
         <v>218</v>
@@ -6607,19 +6655,19 @@
         <v>230</v>
       </c>
       <c r="K21" s="9">
-        <v>21757</v>
+        <v>21970</v>
       </c>
       <c r="L21" s="10" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="M21" s="9">
         <v>168</v>
       </c>
       <c r="N21" s="9">
-        <v>22550</v>
+        <v>22763</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>295</v>
+        <v>380</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6645,36 +6693,36 @@
         <v>47</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="I22" s="9">
         <v>63</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="K22" s="9">
-        <v>6531</v>
+        <v>6591</v>
       </c>
       <c r="L22" s="10" t="s">
-        <v>368</v>
+        <v>383</v>
       </c>
       <c r="M22" s="9">
         <v>38</v>
       </c>
       <c r="N22" s="9">
-        <v>6679</v>
+        <v>6739</v>
       </c>
       <c r="O22" s="10" t="s">
-        <v>303</v>
+        <v>384</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B23" s="11" t="s">
         <v>103</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>104</v>
       </c>
       <c r="C23" s="12">
         <v>1529</v>
@@ -6701,7 +6749,7 @@
         <v>324</v>
       </c>
       <c r="K23" s="12">
-        <v>191800</v>
+        <v>193697</v>
       </c>
       <c r="L23" s="13" t="s">
         <v>325</v>
@@ -6710,15 +6758,15 @@
         <v>961</v>
       </c>
       <c r="N23" s="12">
-        <v>194835</v>
+        <v>196732</v>
       </c>
       <c r="O23" s="13" t="s">
-        <v>185</v>
+        <v>326</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B25" s="14"/>
       <c r="C25" s="14"/>
@@ -6737,10 +6785,10 @@
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>369</v>
+        <v>385</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="C26" s="16"/>
       <c r="D26" s="16"/>
@@ -6758,10 +6806,10 @@
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
-        <v>371</v>
+        <v>387</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>372</v>
+        <v>388</v>
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
@@ -6779,10 +6827,10 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
-        <v>373</v>
+        <v>389</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>374</v>
+        <v>390</v>
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="16"/>
@@ -6800,10 +6848,10 @@
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>375</v>
+        <v>391</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>376</v>
+        <v>392</v>
       </c>
       <c r="C29" s="16"/>
       <c r="D29" s="16"/>
@@ -6821,10 +6869,10 @@
     </row>
     <row r="30" ht="24" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>378</v>
+        <v>394</v>
       </c>
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
@@ -6845,7 +6893,7 @@
         <v>321</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="C31" s="16"/>
       <c r="D31" s="16"/>
@@ -6908,7 +6956,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>380</v>
+        <v>396</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6956,10 +7004,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>381</v>
+        <v>397</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -6973,10 +7021,10 @@
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>384</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -6984,40 +7032,40 @@
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="F5" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>125</v>
-      </c>
       <c r="H5" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>139</v>
-      </c>
       <c r="J5" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>128</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>129</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>12</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="N5" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="O5" s="3" t="s">
         <v>132</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>133</v>
       </c>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
@@ -7054,25 +7102,25 @@
         <v>22</v>
       </c>
       <c r="K6" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="L6" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="M6" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="N6" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="N6" s="4" t="s">
+      <c r="O6" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="O6" s="4" t="s">
+      <c r="P6" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="P6" s="4" t="s">
+      <c r="Q6" s="4" t="s">
         <v>154</v>
-      </c>
-      <c r="Q6" s="4" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7089,43 +7137,43 @@
         <v>1003864</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>385</v>
+        <v>401</v>
       </c>
       <c r="F7" s="6">
         <v>491970</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>386</v>
+        <v>402</v>
       </c>
       <c r="H7" s="6">
         <v>7854</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>387</v>
+        <v>403</v>
       </c>
       <c r="J7" s="6">
         <v>202062</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>388</v>
+        <v>404</v>
       </c>
       <c r="L7" s="6">
         <v>702163</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="N7" s="6">
         <v>312</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P7" s="6">
         <v>1706027</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>390</v>
+        <v>406</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7142,43 +7190,43 @@
         <v>60007</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>391</v>
+        <v>407</v>
       </c>
       <c r="F8" s="9">
         <v>20239</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>392</v>
+        <v>408</v>
       </c>
       <c r="H8" s="9">
         <v>516</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>393</v>
+        <v>409</v>
       </c>
       <c r="J8" s="9">
         <v>9513</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="L8" s="9">
         <v>30718</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>395</v>
+        <v>411</v>
       </c>
       <c r="N8" s="9">
         <v>20</v>
       </c>
       <c r="O8" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P8" s="9">
         <v>90725</v>
       </c>
       <c r="Q8" s="10" t="s">
-        <v>396</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7195,43 +7243,43 @@
         <v>74569</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>397</v>
+        <v>413</v>
       </c>
       <c r="F9" s="9">
         <v>40875</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>398</v>
+        <v>414</v>
       </c>
       <c r="H9" s="9">
         <v>732</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>399</v>
+        <v>415</v>
       </c>
       <c r="J9" s="9">
         <v>13447</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>400</v>
+        <v>416</v>
       </c>
       <c r="L9" s="9">
         <v>56490</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>401</v>
+        <v>417</v>
       </c>
       <c r="N9" s="9">
         <v>16</v>
       </c>
       <c r="O9" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P9" s="9">
         <v>131059</v>
       </c>
       <c r="Q9" s="10" t="s">
-        <v>402</v>
+        <v>418</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7248,43 +7296,43 @@
         <v>71557</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="F10" s="9">
         <v>44153</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>404</v>
+        <v>420</v>
       </c>
       <c r="H10" s="9">
         <v>363</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>405</v>
+        <v>421</v>
       </c>
       <c r="J10" s="9">
         <v>28892</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>406</v>
+        <v>422</v>
       </c>
       <c r="L10" s="9">
         <v>61293</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>407</v>
+        <v>423</v>
       </c>
       <c r="N10" s="9">
         <v>17</v>
       </c>
       <c r="O10" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P10" s="9">
         <v>132850</v>
       </c>
       <c r="Q10" s="10" t="s">
-        <v>408</v>
+        <v>424</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7301,13 +7349,13 @@
         <v>165793</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>409</v>
+        <v>425</v>
       </c>
       <c r="F11" s="9">
         <v>74854</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c r="H11" s="9">
         <v>757</v>
@@ -7319,25 +7367,25 @@
         <v>28692</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>411</v>
+        <v>427</v>
       </c>
       <c r="L11" s="9">
         <v>120329</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>412</v>
+        <v>428</v>
       </c>
       <c r="N11" s="9">
         <v>55</v>
       </c>
       <c r="O11" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P11" s="9">
         <v>286122</v>
       </c>
       <c r="Q11" s="10" t="s">
-        <v>413</v>
+        <v>429</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7354,43 +7402,43 @@
         <v>199723</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
       <c r="F12" s="9">
         <v>85793</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
       <c r="H12" s="9">
         <v>806</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J12" s="9">
         <v>43644</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>416</v>
+        <v>432</v>
       </c>
       <c r="L12" s="9">
         <v>129967</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>417</v>
+        <v>433</v>
       </c>
       <c r="N12" s="9">
         <v>57</v>
       </c>
       <c r="O12" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P12" s="9">
         <v>329690</v>
       </c>
       <c r="Q12" s="10" t="s">
-        <v>418</v>
+        <v>434</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7407,7 +7455,7 @@
         <v>59427</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>419</v>
+        <v>435</v>
       </c>
       <c r="F13" s="9">
         <v>24311</v>
@@ -7419,31 +7467,31 @@
         <v>266</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>420</v>
+        <v>436</v>
       </c>
       <c r="J13" s="9">
         <v>21629</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="L13" s="9">
         <v>46806</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>422</v>
+        <v>438</v>
       </c>
       <c r="N13" s="9">
         <v>15</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P13" s="9">
         <v>106233</v>
       </c>
       <c r="Q13" s="10" t="s">
-        <v>423</v>
+        <v>439</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7460,13 +7508,13 @@
         <v>58483</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>424</v>
+        <v>440</v>
       </c>
       <c r="F14" s="9">
         <v>26620</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>425</v>
+        <v>441</v>
       </c>
       <c r="H14" s="9">
         <v>216</v>
@@ -7478,25 +7526,25 @@
         <v>10802</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>426</v>
+        <v>442</v>
       </c>
       <c r="L14" s="9">
         <v>47019</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>427</v>
+        <v>443</v>
       </c>
       <c r="N14" s="9">
         <v>17</v>
       </c>
       <c r="O14" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P14" s="9">
         <v>105502</v>
       </c>
       <c r="Q14" s="10" t="s">
-        <v>428</v>
+        <v>444</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7513,43 +7561,43 @@
         <v>46901</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
       <c r="F15" s="9">
         <v>28368</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>430</v>
+        <v>446</v>
       </c>
       <c r="H15" s="9">
         <v>516</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>431</v>
+        <v>447</v>
       </c>
       <c r="J15" s="9">
         <v>5433</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>432</v>
+        <v>448</v>
       </c>
       <c r="L15" s="9">
         <v>29803</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>433</v>
+        <v>449</v>
       </c>
       <c r="N15" s="9">
         <v>6</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P15" s="9">
         <v>76704</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>434</v>
+        <v>450</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7566,43 +7614,43 @@
         <v>78420</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>435</v>
+        <v>451</v>
       </c>
       <c r="F16" s="9">
         <v>41403</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>436</v>
+        <v>452</v>
       </c>
       <c r="H16" s="9">
         <v>1078</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>437</v>
+        <v>453</v>
       </c>
       <c r="J16" s="9">
         <v>10556</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>438</v>
+        <v>454</v>
       </c>
       <c r="L16" s="9">
         <v>35195</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>439</v>
+        <v>455</v>
       </c>
       <c r="N16" s="9">
         <v>25</v>
       </c>
       <c r="O16" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P16" s="9">
         <v>113615</v>
       </c>
       <c r="Q16" s="10" t="s">
-        <v>440</v>
+        <v>456</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7619,43 +7667,43 @@
         <v>53838</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>441</v>
+        <v>457</v>
       </c>
       <c r="F17" s="9">
         <v>33086</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>442</v>
+        <v>458</v>
       </c>
       <c r="H17" s="9">
         <v>648</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>443</v>
+        <v>459</v>
       </c>
       <c r="J17" s="9">
         <v>6876</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>444</v>
+        <v>460</v>
       </c>
       <c r="L17" s="9">
         <v>30539</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N17" s="9">
         <v>5</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P17" s="9">
         <v>84377</v>
       </c>
       <c r="Q17" s="10" t="s">
-        <v>445</v>
+        <v>461</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7672,31 +7720,31 @@
         <v>37570</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>446</v>
+        <v>462</v>
       </c>
       <c r="F18" s="9">
         <v>23705</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>447</v>
+        <v>463</v>
       </c>
       <c r="H18" s="9">
         <v>555</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>448</v>
+        <v>464</v>
       </c>
       <c r="J18" s="9">
         <v>9891</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>449</v>
+        <v>465</v>
       </c>
       <c r="L18" s="9">
         <v>22465</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>450</v>
+        <v>466</v>
       </c>
       <c r="N18" s="9">
         <v>36</v>
@@ -7708,7 +7756,7 @@
         <v>60035</v>
       </c>
       <c r="Q18" s="10" t="s">
-        <v>451</v>
+        <v>467</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7725,43 +7773,43 @@
         <v>56908</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>452</v>
+        <v>468</v>
       </c>
       <c r="F19" s="9">
         <v>23775</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>453</v>
+        <v>469</v>
       </c>
       <c r="H19" s="9">
         <v>545</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>454</v>
+        <v>470</v>
       </c>
       <c r="J19" s="9">
         <v>7692</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>455</v>
+        <v>471</v>
       </c>
       <c r="L19" s="9">
         <v>31976</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>456</v>
+        <v>472</v>
       </c>
       <c r="N19" s="9">
         <v>13</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P19" s="9">
         <v>88884</v>
       </c>
       <c r="Q19" s="10" t="s">
-        <v>457</v>
+        <v>473</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7778,43 +7826,43 @@
         <v>27445</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>458</v>
+        <v>474</v>
       </c>
       <c r="F20" s="9">
         <v>14856</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>459</v>
+        <v>475</v>
       </c>
       <c r="H20" s="9">
         <v>223</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>399</v>
+        <v>415</v>
       </c>
       <c r="J20" s="9">
         <v>2469</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>460</v>
+        <v>476</v>
       </c>
       <c r="L20" s="9">
         <v>13408</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>461</v>
+        <v>477</v>
       </c>
       <c r="N20" s="9">
         <v>6</v>
       </c>
       <c r="O20" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P20" s="9">
         <v>40853</v>
       </c>
       <c r="Q20" s="10" t="s">
-        <v>462</v>
+        <v>478</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7831,43 +7879,43 @@
         <v>2805</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>463</v>
+        <v>479</v>
       </c>
       <c r="F21" s="9">
         <v>3515</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>464</v>
+        <v>480</v>
       </c>
       <c r="H21" s="9">
         <v>94</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>465</v>
+        <v>481</v>
       </c>
       <c r="J21" s="9">
         <v>1790</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>466</v>
+        <v>482</v>
       </c>
       <c r="L21" s="9">
         <v>37761</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>467</v>
+        <v>483</v>
       </c>
       <c r="N21" s="9">
         <v>18</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P21" s="9">
         <v>40566</v>
       </c>
       <c r="Q21" s="10" t="s">
-        <v>468</v>
+        <v>484</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7884,51 +7932,51 @@
         <v>10418</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>469</v>
+        <v>485</v>
       </c>
       <c r="F22" s="9">
         <v>6417</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>470</v>
+        <v>486</v>
       </c>
       <c r="H22" s="9">
         <v>539</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="J22" s="9">
         <v>736</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>472</v>
+        <v>488</v>
       </c>
       <c r="L22" s="9">
         <v>8394</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>473</v>
+        <v>489</v>
       </c>
       <c r="N22" s="9">
         <v>6</v>
       </c>
       <c r="O22" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P22" s="9">
         <v>18812</v>
       </c>
       <c r="Q22" s="10" t="s">
-        <v>474</v>
+        <v>490</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B23" s="11" t="s">
         <v>103</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>104</v>
       </c>
       <c r="C23" s="12">
         <v>2153713</v>
@@ -7937,48 +7985,48 @@
         <v>1003864</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>385</v>
+        <v>401</v>
       </c>
       <c r="F23" s="12">
         <v>491970</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>386</v>
+        <v>402</v>
       </c>
       <c r="H23" s="12">
         <v>7854</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>387</v>
+        <v>403</v>
       </c>
       <c r="J23" s="12">
         <v>202062</v>
       </c>
       <c r="K23" s="13" t="s">
-        <v>388</v>
+        <v>404</v>
       </c>
       <c r="L23" s="12">
         <v>702163</v>
       </c>
       <c r="M23" s="13" t="s">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="N23" s="12">
         <v>312</v>
       </c>
       <c r="O23" s="13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P23" s="12">
         <v>1706027</v>
       </c>
       <c r="Q23" s="13" t="s">
-        <v>390</v>
+        <v>406</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B25" s="14"/>
       <c r="C25" s="14"/>
@@ -7999,7 +8047,7 @@
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>475</v>
+        <v>491</v>
       </c>
       <c r="B26" s="16" t="s">
         <v>307</v>
@@ -8064,7 +8112,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>476</v>
+        <v>492</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -8116,16 +8164,16 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>381</v>
+        <v>397</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>478</v>
+        <v>494</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
@@ -8133,7 +8181,7 @@
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3" t="s">
-        <v>479</v>
+        <v>495</v>
       </c>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -8154,40 +8202,40 @@
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>134</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>135</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>480</v>
+        <v>496</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>481</v>
+        <v>497</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>482</v>
+        <v>498</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>483</v>
+        <v>499</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>484</v>
+        <v>500</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>485</v>
+        <v>501</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>486</v>
+        <v>502</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>487</v>
+        <v>503</v>
       </c>
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
@@ -8224,31 +8272,31 @@
         <v>22</v>
       </c>
       <c r="K6" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="L6" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="M6" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="N6" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="N6" s="4" t="s">
+      <c r="O6" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="O6" s="4" t="s">
+      <c r="P6" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="P6" s="4" t="s">
+      <c r="Q6" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="Q6" s="4" t="s">
+      <c r="R6" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="R6" s="4" t="s">
+      <c r="S6" s="4" t="s">
         <v>156</v>
-      </c>
-      <c r="S6" s="4" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8271,43 +8319,43 @@
         <v>84171</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>488</v>
+        <v>504</v>
       </c>
       <c r="H7" s="6">
         <v>110664</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J7" s="6">
         <v>194835</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L7" s="6">
         <v>1003864</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>385</v>
+        <v>401</v>
       </c>
       <c r="N7" s="6">
         <v>702163</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="P7" s="6">
         <v>1706027</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="R7" s="6">
         <v>1900862</v>
       </c>
       <c r="S7" s="7" t="s">
-        <v>489</v>
+        <v>505</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8330,43 +8378,43 @@
         <v>1990</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>490</v>
+        <v>506</v>
       </c>
       <c r="H8" s="9">
         <v>2053</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J8" s="9">
         <v>4043</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L8" s="9">
         <v>60007</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>391</v>
+        <v>407</v>
       </c>
       <c r="N8" s="9">
         <v>30718</v>
       </c>
       <c r="O8" s="10" t="s">
-        <v>395</v>
+        <v>411</v>
       </c>
       <c r="P8" s="9">
         <v>90725</v>
       </c>
       <c r="Q8" s="10" t="s">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="R8" s="9">
         <v>94768</v>
       </c>
       <c r="S8" s="10" t="s">
-        <v>491</v>
+        <v>507</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8389,43 +8437,43 @@
         <v>4867</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>492</v>
+        <v>508</v>
       </c>
       <c r="H9" s="9">
         <v>5191</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J9" s="9">
         <v>10058</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="L9" s="9">
         <v>74569</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>397</v>
+        <v>413</v>
       </c>
       <c r="N9" s="9">
         <v>56490</v>
       </c>
       <c r="O9" s="10" t="s">
-        <v>401</v>
+        <v>417</v>
       </c>
       <c r="P9" s="9">
         <v>131059</v>
       </c>
       <c r="Q9" s="10" t="s">
-        <v>402</v>
+        <v>418</v>
       </c>
       <c r="R9" s="9">
         <v>141117</v>
       </c>
       <c r="S9" s="10" t="s">
-        <v>493</v>
+        <v>509</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8448,7 +8496,7 @@
         <v>5390</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>494</v>
+        <v>510</v>
       </c>
       <c r="H10" s="9">
         <v>12574</v>
@@ -8466,25 +8514,25 @@
         <v>71557</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="N10" s="9">
         <v>61293</v>
       </c>
       <c r="O10" s="10" t="s">
-        <v>407</v>
+        <v>423</v>
       </c>
       <c r="P10" s="9">
         <v>132850</v>
       </c>
       <c r="Q10" s="10" t="s">
-        <v>408</v>
+        <v>424</v>
       </c>
       <c r="R10" s="9">
         <v>150814</v>
       </c>
       <c r="S10" s="10" t="s">
-        <v>495</v>
+        <v>511</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8507,7 +8555,7 @@
         <v>14089</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>496</v>
+        <v>512</v>
       </c>
       <c r="H11" s="9">
         <v>15248</v>
@@ -8525,25 +8573,25 @@
         <v>165793</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>409</v>
+        <v>425</v>
       </c>
       <c r="N11" s="9">
         <v>120329</v>
       </c>
       <c r="O11" s="10" t="s">
-        <v>412</v>
+        <v>428</v>
       </c>
       <c r="P11" s="9">
         <v>286122</v>
       </c>
       <c r="Q11" s="10" t="s">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="R11" s="9">
         <v>315459</v>
       </c>
       <c r="S11" s="10" t="s">
-        <v>497</v>
+        <v>513</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8566,7 +8614,7 @@
         <v>13538</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>498</v>
+        <v>514</v>
       </c>
       <c r="H12" s="9">
         <v>20572</v>
@@ -8584,25 +8632,25 @@
         <v>199723</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
       <c r="N12" s="9">
         <v>129967</v>
       </c>
       <c r="O12" s="10" t="s">
-        <v>417</v>
+        <v>433</v>
       </c>
       <c r="P12" s="9">
         <v>329690</v>
       </c>
       <c r="Q12" s="10" t="s">
-        <v>418</v>
+        <v>434</v>
       </c>
       <c r="R12" s="9">
         <v>363800</v>
       </c>
       <c r="S12" s="10" t="s">
-        <v>499</v>
+        <v>515</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8625,7 +8673,7 @@
         <v>4546</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>500</v>
+        <v>516</v>
       </c>
       <c r="H13" s="9">
         <v>7317</v>
@@ -8643,25 +8691,25 @@
         <v>59427</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>419</v>
+        <v>435</v>
       </c>
       <c r="N13" s="9">
         <v>46806</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>422</v>
+        <v>438</v>
       </c>
       <c r="P13" s="9">
         <v>106233</v>
       </c>
       <c r="Q13" s="10" t="s">
-        <v>423</v>
+        <v>439</v>
       </c>
       <c r="R13" s="9">
         <v>118096</v>
       </c>
       <c r="S13" s="10" t="s">
-        <v>501</v>
+        <v>517</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8684,13 +8732,13 @@
         <v>2302</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>502</v>
+        <v>518</v>
       </c>
       <c r="H14" s="9">
         <v>5202</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J14" s="9">
         <v>7504</v>
@@ -8702,25 +8750,25 @@
         <v>58483</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>424</v>
+        <v>440</v>
       </c>
       <c r="N14" s="9">
         <v>47019</v>
       </c>
       <c r="O14" s="10" t="s">
-        <v>427</v>
+        <v>443</v>
       </c>
       <c r="P14" s="9">
         <v>105502</v>
       </c>
       <c r="Q14" s="10" t="s">
-        <v>428</v>
+        <v>444</v>
       </c>
       <c r="R14" s="9">
         <v>113006</v>
       </c>
       <c r="S14" s="10" t="s">
-        <v>503</v>
+        <v>519</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8743,7 +8791,7 @@
         <v>3689</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>504</v>
+        <v>520</v>
       </c>
       <c r="H15" s="9">
         <v>4462</v>
@@ -8761,25 +8809,25 @@
         <v>46901</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
       <c r="N15" s="9">
         <v>29803</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>433</v>
+        <v>449</v>
       </c>
       <c r="P15" s="9">
         <v>76704</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>434</v>
+        <v>450</v>
       </c>
       <c r="R15" s="9">
         <v>84855</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>505</v>
+        <v>521</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8802,7 +8850,7 @@
         <v>5509</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>506</v>
+        <v>522</v>
       </c>
       <c r="H16" s="9">
         <v>5867</v>
@@ -8820,25 +8868,25 @@
         <v>78420</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>435</v>
+        <v>451</v>
       </c>
       <c r="N16" s="9">
         <v>35195</v>
       </c>
       <c r="O16" s="10" t="s">
-        <v>439</v>
+        <v>455</v>
       </c>
       <c r="P16" s="9">
         <v>113615</v>
       </c>
       <c r="Q16" s="10" t="s">
-        <v>440</v>
+        <v>456</v>
       </c>
       <c r="R16" s="9">
         <v>124991</v>
       </c>
       <c r="S16" s="10" t="s">
-        <v>507</v>
+        <v>523</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8861,7 +8909,7 @@
         <v>7274</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>508</v>
+        <v>524</v>
       </c>
       <c r="H17" s="9">
         <v>5678</v>
@@ -8879,25 +8927,25 @@
         <v>53838</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>441</v>
+        <v>457</v>
       </c>
       <c r="N17" s="9">
         <v>30539</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="P17" s="9">
         <v>84377</v>
       </c>
       <c r="Q17" s="10" t="s">
-        <v>445</v>
+        <v>461</v>
       </c>
       <c r="R17" s="9">
         <v>97329</v>
       </c>
       <c r="S17" s="10" t="s">
-        <v>509</v>
+        <v>525</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8920,7 +8968,7 @@
         <v>3096</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>510</v>
+        <v>526</v>
       </c>
       <c r="H18" s="9">
         <v>3794</v>
@@ -8938,25 +8986,25 @@
         <v>37570</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>446</v>
+        <v>462</v>
       </c>
       <c r="N18" s="9">
         <v>22465</v>
       </c>
       <c r="O18" s="10" t="s">
-        <v>450</v>
+        <v>466</v>
       </c>
       <c r="P18" s="9">
         <v>60035</v>
       </c>
       <c r="Q18" s="10" t="s">
-        <v>451</v>
+        <v>467</v>
       </c>
       <c r="R18" s="9">
         <v>66925</v>
       </c>
       <c r="S18" s="10" t="s">
-        <v>511</v>
+        <v>527</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8979,7 +9027,7 @@
         <v>4195</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>512</v>
+        <v>528</v>
       </c>
       <c r="H19" s="9">
         <v>4264</v>
@@ -8997,25 +9045,25 @@
         <v>56908</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>452</v>
+        <v>468</v>
       </c>
       <c r="N19" s="9">
         <v>31976</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>456</v>
+        <v>472</v>
       </c>
       <c r="P19" s="9">
         <v>88884</v>
       </c>
       <c r="Q19" s="10" t="s">
-        <v>457</v>
+        <v>473</v>
       </c>
       <c r="R19" s="9">
         <v>97343</v>
       </c>
       <c r="S19" s="10" t="s">
-        <v>513</v>
+        <v>529</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9038,7 +9086,7 @@
         <v>1189</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>514</v>
+        <v>530</v>
       </c>
       <c r="H20" s="9">
         <v>1710</v>
@@ -9056,25 +9104,25 @@
         <v>27445</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>458</v>
+        <v>474</v>
       </c>
       <c r="N20" s="9">
         <v>13408</v>
       </c>
       <c r="O20" s="10" t="s">
-        <v>461</v>
+        <v>477</v>
       </c>
       <c r="P20" s="9">
         <v>40853</v>
       </c>
       <c r="Q20" s="10" t="s">
-        <v>462</v>
+        <v>478</v>
       </c>
       <c r="R20" s="9">
         <v>43752</v>
       </c>
       <c r="S20" s="10" t="s">
-        <v>515</v>
+        <v>531</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9097,7 +9145,7 @@
         <v>8847</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>516</v>
+        <v>532</v>
       </c>
       <c r="H21" s="9">
         <v>13703</v>
@@ -9115,25 +9163,25 @@
         <v>2805</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>463</v>
+        <v>479</v>
       </c>
       <c r="N21" s="9">
         <v>37761</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>467</v>
+        <v>483</v>
       </c>
       <c r="P21" s="9">
         <v>40566</v>
       </c>
       <c r="Q21" s="10" t="s">
-        <v>468</v>
+        <v>484</v>
       </c>
       <c r="R21" s="9">
         <v>63116</v>
       </c>
       <c r="S21" s="10" t="s">
-        <v>517</v>
+        <v>533</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9156,7 +9204,7 @@
         <v>3650</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>518</v>
+        <v>534</v>
       </c>
       <c r="H22" s="9">
         <v>3029</v>
@@ -9174,33 +9222,33 @@
         <v>10418</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>469</v>
+        <v>485</v>
       </c>
       <c r="N22" s="9">
         <v>8394</v>
       </c>
       <c r="O22" s="10" t="s">
-        <v>473</v>
+        <v>489</v>
       </c>
       <c r="P22" s="9">
         <v>18812</v>
       </c>
       <c r="Q22" s="10" t="s">
-        <v>474</v>
+        <v>490</v>
       </c>
       <c r="R22" s="9">
         <v>25491</v>
       </c>
       <c r="S22" s="10" t="s">
-        <v>519</v>
+        <v>535</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B23" s="11" t="s">
         <v>103</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>104</v>
       </c>
       <c r="C23" s="12">
         <v>760551</v>
@@ -9215,48 +9263,48 @@
         <v>84171</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>488</v>
+        <v>504</v>
       </c>
       <c r="H23" s="12">
         <v>110664</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J23" s="12">
         <v>194835</v>
       </c>
       <c r="K23" s="13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L23" s="12">
         <v>1003864</v>
       </c>
       <c r="M23" s="13" t="s">
-        <v>385</v>
+        <v>401</v>
       </c>
       <c r="N23" s="12">
         <v>702163</v>
       </c>
       <c r="O23" s="13" t="s">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="P23" s="12">
         <v>1706027</v>
       </c>
       <c r="Q23" s="13" t="s">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="R23" s="12">
         <v>1900862</v>
       </c>
       <c r="S23" s="13" t="s">
-        <v>489</v>
+        <v>505</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B25" s="14"/>
       <c r="C25" s="14"/>
@@ -9279,10 +9327,10 @@
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>520</v>
+        <v>536</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>521</v>
+        <v>537</v>
       </c>
       <c r="C26" s="16"/>
       <c r="D26" s="16"/>
@@ -9304,10 +9352,10 @@
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
-        <v>522</v>
+        <v>538</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>523</v>
+        <v>539</v>
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
@@ -9329,10 +9377,10 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
-        <v>524</v>
+        <v>540</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>525</v>
+        <v>541</v>
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="16"/>
@@ -9354,10 +9402,10 @@
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>526</v>
+        <v>542</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>527</v>
+        <v>543</v>
       </c>
       <c r="C29" s="16"/>
       <c r="D29" s="16"/>
@@ -9379,10 +9427,10 @@
     </row>
     <row r="30" ht="24" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
-        <v>528</v>
+        <v>544</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>529</v>
+        <v>545</v>
       </c>
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
@@ -9443,7 +9491,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>530</v>
+        <v>546</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -9471,19 +9519,19 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>531</v>
+        <v>547</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>304</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>532</v>
+        <v>548</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>533</v>
+        <v>549</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>534</v>
+        <v>550</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -9523,13 +9571,13 @@
         <v>194835</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>535</v>
+        <v>551</v>
       </c>
       <c r="F6" s="6">
         <v>1706027</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>536</v>
+        <v>552</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -9546,13 +9594,13 @@
         <v>4043</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>537</v>
+        <v>553</v>
       </c>
       <c r="F7" s="9">
         <v>90725</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>538</v>
+        <v>554</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -9575,7 +9623,7 @@
         <v>131059</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>539</v>
+        <v>555</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -9592,13 +9640,13 @@
         <v>17964</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>540</v>
+        <v>556</v>
       </c>
       <c r="F9" s="9">
         <v>132850</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>541</v>
+        <v>557</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -9615,13 +9663,13 @@
         <v>29337</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>542</v>
+        <v>558</v>
       </c>
       <c r="F10" s="9">
         <v>286122</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>543</v>
+        <v>559</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -9638,13 +9686,13 @@
         <v>34110</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>544</v>
+        <v>560</v>
       </c>
       <c r="F11" s="9">
         <v>329690</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>545</v>
+        <v>561</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -9661,13 +9709,13 @@
         <v>11863</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>546</v>
+        <v>562</v>
       </c>
       <c r="F12" s="9">
         <v>106233</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>547</v>
+        <v>563</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -9684,13 +9732,13 @@
         <v>7504</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>548</v>
+        <v>564</v>
       </c>
       <c r="F13" s="9">
         <v>105502</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>549</v>
+        <v>565</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -9707,13 +9755,13 @@
         <v>8151</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>550</v>
+        <v>566</v>
       </c>
       <c r="F14" s="9">
         <v>76704</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>551</v>
+        <v>567</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -9736,7 +9784,7 @@
         <v>113615</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>552</v>
+        <v>568</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -9753,13 +9801,13 @@
         <v>12952</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>553</v>
+        <v>569</v>
       </c>
       <c r="F16" s="9">
         <v>84377</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>554</v>
+        <v>570</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -9776,13 +9824,13 @@
         <v>6890</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>555</v>
+        <v>571</v>
       </c>
       <c r="F17" s="9">
         <v>60035</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>556</v>
+        <v>572</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -9799,13 +9847,13 @@
         <v>8459</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>557</v>
+        <v>573</v>
       </c>
       <c r="F18" s="9">
         <v>88884</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>558</v>
+        <v>574</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -9822,13 +9870,13 @@
         <v>2899</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>559</v>
+        <v>575</v>
       </c>
       <c r="F19" s="9">
         <v>40853</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>560</v>
+        <v>576</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -9845,13 +9893,13 @@
         <v>22550</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>561</v>
+        <v>577</v>
       </c>
       <c r="F20" s="9">
         <v>40566</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>340</v>
+        <v>578</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -9868,21 +9916,21 @@
         <v>6679</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>562</v>
+        <v>579</v>
       </c>
       <c r="F21" s="9">
         <v>18812</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>563</v>
+        <v>580</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B22" s="11" t="s">
         <v>103</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>104</v>
       </c>
       <c r="C22" s="12">
         <v>3112785</v>
@@ -9891,18 +9939,18 @@
         <v>194835</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>535</v>
+        <v>551</v>
       </c>
       <c r="F22" s="12">
         <v>1706027</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>536</v>
+        <v>552</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B24" s="14"/>
       <c r="C24" s="14"/>
@@ -9913,10 +9961,10 @@
     </row>
     <row r="25" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
-        <v>564</v>
+        <v>581</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>565</v>
+        <v>582</v>
       </c>
       <c r="C25" s="16"/>
       <c r="D25" s="16"/>
@@ -9949,7 +9997,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>566</v>
+        <v>583</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -9979,7 +10027,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>567</v>
+        <v>584</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -9991,22 +10039,22 @@
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3" t="s">
-        <v>568</v>
+        <v>585</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>569</v>
+        <v>586</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>570</v>
+        <v>587</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>571</v>
+        <v>588</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>572</v>
+        <v>589</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>573</v>
+        <v>590</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10453,10 +10501,10 @@
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B23" s="11" t="s">
         <v>103</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>104</v>
       </c>
       <c r="C23" s="12">
         <v>1892307</v>
@@ -10511,7 +10559,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>574</v>
+        <v>591</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -10559,16 +10607,16 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>576</v>
+        <v>593</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>577</v>
+        <v>594</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
@@ -10576,7 +10624,7 @@
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3" t="s">
-        <v>479</v>
+        <v>495</v>
       </c>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -10591,22 +10639,22 @@
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>579</v>
+        <v>596</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3" t="s">
-        <v>580</v>
+        <v>597</v>
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3" t="s">
-        <v>579</v>
+        <v>596</v>
       </c>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3" t="s">
-        <v>580</v>
+        <v>597</v>
       </c>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
@@ -10618,40 +10666,40 @@
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>581</v>
+        <v>598</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>582</v>
+        <v>599</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>583</v>
+        <v>600</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>584</v>
+        <v>601</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>585</v>
+        <v>602</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>587</v>
+        <v>604</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>588</v>
+        <v>605</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>589</v>
+        <v>606</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>590</v>
+        <v>607</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>591</v>
+        <v>608</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>592</v>
+        <v>609</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -10686,25 +10734,25 @@
         <v>22</v>
       </c>
       <c r="K7" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="L7" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="L7" s="4" t="s">
+      <c r="M7" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="M7" s="4" t="s">
+      <c r="N7" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="N7" s="4" t="s">
+      <c r="O7" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="O7" s="4" t="s">
+      <c r="P7" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="P7" s="4" t="s">
+      <c r="Q7" s="4" t="s">
         <v>154</v>
-      </c>
-      <c r="Q7" s="4" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -10724,40 +10772,40 @@
         <v>2027897</v>
       </c>
       <c r="F8" s="6">
-        <v>1488</v>
+        <v>1501</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>593</v>
+        <v>610</v>
       </c>
       <c r="H8" s="6">
-        <v>82683</v>
+        <v>83473</v>
       </c>
       <c r="I8" s="6">
-        <v>4644</v>
+        <v>4690</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>594</v>
+        <v>611</v>
       </c>
       <c r="K8" s="6">
-        <v>106020</v>
+        <v>107089</v>
       </c>
       <c r="L8" s="6">
-        <v>935020</v>
+        <v>941223</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>536</v>
+        <v>612</v>
       </c>
       <c r="N8" s="6">
-        <v>68844</v>
+        <v>69292</v>
       </c>
       <c r="O8" s="6">
-        <v>417649</v>
+        <v>420074</v>
       </c>
       <c r="P8" s="7" t="s">
-        <v>595</v>
+        <v>613</v>
       </c>
       <c r="Q8" s="6">
-        <v>284514</v>
+        <v>286647</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -10780,37 +10828,37 @@
         <v>19</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>596</v>
+        <v>614</v>
       </c>
       <c r="H9" s="9">
-        <v>1971</v>
+        <v>1978</v>
       </c>
       <c r="I9" s="9">
         <v>130</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>597</v>
+        <v>615</v>
       </c>
       <c r="K9" s="9">
-        <v>1923</v>
+        <v>1929</v>
       </c>
       <c r="L9" s="9">
-        <v>51684</v>
+        <v>51847</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>598</v>
+        <v>616</v>
       </c>
       <c r="N9" s="9">
-        <v>8323</v>
+        <v>8348</v>
       </c>
       <c r="O9" s="9">
-        <v>23424</v>
+        <v>23505</v>
       </c>
       <c r="P9" s="10" t="s">
-        <v>599</v>
+        <v>617</v>
       </c>
       <c r="Q9" s="9">
-        <v>7294</v>
+        <v>7319</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -10833,37 +10881,37 @@
         <v>122</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>600</v>
+        <v>618</v>
       </c>
       <c r="H10" s="9">
-        <v>4745</v>
+        <v>4774</v>
       </c>
       <c r="I10" s="9">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>601</v>
+        <v>619</v>
       </c>
       <c r="K10" s="9">
-        <v>4854</v>
+        <v>4894</v>
       </c>
       <c r="L10" s="9">
-        <v>74174</v>
+        <v>74568</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>602</v>
+        <v>620</v>
       </c>
       <c r="N10" s="9">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="O10" s="9">
-        <v>32832</v>
+        <v>32971</v>
       </c>
       <c r="P10" s="10" t="s">
-        <v>603</v>
+        <v>621</v>
       </c>
       <c r="Q10" s="9">
-        <v>23658</v>
+        <v>23843</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -10883,40 +10931,40 @@
         <v>202453</v>
       </c>
       <c r="F11" s="9">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>604</v>
+        <v>622</v>
       </c>
       <c r="H11" s="9">
-        <v>5198</v>
+        <v>5249</v>
       </c>
       <c r="I11" s="9">
-        <v>1081</v>
+        <v>1091</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>605</v>
+        <v>183</v>
       </c>
       <c r="K11" s="9">
-        <v>11493</v>
+        <v>11624</v>
       </c>
       <c r="L11" s="9">
-        <v>71091</v>
+        <v>71550</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>606</v>
+        <v>623</v>
       </c>
       <c r="N11" s="9">
         <v>466</v>
       </c>
       <c r="O11" s="9">
-        <v>29833</v>
+        <v>29987</v>
       </c>
       <c r="P11" s="10" t="s">
-        <v>607</v>
+        <v>624</v>
       </c>
       <c r="Q11" s="9">
-        <v>31460</v>
+        <v>31660</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -10936,40 +10984,40 @@
         <v>347651</v>
       </c>
       <c r="F12" s="9">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>608</v>
+        <v>625</v>
       </c>
       <c r="H12" s="9">
-        <v>13757</v>
+        <v>13870</v>
       </c>
       <c r="I12" s="9">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>609</v>
+        <v>626</v>
       </c>
       <c r="K12" s="9">
-        <v>14859</v>
+        <v>15015</v>
       </c>
       <c r="L12" s="9">
-        <v>164805</v>
+        <v>165904</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>610</v>
+        <v>627</v>
       </c>
       <c r="N12" s="9">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="O12" s="9">
-        <v>73249</v>
+        <v>73701</v>
       </c>
       <c r="P12" s="10" t="s">
-        <v>611</v>
+        <v>628</v>
       </c>
       <c r="Q12" s="9">
-        <v>47080</v>
+        <v>47407</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -10989,40 +11037,40 @@
         <v>416503</v>
       </c>
       <c r="F13" s="9">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>612</v>
+        <v>629</v>
       </c>
       <c r="H13" s="9">
-        <v>13144</v>
+        <v>13285</v>
       </c>
       <c r="I13" s="9">
-        <v>660</v>
+        <v>671</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>613</v>
+        <v>630</v>
       </c>
       <c r="K13" s="9">
-        <v>19912</v>
+        <v>20186</v>
       </c>
       <c r="L13" s="9">
-        <v>199050</v>
+        <v>200601</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>614</v>
+        <v>631</v>
       </c>
       <c r="N13" s="9">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="O13" s="9">
-        <v>85385</v>
+        <v>86007</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>615</v>
+        <v>632</v>
       </c>
       <c r="Q13" s="9">
-        <v>44582</v>
+        <v>44936</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -11042,40 +11090,40 @@
         <v>128482</v>
       </c>
       <c r="F14" s="9">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>616</v>
+        <v>633</v>
       </c>
       <c r="H14" s="9">
-        <v>4426</v>
+        <v>4474</v>
       </c>
       <c r="I14" s="9">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>617</v>
+        <v>634</v>
       </c>
       <c r="K14" s="9">
-        <v>7122</v>
+        <v>7182</v>
       </c>
       <c r="L14" s="9">
-        <v>59214</v>
+        <v>59728</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="N14" s="9">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="O14" s="9">
-        <v>27702</v>
+        <v>27883</v>
       </c>
       <c r="P14" s="10" t="s">
-        <v>433</v>
+        <v>636</v>
       </c>
       <c r="Q14" s="9">
-        <v>19104</v>
+        <v>19261</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -11098,37 +11146,37 @@
         <v>62</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>619</v>
+        <v>637</v>
       </c>
       <c r="H15" s="9">
-        <v>2240</v>
+        <v>2260</v>
       </c>
       <c r="I15" s="9">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>620</v>
+        <v>638</v>
       </c>
       <c r="K15" s="9">
-        <v>4875</v>
+        <v>4935</v>
       </c>
       <c r="L15" s="9">
-        <v>58168</v>
+        <v>58618</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>621</v>
+        <v>639</v>
       </c>
       <c r="N15" s="9">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O15" s="9">
-        <v>30809</v>
+        <v>31012</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>622</v>
+        <v>640</v>
       </c>
       <c r="Q15" s="9">
-        <v>16210</v>
+        <v>16316</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -11148,40 +11196,40 @@
         <v>95779</v>
       </c>
       <c r="F16" s="9">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>241</v>
+        <v>296</v>
       </c>
       <c r="H16" s="9">
-        <v>3670</v>
+        <v>3725</v>
       </c>
       <c r="I16" s="9">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>623</v>
+        <v>641</v>
       </c>
       <c r="K16" s="9">
-        <v>4192</v>
+        <v>4251</v>
       </c>
       <c r="L16" s="9">
-        <v>38966</v>
+        <v>39426</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>624</v>
+        <v>642</v>
       </c>
       <c r="N16" s="9">
-        <v>7935</v>
+        <v>8032</v>
       </c>
       <c r="O16" s="9">
-        <v>21156</v>
+        <v>21361</v>
       </c>
       <c r="P16" s="10" t="s">
-        <v>625</v>
+        <v>643</v>
       </c>
       <c r="Q16" s="9">
-        <v>8647</v>
+        <v>8761</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -11204,37 +11252,37 @@
         <v>60</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>626</v>
+        <v>644</v>
       </c>
       <c r="H17" s="9">
-        <v>5449</v>
+        <v>5496</v>
       </c>
       <c r="I17" s="9">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>627</v>
+        <v>645</v>
       </c>
       <c r="K17" s="9">
-        <v>5694</v>
+        <v>5725</v>
       </c>
       <c r="L17" s="9">
-        <v>63148</v>
+        <v>63498</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>628</v>
+        <v>646</v>
       </c>
       <c r="N17" s="9">
-        <v>15272</v>
+        <v>15358</v>
       </c>
       <c r="O17" s="9">
-        <v>22392</v>
+        <v>22474</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>629</v>
+        <v>647</v>
       </c>
       <c r="Q17" s="9">
-        <v>12803</v>
+        <v>12861</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -11260,34 +11308,34 @@
         <v>296</v>
       </c>
       <c r="H18" s="9">
-        <v>7242</v>
+        <v>7299</v>
       </c>
       <c r="I18" s="9">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J18" s="10" t="s">
         <v>210</v>
       </c>
       <c r="K18" s="9">
-        <v>5343</v>
+        <v>5374</v>
       </c>
       <c r="L18" s="9">
-        <v>41435</v>
+        <v>41693</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>630</v>
+        <v>648</v>
       </c>
       <c r="N18" s="9">
-        <v>12403</v>
+        <v>12489</v>
       </c>
       <c r="O18" s="9">
-        <v>17357</v>
+        <v>17478</v>
       </c>
       <c r="P18" s="10" t="s">
-        <v>631</v>
+        <v>649</v>
       </c>
       <c r="Q18" s="9">
-        <v>13182</v>
+        <v>13262</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -11307,40 +11355,40 @@
         <v>71663</v>
       </c>
       <c r="F19" s="9">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>632</v>
+        <v>459</v>
       </c>
       <c r="H19" s="9">
-        <v>3060</v>
+        <v>3077</v>
       </c>
       <c r="I19" s="9">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>233</v>
+        <v>650</v>
       </c>
       <c r="K19" s="9">
-        <v>3316</v>
+        <v>3329</v>
       </c>
       <c r="L19" s="9">
-        <v>32642</v>
+        <v>32736</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>633</v>
+        <v>651</v>
       </c>
       <c r="N19" s="9">
-        <v>4928</v>
+        <v>4951</v>
       </c>
       <c r="O19" s="9">
-        <v>16470</v>
+        <v>16516</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>634</v>
+        <v>652</v>
       </c>
       <c r="Q19" s="9">
-        <v>5995</v>
+        <v>6015</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -11360,40 +11408,40 @@
         <v>88014</v>
       </c>
       <c r="F20" s="9">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>420</v>
+        <v>272</v>
       </c>
       <c r="H20" s="9">
-        <v>4177</v>
+        <v>4234</v>
       </c>
       <c r="I20" s="9">
         <v>98</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>612</v>
+        <v>629</v>
       </c>
       <c r="K20" s="9">
-        <v>4166</v>
+        <v>4225</v>
       </c>
       <c r="L20" s="9">
-        <v>49493</v>
+        <v>49763</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>635</v>
+        <v>653</v>
       </c>
       <c r="N20" s="9">
-        <v>7415</v>
+        <v>7484</v>
       </c>
       <c r="O20" s="9">
-        <v>24270</v>
+        <v>24359</v>
       </c>
       <c r="P20" s="10" t="s">
-        <v>636</v>
+        <v>654</v>
       </c>
       <c r="Q20" s="9">
-        <v>7706</v>
+        <v>7757</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -11416,37 +11464,37 @@
         <v>10</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>637</v>
+        <v>655</v>
       </c>
       <c r="H21" s="9">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="I21" s="9">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>638</v>
+        <v>656</v>
       </c>
       <c r="K21" s="9">
-        <v>1647</v>
+        <v>1662</v>
       </c>
       <c r="L21" s="9">
-        <v>23235</v>
+        <v>23311</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>639</v>
+        <v>570</v>
       </c>
       <c r="N21" s="9">
-        <v>4210</v>
+        <v>4223</v>
       </c>
       <c r="O21" s="9">
-        <v>9751</v>
+        <v>9778</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>640</v>
+        <v>657</v>
       </c>
       <c r="Q21" s="9">
-        <v>3657</v>
+        <v>3666</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -11466,40 +11514,40 @@
         <v>12256</v>
       </c>
       <c r="F22" s="9">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>641</v>
+        <v>436</v>
       </c>
       <c r="H22" s="9">
-        <v>8801</v>
+        <v>8909</v>
       </c>
       <c r="I22" s="9">
         <v>96</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>399</v>
+        <v>415</v>
       </c>
       <c r="K22" s="9">
-        <v>13607</v>
+        <v>13719</v>
       </c>
       <c r="L22" s="9">
-        <v>2659</v>
+        <v>2685</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>642</v>
+        <v>658</v>
       </c>
       <c r="N22" s="9">
         <v>146</v>
       </c>
       <c r="O22" s="9">
-        <v>998</v>
+        <v>1005</v>
       </c>
       <c r="P22" s="10" t="s">
-        <v>643</v>
+        <v>659</v>
       </c>
       <c r="Q22" s="9">
-        <v>36763</v>
+        <v>37164</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -11522,45 +11570,45 @@
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>644</v>
+        <v>660</v>
       </c>
       <c r="H23" s="9">
-        <v>3624</v>
+        <v>3662</v>
       </c>
       <c r="I23" s="9">
         <v>12</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>405</v>
+        <v>421</v>
       </c>
       <c r="K23" s="9">
-        <v>3017</v>
+        <v>3039</v>
       </c>
       <c r="L23" s="9">
-        <v>5256</v>
+        <v>5295</v>
       </c>
       <c r="M23" s="10" t="s">
-        <v>645</v>
+        <v>661</v>
       </c>
       <c r="N23" s="9">
-        <v>5162</v>
+        <v>5202</v>
       </c>
       <c r="O23" s="9">
-        <v>2021</v>
+        <v>2037</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>646</v>
+        <v>662</v>
       </c>
       <c r="Q23" s="9">
-        <v>6373</v>
+        <v>6419</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" s="11" t="s">
         <v>103</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>104</v>
       </c>
       <c r="C24" s="12">
         <v>760551</v>
@@ -11572,45 +11620,45 @@
         <v>2027897</v>
       </c>
       <c r="F24" s="12">
-        <v>1488</v>
+        <v>1501</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>593</v>
+        <v>610</v>
       </c>
       <c r="H24" s="12">
-        <v>82683</v>
+        <v>83473</v>
       </c>
       <c r="I24" s="12">
-        <v>4644</v>
+        <v>4690</v>
       </c>
       <c r="J24" s="13" t="s">
-        <v>594</v>
+        <v>611</v>
       </c>
       <c r="K24" s="12">
-        <v>106020</v>
+        <v>107089</v>
       </c>
       <c r="L24" s="12">
-        <v>935020</v>
+        <v>941223</v>
       </c>
       <c r="M24" s="13" t="s">
-        <v>536</v>
+        <v>612</v>
       </c>
       <c r="N24" s="12">
-        <v>68844</v>
+        <v>69292</v>
       </c>
       <c r="O24" s="12">
-        <v>417649</v>
+        <v>420074</v>
       </c>
       <c r="P24" s="13" t="s">
-        <v>595</v>
+        <v>613</v>
       </c>
       <c r="Q24" s="12">
-        <v>284514</v>
+        <v>286647</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -11631,10 +11679,10 @@
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
-        <v>647</v>
+        <v>663</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>648</v>
+        <v>664</v>
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
@@ -11654,10 +11702,10 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
-        <v>649</v>
+        <v>665</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>650</v>
+        <v>666</v>
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="16"/>
@@ -11677,10 +11725,10 @@
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>651</v>
+        <v>667</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>652</v>
+        <v>668</v>
       </c>
       <c r="C29" s="16"/>
       <c r="D29" s="16"/>
@@ -11700,10 +11748,10 @@
     </row>
     <row r="30" ht="24" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
-        <v>653</v>
+        <v>669</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>654</v>
+        <v>670</v>
       </c>
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>

--- a/data/Export_Progres_Pendataan_Kabupaten_Kota.xlsx
+++ b/data/Export_Progres_Pendataan_Kabupaten_Kota.xlsx
@@ -18,12 +18,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1402" uniqueCount="671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1402" uniqueCount="684">
   <si>
     <t>PROGRES PENDATAAN - PROGRES PENDATAAN</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 18 Agu 2026, 18.00 | Dicetak: 18 Agu 2026, 20.52</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 19 Agu 2026, 06.00 | Dicetak: 19 Agu 2026, 14.10</t>
   </si>
   <si>
     <t>Kode</t>
@@ -122,13 +122,13 @@
     <t>LAMPUNG</t>
   </si>
   <si>
-    <t>108,53</t>
-  </si>
-  <si>
-    <t>65,71</t>
-  </si>
-  <si>
-    <t>4,96</t>
+    <t>109,21</t>
+  </si>
+  <si>
+    <t>66,13</t>
+  </si>
+  <si>
+    <t>4,72</t>
   </si>
   <si>
     <t>1801</t>
@@ -137,13 +137,13 @@
     <t>LAMPUNG BARAT</t>
   </si>
   <si>
-    <t>124,36</t>
-  </si>
-  <si>
-    <t>84,64</t>
-  </si>
-  <si>
-    <t>1,62</t>
+    <t>124,65</t>
+  </si>
+  <si>
+    <t>84,86</t>
+  </si>
+  <si>
+    <t>1,49</t>
   </si>
   <si>
     <t>1802</t>
@@ -152,13 +152,13 @@
     <t>TANGGAMUS</t>
   </si>
   <si>
-    <t>107,44</t>
-  </si>
-  <si>
-    <t>67,82</t>
-  </si>
-  <si>
-    <t>7,13</t>
+    <t>108,14</t>
+  </si>
+  <si>
+    <t>68,26</t>
+  </si>
+  <si>
+    <t>6,84</t>
   </si>
   <si>
     <t>1803</t>
@@ -167,13 +167,13 @@
     <t>LAMPUNG SELATAN</t>
   </si>
   <si>
-    <t>105,22</t>
-  </si>
-  <si>
-    <t>59,98</t>
-  </si>
-  <si>
-    <t>6,12</t>
+    <t>106,1</t>
+  </si>
+  <si>
+    <t>60,5</t>
+  </si>
+  <si>
+    <t>5,82</t>
   </si>
   <si>
     <t>1804</t>
@@ -182,13 +182,13 @@
     <t>LAMPUNG TIMUR</t>
   </si>
   <si>
-    <t>103,94</t>
-  </si>
-  <si>
-    <t>63,96</t>
-  </si>
-  <si>
-    <t>4,38</t>
+    <t>104,46</t>
+  </si>
+  <si>
+    <t>64,31</t>
+  </si>
+  <si>
+    <t>4,22</t>
   </si>
   <si>
     <t>1805</t>
@@ -197,13 +197,13 @@
     <t>LAMPUNG TENGAH</t>
   </si>
   <si>
-    <t>104,8</t>
-  </si>
-  <si>
-    <t>64,43</t>
-  </si>
-  <si>
-    <t>5,4</t>
+    <t>105,53</t>
+  </si>
+  <si>
+    <t>64,89</t>
+  </si>
+  <si>
+    <t>5,14</t>
   </si>
   <si>
     <t>1806</t>
@@ -212,13 +212,13 @@
     <t>LAMPUNG UTARA</t>
   </si>
   <si>
-    <t>111,74</t>
-  </si>
-  <si>
-    <t>63,87</t>
-  </si>
-  <si>
-    <t>2,87</t>
+    <t>112,52</t>
+  </si>
+  <si>
+    <t>64,37</t>
+  </si>
+  <si>
+    <t>2,66</t>
   </si>
   <si>
     <t>1807</t>
@@ -227,13 +227,13 @@
     <t>WAY KANAN</t>
   </si>
   <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>65,51</t>
-  </si>
-  <si>
-    <t>5,03</t>
+    <t>109,84</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>4,84</t>
   </si>
   <si>
     <t>1808</t>
@@ -242,1630 +242,1780 @@
     <t>TULANG BAWANG</t>
   </si>
   <si>
-    <t>109,94</t>
-  </si>
-  <si>
-    <t>65,5</t>
+    <t>110,83</t>
+  </si>
+  <si>
+    <t>66,08</t>
+  </si>
+  <si>
+    <t>5,63</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>PESAWARAN</t>
+  </si>
+  <si>
+    <t>120,81</t>
+  </si>
+  <si>
+    <t>82,04</t>
+  </si>
+  <si>
+    <t>3,27</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>PRINGSEWU</t>
+  </si>
+  <si>
+    <t>108,9</t>
+  </si>
+  <si>
+    <t>77,01</t>
+  </si>
+  <si>
+    <t>6,66</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>MESUJI</t>
+  </si>
+  <si>
+    <t>132,51</t>
+  </si>
+  <si>
+    <t>86,74</t>
+  </si>
+  <si>
+    <t>0,26</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG BARAT</t>
+  </si>
+  <si>
+    <t>127,15</t>
+  </si>
+  <si>
+    <t>85,75</t>
+  </si>
+  <si>
+    <t>1,56</t>
+  </si>
+  <si>
+    <t>1813</t>
+  </si>
+  <si>
+    <t>PESISIR BARAT</t>
+  </si>
+  <si>
+    <t>129,43</t>
+  </si>
+  <si>
+    <t>93,5</t>
+  </si>
+  <si>
+    <t>0,83</t>
+  </si>
+  <si>
+    <t>1871</t>
+  </si>
+  <si>
+    <t>BANDAR LAMPUNG</t>
+  </si>
+  <si>
+    <t>101,27</t>
+  </si>
+  <si>
+    <t>48,46</t>
+  </si>
+  <si>
+    <t>5,89</t>
+  </si>
+  <si>
+    <t>1872</t>
+  </si>
+  <si>
+    <t>METRO</t>
+  </si>
+  <si>
+    <t>105,61</t>
+  </si>
+  <si>
+    <t>64,38</t>
+  </si>
+  <si>
+    <t>6,14</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Catatan</t>
+  </si>
+  <si>
+    <t>Jumlah prelist terkini pada FASIH bersifat dinamis menyesuaikan perpindahan wilayah assignment.</t>
+  </si>
+  <si>
+    <t>Jumlah hasil verifikasi lapangan assignment usaha dan keluarga yang tidak berstatus open atau draft, mencakup seluruh status keberadaan (ditemukan, tutup, ganda, tidak ditemukan, baru, dan lainnya).</t>
+  </si>
+  <si>
+    <t>Responden Didata (Usaha &amp; Keluarga Ditemukan/Baru/Force Submit)</t>
+  </si>
+  <si>
+    <t>Jumlah responden usaha BKU dan keluarga yang telah berhasil didata (selain status open/draft) dengan kriteria keberadaan ditemukan dan baru termasuk usaha BKU yang diklaim sebagai usaha keluarga (force submit).</t>
+  </si>
+  <si>
+    <t>Jumlah Responden Sedang Didata</t>
+  </si>
+  <si>
+    <t>Jumlah responden dengan status Draft.</t>
+  </si>
+  <si>
+    <t>PROGRES PENDATAAN - USAHA/PERUSAHAAN</t>
+  </si>
+  <si>
+    <t>Jumlah Prelist Usaha</t>
+  </si>
+  <si>
+    <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA</t>
+  </si>
+  <si>
+    <t>Total Usaha BKU (UM+UMK)</t>
+  </si>
+  <si>
+    <t>Persentase Total Usaha BKU (UM+UMK)</t>
+  </si>
+  <si>
+    <t>UMKM</t>
+  </si>
+  <si>
+    <t>Ditemukan/Pindah Dapat Ditelusuri</t>
+  </si>
+  <si>
+    <t>Persentase Ditemukan/Pindah Dapat Ditelusuri</t>
+  </si>
+  <si>
+    <t>Ditemukan Tetapi Bukan Cakupan Survei</t>
+  </si>
+  <si>
+    <t>Persentase Ditemukan Tetapi Bukan Cakupan Survei</t>
+  </si>
+  <si>
+    <t>Pindah Tidak Dapat Ditelusuri</t>
+  </si>
+  <si>
+    <t>Persentase Pindah Tidak Dapat Ditelusuri</t>
+  </si>
+  <si>
+    <t>Tutup</t>
+  </si>
+  <si>
+    <t>Persentase Tutup</t>
+  </si>
+  <si>
+    <t>Duplikat</t>
+  </si>
+  <si>
+    <t>Persentase Duplikat</t>
+  </si>
+  <si>
+    <t>Tidak Ditemukan</t>
+  </si>
+  <si>
+    <t>Persentase Tidak Ditemukan</t>
+  </si>
+  <si>
+    <t>Data Diperoleh dari Kantor Pusat</t>
+  </si>
+  <si>
+    <t>Persentase Data Diperoleh dari Kantor Pusat</t>
+  </si>
+  <si>
+    <t>Nonrespon</t>
+  </si>
+  <si>
+    <t>Persentase Nonrespon</t>
+  </si>
+  <si>
+    <t>Total UB</t>
+  </si>
+  <si>
+    <t>Persentase Total UB</t>
+  </si>
+  <si>
+    <t>Ditemukan</t>
+  </si>
+  <si>
+    <t>Persentase Ditemukan</t>
+  </si>
+  <si>
+    <t>Tutup​</t>
+  </si>
+  <si>
+    <t>Persentase Tutup​</t>
+  </si>
+  <si>
+    <t>Ganda</t>
+  </si>
+  <si>
+    <t>Persentase Ganda</t>
+  </si>
+  <si>
+    <t>Tidak Ditemukan​</t>
+  </si>
+  <si>
+    <t>Persentase Tidak Ditemukan​</t>
+  </si>
+  <si>
+    <t>Persentase Baru</t>
+  </si>
+  <si>
+    <t>Data Diperoleh dari Kantor Pusat​</t>
+  </si>
+  <si>
+    <t>Persentase Data Diperoleh dari Kantor Pusat​</t>
+  </si>
+  <si>
+    <t>Nonrespon​</t>
+  </si>
+  <si>
+    <t>Persentase Nonrespon​</t>
+  </si>
+  <si>
+    <t>Force Submit (Diklaim Sebagai Usaha Keluarga)</t>
+  </si>
+  <si>
+    <t>Persentase Force Submit (Diklaim Sebagai Usaha Keluarga)</t>
+  </si>
+  <si>
+    <t>Total UMKM</t>
+  </si>
+  <si>
+    <t>Persentase Total UMKM</t>
+  </si>
+  <si>
+    <t>(15)</t>
+  </si>
+  <si>
+    <t>(16)</t>
+  </si>
+  <si>
+    <t>(17)</t>
+  </si>
+  <si>
+    <t>(18)</t>
+  </si>
+  <si>
+    <t>(19)</t>
+  </si>
+  <si>
+    <t>(20)</t>
+  </si>
+  <si>
+    <t>(21)</t>
+  </si>
+  <si>
+    <t>(22)</t>
+  </si>
+  <si>
+    <t>(23)</t>
+  </si>
+  <si>
+    <t>(24)</t>
+  </si>
+  <si>
+    <t>(25)</t>
+  </si>
+  <si>
+    <t>(26)</t>
+  </si>
+  <si>
+    <t>(27)</t>
+  </si>
+  <si>
+    <t>(28)</t>
+  </si>
+  <si>
+    <t>(29)</t>
+  </si>
+  <si>
+    <t>(30)</t>
+  </si>
+  <si>
+    <t>(31)</t>
+  </si>
+  <si>
+    <t>(32)</t>
+  </si>
+  <si>
+    <t>(33)</t>
+  </si>
+  <si>
+    <t>(34)</t>
+  </si>
+  <si>
+    <t>(35)</t>
+  </si>
+  <si>
+    <t>(36)</t>
+  </si>
+  <si>
+    <t>(37)</t>
+  </si>
+  <si>
+    <t>(38)</t>
+  </si>
+  <si>
+    <t>(39)</t>
+  </si>
+  <si>
+    <t>(40)</t>
+  </si>
+  <si>
+    <t>(41)</t>
+  </si>
+  <si>
+    <t>0,15</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>0,01</t>
+  </si>
+  <si>
+    <t>0,02</t>
+  </si>
+  <si>
+    <t>11,14</t>
+  </si>
+  <si>
+    <t>16,98</t>
+  </si>
+  <si>
+    <t>7,67</t>
+  </si>
+  <si>
+    <t>43,01</t>
+  </si>
+  <si>
+    <t>14,88</t>
+  </si>
+  <si>
+    <t>6,23</t>
+  </si>
+  <si>
+    <t>26,02</t>
+  </si>
+  <si>
+    <t>26,17</t>
+  </si>
+  <si>
+    <t>0,19</t>
+  </si>
+  <si>
+    <t>0,03</t>
+  </si>
+  <si>
+    <t>16,6</t>
+  </si>
+  <si>
+    <t>16,58</t>
+  </si>
+  <si>
+    <t>12,66</t>
+  </si>
+  <si>
+    <t>41,72</t>
+  </si>
+  <si>
+    <t>17,35</t>
+  </si>
+  <si>
+    <t>1,52</t>
+  </si>
+  <si>
+    <t>33,95</t>
+  </si>
+  <si>
+    <t>34,14</t>
+  </si>
+  <si>
+    <t>0,09</t>
+  </si>
+  <si>
+    <t>0,05</t>
+  </si>
+  <si>
+    <t>8,52</t>
+  </si>
+  <si>
+    <t>21,7</t>
+  </si>
+  <si>
+    <t>15,11</t>
+  </si>
+  <si>
+    <t>26,37</t>
+  </si>
+  <si>
+    <t>9,24</t>
+  </si>
+  <si>
+    <t>10,1</t>
+  </si>
+  <si>
+    <t>17,76</t>
+  </si>
+  <si>
+    <t>17,85</t>
+  </si>
+  <si>
+    <t>0,14</t>
+  </si>
+  <si>
+    <t>5,77</t>
+  </si>
+  <si>
+    <t>11,29</t>
+  </si>
+  <si>
+    <t>3,99</t>
+  </si>
+  <si>
+    <t>61,04</t>
+  </si>
+  <si>
+    <t>13,81</t>
+  </si>
+  <si>
+    <t>2,71</t>
+  </si>
+  <si>
+    <t>19,58</t>
+  </si>
+  <si>
+    <t>19,72</t>
+  </si>
+  <si>
+    <t>0,06</t>
+  </si>
+  <si>
+    <t>11,21</t>
+  </si>
+  <si>
+    <t>21,74</t>
+  </si>
+  <si>
+    <t>7,59</t>
+  </si>
+  <si>
+    <t>33,06</t>
+  </si>
+  <si>
+    <t>12,27</t>
+  </si>
+  <si>
+    <t>11,07</t>
+  </si>
+  <si>
+    <t>23,48</t>
+  </si>
+  <si>
+    <t>23,54</t>
+  </si>
+  <si>
+    <t>10,45</t>
+  </si>
+  <si>
+    <t>18,75</t>
+  </si>
+  <si>
+    <t>9,08</t>
+  </si>
+  <si>
+    <t>44,43</t>
+  </si>
+  <si>
+    <t>16,1</t>
+  </si>
+  <si>
+    <t>5,99</t>
+  </si>
+  <si>
+    <t>26,55</t>
+  </si>
+  <si>
+    <t>26,64</t>
+  </si>
+  <si>
+    <t>0,08</t>
+  </si>
+  <si>
+    <t>7,18</t>
+  </si>
+  <si>
+    <t>14,95</t>
+  </si>
+  <si>
+    <t>5,19</t>
+  </si>
+  <si>
+    <t>57,86</t>
+  </si>
+  <si>
+    <t>11,69</t>
+  </si>
+  <si>
+    <t>7,19</t>
+  </si>
+  <si>
+    <t>18,86</t>
+  </si>
+  <si>
+    <t>18,94</t>
+  </si>
+  <si>
+    <t>5,62</t>
+  </si>
+  <si>
+    <t>20,82</t>
+  </si>
+  <si>
+    <t>6,11</t>
+  </si>
+  <si>
+    <t>44,65</t>
+  </si>
+  <si>
+    <t>12,96</t>
+  </si>
+  <si>
+    <t>9,52</t>
+  </si>
+  <si>
+    <t>18,59</t>
+  </si>
+  <si>
+    <t>18,67</t>
+  </si>
+  <si>
+    <t>0,23</t>
+  </si>
+  <si>
+    <t>19,22</t>
+  </si>
+  <si>
+    <t>12,39</t>
+  </si>
+  <si>
+    <t>4,49</t>
+  </si>
+  <si>
+    <t>41,51</t>
+  </si>
+  <si>
+    <t>23,58</t>
+  </si>
+  <si>
+    <t>0,95</t>
+  </si>
+  <si>
+    <t>42,81</t>
+  </si>
+  <si>
+    <t>43,04</t>
+  </si>
+  <si>
+    <t>30,16</t>
+  </si>
+  <si>
+    <t>14,12</t>
+  </si>
+  <si>
+    <t>5,15</t>
+  </si>
+  <si>
+    <t>35,96</t>
+  </si>
+  <si>
+    <t>32,28</t>
+  </si>
+  <si>
+    <t>2,08</t>
+  </si>
+  <si>
+    <t>62,44</t>
+  </si>
+  <si>
+    <t>62,7</t>
+  </si>
+  <si>
+    <t>33,51</t>
+  </si>
+  <si>
+    <t>13,28</t>
+  </si>
+  <si>
+    <t>3,29</t>
+  </si>
+  <si>
+    <t>28,84</t>
+  </si>
+  <si>
+    <t>26,15</t>
+  </si>
+  <si>
+    <t>1,59</t>
+  </si>
+  <si>
+    <t>59,66</t>
+  </si>
+  <si>
+    <t>59,8</t>
+  </si>
+  <si>
+    <t>0,24</t>
+  </si>
+  <si>
+    <t>27,95</t>
+  </si>
+  <si>
+    <t>19,02</t>
+  </si>
+  <si>
+    <t>12,15</t>
+  </si>
+  <si>
+    <t>27,98</t>
+  </si>
+  <si>
+    <t>34,55</t>
+  </si>
+  <si>
+    <t>0,89</t>
+  </si>
+  <si>
+    <t>62,5</t>
+  </si>
+  <si>
+    <t>62,74</t>
+  </si>
+  <si>
+    <t>0,22</t>
+  </si>
+  <si>
+    <t>43,12</t>
+  </si>
+  <si>
+    <t>4,78</t>
+  </si>
+  <si>
+    <t>19,11</t>
+  </si>
+  <si>
+    <t>44,04</t>
+  </si>
+  <si>
+    <t>1,75</t>
+  </si>
+  <si>
+    <t>87,16</t>
+  </si>
+  <si>
+    <t>87,39</t>
+  </si>
+  <si>
+    <t>0,17</t>
+  </si>
+  <si>
+    <t>22,04</t>
+  </si>
+  <si>
+    <t>16,75</t>
+  </si>
+  <si>
+    <t>40,59</t>
+  </si>
+  <si>
+    <t>32,16</t>
+  </si>
+  <si>
+    <t>1,17</t>
+  </si>
+  <si>
+    <t>54,2</t>
+  </si>
+  <si>
+    <t>54,37</t>
+  </si>
+  <si>
+    <t>0,3</t>
+  </si>
+  <si>
+    <t>0,04</t>
+  </si>
+  <si>
+    <t>6,62</t>
+  </si>
+  <si>
+    <t>13,46</t>
+  </si>
+  <si>
+    <t>7,01</t>
+  </si>
+  <si>
+    <t>47,68</t>
+  </si>
+  <si>
+    <t>10,7</t>
+  </si>
+  <si>
+    <t>5,27</t>
+  </si>
+  <si>
+    <t>17,31</t>
+  </si>
+  <si>
+    <t>17,61</t>
+  </si>
+  <si>
+    <t>0,25</t>
+  </si>
+  <si>
+    <t>21,83</t>
+  </si>
+  <si>
+    <t>19,17</t>
+  </si>
+  <si>
+    <t>18,2</t>
+  </si>
+  <si>
+    <t>20,81</t>
+  </si>
+  <si>
+    <t>18,12</t>
+  </si>
+  <si>
+    <t>1,67</t>
+  </si>
+  <si>
+    <t>39,95</t>
+  </si>
+  <si>
+    <t>40,21</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha BKU</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha yang Ditemukan dan Baru (UB + UMKM)</t>
+  </si>
+  <si>
+    <t>Persentase Kolom 4 21</t>
+  </si>
+  <si>
+    <t>Persentase hasil bagi jumlah usaha pada kolom tersebut dengan jumlah prelist usaha (kolom 3).</t>
+  </si>
+  <si>
+    <t>PROGRES PENDATAAN - SKALA USAHA</t>
+  </si>
+  <si>
+    <t>JUMLAH PRELIST</t>
+  </si>
+  <si>
+    <t>JUMLAH USAHA BKU MENURUT STATUS SKALA USAHA (UB, UM, UMK)</t>
+  </si>
+  <si>
+    <t>UB​</t>
+  </si>
+  <si>
+    <t>Persentase UB​</t>
+  </si>
+  <si>
+    <t>UM​</t>
+  </si>
+  <si>
+    <t>Persentase UM​</t>
+  </si>
+  <si>
+    <t>UMK​</t>
+  </si>
+  <si>
+    <t>Persentase UMK​</t>
+  </si>
+  <si>
+    <t>Tidak Dapat Diklasifikasikan</t>
+  </si>
+  <si>
+    <t>Total Usaha BKU</t>
+  </si>
+  <si>
+    <t>Persentase Total Usaha BKU</t>
+  </si>
+  <si>
+    <t>82,28</t>
+  </si>
+  <si>
+    <t>11,31</t>
+  </si>
+  <si>
+    <t>26,35</t>
+  </si>
+  <si>
+    <t>26,43</t>
+  </si>
+  <si>
+    <t>126,09</t>
+  </si>
+  <si>
+    <t>38,41</t>
+  </si>
+  <si>
+    <t>34,29</t>
+  </si>
+  <si>
+    <t>51,75</t>
+  </si>
+  <si>
+    <t>16,88</t>
+  </si>
+  <si>
+    <t>17,82</t>
+  </si>
+  <si>
+    <t>104,11</t>
+  </si>
+  <si>
+    <t>8,73</t>
+  </si>
+  <si>
+    <t>19,87</t>
+  </si>
+  <si>
+    <t>19,99</t>
+  </si>
+  <si>
+    <t>122,78</t>
+  </si>
+  <si>
+    <t>20,36</t>
+  </si>
+  <si>
+    <t>23,49</t>
+  </si>
+  <si>
+    <t>23,7</t>
+  </si>
+  <si>
+    <t>104,32</t>
+  </si>
+  <si>
+    <t>15,46</t>
+  </si>
+  <si>
+    <t>26,77</t>
+  </si>
+  <si>
+    <t>26,9</t>
+  </si>
+  <si>
+    <t>82,67</t>
+  </si>
+  <si>
+    <t>17,27</t>
+  </si>
+  <si>
+    <t>19,04</t>
+  </si>
+  <si>
+    <t>19,16</t>
+  </si>
+  <si>
+    <t>125,71</t>
+  </si>
+  <si>
+    <t>11,63</t>
+  </si>
+  <si>
+    <t>18,92</t>
+  </si>
+  <si>
+    <t>19,12</t>
+  </si>
+  <si>
+    <t>96,08</t>
+  </si>
+  <si>
+    <t>5,26</t>
+  </si>
+  <si>
+    <t>44,23</t>
+  </si>
+  <si>
+    <t>43,71</t>
+  </si>
+  <si>
+    <t>96,36</t>
+  </si>
+  <si>
+    <t>36,36</t>
+  </si>
+  <si>
+    <t>63,01</t>
+  </si>
+  <si>
+    <t>63,15</t>
+  </si>
+  <si>
+    <t>128,13</t>
+  </si>
+  <si>
+    <t>144,44</t>
+  </si>
+  <si>
+    <t>60,08</t>
+  </si>
+  <si>
+    <t>60,54</t>
+  </si>
+  <si>
+    <t>111,11</t>
+  </si>
+  <si>
+    <t>33,33</t>
+  </si>
+  <si>
+    <t>62,95</t>
+  </si>
+  <si>
+    <t>63,03</t>
+  </si>
+  <si>
+    <t>117,39</t>
+  </si>
+  <si>
+    <t>88,31</t>
+  </si>
+  <si>
+    <t>88,13</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>54,32</t>
+  </si>
+  <si>
+    <t>54,46</t>
+  </si>
+  <si>
+    <t>60,74</t>
+  </si>
+  <si>
+    <t>6,2</t>
+  </si>
+  <si>
+    <t>17,8</t>
+  </si>
+  <si>
+    <t>117,5</t>
+  </si>
+  <si>
+    <t>36,98</t>
+  </si>
+  <si>
+    <t>40,2</t>
+  </si>
+  <si>
+    <t>40,57</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha (UB/UM/UMK)</t>
+  </si>
+  <si>
+    <t>Jumlah prelist usaha yang berhasil didata (keberadaan ditemukan, baru, pindah dapat ditelusuri) berdasarkan skala usaha, untuk usaha baru didekati dengan omzet sebagai berikut: UB (lebih dari 50 Milyar), UM (15-50 Milyar), UMK - Kecil (2-15 Milyar), UMK - Mikro (0-2 Milyar).</t>
+  </si>
+  <si>
+    <t>Tidak Dapat Diklasifikasikan (Kolom 10)</t>
+  </si>
+  <si>
+    <t>Usaha baru dengan nilai omzet/pendapatan kosong sehingga tidak dapat diklasifikasikan skala usahanya, misalnya usaha unit pembantu/penunjang.</t>
+  </si>
+  <si>
+    <t>Persentase Jumlah UB</t>
+  </si>
+  <si>
+    <t>Persentase hasil bagi jumlah UB yang berhasil didata dengan jumlah prelist UB (kolom 3).</t>
+  </si>
+  <si>
+    <t>Persentase Jumlah UM</t>
+  </si>
+  <si>
+    <t>Persentase hasil bagi jumlah UM yang berhasil didata dengan jumlah prelist UM (kolom 4).</t>
+  </si>
+  <si>
+    <t>Persentase Jumlah UMK</t>
+  </si>
+  <si>
+    <t>Persentase hasil bagi jumlah UMK yang berhasil didata dengan jumlah prelist UMK (kolom 5).</t>
+  </si>
+  <si>
+    <t>PROGRES PENDATAAN - USAHA KELUARGA</t>
+  </si>
+  <si>
+    <t>Jumlah Prelist Usaha Keluarga (ST2023 + UMKM)</t>
+  </si>
+  <si>
+    <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha dalam Keluarga (Ditemukan + Baru)</t>
+  </si>
+  <si>
+    <t>Persentase Usaha dalam Keluarga (Ditemukan + Baru)</t>
+  </si>
+  <si>
+    <t>47,25</t>
+  </si>
+  <si>
+    <t>23,23</t>
+  </si>
+  <si>
+    <t>0,37</t>
+  </si>
+  <si>
+    <t>9,43</t>
+  </si>
+  <si>
+    <t>33,03</t>
+  </si>
+  <si>
+    <t>80,29</t>
+  </si>
+  <si>
+    <t>58,28</t>
+  </si>
+  <si>
+    <t>19,7</t>
+  </si>
+  <si>
+    <t>0,5</t>
+  </si>
+  <si>
+    <t>29,83</t>
+  </si>
+  <si>
+    <t>88,11</t>
+  </si>
+  <si>
+    <t>43,91</t>
+  </si>
+  <si>
+    <t>24,11</t>
+  </si>
+  <si>
+    <t>0,43</t>
+  </si>
+  <si>
+    <t>7,88</t>
+  </si>
+  <si>
+    <t>33,28</t>
+  </si>
+  <si>
+    <t>77,19</t>
+  </si>
+  <si>
+    <t>35,99</t>
+  </si>
+  <si>
+    <t>22,23</t>
+  </si>
+  <si>
+    <t>0,18</t>
+  </si>
+  <si>
+    <t>14,5</t>
+  </si>
+  <si>
+    <t>30,78</t>
+  </si>
+  <si>
+    <t>66,77</t>
+  </si>
+  <si>
+    <t>21,94</t>
+  </si>
+  <si>
+    <t>8,31</t>
+  </si>
+  <si>
+    <t>35,16</t>
+  </si>
+  <si>
+    <t>83,61</t>
+  </si>
+  <si>
+    <t>48,77</t>
+  </si>
+  <si>
+    <t>21,07</t>
+  </si>
+  <si>
+    <t>0,21</t>
+  </si>
+  <si>
+    <t>10,52</t>
+  </si>
+  <si>
+    <t>31,69</t>
+  </si>
+  <si>
+    <t>80,46</t>
+  </si>
+  <si>
+    <t>47,05</t>
+  </si>
+  <si>
+    <t>19,3</t>
+  </si>
+  <si>
+    <t>17,03</t>
+  </si>
+  <si>
+    <t>36,97</t>
+  </si>
+  <si>
+    <t>84,03</t>
+  </si>
+  <si>
+    <t>46,22</t>
+  </si>
+  <si>
+    <t>21,21</t>
+  </si>
+  <si>
+    <t>8,38</t>
+  </si>
+  <si>
+    <t>37,12</t>
+  </si>
+  <si>
+    <t>83,34</t>
+  </si>
+  <si>
+    <t>41,96</t>
+  </si>
+  <si>
+    <t>25,48</t>
+  </si>
+  <si>
+    <t>0,47</t>
+  </si>
+  <si>
+    <t>4,81</t>
+  </si>
+  <si>
+    <t>26,59</t>
+  </si>
+  <si>
+    <t>68,55</t>
+  </si>
+  <si>
+    <t>51,36</t>
+  </si>
+  <si>
+    <t>27,1</t>
+  </si>
+  <si>
+    <t>0,71</t>
+  </si>
+  <si>
+    <t>22,98</t>
+  </si>
+  <si>
+    <t>74,33</t>
+  </si>
+  <si>
+    <t>46,36</t>
+  </si>
+  <si>
+    <t>28,57</t>
+  </si>
+  <si>
+    <t>0,56</t>
+  </si>
+  <si>
+    <t>26,31</t>
+  </si>
+  <si>
+    <t>72,67</t>
+  </si>
+  <si>
+    <t>46,81</t>
+  </si>
+  <si>
+    <t>29,72</t>
+  </si>
+  <si>
+    <t>12,2</t>
+  </si>
+  <si>
+    <t>74,79</t>
+  </si>
+  <si>
+    <t>56,74</t>
+  </si>
+  <si>
+    <t>23,73</t>
+  </si>
+  <si>
+    <t>0,55</t>
+  </si>
+  <si>
+    <t>31,76</t>
+  </si>
+  <si>
+    <t>88,5</t>
+  </si>
+  <si>
+    <t>53,84</t>
+  </si>
+  <si>
+    <t>29,13</t>
+  </si>
+  <si>
+    <t>4,82</t>
+  </si>
+  <si>
+    <t>26,28</t>
+  </si>
+  <si>
+    <t>80,12</t>
+  </si>
+  <si>
+    <t>22,66</t>
+  </si>
+  <si>
+    <t>28,49</t>
+  </si>
+  <si>
+    <t>0,77</t>
+  </si>
+  <si>
+    <t>14,36</t>
+  </si>
+  <si>
+    <t>306,34</t>
+  </si>
+  <si>
+    <t>329</t>
+  </si>
+  <si>
+    <t>44,57</t>
+  </si>
+  <si>
+    <t>27,4</t>
+  </si>
+  <si>
+    <t>2,31</t>
+  </si>
+  <si>
+    <t>3,09</t>
+  </si>
+  <si>
+    <t>35,79</t>
+  </si>
+  <si>
+    <t>80,36</t>
+  </si>
+  <si>
+    <t>Persentase Kolom 4 9</t>
+  </si>
+  <si>
+    <t>PROGRES PENDATAAN - KESELURUHAN USAHA</t>
+  </si>
+  <si>
+    <t>Total Prelist Usaha dan Usaha Keluarga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USAHA BKU </t>
+  </si>
+  <si>
+    <t>USAHA DALAM KELUARGA</t>
+  </si>
+  <si>
+    <t>Total Usaha</t>
+  </si>
+  <si>
+    <t>Persentase Total Usaha</t>
+  </si>
+  <si>
+    <t>Subtotal</t>
+  </si>
+  <si>
+    <t>Persentase Subtotal</t>
+  </si>
+  <si>
+    <t>Ditemukan​</t>
+  </si>
+  <si>
+    <t>Persentase Ditemukan​</t>
+  </si>
+  <si>
+    <t>Baru​</t>
+  </si>
+  <si>
+    <t>Persentase Baru​</t>
+  </si>
+  <si>
+    <t>Subtotal​</t>
+  </si>
+  <si>
+    <t>Persentase Subtotal​</t>
+  </si>
+  <si>
+    <t>66,16</t>
+  </si>
+  <si>
+    <t>16,79</t>
+  </si>
+  <si>
+    <t>82,53</t>
+  </si>
+  <si>
+    <t>8,61</t>
+  </si>
+  <si>
+    <t>62,32</t>
+  </si>
+  <si>
+    <t>5,91</t>
+  </si>
+  <si>
+    <t>51,88</t>
+  </si>
+  <si>
+    <t>11,27</t>
+  </si>
+  <si>
+    <t>67,51</t>
+  </si>
+  <si>
+    <t>10,54</t>
+  </si>
+  <si>
+    <t>67,57</t>
+  </si>
+  <si>
+    <t>7,26</t>
+  </si>
+  <si>
+    <t>62,39</t>
+  </si>
+  <si>
+    <t>5,71</t>
+  </si>
+  <si>
+    <t>67,62</t>
+  </si>
+  <si>
+    <t>19,45</t>
+  </si>
+  <si>
+    <t>64,83</t>
+  </si>
+  <si>
+    <t>30,42</t>
+  </si>
+  <si>
+    <t>73,09</t>
+  </si>
+  <si>
+    <t>33,65</t>
+  </si>
+  <si>
+    <t>70,64</t>
+  </si>
+  <si>
+    <t>28,19</t>
+  </si>
+  <si>
+    <t>73,33</t>
+  </si>
+  <si>
+    <t>43,34</t>
+  </si>
+  <si>
+    <t>88,4</t>
+  </si>
+  <si>
+    <t>22,21</t>
+  </si>
+  <si>
+    <t>77,67</t>
+  </si>
+  <si>
+    <t>6,92</t>
+  </si>
+  <si>
+    <t>44,88</t>
+  </si>
+  <si>
+    <t>22,09</t>
+  </si>
+  <si>
+    <t>63,63</t>
+  </si>
+  <si>
+    <t>Total Prelist Usaha Dan Usaha Keluarga</t>
+  </si>
+  <si>
+    <t>Jumlah Prelist Usaha Ditambah Jumlah Prelist Usaha Keluarga (ST2023 + UMKM) atau Kolom (3) + (4).</t>
+  </si>
+  <si>
+    <t>Persentase Usaha BKU Ditemukan</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha BKU Ditemukan/Pindah Dapat Ditelusuri (CAPI dan CAWI) dibagi dengan Jumlah Prelist Usaha (kolom 3).</t>
+  </si>
+  <si>
+    <t>Persentase Usaha BKU Baru</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha BKU Baru (CAPI) dibagi Jumlah Prelist Usaha (kolom 3).</t>
+  </si>
+  <si>
+    <t>Persentase Usaha Keluarga Ditemukan</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha Keluarga Ditemukan dibagi dengan Jumlah Prelist Usaha Keluarga (ST2023 + UMKM) atau Kolom (4).</t>
+  </si>
+  <si>
+    <t>Persentase Usaha Keluarga Baru</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha Keluarga Baru dibagi dengan Jumlah Prelist Usaha Keluarga (ST2023 + UMKM) atau Kolom (4).</t>
+  </si>
+  <si>
+    <t>PROGRES PENDATAAN - PROPORSI USAHA</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha (Semua Status Keberadaan Usaha)</t>
+  </si>
+  <si>
+    <t>Persentase Usaha BKU</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha dalam Keluarga</t>
+  </si>
+  <si>
+    <t>Persentase Usaha dalam Keluarga</t>
+  </si>
+  <si>
+    <t>6,31</t>
+  </si>
+  <si>
+    <t>54,81</t>
+  </si>
+  <si>
+    <t>3,03</t>
+  </si>
+  <si>
+    <t>67,95</t>
+  </si>
+  <si>
+    <t>4,36</t>
+  </si>
+  <si>
+    <t>56,45</t>
+  </si>
+  <si>
+    <t>6,16</t>
+  </si>
+  <si>
+    <t>45,07</t>
+  </si>
+  <si>
+    <t>5,92</t>
+  </si>
+  <si>
+    <t>57,45</t>
   </si>
   <si>
     <t>5,85</t>
   </si>
   <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>PESAWARAN</t>
-  </si>
-  <si>
-    <t>120,21</t>
-  </si>
-  <si>
-    <t>81,6</t>
-  </si>
-  <si>
-    <t>3,56</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>PRINGSEWU</t>
-  </si>
-  <si>
-    <t>108,11</t>
-  </si>
-  <si>
-    <t>76,49</t>
-  </si>
-  <si>
-    <t>7,06</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>MESUJI</t>
-  </si>
-  <si>
-    <t>132,3</t>
-  </si>
-  <si>
-    <t>86,59</t>
-  </si>
-  <si>
-    <t>0,47</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG BARAT</t>
-  </si>
-  <si>
-    <t>126,66</t>
-  </si>
-  <si>
-    <t>85,4</t>
-  </si>
-  <si>
-    <t>1,81</t>
-  </si>
-  <si>
-    <t>1813</t>
-  </si>
-  <si>
-    <t>PESISIR BARAT</t>
-  </si>
-  <si>
-    <t>129,38</t>
-  </si>
-  <si>
-    <t>93,45</t>
-  </si>
-  <si>
-    <t>0,87</t>
-  </si>
-  <si>
-    <t>1871</t>
-  </si>
-  <si>
-    <t>BANDAR LAMPUNG</t>
-  </si>
-  <si>
-    <t>100,56</t>
-  </si>
-  <si>
-    <t>48,13</t>
-  </si>
-  <si>
-    <t>6,11</t>
-  </si>
-  <si>
-    <t>1872</t>
-  </si>
-  <si>
-    <t>METRO</t>
-  </si>
-  <si>
-    <t>104,95</t>
-  </si>
-  <si>
-    <t>63,97</t>
-  </si>
-  <si>
-    <t>6,49</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Catatan</t>
-  </si>
-  <si>
-    <t>Jumlah prelist terkini pada FASIH bersifat dinamis menyesuaikan perpindahan wilayah assignment.</t>
-  </si>
-  <si>
-    <t>Jumlah hasil verifikasi lapangan assignment usaha dan keluarga yang tidak berstatus open atau draft, mencakup seluruh status keberadaan (ditemukan, tutup, ganda, tidak ditemukan, baru, dan lainnya).</t>
-  </si>
-  <si>
-    <t>Responden Didata (Usaha &amp; Keluarga Ditemukan/Baru/Force Submit)</t>
-  </si>
-  <si>
-    <t>Jumlah responden usaha BKU dan keluarga yang telah berhasil didata (selain status open/draft) dengan kriteria keberadaan ditemukan dan baru termasuk usaha BKU yang diklaim sebagai usaha keluarga (force submit).</t>
-  </si>
-  <si>
-    <t>Jumlah Responden Sedang Didata</t>
-  </si>
-  <si>
-    <t>Jumlah responden dengan status Draft.</t>
-  </si>
-  <si>
-    <t>PROGRES PENDATAAN - USAHA/PERUSAHAAN</t>
-  </si>
-  <si>
-    <t>Jumlah Prelist Usaha</t>
-  </si>
-  <si>
-    <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA</t>
-  </si>
-  <si>
-    <t>Total Usaha BKU (UM+UMKM)</t>
-  </si>
-  <si>
-    <t>Persentase Total Usaha BKU (UM+UMKM)</t>
-  </si>
-  <si>
-    <t>UMKM</t>
-  </si>
-  <si>
-    <t>Ditemukan/Pindah Dapat Ditelusuri</t>
-  </si>
-  <si>
-    <t>Persentase Ditemukan/Pindah Dapat Ditelusuri</t>
-  </si>
-  <si>
-    <t>Ditemukan Tetapi Bukan Cakupan Survei</t>
-  </si>
-  <si>
-    <t>Persentase Ditemukan Tetapi Bukan Cakupan Survei</t>
-  </si>
-  <si>
-    <t>Pindah Tidak Dapat Ditelusuri</t>
-  </si>
-  <si>
-    <t>Persentase Pindah Tidak Dapat Ditelusuri</t>
-  </si>
-  <si>
-    <t>Tutup</t>
-  </si>
-  <si>
-    <t>Persentase Tutup</t>
-  </si>
-  <si>
-    <t>Duplikat</t>
-  </si>
-  <si>
-    <t>Persentase Duplikat</t>
-  </si>
-  <si>
-    <t>Tidak Ditemukan</t>
-  </si>
-  <si>
-    <t>Persentase Tidak Ditemukan</t>
-  </si>
-  <si>
-    <t>Data Diperoleh dari Kantor Pusat</t>
-  </si>
-  <si>
-    <t>Persentase Data Diperoleh dari Kantor Pusat</t>
-  </si>
-  <si>
-    <t>Nonrespon</t>
-  </si>
-  <si>
-    <t>Persentase Nonrespon</t>
-  </si>
-  <si>
-    <t>Total UB</t>
-  </si>
-  <si>
-    <t>Persentase Total UB</t>
-  </si>
-  <si>
-    <t>Ditemukan</t>
-  </si>
-  <si>
-    <t>Persentase Ditemukan</t>
-  </si>
-  <si>
-    <t>Tutup​</t>
-  </si>
-  <si>
-    <t>Persentase Tutup​</t>
-  </si>
-  <si>
-    <t>Ganda</t>
-  </si>
-  <si>
-    <t>Persentase Ganda</t>
-  </si>
-  <si>
-    <t>Tidak Ditemukan​</t>
-  </si>
-  <si>
-    <t>Persentase Tidak Ditemukan​</t>
-  </si>
-  <si>
-    <t>Persentase Baru</t>
-  </si>
-  <si>
-    <t>Data Diperoleh dari Kantor Pusat​</t>
-  </si>
-  <si>
-    <t>Persentase Data Diperoleh dari Kantor Pusat​</t>
-  </si>
-  <si>
-    <t>Nonrespon​</t>
-  </si>
-  <si>
-    <t>Persentase Nonrespon​</t>
-  </si>
-  <si>
-    <t>Force Submit (Diklaim Sebagai Usaha Keluarga)</t>
-  </si>
-  <si>
-    <t>Persentase Force Submit (Diklaim Sebagai Usaha Keluarga)</t>
-  </si>
-  <si>
-    <t>Total UMKM</t>
-  </si>
-  <si>
-    <t>Persentase Total UMKM</t>
-  </si>
-  <si>
-    <t>(15)</t>
-  </si>
-  <si>
-    <t>(16)</t>
-  </si>
-  <si>
-    <t>(17)</t>
-  </si>
-  <si>
-    <t>(18)</t>
-  </si>
-  <si>
-    <t>(19)</t>
-  </si>
-  <si>
-    <t>(20)</t>
-  </si>
-  <si>
-    <t>(21)</t>
-  </si>
-  <si>
-    <t>(22)</t>
-  </si>
-  <si>
-    <t>(23)</t>
-  </si>
-  <si>
-    <t>(24)</t>
-  </si>
-  <si>
-    <t>(25)</t>
-  </si>
-  <si>
-    <t>(26)</t>
-  </si>
-  <si>
-    <t>(27)</t>
-  </si>
-  <si>
-    <t>(28)</t>
-  </si>
-  <si>
-    <t>(29)</t>
-  </si>
-  <si>
-    <t>(30)</t>
-  </si>
-  <si>
-    <t>(31)</t>
-  </si>
-  <si>
-    <t>(32)</t>
-  </si>
-  <si>
-    <t>(33)</t>
-  </si>
-  <si>
-    <t>(34)</t>
-  </si>
-  <si>
-    <t>(35)</t>
-  </si>
-  <si>
-    <t>(36)</t>
-  </si>
-  <si>
-    <t>(37)</t>
-  </si>
-  <si>
-    <t>(38)</t>
-  </si>
-  <si>
-    <t>(39)</t>
-  </si>
-  <si>
-    <t>(40)</t>
-  </si>
-  <si>
-    <t>(41)</t>
-  </si>
-  <si>
-    <t>0,15</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>0,01</t>
-  </si>
-  <si>
-    <t>0,02</t>
-  </si>
-  <si>
-    <t>11,14</t>
-  </si>
-  <si>
-    <t>16,98</t>
-  </si>
-  <si>
-    <t>7,67</t>
-  </si>
-  <si>
-    <t>43,01</t>
-  </si>
-  <si>
-    <t>14,88</t>
-  </si>
-  <si>
-    <t>6,18</t>
-  </si>
-  <si>
-    <t>26,02</t>
-  </si>
-  <si>
-    <t>26,17</t>
-  </si>
-  <si>
-    <t>0,19</t>
-  </si>
-  <si>
-    <t>0,03</t>
-  </si>
-  <si>
-    <t>16,6</t>
-  </si>
-  <si>
-    <t>16,58</t>
-  </si>
-  <si>
-    <t>12,66</t>
-  </si>
-  <si>
-    <t>41,72</t>
-  </si>
-  <si>
-    <t>17,35</t>
-  </si>
-  <si>
-    <t>1,5</t>
-  </si>
-  <si>
-    <t>33,95</t>
-  </si>
-  <si>
-    <t>34,14</t>
-  </si>
-  <si>
-    <t>0,09</t>
-  </si>
-  <si>
-    <t>0,05</t>
-  </si>
-  <si>
-    <t>8,52</t>
-  </si>
-  <si>
-    <t>21,7</t>
-  </si>
-  <si>
-    <t>15,11</t>
-  </si>
-  <si>
-    <t>26,37</t>
-  </si>
-  <si>
-    <t>9,24</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>17,76</t>
-  </si>
-  <si>
-    <t>17,85</t>
-  </si>
-  <si>
-    <t>0,14</t>
-  </si>
-  <si>
-    <t>5,77</t>
-  </si>
-  <si>
-    <t>11,29</t>
-  </si>
-  <si>
-    <t>3,99</t>
-  </si>
-  <si>
-    <t>61,04</t>
-  </si>
-  <si>
-    <t>13,81</t>
-  </si>
-  <si>
-    <t>2,68</t>
-  </si>
-  <si>
-    <t>19,58</t>
-  </si>
-  <si>
-    <t>19,72</t>
-  </si>
-  <si>
-    <t>0,06</t>
-  </si>
-  <si>
-    <t>11,21</t>
-  </si>
-  <si>
-    <t>21,74</t>
-  </si>
-  <si>
-    <t>7,59</t>
-  </si>
-  <si>
-    <t>33,06</t>
-  </si>
-  <si>
-    <t>12,27</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>23,48</t>
-  </si>
-  <si>
-    <t>23,54</t>
-  </si>
-  <si>
-    <t>10,45</t>
-  </si>
-  <si>
-    <t>18,75</t>
-  </si>
-  <si>
-    <t>9,08</t>
-  </si>
-  <si>
-    <t>44,43</t>
-  </si>
-  <si>
-    <t>16,1</t>
-  </si>
-  <si>
-    <t>5,92</t>
-  </si>
-  <si>
-    <t>26,55</t>
-  </si>
-  <si>
-    <t>26,64</t>
-  </si>
-  <si>
-    <t>0,08</t>
-  </si>
-  <si>
-    <t>7,18</t>
-  </si>
-  <si>
-    <t>14,95</t>
-  </si>
-  <si>
-    <t>5,19</t>
-  </si>
-  <si>
-    <t>57,86</t>
-  </si>
-  <si>
-    <t>11,69</t>
-  </si>
-  <si>
-    <t>7,11</t>
-  </si>
-  <si>
-    <t>18,86</t>
-  </si>
-  <si>
-    <t>18,94</t>
-  </si>
-  <si>
-    <t>5,62</t>
-  </si>
-  <si>
-    <t>20,82</t>
-  </si>
-  <si>
-    <t>44,65</t>
-  </si>
-  <si>
-    <t>12,96</t>
-  </si>
-  <si>
-    <t>9,43</t>
-  </si>
-  <si>
-    <t>18,59</t>
-  </si>
-  <si>
-    <t>18,67</t>
-  </si>
-  <si>
-    <t>0,23</t>
-  </si>
-  <si>
-    <t>19,22</t>
-  </si>
-  <si>
-    <t>12,39</t>
-  </si>
-  <si>
-    <t>4,49</t>
-  </si>
-  <si>
-    <t>41,51</t>
-  </si>
-  <si>
-    <t>23,58</t>
-  </si>
-  <si>
-    <t>0,94</t>
-  </si>
-  <si>
-    <t>42,81</t>
-  </si>
-  <si>
-    <t>43,04</t>
-  </si>
-  <si>
-    <t>0,26</t>
-  </si>
-  <si>
-    <t>30,16</t>
-  </si>
-  <si>
-    <t>14,12</t>
-  </si>
-  <si>
-    <t>5,15</t>
-  </si>
-  <si>
-    <t>35,96</t>
-  </si>
-  <si>
-    <t>32,28</t>
-  </si>
-  <si>
-    <t>2,08</t>
-  </si>
-  <si>
-    <t>62,44</t>
-  </si>
-  <si>
-    <t>62,7</t>
-  </si>
-  <si>
-    <t>33,51</t>
-  </si>
-  <si>
-    <t>13,28</t>
-  </si>
-  <si>
-    <t>3,29</t>
-  </si>
-  <si>
-    <t>28,84</t>
-  </si>
-  <si>
-    <t>26,15</t>
-  </si>
-  <si>
-    <t>1,58</t>
-  </si>
-  <si>
-    <t>59,66</t>
-  </si>
-  <si>
-    <t>59,8</t>
-  </si>
-  <si>
-    <t>0,24</t>
-  </si>
-  <si>
-    <t>27,95</t>
-  </si>
-  <si>
-    <t>19,02</t>
-  </si>
-  <si>
-    <t>12,15</t>
-  </si>
-  <si>
-    <t>27,98</t>
-  </si>
-  <si>
-    <t>34,55</t>
-  </si>
-  <si>
-    <t>0,89</t>
-  </si>
-  <si>
-    <t>62,5</t>
-  </si>
-  <si>
-    <t>62,74</t>
-  </si>
-  <si>
-    <t>0,22</t>
-  </si>
-  <si>
-    <t>43,12</t>
-  </si>
-  <si>
-    <t>4,78</t>
-  </si>
-  <si>
-    <t>19,11</t>
-  </si>
-  <si>
-    <t>44,04</t>
-  </si>
-  <si>
-    <t>1,75</t>
-  </si>
-  <si>
-    <t>87,16</t>
-  </si>
-  <si>
-    <t>87,39</t>
-  </si>
-  <si>
-    <t>0,17</t>
-  </si>
-  <si>
-    <t>22,04</t>
-  </si>
-  <si>
-    <t>16,75</t>
-  </si>
-  <si>
-    <t>7,19</t>
-  </si>
-  <si>
-    <t>40,59</t>
-  </si>
-  <si>
-    <t>32,16</t>
-  </si>
-  <si>
-    <t>1,21</t>
-  </si>
-  <si>
-    <t>54,2</t>
-  </si>
-  <si>
-    <t>54,37</t>
-  </si>
-  <si>
-    <t>0,3</t>
-  </si>
-  <si>
-    <t>0,04</t>
-  </si>
-  <si>
-    <t>6,62</t>
-  </si>
-  <si>
-    <t>13,46</t>
-  </si>
-  <si>
-    <t>7,01</t>
-  </si>
-  <si>
-    <t>47,68</t>
-  </si>
-  <si>
-    <t>10,7</t>
-  </si>
-  <si>
-    <t>5,21</t>
-  </si>
-  <si>
-    <t>17,31</t>
-  </si>
-  <si>
-    <t>17,61</t>
-  </si>
-  <si>
-    <t>0,25</t>
-  </si>
-  <si>
-    <t>21,83</t>
-  </si>
-  <si>
-    <t>19,17</t>
-  </si>
-  <si>
-    <t>18,2</t>
-  </si>
-  <si>
-    <t>20,81</t>
-  </si>
-  <si>
-    <t>18,12</t>
-  </si>
-  <si>
-    <t>1,67</t>
-  </si>
-  <si>
-    <t>39,95</t>
-  </si>
-  <si>
-    <t>40,21</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha BKU</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha yang Ditemukan dan Baru (UB + UMKM)</t>
-  </si>
-  <si>
-    <t>Persentase Kolom 4 21</t>
-  </si>
-  <si>
-    <t>Persentase hasil bagi jumlah usaha pada kolom tersebut dengan jumlah prelist usaha (kolom 3).</t>
-  </si>
-  <si>
-    <t>PROGRES PENDATAAN - SKALA USAHA</t>
-  </si>
-  <si>
-    <t>JUMLAH PRELIST</t>
-  </si>
-  <si>
-    <t>JUMLAH USAHA BKU MENURUT STATUS SKALA USAHA (UB, UM, UMK)</t>
-  </si>
-  <si>
-    <t>UB​</t>
-  </si>
-  <si>
-    <t>Persentase UB​</t>
-  </si>
-  <si>
-    <t>UM​</t>
-  </si>
-  <si>
-    <t>Persentase UM​</t>
-  </si>
-  <si>
-    <t>UMK​</t>
-  </si>
-  <si>
-    <t>Persentase UMK​</t>
-  </si>
-  <si>
-    <t>Tidak Dapat Diklasifikasikan</t>
-  </si>
-  <si>
-    <t>Total Usaha BKU</t>
-  </si>
-  <si>
-    <t>Persentase Total Usaha BKU</t>
-  </si>
-  <si>
-    <t>82,21</t>
-  </si>
-  <si>
-    <t>10,87</t>
+    <t>56,1</t>
+  </si>
+  <si>
+    <t>5,59</t>
+  </si>
+  <si>
+    <t>49,76</t>
+  </si>
+  <si>
+    <t>58,65</t>
+  </si>
+  <si>
+    <t>6,3</t>
+  </si>
+  <si>
+    <t>58,78</t>
+  </si>
+  <si>
+    <t>6,07</t>
+  </si>
+  <si>
+    <t>60,41</t>
+  </si>
+  <si>
+    <t>8,81</t>
+  </si>
+  <si>
+    <t>57,02</t>
+  </si>
+  <si>
+    <t>6,43</t>
+  </si>
+  <si>
+    <t>55,74</t>
+  </si>
+  <si>
+    <t>6,41</t>
+  </si>
+  <si>
+    <t>66,46</t>
+  </si>
+  <si>
+    <t>63,09</t>
+  </si>
+  <si>
+    <t>14,47</t>
+  </si>
+  <si>
+    <t>25,95</t>
+  </si>
+  <si>
+    <t>15,65</t>
+  </si>
+  <si>
+    <t>43,81</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha (Semua Status Keberadaan Usaha) Kolom 3</t>
+  </si>
+  <si>
+    <t>Jumlah seluruh usaha BKU dan Usaha Keluarga dari CAPI dan CAWI dengan semua status keberadaan.</t>
+  </si>
+  <si>
+    <t>PROGRES PENDATAAN - JARINGAN USAHA</t>
+  </si>
+  <si>
+    <t>JUMLAH USAHA BERDASARKAN JARINGAN USAHA</t>
+  </si>
+  <si>
+    <t>Tunggal</t>
+  </si>
+  <si>
+    <t>Kantor Pusat</t>
+  </si>
+  <si>
+    <t>Cabang</t>
+  </si>
+  <si>
+    <t>Perwakilan</t>
+  </si>
+  <si>
+    <t>Pabrik</t>
+  </si>
+  <si>
+    <t>Unit Pembantu</t>
+  </si>
+  <si>
+    <t>PROGRES PENDATAAN - PROPORSI PERTANIAN</t>
+  </si>
+  <si>
+    <t>Jumlah Prelist Usaha SE2026</t>
+  </si>
+  <si>
+    <t>Target Berdasarkan Data ST</t>
+  </si>
+  <si>
+    <t>Jumlah UTP Subsektor Prelist</t>
+  </si>
+  <si>
+    <t>USAHA PERTANIAN BKU</t>
+  </si>
+  <si>
+    <t>USAHA PERTANIAN DALAM KELUARGA</t>
+  </si>
+  <si>
+    <t>24,28</t>
+  </si>
+  <si>
+    <t>75,72</t>
+  </si>
+  <si>
+    <t>69,18</t>
+  </si>
+  <si>
+    <t>30,82</t>
+  </si>
+  <si>
+    <t>12,16</t>
+  </si>
+  <si>
+    <t>87,84</t>
+  </si>
+  <si>
+    <t>68,8</t>
+  </si>
+  <si>
+    <t>31,2</t>
+  </si>
+  <si>
+    <t>73,85</t>
+  </si>
+  <si>
+    <t>69,34</t>
+  </si>
+  <si>
+    <t>30,66</t>
+  </si>
+  <si>
+    <t>14,96</t>
+  </si>
+  <si>
+    <t>85,04</t>
+  </si>
+  <si>
+    <t>70,54</t>
+  </si>
+  <si>
+    <t>29,46</t>
+  </si>
+  <si>
+    <t>46,04</t>
+  </si>
+  <si>
+    <t>53,96</t>
+  </si>
+  <si>
+    <t>69,25</t>
+  </si>
+  <si>
+    <t>30,75</t>
+  </si>
+  <si>
+    <t>37,09</t>
+  </si>
+  <si>
+    <t>62,91</t>
+  </si>
+  <si>
+    <t>70,04</t>
+  </si>
+  <si>
+    <t>29,96</t>
+  </si>
+  <si>
+    <t>37,8</t>
+  </si>
+  <si>
+    <t>62,2</t>
+  </si>
+  <si>
+    <t>31,74</t>
+  </si>
+  <si>
+    <t>15,48</t>
+  </si>
+  <si>
+    <t>84,52</t>
+  </si>
+  <si>
+    <t>65,43</t>
+  </si>
+  <si>
+    <t>34,57</t>
+  </si>
+  <si>
+    <t>6,91</t>
+  </si>
+  <si>
+    <t>93,09</t>
+  </si>
+  <si>
+    <t>64,92</t>
+  </si>
+  <si>
+    <t>35,08</t>
+  </si>
+  <si>
+    <t>25,21</t>
+  </si>
+  <si>
+    <t>73,92</t>
   </si>
   <si>
     <t>26,08</t>
   </si>
   <si>
-    <t>126,09</t>
-  </si>
-  <si>
-    <t>39,07</t>
-  </si>
-  <si>
-    <t>33,79</t>
-  </si>
-  <si>
-    <t>52,21</t>
-  </si>
-  <si>
-    <t>16,88</t>
-  </si>
-  <si>
-    <t>17,68</t>
-  </si>
-  <si>
-    <t>103,42</t>
-  </si>
-  <si>
-    <t>8,62</t>
-  </si>
-  <si>
-    <t>19,59</t>
-  </si>
-  <si>
-    <t>122,78</t>
-  </si>
-  <si>
-    <t>20,36</t>
-  </si>
-  <si>
-    <t>23,34</t>
-  </si>
-  <si>
-    <t>104,32</t>
-  </si>
-  <si>
-    <t>26,51</t>
-  </si>
-  <si>
-    <t>81,33</t>
-  </si>
-  <si>
-    <t>17,27</t>
-  </si>
-  <si>
-    <t>18,82</t>
-  </si>
-  <si>
-    <t>125,71</t>
-  </si>
-  <si>
-    <t>11,63</t>
-  </si>
-  <si>
-    <t>18,47</t>
-  </si>
-  <si>
-    <t>96,08</t>
-  </si>
-  <si>
-    <t>5,26</t>
-  </si>
-  <si>
-    <t>43,55</t>
-  </si>
-  <si>
-    <t>96,36</t>
-  </si>
-  <si>
-    <t>36,36</t>
-  </si>
-  <si>
-    <t>62,57</t>
-  </si>
-  <si>
-    <t>128,13</t>
-  </si>
-  <si>
-    <t>133,33</t>
-  </si>
-  <si>
-    <t>59,34</t>
-  </si>
-  <si>
-    <t>111,11</t>
-  </si>
-  <si>
-    <t>31,58</t>
-  </si>
-  <si>
-    <t>62,67</t>
-  </si>
-  <si>
-    <t>117,39</t>
-  </si>
-  <si>
-    <t>31,82</t>
-  </si>
-  <si>
-    <t>87,57</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>54,25</t>
-  </si>
-  <si>
-    <t>60,79</t>
-  </si>
-  <si>
-    <t>17,65</t>
-  </si>
-  <si>
-    <t>117,5</t>
-  </si>
-  <si>
-    <t>35,42</t>
-  </si>
-  <si>
-    <t>39,85</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha (UB/UM/UMK)</t>
-  </si>
-  <si>
-    <t>Jumlah prelist usaha yang berhasil didata (keberadaan ditemukan, baru, pindah dapat ditelusuri) berdasarkan skala usaha, untuk usaha baru didekati dengan omzet sebagai berikut: UB (lebih dari 50 Milyar), UM (15-50 Milyar), UMK - Kecil (2-15 Milyar), UMK - Mikro (0-2 Milyar).</t>
-  </si>
-  <si>
-    <t>Tidak Dapat Diklasifikasikan (Kolom 10)</t>
-  </si>
-  <si>
-    <t>Usaha baru dengan nilai omzet/pendapatan kosong sehingga tidak dapat diklasifikasikan skala usahanya, misalnya usaha unit pembantu/penunjang.</t>
-  </si>
-  <si>
-    <t>Persentase Jumlah UB</t>
-  </si>
-  <si>
-    <t>Persentase hasil bagi jumlah UB yang berhasil didata dengan jumlah prelist UB (kolom 3).</t>
-  </si>
-  <si>
-    <t>Persentase Jumlah UM</t>
-  </si>
-  <si>
-    <t>Persentase hasil bagi jumlah UM yang berhasil didata dengan jumlah prelist UM (kolom 4).</t>
-  </si>
-  <si>
-    <t>Persentase Jumlah UMK</t>
-  </si>
-  <si>
-    <t>Persentase hasil bagi jumlah UMK yang berhasil didata dengan jumlah prelist UMK (kolom 5).</t>
-  </si>
-  <si>
-    <t>PROGRES PENDATAAN - USAHA KELUARGA</t>
-  </si>
-  <si>
-    <t>Jumlah Prelist Usaha Keluarga (ST2023 + UMKM)</t>
-  </si>
-  <si>
-    <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha dalam Keluarga (Ditemukan + Baru)</t>
-  </si>
-  <si>
-    <t>Persentase Usaha dalam Keluarga (Ditemukan + Baru)</t>
-  </si>
-  <si>
-    <t>47,25</t>
-  </si>
-  <si>
-    <t>23,23</t>
-  </si>
-  <si>
-    <t>0,37</t>
-  </si>
-  <si>
-    <t>33,03</t>
-  </si>
-  <si>
-    <t>80,29</t>
-  </si>
-  <si>
-    <t>58,28</t>
-  </si>
-  <si>
-    <t>19,7</t>
-  </si>
-  <si>
-    <t>0,5</t>
-  </si>
-  <si>
-    <t>29,83</t>
-  </si>
-  <si>
-    <t>88,11</t>
-  </si>
-  <si>
-    <t>43,91</t>
-  </si>
-  <si>
-    <t>24,11</t>
-  </si>
-  <si>
-    <t>0,43</t>
-  </si>
-  <si>
-    <t>7,88</t>
-  </si>
-  <si>
-    <t>33,28</t>
-  </si>
-  <si>
-    <t>77,19</t>
-  </si>
-  <si>
-    <t>35,99</t>
-  </si>
-  <si>
-    <t>22,23</t>
-  </si>
-  <si>
-    <t>0,18</t>
-  </si>
-  <si>
-    <t>14,5</t>
-  </si>
-  <si>
-    <t>30,78</t>
-  </si>
-  <si>
-    <t>66,77</t>
-  </si>
-  <si>
-    <t>48,46</t>
-  </si>
-  <si>
-    <t>21,94</t>
-  </si>
-  <si>
-    <t>8,31</t>
-  </si>
-  <si>
-    <t>35,16</t>
-  </si>
-  <si>
-    <t>83,61</t>
-  </si>
-  <si>
-    <t>48,77</t>
-  </si>
-  <si>
-    <t>21,07</t>
-  </si>
-  <si>
-    <t>0,21</t>
-  </si>
-  <si>
-    <t>10,52</t>
-  </si>
-  <si>
-    <t>31,69</t>
-  </si>
-  <si>
-    <t>80,46</t>
-  </si>
-  <si>
-    <t>47,05</t>
-  </si>
-  <si>
-    <t>19,3</t>
-  </si>
-  <si>
-    <t>17,03</t>
-  </si>
-  <si>
-    <t>36,97</t>
-  </si>
-  <si>
-    <t>84,03</t>
-  </si>
-  <si>
-    <t>46,22</t>
-  </si>
-  <si>
-    <t>21,21</t>
-  </si>
-  <si>
-    <t>8,38</t>
-  </si>
-  <si>
-    <t>37,12</t>
-  </si>
-  <si>
-    <t>83,34</t>
-  </si>
-  <si>
-    <t>41,96</t>
-  </si>
-  <si>
-    <t>25,48</t>
-  </si>
-  <si>
-    <t>4,81</t>
-  </si>
-  <si>
-    <t>26,59</t>
-  </si>
-  <si>
-    <t>68,55</t>
-  </si>
-  <si>
-    <t>51,36</t>
-  </si>
-  <si>
-    <t>27,1</t>
-  </si>
-  <si>
-    <t>0,71</t>
-  </si>
-  <si>
-    <t>6,84</t>
-  </si>
-  <si>
-    <t>22,98</t>
-  </si>
-  <si>
-    <t>74,33</t>
-  </si>
-  <si>
-    <t>46,36</t>
-  </si>
-  <si>
-    <t>28,57</t>
-  </si>
-  <si>
-    <t>0,56</t>
-  </si>
-  <si>
-    <t>5,89</t>
-  </si>
-  <si>
-    <t>26,31</t>
-  </si>
-  <si>
-    <t>72,67</t>
-  </si>
-  <si>
-    <t>46,81</t>
-  </si>
-  <si>
-    <t>29,72</t>
-  </si>
-  <si>
-    <t>12,2</t>
-  </si>
-  <si>
-    <t>74,79</t>
-  </si>
-  <si>
-    <t>56,74</t>
-  </si>
-  <si>
-    <t>23,73</t>
-  </si>
-  <si>
-    <t>0,55</t>
-  </si>
-  <si>
-    <t>31,76</t>
-  </si>
-  <si>
-    <t>88,5</t>
-  </si>
-  <si>
-    <t>53,84</t>
-  </si>
-  <si>
-    <t>29,13</t>
-  </si>
-  <si>
-    <t>4,82</t>
-  </si>
-  <si>
-    <t>26,28</t>
-  </si>
-  <si>
-    <t>80,12</t>
-  </si>
-  <si>
-    <t>22,66</t>
-  </si>
-  <si>
-    <t>28,49</t>
-  </si>
-  <si>
-    <t>0,77</t>
-  </si>
-  <si>
-    <t>14,36</t>
-  </si>
-  <si>
-    <t>306,34</t>
-  </si>
-  <si>
-    <t>329</t>
-  </si>
-  <si>
-    <t>44,57</t>
-  </si>
-  <si>
-    <t>27,4</t>
-  </si>
-  <si>
-    <t>2,31</t>
-  </si>
-  <si>
-    <t>3,09</t>
-  </si>
-  <si>
-    <t>35,79</t>
-  </si>
-  <si>
-    <t>80,36</t>
-  </si>
-  <si>
-    <t>Persentase Kolom 4 9</t>
-  </si>
-  <si>
-    <t>PROGRES PENDATAAN - KESELURUHAN USAHA</t>
-  </si>
-  <si>
-    <t>Total Prelist Usaha dan Usaha Keluarga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USAHA BKU </t>
-  </si>
-  <si>
-    <t>USAHA DALAM KELUARGA</t>
-  </si>
-  <si>
-    <t>Total Usaha</t>
-  </si>
-  <si>
-    <t>Persentase Total Usaha</t>
-  </si>
-  <si>
-    <t>Subtotal</t>
-  </si>
-  <si>
-    <t>Persentase Subtotal</t>
-  </si>
-  <si>
-    <t>Ditemukan​</t>
-  </si>
-  <si>
-    <t>Persentase Ditemukan​</t>
-  </si>
-  <si>
-    <t>Baru​</t>
-  </si>
-  <si>
-    <t>Persentase Baru​</t>
-  </si>
-  <si>
-    <t>Subtotal​</t>
-  </si>
-  <si>
-    <t>Persentase Subtotal​</t>
-  </si>
-  <si>
-    <t>66,16</t>
-  </si>
-  <si>
-    <t>16,79</t>
-  </si>
-  <si>
-    <t>82,53</t>
-  </si>
-  <si>
-    <t>8,61</t>
-  </si>
-  <si>
-    <t>62,32</t>
-  </si>
-  <si>
-    <t>5,91</t>
-  </si>
-  <si>
-    <t>51,88</t>
-  </si>
-  <si>
-    <t>11,27</t>
-  </si>
-  <si>
-    <t>67,51</t>
-  </si>
-  <si>
-    <t>10,54</t>
-  </si>
-  <si>
-    <t>67,57</t>
-  </si>
-  <si>
-    <t>7,26</t>
-  </si>
-  <si>
-    <t>62,39</t>
-  </si>
-  <si>
-    <t>5,71</t>
-  </si>
-  <si>
-    <t>67,62</t>
-  </si>
-  <si>
-    <t>19,45</t>
-  </si>
-  <si>
-    <t>64,83</t>
-  </si>
-  <si>
-    <t>30,42</t>
-  </si>
-  <si>
-    <t>73,09</t>
-  </si>
-  <si>
-    <t>33,65</t>
-  </si>
-  <si>
-    <t>70,64</t>
-  </si>
-  <si>
-    <t>28,19</t>
-  </si>
-  <si>
-    <t>73,33</t>
-  </si>
-  <si>
-    <t>43,34</t>
-  </si>
-  <si>
-    <t>88,4</t>
-  </si>
-  <si>
-    <t>22,21</t>
-  </si>
-  <si>
-    <t>77,67</t>
-  </si>
-  <si>
-    <t>6,92</t>
-  </si>
-  <si>
-    <t>44,88</t>
-  </si>
-  <si>
-    <t>22,09</t>
-  </si>
-  <si>
-    <t>63,63</t>
-  </si>
-  <si>
-    <t>Total Prelist Usaha Dan Usaha Keluarga</t>
-  </si>
-  <si>
-    <t>Jumlah Prelist Usaha Ditambah Jumlah Prelist Usaha Keluarga (ST2023 + UMKM) atau Kolom (3) + (4).</t>
-  </si>
-  <si>
-    <t>Persentase Usaha BKU Ditemukan</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha BKU Ditemukan/Pindah Dapat Ditelusuri (CAPI dan CAWI) dibagi dengan Jumlah Prelist Usaha (kolom 3).</t>
-  </si>
-  <si>
-    <t>Persentase Usaha BKU Baru</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha BKU Baru (CAPI) dibagi Jumlah Prelist Usaha (kolom 3).</t>
-  </si>
-  <si>
-    <t>Persentase Usaha Keluarga Ditemukan</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha Keluarga Ditemukan dibagi dengan Jumlah Prelist Usaha Keluarga (ST2023 + UMKM) atau Kolom (4).</t>
-  </si>
-  <si>
-    <t>Persentase Usaha Keluarga Baru</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha Keluarga Baru dibagi dengan Jumlah Prelist Usaha Keluarga (ST2023 + UMKM) atau Kolom (4).</t>
-  </si>
-  <si>
-    <t>PROGRES PENDATAAN - PROPORSI USAHA</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha (Semua Status Keberadaan Usaha)</t>
-  </si>
-  <si>
-    <t>Persentase Usaha BKU</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha dalam Keluarga</t>
-  </si>
-  <si>
-    <t>Persentase Usaha dalam Keluarga</t>
-  </si>
-  <si>
-    <t>6,31</t>
-  </si>
-  <si>
-    <t>54,81</t>
-  </si>
-  <si>
-    <t>3,03</t>
-  </si>
-  <si>
-    <t>67,95</t>
-  </si>
-  <si>
-    <t>4,36</t>
-  </si>
-  <si>
-    <t>56,45</t>
-  </si>
-  <si>
-    <t>6,16</t>
-  </si>
-  <si>
-    <t>45,07</t>
-  </si>
-  <si>
-    <t>57,45</t>
-  </si>
-  <si>
-    <t>56,1</t>
-  </si>
-  <si>
-    <t>5,59</t>
-  </si>
-  <si>
-    <t>49,76</t>
-  </si>
-  <si>
-    <t>4,22</t>
-  </si>
-  <si>
-    <t>58,65</t>
-  </si>
-  <si>
-    <t>6,3</t>
-  </si>
-  <si>
-    <t>58,78</t>
-  </si>
-  <si>
-    <t>6,07</t>
-  </si>
-  <si>
-    <t>60,41</t>
-  </si>
-  <si>
-    <t>8,81</t>
-  </si>
-  <si>
-    <t>57,02</t>
-  </si>
-  <si>
-    <t>6,43</t>
-  </si>
-  <si>
-    <t>55,74</t>
-  </si>
-  <si>
-    <t>6,41</t>
-  </si>
-  <si>
-    <t>66,46</t>
-  </si>
-  <si>
-    <t>63,09</t>
-  </si>
-  <si>
-    <t>14,47</t>
-  </si>
-  <si>
-    <t>25,95</t>
-  </si>
-  <si>
-    <t>15,65</t>
-  </si>
-  <si>
-    <t>43,81</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha (Semua Status Keberadaan Usaha) Kolom 3</t>
-  </si>
-  <si>
-    <t>Jumlah seluruh usaha BKU dan Usaha Keluarga dari CAPI dan CAWI dengan semua status keberadaan.</t>
-  </si>
-  <si>
-    <t>PROGRES PENDATAAN - JARINGAN USAHA</t>
-  </si>
-  <si>
-    <t>JUMLAH USAHA BERDASARKAN JARINGAN USAHA</t>
-  </si>
-  <si>
-    <t>Tunggal</t>
-  </si>
-  <si>
-    <t>Kantor Pusat</t>
-  </si>
-  <si>
-    <t>Cabang</t>
-  </si>
-  <si>
-    <t>Perwakilan</t>
-  </si>
-  <si>
-    <t>Pabrik</t>
-  </si>
-  <si>
-    <t>Unit Pembantu</t>
-  </si>
-  <si>
-    <t>PROGRES PENDATAAN - PROPORSI PERTANIAN</t>
-  </si>
-  <si>
-    <t>Jumlah Prelist Usaha SE2026</t>
-  </si>
-  <si>
-    <t>Target Berdasarkan Data ST</t>
-  </si>
-  <si>
-    <t>Jumlah UTP Subsektor Prelist</t>
-  </si>
-  <si>
-    <t>USAHA PERTANIAN BKU</t>
-  </si>
-  <si>
-    <t>USAHA PERTANIAN DALAM KELUARGA</t>
-  </si>
-  <si>
-    <t>24,21</t>
-  </si>
-  <si>
-    <t>75,79</t>
-  </si>
-  <si>
-    <t>69,16</t>
-  </si>
-  <si>
-    <t>30,84</t>
-  </si>
-  <si>
-    <t>12,75</t>
-  </si>
-  <si>
-    <t>87,25</t>
-  </si>
-  <si>
-    <t>68,81</t>
-  </si>
-  <si>
-    <t>31,19</t>
-  </si>
-  <si>
-    <t>26,11</t>
-  </si>
-  <si>
-    <t>73,89</t>
-  </si>
-  <si>
-    <t>69,35</t>
-  </si>
-  <si>
-    <t>30,65</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>85</t>
+    <t>9,09</t>
+  </si>
+  <si>
+    <t>90,91</t>
+  </si>
+  <si>
+    <t>70,49</t>
+  </si>
+  <si>
+    <t>29,51</t>
+  </si>
+  <si>
+    <t>7,46</t>
+  </si>
+  <si>
+    <t>92,54</t>
+  </si>
+  <si>
+    <t>66,5</t>
+  </si>
+  <si>
+    <t>33,5</t>
+  </si>
+  <si>
+    <t>16,95</t>
+  </si>
+  <si>
+    <t>83,05</t>
+  </si>
+  <si>
+    <t>67,24</t>
+  </si>
+  <si>
+    <t>32,76</t>
+  </si>
+  <si>
+    <t>13,51</t>
+  </si>
+  <si>
+    <t>86,49</t>
   </si>
   <si>
     <t>70,48</t>
@@ -1874,139 +2024,28 @@
     <t>29,52</t>
   </si>
   <si>
-    <t>45,92</t>
-  </si>
-  <si>
-    <t>54,08</t>
-  </si>
-  <si>
-    <t>69,25</t>
-  </si>
-  <si>
-    <t>30,75</t>
-  </si>
-  <si>
-    <t>37,18</t>
-  </si>
-  <si>
-    <t>62,82</t>
-  </si>
-  <si>
-    <t>70,02</t>
-  </si>
-  <si>
-    <t>29,98</t>
-  </si>
-  <si>
-    <t>37,65</t>
-  </si>
-  <si>
-    <t>62,35</t>
-  </si>
-  <si>
-    <t>68,21</t>
-  </si>
-  <si>
-    <t>31,79</t>
-  </si>
-  <si>
-    <t>15,46</t>
-  </si>
-  <si>
-    <t>84,54</t>
-  </si>
-  <si>
-    <t>65,41</t>
-  </si>
-  <si>
-    <t>34,59</t>
-  </si>
-  <si>
-    <t>7,02</t>
-  </si>
-  <si>
-    <t>92,98</t>
-  </si>
-  <si>
-    <t>64,88</t>
-  </si>
-  <si>
-    <t>35,12</t>
-  </si>
-  <si>
-    <t>25,1</t>
-  </si>
-  <si>
-    <t>74,9</t>
-  </si>
-  <si>
-    <t>9,12</t>
-  </si>
-  <si>
-    <t>90,88</t>
-  </si>
-  <si>
-    <t>70,45</t>
-  </si>
-  <si>
-    <t>29,55</t>
-  </si>
-  <si>
-    <t>7,46</t>
-  </si>
-  <si>
-    <t>92,54</t>
-  </si>
-  <si>
-    <t>66,48</t>
-  </si>
-  <si>
-    <t>33,52</t>
-  </si>
-  <si>
-    <t>16,24</t>
-  </si>
-  <si>
-    <t>83,76</t>
-  </si>
-  <si>
-    <t>67,19</t>
-  </si>
-  <si>
-    <t>32,81</t>
-  </si>
-  <si>
-    <t>13,51</t>
-  </si>
-  <si>
-    <t>86,49</t>
-  </si>
-  <si>
-    <t>70,46</t>
-  </si>
-  <si>
-    <t>29,54</t>
-  </si>
-  <si>
-    <t>33,1</t>
-  </si>
-  <si>
-    <t>66,9</t>
-  </si>
-  <si>
-    <t>72,77</t>
-  </si>
-  <si>
-    <t>27,23</t>
-  </si>
-  <si>
-    <t>68,42</t>
-  </si>
-  <si>
-    <t>72,3</t>
-  </si>
-  <si>
-    <t>27,7</t>
+    <t>34,53</t>
+  </si>
+  <si>
+    <t>65,47</t>
+  </si>
+  <si>
+    <t>72,88</t>
+  </si>
+  <si>
+    <t>27,12</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>72,34</t>
+  </si>
+  <si>
+    <t>27,66</t>
   </si>
   <si>
     <t>Persentase Usaha Pertanian BKU Ditemukan</t>
@@ -2710,22 +2749,22 @@
         <v>3491483</v>
       </c>
       <c r="D7" s="6">
-        <v>801748</v>
+        <v>804430</v>
       </c>
       <c r="E7" s="6">
-        <v>3789240</v>
+        <v>3813155</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>34</v>
       </c>
       <c r="G7" s="6">
-        <v>2294289</v>
+        <v>2309055</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>35</v>
       </c>
       <c r="I7" s="6">
-        <v>173276</v>
+        <v>164830</v>
       </c>
       <c r="J7" s="7" t="s">
         <v>36</v>
@@ -2734,13 +2773,13 @@
         <v>98</v>
       </c>
       <c r="L7" s="6">
-        <v>1273</v>
+        <v>1214</v>
       </c>
       <c r="M7" s="6">
-        <v>69915</v>
+        <v>66900</v>
       </c>
       <c r="N7" s="6">
-        <v>259429</v>
+        <v>249716</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -2754,22 +2793,22 @@
         <v>97072</v>
       </c>
       <c r="D8" s="9">
-        <v>24845</v>
+        <v>24871</v>
       </c>
       <c r="E8" s="9">
-        <v>120716</v>
+        <v>121001</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>39</v>
       </c>
       <c r="G8" s="9">
-        <v>82157</v>
+        <v>82376</v>
       </c>
       <c r="H8" s="10" t="s">
         <v>40</v>
       </c>
       <c r="I8" s="9">
-        <v>1570</v>
+        <v>1443</v>
       </c>
       <c r="J8" s="10" t="s">
         <v>41</v>
@@ -2781,10 +2820,10 @@
         <v>0</v>
       </c>
       <c r="M8" s="9">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="N8" s="9">
-        <v>-491</v>
+        <v>-606</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -2795,25 +2834,25 @@
         <v>43</v>
       </c>
       <c r="C9" s="9">
-        <v>230430</v>
+        <v>230431</v>
       </c>
       <c r="D9" s="9">
-        <v>56505</v>
+        <v>56669</v>
       </c>
       <c r="E9" s="9">
-        <v>247575</v>
+        <v>249180</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>44</v>
       </c>
       <c r="G9" s="9">
-        <v>156275</v>
+        <v>157286</v>
       </c>
       <c r="H9" s="10" t="s">
         <v>45</v>
       </c>
       <c r="I9" s="9">
-        <v>16432</v>
+        <v>15755</v>
       </c>
       <c r="J9" s="10" t="s">
         <v>46</v>
@@ -2825,10 +2864,10 @@
         <v>9</v>
       </c>
       <c r="M9" s="9">
-        <v>5673</v>
+        <v>5460</v>
       </c>
       <c r="N9" s="9">
-        <v>17241</v>
+        <v>16691</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -2842,22 +2881,22 @@
         <v>436273</v>
       </c>
       <c r="D10" s="9">
-        <v>117850</v>
+        <v>118352</v>
       </c>
       <c r="E10" s="9">
-        <v>459053</v>
+        <v>462872</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>49</v>
       </c>
       <c r="G10" s="9">
-        <v>261683</v>
+        <v>263929</v>
       </c>
       <c r="H10" s="10" t="s">
         <v>50</v>
       </c>
       <c r="I10" s="9">
-        <v>26711</v>
+        <v>25389</v>
       </c>
       <c r="J10" s="10" t="s">
         <v>51</v>
@@ -2866,13 +2905,13 @@
         <v>7</v>
       </c>
       <c r="L10" s="9">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="M10" s="9">
-        <v>10943</v>
+        <v>10448</v>
       </c>
       <c r="N10" s="9">
-        <v>57215</v>
+        <v>55721</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -2886,22 +2925,22 @@
         <v>489942</v>
       </c>
       <c r="D11" s="9">
-        <v>91339</v>
+        <v>91602</v>
       </c>
       <c r="E11" s="9">
-        <v>509245</v>
+        <v>511817</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>54</v>
       </c>
       <c r="G11" s="9">
-        <v>313386</v>
+        <v>315074</v>
       </c>
       <c r="H11" s="10" t="s">
         <v>55</v>
       </c>
       <c r="I11" s="9">
-        <v>21478</v>
+        <v>20690</v>
       </c>
       <c r="J11" s="10" t="s">
         <v>56</v>
@@ -2910,13 +2949,13 @@
         <v>1</v>
       </c>
       <c r="L11" s="9">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M11" s="9">
-        <v>11691</v>
+        <v>11288</v>
       </c>
       <c r="N11" s="9">
-        <v>38814</v>
+        <v>37697</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -2930,22 +2969,22 @@
         <v>580719</v>
       </c>
       <c r="D12" s="9">
-        <v>111883</v>
+        <v>112283</v>
       </c>
       <c r="E12" s="9">
-        <v>608609</v>
+        <v>612842</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>59</v>
       </c>
       <c r="G12" s="9">
-        <v>374149</v>
+        <v>376841</v>
       </c>
       <c r="H12" s="10" t="s">
         <v>60</v>
       </c>
       <c r="I12" s="9">
-        <v>31387</v>
+        <v>29863</v>
       </c>
       <c r="J12" s="10" t="s">
         <v>61</v>
@@ -2954,13 +2993,13 @@
         <v>5</v>
       </c>
       <c r="L12" s="9">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="M12" s="9">
-        <v>9375</v>
+        <v>8872</v>
       </c>
       <c r="N12" s="9">
-        <v>43146</v>
+        <v>41347</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -2974,22 +3013,22 @@
         <v>263315</v>
       </c>
       <c r="D13" s="9">
-        <v>52749</v>
+        <v>52974</v>
       </c>
       <c r="E13" s="9">
-        <v>294225</v>
+        <v>296281</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>64</v>
       </c>
       <c r="G13" s="9">
-        <v>168186</v>
+        <v>169506</v>
       </c>
       <c r="H13" s="10" t="s">
         <v>65</v>
       </c>
       <c r="I13" s="9">
-        <v>7561</v>
+        <v>7008</v>
       </c>
       <c r="J13" s="10" t="s">
         <v>66</v>
@@ -3001,10 +3040,10 @@
         <v>14</v>
       </c>
       <c r="M13" s="9">
-        <v>3014</v>
+        <v>2739</v>
       </c>
       <c r="N13" s="9">
-        <v>11247</v>
+        <v>10244</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -3018,22 +3057,22 @@
         <v>187422</v>
       </c>
       <c r="D14" s="9">
-        <v>45976</v>
+        <v>46265</v>
       </c>
       <c r="E14" s="9">
-        <v>204293</v>
+        <v>205866</v>
       </c>
       <c r="F14" s="10" t="s">
         <v>69</v>
       </c>
       <c r="G14" s="9">
-        <v>122788</v>
+        <v>123698</v>
       </c>
       <c r="H14" s="10" t="s">
         <v>70</v>
       </c>
       <c r="I14" s="9">
-        <v>9433</v>
+        <v>9072</v>
       </c>
       <c r="J14" s="10" t="s">
         <v>71</v>
@@ -3042,13 +3081,13 @@
         <v>2</v>
       </c>
       <c r="L14" s="9">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="M14" s="9">
-        <v>3558</v>
+        <v>3330</v>
       </c>
       <c r="N14" s="9">
-        <v>16085</v>
+        <v>15393</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -3062,22 +3101,22 @@
         <v>154763</v>
       </c>
       <c r="D15" s="9">
-        <v>39234</v>
+        <v>39441</v>
       </c>
       <c r="E15" s="9">
-        <v>170151</v>
+        <v>171526</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>74</v>
       </c>
       <c r="G15" s="9">
-        <v>101370</v>
+        <v>102269</v>
       </c>
       <c r="H15" s="10" t="s">
         <v>75</v>
       </c>
       <c r="I15" s="9">
-        <v>9048</v>
+        <v>8719</v>
       </c>
       <c r="J15" s="10" t="s">
         <v>76</v>
@@ -3089,10 +3128,10 @@
         <v>7</v>
       </c>
       <c r="M15" s="9">
-        <v>1936</v>
+        <v>1859</v>
       </c>
       <c r="N15" s="9">
-        <v>12853</v>
+        <v>12091</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -3106,22 +3145,22 @@
         <v>170543</v>
       </c>
       <c r="D16" s="9">
-        <v>44952</v>
+        <v>45038</v>
       </c>
       <c r="E16" s="9">
-        <v>205015</v>
+        <v>206032</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>79</v>
       </c>
       <c r="G16" s="9">
-        <v>139164</v>
+        <v>139922</v>
       </c>
       <c r="H16" s="10" t="s">
         <v>80</v>
       </c>
       <c r="I16" s="9">
-        <v>6077</v>
+        <v>5579</v>
       </c>
       <c r="J16" s="10" t="s">
         <v>81</v>
@@ -3133,10 +3172,10 @@
         <v>2</v>
       </c>
       <c r="M16" s="9">
-        <v>723</v>
+        <v>679</v>
       </c>
       <c r="N16" s="9">
-        <v>3678</v>
+        <v>3289</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -3150,22 +3189,22 @@
         <v>157837</v>
       </c>
       <c r="D17" s="9">
-        <v>33783</v>
+        <v>33876</v>
       </c>
       <c r="E17" s="9">
-        <v>170638</v>
+        <v>171888</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>84</v>
       </c>
       <c r="G17" s="9">
-        <v>120736</v>
+        <v>121556</v>
       </c>
       <c r="H17" s="10" t="s">
         <v>85</v>
       </c>
       <c r="I17" s="9">
-        <v>11144</v>
+        <v>10506</v>
       </c>
       <c r="J17" s="10" t="s">
         <v>86</v>
@@ -3177,10 +3216,10 @@
         <v>2</v>
       </c>
       <c r="M17" s="9">
-        <v>1990</v>
+        <v>1907</v>
       </c>
       <c r="N17" s="9">
-        <v>7846</v>
+        <v>7410</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -3194,22 +3233,22 @@
         <v>86207</v>
       </c>
       <c r="D18" s="9">
-        <v>26734</v>
+        <v>26755</v>
       </c>
       <c r="E18" s="9">
-        <v>114049</v>
+        <v>114236</v>
       </c>
       <c r="F18" s="10" t="s">
         <v>89</v>
       </c>
       <c r="G18" s="9">
-        <v>74648</v>
+        <v>74777</v>
       </c>
       <c r="H18" s="10" t="s">
         <v>90</v>
       </c>
       <c r="I18" s="9">
-        <v>409</v>
+        <v>225</v>
       </c>
       <c r="J18" s="10" t="s">
         <v>91</v>
@@ -3221,10 +3260,10 @@
         <v>0</v>
       </c>
       <c r="M18" s="9">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="N18" s="9">
-        <v>-1530</v>
+        <v>-1503</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -3238,22 +3277,22 @@
         <v>109078</v>
       </c>
       <c r="D19" s="9">
-        <v>30296</v>
+        <v>30359</v>
       </c>
       <c r="E19" s="9">
-        <v>138160</v>
+        <v>138691</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>94</v>
       </c>
       <c r="G19" s="9">
-        <v>93150</v>
+        <v>93531</v>
       </c>
       <c r="H19" s="10" t="s">
         <v>95</v>
       </c>
       <c r="I19" s="9">
-        <v>1976</v>
+        <v>1707</v>
       </c>
       <c r="J19" s="10" t="s">
         <v>96</v>
@@ -3265,10 +3304,10 @@
         <v>1</v>
       </c>
       <c r="M19" s="9">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="N19" s="9">
-        <v>-984</v>
+        <v>-1162</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -3282,22 +3321,22 @@
         <v>47152</v>
       </c>
       <c r="D20" s="9">
-        <v>14026</v>
+        <v>14039</v>
       </c>
       <c r="E20" s="9">
-        <v>61005</v>
+        <v>61031</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>99</v>
       </c>
       <c r="G20" s="9">
-        <v>44064</v>
+        <v>44089</v>
       </c>
       <c r="H20" s="10" t="s">
         <v>100</v>
       </c>
       <c r="I20" s="9">
-        <v>412</v>
+        <v>390</v>
       </c>
       <c r="J20" s="10" t="s">
         <v>101</v>
@@ -3309,10 +3348,10 @@
         <v>0</v>
       </c>
       <c r="M20" s="9">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N20" s="9">
-        <v>-274</v>
+        <v>-264</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -3323,25 +3362,25 @@
         <v>103</v>
       </c>
       <c r="C21" s="9">
-        <v>410237</v>
+        <v>410236</v>
       </c>
       <c r="D21" s="9">
-        <v>96834</v>
+        <v>97131</v>
       </c>
       <c r="E21" s="9">
-        <v>412527</v>
+        <v>415442</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>104</v>
       </c>
       <c r="G21" s="9">
-        <v>197437</v>
+        <v>198820</v>
       </c>
       <c r="H21" s="10" t="s">
         <v>105</v>
       </c>
       <c r="I21" s="9">
-        <v>25061</v>
+        <v>24158</v>
       </c>
       <c r="J21" s="10" t="s">
         <v>106</v>
@@ -3350,13 +3389,13 @@
         <v>71</v>
       </c>
       <c r="L21" s="9">
-        <v>880</v>
+        <v>838</v>
       </c>
       <c r="M21" s="9">
-        <v>18879</v>
+        <v>18284</v>
       </c>
       <c r="N21" s="9">
-        <v>49653</v>
+        <v>48574</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -3370,22 +3409,22 @@
         <v>70493</v>
       </c>
       <c r="D22" s="9">
-        <v>14742</v>
+        <v>14775</v>
       </c>
       <c r="E22" s="9">
-        <v>73979</v>
+        <v>74450</v>
       </c>
       <c r="F22" s="10" t="s">
         <v>109</v>
       </c>
       <c r="G22" s="9">
-        <v>45096</v>
+        <v>45381</v>
       </c>
       <c r="H22" s="10" t="s">
         <v>110</v>
       </c>
       <c r="I22" s="9">
-        <v>4577</v>
+        <v>4326</v>
       </c>
       <c r="J22" s="10" t="s">
         <v>111</v>
@@ -3397,10 +3436,10 @@
         <v>5</v>
       </c>
       <c r="M22" s="9">
-        <v>1744</v>
+        <v>1693</v>
       </c>
       <c r="N22" s="9">
-        <v>4930</v>
+        <v>4794</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -3414,22 +3453,22 @@
         <v>3491483</v>
       </c>
       <c r="D23" s="12">
-        <v>801748</v>
+        <v>804430</v>
       </c>
       <c r="E23" s="12">
-        <v>3789240</v>
+        <v>3813155</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>34</v>
       </c>
       <c r="G23" s="12">
-        <v>2294289</v>
+        <v>2309055</v>
       </c>
       <c r="H23" s="13" t="s">
         <v>35</v>
       </c>
       <c r="I23" s="12">
-        <v>173276</v>
+        <v>164830</v>
       </c>
       <c r="J23" s="13" t="s">
         <v>36</v>
@@ -3438,13 +3477,13 @@
         <v>98</v>
       </c>
       <c r="L23" s="12">
-        <v>1273</v>
+        <v>1214</v>
       </c>
       <c r="M23" s="12">
-        <v>69915</v>
+        <v>66900</v>
       </c>
       <c r="N23" s="12">
-        <v>259429</v>
+        <v>249716</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
@@ -4097,7 +4136,7 @@
         <v>191</v>
       </c>
       <c r="P8" s="6">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q8" s="7" t="s">
         <v>192</v>
@@ -4151,13 +4190,13 @@
         <v>190</v>
       </c>
       <c r="AH8" s="6">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI8" s="7" t="s">
         <v>191</v>
       </c>
       <c r="AJ8" s="6">
-        <v>46974</v>
+        <v>47400</v>
       </c>
       <c r="AK8" s="7" t="s">
         <v>198</v>
@@ -4282,7 +4321,7 @@
         <v>190</v>
       </c>
       <c r="AJ9" s="9">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AK9" s="10" t="s">
         <v>208</v>
@@ -4308,7 +4347,7 @@
         <v>43</v>
       </c>
       <c r="C10" s="9">
-        <v>57473</v>
+        <v>57474</v>
       </c>
       <c r="D10" s="9">
         <v>52</v>
@@ -4401,13 +4440,13 @@
         <v>190</v>
       </c>
       <c r="AH10" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI10" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AJ10" s="9">
-        <v>5745</v>
+        <v>5806</v>
       </c>
       <c r="AK10" s="10" t="s">
         <v>218</v>
@@ -4532,7 +4571,7 @@
         <v>191</v>
       </c>
       <c r="AJ11" s="9">
-        <v>2510</v>
+        <v>2534</v>
       </c>
       <c r="AK11" s="10" t="s">
         <v>227</v>
@@ -4657,7 +4696,7 @@
         <v>190</v>
       </c>
       <c r="AJ12" s="9">
-        <v>13978</v>
+        <v>14073</v>
       </c>
       <c r="AK12" s="10" t="s">
         <v>236</v>
@@ -4782,7 +4821,7 @@
         <v>191</v>
       </c>
       <c r="AJ13" s="9">
-        <v>7768</v>
+        <v>7850</v>
       </c>
       <c r="AK13" s="10" t="s">
         <v>244</v>
@@ -4907,7 +4946,7 @@
         <v>190</v>
       </c>
       <c r="AJ14" s="9">
-        <v>4545</v>
+        <v>4593</v>
       </c>
       <c r="AK14" s="10" t="s">
         <v>253</v>
@@ -5005,19 +5044,19 @@
         <v>2525</v>
       </c>
       <c r="AA15" s="10" t="s">
-        <v>106</v>
+        <v>258</v>
       </c>
       <c r="AB15" s="9">
         <v>18452</v>
       </c>
       <c r="AC15" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AD15" s="9">
         <v>5358</v>
       </c>
       <c r="AE15" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AF15" s="9">
         <v>0</v>
@@ -5032,22 +5071,22 @@
         <v>190</v>
       </c>
       <c r="AJ15" s="9">
-        <v>3897</v>
+        <v>3934</v>
       </c>
       <c r="AK15" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AL15" s="9">
         <v>7682</v>
       </c>
       <c r="AM15" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN15" s="9">
         <v>7718</v>
       </c>
       <c r="AO15" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -5064,7 +5103,7 @@
         <v>45</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F16" s="9">
         <v>1</v>
@@ -5112,37 +5151,37 @@
         <v>45</v>
       </c>
       <c r="U16" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="V16" s="9">
         <v>3750</v>
       </c>
       <c r="W16" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="X16" s="9">
         <v>2417</v>
       </c>
       <c r="Y16" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Z16" s="9">
         <v>875</v>
       </c>
       <c r="AA16" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AB16" s="9">
         <v>8098</v>
       </c>
       <c r="AC16" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AD16" s="9">
         <v>4600</v>
       </c>
       <c r="AE16" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AF16" s="9">
         <v>0</v>
@@ -5157,22 +5196,22 @@
         <v>190</v>
       </c>
       <c r="AJ16" s="9">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AK16" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AL16" s="9">
         <v>8350</v>
       </c>
       <c r="AM16" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AN16" s="9">
         <v>8395</v>
       </c>
       <c r="AO16" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -5189,7 +5228,7 @@
         <v>48</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>272</v>
+        <v>91</v>
       </c>
       <c r="F17" s="9">
         <v>0</v>
@@ -5237,7 +5276,7 @@
         <v>48</v>
       </c>
       <c r="U17" s="10" t="s">
-        <v>272</v>
+        <v>91</v>
       </c>
       <c r="V17" s="9">
         <v>5545</v>
@@ -5282,7 +5321,7 @@
         <v>191</v>
       </c>
       <c r="AJ17" s="9">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AK17" s="10" t="s">
         <v>278</v>
@@ -5407,7 +5446,7 @@
         <v>190</v>
       </c>
       <c r="AJ18" s="9">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AK18" s="10" t="s">
         <v>286</v>
@@ -5755,19 +5794,19 @@
         <v>387</v>
       </c>
       <c r="AA21" s="10" t="s">
-        <v>309</v>
+        <v>253</v>
       </c>
       <c r="AB21" s="9">
         <v>2184</v>
       </c>
       <c r="AC21" s="10" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AD21" s="9">
         <v>1730</v>
       </c>
       <c r="AE21" s="10" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AF21" s="9">
         <v>0</v>
@@ -5782,22 +5821,22 @@
         <v>190</v>
       </c>
       <c r="AJ21" s="9">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AK21" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AL21" s="9">
         <v>2916</v>
       </c>
       <c r="AM21" s="10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AN21" s="9">
         <v>2925</v>
       </c>
       <c r="AO21" s="10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -5808,13 +5847,13 @@
         <v>103</v>
       </c>
       <c r="C22" s="9">
-        <v>130759</v>
+        <v>130758</v>
       </c>
       <c r="D22" s="9">
         <v>391</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F22" s="9">
         <v>2</v>
@@ -5832,13 +5871,13 @@
         <v>50</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="L22" s="9">
         <v>52</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="N22" s="9">
         <v>42</v>
@@ -5847,7 +5886,7 @@
         <v>202</v>
       </c>
       <c r="P22" s="9">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q22" s="10" t="s">
         <v>230</v>
@@ -5862,37 +5901,37 @@
         <v>391</v>
       </c>
       <c r="U22" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="V22" s="9">
         <v>8651</v>
       </c>
       <c r="W22" s="10" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="X22" s="9">
         <v>17594</v>
       </c>
       <c r="Y22" s="10" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Z22" s="9">
         <v>9167</v>
       </c>
       <c r="AA22" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AB22" s="9">
         <v>62349</v>
       </c>
       <c r="AC22" s="10" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AD22" s="9">
         <v>13986</v>
       </c>
       <c r="AE22" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF22" s="9">
         <v>3</v>
@@ -5907,22 +5946,22 @@
         <v>202</v>
       </c>
       <c r="AJ22" s="9">
-        <v>6815</v>
+        <v>6892</v>
       </c>
       <c r="AK22" s="10" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AL22" s="9">
         <v>22637</v>
       </c>
       <c r="AM22" s="10" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AN22" s="9">
         <v>23028</v>
       </c>
       <c r="AO22" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -5939,7 +5978,7 @@
         <v>43</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
@@ -5987,37 +6026,37 @@
         <v>43</v>
       </c>
       <c r="U23" s="10" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="V23" s="9">
         <v>3709</v>
       </c>
       <c r="W23" s="10" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="X23" s="9">
         <v>3257</v>
       </c>
       <c r="Y23" s="10" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z23" s="9">
         <v>3091</v>
       </c>
       <c r="AA23" s="10" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AB23" s="9">
         <v>3535</v>
       </c>
       <c r="AC23" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AD23" s="9">
         <v>3078</v>
       </c>
       <c r="AE23" s="10" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AF23" s="9">
         <v>0</v>
@@ -6035,19 +6074,19 @@
         <v>283</v>
       </c>
       <c r="AK23" s="10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AL23" s="9">
         <v>6787</v>
       </c>
       <c r="AM23" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN23" s="9">
         <v>6830</v>
       </c>
       <c r="AO23" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -6097,7 +6136,7 @@
         <v>191</v>
       </c>
       <c r="P24" s="12">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q24" s="13" t="s">
         <v>192</v>
@@ -6151,13 +6190,13 @@
         <v>190</v>
       </c>
       <c r="AH24" s="12">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI24" s="13" t="s">
         <v>191</v>
       </c>
       <c r="AJ24" s="12">
-        <v>46974</v>
+        <v>47400</v>
       </c>
       <c r="AK24" s="13" t="s">
         <v>198</v>
@@ -6222,10 +6261,10 @@
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
+        <v>333</v>
+      </c>
+      <c r="B27" s="16" t="s">
         <v>334</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>335</v>
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
@@ -6269,10 +6308,10 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
+        <v>335</v>
+      </c>
+      <c r="B28" s="16" t="s">
         <v>336</v>
-      </c>
-      <c r="B28" s="16" t="s">
-        <v>337</v>
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="16"/>
@@ -6355,7 +6394,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6399,13 +6438,13 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
@@ -6432,31 +6471,31 @@
         <v>122</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="I5" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="K5" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="L5" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="M5" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="N5" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="N5" s="3" t="s">
+      <c r="O5" s="3" t="s">
         <v>348</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6526,31 +6565,31 @@
         <v>760551</v>
       </c>
       <c r="G7" s="6">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="H7" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="I7" s="6">
+        <v>906</v>
+      </c>
+      <c r="J7" s="7" t="s">
         <v>350</v>
       </c>
-      <c r="I7" s="6">
-        <v>871</v>
-      </c>
-      <c r="J7" s="7" t="s">
+      <c r="K7" s="6">
+        <v>197866</v>
+      </c>
+      <c r="L7" s="7" t="s">
         <v>351</v>
       </c>
-      <c r="K7" s="6">
-        <v>195894</v>
-      </c>
-      <c r="L7" s="7" t="s">
+      <c r="M7" s="6">
+        <v>991</v>
+      </c>
+      <c r="N7" s="6">
+        <v>201021</v>
+      </c>
+      <c r="O7" s="7" t="s">
         <v>352</v>
-      </c>
-      <c r="M7" s="6">
-        <v>979</v>
-      </c>
-      <c r="N7" s="6">
-        <v>199001</v>
-      </c>
-      <c r="O7" s="7" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6579,25 +6618,25 @@
         <v>353</v>
       </c>
       <c r="I8" s="9">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J8" s="10" t="s">
         <v>354</v>
       </c>
       <c r="K8" s="9">
-        <v>3971</v>
+        <v>3990</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>355</v>
+        <v>209</v>
       </c>
       <c r="M8" s="9">
         <v>13</v>
       </c>
       <c r="N8" s="9">
-        <v>4072</v>
+        <v>4090</v>
       </c>
       <c r="O8" s="10" t="s">
-        <v>210</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6608,7 +6647,7 @@
         <v>43</v>
       </c>
       <c r="C9" s="9">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D9" s="9">
         <v>77</v>
@@ -6617,7 +6656,7 @@
         <v>57283</v>
       </c>
       <c r="F9" s="9">
-        <v>57473</v>
+        <v>57474</v>
       </c>
       <c r="G9" s="9">
         <v>59</v>
@@ -6632,7 +6671,7 @@
         <v>357</v>
       </c>
       <c r="K9" s="9">
-        <v>10125</v>
+        <v>10209</v>
       </c>
       <c r="L9" s="10" t="s">
         <v>358</v>
@@ -6641,10 +6680,10 @@
         <v>62</v>
       </c>
       <c r="N9" s="9">
-        <v>10259</v>
+        <v>10343</v>
       </c>
       <c r="O9" s="10" t="s">
-        <v>220</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6667,31 +6706,31 @@
         <v>93539</v>
       </c>
       <c r="G10" s="9">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H10" s="10" t="s">
         <v>359</v>
       </c>
       <c r="I10" s="9">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J10" s="10" t="s">
         <v>360</v>
       </c>
       <c r="K10" s="9">
-        <v>18113</v>
+        <v>18369</v>
       </c>
       <c r="L10" s="10" t="s">
         <v>361</v>
       </c>
       <c r="M10" s="9">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="N10" s="9">
-        <v>18442</v>
+        <v>18703</v>
       </c>
       <c r="O10" s="10" t="s">
-        <v>229</v>
+        <v>362</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6717,28 +6756,28 @@
         <v>97</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="I11" s="9">
         <v>79</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K11" s="9">
-        <v>29556</v>
+        <v>29750</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M11" s="9">
         <v>192</v>
       </c>
       <c r="N11" s="9">
-        <v>29924</v>
+        <v>30118</v>
       </c>
       <c r="O11" s="10" t="s">
-        <v>238</v>
+        <v>366</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6764,28 +6803,28 @@
         <v>145</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="I12" s="9">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>215</v>
+        <v>368</v>
       </c>
       <c r="K12" s="9">
-        <v>34503</v>
+        <v>34843</v>
       </c>
       <c r="L12" s="10" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="M12" s="9">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N12" s="9">
-        <v>34940</v>
+        <v>35284</v>
       </c>
       <c r="O12" s="10" t="s">
-        <v>246</v>
+        <v>370</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6808,31 +6847,31 @@
         <v>63919</v>
       </c>
       <c r="G13" s="9">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="I13" s="9">
         <v>67</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="K13" s="9">
-        <v>11942</v>
+        <v>12082</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="M13" s="9">
         <v>39</v>
       </c>
       <c r="N13" s="9">
-        <v>12109</v>
+        <v>12250</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>255</v>
+        <v>374</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6858,28 +6897,28 @@
         <v>44</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="I14" s="9">
         <v>15</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="K14" s="9">
-        <v>7605</v>
+        <v>7787</v>
       </c>
       <c r="L14" s="10" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="M14" s="9">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N14" s="9">
-        <v>7718</v>
+        <v>7901</v>
       </c>
       <c r="O14" s="10" t="s">
-        <v>262</v>
+        <v>378</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6905,28 +6944,28 @@
         <v>49</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="I15" s="9">
         <v>19</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="K15" s="9">
-        <v>8315</v>
+        <v>8446</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="M15" s="9">
         <v>12</v>
       </c>
       <c r="N15" s="9">
-        <v>8395</v>
+        <v>8526</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>271</v>
+        <v>382</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6952,28 +6991,28 @@
         <v>53</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="I16" s="9">
         <v>48</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="K16" s="9">
-        <v>11386</v>
+        <v>11466</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="M16" s="9">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N16" s="9">
-        <v>11528</v>
+        <v>11610</v>
       </c>
       <c r="O16" s="10" t="s">
-        <v>280</v>
+        <v>386</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6999,28 +7038,28 @@
         <v>41</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="I17" s="9">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="K17" s="9">
-        <v>13087</v>
+        <v>13250</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="M17" s="9">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N17" s="9">
-        <v>13213</v>
+        <v>13378</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>288</v>
+        <v>390</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -7046,28 +7085,28 @@
         <v>30</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="I18" s="9">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="K18" s="9">
-        <v>6899</v>
+        <v>6930</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="M18" s="9">
         <v>12</v>
       </c>
       <c r="N18" s="9">
-        <v>6959</v>
+        <v>6991</v>
       </c>
       <c r="O18" s="10" t="s">
-        <v>297</v>
+        <v>394</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -7093,28 +7132,28 @@
         <v>27</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="I19" s="9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="K19" s="9">
-        <v>8599</v>
+        <v>8672</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="M19" s="9">
         <v>12</v>
       </c>
       <c r="N19" s="9">
-        <v>8659</v>
+        <v>8733</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>305</v>
+        <v>397</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -7140,28 +7179,28 @@
         <v>10</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="I20" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J20" s="10" t="s">
         <v>190</v>
       </c>
       <c r="K20" s="9">
-        <v>2913</v>
+        <v>2917</v>
       </c>
       <c r="L20" s="10" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="M20" s="9">
         <v>0</v>
       </c>
       <c r="N20" s="9">
-        <v>2925</v>
+        <v>2930</v>
       </c>
       <c r="O20" s="10" t="s">
-        <v>314</v>
+        <v>400</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -7172,7 +7211,7 @@
         <v>103</v>
       </c>
       <c r="C21" s="9">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D21" s="9">
         <v>4256</v>
@@ -7181,34 +7220,34 @@
         <v>125822</v>
       </c>
       <c r="F21" s="9">
-        <v>130759</v>
+        <v>130758</v>
       </c>
       <c r="G21" s="9">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="I21" s="9">
-        <v>239</v>
+        <v>264</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>256</v>
+        <v>402</v>
       </c>
       <c r="K21" s="9">
-        <v>22203</v>
+        <v>22419</v>
       </c>
       <c r="L21" s="10" t="s">
-        <v>391</v>
+        <v>358</v>
       </c>
       <c r="M21" s="9">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="N21" s="9">
-        <v>23028</v>
+        <v>23272</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>324</v>
+        <v>403</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -7234,28 +7273,28 @@
         <v>47</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="I22" s="9">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="K22" s="9">
-        <v>6677</v>
+        <v>6736</v>
       </c>
       <c r="L22" s="10" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="M22" s="9">
         <v>38</v>
       </c>
       <c r="N22" s="9">
-        <v>6830</v>
+        <v>6892</v>
       </c>
       <c r="O22" s="10" t="s">
-        <v>333</v>
+        <v>407</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -7278,31 +7317,31 @@
         <v>760551</v>
       </c>
       <c r="G23" s="12">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="H23" s="13" t="s">
+        <v>349</v>
+      </c>
+      <c r="I23" s="12">
+        <v>906</v>
+      </c>
+      <c r="J23" s="13" t="s">
         <v>350</v>
       </c>
-      <c r="I23" s="12">
-        <v>871</v>
-      </c>
-      <c r="J23" s="13" t="s">
+      <c r="K23" s="12">
+        <v>197866</v>
+      </c>
+      <c r="L23" s="13" t="s">
         <v>351</v>
       </c>
-      <c r="K23" s="12">
-        <v>195894</v>
-      </c>
-      <c r="L23" s="13" t="s">
+      <c r="M23" s="12">
+        <v>991</v>
+      </c>
+      <c r="N23" s="12">
+        <v>201021</v>
+      </c>
+      <c r="O23" s="13" t="s">
         <v>352</v>
-      </c>
-      <c r="M23" s="12">
-        <v>979</v>
-      </c>
-      <c r="N23" s="12">
-        <v>199001</v>
-      </c>
-      <c r="O23" s="13" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -7326,10 +7365,10 @@
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>395</v>
+        <v>408</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="C26" s="16"/>
       <c r="D26" s="16"/>
@@ -7347,10 +7386,10 @@
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
-        <v>397</v>
+        <v>410</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
@@ -7368,10 +7407,10 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="16"/>
@@ -7389,10 +7428,10 @@
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="C29" s="16"/>
       <c r="D29" s="16"/>
@@ -7410,10 +7449,10 @@
     </row>
     <row r="30" ht="24" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>404</v>
+        <v>417</v>
       </c>
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
@@ -7475,7 +7514,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7523,10 +7562,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -7540,10 +7579,10 @@
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3" t="s">
-        <v>408</v>
+        <v>421</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>409</v>
+        <v>422</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7656,31 +7695,31 @@
         <v>1017668</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="F7" s="6">
         <v>500243</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="H7" s="6">
         <v>8064</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="J7" s="6">
         <v>203183</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>260</v>
+        <v>426</v>
       </c>
       <c r="L7" s="6">
         <v>711448</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="N7" s="6">
         <v>313</v>
@@ -7692,7 +7731,7 @@
         <v>1729116</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7709,19 +7748,19 @@
         <v>60312</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c r="F8" s="9">
         <v>20382</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="H8" s="9">
         <v>520</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>417</v>
+        <v>431</v>
       </c>
       <c r="J8" s="9">
         <v>9558</v>
@@ -7733,7 +7772,7 @@
         <v>30868</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="N8" s="9">
         <v>20</v>
@@ -7745,7 +7784,7 @@
         <v>91180</v>
       </c>
       <c r="Q8" s="10" t="s">
-        <v>419</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7762,31 +7801,31 @@
         <v>75479</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="F9" s="9">
         <v>41448</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="H9" s="9">
         <v>738</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="J9" s="9">
         <v>13545</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>423</v>
+        <v>437</v>
       </c>
       <c r="L9" s="9">
         <v>57211</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="N9" s="9">
         <v>16</v>
@@ -7798,7 +7837,7 @@
         <v>132690</v>
       </c>
       <c r="Q9" s="10" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7815,31 +7854,31 @@
         <v>72700</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>426</v>
+        <v>440</v>
       </c>
       <c r="F10" s="9">
         <v>44894</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="H10" s="9">
         <v>372</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>428</v>
+        <v>442</v>
       </c>
       <c r="J10" s="9">
         <v>29280</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>429</v>
+        <v>443</v>
       </c>
       <c r="L10" s="9">
         <v>62167</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="N10" s="9">
         <v>17</v>
@@ -7851,7 +7890,7 @@
         <v>134867</v>
       </c>
       <c r="Q10" s="10" t="s">
-        <v>431</v>
+        <v>445</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7868,13 +7907,13 @@
         <v>168209</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>432</v>
+        <v>105</v>
       </c>
       <c r="F11" s="9">
         <v>76152</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>433</v>
+        <v>446</v>
       </c>
       <c r="H11" s="9">
         <v>769</v>
@@ -7886,13 +7925,13 @@
         <v>28845</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>434</v>
+        <v>447</v>
       </c>
       <c r="L11" s="9">
         <v>122052</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>435</v>
+        <v>448</v>
       </c>
       <c r="N11" s="9">
         <v>56</v>
@@ -7904,7 +7943,7 @@
         <v>290261</v>
       </c>
       <c r="Q11" s="10" t="s">
-        <v>436</v>
+        <v>449</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7921,31 +7960,31 @@
         <v>202943</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>437</v>
+        <v>450</v>
       </c>
       <c r="F12" s="9">
         <v>87661</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>438</v>
+        <v>451</v>
       </c>
       <c r="H12" s="9">
         <v>887</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>439</v>
+        <v>452</v>
       </c>
       <c r="J12" s="9">
         <v>43774</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="L12" s="9">
         <v>131892</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="N12" s="9">
         <v>57</v>
@@ -7957,7 +7996,7 @@
         <v>334835</v>
       </c>
       <c r="Q12" s="10" t="s">
-        <v>442</v>
+        <v>455</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7974,31 +8013,31 @@
         <v>60385</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c r="F13" s="9">
         <v>24766</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="H13" s="9">
         <v>270</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>439</v>
+        <v>452</v>
       </c>
       <c r="J13" s="9">
         <v>21851</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>445</v>
+        <v>458</v>
       </c>
       <c r="L13" s="9">
         <v>47449</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="N13" s="9">
         <v>15</v>
@@ -8010,7 +8049,7 @@
         <v>107834</v>
       </c>
       <c r="Q13" s="10" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8027,13 +8066,13 @@
         <v>59493</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="F14" s="9">
         <v>27298</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>449</v>
+        <v>462</v>
       </c>
       <c r="H14" s="9">
         <v>225</v>
@@ -8045,13 +8084,13 @@
         <v>10791</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="L14" s="9">
         <v>47777</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="N14" s="9">
         <v>17</v>
@@ -8063,7 +8102,7 @@
         <v>107270</v>
       </c>
       <c r="Q14" s="10" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8080,31 +8119,31 @@
         <v>47952</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>453</v>
+        <v>466</v>
       </c>
       <c r="F15" s="9">
         <v>29118</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>454</v>
+        <v>467</v>
       </c>
       <c r="H15" s="9">
         <v>536</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>91</v>
+        <v>468</v>
       </c>
       <c r="J15" s="9">
         <v>5495</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>455</v>
+        <v>469</v>
       </c>
       <c r="L15" s="9">
         <v>30388</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>456</v>
+        <v>470</v>
       </c>
       <c r="N15" s="9">
         <v>6</v>
@@ -8116,7 +8155,7 @@
         <v>78340</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8133,31 +8172,31 @@
         <v>79247</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>458</v>
+        <v>472</v>
       </c>
       <c r="F16" s="9">
         <v>41824</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>459</v>
+        <v>473</v>
       </c>
       <c r="H16" s="9">
         <v>1091</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>460</v>
+        <v>474</v>
       </c>
       <c r="J16" s="9">
         <v>10558</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>461</v>
+        <v>46</v>
       </c>
       <c r="L16" s="9">
         <v>35456</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>462</v>
+        <v>475</v>
       </c>
       <c r="N16" s="9">
         <v>25</v>
@@ -8169,7 +8208,7 @@
         <v>114703</v>
       </c>
       <c r="Q16" s="10" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8186,31 +8225,31 @@
         <v>54547</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="F17" s="9">
         <v>33609</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="H17" s="9">
         <v>659</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>466</v>
+        <v>479</v>
       </c>
       <c r="J17" s="9">
         <v>6934</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>467</v>
+        <v>106</v>
       </c>
       <c r="L17" s="9">
         <v>30950</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="N17" s="9">
         <v>5</v>
@@ -8222,7 +8261,7 @@
         <v>85497</v>
       </c>
       <c r="Q17" s="10" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8239,25 +8278,25 @@
         <v>37776</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="F18" s="9">
         <v>23983</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="H18" s="9">
         <v>571</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>460</v>
+        <v>474</v>
       </c>
       <c r="J18" s="9">
         <v>9844</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="L18" s="9">
         <v>22578</v>
@@ -8269,13 +8308,13 @@
         <v>36</v>
       </c>
       <c r="O18" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="P18" s="9">
         <v>60354</v>
       </c>
       <c r="Q18" s="10" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8292,19 +8331,19 @@
         <v>57568</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="F19" s="9">
         <v>24075</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="H19" s="9">
         <v>556</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="J19" s="9">
         <v>7698</v>
@@ -8316,7 +8355,7 @@
         <v>32223</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="N19" s="9">
         <v>13</v>
@@ -8328,7 +8367,7 @@
         <v>89791</v>
       </c>
       <c r="Q19" s="10" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8345,31 +8384,31 @@
         <v>27611</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="F20" s="9">
         <v>14938</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="H20" s="9">
         <v>223</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="J20" s="9">
         <v>2474</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="L20" s="9">
         <v>13474</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="N20" s="9">
         <v>6</v>
@@ -8381,7 +8420,7 @@
         <v>41085</v>
       </c>
       <c r="Q20" s="10" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8398,31 +8437,31 @@
         <v>2844</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="F21" s="9">
         <v>3576</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="H21" s="9">
         <v>97</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="J21" s="9">
         <v>1802</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="L21" s="9">
         <v>38449</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="N21" s="9">
         <v>18</v>
@@ -8434,7 +8473,7 @@
         <v>41293</v>
       </c>
       <c r="Q21" s="10" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8451,31 +8490,31 @@
         <v>10602</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="F22" s="9">
         <v>6519</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="H22" s="9">
         <v>550</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="J22" s="9">
         <v>734</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="L22" s="9">
         <v>8514</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="N22" s="9">
         <v>6</v>
@@ -8487,7 +8526,7 @@
         <v>19116</v>
       </c>
       <c r="Q22" s="10" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8504,31 +8543,31 @@
         <v>1017668</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="F23" s="12">
         <v>500243</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="H23" s="12">
         <v>8064</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="J23" s="12">
         <v>203183</v>
       </c>
       <c r="K23" s="13" t="s">
-        <v>260</v>
+        <v>426</v>
       </c>
       <c r="L23" s="12">
         <v>711448</v>
       </c>
       <c r="M23" s="13" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="N23" s="12">
         <v>313</v>
@@ -8540,7 +8579,7 @@
         <v>1729116</v>
       </c>
       <c r="Q23" s="13" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -8566,10 +8605,10 @@
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C26" s="16"/>
       <c r="D26" s="16"/>
@@ -8631,7 +8670,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -8686,13 +8725,13 @@
         <v>122</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
@@ -8700,7 +8739,7 @@
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -8708,10 +8747,10 @@
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
       <c r="R4" s="3" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8733,28 +8772,28 @@
         <v>153</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
@@ -8856,25 +8895,25 @@
         <v>1017668</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="N7" s="6">
         <v>711448</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="P7" s="6">
         <v>1729116</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="R7" s="6">
         <v>1928117</v>
       </c>
       <c r="S7" s="7" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8897,7 +8936,7 @@
         <v>2003</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="H8" s="9">
         <v>2069</v>
@@ -8915,25 +8954,25 @@
         <v>60312</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c r="N8" s="9">
         <v>30868</v>
       </c>
       <c r="O8" s="10" t="s">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="P8" s="9">
         <v>91180</v>
       </c>
       <c r="Q8" s="10" t="s">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="R8" s="9">
         <v>95252</v>
       </c>
       <c r="S8" s="10" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8944,19 +8983,19 @@
         <v>43</v>
       </c>
       <c r="C9" s="9">
-        <v>57473</v>
+        <v>57474</v>
       </c>
       <c r="D9" s="9">
         <v>171893</v>
       </c>
       <c r="E9" s="9">
-        <v>229366</v>
+        <v>229367</v>
       </c>
       <c r="F9" s="9">
         <v>4950</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="H9" s="9">
         <v>5309</v>
@@ -8974,25 +9013,25 @@
         <v>75479</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="N9" s="9">
         <v>57211</v>
       </c>
       <c r="O9" s="10" t="s">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="P9" s="9">
         <v>132690</v>
       </c>
       <c r="Q9" s="10" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="R9" s="9">
         <v>142949</v>
       </c>
       <c r="S9" s="10" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9015,7 +9054,7 @@
         <v>5525</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="H10" s="9">
         <v>12917</v>
@@ -9033,25 +9072,25 @@
         <v>72700</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>426</v>
+        <v>440</v>
       </c>
       <c r="N10" s="9">
         <v>62167</v>
       </c>
       <c r="O10" s="10" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="P10" s="9">
         <v>134867</v>
       </c>
       <c r="Q10" s="10" t="s">
-        <v>431</v>
+        <v>445</v>
       </c>
       <c r="R10" s="9">
         <v>153309</v>
       </c>
       <c r="S10" s="10" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9074,7 +9113,7 @@
         <v>14322</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="H11" s="9">
         <v>15602</v>
@@ -9092,25 +9131,25 @@
         <v>168209</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>432</v>
+        <v>105</v>
       </c>
       <c r="N11" s="9">
         <v>122052</v>
       </c>
       <c r="O11" s="10" t="s">
-        <v>435</v>
+        <v>448</v>
       </c>
       <c r="P11" s="9">
         <v>290261</v>
       </c>
       <c r="Q11" s="10" t="s">
-        <v>436</v>
+        <v>449</v>
       </c>
       <c r="R11" s="9">
         <v>320185</v>
       </c>
       <c r="S11" s="10" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9133,7 +9172,7 @@
         <v>13821</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="H12" s="9">
         <v>21119</v>
@@ -9151,25 +9190,25 @@
         <v>202943</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>437</v>
+        <v>450</v>
       </c>
       <c r="N12" s="9">
         <v>131892</v>
       </c>
       <c r="O12" s="10" t="s">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="P12" s="9">
         <v>334835</v>
       </c>
       <c r="Q12" s="10" t="s">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="R12" s="9">
         <v>369775</v>
       </c>
       <c r="S12" s="10" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9192,7 +9231,7 @@
         <v>4640</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="H13" s="9">
         <v>7469</v>
@@ -9210,25 +9249,25 @@
         <v>60385</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c r="N13" s="9">
         <v>47449</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="P13" s="9">
         <v>107834</v>
       </c>
       <c r="Q13" s="10" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="R13" s="9">
         <v>119943</v>
       </c>
       <c r="S13" s="10" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9251,43 +9290,43 @@
         <v>2360</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="H14" s="9">
         <v>5358</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J14" s="9">
         <v>7718</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L14" s="9">
         <v>59493</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="N14" s="9">
         <v>47777</v>
       </c>
       <c r="O14" s="10" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="P14" s="9">
         <v>107270</v>
       </c>
       <c r="Q14" s="10" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="R14" s="9">
         <v>114988</v>
       </c>
       <c r="S14" s="10" t="s">
-        <v>525</v>
+        <v>537</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9310,43 +9349,43 @@
         <v>3795</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="H15" s="9">
         <v>4600</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J15" s="9">
         <v>8395</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L15" s="9">
         <v>47952</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>453</v>
+        <v>466</v>
       </c>
       <c r="N15" s="9">
         <v>30388</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>456</v>
+        <v>470</v>
       </c>
       <c r="P15" s="9">
         <v>78340</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="R15" s="9">
         <v>86735</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>527</v>
+        <v>539</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9369,7 +9408,7 @@
         <v>5593</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="H16" s="9">
         <v>5935</v>
@@ -9387,25 +9426,25 @@
         <v>79247</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>458</v>
+        <v>472</v>
       </c>
       <c r="N16" s="9">
         <v>35456</v>
       </c>
       <c r="O16" s="10" t="s">
-        <v>462</v>
+        <v>475</v>
       </c>
       <c r="P16" s="9">
         <v>114703</v>
       </c>
       <c r="Q16" s="10" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="R16" s="9">
         <v>126231</v>
       </c>
       <c r="S16" s="10" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9428,7 +9467,7 @@
         <v>7435</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="H17" s="9">
         <v>5778</v>
@@ -9446,25 +9485,25 @@
         <v>54547</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="N17" s="9">
         <v>30950</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="P17" s="9">
         <v>85497</v>
       </c>
       <c r="Q17" s="10" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="R17" s="9">
         <v>98710</v>
       </c>
       <c r="S17" s="10" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9487,7 +9526,7 @@
         <v>3127</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="H18" s="9">
         <v>3832</v>
@@ -9505,7 +9544,7 @@
         <v>37776</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="N18" s="9">
         <v>22578</v>
@@ -9517,13 +9556,13 @@
         <v>60354</v>
       </c>
       <c r="Q18" s="10" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="R18" s="9">
         <v>67313</v>
       </c>
       <c r="S18" s="10" t="s">
-        <v>533</v>
+        <v>545</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9546,7 +9585,7 @@
         <v>4295</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="H19" s="9">
         <v>4364</v>
@@ -9564,25 +9603,25 @@
         <v>57568</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="N19" s="9">
         <v>32223</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="P19" s="9">
         <v>89791</v>
       </c>
       <c r="Q19" s="10" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="R19" s="9">
         <v>98450</v>
       </c>
       <c r="S19" s="10" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9605,43 +9644,43 @@
         <v>1195</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="H20" s="9">
         <v>1730</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="J20" s="9">
         <v>2925</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="L20" s="9">
         <v>27611</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="N20" s="9">
         <v>13474</v>
       </c>
       <c r="O20" s="10" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="P20" s="9">
         <v>41085</v>
       </c>
       <c r="Q20" s="10" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="R20" s="9">
         <v>44010</v>
       </c>
       <c r="S20" s="10" t="s">
-        <v>537</v>
+        <v>549</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9652,55 +9691,55 @@
         <v>103</v>
       </c>
       <c r="C21" s="9">
-        <v>130759</v>
+        <v>130758</v>
       </c>
       <c r="D21" s="9">
         <v>12551</v>
       </c>
       <c r="E21" s="9">
-        <v>143310</v>
+        <v>143309</v>
       </c>
       <c r="F21" s="9">
         <v>9042</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="H21" s="9">
         <v>13986</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="J21" s="9">
         <v>23028</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="L21" s="9">
         <v>2844</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="N21" s="9">
         <v>38449</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="P21" s="9">
         <v>41293</v>
       </c>
       <c r="Q21" s="10" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="R21" s="9">
         <v>64321</v>
       </c>
       <c r="S21" s="10" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9723,43 +9762,43 @@
         <v>3752</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="H22" s="9">
         <v>3078</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J22" s="9">
         <v>6830</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="L22" s="9">
         <v>10602</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="N22" s="9">
         <v>8514</v>
       </c>
       <c r="O22" s="10" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="P22" s="9">
         <v>19116</v>
       </c>
       <c r="Q22" s="10" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="R22" s="9">
         <v>25946</v>
       </c>
       <c r="S22" s="10" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9800,25 +9839,25 @@
         <v>1017668</v>
       </c>
       <c r="M23" s="13" t="s">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="N23" s="12">
         <v>711448</v>
       </c>
       <c r="O23" s="13" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="P23" s="12">
         <v>1729116</v>
       </c>
       <c r="Q23" s="13" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="R23" s="12">
         <v>1928117</v>
       </c>
       <c r="S23" s="13" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
@@ -9846,10 +9885,10 @@
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="C26" s="16"/>
       <c r="D26" s="16"/>
@@ -9871,10 +9910,10 @@
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
@@ -9896,10 +9935,10 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="16"/>
@@ -9921,10 +9960,10 @@
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="C29" s="16"/>
       <c r="D29" s="16"/>
@@ -9946,10 +9985,10 @@
     </row>
     <row r="30" ht="24" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
@@ -10010,7 +10049,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -10038,19 +10077,19 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10084,19 +10123,19 @@
         <v>33</v>
       </c>
       <c r="C6" s="6">
-        <v>3154616</v>
+        <v>3154617</v>
       </c>
       <c r="D6" s="6">
         <v>199001</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="F6" s="6">
         <v>1729116</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10113,13 +10152,13 @@
         <v>4072</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="F7" s="9">
         <v>91180</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>560</v>
+        <v>572</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10136,13 +10175,13 @@
         <v>10259</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="F8" s="9">
         <v>132690</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10159,13 +10198,13 @@
         <v>18442</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="F9" s="9">
         <v>134867</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>564</v>
+        <v>576</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10182,13 +10221,13 @@
         <v>29924</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>244</v>
+        <v>577</v>
       </c>
       <c r="F10" s="9">
         <v>290261</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>565</v>
+        <v>578</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10205,13 +10244,13 @@
         <v>34940</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>76</v>
+        <v>579</v>
       </c>
       <c r="F11" s="9">
         <v>334835</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>566</v>
+        <v>580</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10228,13 +10267,13 @@
         <v>12109</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>567</v>
+        <v>581</v>
       </c>
       <c r="F12" s="9">
         <v>107834</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>568</v>
+        <v>582</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10251,13 +10290,13 @@
         <v>7718</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>569</v>
+        <v>56</v>
       </c>
       <c r="F13" s="9">
         <v>107270</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>570</v>
+        <v>583</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10274,13 +10313,13 @@
         <v>8395</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>571</v>
+        <v>584</v>
       </c>
       <c r="F14" s="9">
         <v>78340</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>572</v>
+        <v>585</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10297,13 +10336,13 @@
         <v>11528</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>573</v>
+        <v>586</v>
       </c>
       <c r="F15" s="9">
         <v>114703</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>574</v>
+        <v>587</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10320,13 +10359,13 @@
         <v>13213</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>575</v>
+        <v>588</v>
       </c>
       <c r="F16" s="9">
         <v>85497</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>576</v>
+        <v>589</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10343,13 +10382,13 @@
         <v>6959</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>577</v>
+        <v>590</v>
       </c>
       <c r="F17" s="9">
         <v>60354</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>578</v>
+        <v>591</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10366,13 +10405,13 @@
         <v>8659</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>579</v>
+        <v>592</v>
       </c>
       <c r="F18" s="9">
         <v>89791</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>580</v>
+        <v>593</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10389,13 +10428,13 @@
         <v>2925</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F19" s="9">
         <v>41085</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>581</v>
+        <v>594</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10406,19 +10445,19 @@
         <v>103</v>
       </c>
       <c r="C20" s="9">
-        <v>159135</v>
+        <v>159136</v>
       </c>
       <c r="D20" s="9">
         <v>23028</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>582</v>
+        <v>595</v>
       </c>
       <c r="F20" s="9">
         <v>41293</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>583</v>
+        <v>596</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10435,13 +10474,13 @@
         <v>6830</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>584</v>
+        <v>597</v>
       </c>
       <c r="F21" s="9">
         <v>19116</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>585</v>
+        <v>598</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10452,19 +10491,19 @@
         <v>113</v>
       </c>
       <c r="C22" s="12">
-        <v>3154616</v>
+        <v>3154617</v>
       </c>
       <c r="D22" s="12">
         <v>199001</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="F22" s="12">
         <v>1729116</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -10480,10 +10519,10 @@
     </row>
     <row r="25" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
-        <v>586</v>
+        <v>599</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>587</v>
+        <v>600</v>
       </c>
       <c r="C25" s="16"/>
       <c r="D25" s="16"/>
@@ -10516,7 +10555,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>588</v>
+        <v>601</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -10546,7 +10585,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>589</v>
+        <v>602</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -10558,22 +10597,22 @@
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3" t="s">
-        <v>590</v>
+        <v>603</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>592</v>
+        <v>605</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>593</v>
+        <v>606</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>594</v>
+        <v>607</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>595</v>
+        <v>608</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10610,13 +10649,13 @@
         <v>33</v>
       </c>
       <c r="C7" s="6">
-        <v>1919395</v>
+        <v>1933022</v>
       </c>
       <c r="D7" s="6">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E7" s="6">
-        <v>3969</v>
+        <v>4012</v>
       </c>
       <c r="F7" s="6">
         <v>195</v>
@@ -10625,7 +10664,7 @@
         <v>84</v>
       </c>
       <c r="H7" s="6">
-        <v>1433</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10636,7 +10675,7 @@
         <v>38</v>
       </c>
       <c r="C8" s="9">
-        <v>95101</v>
+        <v>95337</v>
       </c>
       <c r="D8" s="9">
         <v>4</v>
@@ -10651,7 +10690,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="9">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10662,10 +10701,10 @@
         <v>43</v>
       </c>
       <c r="C9" s="9">
-        <v>142271</v>
+        <v>143283</v>
       </c>
       <c r="D9" s="9">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E9" s="9">
         <v>140</v>
@@ -10688,10 +10727,10 @@
         <v>48</v>
       </c>
       <c r="C10" s="9">
-        <v>152614</v>
+        <v>154039</v>
       </c>
       <c r="D10" s="9">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E10" s="9">
         <v>425</v>
@@ -10703,7 +10742,7 @@
         <v>17</v>
       </c>
       <c r="H10" s="9">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10714,13 +10753,13 @@
         <v>53</v>
       </c>
       <c r="C11" s="9">
-        <v>318603</v>
+        <v>320688</v>
       </c>
       <c r="D11" s="9">
         <v>31</v>
       </c>
       <c r="E11" s="9">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F11" s="9">
         <v>25</v>
@@ -10729,7 +10768,7 @@
         <v>13</v>
       </c>
       <c r="H11" s="9">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10740,13 +10779,13 @@
         <v>58</v>
       </c>
       <c r="C12" s="9">
-        <v>368497</v>
+        <v>371398</v>
       </c>
       <c r="D12" s="9">
         <v>33</v>
       </c>
       <c r="E12" s="9">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="F12" s="9">
         <v>23</v>
@@ -10755,7 +10794,7 @@
         <v>22</v>
       </c>
       <c r="H12" s="9">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10766,13 +10805,13 @@
         <v>63</v>
       </c>
       <c r="C13" s="9">
-        <v>119432</v>
+        <v>120424</v>
       </c>
       <c r="D13" s="9">
         <v>7</v>
       </c>
       <c r="E13" s="9">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F13" s="9">
         <v>9</v>
@@ -10792,7 +10831,7 @@
         <v>68</v>
       </c>
       <c r="C14" s="9">
-        <v>114541</v>
+        <v>115624</v>
       </c>
       <c r="D14" s="9">
         <v>4</v>
@@ -10807,7 +10846,7 @@
         <v>3</v>
       </c>
       <c r="H14" s="9">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10818,10 +10857,10 @@
         <v>73</v>
       </c>
       <c r="C15" s="9">
-        <v>86511</v>
+        <v>87419</v>
       </c>
       <c r="D15" s="9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E15" s="9">
         <v>166</v>
@@ -10844,13 +10883,13 @@
         <v>78</v>
       </c>
       <c r="C16" s="9">
-        <v>125979</v>
+        <v>126662</v>
       </c>
       <c r="D16" s="9">
         <v>12</v>
       </c>
       <c r="E16" s="9">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F16" s="9">
         <v>2</v>
@@ -10859,7 +10898,7 @@
         <v>2</v>
       </c>
       <c r="H16" s="9">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10870,22 +10909,22 @@
         <v>83</v>
       </c>
       <c r="C17" s="9">
-        <v>98344</v>
+        <v>99176</v>
       </c>
       <c r="D17" s="9">
         <v>11</v>
       </c>
       <c r="E17" s="9">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="F17" s="9">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G17" s="9">
         <v>2</v>
       </c>
       <c r="H17" s="9">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10896,13 +10935,13 @@
         <v>88</v>
       </c>
       <c r="C18" s="9">
-        <v>67138</v>
+        <v>67282</v>
       </c>
       <c r="D18" s="9">
         <v>4</v>
       </c>
       <c r="E18" s="9">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F18" s="9">
         <v>6</v>
@@ -10922,13 +10961,13 @@
         <v>93</v>
       </c>
       <c r="C19" s="9">
-        <v>98309</v>
+        <v>98805</v>
       </c>
       <c r="D19" s="9">
         <v>4</v>
       </c>
       <c r="E19" s="9">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F19" s="9">
         <v>9</v>
@@ -10948,13 +10987,13 @@
         <v>98</v>
       </c>
       <c r="C20" s="9">
-        <v>43960</v>
+        <v>44045</v>
       </c>
       <c r="D20" s="9">
         <v>2</v>
       </c>
       <c r="E20" s="9">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F20" s="9">
         <v>3</v>
@@ -10974,22 +11013,22 @@
         <v>103</v>
       </c>
       <c r="C21" s="9">
-        <v>62516</v>
+        <v>63066</v>
       </c>
       <c r="D21" s="9">
         <v>93</v>
       </c>
       <c r="E21" s="9">
-        <v>1262</v>
+        <v>1280</v>
       </c>
       <c r="F21" s="9">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G21" s="9">
         <v>8</v>
       </c>
       <c r="H21" s="9">
-        <v>241</v>
+        <v>251</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11000,13 +11039,13 @@
         <v>108</v>
       </c>
       <c r="C22" s="9">
-        <v>25579</v>
+        <v>25774</v>
       </c>
       <c r="D22" s="9">
         <v>28</v>
       </c>
       <c r="E22" s="9">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F22" s="9">
         <v>9</v>
@@ -11026,13 +11065,13 @@
         <v>113</v>
       </c>
       <c r="C23" s="12">
-        <v>1919395</v>
+        <v>1933022</v>
       </c>
       <c r="D23" s="12">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E23" s="12">
-        <v>3969</v>
+        <v>4012</v>
       </c>
       <c r="F23" s="12">
         <v>195</v>
@@ -11041,7 +11080,7 @@
         <v>84</v>
       </c>
       <c r="H23" s="12">
-        <v>1433</v>
+        <v>1451</v>
       </c>
     </row>
   </sheetData>
@@ -11077,7 +11116,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>596</v>
+        <v>609</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -11117,22 +11156,22 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>597</v>
+        <v>610</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>598</v>
+        <v>611</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>599</v>
+        <v>612</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>600</v>
+        <v>613</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>601</v>
+        <v>614</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
@@ -11157,16 +11196,16 @@
         <v>153</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11227,28 +11266,28 @@
         <v>2027897</v>
       </c>
       <c r="F7" s="6">
-        <v>1518</v>
+        <v>1535</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>602</v>
+        <v>615</v>
       </c>
       <c r="H7" s="6">
-        <v>4752</v>
+        <v>4787</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>603</v>
+        <v>616</v>
       </c>
       <c r="J7" s="6">
-        <v>947892</v>
+        <v>954483</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>604</v>
+        <v>617</v>
       </c>
       <c r="L7" s="6">
-        <v>422663</v>
+        <v>425175</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>605</v>
+        <v>618</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11268,28 +11307,28 @@
         <v>88621</v>
       </c>
       <c r="F8" s="9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>606</v>
+        <v>619</v>
       </c>
       <c r="H8" s="9">
         <v>130</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>607</v>
+        <v>620</v>
       </c>
       <c r="J8" s="9">
-        <v>51943</v>
+        <v>52069</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>608</v>
+        <v>621</v>
       </c>
       <c r="L8" s="9">
-        <v>23543</v>
+        <v>23611</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>609</v>
+        <v>622</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11300,7 +11339,7 @@
         <v>43</v>
       </c>
       <c r="C9" s="9">
-        <v>57473</v>
+        <v>57474</v>
       </c>
       <c r="D9" s="9">
         <v>210686</v>
@@ -11309,28 +11348,28 @@
         <v>172111</v>
       </c>
       <c r="F9" s="9">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>610</v>
+        <v>285</v>
       </c>
       <c r="H9" s="9">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>611</v>
+        <v>623</v>
       </c>
       <c r="J9" s="9">
-        <v>75082</v>
+        <v>75580</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>612</v>
+        <v>624</v>
       </c>
       <c r="L9" s="9">
-        <v>33176</v>
+        <v>33418</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11350,28 +11389,28 @@
         <v>202453</v>
       </c>
       <c r="F10" s="9">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>614</v>
+        <v>626</v>
       </c>
       <c r="H10" s="9">
-        <v>1105</v>
+        <v>1114</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>615</v>
+        <v>627</v>
       </c>
       <c r="J10" s="9">
-        <v>72233</v>
+        <v>72914</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>616</v>
+        <v>628</v>
       </c>
       <c r="L10" s="9">
-        <v>30252</v>
+        <v>30448</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>617</v>
+        <v>629</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11391,28 +11430,28 @@
         <v>347651</v>
       </c>
       <c r="F11" s="9">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>618</v>
+        <v>630</v>
       </c>
       <c r="H11" s="9">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="J11" s="9">
-        <v>167212</v>
+        <v>168297</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>620</v>
+        <v>632</v>
       </c>
       <c r="L11" s="9">
-        <v>74244</v>
+        <v>74719</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>621</v>
+        <v>633</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11432,28 +11471,28 @@
         <v>416503</v>
       </c>
       <c r="F12" s="9">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>622</v>
+        <v>634</v>
       </c>
       <c r="H12" s="9">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>623</v>
+        <v>635</v>
       </c>
       <c r="J12" s="9">
-        <v>202262</v>
+        <v>203866</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>624</v>
+        <v>636</v>
       </c>
       <c r="L12" s="9">
-        <v>86595</v>
+        <v>87204</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>625</v>
+        <v>637</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11473,28 +11512,28 @@
         <v>128482</v>
       </c>
       <c r="F13" s="9">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>626</v>
+        <v>638</v>
       </c>
       <c r="H13" s="9">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>627</v>
+        <v>639</v>
       </c>
       <c r="J13" s="9">
-        <v>60170</v>
+        <v>60697</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>628</v>
+        <v>45</v>
       </c>
       <c r="L13" s="9">
-        <v>28038</v>
+        <v>28218</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>629</v>
+        <v>640</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11514,28 +11553,28 @@
         <v>128768</v>
       </c>
       <c r="F14" s="9">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>630</v>
+        <v>641</v>
       </c>
       <c r="H14" s="9">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>631</v>
+        <v>642</v>
       </c>
       <c r="J14" s="9">
-        <v>59183</v>
+        <v>59694</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>632</v>
+        <v>643</v>
       </c>
       <c r="L14" s="9">
-        <v>31302</v>
+        <v>31539</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>633</v>
+        <v>644</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11558,25 +11597,25 @@
         <v>21</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>634</v>
+        <v>645</v>
       </c>
       <c r="H15" s="9">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>635</v>
+        <v>646</v>
       </c>
       <c r="J15" s="9">
-        <v>39809</v>
+        <v>40203</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>636</v>
+        <v>647</v>
       </c>
       <c r="L15" s="9">
-        <v>21553</v>
+        <v>21726</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>637</v>
+        <v>648</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11596,28 +11635,28 @@
         <v>125712</v>
       </c>
       <c r="F16" s="9">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>638</v>
+        <v>649</v>
       </c>
       <c r="H16" s="9">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>639</v>
+        <v>485</v>
       </c>
       <c r="J16" s="9">
-        <v>63794</v>
+        <v>64136</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>611</v>
+        <v>650</v>
       </c>
       <c r="L16" s="9">
-        <v>22537</v>
+        <v>22624</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>610</v>
+        <v>651</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11640,25 +11679,25 @@
         <v>34</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>640</v>
+        <v>652</v>
       </c>
       <c r="H17" s="9">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>641</v>
+        <v>653</v>
       </c>
       <c r="J17" s="9">
-        <v>41955</v>
+        <v>42304</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>642</v>
+        <v>654</v>
       </c>
       <c r="L17" s="9">
-        <v>17597</v>
+        <v>17708</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>643</v>
+        <v>655</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11681,25 +11720,25 @@
         <v>39</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>644</v>
+        <v>656</v>
       </c>
       <c r="H18" s="9">
         <v>484</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>645</v>
+        <v>657</v>
       </c>
       <c r="J18" s="9">
-        <v>32809</v>
+        <v>32882</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>646</v>
+        <v>658</v>
       </c>
       <c r="L18" s="9">
-        <v>16540</v>
+        <v>16561</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11719,28 +11758,28 @@
         <v>88014</v>
       </c>
       <c r="F19" s="9">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>648</v>
+        <v>660</v>
       </c>
       <c r="H19" s="9">
         <v>98</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>649</v>
+        <v>661</v>
       </c>
       <c r="J19" s="9">
-        <v>50023</v>
+        <v>50292</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>650</v>
+        <v>662</v>
       </c>
       <c r="L19" s="9">
-        <v>24430</v>
+        <v>24508</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>651</v>
+        <v>663</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11763,25 +11802,25 @@
         <v>10</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>652</v>
+        <v>664</v>
       </c>
       <c r="H20" s="9">
         <v>64</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>653</v>
+        <v>665</v>
       </c>
       <c r="J20" s="9">
-        <v>23372</v>
+        <v>23430</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>654</v>
+        <v>666</v>
       </c>
       <c r="L20" s="9">
-        <v>9798</v>
+        <v>9814</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11792,7 +11831,7 @@
         <v>103</v>
       </c>
       <c r="C21" s="9">
-        <v>130759</v>
+        <v>130758</v>
       </c>
       <c r="D21" s="9">
         <v>15314</v>
@@ -11801,28 +11840,28 @@
         <v>12256</v>
       </c>
       <c r="F21" s="9">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>656</v>
+        <v>668</v>
       </c>
       <c r="H21" s="9">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>657</v>
+        <v>669</v>
       </c>
       <c r="J21" s="9">
-        <v>2696</v>
+        <v>2727</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>658</v>
+        <v>670</v>
       </c>
       <c r="L21" s="9">
-        <v>1009</v>
+        <v>1015</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>659</v>
+        <v>671</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11842,28 +11881,28 @@
         <v>13005</v>
       </c>
       <c r="F22" s="9">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="H22" s="9">
         <v>12</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>383</v>
+        <v>673</v>
       </c>
       <c r="J22" s="9">
-        <v>5349</v>
+        <v>5392</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>661</v>
+        <v>674</v>
       </c>
       <c r="L22" s="9">
-        <v>2049</v>
+        <v>2062</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>662</v>
+        <v>675</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11883,28 +11922,28 @@
         <v>2027897</v>
       </c>
       <c r="F23" s="12">
-        <v>1518</v>
+        <v>1535</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>602</v>
+        <v>615</v>
       </c>
       <c r="H23" s="12">
-        <v>4752</v>
+        <v>4787</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>603</v>
+        <v>616</v>
       </c>
       <c r="J23" s="12">
-        <v>947892</v>
+        <v>954483</v>
       </c>
       <c r="K23" s="13" t="s">
-        <v>604</v>
+        <v>617</v>
       </c>
       <c r="L23" s="12">
-        <v>422663</v>
+        <v>425175</v>
       </c>
       <c r="M23" s="13" t="s">
-        <v>605</v>
+        <v>618</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
@@ -11926,10 +11965,10 @@
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>663</v>
+        <v>676</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>664</v>
+        <v>677</v>
       </c>
       <c r="C26" s="16"/>
       <c r="D26" s="16"/>
@@ -11945,10 +11984,10 @@
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
-        <v>665</v>
+        <v>678</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>666</v>
+        <v>679</v>
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
@@ -11964,10 +12003,10 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
-        <v>667</v>
+        <v>680</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>668</v>
+        <v>681</v>
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="16"/>
@@ -11983,10 +12022,10 @@
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>669</v>
+        <v>682</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>670</v>
+        <v>683</v>
       </c>
       <c r="C29" s="16"/>
       <c r="D29" s="16"/>

--- a/data/Export_Progres_Pendataan_Kabupaten_Kota.xlsx
+++ b/data/Export_Progres_Pendataan_Kabupaten_Kota.xlsx
@@ -18,12 +18,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1402" uniqueCount="678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1402" uniqueCount="682">
   <si>
     <t>PROGRES PENDATAAN - PROGRES PENDATAAN</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 19 Agu 2026, 18.00 | Dicetak: 19 Agu 2026, 20.45</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 20 Agu 2026, 06.00 | Dicetak: 20 Agu 2026, 06.40</t>
   </si>
   <si>
     <t>Kode</t>
@@ -122,10 +122,10 @@
     <t>LAMPUNG</t>
   </si>
   <si>
-    <t>109,98</t>
-  </si>
-  <si>
-    <t>66,68</t>
+    <t>110,65</t>
+  </si>
+  <si>
+    <t>67,12</t>
   </si>
   <si>
     <t>4,71</t>
@@ -137,7 +137,7 @@
     <t>LAMPUNG BARAT</t>
   </si>
   <si>
-    <t>124,86</t>
+    <t>124,91</t>
   </si>
   <si>
     <t>84,96</t>
@@ -152,10 +152,10 @@
     <t>TANGGAMUS</t>
   </si>
   <si>
-    <t>108,98</t>
-  </si>
-  <si>
-    <t>68,82</t>
+    <t>109,65</t>
+  </si>
+  <si>
+    <t>69,27</t>
   </si>
   <si>
     <t>6,86</t>
@@ -167,10 +167,10 @@
     <t>LAMPUNG SELATAN</t>
   </si>
   <si>
-    <t>106,99</t>
-  </si>
-  <si>
-    <t>61,08</t>
+    <t>107,88</t>
+  </si>
+  <si>
+    <t>61,62</t>
   </si>
   <si>
     <t>6,04</t>
@@ -182,10 +182,10 @@
     <t>LAMPUNG TIMUR</t>
   </si>
   <si>
-    <t>105,18</t>
-  </si>
-  <si>
-    <t>64,82</t>
+    <t>105,74</t>
+  </si>
+  <si>
+    <t>65,23</t>
   </si>
   <si>
     <t>4,17</t>
@@ -197,10 +197,10 @@
     <t>LAMPUNG TENGAH</t>
   </si>
   <si>
-    <t>106,25</t>
-  </si>
-  <si>
-    <t>65,44</t>
+    <t>106,92</t>
+  </si>
+  <si>
+    <t>65,91</t>
   </si>
   <si>
     <t>5,08</t>
@@ -212,10 +212,10 @@
     <t>LAMPUNG UTARA</t>
   </si>
   <si>
-    <t>113,27</t>
-  </si>
-  <si>
-    <t>64,92</t>
+    <t>113,99</t>
+  </si>
+  <si>
+    <t>65,35</t>
   </si>
   <si>
     <t>2,53</t>
@@ -227,10 +227,10 @@
     <t>WAY KANAN</t>
   </si>
   <si>
-    <t>110,83</t>
-  </si>
-  <si>
-    <t>66,74</t>
+    <t>111,76</t>
+  </si>
+  <si>
+    <t>67,36</t>
   </si>
   <si>
     <t>4,85</t>
@@ -242,10 +242,10 @@
     <t>TULANG BAWANG</t>
   </si>
   <si>
-    <t>111,9</t>
-  </si>
-  <si>
-    <t>66,9</t>
+    <t>113,01</t>
+  </si>
+  <si>
+    <t>67,63</t>
   </si>
   <si>
     <t>5,67</t>
@@ -257,10 +257,10 @@
     <t>PESAWARAN</t>
   </si>
   <si>
-    <t>121,44</t>
-  </si>
-  <si>
-    <t>82,54</t>
+    <t>122,02</t>
+  </si>
+  <si>
+    <t>82,94</t>
   </si>
   <si>
     <t>3,29</t>
@@ -272,10 +272,10 @@
     <t>PRINGSEWU</t>
   </si>
   <si>
-    <t>109,9</t>
-  </si>
-  <si>
-    <t>77,78</t>
+    <t>110,59</t>
+  </si>
+  <si>
+    <t>78,41</t>
   </si>
   <si>
     <t>6,45</t>
@@ -287,10 +287,10 @@
     <t>MESUJI</t>
   </si>
   <si>
-    <t>132,7</t>
-  </si>
-  <si>
-    <t>86,92</t>
+    <t>132,73</t>
+  </si>
+  <si>
+    <t>86,97</t>
   </si>
   <si>
     <t>0,13</t>
@@ -302,10 +302,10 @@
     <t>TULANG BAWANG BARAT</t>
   </si>
   <si>
-    <t>127,66</t>
-  </si>
-  <si>
-    <t>86,23</t>
+    <t>128,01</t>
+  </si>
+  <si>
+    <t>86,5</t>
   </si>
   <si>
     <t>1,45</t>
@@ -317,10 +317,10 @@
     <t>PESISIR BARAT</t>
   </si>
   <si>
-    <t>129,63</t>
-  </si>
-  <si>
-    <t>93,67</t>
+    <t>129,86</t>
+  </si>
+  <si>
+    <t>93,86</t>
   </si>
   <si>
     <t>0,82</t>
@@ -332,10 +332,10 @@
     <t>BANDAR LAMPUNG</t>
   </si>
   <si>
-    <t>102,13</t>
-  </si>
-  <si>
-    <t>48,96</t>
+    <t>102,91</t>
+  </si>
+  <si>
+    <t>49,36</t>
   </si>
   <si>
     <t>5,86</t>
@@ -347,10 +347,10 @@
     <t>METRO</t>
   </si>
   <si>
-    <t>106,42</t>
-  </si>
-  <si>
-    <t>64,94</t>
+    <t>106,86</t>
+  </si>
+  <si>
+    <t>65,26</t>
   </si>
   <si>
     <t>6,13</t>
@@ -599,28 +599,28 @@
     <t>0,02</t>
   </si>
   <si>
-    <t>11,37</t>
-  </si>
-  <si>
-    <t>17,24</t>
-  </si>
-  <si>
-    <t>7,79</t>
-  </si>
-  <si>
-    <t>43,24</t>
-  </si>
-  <si>
-    <t>15,17</t>
+    <t>11,48</t>
+  </si>
+  <si>
+    <t>17,4</t>
+  </si>
+  <si>
+    <t>7,85</t>
+  </si>
+  <si>
+    <t>43,39</t>
+  </si>
+  <si>
+    <t>15,33</t>
   </si>
   <si>
     <t>6,3</t>
   </si>
   <si>
-    <t>26,53</t>
-  </si>
-  <si>
-    <t>26,68</t>
+    <t>26,81</t>
+  </si>
+  <si>
+    <t>26,95</t>
   </si>
   <si>
     <t>0,19</t>
@@ -629,28 +629,28 @@
     <t>0,03</t>
   </si>
   <si>
-    <t>16,75</t>
-  </si>
-  <si>
-    <t>16,57</t>
-  </si>
-  <si>
-    <t>12,7</t>
-  </si>
-  <si>
-    <t>41,89</t>
-  </si>
-  <si>
-    <t>17,43</t>
+    <t>16,82</t>
+  </si>
+  <si>
+    <t>16,67</t>
+  </si>
+  <si>
+    <t>12,72</t>
+  </si>
+  <si>
+    <t>41,81</t>
+  </si>
+  <si>
+    <t>17,47</t>
   </si>
   <si>
     <t>1,52</t>
   </si>
   <si>
-    <t>34,18</t>
-  </si>
-  <si>
-    <t>34,38</t>
+    <t>34,29</t>
+  </si>
+  <si>
+    <t>34,48</t>
   </si>
   <si>
     <t>0,09</t>
@@ -659,1009 +659,1015 @@
     <t>0,05</t>
   </si>
   <si>
-    <t>8,65</t>
-  </si>
-  <si>
-    <t>21,91</t>
-  </si>
-  <si>
-    <t>15,23</t>
-  </si>
-  <si>
-    <t>26,66</t>
-  </si>
-  <si>
-    <t>9,42</t>
+    <t>8,71</t>
+  </si>
+  <si>
+    <t>22,05</t>
+  </si>
+  <si>
+    <t>15,3</t>
+  </si>
+  <si>
+    <t>26,83</t>
+  </si>
+  <si>
+    <t>9,57</t>
   </si>
   <si>
     <t>10,19</t>
   </si>
   <si>
-    <t>18,07</t>
-  </si>
-  <si>
-    <t>18,16</t>
+    <t>18,28</t>
+  </si>
+  <si>
+    <t>18,38</t>
   </si>
   <si>
     <t>0,14</t>
   </si>
   <si>
-    <t>5,89</t>
-  </si>
-  <si>
-    <t>11,49</t>
-  </si>
-  <si>
-    <t>4,05</t>
-  </si>
-  <si>
-    <t>61,63</t>
-  </si>
-  <si>
-    <t>14,12</t>
+    <t>5,96</t>
+  </si>
+  <si>
+    <t>11,63</t>
+  </si>
+  <si>
+    <t>4,14</t>
+  </si>
+  <si>
+    <t>61,98</t>
+  </si>
+  <si>
+    <t>14,31</t>
   </si>
   <si>
     <t>2,75</t>
   </si>
   <si>
-    <t>20,02</t>
-  </si>
-  <si>
-    <t>20,15</t>
+    <t>20,27</t>
+  </si>
+  <si>
+    <t>20,41</t>
   </si>
   <si>
     <t>0,06</t>
   </si>
   <si>
-    <t>11,38</t>
-  </si>
-  <si>
-    <t>21,95</t>
-  </si>
-  <si>
-    <t>7,67</t>
-  </si>
-  <si>
-    <t>33,28</t>
-  </si>
-  <si>
-    <t>12,46</t>
+    <t>11,47</t>
+  </si>
+  <si>
+    <t>22,13</t>
+  </si>
+  <si>
+    <t>7,69</t>
+  </si>
+  <si>
+    <t>33,35</t>
+  </si>
+  <si>
+    <t>12,57</t>
   </si>
   <si>
     <t>11,16</t>
   </si>
   <si>
-    <t>23,84</t>
+    <t>24,04</t>
+  </si>
+  <si>
+    <t>24,1</t>
+  </si>
+  <si>
+    <t>10,71</t>
+  </si>
+  <si>
+    <t>19,18</t>
+  </si>
+  <si>
+    <t>9,33</t>
+  </si>
+  <si>
+    <t>44,59</t>
+  </si>
+  <si>
+    <t>16,58</t>
+  </si>
+  <si>
+    <t>6,05</t>
+  </si>
+  <si>
+    <t>27,29</t>
+  </si>
+  <si>
+    <t>27,39</t>
+  </si>
+  <si>
+    <t>0,08</t>
+  </si>
+  <si>
+    <t>7,4</t>
+  </si>
+  <si>
+    <t>15,34</t>
+  </si>
+  <si>
+    <t>5,32</t>
+  </si>
+  <si>
+    <t>58,47</t>
+  </si>
+  <si>
+    <t>11,99</t>
+  </si>
+  <si>
+    <t>7,36</t>
+  </si>
+  <si>
+    <t>19,39</t>
+  </si>
+  <si>
+    <t>19,47</t>
+  </si>
+  <si>
+    <t>5,85</t>
+  </si>
+  <si>
+    <t>21,65</t>
+  </si>
+  <si>
+    <t>6,29</t>
+  </si>
+  <si>
+    <t>44,83</t>
+  </si>
+  <si>
+    <t>13,81</t>
+  </si>
+  <si>
+    <t>9,62</t>
+  </si>
+  <si>
+    <t>19,66</t>
+  </si>
+  <si>
+    <t>19,75</t>
+  </si>
+  <si>
+    <t>0,24</t>
+  </si>
+  <si>
+    <t>20,12</t>
+  </si>
+  <si>
+    <t>12,61</t>
+  </si>
+  <si>
+    <t>4,66</t>
+  </si>
+  <si>
+    <t>41,65</t>
+  </si>
+  <si>
+    <t>24,66</t>
+  </si>
+  <si>
+    <t>0,95</t>
+  </si>
+  <si>
+    <t>44,78</t>
+  </si>
+  <si>
+    <t>45,02</t>
+  </si>
+  <si>
+    <t>0,26</t>
+  </si>
+  <si>
+    <t>30,8</t>
+  </si>
+  <si>
+    <t>14,35</t>
+  </si>
+  <si>
+    <t>5,37</t>
+  </si>
+  <si>
+    <t>35,86</t>
+  </si>
+  <si>
+    <t>32,96</t>
+  </si>
+  <si>
+    <t>2,07</t>
+  </si>
+  <si>
+    <t>63,76</t>
+  </si>
+  <si>
+    <t>64,02</t>
+  </si>
+  <si>
+    <t>35,3</t>
+  </si>
+  <si>
+    <t>13,5</t>
+  </si>
+  <si>
+    <t>3,38</t>
+  </si>
+  <si>
+    <t>29,33</t>
+  </si>
+  <si>
+    <t>27,24</t>
+  </si>
+  <si>
+    <t>1,6</t>
+  </si>
+  <si>
+    <t>62,54</t>
+  </si>
+  <si>
+    <t>62,68</t>
+  </si>
+  <si>
+    <t>28,18</t>
+  </si>
+  <si>
+    <t>12,17</t>
+  </si>
+  <si>
+    <t>27,93</t>
+  </si>
+  <si>
+    <t>34,78</t>
+  </si>
+  <si>
+    <t>0,89</t>
+  </si>
+  <si>
+    <t>62,96</t>
+  </si>
+  <si>
+    <t>63,21</t>
+  </si>
+  <si>
+    <t>0,22</t>
+  </si>
+  <si>
+    <t>44,28</t>
+  </si>
+  <si>
+    <t>19,83</t>
+  </si>
+  <si>
+    <t>4,83</t>
+  </si>
+  <si>
+    <t>19,13</t>
+  </si>
+  <si>
+    <t>45,04</t>
+  </si>
+  <si>
+    <t>1,74</t>
+  </si>
+  <si>
+    <t>89,32</t>
+  </si>
+  <si>
+    <t>89,54</t>
+  </si>
+  <si>
+    <t>0,17</t>
+  </si>
+  <si>
+    <t>22,45</t>
+  </si>
+  <si>
+    <t>17,01</t>
+  </si>
+  <si>
+    <t>7,49</t>
+  </si>
+  <si>
+    <t>40,02</t>
+  </si>
+  <si>
+    <t>32,45</t>
+  </si>
+  <si>
+    <t>1,17</t>
+  </si>
+  <si>
+    <t>54,91</t>
+  </si>
+  <si>
+    <t>55,07</t>
+  </si>
+  <si>
+    <t>0,3</t>
+  </si>
+  <si>
+    <t>0,04</t>
+  </si>
+  <si>
+    <t>6,88</t>
+  </si>
+  <si>
+    <t>14,04</t>
+  </si>
+  <si>
+    <t>7,27</t>
+  </si>
+  <si>
+    <t>48,16</t>
+  </si>
+  <si>
+    <t>11,01</t>
+  </si>
+  <si>
+    <t>17,88</t>
+  </si>
+  <si>
+    <t>18,19</t>
+  </si>
+  <si>
+    <t>0,25</t>
+  </si>
+  <si>
+    <t>22,46</t>
+  </si>
+  <si>
+    <t>19,43</t>
+  </si>
+  <si>
+    <t>18,5</t>
+  </si>
+  <si>
+    <t>20,87</t>
+  </si>
+  <si>
+    <t>18,7</t>
+  </si>
+  <si>
+    <t>1,67</t>
+  </si>
+  <si>
+    <t>41,16</t>
+  </si>
+  <si>
+    <t>41,41</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha BKU</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha yang Ditemukan dan Baru (UB + UMKM)</t>
+  </si>
+  <si>
+    <t>Persentase Kolom 4 21</t>
+  </si>
+  <si>
+    <t>Persentase hasil bagi jumlah usaha pada kolom tersebut dengan jumlah prelist usaha (kolom 3).</t>
+  </si>
+  <si>
+    <t>PROGRES PENDATAAN - SKALA USAHA</t>
+  </si>
+  <si>
+    <t>JUMLAH PRELIST</t>
+  </si>
+  <si>
+    <t>JUMLAH USAHA BKU MENURUT STATUS SKALA USAHA (UB, UM, UMK)</t>
+  </si>
+  <si>
+    <t>UB​</t>
+  </si>
+  <si>
+    <t>Persentase UB​</t>
+  </si>
+  <si>
+    <t>UM​</t>
+  </si>
+  <si>
+    <t>Persentase UM​</t>
+  </si>
+  <si>
+    <t>UMK​</t>
+  </si>
+  <si>
+    <t>Persentase UMK​</t>
+  </si>
+  <si>
+    <t>Tidak Dapat Diklasifikasikan</t>
+  </si>
+  <si>
+    <t>Total Usaha BKU</t>
+  </si>
+  <si>
+    <t>Persentase Total Usaha BKU</t>
+  </si>
+  <si>
+    <t>83,52</t>
+  </si>
+  <si>
+    <t>11,95</t>
+  </si>
+  <si>
+    <t>26,86</t>
+  </si>
+  <si>
+    <t>117,39</t>
+  </si>
+  <si>
+    <t>39,07</t>
+  </si>
+  <si>
+    <t>34,15</t>
+  </si>
+  <si>
+    <t>54,39</t>
+  </si>
+  <si>
+    <t>16,88</t>
+  </si>
+  <si>
+    <t>18,2</t>
+  </si>
+  <si>
+    <t>104,83</t>
+  </si>
+  <si>
+    <t>8,83</t>
+  </si>
+  <si>
+    <t>20,28</t>
+  </si>
+  <si>
+    <t>20,4</t>
+  </si>
+  <si>
+    <t>122,78</t>
+  </si>
+  <si>
+    <t>20,88</t>
   </si>
   <si>
     <t>23,9</t>
   </si>
   <si>
-    <t>10,63</t>
-  </si>
-  <si>
-    <t>19,06</t>
-  </si>
-  <si>
-    <t>9,28</t>
-  </si>
-  <si>
-    <t>44,57</t>
-  </si>
-  <si>
-    <t>16,42</t>
-  </si>
-  <si>
-    <t>6,05</t>
-  </si>
-  <si>
-    <t>27,06</t>
-  </si>
-  <si>
-    <t>27,15</t>
-  </si>
-  <si>
-    <t>0,08</t>
-  </si>
-  <si>
-    <t>7,32</t>
-  </si>
-  <si>
-    <t>15,2</t>
-  </si>
-  <si>
-    <t>5,26</t>
-  </si>
-  <si>
-    <t>58,18</t>
-  </si>
-  <si>
-    <t>11,92</t>
-  </si>
-  <si>
-    <t>7,36</t>
-  </si>
-  <si>
-    <t>19,24</t>
-  </si>
-  <si>
-    <t>19,32</t>
-  </si>
-  <si>
-    <t>5,78</t>
-  </si>
-  <si>
-    <t>21,28</t>
-  </si>
-  <si>
-    <t>6,21</t>
-  </si>
-  <si>
-    <t>44,76</t>
-  </si>
-  <si>
-    <t>13,56</t>
-  </si>
-  <si>
-    <t>9,62</t>
+    <t>105,76</t>
+  </si>
+  <si>
+    <t>15,93</t>
+  </si>
+  <si>
+    <t>27,25</t>
+  </si>
+  <si>
+    <t>82,67</t>
+  </si>
+  <si>
+    <t>17,78</t>
   </si>
   <si>
     <t>19,34</t>
   </si>
   <si>
-    <t>19,43</t>
-  </si>
-  <si>
-    <t>0,24</t>
-  </si>
-  <si>
-    <t>19,81</t>
-  </si>
-  <si>
-    <t>12,52</t>
-  </si>
-  <si>
-    <t>4,58</t>
-  </si>
-  <si>
-    <t>41,61</t>
-  </si>
-  <si>
-    <t>24,33</t>
-  </si>
-  <si>
-    <t>0,95</t>
-  </si>
-  <si>
-    <t>44,14</t>
-  </si>
-  <si>
-    <t>44,38</t>
-  </si>
-  <si>
-    <t>0,26</t>
-  </si>
-  <si>
-    <t>30,56</t>
-  </si>
-  <si>
-    <t>14,23</t>
-  </si>
-  <si>
-    <t>5,3</t>
-  </si>
-  <si>
-    <t>35,93</t>
-  </si>
-  <si>
-    <t>32,76</t>
-  </si>
-  <si>
-    <t>2,07</t>
+    <t>19,46</t>
+  </si>
+  <si>
+    <t>128,57</t>
+  </si>
+  <si>
+    <t>13,18</t>
+  </si>
+  <si>
+    <t>19,55</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>5,82</t>
+  </si>
+  <si>
+    <t>45,55</t>
+  </si>
+  <si>
+    <t>98,18</t>
+  </si>
+  <si>
+    <t>38,64</t>
+  </si>
+  <si>
+    <t>63,86</t>
+  </si>
+  <si>
+    <t>128,13</t>
+  </si>
+  <si>
+    <t>155,56</t>
+  </si>
+  <si>
+    <t>62,2</t>
+  </si>
+  <si>
+    <t>62,67</t>
+  </si>
+  <si>
+    <t>111,11</t>
+  </si>
+  <si>
+    <t>36,84</t>
+  </si>
+  <si>
+    <t>63,11</t>
+  </si>
+  <si>
+    <t>63,2</t>
+  </si>
+  <si>
+    <t>34,85</t>
+  </si>
+  <si>
+    <t>89,71</t>
+  </si>
+  <si>
+    <t>89,53</t>
+  </si>
+  <si>
+    <t>54,92</t>
+  </si>
+  <si>
+    <t>62,41</t>
+  </si>
+  <si>
+    <t>6,79</t>
+  </si>
+  <si>
+    <t>117,5</t>
+  </si>
+  <si>
+    <t>39,06</t>
+  </si>
+  <si>
+    <t>41,01</t>
+  </si>
+  <si>
+    <t>41,4</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha (UB/UM/UMK)</t>
+  </si>
+  <si>
+    <t>Jumlah prelist usaha yang berhasil didata (keberadaan ditemukan, baru, pindah dapat ditelusuri) berdasarkan skala usaha, untuk usaha baru didekati dengan omzet sebagai berikut: UB (lebih dari 50 Milyar), UM (15-50 Milyar), UMK - Kecil (2-15 Milyar), UMK - Mikro (0-2 Milyar).</t>
+  </si>
+  <si>
+    <t>Tidak Dapat Diklasifikasikan (Kolom 10)</t>
+  </si>
+  <si>
+    <t>Usaha baru dengan nilai omzet/pendapatan kosong sehingga tidak dapat diklasifikasikan skala usahanya, misalnya usaha unit pembantu/penunjang.</t>
+  </si>
+  <si>
+    <t>Persentase Jumlah UB</t>
+  </si>
+  <si>
+    <t>Persentase hasil bagi jumlah UB yang berhasil didata dengan jumlah prelist UB (kolom 3).</t>
+  </si>
+  <si>
+    <t>Persentase Jumlah UM</t>
+  </si>
+  <si>
+    <t>Persentase hasil bagi jumlah UM yang berhasil didata dengan jumlah prelist UM (kolom 4).</t>
+  </si>
+  <si>
+    <t>Persentase Jumlah UMK</t>
+  </si>
+  <si>
+    <t>Persentase hasil bagi jumlah UMK yang berhasil didata dengan jumlah prelist UMK (kolom 5).</t>
+  </si>
+  <si>
+    <t>PROGRES PENDATAAN - USAHA KELUARGA</t>
+  </si>
+  <si>
+    <t>Jumlah Prelist Usaha Keluarga (ST2023 + UMKM)</t>
+  </si>
+  <si>
+    <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha dalam Keluarga (Ditemukan + Baru)</t>
+  </si>
+  <si>
+    <t>Persentase Usaha dalam Keluarga (Ditemukan + Baru)</t>
+  </si>
+  <si>
+    <t>47,82</t>
+  </si>
+  <si>
+    <t>23,57</t>
+  </si>
+  <si>
+    <t>0,38</t>
+  </si>
+  <si>
+    <t>9,48</t>
+  </si>
+  <si>
+    <t>33,42</t>
+  </si>
+  <si>
+    <t>81,24</t>
+  </si>
+  <si>
+    <t>58,39</t>
+  </si>
+  <si>
+    <t>19,87</t>
+  </si>
+  <si>
+    <t>0,51</t>
+  </si>
+  <si>
+    <t>9,16</t>
+  </si>
+  <si>
+    <t>29,91</t>
+  </si>
+  <si>
+    <t>88,3</t>
+  </si>
+  <si>
+    <t>44,41</t>
+  </si>
+  <si>
+    <t>24,43</t>
+  </si>
+  <si>
+    <t>0,45</t>
+  </si>
+  <si>
+    <t>7,92</t>
+  </si>
+  <si>
+    <t>33,74</t>
+  </si>
+  <si>
+    <t>78,15</t>
+  </si>
+  <si>
+    <t>36,6</t>
+  </si>
+  <si>
+    <t>22,62</t>
+  </si>
+  <si>
+    <t>14,66</t>
+  </si>
+  <si>
+    <t>31,2</t>
+  </si>
+  <si>
+    <t>67,8</t>
+  </si>
+  <si>
+    <t>49,04</t>
+  </si>
+  <si>
+    <t>22,25</t>
+  </si>
+  <si>
+    <t>8,33</t>
+  </si>
+  <si>
+    <t>35,62</t>
+  </si>
+  <si>
+    <t>84,67</t>
+  </si>
+  <si>
+    <t>49,45</t>
+  </si>
+  <si>
+    <t>21,47</t>
+  </si>
+  <si>
+    <t>0,23</t>
+  </si>
+  <si>
+    <t>10,57</t>
+  </si>
+  <si>
+    <t>32,09</t>
+  </si>
+  <si>
+    <t>81,54</t>
+  </si>
+  <si>
+    <t>47,73</t>
+  </si>
+  <si>
+    <t>19,7</t>
+  </si>
+  <si>
+    <t>17,12</t>
+  </si>
+  <si>
+    <t>37,43</t>
+  </si>
+  <si>
+    <t>85,16</t>
+  </si>
+  <si>
+    <t>46,95</t>
+  </si>
+  <si>
+    <t>21,64</t>
+  </si>
+  <si>
+    <t>0,18</t>
+  </si>
+  <si>
+    <t>8,39</t>
+  </si>
+  <si>
+    <t>37,65</t>
+  </si>
+  <si>
+    <t>84,6</t>
+  </si>
+  <si>
+    <t>42,75</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>0,48</t>
+  </si>
+  <si>
+    <t>4,84</t>
+  </si>
+  <si>
+    <t>27,03</t>
+  </si>
+  <si>
+    <t>69,77</t>
+  </si>
+  <si>
+    <t>51,84</t>
+  </si>
+  <si>
+    <t>27,36</t>
+  </si>
+  <si>
+    <t>0,72</t>
+  </si>
+  <si>
+    <t>6,85</t>
+  </si>
+  <si>
+    <t>23,16</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>47,06</t>
+  </si>
+  <si>
+    <t>28,98</t>
+  </si>
+  <si>
+    <t>0,57</t>
+  </si>
+  <si>
+    <t>5,95</t>
+  </si>
+  <si>
+    <t>26,6</t>
+  </si>
+  <si>
+    <t>73,66</t>
+  </si>
+  <si>
+    <t>46,97</t>
+  </si>
+  <si>
+    <t>29,9</t>
+  </si>
+  <si>
+    <t>0,71</t>
+  </si>
+  <si>
+    <t>12,18</t>
+  </si>
+  <si>
+    <t>28,03</t>
+  </si>
+  <si>
+    <t>57,26</t>
+  </si>
+  <si>
+    <t>23,98</t>
+  </si>
+  <si>
+    <t>0,56</t>
+  </si>
+  <si>
+    <t>7,61</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>89,26</t>
+  </si>
+  <si>
+    <t>54,04</t>
+  </si>
+  <si>
+    <t>29,22</t>
+  </si>
+  <si>
+    <t>0,44</t>
+  </si>
+  <si>
+    <t>26,41</t>
+  </si>
+  <si>
+    <t>80,46</t>
+  </si>
+  <si>
+    <t>23,03</t>
+  </si>
+  <si>
+    <t>29,12</t>
+  </si>
+  <si>
+    <t>0,81</t>
+  </si>
+  <si>
+    <t>14,47</t>
+  </si>
+  <si>
+    <t>310,46</t>
+  </si>
+  <si>
+    <t>333,49</t>
+  </si>
+  <si>
+    <t>45,17</t>
+  </si>
+  <si>
+    <t>27,75</t>
+  </si>
+  <si>
+    <t>2,36</t>
+  </si>
+  <si>
+    <t>3,09</t>
+  </si>
+  <si>
+    <t>36,27</t>
+  </si>
+  <si>
+    <t>81,44</t>
+  </si>
+  <si>
+    <t>Persentase Kolom 4 9</t>
+  </si>
+  <si>
+    <t>PROGRES PENDATAAN - KESELURUHAN USAHA</t>
+  </si>
+  <si>
+    <t>Total Prelist Usaha dan Usaha Keluarga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USAHA BKU </t>
+  </si>
+  <si>
+    <t>USAHA DALAM KELUARGA</t>
+  </si>
+  <si>
+    <t>Total Usaha</t>
+  </si>
+  <si>
+    <t>Persentase Total Usaha</t>
+  </si>
+  <si>
+    <t>Subtotal</t>
+  </si>
+  <si>
+    <t>Persentase Subtotal</t>
+  </si>
+  <si>
+    <t>Ditemukan​</t>
+  </si>
+  <si>
+    <t>Persentase Ditemukan​</t>
+  </si>
+  <si>
+    <t>Baru​</t>
+  </si>
+  <si>
+    <t>Persentase Baru​</t>
+  </si>
+  <si>
+    <t>Subtotal​</t>
+  </si>
+  <si>
+    <t>Persentase Subtotal​</t>
+  </si>
+  <si>
+    <t>11,62</t>
+  </si>
+  <si>
+    <t>67,08</t>
+  </si>
+  <si>
+    <t>82,74</t>
+  </si>
+  <si>
+    <t>8,8</t>
+  </si>
+  <si>
+    <t>63,17</t>
+  </si>
+  <si>
+    <t>6,1</t>
+  </si>
+  <si>
+    <t>52,8</t>
+  </si>
+  <si>
+    <t>11,53</t>
+  </si>
+  <si>
+    <t>68,43</t>
+  </si>
+  <si>
+    <t>10,8</t>
+  </si>
+  <si>
+    <t>68,56</t>
+  </si>
+  <si>
+    <t>7,48</t>
   </si>
   <si>
     <t>63,32</t>
   </si>
   <si>
-    <t>63,58</t>
-  </si>
-  <si>
-    <t>34,65</t>
-  </si>
-  <si>
-    <t>13,38</t>
-  </si>
-  <si>
-    <t>3,35</t>
-  </si>
-  <si>
-    <t>29,14</t>
-  </si>
-  <si>
-    <t>26,74</t>
-  </si>
-  <si>
-    <t>1,6</t>
-  </si>
-  <si>
-    <t>61,4</t>
-  </si>
-  <si>
-    <t>61,54</t>
-  </si>
-  <si>
-    <t>28,17</t>
-  </si>
-  <si>
-    <t>19,17</t>
-  </si>
-  <si>
-    <t>12,17</t>
-  </si>
-  <si>
-    <t>27,93</t>
-  </si>
-  <si>
-    <t>34,72</t>
-  </si>
-  <si>
-    <t>0,89</t>
-  </si>
-  <si>
-    <t>62,89</t>
-  </si>
-  <si>
-    <t>63,14</t>
-  </si>
-  <si>
-    <t>0,22</t>
-  </si>
-  <si>
-    <t>43,99</t>
-  </si>
-  <si>
-    <t>4,78</t>
-  </si>
-  <si>
-    <t>19,09</t>
-  </si>
-  <si>
-    <t>44,69</t>
-  </si>
-  <si>
-    <t>1,74</t>
-  </si>
-  <si>
-    <t>88,68</t>
-  </si>
-  <si>
-    <t>88,9</t>
-  </si>
-  <si>
-    <t>0,17</t>
-  </si>
-  <si>
-    <t>22,32</t>
-  </si>
-  <si>
-    <t>16,99</t>
-  </si>
-  <si>
-    <t>7,47</t>
-  </si>
-  <si>
-    <t>40,06</t>
-  </si>
-  <si>
-    <t>32,16</t>
-  </si>
-  <si>
-    <t>1,17</t>
-  </si>
-  <si>
-    <t>54,48</t>
-  </si>
-  <si>
-    <t>54,65</t>
-  </si>
-  <si>
-    <t>0,3</t>
-  </si>
-  <si>
-    <t>0,04</t>
-  </si>
-  <si>
-    <t>6,78</t>
-  </si>
-  <si>
-    <t>13,84</t>
-  </si>
-  <si>
-    <t>7,19</t>
-  </si>
-  <si>
-    <t>47,92</t>
-  </si>
-  <si>
-    <t>10,87</t>
-  </si>
-  <si>
-    <t>5,32</t>
-  </si>
-  <si>
-    <t>17,65</t>
-  </si>
-  <si>
-    <t>17,96</t>
-  </si>
-  <si>
-    <t>0,25</t>
-  </si>
-  <si>
-    <t>22,39</t>
-  </si>
-  <si>
-    <t>19,35</t>
-  </si>
-  <si>
-    <t>18,45</t>
-  </si>
-  <si>
-    <t>20,82</t>
-  </si>
-  <si>
-    <t>18,44</t>
-  </si>
-  <si>
-    <t>1,67</t>
-  </si>
-  <si>
-    <t>40,83</t>
-  </si>
-  <si>
-    <t>41,08</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha BKU</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha yang Ditemukan dan Baru (UB + UMKM)</t>
-  </si>
-  <si>
-    <t>Persentase Kolom 4 21</t>
-  </si>
-  <si>
-    <t>Persentase hasil bagi jumlah usaha pada kolom tersebut dengan jumlah prelist usaha (kolom 3).</t>
-  </si>
-  <si>
-    <t>PROGRES PENDATAAN - SKALA USAHA</t>
-  </si>
-  <si>
-    <t>JUMLAH PRELIST</t>
-  </si>
-  <si>
-    <t>JUMLAH USAHA BKU MENURUT STATUS SKALA USAHA (UB, UM, UMK)</t>
-  </si>
-  <si>
-    <t>UB​</t>
-  </si>
-  <si>
-    <t>Persentase UB​</t>
-  </si>
-  <si>
-    <t>UM​</t>
-  </si>
-  <si>
-    <t>Persentase UM​</t>
-  </si>
-  <si>
-    <t>UMK​</t>
-  </si>
-  <si>
-    <t>Persentase UMK​</t>
-  </si>
-  <si>
-    <t>Tidak Dapat Diklasifikasikan</t>
-  </si>
-  <si>
-    <t>Total Usaha BKU</t>
-  </si>
-  <si>
-    <t>Persentase Total Usaha BKU</t>
-  </si>
-  <si>
-    <t>83</t>
-  </si>
-  <si>
-    <t>11,58</t>
-  </si>
-  <si>
-    <t>26,59</t>
-  </si>
-  <si>
-    <t>126,09</t>
-  </si>
-  <si>
-    <t>39,07</t>
-  </si>
-  <si>
-    <t>34,03</t>
-  </si>
-  <si>
-    <t>51,75</t>
-  </si>
-  <si>
-    <t>16,88</t>
-  </si>
-  <si>
-    <t>17,98</t>
-  </si>
-  <si>
-    <t>104,11</t>
-  </si>
-  <si>
-    <t>8,73</t>
-  </si>
-  <si>
-    <t>20,03</t>
-  </si>
-  <si>
-    <t>122,78</t>
+    <t>5,94</t>
+  </si>
+  <si>
+    <t>68,84</t>
   </si>
   <si>
     <t>20,36</t>
   </si>
   <si>
-    <t>23,7</t>
-  </si>
-  <si>
-    <t>105,04</t>
-  </si>
-  <si>
-    <t>15,57</t>
-  </si>
-  <si>
-    <t>27,02</t>
-  </si>
-  <si>
-    <t>82,67</t>
-  </si>
-  <si>
-    <t>17,53</t>
-  </si>
-  <si>
-    <t>19,19</t>
-  </si>
-  <si>
-    <t>128,57</t>
-  </si>
-  <si>
-    <t>12,4</t>
-  </si>
-  <si>
-    <t>19,22</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>44,91</t>
-  </si>
-  <si>
-    <t>98,18</t>
-  </si>
-  <si>
-    <t>37,12</t>
-  </si>
-  <si>
-    <t>63,43</t>
-  </si>
-  <si>
-    <t>128,13</t>
-  </si>
-  <si>
-    <t>155,56</t>
-  </si>
-  <si>
-    <t>61,07</t>
-  </si>
-  <si>
-    <t>111,11</t>
-  </si>
-  <si>
-    <t>35,09</t>
-  </si>
-  <si>
-    <t>63,05</t>
-  </si>
-  <si>
-    <t>113,04</t>
-  </si>
-  <si>
-    <t>34,85</t>
-  </si>
-  <si>
-    <t>89,08</t>
-  </si>
-  <si>
-    <t>54,51</t>
-  </si>
-  <si>
-    <t>61,76</t>
-  </si>
-  <si>
-    <t>6,44</t>
-  </si>
-  <si>
-    <t>17,97</t>
-  </si>
-  <si>
-    <t>117,5</t>
-  </si>
-  <si>
-    <t>39,06</t>
-  </si>
-  <si>
-    <t>40,69</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha (UB/UM/UMK)</t>
-  </si>
-  <si>
-    <t>Jumlah prelist usaha yang berhasil didata (keberadaan ditemukan, baru, pindah dapat ditelusuri) berdasarkan skala usaha, untuk usaha baru didekati dengan omzet sebagai berikut: UB (lebih dari 50 Milyar), UM (15-50 Milyar), UMK - Kecil (2-15 Milyar), UMK - Mikro (0-2 Milyar).</t>
-  </si>
-  <si>
-    <t>Tidak Dapat Diklasifikasikan (Kolom 10)</t>
-  </si>
-  <si>
-    <t>Usaha baru dengan nilai omzet/pendapatan kosong sehingga tidak dapat diklasifikasikan skala usahanya, misalnya usaha unit pembantu/penunjang.</t>
-  </si>
-  <si>
-    <t>Persentase Jumlah UB</t>
-  </si>
-  <si>
-    <t>Persentase hasil bagi jumlah UB yang berhasil didata dengan jumlah prelist UB (kolom 3).</t>
-  </si>
-  <si>
-    <t>Persentase Jumlah UM</t>
-  </si>
-  <si>
-    <t>Persentase hasil bagi jumlah UM yang berhasil didata dengan jumlah prelist UM (kolom 4).</t>
-  </si>
-  <si>
-    <t>Persentase Jumlah UMK</t>
-  </si>
-  <si>
-    <t>Persentase hasil bagi jumlah UMK yang berhasil didata dengan jumlah prelist UMK (kolom 5).</t>
-  </si>
-  <si>
-    <t>PROGRES PENDATAAN - USAHA KELUARGA</t>
-  </si>
-  <si>
-    <t>Jumlah Prelist Usaha Keluarga (ST2023 + UMKM)</t>
-  </si>
-  <si>
-    <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha dalam Keluarga (Ditemukan + Baru)</t>
-  </si>
-  <si>
-    <t>Persentase Usaha dalam Keluarga (Ditemukan + Baru)</t>
-  </si>
-  <si>
-    <t>47,82</t>
-  </si>
-  <si>
-    <t>23,57</t>
-  </si>
-  <si>
-    <t>0,38</t>
-  </si>
-  <si>
-    <t>9,48</t>
-  </si>
-  <si>
-    <t>33,42</t>
-  </si>
-  <si>
-    <t>81,24</t>
-  </si>
-  <si>
-    <t>58,39</t>
-  </si>
-  <si>
-    <t>19,87</t>
-  </si>
-  <si>
-    <t>0,51</t>
-  </si>
-  <si>
-    <t>9,16</t>
-  </si>
-  <si>
-    <t>29,91</t>
-  </si>
-  <si>
-    <t>88,3</t>
-  </si>
-  <si>
-    <t>44,41</t>
-  </si>
-  <si>
-    <t>24,43</t>
-  </si>
-  <si>
-    <t>0,45</t>
-  </si>
-  <si>
-    <t>7,92</t>
-  </si>
-  <si>
-    <t>33,74</t>
-  </si>
-  <si>
-    <t>78,15</t>
-  </si>
-  <si>
-    <t>36,6</t>
-  </si>
-  <si>
-    <t>22,62</t>
-  </si>
-  <si>
-    <t>14,66</t>
-  </si>
-  <si>
-    <t>31,2</t>
-  </si>
-  <si>
-    <t>67,8</t>
-  </si>
-  <si>
-    <t>49,04</t>
-  </si>
-  <si>
-    <t>22,25</t>
-  </si>
-  <si>
-    <t>8,33</t>
-  </si>
-  <si>
-    <t>35,62</t>
-  </si>
-  <si>
-    <t>84,67</t>
-  </si>
-  <si>
-    <t>49,45</t>
-  </si>
-  <si>
-    <t>21,47</t>
-  </si>
-  <si>
-    <t>0,23</t>
-  </si>
-  <si>
-    <t>10,57</t>
-  </si>
-  <si>
-    <t>32,09</t>
-  </si>
-  <si>
-    <t>81,54</t>
-  </si>
-  <si>
-    <t>47,73</t>
-  </si>
-  <si>
-    <t>19,7</t>
-  </si>
-  <si>
-    <t>17,12</t>
-  </si>
-  <si>
-    <t>37,43</t>
-  </si>
-  <si>
-    <t>85,16</t>
-  </si>
-  <si>
-    <t>46,95</t>
-  </si>
-  <si>
-    <t>21,64</t>
-  </si>
-  <si>
-    <t>0,18</t>
-  </si>
-  <si>
-    <t>8,39</t>
-  </si>
-  <si>
-    <t>37,65</t>
-  </si>
-  <si>
-    <t>84,6</t>
-  </si>
-  <si>
-    <t>42,75</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>0,48</t>
-  </si>
-  <si>
-    <t>4,84</t>
-  </si>
-  <si>
-    <t>27,03</t>
-  </si>
-  <si>
-    <t>69,77</t>
-  </si>
-  <si>
-    <t>51,84</t>
-  </si>
-  <si>
-    <t>27,36</t>
-  </si>
-  <si>
-    <t>0,72</t>
-  </si>
-  <si>
-    <t>6,85</t>
-  </si>
-  <si>
-    <t>23,16</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>47,06</t>
-  </si>
-  <si>
-    <t>28,98</t>
-  </si>
-  <si>
-    <t>0,57</t>
-  </si>
-  <si>
-    <t>5,95</t>
-  </si>
-  <si>
-    <t>26,6</t>
-  </si>
-  <si>
-    <t>73,66</t>
-  </si>
-  <si>
-    <t>46,97</t>
-  </si>
-  <si>
-    <t>29,9</t>
-  </si>
-  <si>
-    <t>0,71</t>
-  </si>
-  <si>
-    <t>12,18</t>
-  </si>
-  <si>
-    <t>28,03</t>
-  </si>
-  <si>
-    <t>57,26</t>
-  </si>
-  <si>
-    <t>23,98</t>
-  </si>
-  <si>
-    <t>0,56</t>
-  </si>
-  <si>
-    <t>7,61</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>89,26</t>
-  </si>
-  <si>
-    <t>54,04</t>
-  </si>
-  <si>
-    <t>29,22</t>
-  </si>
-  <si>
-    <t>0,44</t>
-  </si>
-  <si>
-    <t>26,41</t>
-  </si>
-  <si>
-    <t>80,46</t>
-  </si>
-  <si>
-    <t>23,03</t>
-  </si>
-  <si>
-    <t>29,12</t>
-  </si>
-  <si>
-    <t>0,81</t>
-  </si>
-  <si>
-    <t>14,47</t>
-  </si>
-  <si>
-    <t>310,46</t>
-  </si>
-  <si>
-    <t>333,49</t>
-  </si>
-  <si>
-    <t>45,17</t>
-  </si>
-  <si>
-    <t>27,75</t>
-  </si>
-  <si>
-    <t>2,36</t>
-  </si>
-  <si>
-    <t>3,09</t>
-  </si>
-  <si>
-    <t>36,27</t>
-  </si>
-  <si>
-    <t>81,44</t>
-  </si>
-  <si>
-    <t>Persentase Kolom 4 9</t>
-  </si>
-  <si>
-    <t>PROGRES PENDATAAN - KESELURUHAN USAHA</t>
-  </si>
-  <si>
-    <t>Total Prelist Usaha dan Usaha Keluarga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USAHA BKU </t>
-  </si>
-  <si>
-    <t>USAHA DALAM KELUARGA</t>
-  </si>
-  <si>
-    <t>Total Usaha</t>
-  </si>
-  <si>
-    <t>Persentase Total Usaha</t>
-  </si>
-  <si>
-    <t>Subtotal</t>
-  </si>
-  <si>
-    <t>Persentase Subtotal</t>
-  </si>
-  <si>
-    <t>Ditemukan​</t>
-  </si>
-  <si>
-    <t>Persentase Ditemukan​</t>
-  </si>
-  <si>
-    <t>Baru​</t>
-  </si>
-  <si>
-    <t>Persentase Baru​</t>
-  </si>
-  <si>
-    <t>Subtotal​</t>
-  </si>
-  <si>
-    <t>Persentase Subtotal​</t>
-  </si>
-  <si>
-    <t>11,51</t>
-  </si>
-  <si>
-    <t>67</t>
-  </si>
-  <si>
-    <t>16,94</t>
-  </si>
-  <si>
-    <t>82,73</t>
-  </si>
-  <si>
-    <t>8,74</t>
-  </si>
-  <si>
-    <t>63,12</t>
-  </si>
-  <si>
-    <t>6,03</t>
-  </si>
-  <si>
-    <t>52,72</t>
-  </si>
-  <si>
-    <t>11,44</t>
-  </si>
-  <si>
-    <t>68,38</t>
-  </si>
-  <si>
-    <t>10,73</t>
-  </si>
-  <si>
-    <t>68,51</t>
-  </si>
-  <si>
-    <t>7,4</t>
-  </si>
-  <si>
-    <t>63,27</t>
-  </si>
-  <si>
-    <t>5,87</t>
-  </si>
-  <si>
-    <t>68,76</t>
-  </si>
-  <si>
-    <t>20,05</t>
-  </si>
-  <si>
-    <t>66,07</t>
-  </si>
-  <si>
-    <t>30,82</t>
-  </si>
-  <si>
-    <t>73,78</t>
-  </si>
-  <si>
-    <t>34,79</t>
-  </si>
-  <si>
-    <t>71,74</t>
-  </si>
-  <si>
-    <t>28,42</t>
+    <t>66,16</t>
+  </si>
+  <si>
+    <t>31,06</t>
+  </si>
+  <si>
+    <t>73,83</t>
+  </si>
+  <si>
+    <t>35,44</t>
+  </si>
+  <si>
+    <t>71,92</t>
+  </si>
+  <si>
+    <t>28,43</t>
   </si>
   <si>
     <t>73,57</t>
   </si>
   <si>
-    <t>44,21</t>
-  </si>
-  <si>
-    <t>89,23</t>
-  </si>
-  <si>
-    <t>22,49</t>
-  </si>
-  <si>
-    <t>78,01</t>
-  </si>
-  <si>
-    <t>7,08</t>
-  </si>
-  <si>
-    <t>45,59</t>
-  </si>
-  <si>
-    <t>22,65</t>
-  </si>
-  <si>
-    <t>64,63</t>
+    <t>44,5</t>
+  </si>
+  <si>
+    <t>89,28</t>
+  </si>
+  <si>
+    <t>78,05</t>
+  </si>
+  <si>
+    <t>7,18</t>
+  </si>
+  <si>
+    <t>45,8</t>
+  </si>
+  <si>
+    <t>22,71</t>
+  </si>
+  <si>
+    <t>64,76</t>
   </si>
   <si>
     <t>Total Prelist Usaha Dan Usaha Keluarga</t>
@@ -1709,88 +1715,97 @@
     <t>Persentase Usaha dalam Keluarga</t>
   </si>
   <si>
-    <t>6,36</t>
-  </si>
-  <si>
-    <t>54,81</t>
-  </si>
-  <si>
-    <t>3,05</t>
-  </si>
-  <si>
-    <t>67,92</t>
+    <t>6,41</t>
+  </si>
+  <si>
+    <t>54,73</t>
+  </si>
+  <si>
+    <t>3,06</t>
+  </si>
+  <si>
+    <t>67,91</t>
+  </si>
+  <si>
+    <t>4,43</t>
+  </si>
+  <si>
+    <t>56,39</t>
+  </si>
+  <si>
+    <t>6,27</t>
+  </si>
+  <si>
+    <t>44,98</t>
+  </si>
+  <si>
+    <t>5,99</t>
+  </si>
+  <si>
+    <t>57,43</t>
+  </si>
+  <si>
+    <t>5,93</t>
+  </si>
+  <si>
+    <t>56,05</t>
+  </si>
+  <si>
+    <t>5,66</t>
+  </si>
+  <si>
+    <t>49,7</t>
   </si>
   <si>
     <t>4,39</t>
   </si>
   <si>
-    <t>56,47</t>
-  </si>
-  <si>
-    <t>45,09</t>
-  </si>
-  <si>
-    <t>5,94</t>
-  </si>
-  <si>
-    <t>57,5</t>
-  </si>
-  <si>
-    <t>56,1</t>
-  </si>
-  <si>
-    <t>5,63</t>
-  </si>
-  <si>
-    <t>49,8</t>
-  </si>
-  <si>
-    <t>4,32</t>
-  </si>
-  <si>
-    <t>58,65</t>
-  </si>
-  <si>
-    <t>6,38</t>
-  </si>
-  <si>
-    <t>58,78</t>
-  </si>
-  <si>
-    <t>6,1</t>
-  </si>
-  <si>
-    <t>60,42</t>
-  </si>
-  <si>
-    <t>8,94</t>
-  </si>
-  <si>
-    <t>56,95</t>
+    <t>58,53</t>
+  </si>
+  <si>
+    <t>6,47</t>
+  </si>
+  <si>
+    <t>58,71</t>
+  </si>
+  <si>
+    <t>6,14</t>
+  </si>
+  <si>
+    <t>60,39</t>
+  </si>
+  <si>
+    <t>9,08</t>
+  </si>
+  <si>
+    <t>56,83</t>
   </si>
   <si>
     <t>55,71</t>
   </si>
   <si>
-    <t>6,46</t>
-  </si>
-  <si>
-    <t>66,43</t>
-  </si>
-  <si>
-    <t>4,5</t>
-  </si>
-  <si>
-    <t>14,56</t>
-  </si>
-  <si>
-    <t>25,95</t>
-  </si>
-  <si>
-    <t>15,79</t>
-  </si>
-  <si>
-    <t>43,82</t>
+    <t>6,51</t>
+  </si>
+  <si>
+    <t>66,4</t>
+  </si>
+  <si>
+    <t>4,53</t>
+  </si>
+  <si>
+    <t>63,1</t>
+  </si>
+  <si>
+    <t>14,65</t>
+  </si>
+  <si>
+    <t>25,79</t>
+  </si>
+  <si>
+    <t>15,88</t>
+  </si>
+  <si>
+    <t>43,74</t>
   </si>
   <si>
     <t>Jumlah Usaha (Semua Status Keberadaan Usaha) Kolom 3</t>
@@ -1980,9 +1995,6 @@
   </si>
   <si>
     <t>33,48</t>
-  </si>
-  <si>
-    <t>16,67</t>
   </si>
   <si>
     <t>83,33</t>
@@ -2731,16 +2743,16 @@
         <v>3491483</v>
       </c>
       <c r="D7" s="6">
-        <v>810810</v>
+        <v>813409</v>
       </c>
       <c r="E7" s="6">
-        <v>3839931</v>
+        <v>3863473</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>34</v>
       </c>
       <c r="G7" s="6">
-        <v>2328018</v>
+        <v>2343589</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>35</v>
@@ -2775,16 +2787,16 @@
         <v>97072</v>
       </c>
       <c r="D8" s="9">
-        <v>24934</v>
+        <v>24948</v>
       </c>
       <c r="E8" s="9">
-        <v>121206</v>
+        <v>121257</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>39</v>
       </c>
       <c r="G8" s="9">
-        <v>82471</v>
+        <v>82473</v>
       </c>
       <c r="H8" s="10" t="s">
         <v>40</v>
@@ -2819,16 +2831,16 @@
         <v>230431</v>
       </c>
       <c r="D9" s="9">
-        <v>57172</v>
+        <v>57381</v>
       </c>
       <c r="E9" s="9">
-        <v>251134</v>
+        <v>252676</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>44</v>
       </c>
       <c r="G9" s="9">
-        <v>158590</v>
+        <v>159609</v>
       </c>
       <c r="H9" s="10" t="s">
         <v>45</v>
@@ -2860,19 +2872,19 @@
         <v>48</v>
       </c>
       <c r="C10" s="9">
-        <v>436273</v>
+        <v>436272</v>
       </c>
       <c r="D10" s="9">
-        <v>119721</v>
+        <v>120236</v>
       </c>
       <c r="E10" s="9">
-        <v>466781</v>
+        <v>470653</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>49</v>
       </c>
       <c r="G10" s="9">
-        <v>266466</v>
+        <v>268813</v>
       </c>
       <c r="H10" s="10" t="s">
         <v>50</v>
@@ -2907,16 +2919,16 @@
         <v>489942</v>
       </c>
       <c r="D11" s="9">
-        <v>92221</v>
+        <v>92487</v>
       </c>
       <c r="E11" s="9">
-        <v>515318</v>
+        <v>518079</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>54</v>
       </c>
       <c r="G11" s="9">
-        <v>317597</v>
+        <v>319612</v>
       </c>
       <c r="H11" s="10" t="s">
         <v>55</v>
@@ -2951,16 +2963,16 @@
         <v>580719</v>
       </c>
       <c r="D12" s="9">
-        <v>113016</v>
+        <v>113397</v>
       </c>
       <c r="E12" s="9">
-        <v>617010</v>
+        <v>620890</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>59</v>
       </c>
       <c r="G12" s="9">
-        <v>380022</v>
+        <v>382775</v>
       </c>
       <c r="H12" s="10" t="s">
         <v>60</v>
@@ -2995,16 +3007,16 @@
         <v>263315</v>
       </c>
       <c r="D13" s="9">
-        <v>53327</v>
+        <v>53506</v>
       </c>
       <c r="E13" s="9">
-        <v>298254</v>
+        <v>300153</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>64</v>
       </c>
       <c r="G13" s="9">
-        <v>170951</v>
+        <v>172069</v>
       </c>
       <c r="H13" s="10" t="s">
         <v>65</v>
@@ -3039,16 +3051,16 @@
         <v>187422</v>
       </c>
       <c r="D14" s="9">
-        <v>46829</v>
+        <v>47087</v>
       </c>
       <c r="E14" s="9">
-        <v>207720</v>
+        <v>209455</v>
       </c>
       <c r="F14" s="10" t="s">
         <v>69</v>
       </c>
       <c r="G14" s="9">
-        <v>125080</v>
+        <v>126251</v>
       </c>
       <c r="H14" s="10" t="s">
         <v>70</v>
@@ -3083,16 +3095,16 @@
         <v>154763</v>
       </c>
       <c r="D15" s="9">
-        <v>39810</v>
+        <v>39995</v>
       </c>
       <c r="E15" s="9">
-        <v>173181</v>
+        <v>174893</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>74</v>
       </c>
       <c r="G15" s="9">
-        <v>103535</v>
+        <v>104668</v>
       </c>
       <c r="H15" s="10" t="s">
         <v>75</v>
@@ -3127,16 +3139,16 @@
         <v>170543</v>
       </c>
       <c r="D16" s="9">
-        <v>45406</v>
+        <v>45504</v>
       </c>
       <c r="E16" s="9">
-        <v>207110</v>
+        <v>208099</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>79</v>
       </c>
       <c r="G16" s="9">
-        <v>140759</v>
+        <v>141456</v>
       </c>
       <c r="H16" s="10" t="s">
         <v>80</v>
@@ -3171,16 +3183,16 @@
         <v>157837</v>
       </c>
       <c r="D17" s="9">
-        <v>34095</v>
+        <v>34157</v>
       </c>
       <c r="E17" s="9">
-        <v>173467</v>
+        <v>174547</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>84</v>
       </c>
       <c r="G17" s="9">
-        <v>122765</v>
+        <v>123764</v>
       </c>
       <c r="H17" s="10" t="s">
         <v>85</v>
@@ -3215,16 +3227,16 @@
         <v>86207</v>
       </c>
       <c r="D18" s="9">
-        <v>26795</v>
+        <v>26800</v>
       </c>
       <c r="E18" s="9">
-        <v>114393</v>
+        <v>114422</v>
       </c>
       <c r="F18" s="10" t="s">
         <v>89</v>
       </c>
       <c r="G18" s="9">
-        <v>74930</v>
+        <v>74973</v>
       </c>
       <c r="H18" s="10" t="s">
         <v>90</v>
@@ -3259,16 +3271,16 @@
         <v>109078</v>
       </c>
       <c r="D19" s="9">
-        <v>30514</v>
+        <v>30566</v>
       </c>
       <c r="E19" s="9">
-        <v>139246</v>
+        <v>139636</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>94</v>
       </c>
       <c r="G19" s="9">
-        <v>94063</v>
+        <v>94356</v>
       </c>
       <c r="H19" s="10" t="s">
         <v>95</v>
@@ -3303,16 +3315,16 @@
         <v>47152</v>
       </c>
       <c r="D20" s="9">
-        <v>14077</v>
+        <v>14101</v>
       </c>
       <c r="E20" s="9">
-        <v>61125</v>
+        <v>61232</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>99</v>
       </c>
       <c r="G20" s="9">
-        <v>44168</v>
+        <v>44255</v>
       </c>
       <c r="H20" s="10" t="s">
         <v>100</v>
@@ -3344,19 +3356,19 @@
         <v>103</v>
       </c>
       <c r="C21" s="9">
-        <v>410236</v>
+        <v>410237</v>
       </c>
       <c r="D21" s="9">
-        <v>97940</v>
+        <v>98260</v>
       </c>
       <c r="E21" s="9">
-        <v>418970</v>
+        <v>422155</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>104</v>
       </c>
       <c r="G21" s="9">
-        <v>200841</v>
+        <v>202508</v>
       </c>
       <c r="H21" s="10" t="s">
         <v>105</v>
@@ -3391,16 +3403,16 @@
         <v>70493</v>
       </c>
       <c r="D22" s="9">
-        <v>14953</v>
+        <v>14984</v>
       </c>
       <c r="E22" s="9">
-        <v>75016</v>
+        <v>75326</v>
       </c>
       <c r="F22" s="10" t="s">
         <v>109</v>
       </c>
       <c r="G22" s="9">
-        <v>45780</v>
+        <v>46007</v>
       </c>
       <c r="H22" s="10" t="s">
         <v>110</v>
@@ -3435,16 +3447,16 @@
         <v>3491483</v>
       </c>
       <c r="D23" s="12">
-        <v>810810</v>
+        <v>813409</v>
       </c>
       <c r="E23" s="12">
-        <v>3839931</v>
+        <v>3863473</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>34</v>
       </c>
       <c r="G23" s="12">
-        <v>2328018</v>
+        <v>2343589</v>
       </c>
       <c r="H23" s="13" t="s">
         <v>35</v>
@@ -4136,31 +4148,31 @@
         <v>189</v>
       </c>
       <c r="V8" s="6">
-        <v>86450</v>
+        <v>87283</v>
       </c>
       <c r="W8" s="7" t="s">
         <v>193</v>
       </c>
       <c r="X8" s="6">
-        <v>131133</v>
+        <v>132312</v>
       </c>
       <c r="Y8" s="7" t="s">
         <v>194</v>
       </c>
       <c r="Z8" s="6">
-        <v>59264</v>
+        <v>59728</v>
       </c>
       <c r="AA8" s="7" t="s">
         <v>195</v>
       </c>
       <c r="AB8" s="6">
-        <v>328895</v>
+        <v>330011</v>
       </c>
       <c r="AC8" s="7" t="s">
         <v>196</v>
       </c>
       <c r="AD8" s="6">
-        <v>115346</v>
+        <v>116583</v>
       </c>
       <c r="AE8" s="7" t="s">
         <v>197</v>
@@ -4172,7 +4184,7 @@
         <v>190</v>
       </c>
       <c r="AH8" s="6">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI8" s="7" t="s">
         <v>191</v>
@@ -4184,13 +4196,13 @@
         <v>198</v>
       </c>
       <c r="AL8" s="6">
-        <v>201796</v>
+        <v>203866</v>
       </c>
       <c r="AM8" s="7" t="s">
         <v>199</v>
       </c>
       <c r="AN8" s="6">
-        <v>202908</v>
+        <v>204978</v>
       </c>
       <c r="AO8" s="7" t="s">
         <v>200</v>
@@ -4261,31 +4273,31 @@
         <v>201</v>
       </c>
       <c r="V9" s="9">
-        <v>1998</v>
+        <v>2006</v>
       </c>
       <c r="W9" s="10" t="s">
         <v>203</v>
       </c>
       <c r="X9" s="9">
-        <v>1976</v>
+        <v>1988</v>
       </c>
       <c r="Y9" s="10" t="s">
         <v>204</v>
       </c>
       <c r="Z9" s="9">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="AA9" s="10" t="s">
         <v>205</v>
       </c>
       <c r="AB9" s="9">
-        <v>4996</v>
+        <v>4987</v>
       </c>
       <c r="AC9" s="10" t="s">
         <v>206</v>
       </c>
       <c r="AD9" s="9">
-        <v>2079</v>
+        <v>2084</v>
       </c>
       <c r="AE9" s="10" t="s">
         <v>207</v>
@@ -4309,13 +4321,13 @@
         <v>208</v>
       </c>
       <c r="AL9" s="9">
-        <v>4077</v>
+        <v>4090</v>
       </c>
       <c r="AM9" s="10" t="s">
         <v>209</v>
       </c>
       <c r="AN9" s="9">
-        <v>4100</v>
+        <v>4113</v>
       </c>
       <c r="AO9" s="10" t="s">
         <v>210</v>
@@ -4386,31 +4398,31 @@
         <v>211</v>
       </c>
       <c r="V10" s="9">
-        <v>4971</v>
+        <v>5008</v>
       </c>
       <c r="W10" s="10" t="s">
         <v>213</v>
       </c>
       <c r="X10" s="9">
-        <v>12594</v>
+        <v>12675</v>
       </c>
       <c r="Y10" s="10" t="s">
         <v>214</v>
       </c>
       <c r="Z10" s="9">
-        <v>8753</v>
+        <v>8794</v>
       </c>
       <c r="AA10" s="10" t="s">
         <v>215</v>
       </c>
       <c r="AB10" s="9">
-        <v>15322</v>
+        <v>15419</v>
       </c>
       <c r="AC10" s="10" t="s">
         <v>216</v>
       </c>
       <c r="AD10" s="9">
-        <v>5413</v>
+        <v>5501</v>
       </c>
       <c r="AE10" s="10" t="s">
         <v>217</v>
@@ -4434,13 +4446,13 @@
         <v>218</v>
       </c>
       <c r="AL10" s="9">
-        <v>10384</v>
+        <v>10509</v>
       </c>
       <c r="AM10" s="10" t="s">
         <v>219</v>
       </c>
       <c r="AN10" s="9">
-        <v>10436</v>
+        <v>10561</v>
       </c>
       <c r="AO10" s="10" t="s">
         <v>220</v>
@@ -4454,7 +4466,7 @@
         <v>48</v>
       </c>
       <c r="C11" s="9">
-        <v>93539</v>
+        <v>93538</v>
       </c>
       <c r="D11" s="9">
         <v>127</v>
@@ -4511,31 +4523,31 @@
         <v>221</v>
       </c>
       <c r="V11" s="9">
-        <v>5512</v>
+        <v>5577</v>
       </c>
       <c r="W11" s="10" t="s">
         <v>222</v>
       </c>
       <c r="X11" s="9">
-        <v>10744</v>
+        <v>10877</v>
       </c>
       <c r="Y11" s="10" t="s">
         <v>223</v>
       </c>
       <c r="Z11" s="9">
-        <v>3793</v>
+        <v>3875</v>
       </c>
       <c r="AA11" s="10" t="s">
         <v>224</v>
       </c>
       <c r="AB11" s="9">
-        <v>57649</v>
+        <v>57977</v>
       </c>
       <c r="AC11" s="10" t="s">
         <v>225</v>
       </c>
       <c r="AD11" s="9">
-        <v>13212</v>
+        <v>13386</v>
       </c>
       <c r="AE11" s="10" t="s">
         <v>226</v>
@@ -4547,7 +4559,7 @@
         <v>190</v>
       </c>
       <c r="AH11" s="9">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AI11" s="10" t="s">
         <v>191</v>
@@ -4559,13 +4571,13 @@
         <v>227</v>
       </c>
       <c r="AL11" s="9">
-        <v>18724</v>
+        <v>18963</v>
       </c>
       <c r="AM11" s="10" t="s">
         <v>228</v>
       </c>
       <c r="AN11" s="9">
-        <v>18851</v>
+        <v>19090</v>
       </c>
       <c r="AO11" s="10" t="s">
         <v>229</v>
@@ -4636,31 +4648,31 @@
         <v>230</v>
       </c>
       <c r="V12" s="9">
-        <v>14463</v>
+        <v>14582</v>
       </c>
       <c r="W12" s="10" t="s">
         <v>231</v>
       </c>
       <c r="X12" s="9">
-        <v>27903</v>
+        <v>28123</v>
       </c>
       <c r="Y12" s="10" t="s">
         <v>232</v>
       </c>
       <c r="Z12" s="9">
-        <v>9744</v>
+        <v>9776</v>
       </c>
       <c r="AA12" s="10" t="s">
         <v>233</v>
       </c>
       <c r="AB12" s="9">
-        <v>42294</v>
+        <v>42383</v>
       </c>
       <c r="AC12" s="10" t="s">
         <v>234</v>
       </c>
       <c r="AD12" s="9">
-        <v>15843</v>
+        <v>15972</v>
       </c>
       <c r="AE12" s="10" t="s">
         <v>235</v>
@@ -4684,13 +4696,13 @@
         <v>236</v>
       </c>
       <c r="AL12" s="9">
-        <v>30306</v>
+        <v>30554</v>
       </c>
       <c r="AM12" s="10" t="s">
         <v>237</v>
       </c>
       <c r="AN12" s="9">
-        <v>30383</v>
+        <v>30631</v>
       </c>
       <c r="AO12" s="10" t="s">
         <v>238</v>
@@ -4761,31 +4773,31 @@
         <v>211</v>
       </c>
       <c r="V13" s="9">
-        <v>13944</v>
+        <v>14048</v>
       </c>
       <c r="W13" s="10" t="s">
         <v>239</v>
       </c>
       <c r="X13" s="9">
-        <v>25000</v>
+        <v>25148</v>
       </c>
       <c r="Y13" s="10" t="s">
         <v>240</v>
       </c>
       <c r="Z13" s="9">
-        <v>12167</v>
+        <v>12237</v>
       </c>
       <c r="AA13" s="10" t="s">
         <v>241</v>
       </c>
       <c r="AB13" s="9">
-        <v>58447</v>
+        <v>58478</v>
       </c>
       <c r="AC13" s="10" t="s">
         <v>242</v>
       </c>
       <c r="AD13" s="9">
-        <v>21540</v>
+        <v>21744</v>
       </c>
       <c r="AE13" s="10" t="s">
         <v>243</v>
@@ -4809,13 +4821,13 @@
         <v>244</v>
       </c>
       <c r="AL13" s="9">
-        <v>35484</v>
+        <v>35792</v>
       </c>
       <c r="AM13" s="10" t="s">
         <v>245</v>
       </c>
       <c r="AN13" s="9">
-        <v>35606</v>
+        <v>35914</v>
       </c>
       <c r="AO13" s="10" t="s">
         <v>246</v>
@@ -4886,31 +4898,31 @@
         <v>247</v>
       </c>
       <c r="V14" s="9">
-        <v>4679</v>
+        <v>4727</v>
       </c>
       <c r="W14" s="10" t="s">
         <v>248</v>
       </c>
       <c r="X14" s="9">
-        <v>9716</v>
+        <v>9805</v>
       </c>
       <c r="Y14" s="10" t="s">
         <v>249</v>
       </c>
       <c r="Z14" s="9">
-        <v>3359</v>
+        <v>3400</v>
       </c>
       <c r="AA14" s="10" t="s">
         <v>250</v>
       </c>
       <c r="AB14" s="9">
-        <v>37189</v>
+        <v>37372</v>
       </c>
       <c r="AC14" s="10" t="s">
         <v>251</v>
       </c>
       <c r="AD14" s="9">
-        <v>7616</v>
+        <v>7664</v>
       </c>
       <c r="AE14" s="10" t="s">
         <v>252</v>
@@ -4922,10 +4934,10 @@
         <v>190</v>
       </c>
       <c r="AH14" s="9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AI14" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AJ14" s="9">
         <v>4704</v>
@@ -4934,13 +4946,13 @@
         <v>253</v>
       </c>
       <c r="AL14" s="9">
-        <v>12295</v>
+        <v>12391</v>
       </c>
       <c r="AM14" s="10" t="s">
         <v>254</v>
       </c>
       <c r="AN14" s="9">
-        <v>12346</v>
+        <v>12442</v>
       </c>
       <c r="AO14" s="10" t="s">
         <v>255</v>
@@ -5011,31 +5023,31 @@
         <v>211</v>
       </c>
       <c r="V15" s="9">
-        <v>2389</v>
+        <v>2419</v>
       </c>
       <c r="W15" s="10" t="s">
         <v>256</v>
       </c>
       <c r="X15" s="9">
-        <v>8796</v>
+        <v>8949</v>
       </c>
       <c r="Y15" s="10" t="s">
         <v>257</v>
       </c>
       <c r="Z15" s="9">
-        <v>2567</v>
+        <v>2600</v>
       </c>
       <c r="AA15" s="10" t="s">
         <v>258</v>
       </c>
       <c r="AB15" s="9">
-        <v>18498</v>
+        <v>18529</v>
       </c>
       <c r="AC15" s="10" t="s">
         <v>259</v>
       </c>
       <c r="AD15" s="9">
-        <v>5605</v>
+        <v>5708</v>
       </c>
       <c r="AE15" s="10" t="s">
         <v>260</v>
@@ -5059,13 +5071,13 @@
         <v>261</v>
       </c>
       <c r="AL15" s="9">
-        <v>7994</v>
+        <v>8127</v>
       </c>
       <c r="AM15" s="10" t="s">
         <v>262</v>
       </c>
       <c r="AN15" s="9">
-        <v>8030</v>
+        <v>8163</v>
       </c>
       <c r="AO15" s="10" t="s">
         <v>263</v>
@@ -5136,31 +5148,31 @@
         <v>264</v>
       </c>
       <c r="V16" s="9">
-        <v>3865</v>
+        <v>3925</v>
       </c>
       <c r="W16" s="10" t="s">
         <v>265</v>
       </c>
       <c r="X16" s="9">
-        <v>2443</v>
+        <v>2459</v>
       </c>
       <c r="Y16" s="10" t="s">
         <v>266</v>
       </c>
       <c r="Z16" s="9">
-        <v>893</v>
+        <v>909</v>
       </c>
       <c r="AA16" s="10" t="s">
         <v>267</v>
       </c>
       <c r="AB16" s="9">
-        <v>8116</v>
+        <v>8124</v>
       </c>
       <c r="AC16" s="10" t="s">
         <v>268</v>
       </c>
       <c r="AD16" s="9">
-        <v>4746</v>
+        <v>4810</v>
       </c>
       <c r="AE16" s="10" t="s">
         <v>269</v>
@@ -5184,13 +5196,13 @@
         <v>270</v>
       </c>
       <c r="AL16" s="9">
-        <v>8611</v>
+        <v>8735</v>
       </c>
       <c r="AM16" s="10" t="s">
         <v>271</v>
       </c>
       <c r="AN16" s="9">
-        <v>8658</v>
+        <v>8782</v>
       </c>
       <c r="AO16" s="10" t="s">
         <v>272</v>
@@ -5261,31 +5273,31 @@
         <v>273</v>
       </c>
       <c r="V17" s="9">
-        <v>5618</v>
+        <v>5663</v>
       </c>
       <c r="W17" s="10" t="s">
         <v>274</v>
       </c>
       <c r="X17" s="9">
-        <v>2616</v>
+        <v>2638</v>
       </c>
       <c r="Y17" s="10" t="s">
         <v>275</v>
       </c>
       <c r="Z17" s="9">
-        <v>975</v>
+        <v>988</v>
       </c>
       <c r="AA17" s="10" t="s">
         <v>276</v>
       </c>
       <c r="AB17" s="9">
-        <v>6606</v>
+        <v>6593</v>
       </c>
       <c r="AC17" s="10" t="s">
         <v>277</v>
       </c>
       <c r="AD17" s="9">
-        <v>6023</v>
+        <v>6059</v>
       </c>
       <c r="AE17" s="10" t="s">
         <v>278</v>
@@ -5309,13 +5321,13 @@
         <v>279</v>
       </c>
       <c r="AL17" s="9">
-        <v>11641</v>
+        <v>11722</v>
       </c>
       <c r="AM17" s="10" t="s">
         <v>280</v>
       </c>
       <c r="AN17" s="9">
-        <v>11689</v>
+        <v>11770</v>
       </c>
       <c r="AO17" s="10" t="s">
         <v>281</v>
@@ -5386,31 +5398,31 @@
         <v>221</v>
       </c>
       <c r="V18" s="9">
-        <v>7657</v>
+        <v>7800</v>
       </c>
       <c r="W18" s="10" t="s">
         <v>282</v>
       </c>
       <c r="X18" s="9">
-        <v>2957</v>
+        <v>2984</v>
       </c>
       <c r="Y18" s="10" t="s">
         <v>283</v>
       </c>
       <c r="Z18" s="9">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="AA18" s="10" t="s">
         <v>284</v>
       </c>
       <c r="AB18" s="9">
-        <v>6439</v>
+        <v>6481</v>
       </c>
       <c r="AC18" s="10" t="s">
         <v>285</v>
       </c>
       <c r="AD18" s="9">
-        <v>5909</v>
+        <v>6019</v>
       </c>
       <c r="AE18" s="10" t="s">
         <v>286</v>
@@ -5434,13 +5446,13 @@
         <v>287</v>
       </c>
       <c r="AL18" s="9">
-        <v>13566</v>
+        <v>13819</v>
       </c>
       <c r="AM18" s="10" t="s">
         <v>288</v>
       </c>
       <c r="AN18" s="9">
-        <v>13597</v>
+        <v>13850</v>
       </c>
       <c r="AO18" s="10" t="s">
         <v>289</v>
@@ -5511,34 +5523,34 @@
         <v>264</v>
       </c>
       <c r="V19" s="9">
-        <v>3125</v>
+        <v>3126</v>
       </c>
       <c r="W19" s="10" t="s">
         <v>290</v>
       </c>
       <c r="X19" s="9">
-        <v>2126</v>
+        <v>2127</v>
       </c>
       <c r="Y19" s="10" t="s">
-        <v>291</v>
+        <v>240</v>
       </c>
       <c r="Z19" s="9">
         <v>1350</v>
       </c>
       <c r="AA19" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AB19" s="9">
         <v>3098</v>
       </c>
       <c r="AC19" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="AD19" s="9">
+        <v>3858</v>
+      </c>
+      <c r="AE19" s="10" t="s">
         <v>293</v>
-      </c>
-      <c r="AD19" s="9">
-        <v>3851</v>
-      </c>
-      <c r="AE19" s="10" t="s">
-        <v>294</v>
       </c>
       <c r="AF19" s="9">
         <v>0</v>
@@ -5556,19 +5568,19 @@
         <v>99</v>
       </c>
       <c r="AK19" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="AL19" s="9">
+        <v>6984</v>
+      </c>
+      <c r="AM19" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="AL19" s="9">
-        <v>6976</v>
-      </c>
-      <c r="AM19" s="10" t="s">
+      <c r="AN19" s="9">
+        <v>7011</v>
+      </c>
+      <c r="AO19" s="10" t="s">
         <v>296</v>
-      </c>
-      <c r="AN19" s="9">
-        <v>7003</v>
-      </c>
-      <c r="AO19" s="10" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -5585,7 +5597,7 @@
         <v>22</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F20" s="9">
         <v>0</v>
@@ -5633,34 +5645,34 @@
         <v>22</v>
       </c>
       <c r="U20" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="V20" s="9">
+        <v>4388</v>
+      </c>
+      <c r="W20" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="V20" s="9">
-        <v>4359</v>
-      </c>
-      <c r="W20" s="10" t="s">
+      <c r="X20" s="9">
+        <v>1965</v>
+      </c>
+      <c r="Y20" s="10" t="s">
         <v>299</v>
       </c>
-      <c r="X20" s="9">
-        <v>1963</v>
-      </c>
-      <c r="Y20" s="10" t="s">
-        <v>265</v>
-      </c>
       <c r="Z20" s="9">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="AA20" s="10" t="s">
         <v>300</v>
       </c>
       <c r="AB20" s="9">
-        <v>1892</v>
+        <v>1896</v>
       </c>
       <c r="AC20" s="10" t="s">
         <v>301</v>
       </c>
       <c r="AD20" s="9">
-        <v>4428</v>
+        <v>4463</v>
       </c>
       <c r="AE20" s="10" t="s">
         <v>302</v>
@@ -5684,13 +5696,13 @@
         <v>303</v>
       </c>
       <c r="AL20" s="9">
-        <v>8787</v>
+        <v>8851</v>
       </c>
       <c r="AM20" s="10" t="s">
         <v>304</v>
       </c>
       <c r="AN20" s="9">
-        <v>8809</v>
+        <v>8873</v>
       </c>
       <c r="AO20" s="10" t="s">
         <v>305</v>
@@ -5761,31 +5773,31 @@
         <v>306</v>
       </c>
       <c r="V21" s="9">
-        <v>1201</v>
+        <v>1208</v>
       </c>
       <c r="W21" s="10" t="s">
         <v>307</v>
       </c>
       <c r="X21" s="9">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="Y21" s="10" t="s">
         <v>308</v>
       </c>
       <c r="Z21" s="9">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AA21" s="10" t="s">
         <v>309</v>
       </c>
       <c r="AB21" s="9">
-        <v>2155</v>
+        <v>2153</v>
       </c>
       <c r="AC21" s="10" t="s">
         <v>310</v>
       </c>
       <c r="AD21" s="9">
-        <v>1730</v>
+        <v>1746</v>
       </c>
       <c r="AE21" s="10" t="s">
         <v>311</v>
@@ -5809,13 +5821,13 @@
         <v>312</v>
       </c>
       <c r="AL21" s="9">
-        <v>2931</v>
+        <v>2954</v>
       </c>
       <c r="AM21" s="10" t="s">
         <v>313</v>
       </c>
       <c r="AN21" s="9">
-        <v>2940</v>
+        <v>2963</v>
       </c>
       <c r="AO21" s="10" t="s">
         <v>314</v>
@@ -5829,7 +5841,7 @@
         <v>103</v>
       </c>
       <c r="C22" s="9">
-        <v>130758</v>
+        <v>130759</v>
       </c>
       <c r="D22" s="9">
         <v>397</v>
@@ -5886,31 +5898,31 @@
         <v>315</v>
       </c>
       <c r="V22" s="9">
-        <v>8865</v>
+        <v>8991</v>
       </c>
       <c r="W22" s="10" t="s">
         <v>317</v>
       </c>
       <c r="X22" s="9">
-        <v>18098</v>
+        <v>18358</v>
       </c>
       <c r="Y22" s="10" t="s">
         <v>318</v>
       </c>
       <c r="Z22" s="9">
-        <v>9398</v>
+        <v>9512</v>
       </c>
       <c r="AA22" s="10" t="s">
         <v>319</v>
       </c>
       <c r="AB22" s="9">
-        <v>62658</v>
+        <v>62976</v>
       </c>
       <c r="AC22" s="10" t="s">
         <v>320</v>
       </c>
       <c r="AD22" s="9">
-        <v>14219</v>
+        <v>14393</v>
       </c>
       <c r="AE22" s="10" t="s">
         <v>321</v>
@@ -5922,7 +5934,7 @@
         <v>190</v>
       </c>
       <c r="AH22" s="9">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AI22" s="10" t="s">
         <v>202</v>
@@ -5931,19 +5943,19 @@
         <v>6957</v>
       </c>
       <c r="AK22" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="AL22" s="9">
+        <v>23384</v>
+      </c>
+      <c r="AM22" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="AL22" s="9">
-        <v>23084</v>
-      </c>
-      <c r="AM22" s="10" t="s">
+      <c r="AN22" s="9">
+        <v>23781</v>
+      </c>
+      <c r="AO22" s="10" t="s">
         <v>323</v>
-      </c>
-      <c r="AN22" s="9">
-        <v>23481</v>
-      </c>
-      <c r="AO22" s="10" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -5960,7 +5972,7 @@
         <v>43</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
@@ -6008,37 +6020,37 @@
         <v>43</v>
       </c>
       <c r="U23" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="V23" s="9">
+        <v>3815</v>
+      </c>
+      <c r="W23" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="V23" s="9">
-        <v>3804</v>
-      </c>
-      <c r="W23" s="10" t="s">
+      <c r="X23" s="9">
+        <v>3301</v>
+      </c>
+      <c r="Y23" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="X23" s="9">
-        <v>3287</v>
-      </c>
-      <c r="Y23" s="10" t="s">
+      <c r="Z23" s="9">
+        <v>3142</v>
+      </c>
+      <c r="AA23" s="10" t="s">
         <v>327</v>
       </c>
-      <c r="Z23" s="9">
-        <v>3134</v>
-      </c>
-      <c r="AA23" s="10" t="s">
+      <c r="AB23" s="9">
+        <v>3545</v>
+      </c>
+      <c r="AC23" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="AB23" s="9">
-        <v>3536</v>
-      </c>
-      <c r="AC23" s="10" t="s">
+      <c r="AD23" s="9">
+        <v>3176</v>
+      </c>
+      <c r="AE23" s="10" t="s">
         <v>329</v>
-      </c>
-      <c r="AD23" s="9">
-        <v>3132</v>
-      </c>
-      <c r="AE23" s="10" t="s">
-        <v>330</v>
       </c>
       <c r="AF23" s="9">
         <v>0</v>
@@ -6056,19 +6068,19 @@
         <v>284</v>
       </c>
       <c r="AK23" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="AL23" s="9">
+        <v>6991</v>
+      </c>
+      <c r="AM23" s="10" t="s">
         <v>331</v>
       </c>
-      <c r="AL23" s="9">
-        <v>6936</v>
-      </c>
-      <c r="AM23" s="10" t="s">
+      <c r="AN23" s="9">
+        <v>7034</v>
+      </c>
+      <c r="AO23" s="10" t="s">
         <v>332</v>
-      </c>
-      <c r="AN23" s="9">
-        <v>6979</v>
-      </c>
-      <c r="AO23" s="10" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -6136,31 +6148,31 @@
         <v>189</v>
       </c>
       <c r="V24" s="12">
-        <v>86450</v>
+        <v>87283</v>
       </c>
       <c r="W24" s="13" t="s">
         <v>193</v>
       </c>
       <c r="X24" s="12">
-        <v>131133</v>
+        <v>132312</v>
       </c>
       <c r="Y24" s="13" t="s">
         <v>194</v>
       </c>
       <c r="Z24" s="12">
-        <v>59264</v>
+        <v>59728</v>
       </c>
       <c r="AA24" s="13" t="s">
         <v>195</v>
       </c>
       <c r="AB24" s="12">
-        <v>328895</v>
+        <v>330011</v>
       </c>
       <c r="AC24" s="13" t="s">
         <v>196</v>
       </c>
       <c r="AD24" s="12">
-        <v>115346</v>
+        <v>116583</v>
       </c>
       <c r="AE24" s="13" t="s">
         <v>197</v>
@@ -6172,7 +6184,7 @@
         <v>190</v>
       </c>
       <c r="AH24" s="12">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI24" s="13" t="s">
         <v>191</v>
@@ -6184,13 +6196,13 @@
         <v>198</v>
       </c>
       <c r="AL24" s="12">
-        <v>201796</v>
+        <v>203866</v>
       </c>
       <c r="AM24" s="13" t="s">
         <v>199</v>
       </c>
       <c r="AN24" s="12">
-        <v>202908</v>
+        <v>204978</v>
       </c>
       <c r="AO24" s="13" t="s">
         <v>200</v>
@@ -6243,10 +6255,10 @@
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
+        <v>333</v>
+      </c>
+      <c r="B27" s="16" t="s">
         <v>334</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>335</v>
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
@@ -6290,10 +6302,10 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
+        <v>335</v>
+      </c>
+      <c r="B28" s="16" t="s">
         <v>336</v>
-      </c>
-      <c r="B28" s="16" t="s">
-        <v>337</v>
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="16"/>
@@ -6376,7 +6388,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6420,13 +6432,13 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
@@ -6453,31 +6465,31 @@
         <v>122</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="I5" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="K5" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="L5" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="M5" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="N5" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="N5" s="3" t="s">
+      <c r="O5" s="3" t="s">
         <v>348</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6547,28 +6559,28 @@
         <v>760551</v>
       </c>
       <c r="G7" s="6">
-        <v>1269</v>
+        <v>1277</v>
       </c>
       <c r="H7" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="I7" s="6">
+        <v>957</v>
+      </c>
+      <c r="J7" s="7" t="s">
         <v>350</v>
       </c>
-      <c r="I7" s="6">
-        <v>928</v>
-      </c>
-      <c r="J7" s="7" t="s">
+      <c r="K7" s="6">
+        <v>201735</v>
+      </c>
+      <c r="L7" s="7" t="s">
         <v>351</v>
-      </c>
-      <c r="K7" s="6">
-        <v>199713</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>352</v>
       </c>
       <c r="M7" s="6">
         <v>998</v>
       </c>
       <c r="N7" s="6">
-        <v>202908</v>
+        <v>204967</v>
       </c>
       <c r="O7" s="7" t="s">
         <v>200</v>
@@ -6594,28 +6606,28 @@
         <v>11927</v>
       </c>
       <c r="G8" s="9">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I8" s="9">
         <v>59</v>
       </c>
       <c r="J8" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="K8" s="9">
+        <v>4014</v>
+      </c>
+      <c r="L8" s="10" t="s">
         <v>354</v>
-      </c>
-      <c r="K8" s="9">
-        <v>3999</v>
-      </c>
-      <c r="L8" s="10" t="s">
-        <v>355</v>
       </c>
       <c r="M8" s="9">
         <v>13</v>
       </c>
       <c r="N8" s="9">
-        <v>4100</v>
+        <v>4113</v>
       </c>
       <c r="O8" s="10" t="s">
         <v>210</v>
@@ -6641,28 +6653,28 @@
         <v>57474</v>
       </c>
       <c r="G9" s="9">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="I9" s="9">
         <v>13</v>
       </c>
       <c r="J9" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="K9" s="9">
+        <v>10425</v>
+      </c>
+      <c r="L9" s="10" t="s">
         <v>357</v>
-      </c>
-      <c r="K9" s="9">
-        <v>10302</v>
-      </c>
-      <c r="L9" s="10" t="s">
-        <v>358</v>
       </c>
       <c r="M9" s="9">
         <v>62</v>
       </c>
       <c r="N9" s="9">
-        <v>10436</v>
+        <v>10562</v>
       </c>
       <c r="O9" s="10" t="s">
         <v>220</v>
@@ -6676,7 +6688,7 @@
         <v>48</v>
       </c>
       <c r="C10" s="9">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D10" s="9">
         <v>951</v>
@@ -6685,34 +6697,34 @@
         <v>92442</v>
       </c>
       <c r="F10" s="9">
-        <v>93539</v>
+        <v>93538</v>
       </c>
       <c r="G10" s="9">
         <v>152</v>
       </c>
       <c r="H10" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="I10" s="9">
+        <v>84</v>
+      </c>
+      <c r="J10" s="10" t="s">
         <v>359</v>
       </c>
-      <c r="I10" s="9">
-        <v>83</v>
-      </c>
-      <c r="J10" s="10" t="s">
+      <c r="K10" s="9">
+        <v>18747</v>
+      </c>
+      <c r="L10" s="10" t="s">
         <v>360</v>
-      </c>
-      <c r="K10" s="9">
-        <v>18513</v>
-      </c>
-      <c r="L10" s="10" t="s">
-        <v>361</v>
       </c>
       <c r="M10" s="9">
         <v>103</v>
       </c>
       <c r="N10" s="9">
-        <v>18851</v>
+        <v>19086</v>
       </c>
       <c r="O10" s="10" t="s">
-        <v>229</v>
+        <v>361</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6741,13 +6753,13 @@
         <v>362</v>
       </c>
       <c r="I11" s="9">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J11" s="10" t="s">
         <v>363</v>
       </c>
       <c r="K11" s="9">
-        <v>30016</v>
+        <v>30262</v>
       </c>
       <c r="L11" s="10" t="s">
         <v>364</v>
@@ -6756,7 +6768,7 @@
         <v>191</v>
       </c>
       <c r="N11" s="9">
-        <v>30383</v>
+        <v>30631</v>
       </c>
       <c r="O11" s="10" t="s">
         <v>238</v>
@@ -6782,19 +6794,19 @@
         <v>131144</v>
       </c>
       <c r="G12" s="9">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H12" s="10" t="s">
         <v>365</v>
       </c>
       <c r="I12" s="9">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="J12" s="10" t="s">
         <v>366</v>
       </c>
       <c r="K12" s="9">
-        <v>35162</v>
+        <v>35467</v>
       </c>
       <c r="L12" s="10" t="s">
         <v>367</v>
@@ -6803,7 +6815,7 @@
         <v>165</v>
       </c>
       <c r="N12" s="9">
-        <v>35606</v>
+        <v>35915</v>
       </c>
       <c r="O12" s="10" t="s">
         <v>246</v>
@@ -6835,13 +6847,13 @@
         <v>368</v>
       </c>
       <c r="I13" s="9">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J13" s="10" t="s">
         <v>369</v>
       </c>
       <c r="K13" s="9">
-        <v>12177</v>
+        <v>12271</v>
       </c>
       <c r="L13" s="10" t="s">
         <v>370</v>
@@ -6850,10 +6862,10 @@
         <v>39</v>
       </c>
       <c r="N13" s="9">
-        <v>12346</v>
+        <v>12441</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>255</v>
+        <v>371</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6879,25 +6891,25 @@
         <v>45</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="I14" s="9">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K14" s="9">
-        <v>7914</v>
+        <v>8046</v>
       </c>
       <c r="L14" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M14" s="9">
         <v>55</v>
       </c>
       <c r="N14" s="9">
-        <v>8030</v>
+        <v>8163</v>
       </c>
       <c r="O14" s="10" t="s">
         <v>263</v>
@@ -6926,25 +6938,25 @@
         <v>51</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="I15" s="9">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>250</v>
+        <v>376</v>
       </c>
       <c r="K15" s="9">
-        <v>8575</v>
+        <v>8697</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M15" s="9">
         <v>13</v>
       </c>
       <c r="N15" s="9">
-        <v>8658</v>
+        <v>8782</v>
       </c>
       <c r="O15" s="10" t="s">
         <v>272</v>
@@ -6973,25 +6985,25 @@
         <v>54</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="I16" s="9">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="K16" s="9">
-        <v>11543</v>
+        <v>11622</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M16" s="9">
         <v>43</v>
       </c>
       <c r="N16" s="9">
-        <v>11689</v>
+        <v>11770</v>
       </c>
       <c r="O16" s="10" t="s">
         <v>281</v>
@@ -7020,28 +7032,28 @@
         <v>41</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="I17" s="9">
         <v>14</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="K17" s="9">
-        <v>13468</v>
+        <v>13718</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="M17" s="9">
         <v>74</v>
       </c>
       <c r="N17" s="9">
-        <v>13597</v>
+        <v>13847</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>289</v>
+        <v>384</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -7067,28 +7079,28 @@
         <v>30</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="I18" s="9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="K18" s="9">
-        <v>6941</v>
+        <v>6947</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="M18" s="9">
         <v>12</v>
       </c>
       <c r="N18" s="9">
-        <v>7003</v>
+        <v>7010</v>
       </c>
       <c r="O18" s="10" t="s">
-        <v>297</v>
+        <v>388</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -7111,31 +7123,31 @@
         <v>9909</v>
       </c>
       <c r="G19" s="9">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>385</v>
+        <v>352</v>
       </c>
       <c r="I19" s="9">
         <v>23</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="K19" s="9">
-        <v>8748</v>
+        <v>8810</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="M19" s="9">
         <v>12</v>
       </c>
       <c r="N19" s="9">
-        <v>8809</v>
+        <v>8872</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>305</v>
+        <v>391</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -7161,25 +7173,25 @@
         <v>10</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="I20" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J20" s="10" t="s">
         <v>190</v>
       </c>
       <c r="K20" s="9">
-        <v>2927</v>
+        <v>2949</v>
       </c>
       <c r="L20" s="10" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="M20" s="9">
         <v>0</v>
       </c>
       <c r="N20" s="9">
-        <v>2940</v>
+        <v>2963</v>
       </c>
       <c r="O20" s="10" t="s">
         <v>314</v>
@@ -7193,7 +7205,7 @@
         <v>103</v>
       </c>
       <c r="C21" s="9">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D21" s="9">
         <v>4256</v>
@@ -7202,34 +7214,34 @@
         <v>125822</v>
       </c>
       <c r="F21" s="9">
-        <v>130758</v>
+        <v>130759</v>
       </c>
       <c r="G21" s="9">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="I21" s="9">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="K21" s="9">
-        <v>22610</v>
+        <v>22888</v>
       </c>
       <c r="L21" s="10" t="s">
-        <v>391</v>
+        <v>323</v>
       </c>
       <c r="M21" s="9">
         <v>177</v>
       </c>
       <c r="N21" s="9">
-        <v>23481</v>
+        <v>23779</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -7255,28 +7267,28 @@
         <v>47</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="I22" s="9">
         <v>75</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="K22" s="9">
-        <v>6818</v>
+        <v>6872</v>
       </c>
       <c r="L22" s="10" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="M22" s="9">
         <v>39</v>
       </c>
       <c r="N22" s="9">
-        <v>6979</v>
+        <v>7033</v>
       </c>
       <c r="O22" s="10" t="s">
-        <v>333</v>
+        <v>398</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -7299,28 +7311,28 @@
         <v>760551</v>
       </c>
       <c r="G23" s="12">
-        <v>1269</v>
+        <v>1277</v>
       </c>
       <c r="H23" s="13" t="s">
+        <v>349</v>
+      </c>
+      <c r="I23" s="12">
+        <v>957</v>
+      </c>
+      <c r="J23" s="13" t="s">
         <v>350</v>
       </c>
-      <c r="I23" s="12">
-        <v>928</v>
-      </c>
-      <c r="J23" s="13" t="s">
+      <c r="K23" s="12">
+        <v>201735</v>
+      </c>
+      <c r="L23" s="13" t="s">
         <v>351</v>
-      </c>
-      <c r="K23" s="12">
-        <v>199713</v>
-      </c>
-      <c r="L23" s="13" t="s">
-        <v>352</v>
       </c>
       <c r="M23" s="12">
         <v>998</v>
       </c>
       <c r="N23" s="12">
-        <v>202908</v>
+        <v>204967</v>
       </c>
       <c r="O23" s="13" t="s">
         <v>200</v>
@@ -7347,10 +7359,10 @@
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C26" s="16"/>
       <c r="D26" s="16"/>
@@ -7368,10 +7380,10 @@
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
@@ -7389,10 +7401,10 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="16"/>
@@ -7410,10 +7422,10 @@
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C29" s="16"/>
       <c r="D29" s="16"/>
@@ -7431,10 +7443,10 @@
     </row>
     <row r="30" ht="24" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
@@ -7496,7 +7508,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7544,10 +7556,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -7561,10 +7573,10 @@
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7677,31 +7689,31 @@
         <v>1029980</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F7" s="6">
         <v>507732</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="H7" s="6">
         <v>8286</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="J7" s="6">
         <v>204079</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="L7" s="6">
         <v>719790</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="N7" s="6">
         <v>314</v>
@@ -7713,7 +7725,7 @@
         <v>1749770</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7730,31 +7742,31 @@
         <v>60428</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="F8" s="9">
         <v>20562</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="H8" s="9">
         <v>525</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="J8" s="9">
         <v>9483</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="L8" s="9">
         <v>30950</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="N8" s="9">
         <v>20</v>
@@ -7766,7 +7778,7 @@
         <v>91378</v>
       </c>
       <c r="Q8" s="10" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7783,31 +7795,31 @@
         <v>76335</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="F9" s="9">
         <v>42002</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="H9" s="9">
         <v>765</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="J9" s="9">
         <v>13608</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="L9" s="9">
         <v>57999</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="N9" s="9">
         <v>16</v>
@@ -7819,7 +7831,7 @@
         <v>134334</v>
       </c>
       <c r="Q9" s="10" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7836,13 +7848,13 @@
         <v>73923</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="F10" s="9">
         <v>45693</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="H10" s="9">
         <v>378</v>
@@ -7854,13 +7866,13 @@
         <v>29617</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="L10" s="9">
         <v>63023</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="N10" s="9">
         <v>17</v>
@@ -7872,7 +7884,7 @@
         <v>136946</v>
       </c>
       <c r="Q10" s="10" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7889,31 +7901,31 @@
         <v>170255</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="F11" s="9">
         <v>77236</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="H11" s="9">
         <v>778</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J11" s="9">
         <v>28915</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="L11" s="9">
         <v>123663</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="N11" s="9">
         <v>56</v>
@@ -7925,7 +7937,7 @@
         <v>293918</v>
       </c>
       <c r="Q11" s="10" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7942,31 +7954,31 @@
         <v>205794</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="F12" s="9">
         <v>89353</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="H12" s="9">
         <v>965</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="J12" s="9">
         <v>43993</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="L12" s="9">
         <v>133521</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="N12" s="9">
         <v>57</v>
@@ -7978,7 +7990,7 @@
         <v>339315</v>
       </c>
       <c r="Q12" s="10" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7995,31 +8007,31 @@
         <v>61250</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F13" s="9">
         <v>25287</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="H13" s="9">
         <v>282</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J13" s="9">
         <v>21972</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="L13" s="9">
         <v>48038</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="N13" s="9">
         <v>15</v>
@@ -8031,7 +8043,7 @@
         <v>109288</v>
       </c>
       <c r="Q13" s="10" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8048,31 +8060,31 @@
         <v>60428</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="F14" s="9">
         <v>27861</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="H14" s="9">
         <v>229</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="J14" s="9">
         <v>10806</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="L14" s="9">
         <v>48463</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="N14" s="9">
         <v>17</v>
@@ -8084,7 +8096,7 @@
         <v>108891</v>
       </c>
       <c r="Q14" s="10" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8101,31 +8113,31 @@
         <v>48848</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="F15" s="9">
         <v>29714</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="H15" s="9">
         <v>551</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="J15" s="9">
         <v>5534</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="L15" s="9">
         <v>30883</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="N15" s="9">
         <v>6</v>
@@ -8137,7 +8149,7 @@
         <v>79731</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8154,31 +8166,31 @@
         <v>79999</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="F16" s="9">
         <v>42223</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="H16" s="9">
         <v>1112</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="J16" s="9">
         <v>10573</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="L16" s="9">
         <v>35735</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="N16" s="9">
         <v>26</v>
@@ -8190,7 +8202,7 @@
         <v>115734</v>
       </c>
       <c r="Q16" s="10" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8207,31 +8219,31 @@
         <v>55369</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="F17" s="9">
         <v>34097</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="H17" s="9">
         <v>672</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="J17" s="9">
         <v>6999</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="L17" s="9">
         <v>31289</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="N17" s="9">
         <v>5</v>
@@ -8243,7 +8255,7 @@
         <v>86658</v>
       </c>
       <c r="Q17" s="10" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8260,31 +8272,31 @@
         <v>37907</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="F18" s="9">
         <v>24130</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="H18" s="9">
         <v>577</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="J18" s="9">
         <v>9827</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L18" s="9">
         <v>22619</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="N18" s="9">
         <v>36</v>
@@ -8296,7 +8308,7 @@
         <v>60526</v>
       </c>
       <c r="Q18" s="10" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8313,31 +8325,31 @@
         <v>58095</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="F19" s="9">
         <v>24332</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="H19" s="9">
         <v>565</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="J19" s="9">
         <v>7721</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="L19" s="9">
         <v>32468</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="N19" s="9">
         <v>13</v>
@@ -8349,7 +8361,7 @@
         <v>90563</v>
       </c>
       <c r="Q19" s="10" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8366,31 +8378,31 @@
         <v>27714</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="F20" s="9">
         <v>14985</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="H20" s="9">
         <v>224</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="J20" s="9">
         <v>2480</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="L20" s="9">
         <v>13544</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="N20" s="9">
         <v>6</v>
@@ -8402,7 +8414,7 @@
         <v>41258</v>
       </c>
       <c r="Q20" s="10" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8419,31 +8431,31 @@
         <v>2890</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="F21" s="9">
         <v>3655</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="H21" s="9">
         <v>102</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J21" s="9">
         <v>1816</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="L21" s="9">
         <v>38966</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="N21" s="9">
         <v>18</v>
@@ -8455,7 +8467,7 @@
         <v>41856</v>
       </c>
       <c r="Q21" s="10" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8472,31 +8484,31 @@
         <v>10745</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="F22" s="9">
         <v>6602</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="H22" s="9">
         <v>561</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="J22" s="9">
         <v>735</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="L22" s="9">
         <v>8629</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="N22" s="9">
         <v>6</v>
@@ -8508,7 +8520,7 @@
         <v>19374</v>
       </c>
       <c r="Q22" s="10" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8525,31 +8537,31 @@
         <v>1029980</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F23" s="12">
         <v>507732</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="H23" s="12">
         <v>8286</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="J23" s="12">
         <v>204079</v>
       </c>
       <c r="K23" s="13" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="L23" s="12">
         <v>719790</v>
       </c>
       <c r="M23" s="13" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="N23" s="12">
         <v>314</v>
@@ -8561,7 +8573,7 @@
         <v>1749770</v>
       </c>
       <c r="Q23" s="13" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -8587,10 +8599,10 @@
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C26" s="16"/>
       <c r="D26" s="16"/>
@@ -8652,7 +8664,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -8707,13 +8719,13 @@
         <v>122</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
@@ -8721,7 +8733,7 @@
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -8729,10 +8741,10 @@
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
       <c r="R4" s="3" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8754,28 +8766,28 @@
         <v>153</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
@@ -8856,19 +8868,19 @@
         <v>2914264</v>
       </c>
       <c r="F7" s="6">
-        <v>87562</v>
+        <v>88395</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="H7" s="6">
-        <v>115346</v>
+        <v>116583</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>197</v>
       </c>
       <c r="J7" s="6">
-        <v>202908</v>
+        <v>204978</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>200</v>
@@ -8877,25 +8889,25 @@
         <v>1029980</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="N7" s="6">
         <v>719790</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="P7" s="6">
         <v>1749770</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="R7" s="6">
-        <v>1952678</v>
+        <v>1954748</v>
       </c>
       <c r="S7" s="7" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8915,19 +8927,19 @@
         <v>115412</v>
       </c>
       <c r="F8" s="9">
-        <v>2021</v>
+        <v>2029</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>518</v>
+        <v>308</v>
       </c>
       <c r="H8" s="9">
-        <v>2079</v>
+        <v>2084</v>
       </c>
       <c r="I8" s="10" t="s">
         <v>207</v>
       </c>
       <c r="J8" s="9">
-        <v>4100</v>
+        <v>4113</v>
       </c>
       <c r="K8" s="10" t="s">
         <v>210</v>
@@ -8936,25 +8948,25 @@
         <v>60428</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="N8" s="9">
         <v>30950</v>
       </c>
       <c r="O8" s="10" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="P8" s="9">
         <v>91378</v>
       </c>
       <c r="Q8" s="10" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="R8" s="9">
-        <v>95478</v>
+        <v>95491</v>
       </c>
       <c r="S8" s="10" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8974,19 +8986,19 @@
         <v>229367</v>
       </c>
       <c r="F9" s="9">
-        <v>5023</v>
+        <v>5060</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="H9" s="9">
-        <v>5413</v>
+        <v>5501</v>
       </c>
       <c r="I9" s="10" t="s">
         <v>217</v>
       </c>
       <c r="J9" s="9">
-        <v>10436</v>
+        <v>10561</v>
       </c>
       <c r="K9" s="10" t="s">
         <v>220</v>
@@ -8995,25 +9007,25 @@
         <v>76335</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="N9" s="9">
         <v>57999</v>
       </c>
       <c r="O9" s="10" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="P9" s="9">
         <v>134334</v>
       </c>
       <c r="Q9" s="10" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="R9" s="9">
-        <v>144770</v>
+        <v>144895</v>
       </c>
       <c r="S9" s="10" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9024,28 +9036,28 @@
         <v>48</v>
       </c>
       <c r="C10" s="9">
-        <v>93539</v>
+        <v>93538</v>
       </c>
       <c r="D10" s="9">
         <v>201989</v>
       </c>
       <c r="E10" s="9">
-        <v>295528</v>
+        <v>295527</v>
       </c>
       <c r="F10" s="9">
-        <v>5639</v>
+        <v>5704</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="H10" s="9">
-        <v>13212</v>
+        <v>13386</v>
       </c>
       <c r="I10" s="10" t="s">
         <v>226</v>
       </c>
       <c r="J10" s="9">
-        <v>18851</v>
+        <v>19090</v>
       </c>
       <c r="K10" s="10" t="s">
         <v>229</v>
@@ -9054,25 +9066,25 @@
         <v>73923</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="N10" s="9">
         <v>63023</v>
       </c>
       <c r="O10" s="10" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="P10" s="9">
         <v>136946</v>
       </c>
       <c r="Q10" s="10" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="R10" s="9">
-        <v>155797</v>
+        <v>156036</v>
       </c>
       <c r="S10" s="10" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9092,19 +9104,19 @@
         <v>474247</v>
       </c>
       <c r="F11" s="9">
-        <v>14540</v>
+        <v>14659</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="H11" s="9">
-        <v>15843</v>
+        <v>15972</v>
       </c>
       <c r="I11" s="10" t="s">
         <v>235</v>
       </c>
       <c r="J11" s="9">
-        <v>30383</v>
+        <v>30631</v>
       </c>
       <c r="K11" s="10" t="s">
         <v>238</v>
@@ -9113,25 +9125,25 @@
         <v>170255</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="N11" s="9">
         <v>123663</v>
       </c>
       <c r="O11" s="10" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="P11" s="9">
         <v>293918</v>
       </c>
       <c r="Q11" s="10" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="R11" s="9">
-        <v>324301</v>
+        <v>324549</v>
       </c>
       <c r="S11" s="10" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9151,19 +9163,19 @@
         <v>547278</v>
       </c>
       <c r="F12" s="9">
-        <v>14066</v>
+        <v>14170</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="H12" s="9">
-        <v>21540</v>
+        <v>21744</v>
       </c>
       <c r="I12" s="10" t="s">
         <v>243</v>
       </c>
       <c r="J12" s="9">
-        <v>35606</v>
+        <v>35914</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>246</v>
@@ -9172,25 +9184,25 @@
         <v>205794</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="N12" s="9">
         <v>133521</v>
       </c>
       <c r="O12" s="10" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="P12" s="9">
         <v>339315</v>
       </c>
       <c r="Q12" s="10" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="R12" s="9">
-        <v>374921</v>
+        <v>375229</v>
       </c>
       <c r="S12" s="10" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9210,19 +9222,19 @@
         <v>192251</v>
       </c>
       <c r="F13" s="9">
-        <v>4730</v>
+        <v>4778</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="H13" s="9">
-        <v>7616</v>
+        <v>7664</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>252</v>
       </c>
       <c r="J13" s="9">
-        <v>12346</v>
+        <v>12442</v>
       </c>
       <c r="K13" s="10" t="s">
         <v>255</v>
@@ -9231,25 +9243,25 @@
         <v>61250</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="N13" s="9">
         <v>48038</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="P13" s="9">
         <v>109288</v>
       </c>
       <c r="Q13" s="10" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="R13" s="9">
-        <v>121634</v>
+        <v>121730</v>
       </c>
       <c r="S13" s="10" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9269,19 +9281,19 @@
         <v>170050</v>
       </c>
       <c r="F14" s="9">
-        <v>2425</v>
+        <v>2455</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="H14" s="9">
-        <v>5605</v>
+        <v>5708</v>
       </c>
       <c r="I14" s="10" t="s">
         <v>260</v>
       </c>
       <c r="J14" s="9">
-        <v>8030</v>
+        <v>8163</v>
       </c>
       <c r="K14" s="10" t="s">
         <v>263</v>
@@ -9290,25 +9302,25 @@
         <v>60428</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="N14" s="9">
         <v>48463</v>
       </c>
       <c r="O14" s="10" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="P14" s="9">
         <v>108891</v>
       </c>
       <c r="Q14" s="10" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="R14" s="9">
-        <v>116921</v>
+        <v>117054</v>
       </c>
       <c r="S14" s="10" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9328,19 +9340,19 @@
         <v>133782</v>
       </c>
       <c r="F15" s="9">
-        <v>3912</v>
+        <v>3972</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="H15" s="9">
-        <v>4746</v>
+        <v>4810</v>
       </c>
       <c r="I15" s="10" t="s">
         <v>269</v>
       </c>
       <c r="J15" s="9">
-        <v>8658</v>
+        <v>8782</v>
       </c>
       <c r="K15" s="10" t="s">
         <v>272</v>
@@ -9349,25 +9361,25 @@
         <v>48848</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="N15" s="9">
         <v>30883</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="P15" s="9">
         <v>79731</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="R15" s="9">
-        <v>88389</v>
+        <v>88513</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9387,19 +9399,19 @@
         <v>172696</v>
       </c>
       <c r="F16" s="9">
-        <v>5666</v>
+        <v>5711</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="H16" s="9">
-        <v>6023</v>
+        <v>6059</v>
       </c>
       <c r="I16" s="10" t="s">
         <v>278</v>
       </c>
       <c r="J16" s="9">
-        <v>11689</v>
+        <v>11770</v>
       </c>
       <c r="K16" s="10" t="s">
         <v>281</v>
@@ -9408,25 +9420,25 @@
         <v>79999</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="N16" s="9">
         <v>35735</v>
       </c>
       <c r="O16" s="10" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="P16" s="9">
         <v>115734</v>
       </c>
       <c r="Q16" s="10" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="R16" s="9">
-        <v>127423</v>
+        <v>127504</v>
       </c>
       <c r="S16" s="10" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9446,19 +9458,19 @@
         <v>139743</v>
       </c>
       <c r="F17" s="9">
-        <v>7688</v>
+        <v>7831</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="H17" s="9">
-        <v>5909</v>
+        <v>6019</v>
       </c>
       <c r="I17" s="10" t="s">
         <v>286</v>
       </c>
       <c r="J17" s="9">
-        <v>13597</v>
+        <v>13850</v>
       </c>
       <c r="K17" s="10" t="s">
         <v>289</v>
@@ -9467,25 +9479,25 @@
         <v>55369</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="N17" s="9">
         <v>31289</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="P17" s="9">
         <v>86658</v>
       </c>
       <c r="Q17" s="10" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="R17" s="9">
-        <v>100255</v>
+        <v>100508</v>
       </c>
       <c r="S17" s="10" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9505,46 +9517,46 @@
         <v>91795</v>
       </c>
       <c r="F18" s="9">
-        <v>3152</v>
+        <v>3153</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="H18" s="9">
-        <v>3851</v>
+        <v>3858</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="J18" s="9">
-        <v>7003</v>
+        <v>7011</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="L18" s="9">
         <v>37907</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="N18" s="9">
         <v>22619</v>
       </c>
       <c r="O18" s="10" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="P18" s="9">
         <v>60526</v>
       </c>
       <c r="Q18" s="10" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="R18" s="9">
-        <v>67529</v>
+        <v>67537</v>
       </c>
       <c r="S18" s="10" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9564,19 +9576,19 @@
         <v>111370</v>
       </c>
       <c r="F19" s="9">
-        <v>4381</v>
+        <v>4410</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="H19" s="9">
-        <v>4428</v>
+        <v>4463</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>302</v>
       </c>
       <c r="J19" s="9">
-        <v>8809</v>
+        <v>8873</v>
       </c>
       <c r="K19" s="10" t="s">
         <v>305</v>
@@ -9585,25 +9597,25 @@
         <v>58095</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="N19" s="9">
         <v>32468</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="P19" s="9">
         <v>90563</v>
       </c>
       <c r="Q19" s="10" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="R19" s="9">
-        <v>99372</v>
+        <v>99436</v>
       </c>
       <c r="S19" s="10" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9623,19 +9635,19 @@
         <v>56660</v>
       </c>
       <c r="F20" s="9">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>542</v>
+        <v>433</v>
       </c>
       <c r="H20" s="9">
-        <v>1730</v>
+        <v>1746</v>
       </c>
       <c r="I20" s="10" t="s">
         <v>311</v>
       </c>
       <c r="J20" s="9">
-        <v>2940</v>
+        <v>2963</v>
       </c>
       <c r="K20" s="10" t="s">
         <v>314</v>
@@ -9644,25 +9656,25 @@
         <v>27714</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="N20" s="9">
         <v>13544</v>
       </c>
       <c r="O20" s="10" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="P20" s="9">
         <v>41258</v>
       </c>
       <c r="Q20" s="10" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="R20" s="9">
-        <v>44198</v>
+        <v>44221</v>
       </c>
       <c r="S20" s="10" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9673,55 +9685,55 @@
         <v>103</v>
       </c>
       <c r="C21" s="9">
-        <v>130758</v>
+        <v>130759</v>
       </c>
       <c r="D21" s="9">
         <v>12551</v>
       </c>
       <c r="E21" s="9">
-        <v>143309</v>
+        <v>143310</v>
       </c>
       <c r="F21" s="9">
-        <v>9262</v>
+        <v>9388</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="H21" s="9">
-        <v>14219</v>
+        <v>14393</v>
       </c>
       <c r="I21" s="10" t="s">
         <v>321</v>
       </c>
       <c r="J21" s="9">
-        <v>23481</v>
+        <v>23781</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="L21" s="9">
         <v>2890</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="N21" s="9">
         <v>38966</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="P21" s="9">
         <v>41856</v>
       </c>
       <c r="Q21" s="10" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="R21" s="9">
-        <v>65337</v>
+        <v>65637</v>
       </c>
       <c r="S21" s="10" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9741,46 +9753,46 @@
         <v>40776</v>
       </c>
       <c r="F22" s="9">
-        <v>3847</v>
+        <v>3858</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="H22" s="9">
-        <v>3132</v>
+        <v>3176</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J22" s="9">
-        <v>6979</v>
+        <v>7034</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="L22" s="9">
         <v>10745</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="N22" s="9">
         <v>8629</v>
       </c>
       <c r="O22" s="10" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="P22" s="9">
         <v>19374</v>
       </c>
       <c r="Q22" s="10" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="R22" s="9">
-        <v>26353</v>
+        <v>26408</v>
       </c>
       <c r="S22" s="10" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9800,19 +9812,19 @@
         <v>2914264</v>
       </c>
       <c r="F23" s="12">
-        <v>87562</v>
+        <v>88395</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="H23" s="12">
-        <v>115346</v>
+        <v>116583</v>
       </c>
       <c r="I23" s="13" t="s">
         <v>197</v>
       </c>
       <c r="J23" s="12">
-        <v>202908</v>
+        <v>204978</v>
       </c>
       <c r="K23" s="13" t="s">
         <v>200</v>
@@ -9821,25 +9833,25 @@
         <v>1029980</v>
       </c>
       <c r="M23" s="13" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="N23" s="12">
         <v>719790</v>
       </c>
       <c r="O23" s="13" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="P23" s="12">
         <v>1749770</v>
       </c>
       <c r="Q23" s="13" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="R23" s="12">
-        <v>1952678</v>
+        <v>1954748</v>
       </c>
       <c r="S23" s="13" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
@@ -9867,10 +9879,10 @@
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C26" s="16"/>
       <c r="D26" s="16"/>
@@ -9892,10 +9904,10 @@
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
@@ -9917,10 +9929,10 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="16"/>
@@ -9942,10 +9954,10 @@
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C29" s="16"/>
       <c r="D29" s="16"/>
@@ -9967,10 +9979,10 @@
     </row>
     <row r="30" ht="24" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
@@ -10031,7 +10043,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -10059,19 +10071,19 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10105,19 +10117,19 @@
         <v>33</v>
       </c>
       <c r="C6" s="6">
-        <v>3192471</v>
+        <v>3197300</v>
       </c>
       <c r="D6" s="6">
-        <v>202908</v>
+        <v>204978</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="F6" s="6">
         <v>1749770</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10128,19 +10140,19 @@
         <v>38</v>
       </c>
       <c r="C7" s="9">
-        <v>134540</v>
+        <v>134558</v>
       </c>
       <c r="D7" s="9">
-        <v>4100</v>
+        <v>4113</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="F7" s="9">
         <v>91378</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10151,19 +10163,19 @@
         <v>43</v>
       </c>
       <c r="C8" s="9">
-        <v>237868</v>
+        <v>238212</v>
       </c>
       <c r="D8" s="9">
-        <v>10436</v>
+        <v>10561</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="F8" s="9">
         <v>134334</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10174,19 +10186,19 @@
         <v>48</v>
       </c>
       <c r="C9" s="9">
-        <v>303691</v>
+        <v>304473</v>
       </c>
       <c r="D9" s="9">
-        <v>18851</v>
+        <v>19090</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>258</v>
+        <v>571</v>
       </c>
       <c r="F9" s="9">
         <v>136946</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10197,19 +10209,19 @@
         <v>53</v>
       </c>
       <c r="C10" s="9">
-        <v>511183</v>
+        <v>511772</v>
       </c>
       <c r="D10" s="9">
-        <v>30383</v>
+        <v>30631</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="F10" s="9">
         <v>293918</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10220,19 +10232,19 @@
         <v>58</v>
       </c>
       <c r="C11" s="9">
-        <v>604870</v>
+        <v>605427</v>
       </c>
       <c r="D11" s="9">
-        <v>35606</v>
+        <v>35914</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>222</v>
+        <v>575</v>
       </c>
       <c r="F11" s="9">
         <v>339315</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10243,19 +10255,19 @@
         <v>63</v>
       </c>
       <c r="C12" s="9">
-        <v>219467</v>
+        <v>219876</v>
       </c>
       <c r="D12" s="9">
-        <v>12346</v>
+        <v>12442</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="F12" s="9">
         <v>109288</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10266,19 +10278,19 @@
         <v>68</v>
       </c>
       <c r="C13" s="9">
-        <v>185678</v>
+        <v>186028</v>
       </c>
       <c r="D13" s="9">
-        <v>8030</v>
+        <v>8163</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="F13" s="9">
         <v>108891</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10289,19 +10301,19 @@
         <v>73</v>
       </c>
       <c r="C14" s="9">
-        <v>135650</v>
+        <v>135814</v>
       </c>
       <c r="D14" s="9">
-        <v>8658</v>
+        <v>8782</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="F14" s="9">
         <v>79731</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10312,19 +10324,19 @@
         <v>78</v>
       </c>
       <c r="C15" s="9">
-        <v>191536</v>
+        <v>191639</v>
       </c>
       <c r="D15" s="9">
-        <v>11689</v>
+        <v>11770</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="F15" s="9">
         <v>115734</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10335,19 +10347,19 @@
         <v>83</v>
       </c>
       <c r="C16" s="9">
-        <v>152160</v>
+        <v>152488</v>
       </c>
       <c r="D16" s="9">
-        <v>13597</v>
+        <v>13850</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="F16" s="9">
         <v>86658</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10358,10 +10370,10 @@
         <v>88</v>
       </c>
       <c r="C17" s="9">
-        <v>108639</v>
+        <v>108648</v>
       </c>
       <c r="D17" s="9">
-        <v>7003</v>
+        <v>7011</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>86</v>
@@ -10370,7 +10382,7 @@
         <v>60526</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10381,19 +10393,19 @@
         <v>93</v>
       </c>
       <c r="C18" s="9">
-        <v>136321</v>
+        <v>136396</v>
       </c>
       <c r="D18" s="9">
-        <v>8809</v>
+        <v>8873</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="F18" s="9">
         <v>90563</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10404,19 +10416,19 @@
         <v>98</v>
       </c>
       <c r="C19" s="9">
-        <v>65361</v>
+        <v>65384</v>
       </c>
       <c r="D19" s="9">
-        <v>2940</v>
+        <v>2963</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="F19" s="9">
         <v>41258</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>521</v>
+        <v>591</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10427,19 +10439,19 @@
         <v>103</v>
       </c>
       <c r="C20" s="9">
-        <v>161299</v>
+        <v>162291</v>
       </c>
       <c r="D20" s="9">
-        <v>23481</v>
+        <v>23781</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="F20" s="9">
         <v>41856</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10450,19 +10462,19 @@
         <v>108</v>
       </c>
       <c r="C21" s="9">
-        <v>44208</v>
+        <v>44294</v>
       </c>
       <c r="D21" s="9">
-        <v>6979</v>
+        <v>7034</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="F21" s="9">
         <v>19374</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10473,19 +10485,19 @@
         <v>113</v>
       </c>
       <c r="C22" s="12">
-        <v>3192471</v>
+        <v>3197300</v>
       </c>
       <c r="D22" s="12">
-        <v>202908</v>
+        <v>204978</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="F22" s="12">
         <v>1749770</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -10501,10 +10513,10 @@
     </row>
     <row r="25" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="C25" s="16"/>
       <c r="D25" s="16"/>
@@ -10537,7 +10549,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -10567,7 +10579,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -10579,22 +10591,22 @@
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11098,7 +11110,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -11138,22 +11150,22 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
@@ -11178,16 +11190,16 @@
         <v>153</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11251,25 +11263,25 @@
         <v>1541</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="H7" s="6">
         <v>4807</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="J7" s="6">
         <v>959437</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="L7" s="6">
         <v>427144</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11292,25 +11304,25 @@
         <v>18</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="H8" s="9">
         <v>130</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="J8" s="9">
         <v>52055</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="L8" s="9">
         <v>23606</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11333,25 +11345,25 @@
         <v>126</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="H9" s="9">
         <v>354</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="J9" s="9">
         <v>75938</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="L9" s="9">
         <v>33635</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11362,7 +11374,7 @@
         <v>48</v>
       </c>
       <c r="C10" s="9">
-        <v>93539</v>
+        <v>93538</v>
       </c>
       <c r="D10" s="9">
         <v>247954</v>
@@ -11374,25 +11386,25 @@
         <v>197</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="H10" s="9">
         <v>1118</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="J10" s="9">
         <v>73451</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="L10" s="9">
         <v>30627</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11415,25 +11427,25 @@
         <v>343</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="H11" s="9">
         <v>407</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="J11" s="9">
         <v>169254</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="L11" s="9">
         <v>75137</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11456,25 +11468,25 @@
         <v>409</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="H12" s="9">
         <v>691</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="J12" s="9">
         <v>205112</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="L12" s="9">
         <v>87636</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11497,25 +11509,25 @@
         <v>124</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="H13" s="9">
         <v>201</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="J13" s="9">
         <v>61039</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="L13" s="9">
         <v>28357</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11538,25 +11550,25 @@
         <v>64</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="H14" s="9">
         <v>348</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="J14" s="9">
         <v>60117</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="L14" s="9">
         <v>31701</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11579,25 +11591,25 @@
         <v>22</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="H15" s="9">
         <v>283</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="J15" s="9">
         <v>40513</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="L15" s="9">
         <v>21861</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11620,25 +11632,25 @@
         <v>61</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="H16" s="9">
         <v>182</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="J16" s="9">
         <v>64370</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="L16" s="9">
         <v>22693</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11661,25 +11673,25 @@
         <v>33</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="H17" s="9">
         <v>341</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="J17" s="9">
         <v>42559</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="L17" s="9">
         <v>17791</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11702,25 +11714,25 @@
         <v>39</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="H18" s="9">
         <v>485</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="J18" s="9">
         <v>32921</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="L18" s="9">
         <v>16571</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11743,25 +11755,25 @@
         <v>20</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>654</v>
+        <v>204</v>
       </c>
       <c r="H19" s="9">
         <v>100</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="J19" s="9">
         <v>50479</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="L19" s="9">
         <v>24600</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11784,25 +11796,25 @@
         <v>10</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="H20" s="9">
         <v>64</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="J20" s="9">
         <v>23464</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="L20" s="9">
         <v>9835</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11813,7 +11825,7 @@
         <v>103</v>
       </c>
       <c r="C21" s="9">
-        <v>130758</v>
+        <v>130759</v>
       </c>
       <c r="D21" s="9">
         <v>15314</v>
@@ -11825,25 +11837,25 @@
         <v>47</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="H21" s="9">
         <v>91</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="J21" s="9">
         <v>2743</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="L21" s="9">
         <v>1017</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11866,25 +11878,25 @@
         <v>28</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="H22" s="9">
         <v>12</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="J22" s="9">
         <v>5422</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="L22" s="9">
         <v>2077</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11907,25 +11919,25 @@
         <v>1541</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="H23" s="12">
         <v>4807</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="J23" s="12">
         <v>959437</v>
       </c>
       <c r="K23" s="13" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="L23" s="12">
         <v>427144</v>
       </c>
       <c r="M23" s="13" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
@@ -11947,10 +11959,10 @@
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="C26" s="16"/>
       <c r="D26" s="16"/>
@@ -11966,10 +11978,10 @@
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
@@ -11985,10 +11997,10 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="16"/>
@@ -12004,10 +12016,10 @@
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C29" s="16"/>
       <c r="D29" s="16"/>

--- a/data/Export_Progres_Pendataan_Kabupaten_Kota.xlsx
+++ b/data/Export_Progres_Pendataan_Kabupaten_Kota.xlsx
@@ -18,12 +18,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="678">
   <si>
     <t>PROGRES PENDATAAN - PROGRES PENDATAAN</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 21 Agu 2026, 18.01 | Dicetak: 21 Agu 2026, 21.55</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 22 Agu 2026, 06.01 | Dicetak: 22 Agu 2026, 06.43</t>
   </si>
   <si>
     <t>Kode</t>
@@ -122,10 +122,10 @@
     <t>LAMPUNG</t>
   </si>
   <si>
-    <t>112,54</t>
-  </si>
-  <si>
-    <t>68,41</t>
+    <t>113,22</t>
+  </si>
+  <si>
+    <t>68,85</t>
   </si>
   <si>
     <t>4,36</t>
@@ -137,10 +137,10 @@
     <t>LAMPUNG BARAT</t>
   </si>
   <si>
-    <t>125,45</t>
-  </si>
-  <si>
-    <t>85,36</t>
+    <t>125,66</t>
+  </si>
+  <si>
+    <t>85,53</t>
   </si>
   <si>
     <t>1,78</t>
@@ -152,10 +152,10 @@
     <t>TANGGAMUS</t>
   </si>
   <si>
-    <t>111,76</t>
-  </si>
-  <si>
-    <t>70,66</t>
+    <t>112,44</t>
+  </si>
+  <si>
+    <t>71,09</t>
   </si>
   <si>
     <t>6,43</t>
@@ -167,1854 +167,1848 @@
     <t>LAMPUNG SELATAN</t>
   </si>
   <si>
-    <t>110,32</t>
+    <t>111,34</t>
+  </si>
+  <si>
+    <t>63,89</t>
+  </si>
+  <si>
+    <t>5,83</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>LAMPUNG TIMUR</t>
+  </si>
+  <si>
+    <t>108,23</t>
+  </si>
+  <si>
+    <t>66,97</t>
+  </si>
+  <si>
+    <t>3,87</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>LAMPUNG TENGAH</t>
+  </si>
+  <si>
+    <t>109,47</t>
+  </si>
+  <si>
+    <t>67,71</t>
+  </si>
+  <si>
+    <t>4,57</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>LAMPUNG UTARA</t>
+  </si>
+  <si>
+    <t>116,18</t>
+  </si>
+  <si>
+    <t>66,85</t>
+  </si>
+  <si>
+    <t>2,01</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>WAY KANAN</t>
+  </si>
+  <si>
+    <t>115,04</t>
+  </si>
+  <si>
+    <t>69,67</t>
+  </si>
+  <si>
+    <t>4,5</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG</t>
+  </si>
+  <si>
+    <t>116,27</t>
+  </si>
+  <si>
+    <t>70,1</t>
+  </si>
+  <si>
+    <t>5,3</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>PESAWARAN</t>
+  </si>
+  <si>
+    <t>124,36</t>
+  </si>
+  <si>
+    <t>84,45</t>
+  </si>
+  <si>
+    <t>3,01</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>PRINGSEWU</t>
+  </si>
+  <si>
+    <t>113,59</t>
+  </si>
+  <si>
+    <t>80,62</t>
+  </si>
+  <si>
+    <t>5,65</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>MESUJI</t>
+  </si>
+  <si>
+    <t>132,9</t>
+  </si>
+  <si>
+    <t>87,12</t>
+  </si>
+  <si>
+    <t>0,05</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG BARAT</t>
+  </si>
+  <si>
+    <t>129,27</t>
+  </si>
+  <si>
+    <t>87,49</t>
+  </si>
+  <si>
+    <t>0,86</t>
+  </si>
+  <si>
+    <t>1813</t>
+  </si>
+  <si>
+    <t>PESISIR BARAT</t>
+  </si>
+  <si>
+    <t>130,54</t>
+  </si>
+  <si>
+    <t>94,57</t>
+  </si>
+  <si>
+    <t>0,63</t>
+  </si>
+  <si>
+    <t>1871</t>
+  </si>
+  <si>
+    <t>BANDAR LAMPUNG</t>
+  </si>
+  <si>
+    <t>105,6</t>
+  </si>
+  <si>
+    <t>50,8</t>
+  </si>
+  <si>
+    <t>1872</t>
+  </si>
+  <si>
+    <t>METRO</t>
+  </si>
+  <si>
+    <t>109,08</t>
+  </si>
+  <si>
+    <t>66,87</t>
+  </si>
+  <si>
+    <t>6,2</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Catatan</t>
+  </si>
+  <si>
+    <t>Jumlah prelist terkini pada FASIH bersifat dinamis menyesuaikan perpindahan wilayah assignment.</t>
+  </si>
+  <si>
+    <t>Jumlah hasil verifikasi lapangan assignment usaha dan keluarga yang tidak berstatus open atau draft, mencakup seluruh status keberadaan (ditemukan, tutup, ganda, tidak ditemukan, baru, dan lainnya).</t>
+  </si>
+  <si>
+    <t>Responden Didata (Usaha &amp; Keluarga Ditemukan/Baru/Force Submit)</t>
+  </si>
+  <si>
+    <t>Jumlah responden usaha BKU dan keluarga yang telah berhasil didata (selain status open/draft) dengan kriteria keberadaan ditemukan dan baru termasuk usaha BKU yang diklaim sebagai usaha keluarga (force submit).</t>
+  </si>
+  <si>
+    <t>*Jumlah Responden Sedang Didata</t>
+  </si>
+  <si>
+    <t>Jumlah responden dengan status Draft. Angka dapat berbeda dari hasil pengurangan indikator lain karena perbedaan waktu pemrosesan data.</t>
+  </si>
+  <si>
+    <t>*Jumlah Prelist Belum Didata</t>
+  </si>
+  <si>
+    <t>Jumlah prelist dengan status Open. Angka dapat berbeda dari hasil pengurangan indikator lain karena perbedaan waktu pemrosesan data.</t>
+  </si>
+  <si>
+    <t>PROGRES PENDATAAN - USAHA/PERUSAHAAN</t>
+  </si>
+  <si>
+    <t>Jumlah Prelist Usaha</t>
+  </si>
+  <si>
+    <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA</t>
+  </si>
+  <si>
+    <t>Total Usaha BKU (UM+UMK)</t>
+  </si>
+  <si>
+    <t>Persentase Total Usaha BKU (UM+UMK)</t>
+  </si>
+  <si>
+    <t>UMKM</t>
+  </si>
+  <si>
+    <t>Ditemukan/Pindah Dapat Ditelusuri</t>
+  </si>
+  <si>
+    <t>Persentase Ditemukan/Pindah Dapat Ditelusuri</t>
+  </si>
+  <si>
+    <t>Ditemukan Tetapi Bukan Cakupan Survei</t>
+  </si>
+  <si>
+    <t>Persentase Ditemukan Tetapi Bukan Cakupan Survei</t>
+  </si>
+  <si>
+    <t>Pindah Tidak Dapat Ditelusuri</t>
+  </si>
+  <si>
+    <t>Persentase Pindah Tidak Dapat Ditelusuri</t>
+  </si>
+  <si>
+    <t>Tutup</t>
+  </si>
+  <si>
+    <t>Persentase Tutup</t>
+  </si>
+  <si>
+    <t>Duplikat</t>
+  </si>
+  <si>
+    <t>Persentase Duplikat</t>
+  </si>
+  <si>
+    <t>Tidak Ditemukan</t>
+  </si>
+  <si>
+    <t>Persentase Tidak Ditemukan</t>
+  </si>
+  <si>
+    <t>Data Diperoleh dari Kantor Pusat</t>
+  </si>
+  <si>
+    <t>Persentase Data Diperoleh dari Kantor Pusat</t>
+  </si>
+  <si>
+    <t>Nonrespon</t>
+  </si>
+  <si>
+    <t>Persentase Nonrespon</t>
+  </si>
+  <si>
+    <t>Total UB</t>
+  </si>
+  <si>
+    <t>Persentase Total UB</t>
+  </si>
+  <si>
+    <t>Ditemukan</t>
+  </si>
+  <si>
+    <t>Persentase Ditemukan</t>
+  </si>
+  <si>
+    <t>Tutup​</t>
+  </si>
+  <si>
+    <t>Persentase Tutup​</t>
+  </si>
+  <si>
+    <t>Ganda</t>
+  </si>
+  <si>
+    <t>Persentase Ganda</t>
+  </si>
+  <si>
+    <t>Tidak Ditemukan​</t>
+  </si>
+  <si>
+    <t>Persentase Tidak Ditemukan​</t>
+  </si>
+  <si>
+    <t>Persentase Baru</t>
+  </si>
+  <si>
+    <t>Data Diperoleh dari Kantor Pusat​</t>
+  </si>
+  <si>
+    <t>Persentase Data Diperoleh dari Kantor Pusat​</t>
+  </si>
+  <si>
+    <t>Nonrespon​</t>
+  </si>
+  <si>
+    <t>Persentase Nonrespon​</t>
+  </si>
+  <si>
+    <t>Force Submit (Diklaim Sebagai Usaha Keluarga)</t>
+  </si>
+  <si>
+    <t>Persentase Force Submit (Diklaim Sebagai Usaha Keluarga)</t>
+  </si>
+  <si>
+    <t>Total UMKM</t>
+  </si>
+  <si>
+    <t>Persentase Total UMKM</t>
+  </si>
+  <si>
+    <t>(15)</t>
+  </si>
+  <si>
+    <t>(16)</t>
+  </si>
+  <si>
+    <t>(17)</t>
+  </si>
+  <si>
+    <t>(18)</t>
+  </si>
+  <si>
+    <t>(19)</t>
+  </si>
+  <si>
+    <t>(20)</t>
+  </si>
+  <si>
+    <t>(21)</t>
+  </si>
+  <si>
+    <t>(22)</t>
+  </si>
+  <si>
+    <t>(23)</t>
+  </si>
+  <si>
+    <t>(24)</t>
+  </si>
+  <si>
+    <t>(25)</t>
+  </si>
+  <si>
+    <t>(26)</t>
+  </si>
+  <si>
+    <t>(27)</t>
+  </si>
+  <si>
+    <t>(28)</t>
+  </si>
+  <si>
+    <t>(29)</t>
+  </si>
+  <si>
+    <t>(30)</t>
+  </si>
+  <si>
+    <t>(31)</t>
+  </si>
+  <si>
+    <t>(32)</t>
+  </si>
+  <si>
+    <t>(33)</t>
+  </si>
+  <si>
+    <t>(34)</t>
+  </si>
+  <si>
+    <t>(35)</t>
+  </si>
+  <si>
+    <t>(36)</t>
+  </si>
+  <si>
+    <t>(37)</t>
+  </si>
+  <si>
+    <t>(38)</t>
+  </si>
+  <si>
+    <t>(39)</t>
+  </si>
+  <si>
+    <t>(40)</t>
+  </si>
+  <si>
+    <t>(41)</t>
+  </si>
+  <si>
+    <t>0,15</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>0,01</t>
+  </si>
+  <si>
+    <t>0,02</t>
+  </si>
+  <si>
+    <t>11,9</t>
+  </si>
+  <si>
+    <t>17,96</t>
+  </si>
+  <si>
+    <t>8,11</t>
+  </si>
+  <si>
+    <t>43,77</t>
+  </si>
+  <si>
+    <t>15,99</t>
+  </si>
+  <si>
+    <t>6,53</t>
+  </si>
+  <si>
+    <t>27,89</t>
+  </si>
+  <si>
+    <t>28,04</t>
+  </si>
+  <si>
+    <t>0,2</t>
+  </si>
+  <si>
+    <t>0,03</t>
+  </si>
+  <si>
+    <t>17,16</t>
+  </si>
+  <si>
+    <t>17,05</t>
+  </si>
+  <si>
+    <t>12,8</t>
+  </si>
+  <si>
+    <t>41,55</t>
+  </si>
+  <si>
+    <t>1,53</t>
+  </si>
+  <si>
+    <t>35,12</t>
+  </si>
+  <si>
+    <t>35,32</t>
+  </si>
+  <si>
+    <t>0,1</t>
+  </si>
+  <si>
+    <t>9,04</t>
+  </si>
+  <si>
+    <t>22,58</t>
+  </si>
+  <si>
+    <t>15,75</t>
+  </si>
+  <si>
+    <t>27,36</t>
+  </si>
+  <si>
+    <t>10,3</t>
+  </si>
+  <si>
+    <t>10,51</t>
+  </si>
+  <si>
+    <t>19,33</t>
+  </si>
+  <si>
+    <t>19,44</t>
+  </si>
+  <si>
+    <t>0,14</t>
+  </si>
+  <si>
+    <t>6,29</t>
+  </si>
+  <si>
+    <t>12,07</t>
+  </si>
+  <si>
+    <t>4,33</t>
+  </si>
+  <si>
+    <t>62,92</t>
+  </si>
+  <si>
+    <t>15,07</t>
+  </si>
+  <si>
+    <t>3,1</t>
+  </si>
+  <si>
+    <t>21,36</t>
+  </si>
+  <si>
+    <t>21,5</t>
+  </si>
+  <si>
+    <t>0,06</t>
+  </si>
+  <si>
+    <t>11,81</t>
+  </si>
+  <si>
+    <t>22,64</t>
+  </si>
+  <si>
+    <t>7,86</t>
+  </si>
+  <si>
+    <t>33,74</t>
+  </si>
+  <si>
+    <t>13,09</t>
+  </si>
+  <si>
+    <t>11,48</t>
+  </si>
+  <si>
+    <t>24,9</t>
+  </si>
+  <si>
+    <t>24,96</t>
+  </si>
+  <si>
+    <t>11,09</t>
+  </si>
+  <si>
+    <t>19,98</t>
+  </si>
+  <si>
+    <t>9,69</t>
+  </si>
+  <si>
+    <t>44,41</t>
+  </si>
+  <si>
+    <t>17,37</t>
+  </si>
+  <si>
+    <t>6,22</t>
+  </si>
+  <si>
+    <t>28,46</t>
+  </si>
+  <si>
+    <t>28,55</t>
+  </si>
+  <si>
+    <t>0,08</t>
+  </si>
+  <si>
+    <t>7,66</t>
+  </si>
+  <si>
+    <t>15,85</t>
+  </si>
+  <si>
+    <t>5,49</t>
+  </si>
+  <si>
+    <t>58,85</t>
+  </si>
+  <si>
+    <t>12,37</t>
+  </si>
+  <si>
+    <t>7,7</t>
+  </si>
+  <si>
+    <t>20,02</t>
+  </si>
+  <si>
+    <t>20,1</t>
+  </si>
+  <si>
+    <t>0,09</t>
+  </si>
+  <si>
+    <t>6,21</t>
+  </si>
+  <si>
+    <t>22,56</t>
+  </si>
+  <si>
+    <t>6,49</t>
+  </si>
+  <si>
+    <t>45,01</t>
+  </si>
+  <si>
+    <t>14,91</t>
+  </si>
+  <si>
+    <t>9,92</t>
+  </si>
+  <si>
+    <t>21,12</t>
+  </si>
+  <si>
+    <t>21,21</t>
+  </si>
+  <si>
+    <t>0,25</t>
+  </si>
+  <si>
+    <t>21,43</t>
+  </si>
+  <si>
+    <t>12,86</t>
+  </si>
+  <si>
+    <t>4,88</t>
+  </si>
+  <si>
+    <t>41,97</t>
+  </si>
+  <si>
+    <t>26,28</t>
+  </si>
+  <si>
+    <t>0,99</t>
+  </si>
+  <si>
+    <t>47,71</t>
+  </si>
+  <si>
+    <t>47,96</t>
+  </si>
+  <si>
+    <t>0,26</t>
+  </si>
+  <si>
+    <t>31,44</t>
+  </si>
+  <si>
+    <t>14,88</t>
+  </si>
+  <si>
+    <t>35,66</t>
+  </si>
+  <si>
+    <t>33,86</t>
+  </si>
+  <si>
+    <t>2,06</t>
+  </si>
+  <si>
+    <t>65,3</t>
+  </si>
+  <si>
+    <t>65,56</t>
+  </si>
+  <si>
+    <t>36,6</t>
+  </si>
+  <si>
+    <t>13,79</t>
+  </si>
+  <si>
+    <t>3,51</t>
+  </si>
+  <si>
+    <t>29,73</t>
+  </si>
+  <si>
+    <t>28,2</t>
+  </si>
+  <si>
+    <t>1,66</t>
+  </si>
+  <si>
+    <t>64,81</t>
+  </si>
+  <si>
+    <t>64,95</t>
+  </si>
+  <si>
+    <t>0,24</t>
+  </si>
+  <si>
+    <t>28,24</t>
+  </si>
+  <si>
+    <t>19,28</t>
+  </si>
+  <si>
+    <t>12,12</t>
+  </si>
+  <si>
+    <t>27,98</t>
+  </si>
+  <si>
+    <t>34,85</t>
+  </si>
+  <si>
+    <t>0,89</t>
+  </si>
+  <si>
+    <t>63,09</t>
+  </si>
+  <si>
+    <t>63,33</t>
+  </si>
+  <si>
+    <t>0,23</t>
+  </si>
+  <si>
+    <t>45,74</t>
+  </si>
+  <si>
+    <t>19,91</t>
+  </si>
+  <si>
+    <t>5,04</t>
+  </si>
+  <si>
+    <t>19,08</t>
+  </si>
+  <si>
+    <t>46,02</t>
+  </si>
+  <si>
+    <t>1,76</t>
+  </si>
+  <si>
+    <t>91,75</t>
+  </si>
+  <si>
+    <t>91,99</t>
+  </si>
+  <si>
+    <t>0,17</t>
+  </si>
+  <si>
+    <t>22,7</t>
+  </si>
+  <si>
+    <t>17,29</t>
+  </si>
+  <si>
+    <t>7,51</t>
+  </si>
+  <si>
+    <t>39,16</t>
+  </si>
+  <si>
+    <t>32,9</t>
+  </si>
+  <si>
+    <t>1,19</t>
+  </si>
+  <si>
+    <t>55,59</t>
+  </si>
+  <si>
+    <t>55,76</t>
+  </si>
+  <si>
+    <t>0,32</t>
+  </si>
+  <si>
+    <t>0,04</t>
+  </si>
+  <si>
+    <t>7,26</t>
+  </si>
+  <si>
+    <t>14,67</t>
+  </si>
+  <si>
+    <t>7,62</t>
+  </si>
+  <si>
+    <t>48,98</t>
+  </si>
+  <si>
+    <t>11,38</t>
+  </si>
+  <si>
+    <t>5,52</t>
+  </si>
+  <si>
+    <t>18,63</t>
+  </si>
+  <si>
+    <t>18,96</t>
+  </si>
+  <si>
+    <t>23,17</t>
+  </si>
+  <si>
+    <t>19,69</t>
+  </si>
+  <si>
+    <t>18,73</t>
+  </si>
+  <si>
+    <t>20,96</t>
+  </si>
+  <si>
+    <t>19,67</t>
+  </si>
+  <si>
+    <t>1,67</t>
+  </si>
+  <si>
+    <t>42,84</t>
+  </si>
+  <si>
+    <t>43,1</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha BKU</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha yang Ditemukan dan Baru (UB + UMKM)</t>
+  </si>
+  <si>
+    <t>Persentase Kolom 4 21</t>
+  </si>
+  <si>
+    <t>Persentase hasil bagi jumlah usaha pada kolom tersebut dengan jumlah prelist usaha (kolom 3).</t>
+  </si>
+  <si>
+    <t>PROGRES PENDATAAN - SKALA USAHA</t>
+  </si>
+  <si>
+    <t>JUMLAH PRELIST</t>
+  </si>
+  <si>
+    <t>JUMLAH USAHA BKU MENURUT STATUS SKALA USAHA (UB, UM, UMK)</t>
+  </si>
+  <si>
+    <t>UB​</t>
+  </si>
+  <si>
+    <t>Persentase UB​</t>
+  </si>
+  <si>
+    <t>UM​</t>
+  </si>
+  <si>
+    <t>Persentase UM​</t>
+  </si>
+  <si>
+    <t>UMK​</t>
+  </si>
+  <si>
+    <t>Persentase UMK​</t>
+  </si>
+  <si>
+    <t>Tidak Dapat Diklasifikasikan</t>
+  </si>
+  <si>
+    <t>Total Usaha BKU</t>
+  </si>
+  <si>
+    <t>Persentase Total Usaha BKU</t>
+  </si>
+  <si>
+    <t>86,79</t>
+  </si>
+  <si>
+    <t>14,41</t>
+  </si>
+  <si>
+    <t>27,93</t>
+  </si>
+  <si>
+    <t>130,43</t>
+  </si>
+  <si>
+    <t>37,75</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>58,77</t>
+  </si>
+  <si>
+    <t>19,48</t>
+  </si>
+  <si>
+    <t>19,24</t>
+  </si>
+  <si>
+    <t>108,97</t>
+  </si>
+  <si>
+    <t>126,58</t>
+  </si>
+  <si>
+    <t>22,16</t>
+  </si>
+  <si>
+    <t>24,76</t>
+  </si>
+  <si>
+    <t>107,91</t>
+  </si>
+  <si>
+    <t>17,68</t>
+  </si>
+  <si>
+    <t>28,4</t>
+  </si>
+  <si>
+    <t>86,67</t>
+  </si>
+  <si>
+    <t>18,81</t>
+  </si>
+  <si>
+    <t>19,96</t>
+  </si>
+  <si>
+    <t>134,29</t>
+  </si>
+  <si>
+    <t>13,95</t>
+  </si>
+  <si>
+    <t>20,99</t>
+  </si>
+  <si>
+    <t>113,73</t>
+  </si>
+  <si>
+    <t>7,2</t>
+  </si>
+  <si>
+    <t>48,48</t>
+  </si>
+  <si>
+    <t>47,95</t>
+  </si>
+  <si>
+    <t>98,18</t>
+  </si>
+  <si>
+    <t>39,39</t>
+  </si>
+  <si>
+    <t>65,41</t>
+  </si>
+  <si>
+    <t>131,25</t>
+  </si>
+  <si>
+    <t>155,56</t>
+  </si>
+  <si>
+    <t>64,44</t>
+  </si>
+  <si>
+    <t>64,94</t>
+  </si>
+  <si>
+    <t>114,81</t>
+  </si>
+  <si>
+    <t>36,84</t>
   </si>
   <si>
     <t>63,23</t>
   </si>
   <si>
-    <t>5,83</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>LAMPUNG TIMUR</t>
-  </si>
-  <si>
-    <t>107,64</t>
-  </si>
-  <si>
-    <t>66,59</t>
-  </si>
-  <si>
-    <t>3,87</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>LAMPUNG TENGAH</t>
-  </si>
-  <si>
-    <t>108,77</t>
+    <t>113,04</t>
+  </si>
+  <si>
+    <t>51,52</t>
+  </si>
+  <si>
+    <t>92,05</t>
+  </si>
+  <si>
+    <t>91,98</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>55,61</t>
+  </si>
+  <si>
+    <t>64,9</t>
+  </si>
+  <si>
+    <t>9,8</t>
+  </si>
+  <si>
+    <t>18,86</t>
+  </si>
+  <si>
+    <t>117,5</t>
+  </si>
+  <si>
+    <t>45,83</t>
+  </si>
+  <si>
+    <t>42,64</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha (UB/UM/UMK)</t>
+  </si>
+  <si>
+    <t>Jumlah prelist usaha yang berhasil didata (keberadaan ditemukan, baru, pindah dapat ditelusuri) berdasarkan skala usaha, untuk usaha baru didekati dengan omzet sebagai berikut: UB (lebih dari 50 Milyar), UM (15-50 Milyar), UMK - Kecil (2-15 Milyar), UMK - Mikro (0-2 Milyar).</t>
+  </si>
+  <si>
+    <t>Tidak Dapat Diklasifikasikan (Kolom 10)</t>
+  </si>
+  <si>
+    <t>Usaha baru dengan nilai omzet/pendapatan kosong sehingga tidak dapat diklasifikasikan skala usahanya, misalnya usaha unit pembantu/penunjang.</t>
+  </si>
+  <si>
+    <t>Persentase Jumlah UB</t>
+  </si>
+  <si>
+    <t>Persentase hasil bagi jumlah UB yang berhasil didata dengan jumlah prelist UB (kolom 3).</t>
+  </si>
+  <si>
+    <t>Persentase Jumlah UM</t>
+  </si>
+  <si>
+    <t>Persentase hasil bagi jumlah UM yang berhasil didata dengan jumlah prelist UM (kolom 4).</t>
+  </si>
+  <si>
+    <t>Persentase Jumlah UMK</t>
+  </si>
+  <si>
+    <t>Persentase hasil bagi jumlah UMK yang berhasil didata dengan jumlah prelist UMK (kolom 5).</t>
+  </si>
+  <si>
+    <t>PROGRES PENDATAAN - USAHA KELUARGA</t>
+  </si>
+  <si>
+    <t>Jumlah Prelist Usaha Keluarga (ST2023 + UMKM)</t>
+  </si>
+  <si>
+    <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha dalam Keluarga (Ditemukan + Baru)</t>
+  </si>
+  <si>
+    <t>Persentase Usaha dalam Keluarga (Ditemukan + Baru)</t>
+  </si>
+  <si>
+    <t>48,93</t>
+  </si>
+  <si>
+    <t>24,28</t>
+  </si>
+  <si>
+    <t>0,4</t>
+  </si>
+  <si>
+    <t>9,53</t>
+  </si>
+  <si>
+    <t>34,19</t>
+  </si>
+  <si>
+    <t>83,13</t>
+  </si>
+  <si>
+    <t>58,36</t>
+  </si>
+  <si>
+    <t>20,2</t>
+  </si>
+  <si>
+    <t>0,52</t>
+  </si>
+  <si>
+    <t>8,77</t>
+  </si>
+  <si>
+    <t>29,86</t>
+  </si>
+  <si>
+    <t>88,22</t>
+  </si>
+  <si>
+    <t>45,52</t>
+  </si>
+  <si>
+    <t>25,2</t>
+  </si>
+  <si>
+    <t>0,46</t>
+  </si>
+  <si>
+    <t>7,94</t>
+  </si>
+  <si>
+    <t>34,58</t>
+  </si>
+  <si>
+    <t>80,1</t>
+  </si>
+  <si>
+    <t>37,82</t>
+  </si>
+  <si>
+    <t>23,54</t>
+  </si>
+  <si>
+    <t>0,19</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>32,12</t>
+  </si>
+  <si>
+    <t>69,94</t>
+  </si>
+  <si>
+    <t>50,46</t>
+  </si>
+  <si>
+    <t>22,97</t>
+  </si>
+  <si>
+    <t>8,34</t>
+  </si>
+  <si>
+    <t>36,68</t>
+  </si>
+  <si>
+    <t>87,13</t>
+  </si>
+  <si>
+    <t>50,71</t>
+  </si>
+  <si>
+    <t>22,28</t>
+  </si>
+  <si>
+    <t>10,61</t>
+  </si>
+  <si>
+    <t>32,87</t>
+  </si>
+  <si>
+    <t>83,57</t>
+  </si>
+  <si>
+    <t>48,75</t>
+  </si>
+  <si>
+    <t>20,26</t>
+  </si>
+  <si>
+    <t>0,22</t>
+  </si>
+  <si>
+    <t>17,38</t>
+  </si>
+  <si>
+    <t>38,22</t>
+  </si>
+  <si>
+    <t>86,98</t>
+  </si>
+  <si>
+    <t>48,47</t>
+  </si>
+  <si>
+    <t>22,73</t>
+  </si>
+  <si>
+    <t>8,43</t>
+  </si>
+  <si>
+    <t>38,77</t>
+  </si>
+  <si>
+    <t>87,24</t>
+  </si>
+  <si>
+    <t>44,43</t>
+  </si>
+  <si>
+    <t>27,01</t>
+  </si>
+  <si>
+    <t>0,51</t>
+  </si>
+  <si>
+    <t>4,89</t>
+  </si>
+  <si>
+    <t>27,9</t>
+  </si>
+  <si>
+    <t>72,33</t>
+  </si>
+  <si>
+    <t>52,84</t>
+  </si>
+  <si>
+    <t>0,74</t>
+  </si>
+  <si>
+    <t>6,87</t>
+  </si>
+  <si>
+    <t>23,48</t>
+  </si>
+  <si>
+    <t>76,32</t>
+  </si>
+  <si>
+    <t>48,3</t>
+  </si>
+  <si>
+    <t>29,85</t>
+  </si>
+  <si>
+    <t>0,6</t>
+  </si>
+  <si>
+    <t>6,02</t>
+  </si>
+  <si>
+    <t>27,3</t>
+  </si>
+  <si>
+    <t>75,6</t>
+  </si>
+  <si>
+    <t>47,06</t>
+  </si>
+  <si>
+    <t>30,05</t>
+  </si>
+  <si>
+    <t>0,71</t>
+  </si>
+  <si>
+    <t>12,1</t>
+  </si>
+  <si>
+    <t>28,06</t>
+  </si>
+  <si>
+    <t>75,12</t>
+  </si>
+  <si>
+    <t>57,82</t>
+  </si>
+  <si>
+    <t>24,26</t>
+  </si>
+  <si>
+    <t>0,57</t>
+  </si>
+  <si>
+    <t>7,63</t>
+  </si>
+  <si>
+    <t>32,33</t>
+  </si>
+  <si>
+    <t>90,15</t>
+  </si>
+  <si>
+    <t>54,43</t>
+  </si>
+  <si>
+    <t>29,36</t>
+  </si>
+  <si>
+    <t>0,44</t>
+  </si>
+  <si>
+    <t>4,85</t>
+  </si>
+  <si>
+    <t>26,69</t>
+  </si>
+  <si>
+    <t>81,12</t>
+  </si>
+  <si>
+    <t>23,77</t>
+  </si>
+  <si>
+    <t>30,08</t>
+  </si>
+  <si>
+    <t>0,84</t>
+  </si>
+  <si>
+    <t>14,68</t>
+  </si>
+  <si>
+    <t>318,91</t>
+  </si>
+  <si>
+    <t>342,69</t>
+  </si>
+  <si>
+    <t>46,08</t>
+  </si>
+  <si>
+    <t>28,31</t>
+  </si>
+  <si>
+    <t>2,42</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>83,08</t>
+  </si>
+  <si>
+    <t>Persentase Kolom 4 9</t>
+  </si>
+  <si>
+    <t>PROGRES PENDATAAN - KESELURUHAN USAHA</t>
+  </si>
+  <si>
+    <t>Total Prelist Usaha dan Usaha Keluarga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USAHA BKU </t>
+  </si>
+  <si>
+    <t>USAHA DALAM KELUARGA</t>
+  </si>
+  <si>
+    <t>Total Usaha</t>
+  </si>
+  <si>
+    <t>Persentase Total Usaha</t>
+  </si>
+  <si>
+    <t>Subtotal</t>
+  </si>
+  <si>
+    <t>Persentase Subtotal</t>
+  </si>
+  <si>
+    <t>Ditemukan​</t>
+  </si>
+  <si>
+    <t>Persentase Ditemukan​</t>
+  </si>
+  <si>
+    <t>Baru​</t>
+  </si>
+  <si>
+    <t>Persentase Baru​</t>
+  </si>
+  <si>
+    <t>Subtotal​</t>
+  </si>
+  <si>
+    <t>Persentase Subtotal​</t>
+  </si>
+  <si>
+    <t>12,05</t>
+  </si>
+  <si>
+    <t>68,75</t>
+  </si>
+  <si>
+    <t>17,36</t>
+  </si>
+  <si>
+    <t>82,75</t>
+  </si>
+  <si>
+    <t>9,14</t>
+  </si>
+  <si>
+    <t>54,61</t>
+  </si>
+  <si>
+    <t>11,87</t>
+  </si>
+  <si>
+    <t>70,47</t>
+  </si>
+  <si>
+    <t>11,18</t>
+  </si>
+  <si>
+    <t>70,39</t>
+  </si>
+  <si>
+    <t>7,74</t>
+  </si>
+  <si>
+    <t>64,74</t>
+  </si>
+  <si>
+    <t>6,3</t>
+  </si>
+  <si>
+    <t>71,19</t>
+  </si>
+  <si>
+    <t>21,68</t>
+  </si>
+  <si>
+    <t>68,78</t>
+  </si>
+  <si>
+    <t>31,71</t>
+  </si>
+  <si>
+    <t>75,18</t>
+  </si>
+  <si>
+    <t>36,74</t>
+  </si>
+  <si>
+    <t>73,92</t>
+  </si>
+  <si>
+    <t>28,48</t>
+  </si>
+  <si>
+    <t>73,7</t>
+  </si>
+  <si>
+    <t>45,97</t>
+  </si>
+  <si>
+    <t>90,32</t>
+  </si>
+  <si>
+    <t>22,86</t>
+  </si>
+  <si>
+    <t>78,71</t>
+  </si>
+  <si>
+    <t>7,58</t>
+  </si>
+  <si>
+    <t>47,31</t>
+  </si>
+  <si>
+    <t>23,42</t>
+  </si>
+  <si>
+    <t>66,42</t>
+  </si>
+  <si>
+    <t>Total Prelist Usaha Dan Usaha Keluarga</t>
+  </si>
+  <si>
+    <t>Jumlah Prelist Usaha Ditambah Jumlah Prelist Usaha Keluarga (ST2023 + UMKM) atau Kolom (3) + (4).</t>
+  </si>
+  <si>
+    <t>Persentase Usaha BKU Ditemukan</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha BKU Ditemukan/Pindah Dapat Ditelusuri (CAPI dan CAWI) dibagi dengan Jumlah Prelist Usaha (kolom 3).</t>
+  </si>
+  <si>
+    <t>Persentase Usaha BKU Baru</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha BKU Baru (CAPI) dibagi Jumlah Prelist Usaha (kolom 3).</t>
+  </si>
+  <si>
+    <t>Persentase Usaha Keluarga Ditemukan</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha Keluarga Ditemukan dibagi dengan Jumlah Prelist Usaha Keluarga (ST2023 + UMKM) atau Kolom (4).</t>
+  </si>
+  <si>
+    <t>Persentase Usaha Keluarga Baru</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha Keluarga Baru dibagi dengan Jumlah Prelist Usaha Keluarga (ST2023 + UMKM) atau Kolom (4).</t>
+  </si>
+  <si>
+    <t>PROGRES PENDATAAN - PROPORSI USAHA</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha (Semua Status Keberadaan Usaha)</t>
+  </si>
+  <si>
+    <t>Persentase Usaha BKU</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha dalam Keluarga</t>
+  </si>
+  <si>
+    <t>Persentase Usaha dalam Keluarga</t>
+  </si>
+  <si>
+    <t>6,52</t>
+  </si>
+  <si>
+    <t>54,72</t>
+  </si>
+  <si>
+    <t>3,13</t>
+  </si>
+  <si>
+    <t>67,85</t>
+  </si>
+  <si>
+    <t>56,33</t>
+  </si>
+  <si>
+    <t>6,41</t>
+  </si>
+  <si>
+    <t>45,02</t>
+  </si>
+  <si>
+    <t>6,04</t>
+  </si>
+  <si>
+    <t>57,57</t>
+  </si>
+  <si>
+    <t>56,07</t>
+  </si>
+  <si>
+    <t>5,73</t>
+  </si>
+  <si>
+    <t>49,76</t>
+  </si>
+  <si>
+    <t>4,56</t>
+  </si>
+  <si>
+    <t>58,48</t>
+  </si>
+  <si>
+    <t>6,65</t>
+  </si>
+  <si>
+    <t>58,75</t>
+  </si>
+  <si>
+    <t>6,18</t>
+  </si>
+  <si>
+    <t>60,39</t>
+  </si>
+  <si>
+    <t>9,16</t>
+  </si>
+  <si>
+    <t>56,8</t>
+  </si>
+  <si>
+    <t>6,45</t>
+  </si>
+  <si>
+    <t>55,7</t>
+  </si>
+  <si>
+    <t>6,61</t>
+  </si>
+  <si>
+    <t>66,34</t>
+  </si>
+  <si>
+    <t>63,21</t>
+  </si>
+  <si>
+    <t>14,85</t>
+  </si>
+  <si>
+    <t>25,76</t>
+  </si>
+  <si>
+    <t>16,19</t>
+  </si>
+  <si>
+    <t>43,71</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha (Semua Status Keberadaan Usaha) Kolom 3</t>
+  </si>
+  <si>
+    <t>Jumlah seluruh usaha BKU dan Usaha Keluarga dari CAPI dan CAWI dengan semua status keberadaan.</t>
+  </si>
+  <si>
+    <t>PROGRES PENDATAAN - JARINGAN USAHA</t>
+  </si>
+  <si>
+    <t>JUMLAH USAHA BERDASARKAN JARINGAN USAHA</t>
+  </si>
+  <si>
+    <t>Tunggal</t>
+  </si>
+  <si>
+    <t>Kantor Pusat</t>
+  </si>
+  <si>
+    <t>Cabang</t>
+  </si>
+  <si>
+    <t>Perwakilan</t>
+  </si>
+  <si>
+    <t>Pabrik</t>
+  </si>
+  <si>
+    <t>Unit Pembantu</t>
+  </si>
+  <si>
+    <t>PROGRES PENDATAAN - PROPORSI PERTANIAN</t>
+  </si>
+  <si>
+    <t>Jumlah Prelist Usaha SE2026</t>
+  </si>
+  <si>
+    <t>Target Berdasarkan Data ST</t>
+  </si>
+  <si>
+    <t>Jumlah UTP Subsektor Prelist</t>
+  </si>
+  <si>
+    <t>USAHA PERTANIAN BKU</t>
+  </si>
+  <si>
+    <t>USAHA PERTANIAN DALAM KELUARGA</t>
+  </si>
+  <si>
+    <t>24,23</t>
+  </si>
+  <si>
+    <t>75,77</t>
+  </si>
+  <si>
+    <t>69,26</t>
+  </si>
+  <si>
+    <t>30,74</t>
+  </si>
+  <si>
+    <t>13,51</t>
+  </si>
+  <si>
+    <t>86,49</t>
+  </si>
+  <si>
+    <t>68,83</t>
+  </si>
+  <si>
+    <t>31,17</t>
+  </si>
+  <si>
+    <t>25,05</t>
+  </si>
+  <si>
+    <t>74,95</t>
+  </si>
+  <si>
+    <t>69,36</t>
+  </si>
+  <si>
+    <t>30,64</t>
+  </si>
+  <si>
+    <t>15,58</t>
+  </si>
+  <si>
+    <t>84,42</t>
+  </si>
+  <si>
+    <t>70,72</t>
+  </si>
+  <si>
+    <t>29,28</t>
+  </si>
+  <si>
+    <t>45,7</t>
+  </si>
+  <si>
+    <t>54,3</t>
+  </si>
+  <si>
+    <t>69,32</t>
+  </si>
+  <si>
+    <t>30,68</t>
+  </si>
+  <si>
+    <t>36,85</t>
+  </si>
+  <si>
+    <t>63,15</t>
+  </si>
+  <si>
+    <t>70,13</t>
+  </si>
+  <si>
+    <t>29,87</t>
+  </si>
+  <si>
+    <t>37,97</t>
+  </si>
+  <si>
+    <t>62,03</t>
+  </si>
+  <si>
+    <t>68,35</t>
+  </si>
+  <si>
+    <t>31,65</t>
+  </si>
+  <si>
+    <t>15,17</t>
+  </si>
+  <si>
+    <t>84,83</t>
+  </si>
+  <si>
+    <t>65,58</t>
+  </si>
+  <si>
+    <t>34,42</t>
+  </si>
+  <si>
+    <t>7,55</t>
+  </si>
+  <si>
+    <t>92,45</t>
+  </si>
+  <si>
+    <t>65,13</t>
+  </si>
+  <si>
+    <t>34,87</t>
+  </si>
+  <si>
+    <t>24,12</t>
+  </si>
+  <si>
+    <t>75,88</t>
+  </si>
+  <si>
+    <t>74,06</t>
+  </si>
+  <si>
+    <t>25,94</t>
+  </si>
+  <si>
+    <t>8,64</t>
+  </si>
+  <si>
+    <t>91,36</t>
+  </si>
+  <si>
+    <t>70,53</t>
+  </si>
+  <si>
+    <t>29,47</t>
+  </si>
+  <si>
+    <t>7,24</t>
+  </si>
+  <si>
+    <t>92,76</t>
+  </si>
+  <si>
+    <t>66,53</t>
+  </si>
+  <si>
+    <t>33,47</t>
+  </si>
+  <si>
+    <t>15,32</t>
+  </si>
+  <si>
+    <t>84,68</t>
   </si>
   <si>
     <t>67,22</t>
   </si>
   <si>
-    <t>4,57</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>LAMPUNG UTARA</t>
-  </si>
-  <si>
-    <t>115,61</t>
-  </si>
-  <si>
-    <t>66,46</t>
-  </si>
-  <si>
-    <t>2,01</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>WAY KANAN</t>
-  </si>
-  <si>
-    <t>114,12</t>
-  </si>
-  <si>
-    <t>69,04</t>
-  </si>
-  <si>
-    <t>4,5</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG</t>
-  </si>
-  <si>
-    <t>115,49</t>
-  </si>
-  <si>
-    <t>69,54</t>
-  </si>
-  <si>
-    <t>5,3</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>PESAWARAN</t>
-  </si>
-  <si>
-    <t>123,83</t>
-  </si>
-  <si>
-    <t>84,1</t>
-  </si>
-  <si>
-    <t>3,01</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>PRINGSEWU</t>
-  </si>
-  <si>
-    <t>112,73</t>
-  </si>
-  <si>
-    <t>80,04</t>
-  </si>
-  <si>
-    <t>5,65</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>MESUJI</t>
-  </si>
-  <si>
-    <t>132,85</t>
-  </si>
-  <si>
-    <t>87,08</t>
-  </si>
-  <si>
-    <t>0,05</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG BARAT</t>
-  </si>
-  <si>
-    <t>129,08</t>
-  </si>
-  <si>
-    <t>87,35</t>
-  </si>
-  <si>
-    <t>0,86</t>
-  </si>
-  <si>
-    <t>1813</t>
-  </si>
-  <si>
-    <t>PESISIR BARAT</t>
-  </si>
-  <si>
-    <t>130,29</t>
-  </si>
-  <si>
-    <t>94,34</t>
-  </si>
-  <si>
-    <t>0,63</t>
-  </si>
-  <si>
-    <t>1871</t>
-  </si>
-  <si>
-    <t>BANDAR LAMPUNG</t>
-  </si>
-  <si>
-    <t>104,91</t>
-  </si>
-  <si>
-    <t>50,47</t>
-  </si>
-  <si>
-    <t>1872</t>
-  </si>
-  <si>
-    <t>METRO</t>
-  </si>
-  <si>
-    <t>108,51</t>
-  </si>
-  <si>
-    <t>66,51</t>
-  </si>
-  <si>
-    <t>6,2</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Catatan</t>
-  </si>
-  <si>
-    <t>Jumlah prelist terkini pada FASIH bersifat dinamis menyesuaikan perpindahan wilayah assignment.</t>
-  </si>
-  <si>
-    <t>Jumlah hasil verifikasi lapangan assignment usaha dan keluarga yang tidak berstatus open atau draft, mencakup seluruh status keberadaan (ditemukan, tutup, ganda, tidak ditemukan, baru, dan lainnya).</t>
-  </si>
-  <si>
-    <t>Responden Didata (Usaha &amp; Keluarga Ditemukan/Baru/Force Submit)</t>
-  </si>
-  <si>
-    <t>Jumlah responden usaha BKU dan keluarga yang telah berhasil didata (selain status open/draft) dengan kriteria keberadaan ditemukan dan baru termasuk usaha BKU yang diklaim sebagai usaha keluarga (force submit).</t>
-  </si>
-  <si>
-    <t>*Jumlah Responden Sedang Didata</t>
-  </si>
-  <si>
-    <t>Jumlah responden dengan status Draft. Angka dapat berbeda dari hasil pengurangan indikator lain karena perbedaan waktu pemrosesan data.</t>
-  </si>
-  <si>
-    <t>*Jumlah Prelist Belum Didata</t>
-  </si>
-  <si>
-    <t>Jumlah prelist dengan status Open. Angka dapat berbeda dari hasil pengurangan indikator lain karena perbedaan waktu pemrosesan data.</t>
-  </si>
-  <si>
-    <t>PROGRES PENDATAAN - USAHA/PERUSAHAAN</t>
-  </si>
-  <si>
-    <t>Jumlah Prelist Usaha</t>
-  </si>
-  <si>
-    <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA</t>
-  </si>
-  <si>
-    <t>Total Usaha BKU (UM+UMK)</t>
-  </si>
-  <si>
-    <t>Persentase Total Usaha BKU (UM+UMK)</t>
-  </si>
-  <si>
-    <t>UMKM</t>
-  </si>
-  <si>
-    <t>Ditemukan/Pindah Dapat Ditelusuri</t>
-  </si>
-  <si>
-    <t>Persentase Ditemukan/Pindah Dapat Ditelusuri</t>
-  </si>
-  <si>
-    <t>Ditemukan Tetapi Bukan Cakupan Survei</t>
-  </si>
-  <si>
-    <t>Persentase Ditemukan Tetapi Bukan Cakupan Survei</t>
-  </si>
-  <si>
-    <t>Pindah Tidak Dapat Ditelusuri</t>
-  </si>
-  <si>
-    <t>Persentase Pindah Tidak Dapat Ditelusuri</t>
-  </si>
-  <si>
-    <t>Tutup</t>
-  </si>
-  <si>
-    <t>Persentase Tutup</t>
-  </si>
-  <si>
-    <t>Duplikat</t>
-  </si>
-  <si>
-    <t>Persentase Duplikat</t>
-  </si>
-  <si>
-    <t>Tidak Ditemukan</t>
-  </si>
-  <si>
-    <t>Persentase Tidak Ditemukan</t>
-  </si>
-  <si>
-    <t>Data Diperoleh dari Kantor Pusat</t>
-  </si>
-  <si>
-    <t>Persentase Data Diperoleh dari Kantor Pusat</t>
-  </si>
-  <si>
-    <t>Nonrespon</t>
-  </si>
-  <si>
-    <t>Persentase Nonrespon</t>
-  </si>
-  <si>
-    <t>Total UB</t>
-  </si>
-  <si>
-    <t>Persentase Total UB</t>
-  </si>
-  <si>
-    <t>Ditemukan</t>
-  </si>
-  <si>
-    <t>Persentase Ditemukan</t>
-  </si>
-  <si>
-    <t>Tutup​</t>
-  </si>
-  <si>
-    <t>Persentase Tutup​</t>
-  </si>
-  <si>
-    <t>Ganda</t>
-  </si>
-  <si>
-    <t>Persentase Ganda</t>
-  </si>
-  <si>
-    <t>Tidak Ditemukan​</t>
-  </si>
-  <si>
-    <t>Persentase Tidak Ditemukan​</t>
-  </si>
-  <si>
-    <t>Persentase Baru</t>
-  </si>
-  <si>
-    <t>Data Diperoleh dari Kantor Pusat​</t>
-  </si>
-  <si>
-    <t>Persentase Data Diperoleh dari Kantor Pusat​</t>
-  </si>
-  <si>
-    <t>Nonrespon​</t>
-  </si>
-  <si>
-    <t>Persentase Nonrespon​</t>
-  </si>
-  <si>
-    <t>Force Submit (Diklaim Sebagai Usaha Keluarga)</t>
-  </si>
-  <si>
-    <t>Persentase Force Submit (Diklaim Sebagai Usaha Keluarga)</t>
-  </si>
-  <si>
-    <t>Total UMKM</t>
-  </si>
-  <si>
-    <t>Persentase Total UMKM</t>
-  </si>
-  <si>
-    <t>(15)</t>
-  </si>
-  <si>
-    <t>(16)</t>
-  </si>
-  <si>
-    <t>(17)</t>
-  </si>
-  <si>
-    <t>(18)</t>
-  </si>
-  <si>
-    <t>(19)</t>
-  </si>
-  <si>
-    <t>(20)</t>
-  </si>
-  <si>
-    <t>(21)</t>
-  </si>
-  <si>
-    <t>(22)</t>
-  </si>
-  <si>
-    <t>(23)</t>
-  </si>
-  <si>
-    <t>(24)</t>
-  </si>
-  <si>
-    <t>(25)</t>
-  </si>
-  <si>
-    <t>(26)</t>
-  </si>
-  <si>
-    <t>(27)</t>
-  </si>
-  <si>
-    <t>(28)</t>
-  </si>
-  <si>
-    <t>(29)</t>
-  </si>
-  <si>
-    <t>(30)</t>
-  </si>
-  <si>
-    <t>(31)</t>
-  </si>
-  <si>
-    <t>(32)</t>
-  </si>
-  <si>
-    <t>(33)</t>
-  </si>
-  <si>
-    <t>(34)</t>
-  </si>
-  <si>
-    <t>(35)</t>
-  </si>
-  <si>
-    <t>(36)</t>
-  </si>
-  <si>
-    <t>(37)</t>
-  </si>
-  <si>
-    <t>(38)</t>
-  </si>
-  <si>
-    <t>(39)</t>
-  </si>
-  <si>
-    <t>(40)</t>
-  </si>
-  <si>
-    <t>(41)</t>
-  </si>
-  <si>
-    <t>0,15</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>0,01</t>
-  </si>
-  <si>
-    <t>0,02</t>
-  </si>
-  <si>
-    <t>11,82</t>
-  </si>
-  <si>
-    <t>17,84</t>
-  </si>
-  <si>
-    <t>8,07</t>
-  </si>
-  <si>
-    <t>43,73</t>
-  </si>
-  <si>
-    <t>15,86</t>
-  </si>
-  <si>
-    <t>6,53</t>
-  </si>
-  <si>
-    <t>27,68</t>
-  </si>
-  <si>
-    <t>27,83</t>
-  </si>
-  <si>
-    <t>0,2</t>
-  </si>
-  <si>
-    <t>0,03</t>
-  </si>
-  <si>
-    <t>17,11</t>
-  </si>
-  <si>
-    <t>16,95</t>
-  </si>
-  <si>
-    <t>12,79</t>
-  </si>
-  <si>
-    <t>41,63</t>
-  </si>
-  <si>
-    <t>17,91</t>
-  </si>
-  <si>
-    <t>1,53</t>
-  </si>
-  <si>
-    <t>35,02</t>
-  </si>
-  <si>
-    <t>35,22</t>
-  </si>
-  <si>
-    <t>0,1</t>
-  </si>
-  <si>
-    <t>8,98</t>
-  </si>
-  <si>
-    <t>22,5</t>
-  </si>
-  <si>
-    <t>15,69</t>
-  </si>
-  <si>
-    <t>27,29</t>
-  </si>
-  <si>
-    <t>10,16</t>
-  </si>
-  <si>
-    <t>10,51</t>
-  </si>
-  <si>
-    <t>19,14</t>
-  </si>
-  <si>
-    <t>19,25</t>
-  </si>
-  <si>
-    <t>0,14</t>
-  </si>
-  <si>
-    <t>6,21</t>
-  </si>
-  <si>
-    <t>11,99</t>
-  </si>
-  <si>
-    <t>4,31</t>
-  </si>
-  <si>
-    <t>62,79</t>
-  </si>
-  <si>
-    <t>14,88</t>
-  </si>
-  <si>
-    <t>3,1</t>
-  </si>
-  <si>
-    <t>21,09</t>
-  </si>
-  <si>
-    <t>21,23</t>
-  </si>
-  <si>
-    <t>0,06</t>
-  </si>
-  <si>
-    <t>11,76</t>
-  </si>
-  <si>
-    <t>22,51</t>
-  </si>
-  <si>
-    <t>7,84</t>
-  </si>
-  <si>
-    <t>33,68</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>11,48</t>
-  </si>
-  <si>
-    <t>24,76</t>
-  </si>
-  <si>
-    <t>24,82</t>
-  </si>
-  <si>
-    <t>11,01</t>
-  </si>
-  <si>
-    <t>19,79</t>
-  </si>
-  <si>
-    <t>9,62</t>
-  </si>
-  <si>
-    <t>44,51</t>
-  </si>
-  <si>
-    <t>17,18</t>
-  </si>
-  <si>
-    <t>6,22</t>
-  </si>
-  <si>
-    <t>28,19</t>
-  </si>
-  <si>
-    <t>28,28</t>
-  </si>
-  <si>
-    <t>0,08</t>
-  </si>
-  <si>
-    <t>7,6</t>
-  </si>
-  <si>
-    <t>15,75</t>
-  </si>
-  <si>
-    <t>5,47</t>
-  </si>
-  <si>
-    <t>58,81</t>
-  </si>
-  <si>
-    <t>12,28</t>
-  </si>
-  <si>
-    <t>7,7</t>
-  </si>
-  <si>
-    <t>19,88</t>
-  </si>
-  <si>
-    <t>19,96</t>
-  </si>
-  <si>
-    <t>0,09</t>
-  </si>
-  <si>
-    <t>6,14</t>
-  </si>
-  <si>
-    <t>22,33</t>
-  </si>
-  <si>
-    <t>6,47</t>
-  </si>
-  <si>
-    <t>44,94</t>
-  </si>
-  <si>
-    <t>14,63</t>
-  </si>
-  <si>
-    <t>9,92</t>
-  </si>
-  <si>
-    <t>20,77</t>
-  </si>
-  <si>
-    <t>20,86</t>
-  </si>
-  <si>
-    <t>0,25</t>
-  </si>
-  <si>
-    <t>21,2</t>
-  </si>
-  <si>
-    <t>12,83</t>
-  </si>
-  <si>
-    <t>4,81</t>
-  </si>
-  <si>
-    <t>41,88</t>
-  </si>
-  <si>
-    <t>26,06</t>
-  </si>
-  <si>
-    <t>0,99</t>
-  </si>
-  <si>
-    <t>47,26</t>
-  </si>
-  <si>
-    <t>47,51</t>
-  </si>
-  <si>
-    <t>0,26</t>
-  </si>
-  <si>
-    <t>31,36</t>
-  </si>
-  <si>
-    <t>14,73</t>
-  </si>
-  <si>
-    <t>5,68</t>
-  </si>
-  <si>
-    <t>35,77</t>
-  </si>
-  <si>
-    <t>33,75</t>
-  </si>
-  <si>
-    <t>2,06</t>
-  </si>
-  <si>
-    <t>65,11</t>
-  </si>
-  <si>
-    <t>65,37</t>
-  </si>
-  <si>
-    <t>36,37</t>
-  </si>
-  <si>
-    <t>13,72</t>
-  </si>
-  <si>
-    <t>3,48</t>
+    <t>32,78</t>
+  </si>
+  <si>
+    <t>13,33</t>
   </si>
   <si>
     <t>29,61</t>
   </si>
   <si>
-    <t>27,97</t>
-  </si>
-  <si>
-    <t>1,66</t>
-  </si>
-  <si>
-    <t>64,34</t>
-  </si>
-  <si>
-    <t>64,48</t>
-  </si>
-  <si>
-    <t>0,24</t>
-  </si>
-  <si>
-    <t>28,22</t>
-  </si>
-  <si>
-    <t>19,28</t>
-  </si>
-  <si>
-    <t>12,12</t>
-  </si>
-  <si>
-    <t>27,98</t>
-  </si>
-  <si>
-    <t>34,84</t>
-  </si>
-  <si>
-    <t>0,89</t>
-  </si>
-  <si>
-    <t>63,06</t>
-  </si>
-  <si>
-    <t>63,31</t>
-  </si>
-  <si>
-    <t>0,23</t>
-  </si>
-  <si>
-    <t>45,61</t>
-  </si>
-  <si>
-    <t>19,91</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>19,1</t>
-  </si>
-  <si>
-    <t>45,98</t>
-  </si>
-  <si>
-    <t>1,76</t>
-  </si>
-  <si>
-    <t>91,58</t>
-  </si>
-  <si>
-    <t>91,82</t>
-  </si>
-  <si>
-    <t>0,17</t>
-  </si>
-  <si>
-    <t>22,66</t>
-  </si>
-  <si>
-    <t>17,06</t>
-  </si>
-  <si>
-    <t>7,51</t>
-  </si>
-  <si>
-    <t>39,87</t>
-  </si>
-  <si>
-    <t>32,77</t>
-  </si>
-  <si>
-    <t>1,19</t>
-  </si>
-  <si>
-    <t>55,43</t>
-  </si>
-  <si>
-    <t>55,59</t>
-  </si>
-  <si>
-    <t>0,32</t>
-  </si>
-  <si>
-    <t>0,04</t>
-  </si>
-  <si>
-    <t>7,19</t>
-  </si>
-  <si>
-    <t>14,55</t>
-  </si>
-  <si>
-    <t>7,56</t>
-  </si>
-  <si>
-    <t>48,84</t>
-  </si>
-  <si>
-    <t>11,31</t>
-  </si>
-  <si>
-    <t>5,52</t>
-  </si>
-  <si>
-    <t>18,5</t>
-  </si>
-  <si>
-    <t>18,82</t>
-  </si>
-  <si>
-    <t>23,06</t>
-  </si>
-  <si>
-    <t>19,65</t>
-  </si>
-  <si>
-    <t>18,68</t>
-  </si>
-  <si>
-    <t>20,96</t>
-  </si>
-  <si>
-    <t>19,56</t>
-  </si>
-  <si>
-    <t>1,67</t>
-  </si>
-  <si>
-    <t>42,63</t>
-  </si>
-  <si>
-    <t>42,88</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha BKU</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha yang Ditemukan dan Baru (UB + UMKM)</t>
-  </si>
-  <si>
-    <t>Persentase Kolom 4 21</t>
-  </si>
-  <si>
-    <t>Persentase hasil bagi jumlah usaha pada kolom tersebut dengan jumlah prelist usaha (kolom 3).</t>
-  </si>
-  <si>
-    <t>PROGRES PENDATAAN - SKALA USAHA</t>
-  </si>
-  <si>
-    <t>JUMLAH PRELIST</t>
-  </si>
-  <si>
-    <t>JUMLAH USAHA BKU MENURUT STATUS SKALA USAHA (UB, UM, UMK)</t>
-  </si>
-  <si>
-    <t>UB​</t>
-  </si>
-  <si>
-    <t>Persentase UB​</t>
-  </si>
-  <si>
-    <t>UM​</t>
-  </si>
-  <si>
-    <t>Persentase UM​</t>
-  </si>
-  <si>
-    <t>UMK​</t>
-  </si>
-  <si>
-    <t>Persentase UMK​</t>
-  </si>
-  <si>
-    <t>Tidak Dapat Diklasifikasikan</t>
-  </si>
-  <si>
-    <t>Total Usaha BKU</t>
-  </si>
-  <si>
-    <t>Persentase Total Usaha BKU</t>
-  </si>
-  <si>
-    <t>86,4</t>
-  </si>
-  <si>
-    <t>14,12</t>
-  </si>
-  <si>
-    <t>27,72</t>
-  </si>
-  <si>
-    <t>130,43</t>
-  </si>
-  <si>
-    <t>37,75</t>
-  </si>
-  <si>
-    <t>34,9</t>
-  </si>
-  <si>
-    <t>58,77</t>
-  </si>
-  <si>
-    <t>19,48</t>
-  </si>
-  <si>
-    <t>19,05</t>
-  </si>
-  <si>
-    <t>106,9</t>
-  </si>
-  <si>
-    <t>9,99</t>
-  </si>
-  <si>
-    <t>21,1</t>
-  </si>
-  <si>
-    <t>126,58</t>
-  </si>
-  <si>
-    <t>22,16</t>
-  </si>
-  <si>
-    <t>24,61</t>
-  </si>
-  <si>
-    <t>107,19</t>
-  </si>
-  <si>
-    <t>17,1</t>
-  </si>
-  <si>
-    <t>28,14</t>
-  </si>
-  <si>
-    <t>86,67</t>
-  </si>
-  <si>
-    <t>18,81</t>
-  </si>
-  <si>
-    <t>19,82</t>
-  </si>
-  <si>
-    <t>134,29</t>
-  </si>
-  <si>
-    <t>13,95</t>
-  </si>
-  <si>
-    <t>20,65</t>
-  </si>
-  <si>
-    <t>6,93</t>
-  </si>
-  <si>
-    <t>48,03</t>
-  </si>
-  <si>
-    <t>98,18</t>
-  </si>
-  <si>
-    <t>39,39</t>
-  </si>
-  <si>
-    <t>65,22</t>
-  </si>
-  <si>
-    <t>131,25</t>
-  </si>
-  <si>
-    <t>155,56</t>
-  </si>
-  <si>
-    <t>63,98</t>
-  </si>
-  <si>
-    <t>114,81</t>
-  </si>
-  <si>
-    <t>36,84</t>
-  </si>
-  <si>
-    <t>63,2</t>
-  </si>
-  <si>
-    <t>113,04</t>
-  </si>
-  <si>
-    <t>48,48</t>
-  </si>
-  <si>
-    <t>91,9</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>55,44</t>
-  </si>
-  <si>
-    <t>64,76</t>
-  </si>
-  <si>
-    <t>9,54</t>
-  </si>
-  <si>
-    <t>18,73</t>
-  </si>
-  <si>
-    <t>117,5</t>
-  </si>
-  <si>
-    <t>45,31</t>
-  </si>
-  <si>
-    <t>42,43</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha (UB/UM/UMK)</t>
-  </si>
-  <si>
-    <t>Jumlah prelist usaha yang berhasil didata (keberadaan ditemukan, baru, pindah dapat ditelusuri) berdasarkan skala usaha, untuk usaha baru didekati dengan omzet sebagai berikut: UB (lebih dari 50 Milyar), UM (15-50 Milyar), UMK - Kecil (2-15 Milyar), UMK - Mikro (0-2 Milyar).</t>
-  </si>
-  <si>
-    <t>Tidak Dapat Diklasifikasikan (Kolom 10)</t>
-  </si>
-  <si>
-    <t>Usaha baru dengan nilai omzet/pendapatan kosong sehingga tidak dapat diklasifikasikan skala usahanya, misalnya usaha unit pembantu/penunjang.</t>
-  </si>
-  <si>
-    <t>Persentase Jumlah UB</t>
-  </si>
-  <si>
-    <t>Persentase hasil bagi jumlah UB yang berhasil didata dengan jumlah prelist UB (kolom 3).</t>
-  </si>
-  <si>
-    <t>Persentase Jumlah UM</t>
-  </si>
-  <si>
-    <t>Persentase hasil bagi jumlah UM yang berhasil didata dengan jumlah prelist UM (kolom 4).</t>
-  </si>
-  <si>
-    <t>Persentase Jumlah UMK</t>
-  </si>
-  <si>
-    <t>Persentase hasil bagi jumlah UMK yang berhasil didata dengan jumlah prelist UMK (kolom 5).</t>
-  </si>
-  <si>
-    <t>PROGRES PENDATAAN - USAHA KELUARGA</t>
-  </si>
-  <si>
-    <t>Jumlah Prelist Usaha Keluarga (ST2023 + UMKM)</t>
-  </si>
-  <si>
-    <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha dalam Keluarga (Ditemukan + Baru)</t>
-  </si>
-  <si>
-    <t>Persentase Usaha dalam Keluarga (Ditemukan + Baru)</t>
-  </si>
-  <si>
-    <t>48,93</t>
-  </si>
-  <si>
-    <t>24,28</t>
-  </si>
-  <si>
-    <t>0,4</t>
-  </si>
-  <si>
-    <t>9,53</t>
-  </si>
-  <si>
-    <t>34,19</t>
-  </si>
-  <si>
-    <t>83,13</t>
-  </si>
-  <si>
-    <t>58,36</t>
-  </si>
-  <si>
-    <t>20,2</t>
-  </si>
-  <si>
-    <t>0,52</t>
-  </si>
-  <si>
-    <t>8,77</t>
-  </si>
-  <si>
-    <t>29,86</t>
-  </si>
-  <si>
-    <t>88,22</t>
-  </si>
-  <si>
-    <t>45,52</t>
-  </si>
-  <si>
-    <t>25,2</t>
-  </si>
-  <si>
-    <t>0,46</t>
-  </si>
-  <si>
-    <t>7,94</t>
-  </si>
-  <si>
-    <t>34,58</t>
-  </si>
-  <si>
-    <t>80,1</t>
-  </si>
-  <si>
-    <t>37,82</t>
-  </si>
-  <si>
-    <t>23,54</t>
-  </si>
-  <si>
-    <t>0,19</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>32,12</t>
-  </si>
-  <si>
-    <t>69,94</t>
-  </si>
-  <si>
-    <t>50,46</t>
-  </si>
-  <si>
-    <t>22,97</t>
-  </si>
-  <si>
-    <t>8,34</t>
-  </si>
-  <si>
-    <t>36,68</t>
-  </si>
-  <si>
-    <t>87,13</t>
-  </si>
-  <si>
-    <t>50,71</t>
-  </si>
-  <si>
-    <t>22,28</t>
-  </si>
-  <si>
-    <t>10,61</t>
-  </si>
-  <si>
-    <t>32,87</t>
-  </si>
-  <si>
-    <t>83,57</t>
-  </si>
-  <si>
-    <t>48,75</t>
-  </si>
-  <si>
-    <t>20,26</t>
-  </si>
-  <si>
-    <t>0,22</t>
-  </si>
-  <si>
-    <t>17,38</t>
-  </si>
-  <si>
-    <t>38,22</t>
-  </si>
-  <si>
-    <t>86,98</t>
-  </si>
-  <si>
-    <t>48,47</t>
-  </si>
-  <si>
-    <t>22,73</t>
-  </si>
-  <si>
-    <t>8,43</t>
-  </si>
-  <si>
-    <t>38,77</t>
-  </si>
-  <si>
-    <t>87,24</t>
-  </si>
-  <si>
-    <t>44,43</t>
-  </si>
-  <si>
-    <t>27,01</t>
-  </si>
-  <si>
-    <t>0,51</t>
-  </si>
-  <si>
-    <t>4,89</t>
-  </si>
-  <si>
-    <t>27,9</t>
-  </si>
-  <si>
-    <t>72,33</t>
-  </si>
-  <si>
-    <t>52,84</t>
-  </si>
-  <si>
-    <t>27,93</t>
-  </si>
-  <si>
-    <t>0,74</t>
-  </si>
-  <si>
-    <t>6,87</t>
-  </si>
-  <si>
-    <t>23,48</t>
-  </si>
-  <si>
-    <t>76,32</t>
-  </si>
-  <si>
-    <t>48,3</t>
-  </si>
-  <si>
-    <t>29,85</t>
-  </si>
-  <si>
-    <t>0,6</t>
-  </si>
-  <si>
-    <t>6,02</t>
-  </si>
-  <si>
-    <t>27,3</t>
-  </si>
-  <si>
-    <t>75,6</t>
-  </si>
-  <si>
-    <t>47,06</t>
-  </si>
-  <si>
-    <t>30,05</t>
-  </si>
-  <si>
-    <t>0,71</t>
-  </si>
-  <si>
-    <t>12,1</t>
-  </si>
-  <si>
-    <t>28,06</t>
-  </si>
-  <si>
-    <t>75,12</t>
-  </si>
-  <si>
-    <t>57,82</t>
-  </si>
-  <si>
-    <t>24,26</t>
-  </si>
-  <si>
-    <t>0,57</t>
-  </si>
-  <si>
-    <t>7,63</t>
-  </si>
-  <si>
-    <t>32,33</t>
-  </si>
-  <si>
-    <t>90,15</t>
-  </si>
-  <si>
-    <t>54,43</t>
-  </si>
-  <si>
-    <t>29,36</t>
-  </si>
-  <si>
-    <t>0,44</t>
-  </si>
-  <si>
-    <t>4,85</t>
-  </si>
-  <si>
-    <t>26,69</t>
-  </si>
-  <si>
-    <t>81,12</t>
-  </si>
-  <si>
-    <t>23,77</t>
-  </si>
-  <si>
-    <t>30,08</t>
-  </si>
-  <si>
-    <t>0,84</t>
-  </si>
-  <si>
-    <t>14,68</t>
-  </si>
-  <si>
-    <t>318,91</t>
-  </si>
-  <si>
-    <t>342,69</t>
-  </si>
-  <si>
-    <t>46,08</t>
-  </si>
-  <si>
-    <t>28,31</t>
-  </si>
-  <si>
-    <t>2,42</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>83,08</t>
-  </si>
-  <si>
-    <t>Persentase Kolom 4 9</t>
-  </si>
-  <si>
-    <t>PROGRES PENDATAAN - KESELURUHAN USAHA</t>
-  </si>
-  <si>
-    <t>Total Prelist Usaha dan Usaha Keluarga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USAHA BKU </t>
-  </si>
-  <si>
-    <t>USAHA DALAM KELUARGA</t>
-  </si>
-  <si>
-    <t>Total Usaha</t>
-  </si>
-  <si>
-    <t>Persentase Total Usaha</t>
-  </si>
-  <si>
-    <t>Subtotal</t>
-  </si>
-  <si>
-    <t>Persentase Subtotal</t>
-  </si>
-  <si>
-    <t>Ditemukan​</t>
-  </si>
-  <si>
-    <t>Persentase Ditemukan​</t>
-  </si>
-  <si>
-    <t>Baru​</t>
-  </si>
-  <si>
-    <t>Persentase Baru​</t>
-  </si>
-  <si>
-    <t>Subtotal​</t>
-  </si>
-  <si>
-    <t>Persentase Subtotal​</t>
-  </si>
-  <si>
-    <t>11,97</t>
-  </si>
-  <si>
-    <t>68,7</t>
-  </si>
-  <si>
-    <t>17,31</t>
-  </si>
-  <si>
-    <t>82,74</t>
-  </si>
-  <si>
-    <t>9,08</t>
-  </si>
-  <si>
-    <t>64,85</t>
-  </si>
-  <si>
-    <t>6,35</t>
-  </si>
-  <si>
-    <t>54,52</t>
-  </si>
-  <si>
-    <t>70,43</t>
-  </si>
-  <si>
-    <t>11,1</t>
-  </si>
-  <si>
-    <t>70,32</t>
-  </si>
-  <si>
-    <t>7,68</t>
-  </si>
-  <si>
-    <t>64,7</t>
-  </si>
-  <si>
-    <t>6,23</t>
-  </si>
-  <si>
-    <t>71,11</t>
-  </si>
-  <si>
-    <t>21,45</t>
-  </si>
-  <si>
-    <t>68,71</t>
-  </si>
-  <si>
-    <t>31,62</t>
-  </si>
-  <si>
-    <t>75,16</t>
-  </si>
-  <si>
-    <t>36,51</t>
-  </si>
-  <si>
-    <t>73,84</t>
-  </si>
-  <si>
-    <t>28,46</t>
-  </si>
-  <si>
-    <t>73,7</t>
-  </si>
-  <si>
-    <t>45,84</t>
-  </si>
-  <si>
-    <t>90,3</t>
-  </si>
-  <si>
-    <t>22,83</t>
-  </si>
-  <si>
-    <t>78,69</t>
-  </si>
-  <si>
-    <t>47,19</t>
-  </si>
-  <si>
-    <t>23,32</t>
-  </si>
-  <si>
-    <t>66,33</t>
-  </si>
-  <si>
-    <t>Total Prelist Usaha Dan Usaha Keluarga</t>
-  </si>
-  <si>
-    <t>Jumlah Prelist Usaha Ditambah Jumlah Prelist Usaha Keluarga (ST2023 + UMKM) atau Kolom (3) + (4).</t>
-  </si>
-  <si>
-    <t>Persentase Usaha BKU Ditemukan</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha BKU Ditemukan/Pindah Dapat Ditelusuri (CAPI dan CAWI) dibagi dengan Jumlah Prelist Usaha (kolom 3).</t>
-  </si>
-  <si>
-    <t>Persentase Usaha BKU Baru</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha BKU Baru (CAPI) dibagi Jumlah Prelist Usaha (kolom 3).</t>
-  </si>
-  <si>
-    <t>Persentase Usaha Keluarga Ditemukan</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha Keluarga Ditemukan dibagi dengan Jumlah Prelist Usaha Keluarga (ST2023 + UMKM) atau Kolom (4).</t>
-  </si>
-  <si>
-    <t>Persentase Usaha Keluarga Baru</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha Keluarga Baru dibagi dengan Jumlah Prelist Usaha Keluarga (ST2023 + UMKM) atau Kolom (4).</t>
-  </si>
-  <si>
-    <t>PROGRES PENDATAAN - PROPORSI USAHA</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha (Semua Status Keberadaan Usaha)</t>
-  </si>
-  <si>
-    <t>Persentase Usaha BKU</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha dalam Keluarga</t>
-  </si>
-  <si>
-    <t>Persentase Usaha dalam Keluarga</t>
-  </si>
-  <si>
-    <t>6,48</t>
-  </si>
-  <si>
-    <t>54,77</t>
-  </si>
-  <si>
-    <t>3,12</t>
-  </si>
-  <si>
-    <t>67,86</t>
-  </si>
-  <si>
-    <t>4,53</t>
-  </si>
-  <si>
-    <t>56,39</t>
-  </si>
-  <si>
-    <t>6,34</t>
-  </si>
-  <si>
-    <t>45,08</t>
-  </si>
-  <si>
-    <t>6,01</t>
-  </si>
-  <si>
-    <t>57,62</t>
-  </si>
-  <si>
-    <t>5,99</t>
-  </si>
-  <si>
-    <t>56,12</t>
-  </si>
-  <si>
-    <t>5,69</t>
-  </si>
-  <si>
-    <t>49,8</t>
-  </si>
-  <si>
-    <t>58,57</t>
-  </si>
-  <si>
-    <t>6,59</t>
-  </si>
-  <si>
-    <t>58,8</t>
-  </si>
-  <si>
-    <t>6,16</t>
-  </si>
-  <si>
-    <t>60,41</t>
-  </si>
-  <si>
-    <t>9,11</t>
-  </si>
-  <si>
-    <t>56,86</t>
-  </si>
-  <si>
-    <t>6,45</t>
-  </si>
-  <si>
-    <t>55,7</t>
-  </si>
-  <si>
-    <t>6,6</t>
-  </si>
-  <si>
-    <t>66,34</t>
-  </si>
-  <si>
-    <t>4,54</t>
-  </si>
-  <si>
-    <t>63,19</t>
-  </si>
-  <si>
-    <t>14,79</t>
-  </si>
-  <si>
-    <t>25,85</t>
-  </si>
-  <si>
-    <t>16,13</t>
-  </si>
-  <si>
-    <t>43,76</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha (Semua Status Keberadaan Usaha) Kolom 3</t>
-  </si>
-  <si>
-    <t>Jumlah seluruh usaha BKU dan Usaha Keluarga dari CAPI dan CAWI dengan semua status keberadaan.</t>
-  </si>
-  <si>
-    <t>PROGRES PENDATAAN - JARINGAN USAHA</t>
-  </si>
-  <si>
-    <t>JUMLAH USAHA BERDASARKAN JARINGAN USAHA</t>
-  </si>
-  <si>
-    <t>Tunggal</t>
-  </si>
-  <si>
-    <t>Kantor Pusat</t>
-  </si>
-  <si>
-    <t>Cabang</t>
-  </si>
-  <si>
-    <t>Perwakilan</t>
-  </si>
-  <si>
-    <t>Pabrik</t>
-  </si>
-  <si>
-    <t>Unit Pembantu</t>
-  </si>
-  <si>
-    <t>PROGRES PENDATAAN - PROPORSI PERTANIAN</t>
-  </si>
-  <si>
-    <t>Jumlah Prelist Usaha SE2026</t>
-  </si>
-  <si>
-    <t>Target Berdasarkan Data ST</t>
-  </si>
-  <si>
-    <t>Jumlah UTP Subsektor Prelist</t>
-  </si>
-  <si>
-    <t>USAHA PERTANIAN BKU</t>
-  </si>
-  <si>
-    <t>USAHA PERTANIAN DALAM KELUARGA</t>
-  </si>
-  <si>
-    <t>24,23</t>
-  </si>
-  <si>
-    <t>75,77</t>
-  </si>
-  <si>
-    <t>69,26</t>
-  </si>
-  <si>
-    <t>30,74</t>
-  </si>
-  <si>
-    <t>13,51</t>
-  </si>
-  <si>
-    <t>86,49</t>
-  </si>
-  <si>
-    <t>68,83</t>
-  </si>
-  <si>
-    <t>31,17</t>
-  </si>
-  <si>
-    <t>25,05</t>
-  </si>
-  <si>
-    <t>74,95</t>
-  </si>
-  <si>
-    <t>69,36</t>
-  </si>
-  <si>
-    <t>30,64</t>
-  </si>
-  <si>
-    <t>15,58</t>
-  </si>
-  <si>
-    <t>84,42</t>
-  </si>
-  <si>
-    <t>70,72</t>
-  </si>
-  <si>
-    <t>29,28</t>
-  </si>
-  <si>
-    <t>45,7</t>
-  </si>
-  <si>
-    <t>54,3</t>
-  </si>
-  <si>
-    <t>69,32</t>
-  </si>
-  <si>
-    <t>30,68</t>
-  </si>
-  <si>
-    <t>36,85</t>
-  </si>
-  <si>
-    <t>63,15</t>
-  </si>
-  <si>
-    <t>70,13</t>
-  </si>
-  <si>
-    <t>29,87</t>
-  </si>
-  <si>
-    <t>37,97</t>
-  </si>
-  <si>
-    <t>62,03</t>
-  </si>
-  <si>
-    <t>68,35</t>
-  </si>
-  <si>
-    <t>31,65</t>
-  </si>
-  <si>
-    <t>15,17</t>
-  </si>
-  <si>
-    <t>84,83</t>
-  </si>
-  <si>
-    <t>65,58</t>
-  </si>
-  <si>
-    <t>34,42</t>
-  </si>
-  <si>
-    <t>7,55</t>
-  </si>
-  <si>
-    <t>92,45</t>
-  </si>
-  <si>
-    <t>65,13</t>
-  </si>
-  <si>
-    <t>34,87</t>
-  </si>
-  <si>
-    <t>24,12</t>
-  </si>
-  <si>
-    <t>75,88</t>
-  </si>
-  <si>
-    <t>74,06</t>
-  </si>
-  <si>
-    <t>25,94</t>
-  </si>
-  <si>
-    <t>8,64</t>
-  </si>
-  <si>
-    <t>91,36</t>
-  </si>
-  <si>
-    <t>70,53</t>
-  </si>
-  <si>
-    <t>29,47</t>
-  </si>
-  <si>
-    <t>7,24</t>
-  </si>
-  <si>
-    <t>92,76</t>
-  </si>
-  <si>
-    <t>66,53</t>
-  </si>
-  <si>
-    <t>33,47</t>
-  </si>
-  <si>
-    <t>15,32</t>
-  </si>
-  <si>
-    <t>84,68</t>
-  </si>
-  <si>
-    <t>32,78</t>
-  </si>
-  <si>
-    <t>13,33</t>
-  </si>
-  <si>
-    <t>70,39</t>
-  </si>
-  <si>
     <t>32,86</t>
   </si>
   <si>
@@ -2028,9 +2022,6 @@
   </si>
   <si>
     <t>68,29</t>
-  </si>
-  <si>
-    <t>31,71</t>
   </si>
   <si>
     <t>72,3</t>
@@ -2737,19 +2728,19 @@
         <v>33</v>
       </c>
       <c r="C7" s="6">
-        <v>3491484</v>
+        <v>3491486</v>
       </c>
       <c r="D7" s="6">
-        <v>828304</v>
+        <v>832445</v>
       </c>
       <c r="E7" s="6">
-        <v>3929417</v>
+        <v>3952889</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>34</v>
       </c>
       <c r="G7" s="6">
-        <v>2388685</v>
+        <v>2403893</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>35</v>
@@ -2784,16 +2775,16 @@
         <v>97072</v>
       </c>
       <c r="D8" s="9">
-        <v>25082</v>
+        <v>25094</v>
       </c>
       <c r="E8" s="9">
-        <v>121779</v>
+        <v>121983</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>39</v>
       </c>
       <c r="G8" s="9">
-        <v>82856</v>
+        <v>83028</v>
       </c>
       <c r="H8" s="10" t="s">
         <v>40</v>
@@ -2828,16 +2819,16 @@
         <v>230431</v>
       </c>
       <c r="D9" s="9">
-        <v>58536</v>
+        <v>58784</v>
       </c>
       <c r="E9" s="9">
-        <v>257536</v>
+        <v>259087</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>44</v>
       </c>
       <c r="G9" s="9">
-        <v>162821</v>
+        <v>163824</v>
       </c>
       <c r="H9" s="10" t="s">
         <v>45</v>
@@ -2869,19 +2860,19 @@
         <v>48</v>
       </c>
       <c r="C10" s="9">
-        <v>436272</v>
+        <v>436273</v>
       </c>
       <c r="D10" s="9">
-        <v>123164</v>
+        <v>124187</v>
       </c>
       <c r="E10" s="9">
-        <v>481281</v>
+        <v>485756</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>49</v>
       </c>
       <c r="G10" s="9">
-        <v>275855</v>
+        <v>278725</v>
       </c>
       <c r="H10" s="10" t="s">
         <v>50</v>
@@ -2916,16 +2907,16 @@
         <v>489943</v>
       </c>
       <c r="D11" s="9">
-        <v>94250</v>
+        <v>94676</v>
       </c>
       <c r="E11" s="9">
-        <v>527359</v>
+        <v>530244</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>54</v>
       </c>
       <c r="G11" s="9">
-        <v>326271</v>
+        <v>328101</v>
       </c>
       <c r="H11" s="10" t="s">
         <v>55</v>
@@ -2960,16 +2951,16 @@
         <v>580719</v>
       </c>
       <c r="D12" s="9">
-        <v>115414</v>
+        <v>116015</v>
       </c>
       <c r="E12" s="9">
-        <v>631645</v>
+        <v>635722</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>59</v>
       </c>
       <c r="G12" s="9">
-        <v>390378</v>
+        <v>393179</v>
       </c>
       <c r="H12" s="10" t="s">
         <v>60</v>
@@ -3004,16 +2995,16 @@
         <v>263315</v>
       </c>
       <c r="D13" s="9">
-        <v>54328</v>
+        <v>54619</v>
       </c>
       <c r="E13" s="9">
-        <v>304429</v>
+        <v>305927</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>64</v>
       </c>
       <c r="G13" s="9">
-        <v>174992</v>
+        <v>176037</v>
       </c>
       <c r="H13" s="10" t="s">
         <v>65</v>
@@ -3048,16 +3039,16 @@
         <v>187422</v>
       </c>
       <c r="D14" s="9">
-        <v>48271</v>
+        <v>48652</v>
       </c>
       <c r="E14" s="9">
-        <v>213882</v>
+        <v>215606</v>
       </c>
       <c r="F14" s="10" t="s">
         <v>69</v>
       </c>
       <c r="G14" s="9">
-        <v>129393</v>
+        <v>130573</v>
       </c>
       <c r="H14" s="10" t="s">
         <v>70</v>
@@ -3092,16 +3083,16 @@
         <v>154763</v>
       </c>
       <c r="D15" s="9">
-        <v>40942</v>
+        <v>41180</v>
       </c>
       <c r="E15" s="9">
-        <v>178742</v>
+        <v>179950</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>74</v>
       </c>
       <c r="G15" s="9">
-        <v>107615</v>
+        <v>108483</v>
       </c>
       <c r="H15" s="10" t="s">
         <v>75</v>
@@ -3136,16 +3127,16 @@
         <v>170543</v>
       </c>
       <c r="D16" s="9">
-        <v>46364</v>
+        <v>46514</v>
       </c>
       <c r="E16" s="9">
-        <v>211190</v>
+        <v>212095</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>79</v>
       </c>
       <c r="G16" s="9">
-        <v>143421</v>
+        <v>144026</v>
       </c>
       <c r="H16" s="10" t="s">
         <v>80</v>
@@ -3180,16 +3171,16 @@
         <v>157837</v>
       </c>
       <c r="D17" s="9">
-        <v>34656</v>
+        <v>34793</v>
       </c>
       <c r="E17" s="9">
-        <v>177923</v>
+        <v>179290</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>84</v>
       </c>
       <c r="G17" s="9">
-        <v>126335</v>
+        <v>127245</v>
       </c>
       <c r="H17" s="10" t="s">
         <v>85</v>
@@ -3224,16 +3215,16 @@
         <v>86207</v>
       </c>
       <c r="D18" s="9">
-        <v>26866</v>
+        <v>26901</v>
       </c>
       <c r="E18" s="9">
-        <v>114530</v>
+        <v>114568</v>
       </c>
       <c r="F18" s="10" t="s">
         <v>89</v>
       </c>
       <c r="G18" s="9">
-        <v>75071</v>
+        <v>75106</v>
       </c>
       <c r="H18" s="10" t="s">
         <v>90</v>
@@ -3268,16 +3259,16 @@
         <v>109078</v>
       </c>
       <c r="D19" s="9">
-        <v>30868</v>
+        <v>30903</v>
       </c>
       <c r="E19" s="9">
-        <v>140799</v>
+        <v>141004</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>94</v>
       </c>
       <c r="G19" s="9">
-        <v>95283</v>
+        <v>95433</v>
       </c>
       <c r="H19" s="10" t="s">
         <v>95</v>
@@ -3312,16 +3303,16 @@
         <v>47152</v>
       </c>
       <c r="D20" s="9">
-        <v>14219</v>
+        <v>14255</v>
       </c>
       <c r="E20" s="9">
-        <v>61432</v>
+        <v>61554</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>99</v>
       </c>
       <c r="G20" s="9">
-        <v>44481</v>
+        <v>44591</v>
       </c>
       <c r="H20" s="10" t="s">
         <v>100</v>
@@ -3353,19 +3344,19 @@
         <v>103</v>
       </c>
       <c r="C21" s="9">
-        <v>410237</v>
+        <v>410238</v>
       </c>
       <c r="D21" s="9">
-        <v>99986</v>
+        <v>100405</v>
       </c>
       <c r="E21" s="9">
-        <v>430399</v>
+        <v>433207</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>104</v>
       </c>
       <c r="G21" s="9">
-        <v>207030</v>
+        <v>208404</v>
       </c>
       <c r="H21" s="10" t="s">
         <v>105</v>
@@ -3400,16 +3391,16 @@
         <v>70493</v>
       </c>
       <c r="D22" s="9">
-        <v>15358</v>
+        <v>15467</v>
       </c>
       <c r="E22" s="9">
-        <v>76491</v>
+        <v>76896</v>
       </c>
       <c r="F22" s="10" t="s">
         <v>108</v>
       </c>
       <c r="G22" s="9">
-        <v>46883</v>
+        <v>47138</v>
       </c>
       <c r="H22" s="10" t="s">
         <v>109</v>
@@ -3441,19 +3432,19 @@
         <v>112</v>
       </c>
       <c r="C23" s="12">
-        <v>3491484</v>
+        <v>3491486</v>
       </c>
       <c r="D23" s="12">
-        <v>828304</v>
+        <v>832445</v>
       </c>
       <c r="E23" s="12">
-        <v>3929417</v>
+        <v>3952889</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>34</v>
       </c>
       <c r="G23" s="12">
-        <v>2388685</v>
+        <v>2403893</v>
       </c>
       <c r="H23" s="13" t="s">
         <v>35</v>
@@ -4109,7 +4100,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="6">
-        <v>760551</v>
+        <v>760553</v>
       </c>
       <c r="D8" s="6">
         <v>1157</v>
@@ -4166,31 +4157,31 @@
         <v>190</v>
       </c>
       <c r="V8" s="6">
-        <v>89908</v>
+        <v>90494</v>
       </c>
       <c r="W8" s="7" t="s">
         <v>194</v>
       </c>
       <c r="X8" s="6">
-        <v>135657</v>
+        <v>136586</v>
       </c>
       <c r="Y8" s="7" t="s">
         <v>195</v>
       </c>
       <c r="Z8" s="6">
-        <v>61370</v>
+        <v>61715</v>
       </c>
       <c r="AA8" s="7" t="s">
         <v>196</v>
       </c>
       <c r="AB8" s="6">
-        <v>332574</v>
+        <v>332900</v>
       </c>
       <c r="AC8" s="7" t="s">
         <v>197</v>
       </c>
       <c r="AD8" s="6">
-        <v>120619</v>
+        <v>121644</v>
       </c>
       <c r="AE8" s="7" t="s">
         <v>198</v>
@@ -4214,13 +4205,13 @@
         <v>199</v>
       </c>
       <c r="AL8" s="6">
-        <v>210527</v>
+        <v>212138</v>
       </c>
       <c r="AM8" s="7" t="s">
         <v>200</v>
       </c>
       <c r="AN8" s="6">
-        <v>211684</v>
+        <v>213295</v>
       </c>
       <c r="AO8" s="7" t="s">
         <v>201</v>
@@ -4291,34 +4282,34 @@
         <v>202</v>
       </c>
       <c r="V9" s="9">
-        <v>2041</v>
+        <v>2047</v>
       </c>
       <c r="W9" s="10" t="s">
         <v>204</v>
       </c>
       <c r="X9" s="9">
-        <v>2022</v>
+        <v>2034</v>
       </c>
       <c r="Y9" s="10" t="s">
         <v>205</v>
       </c>
       <c r="Z9" s="9">
-        <v>1525</v>
+        <v>1527</v>
       </c>
       <c r="AA9" s="10" t="s">
         <v>206</v>
       </c>
       <c r="AB9" s="9">
-        <v>4965</v>
+        <v>4956</v>
       </c>
       <c r="AC9" s="10" t="s">
         <v>207</v>
       </c>
       <c r="AD9" s="9">
-        <v>2136</v>
+        <v>2142</v>
       </c>
       <c r="AE9" s="10" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="AF9" s="9">
         <v>1</v>
@@ -4336,19 +4327,19 @@
         <v>182</v>
       </c>
       <c r="AK9" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="AL9" s="9">
+        <v>4189</v>
+      </c>
+      <c r="AM9" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="AL9" s="9">
-        <v>4177</v>
-      </c>
-      <c r="AM9" s="10" t="s">
+      <c r="AN9" s="9">
+        <v>4213</v>
+      </c>
+      <c r="AO9" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="AN9" s="9">
-        <v>4201</v>
-      </c>
-      <c r="AO9" s="10" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -4365,7 +4356,7 @@
         <v>59</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F10" s="9">
         <v>0</v>
@@ -4413,37 +4404,37 @@
         <v>59</v>
       </c>
       <c r="U10" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="V10" s="9">
+        <v>5195</v>
+      </c>
+      <c r="W10" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="V10" s="9">
-        <v>5162</v>
-      </c>
-      <c r="W10" s="10" t="s">
+      <c r="X10" s="9">
+        <v>12979</v>
+      </c>
+      <c r="Y10" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="X10" s="9">
-        <v>12934</v>
-      </c>
-      <c r="Y10" s="10" t="s">
+      <c r="Z10" s="9">
+        <v>9055</v>
+      </c>
+      <c r="AA10" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="Z10" s="9">
-        <v>9017</v>
-      </c>
-      <c r="AA10" s="10" t="s">
+      <c r="AB10" s="9">
+        <v>15727</v>
+      </c>
+      <c r="AC10" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="AB10" s="9">
-        <v>15682</v>
-      </c>
-      <c r="AC10" s="10" t="s">
+      <c r="AD10" s="9">
+        <v>5917</v>
+      </c>
+      <c r="AE10" s="10" t="s">
         <v>216</v>
-      </c>
-      <c r="AD10" s="9">
-        <v>5841</v>
-      </c>
-      <c r="AE10" s="10" t="s">
-        <v>217</v>
       </c>
       <c r="AF10" s="9">
         <v>0</v>
@@ -4461,19 +4452,19 @@
         <v>6038</v>
       </c>
       <c r="AK10" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="AL10" s="9">
+        <v>11112</v>
+      </c>
+      <c r="AM10" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="AL10" s="9">
-        <v>11003</v>
-      </c>
-      <c r="AM10" s="10" t="s">
+      <c r="AN10" s="9">
+        <v>11171</v>
+      </c>
+      <c r="AO10" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="AN10" s="9">
-        <v>11062</v>
-      </c>
-      <c r="AO10" s="10" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -4484,13 +4475,13 @@
         <v>48</v>
       </c>
       <c r="C11" s="9">
-        <v>93538</v>
+        <v>93539</v>
       </c>
       <c r="D11" s="9">
         <v>131</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F11" s="9">
         <v>0</v>
@@ -4538,37 +4529,37 @@
         <v>131</v>
       </c>
       <c r="U11" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="V11" s="9">
+        <v>5888</v>
+      </c>
+      <c r="W11" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="V11" s="9">
-        <v>5810</v>
-      </c>
-      <c r="W11" s="10" t="s">
+      <c r="X11" s="9">
+        <v>11288</v>
+      </c>
+      <c r="Y11" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="X11" s="9">
-        <v>11215</v>
-      </c>
-      <c r="Y11" s="10" t="s">
+      <c r="Z11" s="9">
+        <v>4047</v>
+      </c>
+      <c r="AA11" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="Z11" s="9">
-        <v>4027</v>
-      </c>
-      <c r="AA11" s="10" t="s">
+      <c r="AB11" s="9">
+        <v>58855</v>
+      </c>
+      <c r="AC11" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="AB11" s="9">
-        <v>58734</v>
-      </c>
-      <c r="AC11" s="10" t="s">
+      <c r="AD11" s="9">
+        <v>14094</v>
+      </c>
+      <c r="AE11" s="10" t="s">
         <v>225</v>
-      </c>
-      <c r="AD11" s="9">
-        <v>13920</v>
-      </c>
-      <c r="AE11" s="10" t="s">
-        <v>226</v>
       </c>
       <c r="AF11" s="9">
         <v>1</v>
@@ -4586,19 +4577,19 @@
         <v>2903</v>
       </c>
       <c r="AK11" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="AL11" s="9">
+        <v>19982</v>
+      </c>
+      <c r="AM11" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="AL11" s="9">
-        <v>19730</v>
-      </c>
-      <c r="AM11" s="10" t="s">
+      <c r="AN11" s="9">
+        <v>20113</v>
+      </c>
+      <c r="AO11" s="10" t="s">
         <v>228</v>
-      </c>
-      <c r="AN11" s="9">
-        <v>19861</v>
-      </c>
-      <c r="AO11" s="10" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -4615,7 +4606,7 @@
         <v>78</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F12" s="9">
         <v>0</v>
@@ -4663,37 +4654,37 @@
         <v>78</v>
       </c>
       <c r="U12" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="V12" s="9">
+        <v>15007</v>
+      </c>
+      <c r="W12" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="V12" s="9">
-        <v>14943</v>
-      </c>
-      <c r="W12" s="10" t="s">
+      <c r="X12" s="9">
+        <v>28775</v>
+      </c>
+      <c r="Y12" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="X12" s="9">
-        <v>28606</v>
-      </c>
-      <c r="Y12" s="10" t="s">
+      <c r="Z12" s="9">
+        <v>9993</v>
+      </c>
+      <c r="AA12" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="Z12" s="9">
-        <v>9962</v>
-      </c>
-      <c r="AA12" s="10" t="s">
+      <c r="AB12" s="9">
+        <v>42887</v>
+      </c>
+      <c r="AC12" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="AB12" s="9">
-        <v>42808</v>
-      </c>
-      <c r="AC12" s="10" t="s">
+      <c r="AD12" s="9">
+        <v>16643</v>
+      </c>
+      <c r="AE12" s="10" t="s">
         <v>234</v>
-      </c>
-      <c r="AD12" s="9">
-        <v>16525</v>
-      </c>
-      <c r="AE12" s="10" t="s">
-        <v>235</v>
       </c>
       <c r="AF12" s="9">
         <v>1</v>
@@ -4711,19 +4702,19 @@
         <v>14593</v>
       </c>
       <c r="AK12" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="AL12" s="9">
+        <v>31650</v>
+      </c>
+      <c r="AM12" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="AL12" s="9">
-        <v>31468</v>
-      </c>
-      <c r="AM12" s="10" t="s">
+      <c r="AN12" s="9">
+        <v>31728</v>
+      </c>
+      <c r="AO12" s="10" t="s">
         <v>237</v>
-      </c>
-      <c r="AN12" s="9">
-        <v>31546</v>
-      </c>
-      <c r="AO12" s="10" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -4740,7 +4731,7 @@
         <v>125</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F13" s="9">
         <v>1</v>
@@ -4788,37 +4779,37 @@
         <v>125</v>
       </c>
       <c r="U13" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="V13" s="9">
-        <v>14433</v>
+        <v>14540</v>
       </c>
       <c r="W13" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="X13" s="9">
+        <v>26197</v>
+      </c>
+      <c r="Y13" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="X13" s="9">
-        <v>25954</v>
-      </c>
-      <c r="Y13" s="10" t="s">
+      <c r="Z13" s="9">
+        <v>12710</v>
+      </c>
+      <c r="AA13" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="Z13" s="9">
-        <v>12619</v>
-      </c>
-      <c r="AA13" s="10" t="s">
+      <c r="AB13" s="9">
+        <v>58242</v>
+      </c>
+      <c r="AC13" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="AB13" s="9">
-        <v>58367</v>
-      </c>
-      <c r="AC13" s="10" t="s">
+      <c r="AD13" s="9">
+        <v>22782</v>
+      </c>
+      <c r="AE13" s="10" t="s">
         <v>242</v>
-      </c>
-      <c r="AD13" s="9">
-        <v>22535</v>
-      </c>
-      <c r="AE13" s="10" t="s">
-        <v>243</v>
       </c>
       <c r="AF13" s="9">
         <v>1</v>
@@ -4836,19 +4827,19 @@
         <v>8160</v>
       </c>
       <c r="AK13" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="AL13" s="9">
+        <v>37322</v>
+      </c>
+      <c r="AM13" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="AL13" s="9">
-        <v>36968</v>
-      </c>
-      <c r="AM13" s="10" t="s">
+      <c r="AN13" s="9">
+        <v>37447</v>
+      </c>
+      <c r="AO13" s="10" t="s">
         <v>245</v>
-      </c>
-      <c r="AN13" s="9">
-        <v>37093</v>
-      </c>
-      <c r="AO13" s="10" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -4865,7 +4856,7 @@
         <v>52</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F14" s="9">
         <v>0</v>
@@ -4913,37 +4904,37 @@
         <v>52</v>
       </c>
       <c r="U14" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="V14" s="9">
+        <v>4893</v>
+      </c>
+      <c r="W14" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="V14" s="9">
-        <v>4857</v>
-      </c>
-      <c r="W14" s="10" t="s">
+      <c r="X14" s="9">
+        <v>10134</v>
+      </c>
+      <c r="Y14" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="X14" s="9">
-        <v>10065</v>
-      </c>
-      <c r="Y14" s="10" t="s">
+      <c r="Z14" s="9">
+        <v>3506</v>
+      </c>
+      <c r="AA14" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="Z14" s="9">
-        <v>3495</v>
-      </c>
-      <c r="AA14" s="10" t="s">
+      <c r="AB14" s="9">
+        <v>37614</v>
+      </c>
+      <c r="AC14" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="AB14" s="9">
-        <v>37591</v>
-      </c>
-      <c r="AC14" s="10" t="s">
+      <c r="AD14" s="9">
+        <v>7905</v>
+      </c>
+      <c r="AE14" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="AD14" s="9">
-        <v>7852</v>
-      </c>
-      <c r="AE14" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="AF14" s="9">
         <v>0</v>
@@ -4961,19 +4952,19 @@
         <v>4920</v>
       </c>
       <c r="AK14" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="AL14" s="9">
+        <v>12798</v>
+      </c>
+      <c r="AM14" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="AL14" s="9">
-        <v>12709</v>
-      </c>
-      <c r="AM14" s="10" t="s">
+      <c r="AN14" s="9">
+        <v>12850</v>
+      </c>
+      <c r="AO14" s="10" t="s">
         <v>254</v>
-      </c>
-      <c r="AN14" s="9">
-        <v>12761</v>
-      </c>
-      <c r="AO14" s="10" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -4990,7 +4981,7 @@
         <v>38</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F15" s="9">
         <v>0</v>
@@ -5038,37 +5029,37 @@
         <v>38</v>
       </c>
       <c r="U15" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="V15" s="9">
+        <v>2566</v>
+      </c>
+      <c r="W15" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="V15" s="9">
-        <v>2537</v>
-      </c>
-      <c r="W15" s="10" t="s">
+      <c r="X15" s="9">
+        <v>9324</v>
+      </c>
+      <c r="Y15" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="X15" s="9">
-        <v>9230</v>
-      </c>
-      <c r="Y15" s="10" t="s">
+      <c r="Z15" s="9">
+        <v>2681</v>
+      </c>
+      <c r="AA15" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="Z15" s="9">
-        <v>2672</v>
-      </c>
-      <c r="AA15" s="10" t="s">
+      <c r="AB15" s="9">
+        <v>18603</v>
+      </c>
+      <c r="AC15" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="AB15" s="9">
-        <v>18572</v>
-      </c>
-      <c r="AC15" s="10" t="s">
+      <c r="AD15" s="9">
+        <v>6161</v>
+      </c>
+      <c r="AE15" s="10" t="s">
         <v>260</v>
-      </c>
-      <c r="AD15" s="9">
-        <v>6047</v>
-      </c>
-      <c r="AE15" s="10" t="s">
-        <v>261</v>
       </c>
       <c r="AF15" s="9">
         <v>0</v>
@@ -5086,19 +5077,19 @@
         <v>4098</v>
       </c>
       <c r="AK15" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="AL15" s="9">
+        <v>8727</v>
+      </c>
+      <c r="AM15" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="AL15" s="9">
-        <v>8584</v>
-      </c>
-      <c r="AM15" s="10" t="s">
+      <c r="AN15" s="9">
+        <v>8765</v>
+      </c>
+      <c r="AO15" s="10" t="s">
         <v>263</v>
-      </c>
-      <c r="AN15" s="9">
-        <v>8622</v>
-      </c>
-      <c r="AO15" s="10" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -5115,7 +5106,7 @@
         <v>48</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F16" s="9">
         <v>1</v>
@@ -5163,37 +5154,37 @@
         <v>48</v>
       </c>
       <c r="U16" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="V16" s="9">
+        <v>4181</v>
+      </c>
+      <c r="W16" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="V16" s="9">
-        <v>4136</v>
-      </c>
-      <c r="W16" s="10" t="s">
+      <c r="X16" s="9">
+        <v>2509</v>
+      </c>
+      <c r="Y16" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="X16" s="9">
-        <v>2502</v>
-      </c>
-      <c r="Y16" s="10" t="s">
+      <c r="Z16" s="9">
+        <v>952</v>
+      </c>
+      <c r="AA16" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="Z16" s="9">
-        <v>939</v>
-      </c>
-      <c r="AA16" s="10" t="s">
+      <c r="AB16" s="9">
+        <v>8188</v>
+      </c>
+      <c r="AC16" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="AB16" s="9">
-        <v>8170</v>
-      </c>
-      <c r="AC16" s="10" t="s">
+      <c r="AD16" s="9">
+        <v>5126</v>
+      </c>
+      <c r="AE16" s="10" t="s">
         <v>269</v>
-      </c>
-      <c r="AD16" s="9">
-        <v>5083</v>
-      </c>
-      <c r="AE16" s="10" t="s">
-        <v>270</v>
       </c>
       <c r="AF16" s="9">
         <v>0</v>
@@ -5211,19 +5202,19 @@
         <v>193</v>
       </c>
       <c r="AK16" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="AL16" s="9">
+        <v>9307</v>
+      </c>
+      <c r="AM16" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="AL16" s="9">
-        <v>9219</v>
-      </c>
-      <c r="AM16" s="10" t="s">
+      <c r="AN16" s="9">
+        <v>9355</v>
+      </c>
+      <c r="AO16" s="10" t="s">
         <v>272</v>
-      </c>
-      <c r="AN16" s="9">
-        <v>9267</v>
-      </c>
-      <c r="AO16" s="10" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -5240,7 +5231,7 @@
         <v>48</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F17" s="9">
         <v>0</v>
@@ -5288,37 +5279,37 @@
         <v>48</v>
       </c>
       <c r="U17" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="V17" s="9">
+        <v>5781</v>
+      </c>
+      <c r="W17" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="V17" s="9">
-        <v>5765</v>
-      </c>
-      <c r="W17" s="10" t="s">
+      <c r="X17" s="9">
+        <v>2736</v>
+      </c>
+      <c r="Y17" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="X17" s="9">
-        <v>2708</v>
-      </c>
-      <c r="Y17" s="10" t="s">
+      <c r="Z17" s="9">
+        <v>1071</v>
+      </c>
+      <c r="AA17" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="AB17" s="9">
+        <v>6556</v>
+      </c>
+      <c r="AC17" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="Z17" s="9">
-        <v>1044</v>
-      </c>
-      <c r="AA17" s="10" t="s">
+      <c r="AD17" s="9">
+        <v>6225</v>
+      </c>
+      <c r="AE17" s="10" t="s">
         <v>277</v>
-      </c>
-      <c r="AB17" s="9">
-        <v>6577</v>
-      </c>
-      <c r="AC17" s="10" t="s">
-        <v>278</v>
-      </c>
-      <c r="AD17" s="9">
-        <v>6205</v>
-      </c>
-      <c r="AE17" s="10" t="s">
-        <v>279</v>
       </c>
       <c r="AF17" s="9">
         <v>0</v>
@@ -5336,19 +5327,19 @@
         <v>378</v>
       </c>
       <c r="AK17" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="AL17" s="9">
+        <v>12006</v>
+      </c>
+      <c r="AM17" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="AN17" s="9">
+        <v>12054</v>
+      </c>
+      <c r="AO17" s="10" t="s">
         <v>280</v>
-      </c>
-      <c r="AL17" s="9">
-        <v>11970</v>
-      </c>
-      <c r="AM17" s="10" t="s">
-        <v>281</v>
-      </c>
-      <c r="AN17" s="9">
-        <v>12018</v>
-      </c>
-      <c r="AO17" s="10" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -5365,7 +5356,7 @@
         <v>31</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F18" s="9">
         <v>0</v>
@@ -5413,37 +5404,37 @@
         <v>31</v>
       </c>
       <c r="U18" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="V18" s="9">
-        <v>8036</v>
+        <v>8088</v>
       </c>
       <c r="W18" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="X18" s="9">
+        <v>3048</v>
+      </c>
+      <c r="Y18" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="Z18" s="9">
+        <v>775</v>
+      </c>
+      <c r="AA18" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="X18" s="9">
-        <v>3031</v>
-      </c>
-      <c r="Y18" s="10" t="s">
+      <c r="AB18" s="9">
+        <v>6569</v>
+      </c>
+      <c r="AC18" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="Z18" s="9">
-        <v>769</v>
-      </c>
-      <c r="AA18" s="10" t="s">
+      <c r="AD18" s="9">
+        <v>6232</v>
+      </c>
+      <c r="AE18" s="10" t="s">
         <v>285</v>
-      </c>
-      <c r="AB18" s="9">
-        <v>6542</v>
-      </c>
-      <c r="AC18" s="10" t="s">
-        <v>286</v>
-      </c>
-      <c r="AD18" s="9">
-        <v>6180</v>
-      </c>
-      <c r="AE18" s="10" t="s">
-        <v>287</v>
       </c>
       <c r="AF18" s="9">
         <v>0</v>
@@ -5461,19 +5452,19 @@
         <v>366</v>
       </c>
       <c r="AK18" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="AL18" s="9">
+        <v>14320</v>
+      </c>
+      <c r="AM18" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="AN18" s="9">
+        <v>14351</v>
+      </c>
+      <c r="AO18" s="10" t="s">
         <v>288</v>
-      </c>
-      <c r="AL18" s="9">
-        <v>14216</v>
-      </c>
-      <c r="AM18" s="10" t="s">
-        <v>289</v>
-      </c>
-      <c r="AN18" s="9">
-        <v>14247</v>
-      </c>
-      <c r="AO18" s="10" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -5490,7 +5481,7 @@
         <v>27</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F19" s="9">
         <v>0</v>
@@ -5538,37 +5529,37 @@
         <v>27</v>
       </c>
       <c r="U19" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="V19" s="9">
+        <v>3132</v>
+      </c>
+      <c r="W19" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="X19" s="9">
+        <v>2138</v>
+      </c>
+      <c r="Y19" s="10" t="s">
         <v>291</v>
-      </c>
-      <c r="V19" s="9">
-        <v>3130</v>
-      </c>
-      <c r="W19" s="10" t="s">
-        <v>292</v>
-      </c>
-      <c r="X19" s="9">
-        <v>2139</v>
-      </c>
-      <c r="Y19" s="10" t="s">
-        <v>293</v>
       </c>
       <c r="Z19" s="9">
         <v>1344</v>
       </c>
       <c r="AA19" s="10" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AB19" s="9">
         <v>3103</v>
       </c>
       <c r="AC19" s="10" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="AD19" s="9">
-        <v>3865</v>
+        <v>3866</v>
       </c>
       <c r="AE19" s="10" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AF19" s="9">
         <v>0</v>
@@ -5586,19 +5577,19 @@
         <v>99</v>
       </c>
       <c r="AK19" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="AL19" s="9">
+        <v>6998</v>
+      </c>
+      <c r="AM19" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="AN19" s="9">
+        <v>7025</v>
+      </c>
+      <c r="AO19" s="10" t="s">
         <v>297</v>
-      </c>
-      <c r="AL19" s="9">
-        <v>6995</v>
-      </c>
-      <c r="AM19" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="AN19" s="9">
-        <v>7022</v>
-      </c>
-      <c r="AO19" s="10" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -5615,7 +5606,7 @@
         <v>23</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F20" s="9">
         <v>0</v>
@@ -5663,37 +5654,37 @@
         <v>23</v>
       </c>
       <c r="U20" s="10" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="V20" s="9">
-        <v>4519</v>
+        <v>4532</v>
       </c>
       <c r="W20" s="10" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="X20" s="9">
         <v>1973</v>
       </c>
       <c r="Y20" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="Z20" s="9">
+        <v>499</v>
+      </c>
+      <c r="AA20" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="AB20" s="9">
+        <v>1891</v>
+      </c>
+      <c r="AC20" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="Z20" s="9">
-        <v>495</v>
-      </c>
-      <c r="AA20" s="10" t="s">
+      <c r="AD20" s="9">
+        <v>4560</v>
+      </c>
+      <c r="AE20" s="10" t="s">
         <v>303</v>
-      </c>
-      <c r="AB20" s="9">
-        <v>1893</v>
-      </c>
-      <c r="AC20" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="AD20" s="9">
-        <v>4556</v>
-      </c>
-      <c r="AE20" s="10" t="s">
-        <v>305</v>
       </c>
       <c r="AF20" s="9">
         <v>2</v>
@@ -5711,19 +5702,19 @@
         <v>174</v>
       </c>
       <c r="AK20" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="AL20" s="9">
+        <v>9092</v>
+      </c>
+      <c r="AM20" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="AN20" s="9">
+        <v>9115</v>
+      </c>
+      <c r="AO20" s="10" t="s">
         <v>306</v>
-      </c>
-      <c r="AL20" s="9">
-        <v>9075</v>
-      </c>
-      <c r="AM20" s="10" t="s">
-        <v>307</v>
-      </c>
-      <c r="AN20" s="9">
-        <v>9098</v>
-      </c>
-      <c r="AO20" s="10" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -5740,7 +5731,7 @@
         <v>9</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F21" s="9">
         <v>1</v>
@@ -5788,37 +5779,37 @@
         <v>9</v>
       </c>
       <c r="U21" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="V21" s="9">
+        <v>1221</v>
+      </c>
+      <c r="W21" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="X21" s="9">
+        <v>930</v>
+      </c>
+      <c r="Y21" s="10" t="s">
         <v>309</v>
-      </c>
-      <c r="V21" s="9">
-        <v>1219</v>
-      </c>
-      <c r="W21" s="10" t="s">
-        <v>310</v>
-      </c>
-      <c r="X21" s="9">
-        <v>918</v>
-      </c>
-      <c r="Y21" s="10" t="s">
-        <v>311</v>
       </c>
       <c r="Z21" s="9">
         <v>404</v>
       </c>
       <c r="AA21" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="AB21" s="9">
+        <v>2107</v>
+      </c>
+      <c r="AC21" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="AD21" s="9">
+        <v>1770</v>
+      </c>
+      <c r="AE21" s="10" t="s">
         <v>312</v>
-      </c>
-      <c r="AB21" s="9">
-        <v>2145</v>
-      </c>
-      <c r="AC21" s="10" t="s">
-        <v>313</v>
-      </c>
-      <c r="AD21" s="9">
-        <v>1763</v>
-      </c>
-      <c r="AE21" s="10" t="s">
-        <v>314</v>
       </c>
       <c r="AF21" s="9">
         <v>0</v>
@@ -5836,19 +5827,19 @@
         <v>64</v>
       </c>
       <c r="AK21" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="AL21" s="9">
+        <v>2991</v>
+      </c>
+      <c r="AM21" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN21" s="9">
+        <v>3000</v>
+      </c>
+      <c r="AO21" s="10" t="s">
         <v>315</v>
-      </c>
-      <c r="AL21" s="9">
-        <v>2982</v>
-      </c>
-      <c r="AM21" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="AN21" s="9">
-        <v>2991</v>
-      </c>
-      <c r="AO21" s="10" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -5859,13 +5850,13 @@
         <v>103</v>
       </c>
       <c r="C22" s="9">
-        <v>130759</v>
+        <v>130760</v>
       </c>
       <c r="D22" s="9">
         <v>421</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F22" s="9">
         <v>2</v>
@@ -5883,13 +5874,13 @@
         <v>54</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="L22" s="9">
         <v>57</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="N22" s="9">
         <v>42</v>
@@ -5901,7 +5892,7 @@
         <v>76</v>
       </c>
       <c r="Q22" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="R22" s="9">
         <v>0</v>
@@ -5913,37 +5904,37 @@
         <v>421</v>
       </c>
       <c r="U22" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="V22" s="9">
+        <v>9487</v>
+      </c>
+      <c r="W22" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="V22" s="9">
-        <v>9402</v>
-      </c>
-      <c r="W22" s="10" t="s">
+      <c r="X22" s="9">
+        <v>19177</v>
+      </c>
+      <c r="Y22" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="Z22" s="9">
+        <v>9969</v>
+      </c>
+      <c r="AA22" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="X22" s="9">
-        <v>19022</v>
-      </c>
-      <c r="Y22" s="10" t="s">
+      <c r="AB22" s="9">
+        <v>64041</v>
+      </c>
+      <c r="AC22" s="10" t="s">
         <v>321</v>
       </c>
-      <c r="Z22" s="9">
-        <v>9885</v>
-      </c>
-      <c r="AA22" s="10" t="s">
+      <c r="AD22" s="9">
+        <v>14879</v>
+      </c>
+      <c r="AE22" s="10" t="s">
         <v>322</v>
-      </c>
-      <c r="AB22" s="9">
-        <v>63865</v>
-      </c>
-      <c r="AC22" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="AD22" s="9">
-        <v>14788</v>
-      </c>
-      <c r="AE22" s="10" t="s">
-        <v>324</v>
       </c>
       <c r="AF22" s="9">
         <v>2</v>
@@ -5961,19 +5952,19 @@
         <v>7218</v>
       </c>
       <c r="AK22" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="AL22" s="9">
+        <v>24366</v>
+      </c>
+      <c r="AM22" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="AN22" s="9">
+        <v>24787</v>
+      </c>
+      <c r="AO22" s="10" t="s">
         <v>325</v>
-      </c>
-      <c r="AL22" s="9">
-        <v>24190</v>
-      </c>
-      <c r="AM22" s="10" t="s">
-        <v>326</v>
-      </c>
-      <c r="AN22" s="9">
-        <v>24611</v>
-      </c>
-      <c r="AO22" s="10" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -5990,7 +5981,7 @@
         <v>43</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
@@ -6038,37 +6029,37 @@
         <v>43</v>
       </c>
       <c r="U23" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="V23" s="9">
-        <v>3918</v>
+        <v>3936</v>
       </c>
       <c r="W23" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="X23" s="9">
+        <v>3344</v>
+      </c>
+      <c r="Y23" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="Z23" s="9">
+        <v>3182</v>
+      </c>
+      <c r="AA23" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="X23" s="9">
-        <v>3338</v>
-      </c>
-      <c r="Y23" s="10" t="s">
+      <c r="AB23" s="9">
+        <v>3561</v>
+      </c>
+      <c r="AC23" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="Z23" s="9">
-        <v>3173</v>
-      </c>
-      <c r="AA23" s="10" t="s">
+      <c r="AD23" s="9">
+        <v>3342</v>
+      </c>
+      <c r="AE23" s="10" t="s">
         <v>330</v>
-      </c>
-      <c r="AB23" s="9">
-        <v>3560</v>
-      </c>
-      <c r="AC23" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="AD23" s="9">
-        <v>3323</v>
-      </c>
-      <c r="AE23" s="10" t="s">
-        <v>332</v>
       </c>
       <c r="AF23" s="9">
         <v>0</v>
@@ -6086,19 +6077,19 @@
         <v>284</v>
       </c>
       <c r="AK23" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="AL23" s="9">
+        <v>7278</v>
+      </c>
+      <c r="AM23" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="AN23" s="9">
+        <v>7321</v>
+      </c>
+      <c r="AO23" s="10" t="s">
         <v>333</v>
-      </c>
-      <c r="AL23" s="9">
-        <v>7241</v>
-      </c>
-      <c r="AM23" s="10" t="s">
-        <v>334</v>
-      </c>
-      <c r="AN23" s="9">
-        <v>7284</v>
-      </c>
-      <c r="AO23" s="10" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -6109,7 +6100,7 @@
         <v>112</v>
       </c>
       <c r="C24" s="12">
-        <v>760551</v>
+        <v>760553</v>
       </c>
       <c r="D24" s="12">
         <v>1157</v>
@@ -6166,31 +6157,31 @@
         <v>190</v>
       </c>
       <c r="V24" s="12">
-        <v>89908</v>
+        <v>90494</v>
       </c>
       <c r="W24" s="13" t="s">
         <v>194</v>
       </c>
       <c r="X24" s="12">
-        <v>135657</v>
+        <v>136586</v>
       </c>
       <c r="Y24" s="13" t="s">
         <v>195</v>
       </c>
       <c r="Z24" s="12">
-        <v>61370</v>
+        <v>61715</v>
       </c>
       <c r="AA24" s="13" t="s">
         <v>196</v>
       </c>
       <c r="AB24" s="12">
-        <v>332574</v>
+        <v>332900</v>
       </c>
       <c r="AC24" s="13" t="s">
         <v>197</v>
       </c>
       <c r="AD24" s="12">
-        <v>120619</v>
+        <v>121644</v>
       </c>
       <c r="AE24" s="13" t="s">
         <v>198</v>
@@ -6214,13 +6205,13 @@
         <v>199</v>
       </c>
       <c r="AL24" s="12">
-        <v>210527</v>
+        <v>212138</v>
       </c>
       <c r="AM24" s="13" t="s">
         <v>200</v>
       </c>
       <c r="AN24" s="12">
-        <v>211684</v>
+        <v>213295</v>
       </c>
       <c r="AO24" s="13" t="s">
         <v>201</v>
@@ -6273,10 +6264,10 @@
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
@@ -6320,10 +6311,10 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="16"/>
@@ -6406,7 +6397,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6450,13 +6441,13 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
@@ -6483,31 +6474,31 @@
         <v>123</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="K5" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="L5" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="M5" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="N5" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="O5" s="3" t="s">
         <v>349</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6571,34 +6562,34 @@
         <v>8011</v>
       </c>
       <c r="E7" s="6">
-        <v>751011</v>
+        <v>751013</v>
       </c>
       <c r="F7" s="6">
-        <v>760551</v>
+        <v>760553</v>
       </c>
       <c r="G7" s="6">
-        <v>1321</v>
+        <v>1327</v>
       </c>
       <c r="H7" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="I7" s="6">
+        <v>1154</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="K7" s="6">
+        <v>209745</v>
+      </c>
+      <c r="L7" s="7" t="s">
         <v>352</v>
-      </c>
-      <c r="I7" s="6">
-        <v>1131</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="K7" s="6">
-        <v>208174</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>354</v>
       </c>
       <c r="M7" s="6">
         <v>1058</v>
       </c>
       <c r="N7" s="6">
-        <v>211684</v>
+        <v>213284</v>
       </c>
       <c r="O7" s="7" t="s">
         <v>201</v>
@@ -6627,28 +6618,28 @@
         <v>30</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="I8" s="9">
         <v>57</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="K8" s="9">
-        <v>4102</v>
+        <v>4114</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="M8" s="9">
         <v>12</v>
       </c>
       <c r="N8" s="9">
-        <v>4201</v>
+        <v>4213</v>
       </c>
       <c r="O8" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6674,28 +6665,28 @@
         <v>67</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="I9" s="9">
         <v>15</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="K9" s="9">
-        <v>10912</v>
+        <v>11021</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="M9" s="9">
         <v>68</v>
       </c>
       <c r="N9" s="9">
-        <v>11062</v>
+        <v>11171</v>
       </c>
       <c r="O9" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6712,37 +6703,37 @@
         <v>951</v>
       </c>
       <c r="E10" s="9">
-        <v>92442</v>
+        <v>92443</v>
       </c>
       <c r="F10" s="9">
-        <v>93538</v>
+        <v>93539</v>
       </c>
       <c r="G10" s="9">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="I10" s="9">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>362</v>
+        <v>216</v>
       </c>
       <c r="K10" s="9">
-        <v>19503</v>
+        <v>19749</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>363</v>
+        <v>227</v>
       </c>
       <c r="M10" s="9">
         <v>108</v>
       </c>
       <c r="N10" s="9">
-        <v>19861</v>
+        <v>20113</v>
       </c>
       <c r="O10" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6768,28 +6759,28 @@
         <v>100</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="I11" s="9">
         <v>86</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="K11" s="9">
-        <v>31169</v>
+        <v>31351</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="M11" s="9">
         <v>191</v>
       </c>
       <c r="N11" s="9">
-        <v>31546</v>
+        <v>31728</v>
       </c>
       <c r="O11" s="10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6812,31 +6803,31 @@
         <v>131144</v>
       </c>
       <c r="G12" s="9">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="I12" s="9">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="K12" s="9">
-        <v>36625</v>
+        <v>36968</v>
       </c>
       <c r="L12" s="10" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="M12" s="9">
         <v>173</v>
       </c>
       <c r="N12" s="9">
-        <v>37093</v>
+        <v>37442</v>
       </c>
       <c r="O12" s="10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6862,28 +6853,28 @@
         <v>65</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="I13" s="9">
         <v>73</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="K13" s="9">
-        <v>12580</v>
+        <v>12667</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="M13" s="9">
         <v>43</v>
       </c>
       <c r="N13" s="9">
-        <v>12761</v>
+        <v>12848</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6909,28 +6900,28 @@
         <v>47</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="I14" s="9">
         <v>18</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="K14" s="9">
-        <v>8499</v>
+        <v>8642</v>
       </c>
       <c r="L14" s="10" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="M14" s="9">
         <v>58</v>
       </c>
       <c r="N14" s="9">
-        <v>8622</v>
+        <v>8765</v>
       </c>
       <c r="O14" s="10" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6953,31 +6944,31 @@
         <v>19507</v>
       </c>
       <c r="G15" s="9">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>44</v>
+        <v>372</v>
       </c>
       <c r="I15" s="9">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="K15" s="9">
-        <v>9172</v>
+        <v>9257</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="M15" s="9">
         <v>13</v>
       </c>
       <c r="N15" s="9">
-        <v>9267</v>
+        <v>9354</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>273</v>
+        <v>375</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -7003,28 +6994,28 @@
         <v>54</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="I16" s="9">
         <v>52</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="K16" s="9">
-        <v>11868</v>
+        <v>11903</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="M16" s="9">
         <v>44</v>
       </c>
       <c r="N16" s="9">
-        <v>12018</v>
+        <v>12053</v>
       </c>
       <c r="O16" s="10" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -7050,28 +7041,28 @@
         <v>42</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="I17" s="9">
         <v>14</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="K17" s="9">
-        <v>14110</v>
+        <v>14213</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="M17" s="9">
         <v>81</v>
       </c>
       <c r="N17" s="9">
-        <v>14247</v>
+        <v>14350</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>290</v>
+        <v>382</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -7097,28 +7088,28 @@
         <v>31</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="I18" s="9">
         <v>21</v>
       </c>
       <c r="J18" s="10" t="s">
+        <v>384</v>
+      </c>
+      <c r="K18" s="9">
+        <v>6960</v>
+      </c>
+      <c r="L18" s="10" t="s">
         <v>385</v>
-      </c>
-      <c r="K18" s="9">
-        <v>6957</v>
-      </c>
-      <c r="L18" s="10" t="s">
-        <v>386</v>
       </c>
       <c r="M18" s="9">
         <v>13</v>
       </c>
       <c r="N18" s="9">
-        <v>7022</v>
+        <v>7025</v>
       </c>
       <c r="O18" s="10" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -7144,28 +7135,28 @@
         <v>26</v>
       </c>
       <c r="H19" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="I19" s="9">
+        <v>34</v>
+      </c>
+      <c r="J19" s="10" t="s">
         <v>387</v>
       </c>
-      <c r="I19" s="9">
-        <v>32</v>
-      </c>
-      <c r="J19" s="10" t="s">
+      <c r="K19" s="9">
+        <v>9039</v>
+      </c>
+      <c r="L19" s="10" t="s">
         <v>388</v>
-      </c>
-      <c r="K19" s="9">
-        <v>9025</v>
-      </c>
-      <c r="L19" s="10" t="s">
-        <v>389</v>
       </c>
       <c r="M19" s="9">
         <v>15</v>
       </c>
       <c r="N19" s="9">
-        <v>9098</v>
+        <v>9114</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>308</v>
+        <v>389</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -7200,7 +7191,7 @@
         <v>191</v>
       </c>
       <c r="K20" s="9">
-        <v>2977</v>
+        <v>2986</v>
       </c>
       <c r="L20" s="10" t="s">
         <v>391</v>
@@ -7209,10 +7200,10 @@
         <v>0</v>
       </c>
       <c r="N20" s="9">
-        <v>2991</v>
+        <v>3000</v>
       </c>
       <c r="O20" s="10" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -7229,25 +7220,25 @@
         <v>4256</v>
       </c>
       <c r="E21" s="9">
-        <v>125822</v>
+        <v>125823</v>
       </c>
       <c r="F21" s="9">
-        <v>130759</v>
+        <v>130760</v>
       </c>
       <c r="G21" s="9">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H21" s="10" t="s">
         <v>392</v>
       </c>
       <c r="I21" s="9">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="J21" s="10" t="s">
         <v>393</v>
       </c>
       <c r="K21" s="9">
-        <v>23566</v>
+        <v>23730</v>
       </c>
       <c r="L21" s="10" t="s">
         <v>394</v>
@@ -7256,10 +7247,10 @@
         <v>198</v>
       </c>
       <c r="N21" s="9">
-        <v>24611</v>
+        <v>24787</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -7288,13 +7279,13 @@
         <v>395</v>
       </c>
       <c r="I22" s="9">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J22" s="10" t="s">
         <v>396</v>
       </c>
       <c r="K22" s="9">
-        <v>7109</v>
+        <v>7145</v>
       </c>
       <c r="L22" s="10" t="s">
         <v>397</v>
@@ -7303,10 +7294,10 @@
         <v>41</v>
       </c>
       <c r="N22" s="9">
-        <v>7284</v>
+        <v>7321</v>
       </c>
       <c r="O22" s="10" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -7323,34 +7314,34 @@
         <v>8011</v>
       </c>
       <c r="E23" s="12">
-        <v>751011</v>
+        <v>751013</v>
       </c>
       <c r="F23" s="12">
-        <v>760551</v>
+        <v>760553</v>
       </c>
       <c r="G23" s="12">
-        <v>1321</v>
+        <v>1327</v>
       </c>
       <c r="H23" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="I23" s="12">
+        <v>1154</v>
+      </c>
+      <c r="J23" s="13" t="s">
+        <v>351</v>
+      </c>
+      <c r="K23" s="12">
+        <v>209745</v>
+      </c>
+      <c r="L23" s="13" t="s">
         <v>352</v>
-      </c>
-      <c r="I23" s="12">
-        <v>1131</v>
-      </c>
-      <c r="J23" s="13" t="s">
-        <v>353</v>
-      </c>
-      <c r="K23" s="12">
-        <v>208174</v>
-      </c>
-      <c r="L23" s="13" t="s">
-        <v>354</v>
       </c>
       <c r="M23" s="12">
         <v>1058</v>
       </c>
       <c r="N23" s="12">
-        <v>211684</v>
+        <v>213284</v>
       </c>
       <c r="O23" s="13" t="s">
         <v>201</v>
@@ -7931,7 +7922,7 @@
         <v>803</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="J11" s="9">
         <v>28963</v>
@@ -7984,7 +7975,7 @@
         <v>1003</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="J12" s="9">
         <v>44171</v>
@@ -8190,25 +8181,25 @@
         <v>43094</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>465</v>
+        <v>352</v>
       </c>
       <c r="H16" s="9">
         <v>1138</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="J16" s="9">
         <v>10596</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="L16" s="9">
         <v>36233</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="N16" s="9">
         <v>26</v>
@@ -8220,7 +8211,7 @@
         <v>117775</v>
       </c>
       <c r="Q16" s="10" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8237,31 +8228,31 @@
         <v>56825</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F17" s="9">
         <v>35112</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H17" s="9">
         <v>702</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="J17" s="9">
         <v>7088</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L17" s="9">
         <v>32118</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="N17" s="9">
         <v>5</v>
@@ -8273,7 +8264,7 @@
         <v>88943</v>
       </c>
       <c r="Q17" s="10" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8290,43 +8281,43 @@
         <v>37980</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F18" s="9">
         <v>24255</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H18" s="9">
         <v>577</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J18" s="9">
         <v>9769</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="L18" s="9">
         <v>22648</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="N18" s="9">
         <v>36</v>
       </c>
       <c r="O18" s="10" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="P18" s="9">
         <v>60628</v>
       </c>
       <c r="Q18" s="10" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8343,31 +8334,31 @@
         <v>58668</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F19" s="9">
         <v>24617</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H19" s="9">
         <v>578</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="J19" s="9">
         <v>7745</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="L19" s="9">
         <v>32802</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="N19" s="9">
         <v>13</v>
@@ -8379,7 +8370,7 @@
         <v>91470</v>
       </c>
       <c r="Q19" s="10" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8396,31 +8387,31 @@
         <v>27910</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F20" s="9">
         <v>15056</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H20" s="9">
         <v>228</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="J20" s="9">
         <v>2487</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="L20" s="9">
         <v>13687</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="N20" s="9">
         <v>6</v>
@@ -8432,7 +8423,7 @@
         <v>41597</v>
       </c>
       <c r="Q20" s="10" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8449,43 +8440,43 @@
         <v>2984</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F21" s="9">
         <v>3775</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H21" s="9">
         <v>106</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="J21" s="9">
         <v>1842</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="L21" s="9">
         <v>40027</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="N21" s="9">
         <v>18</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P21" s="9">
         <v>43011</v>
       </c>
       <c r="Q21" s="10" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8502,31 +8493,31 @@
         <v>10962</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F22" s="9">
         <v>6734</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H22" s="9">
         <v>576</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="J22" s="9">
         <v>737</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L22" s="9">
         <v>8801</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="N22" s="9">
         <v>6</v>
@@ -8538,7 +8529,7 @@
         <v>19763</v>
       </c>
       <c r="Q22" s="10" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8617,10 +8608,10 @@
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C26" s="16"/>
       <c r="D26" s="16"/>
@@ -8682,7 +8673,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -8740,10 +8731,10 @@
         <v>409</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>507</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>508</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
@@ -8751,7 +8742,7 @@
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -8759,10 +8750,10 @@
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
       <c r="R4" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="S4" s="3" t="s">
         <v>510</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8784,28 +8775,28 @@
         <v>154</v>
       </c>
       <c r="J5" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="L5" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="M5" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="N5" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="N5" s="3" t="s">
+      <c r="O5" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="O5" s="3" t="s">
+      <c r="P5" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="P5" s="3" t="s">
+      <c r="Q5" s="3" t="s">
         <v>518</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>519</v>
       </c>
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
@@ -8877,28 +8868,28 @@
         <v>33</v>
       </c>
       <c r="C7" s="6">
-        <v>760551</v>
+        <v>760553</v>
       </c>
       <c r="D7" s="6">
         <v>2153713</v>
       </c>
       <c r="E7" s="6">
-        <v>2914264</v>
+        <v>2914266</v>
       </c>
       <c r="F7" s="6">
-        <v>91065</v>
+        <v>91651</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H7" s="6">
-        <v>120619</v>
+        <v>121644</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>198</v>
       </c>
       <c r="J7" s="6">
-        <v>211684</v>
+        <v>213295</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>201</v>
@@ -8922,10 +8913,10 @@
         <v>418</v>
       </c>
       <c r="R7" s="6">
-        <v>2001958</v>
+        <v>2003569</v>
       </c>
       <c r="S7" s="7" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8945,22 +8936,22 @@
         <v>115412</v>
       </c>
       <c r="F8" s="9">
-        <v>2065</v>
+        <v>2071</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H8" s="9">
-        <v>2136</v>
+        <v>2142</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="J8" s="9">
-        <v>4201</v>
+        <v>4213</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L8" s="9">
         <v>60393</v>
@@ -8981,10 +8972,10 @@
         <v>424</v>
       </c>
       <c r="R8" s="9">
-        <v>95493</v>
+        <v>95505</v>
       </c>
       <c r="S8" s="10" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9004,22 +8995,22 @@
         <v>229367</v>
       </c>
       <c r="F9" s="9">
-        <v>5221</v>
+        <v>5254</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H9" s="9">
-        <v>5841</v>
+        <v>5917</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J9" s="9">
-        <v>11062</v>
+        <v>11171</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="L9" s="9">
         <v>78248</v>
@@ -9040,10 +9031,10 @@
         <v>430</v>
       </c>
       <c r="R9" s="9">
-        <v>148753</v>
+        <v>148862</v>
       </c>
       <c r="S9" s="10" t="s">
-        <v>525</v>
+        <v>392</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9054,31 +9045,31 @@
         <v>48</v>
       </c>
       <c r="C10" s="9">
-        <v>93538</v>
+        <v>93539</v>
       </c>
       <c r="D10" s="9">
         <v>201989</v>
       </c>
       <c r="E10" s="9">
-        <v>295527</v>
+        <v>295528</v>
       </c>
       <c r="F10" s="9">
-        <v>5941</v>
+        <v>6019</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>526</v>
+        <v>46</v>
       </c>
       <c r="H10" s="9">
-        <v>13920</v>
+        <v>14094</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J10" s="9">
-        <v>19861</v>
+        <v>20113</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L10" s="9">
         <v>76398</v>
@@ -9099,10 +9090,10 @@
         <v>436</v>
       </c>
       <c r="R10" s="9">
-        <v>161133</v>
+        <v>161385</v>
       </c>
       <c r="S10" s="10" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9122,22 +9113,22 @@
         <v>474247</v>
       </c>
       <c r="F11" s="9">
-        <v>15021</v>
+        <v>15085</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>194</v>
+        <v>525</v>
       </c>
       <c r="H11" s="9">
-        <v>16525</v>
+        <v>16643</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J11" s="9">
-        <v>31546</v>
+        <v>31728</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L11" s="9">
         <v>175159</v>
@@ -9158,10 +9149,10 @@
         <v>441</v>
       </c>
       <c r="R11" s="9">
-        <v>334025</v>
+        <v>334207</v>
       </c>
       <c r="S11" s="10" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9181,22 +9172,22 @@
         <v>547278</v>
       </c>
       <c r="F12" s="9">
-        <v>14558</v>
+        <v>14665</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="H12" s="9">
-        <v>22535</v>
+        <v>22782</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J12" s="9">
-        <v>37093</v>
+        <v>37447</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L12" s="9">
         <v>211010</v>
@@ -9217,10 +9208,10 @@
         <v>446</v>
       </c>
       <c r="R12" s="9">
-        <v>384873</v>
+        <v>385227</v>
       </c>
       <c r="S12" s="10" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9240,22 +9231,22 @@
         <v>192251</v>
       </c>
       <c r="F13" s="9">
-        <v>4909</v>
+        <v>4945</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="H13" s="9">
-        <v>7852</v>
+        <v>7905</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="J13" s="9">
-        <v>12761</v>
+        <v>12850</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L13" s="9">
         <v>62565</v>
@@ -9276,10 +9267,10 @@
         <v>452</v>
       </c>
       <c r="R13" s="9">
-        <v>124379</v>
+        <v>124468</v>
       </c>
       <c r="S13" s="10" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9299,22 +9290,22 @@
         <v>170050</v>
       </c>
       <c r="F14" s="9">
-        <v>2575</v>
+        <v>2604</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="H14" s="9">
-        <v>6047</v>
+        <v>6161</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J14" s="9">
-        <v>8622</v>
+        <v>8765</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L14" s="9">
         <v>62396</v>
@@ -9335,10 +9326,10 @@
         <v>457</v>
       </c>
       <c r="R14" s="9">
-        <v>120919</v>
+        <v>121062</v>
       </c>
       <c r="S14" s="10" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9358,22 +9349,22 @@
         <v>133782</v>
       </c>
       <c r="F15" s="9">
-        <v>4184</v>
+        <v>4229</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H15" s="9">
-        <v>5083</v>
+        <v>5126</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J15" s="9">
-        <v>9267</v>
+        <v>9355</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="L15" s="9">
         <v>50777</v>
@@ -9394,10 +9385,10 @@
         <v>463</v>
       </c>
       <c r="R15" s="9">
-        <v>91925</v>
+        <v>92013</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9417,22 +9408,22 @@
         <v>172696</v>
       </c>
       <c r="F16" s="9">
-        <v>5813</v>
+        <v>5829</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="H16" s="9">
-        <v>6205</v>
+        <v>6225</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="J16" s="9">
-        <v>12018</v>
+        <v>12054</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="L16" s="9">
         <v>81542</v>
@@ -9444,19 +9435,19 @@
         <v>36233</v>
       </c>
       <c r="O16" s="10" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P16" s="9">
         <v>117775</v>
       </c>
       <c r="Q16" s="10" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="R16" s="9">
-        <v>129793</v>
+        <v>129829</v>
       </c>
       <c r="S16" s="10" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9476,46 +9467,46 @@
         <v>139743</v>
       </c>
       <c r="F17" s="9">
-        <v>8067</v>
+        <v>8119</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="H17" s="9">
-        <v>6180</v>
+        <v>6232</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="J17" s="9">
-        <v>14247</v>
+        <v>14351</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="L17" s="9">
         <v>56825</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="N17" s="9">
         <v>32118</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="P17" s="9">
         <v>88943</v>
       </c>
       <c r="Q17" s="10" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="R17" s="9">
-        <v>103190</v>
+        <v>103294</v>
       </c>
       <c r="S17" s="10" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9535,46 +9526,46 @@
         <v>91795</v>
       </c>
       <c r="F18" s="9">
-        <v>3157</v>
+        <v>3159</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="H18" s="9">
-        <v>3865</v>
+        <v>3866</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J18" s="9">
-        <v>7022</v>
+        <v>7025</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L18" s="9">
         <v>37980</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="N18" s="9">
         <v>22648</v>
       </c>
       <c r="O18" s="10" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="P18" s="9">
         <v>60628</v>
       </c>
       <c r="Q18" s="10" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="R18" s="9">
-        <v>67650</v>
+        <v>67653</v>
       </c>
       <c r="S18" s="10" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9594,46 +9585,46 @@
         <v>111370</v>
       </c>
       <c r="F19" s="9">
-        <v>4542</v>
+        <v>4555</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="H19" s="9">
-        <v>4556</v>
+        <v>4560</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="J19" s="9">
-        <v>9098</v>
+        <v>9115</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="L19" s="9">
         <v>58668</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="N19" s="9">
         <v>32802</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="P19" s="9">
         <v>91470</v>
       </c>
       <c r="Q19" s="10" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="R19" s="9">
-        <v>100568</v>
+        <v>100585</v>
       </c>
       <c r="S19" s="10" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9653,46 +9644,46 @@
         <v>56660</v>
       </c>
       <c r="F20" s="9">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="H20" s="9">
-        <v>1763</v>
+        <v>1770</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="J20" s="9">
-        <v>2991</v>
+        <v>3000</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="L20" s="9">
         <v>27910</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="N20" s="9">
         <v>13687</v>
       </c>
       <c r="O20" s="10" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="P20" s="9">
         <v>41597</v>
       </c>
       <c r="Q20" s="10" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="R20" s="9">
-        <v>44588</v>
+        <v>44597</v>
       </c>
       <c r="S20" s="10" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9703,55 +9694,55 @@
         <v>103</v>
       </c>
       <c r="C21" s="9">
-        <v>130759</v>
+        <v>130760</v>
       </c>
       <c r="D21" s="9">
         <v>12551</v>
       </c>
       <c r="E21" s="9">
-        <v>143310</v>
+        <v>143311</v>
       </c>
       <c r="F21" s="9">
-        <v>9823</v>
+        <v>9908</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>312</v>
+        <v>545</v>
       </c>
       <c r="H21" s="9">
-        <v>14788</v>
+        <v>14879</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J21" s="9">
-        <v>24611</v>
+        <v>24787</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="L21" s="9">
         <v>2984</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="N21" s="9">
         <v>40027</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="P21" s="9">
         <v>43011</v>
       </c>
       <c r="Q21" s="10" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="R21" s="9">
-        <v>67622</v>
+        <v>67798</v>
       </c>
       <c r="S21" s="10" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9771,46 +9762,46 @@
         <v>40776</v>
       </c>
       <c r="F22" s="9">
-        <v>3961</v>
+        <v>3979</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H22" s="9">
-        <v>3323</v>
+        <v>3342</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="J22" s="9">
-        <v>7284</v>
+        <v>7321</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="L22" s="9">
         <v>10962</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="N22" s="9">
         <v>8801</v>
       </c>
       <c r="O22" s="10" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="P22" s="9">
         <v>19763</v>
       </c>
       <c r="Q22" s="10" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="R22" s="9">
-        <v>27047</v>
+        <v>27084</v>
       </c>
       <c r="S22" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9821,28 +9812,28 @@
         <v>112</v>
       </c>
       <c r="C23" s="12">
-        <v>760551</v>
+        <v>760553</v>
       </c>
       <c r="D23" s="12">
         <v>2153713</v>
       </c>
       <c r="E23" s="12">
-        <v>2914264</v>
+        <v>2914266</v>
       </c>
       <c r="F23" s="12">
-        <v>91065</v>
+        <v>91651</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H23" s="12">
-        <v>120619</v>
+        <v>121644</v>
       </c>
       <c r="I23" s="13" t="s">
         <v>198</v>
       </c>
       <c r="J23" s="12">
-        <v>211684</v>
+        <v>213295</v>
       </c>
       <c r="K23" s="13" t="s">
         <v>201</v>
@@ -9866,10 +9857,10 @@
         <v>418</v>
       </c>
       <c r="R23" s="12">
-        <v>2001958</v>
+        <v>2003569</v>
       </c>
       <c r="S23" s="13" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
@@ -9897,10 +9888,10 @@
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
+        <v>549</v>
+      </c>
+      <c r="B26" s="16" t="s">
         <v>550</v>
-      </c>
-      <c r="B26" s="16" t="s">
-        <v>551</v>
       </c>
       <c r="C26" s="16"/>
       <c r="D26" s="16"/>
@@ -9922,10 +9913,10 @@
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
+        <v>551</v>
+      </c>
+      <c r="B27" s="16" t="s">
         <v>552</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>553</v>
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
@@ -9947,10 +9938,10 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
+        <v>553</v>
+      </c>
+      <c r="B28" s="16" t="s">
         <v>554</v>
-      </c>
-      <c r="B28" s="16" t="s">
-        <v>555</v>
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="16"/>
@@ -9972,10 +9963,10 @@
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
+        <v>555</v>
+      </c>
+      <c r="B29" s="16" t="s">
         <v>556</v>
-      </c>
-      <c r="B29" s="16" t="s">
-        <v>557</v>
       </c>
       <c r="C29" s="16"/>
       <c r="D29" s="16"/>
@@ -9997,10 +9988,10 @@
     </row>
     <row r="30" ht="24" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
+        <v>557</v>
+      </c>
+      <c r="B30" s="16" t="s">
         <v>558</v>
-      </c>
-      <c r="B30" s="16" t="s">
-        <v>559</v>
       </c>
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
@@ -10061,7 +10052,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -10089,19 +10080,19 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>563</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10135,19 +10126,19 @@
         <v>33</v>
       </c>
       <c r="C6" s="6">
-        <v>3268654</v>
+        <v>3271865</v>
       </c>
       <c r="D6" s="6">
-        <v>211684</v>
+        <v>213295</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="F6" s="6">
         <v>1790274</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10158,19 +10149,19 @@
         <v>38</v>
       </c>
       <c r="C7" s="9">
-        <v>134528</v>
+        <v>134545</v>
       </c>
       <c r="D7" s="9">
-        <v>4201</v>
+        <v>4213</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="F7" s="9">
         <v>91292</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10181,19 +10172,19 @@
         <v>43</v>
       </c>
       <c r="C8" s="9">
-        <v>244196</v>
+        <v>244433</v>
       </c>
       <c r="D8" s="9">
-        <v>11062</v>
+        <v>11171</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>569</v>
+        <v>61</v>
       </c>
       <c r="F8" s="9">
         <v>137691</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10204,19 +10195,19 @@
         <v>48</v>
       </c>
       <c r="C9" s="9">
-        <v>313359</v>
+        <v>313825</v>
       </c>
       <c r="D9" s="9">
-        <v>19861</v>
+        <v>20113</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F9" s="9">
         <v>141272</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10227,19 +10218,19 @@
         <v>53</v>
       </c>
       <c r="C10" s="9">
-        <v>524924</v>
+        <v>525385</v>
       </c>
       <c r="D10" s="9">
-        <v>31546</v>
+        <v>31728</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="F10" s="9">
         <v>302479</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10250,19 +10241,19 @@
         <v>58</v>
       </c>
       <c r="C11" s="9">
-        <v>619743</v>
+        <v>620306</v>
       </c>
       <c r="D11" s="9">
-        <v>37093</v>
+        <v>37447</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="F11" s="9">
         <v>347780</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10273,19 +10264,19 @@
         <v>63</v>
       </c>
       <c r="C12" s="9">
-        <v>224137</v>
+        <v>224329</v>
       </c>
       <c r="D12" s="9">
-        <v>12761</v>
+        <v>12850</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="F12" s="9">
         <v>111618</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10296,19 +10287,19 @@
         <v>68</v>
       </c>
       <c r="C13" s="9">
-        <v>191734</v>
+        <v>192011</v>
       </c>
       <c r="D13" s="9">
-        <v>8622</v>
+        <v>8765</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>71</v>
+        <v>576</v>
       </c>
       <c r="F13" s="9">
         <v>112297</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10319,19 +10310,19 @@
         <v>73</v>
       </c>
       <c r="C14" s="9">
-        <v>140580</v>
+        <v>140706</v>
       </c>
       <c r="D14" s="9">
-        <v>9267</v>
+        <v>9355</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="F14" s="9">
         <v>82658</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10342,19 +10333,19 @@
         <v>78</v>
       </c>
       <c r="C15" s="9">
-        <v>194958</v>
+        <v>195028</v>
       </c>
       <c r="D15" s="9">
-        <v>12018</v>
+        <v>12054</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="F15" s="9">
         <v>117775</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10365,19 +10356,19 @@
         <v>83</v>
       </c>
       <c r="C16" s="9">
-        <v>156435</v>
+        <v>156589</v>
       </c>
       <c r="D16" s="9">
-        <v>14247</v>
+        <v>14351</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="F16" s="9">
         <v>88943</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10388,19 +10379,19 @@
         <v>88</v>
       </c>
       <c r="C17" s="9">
-        <v>108839</v>
+        <v>108841</v>
       </c>
       <c r="D17" s="9">
-        <v>7022</v>
+        <v>7025</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="F17" s="9">
         <v>60628</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10411,19 +10402,19 @@
         <v>93</v>
       </c>
       <c r="C18" s="9">
-        <v>137871</v>
+        <v>137890</v>
       </c>
       <c r="D18" s="9">
-        <v>9098</v>
+        <v>9115</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="F18" s="9">
         <v>91470</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10434,19 +10425,19 @@
         <v>98</v>
       </c>
       <c r="C19" s="9">
-        <v>65829</v>
+        <v>65812</v>
       </c>
       <c r="D19" s="9">
-        <v>2991</v>
+        <v>3000</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>590</v>
+        <v>576</v>
       </c>
       <c r="F19" s="9">
         <v>41597</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10457,19 +10448,19 @@
         <v>103</v>
       </c>
       <c r="C20" s="9">
-        <v>166356</v>
+        <v>166947</v>
       </c>
       <c r="D20" s="9">
-        <v>24611</v>
+        <v>24787</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="F20" s="9">
         <v>43011</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10480,19 +10471,19 @@
         <v>107</v>
       </c>
       <c r="C21" s="9">
-        <v>45165</v>
+        <v>45218</v>
       </c>
       <c r="D21" s="9">
-        <v>7284</v>
+        <v>7321</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="F21" s="9">
         <v>19763</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10503,19 +10494,19 @@
         <v>112</v>
       </c>
       <c r="C22" s="12">
-        <v>3268654</v>
+        <v>3271865</v>
       </c>
       <c r="D22" s="12">
-        <v>211684</v>
+        <v>213295</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="F22" s="12">
         <v>1790274</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -10531,10 +10522,10 @@
     </row>
     <row r="25" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="C25" s="16"/>
       <c r="D25" s="16"/>
@@ -10567,7 +10558,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -10597,7 +10588,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -10609,22 +10600,22 @@
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>600</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>601</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>602</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>603</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11128,7 +11119,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -11168,22 +11159,22 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>607</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>608</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>609</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>610</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
@@ -11208,16 +11199,16 @@
         <v>154</v>
       </c>
       <c r="J5" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="L5" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="M5" s="3" t="s">
         <v>516</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11269,7 +11260,7 @@
         <v>33</v>
       </c>
       <c r="C7" s="6">
-        <v>760551</v>
+        <v>760553</v>
       </c>
       <c r="D7" s="6">
         <v>2491768</v>
@@ -11281,25 +11272,25 @@
         <v>1589</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="H7" s="6">
         <v>4969</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="J7" s="6">
         <v>981975</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="L7" s="6">
         <v>435779</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11322,25 +11313,25 @@
         <v>20</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="H8" s="9">
         <v>128</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="J8" s="9">
         <v>52096</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="L8" s="9">
         <v>23594</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11363,25 +11354,25 @@
         <v>128</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="H9" s="9">
         <v>383</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="J9" s="9">
         <v>77848</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="L9" s="9">
         <v>34391</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11392,7 +11383,7 @@
         <v>48</v>
       </c>
       <c r="C10" s="9">
-        <v>93538</v>
+        <v>93539</v>
       </c>
       <c r="D10" s="9">
         <v>247954</v>
@@ -11404,25 +11395,25 @@
         <v>211</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="H10" s="9">
         <v>1143</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="J10" s="9">
         <v>75923</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="L10" s="9">
         <v>31434</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11445,25 +11436,25 @@
         <v>356</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="H11" s="9">
         <v>423</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="J11" s="9">
         <v>174150</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="L11" s="9">
         <v>77081</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11486,25 +11477,25 @@
         <v>419</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="H12" s="9">
         <v>718</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="J12" s="9">
         <v>210315</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="L12" s="9">
         <v>89564</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11527,25 +11518,25 @@
         <v>131</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="H13" s="9">
         <v>214</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="J13" s="9">
         <v>62343</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="L13" s="9">
         <v>28866</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11568,25 +11559,25 @@
         <v>64</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="H14" s="9">
         <v>358</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="J14" s="9">
         <v>62082</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="L14" s="9">
         <v>32581</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11609,25 +11600,25 @@
         <v>24</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="H15" s="9">
         <v>294</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="J15" s="9">
         <v>42093</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="L15" s="9">
         <v>22536</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11650,25 +11641,25 @@
         <v>62</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="H16" s="9">
         <v>195</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="J16" s="9">
         <v>65586</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="L16" s="9">
         <v>22976</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11691,25 +11682,25 @@
         <v>33</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="H17" s="9">
         <v>349</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="J17" s="9">
         <v>43615</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="L17" s="9">
         <v>18224</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11732,25 +11723,25 @@
         <v>38</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="H18" s="9">
         <v>487</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="J18" s="9">
         <v>32980</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="L18" s="9">
         <v>16588</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11773,25 +11764,25 @@
         <v>19</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="H19" s="9">
         <v>105</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="J19" s="9">
         <v>50940</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>60</v>
+        <v>659</v>
       </c>
       <c r="L19" s="9">
         <v>24838</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11814,25 +11805,25 @@
         <v>10</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="H20" s="9">
         <v>65</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J20" s="9">
         <v>23640</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>664</v>
+        <v>528</v>
       </c>
       <c r="L20" s="9">
         <v>9946</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>286</v>
+        <v>662</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11843,7 +11834,7 @@
         <v>103</v>
       </c>
       <c r="C21" s="9">
-        <v>130759</v>
+        <v>130760</v>
       </c>
       <c r="D21" s="9">
         <v>15314</v>
@@ -11855,25 +11846,25 @@
         <v>46</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="H21" s="9">
         <v>94</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="J21" s="9">
         <v>2833</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="L21" s="9">
         <v>1041</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11896,25 +11887,25 @@
         <v>28</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="H22" s="9">
         <v>13</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>670</v>
+        <v>535</v>
       </c>
       <c r="J22" s="9">
         <v>5531</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="L22" s="9">
         <v>2119</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11925,7 +11916,7 @@
         <v>112</v>
       </c>
       <c r="C23" s="12">
-        <v>760551</v>
+        <v>760553</v>
       </c>
       <c r="D23" s="12">
         <v>2491768</v>
@@ -11937,25 +11928,25 @@
         <v>1589</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="H23" s="12">
         <v>4969</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="J23" s="12">
         <v>981975</v>
       </c>
       <c r="K23" s="13" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="L23" s="12">
         <v>435779</v>
       </c>
       <c r="M23" s="13" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
@@ -11977,10 +11968,10 @@
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="C26" s="16"/>
       <c r="D26" s="16"/>
@@ -11996,10 +11987,10 @@
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
@@ -12015,10 +12006,10 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="16"/>
@@ -12034,10 +12025,10 @@
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="C29" s="16"/>
       <c r="D29" s="16"/>

--- a/data/Export_Progres_Pendataan_Kabupaten_Kota.xlsx
+++ b/data/Export_Progres_Pendataan_Kabupaten_Kota.xlsx
@@ -18,12 +18,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="692">
   <si>
     <t>PROGRES PENDATAAN - PROGRES PENDATAAN</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 22 Agu 2026, 18.00 | Dicetak: 23 Agu 2026, 05.36</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 23 Agu 2026, 06.00 | Dicetak: 23 Agu 2026, 06.28</t>
   </si>
   <si>
     <t>Kode</t>
@@ -122,10 +122,10 @@
     <t>LAMPUNG</t>
   </si>
   <si>
-    <t>113,9</t>
-  </si>
-  <si>
-    <t>69,33</t>
+    <t>114,48</t>
+  </si>
+  <si>
+    <t>69,68</t>
   </si>
   <si>
     <t>4,18</t>
@@ -137,10 +137,10 @@
     <t>LAMPUNG BARAT</t>
   </si>
   <si>
-    <t>125,93</t>
-  </si>
-  <si>
-    <t>85,7</t>
+    <t>125,96</t>
+  </si>
+  <si>
+    <t>85,71</t>
   </si>
   <si>
     <t>1,48</t>
@@ -152,10 +152,10 @@
     <t>TANGGAMUS</t>
   </si>
   <si>
-    <t>113,2</t>
-  </si>
-  <si>
-    <t>71,62</t>
+    <t>113,78</t>
+  </si>
+  <si>
+    <t>71,99</t>
   </si>
   <si>
     <t>6,16</t>
@@ -167,10 +167,10 @@
     <t>LAMPUNG SELATAN</t>
   </si>
   <si>
-    <t>112,41</t>
-  </si>
-  <si>
-    <t>64,58</t>
+    <t>113,35</t>
+  </si>
+  <si>
+    <t>65,12</t>
   </si>
   <si>
     <t>5,55</t>
@@ -182,10 +182,10 @@
     <t>LAMPUNG TIMUR</t>
   </si>
   <si>
-    <t>108,83</t>
-  </si>
-  <si>
-    <t>67,4</t>
+    <t>109,28</t>
+  </si>
+  <si>
+    <t>67,68</t>
   </si>
   <si>
     <t>3,83</t>
@@ -197,10 +197,10 @@
     <t>LAMPUNG TENGAH</t>
   </si>
   <si>
-    <t>110,17</t>
-  </si>
-  <si>
-    <t>68,25</t>
+    <t>110,81</t>
+  </si>
+  <si>
+    <t>68,66</t>
   </si>
   <si>
     <t>4,25</t>
@@ -212,10 +212,10 @@
     <t>LAMPUNG UTARA</t>
   </si>
   <si>
-    <t>116,76</t>
-  </si>
-  <si>
-    <t>67,27</t>
+    <t>117,2</t>
+  </si>
+  <si>
+    <t>67,59</t>
   </si>
   <si>
     <t>1,74</t>
@@ -227,10 +227,10 @@
     <t>WAY KANAN</t>
   </si>
   <si>
-    <t>116,08</t>
-  </si>
-  <si>
-    <t>70,43</t>
+    <t>116,94</t>
+  </si>
+  <si>
+    <t>70,96</t>
   </si>
   <si>
     <t>4,22</t>
@@ -242,10 +242,10 @@
     <t>TULANG BAWANG</t>
   </si>
   <si>
-    <t>117,21</t>
-  </si>
-  <si>
-    <t>70,72</t>
+    <t>117,83</t>
+  </si>
+  <si>
+    <t>71,14</t>
   </si>
   <si>
     <t>5,24</t>
@@ -257,10 +257,10 @@
     <t>PESAWARAN</t>
   </si>
   <si>
-    <t>124,83</t>
-  </si>
-  <si>
-    <t>84,77</t>
+    <t>125,24</t>
+  </si>
+  <si>
+    <t>85,03</t>
   </si>
   <si>
     <t>2,8</t>
@@ -272,10 +272,10 @@
     <t>PRINGSEWU</t>
   </si>
   <si>
-    <t>114,34</t>
-  </si>
-  <si>
-    <t>81,17</t>
+    <t>115,11</t>
+  </si>
+  <si>
+    <t>81,7</t>
   </si>
   <si>
     <t>5,58</t>
@@ -287,10 +287,10 @@
     <t>MESUJI</t>
   </si>
   <si>
-    <t>132,92</t>
-  </si>
-  <si>
-    <t>87,15</t>
+    <t>132,93</t>
+  </si>
+  <si>
+    <t>87,16</t>
   </si>
   <si>
     <t>0,06</t>
@@ -302,10 +302,10 @@
     <t>TULANG BAWANG BARAT</t>
   </si>
   <si>
-    <t>129,46</t>
-  </si>
-  <si>
-    <t>87,63</t>
+    <t>129,85</t>
+  </si>
+  <si>
+    <t>87,87</t>
   </si>
   <si>
     <t>0,63</t>
@@ -317,10 +317,10 @@
     <t>PESISIR BARAT</t>
   </si>
   <si>
-    <t>130,77</t>
-  </si>
-  <si>
-    <t>94,69</t>
+    <t>131,13</t>
+  </si>
+  <si>
+    <t>94,94</t>
   </si>
   <si>
     <t>0,74</t>
@@ -332,10 +332,10 @@
     <t>BANDAR LAMPUNG</t>
   </si>
   <si>
-    <t>106,2</t>
-  </si>
-  <si>
-    <t>51,15</t>
+    <t>106,78</t>
+  </si>
+  <si>
+    <t>51,42</t>
   </si>
   <si>
     <t>5,6</t>
@@ -347,10 +347,10 @@
     <t>METRO</t>
   </si>
   <si>
-    <t>109,88</t>
-  </si>
-  <si>
-    <t>67,31</t>
+    <t>110,4</t>
+  </si>
+  <si>
+    <t>67,63</t>
   </si>
   <si>
     <t>6,18</t>
@@ -1079,546 +1079,597 @@
     <t>Persentase Total Usaha BKU</t>
   </si>
   <si>
-    <t>87,18</t>
-  </si>
-  <si>
-    <t>14,7</t>
-  </si>
-  <si>
-    <t>130,43</t>
-  </si>
-  <si>
-    <t>37,75</t>
-  </si>
-  <si>
-    <t>35,22</t>
+    <t>87,25</t>
+  </si>
+  <si>
+    <t>14,93</t>
+  </si>
+  <si>
+    <t>28,56</t>
+  </si>
+  <si>
+    <t>28,68</t>
+  </si>
+  <si>
+    <t>134,78</t>
+  </si>
+  <si>
+    <t>39,07</t>
+  </si>
+  <si>
+    <t>35,29</t>
+  </si>
+  <si>
+    <t>35,63</t>
   </si>
   <si>
     <t>58,77</t>
   </si>
   <si>
-    <t>20,78</t>
-  </si>
-  <si>
-    <t>19,47</t>
-  </si>
-  <si>
-    <t>108,97</t>
-  </si>
-  <si>
-    <t>10,52</t>
+    <t>22,08</t>
+  </si>
+  <si>
+    <t>19,7</t>
+  </si>
+  <si>
+    <t>19,9</t>
+  </si>
+  <si>
+    <t>109,66</t>
+  </si>
+  <si>
+    <t>10,62</t>
+  </si>
+  <si>
+    <t>22,28</t>
+  </si>
+  <si>
+    <t>22,42</t>
+  </si>
+  <si>
+    <t>127,85</t>
+  </si>
+  <si>
+    <t>22,94</t>
+  </si>
+  <si>
+    <t>25,31</t>
+  </si>
+  <si>
+    <t>25,51</t>
+  </si>
+  <si>
+    <t>107,19</t>
+  </si>
+  <si>
+    <t>18,5</t>
+  </si>
+  <si>
+    <t>29,16</t>
+  </si>
+  <si>
+    <t>29,32</t>
+  </si>
+  <si>
+    <t>86,67</t>
+  </si>
+  <si>
+    <t>19,33</t>
+  </si>
+  <si>
+    <t>20,33</t>
+  </si>
+  <si>
+    <t>20,48</t>
+  </si>
+  <si>
+    <t>137,14</t>
+  </si>
+  <si>
+    <t>16,28</t>
+  </si>
+  <si>
+    <t>21,88</t>
+  </si>
+  <si>
+    <t>22,1</t>
+  </si>
+  <si>
+    <t>113,73</t>
+  </si>
+  <si>
+    <t>7,48</t>
+  </si>
+  <si>
+    <t>49,54</t>
+  </si>
+  <si>
+    <t>49,01</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>39,39</t>
+  </si>
+  <si>
+    <t>66,19</t>
+  </si>
+  <si>
+    <t>66,35</t>
+  </si>
+  <si>
+    <t>131,25</t>
+  </si>
+  <si>
+    <t>144,44</t>
+  </si>
+  <si>
+    <t>65,79</t>
+  </si>
+  <si>
+    <t>66,29</t>
+  </si>
+  <si>
+    <t>111,11</t>
+  </si>
+  <si>
+    <t>36,84</t>
+  </si>
+  <si>
+    <t>63,32</t>
+  </si>
+  <si>
+    <t>63,42</t>
+  </si>
+  <si>
+    <t>113,04</t>
+  </si>
+  <si>
+    <t>57,58</t>
+  </si>
+  <si>
+    <t>92,94</t>
+  </si>
+  <si>
+    <t>56,65</t>
+  </si>
+  <si>
+    <t>56,8</t>
+  </si>
+  <si>
+    <t>65,2</t>
+  </si>
+  <si>
+    <t>10,15</t>
+  </si>
+  <si>
+    <t>19,17</t>
+  </si>
+  <si>
+    <t>19,26</t>
+  </si>
+  <si>
+    <t>122,5</t>
+  </si>
+  <si>
+    <t>46,35</t>
+  </si>
+  <si>
+    <t>43,6</t>
+  </si>
+  <si>
+    <t>44,07</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha (UB/UM/UMK)</t>
+  </si>
+  <si>
+    <t>Jumlah prelist usaha yang berhasil didata (keberadaan ditemukan, baru, pindah dapat ditelusuri) berdasarkan skala usaha, untuk usaha baru didekati dengan omzet sebagai berikut: UB (lebih dari 50 Milyar), UM (15-50 Milyar), UMK - Kecil (2-15 Milyar), UMK - Mikro (0-2 Milyar).</t>
+  </si>
+  <si>
+    <t>Tidak Dapat Diklasifikasikan (Kolom 10)</t>
+  </si>
+  <si>
+    <t>Usaha baru dengan nilai omzet/pendapatan kosong sehingga tidak dapat diklasifikasikan skala usahanya, misalnya usaha unit pembantu/penunjang.</t>
+  </si>
+  <si>
+    <t>Persentase Jumlah UB</t>
+  </si>
+  <si>
+    <t>Persentase hasil bagi jumlah UB yang berhasil didata dengan jumlah prelist UB (kolom 3).</t>
+  </si>
+  <si>
+    <t>Persentase Jumlah UM</t>
+  </si>
+  <si>
+    <t>Persentase hasil bagi jumlah UM yang berhasil didata dengan jumlah prelist UM (kolom 4).</t>
+  </si>
+  <si>
+    <t>Persentase Jumlah UMK</t>
+  </si>
+  <si>
+    <t>Persentase hasil bagi jumlah UMK yang berhasil didata dengan jumlah prelist UMK (kolom 5).</t>
+  </si>
+  <si>
+    <t>PROGRES PENDATAAN - USAHA KELUARGA</t>
+  </si>
+  <si>
+    <t>Jumlah Prelist Usaha Keluarga (ST2023 + UMKM)</t>
+  </si>
+  <si>
+    <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha dalam Keluarga (Ditemukan + Baru)</t>
+  </si>
+  <si>
+    <t>Persentase Usaha dalam Keluarga (Ditemukan + Baru)</t>
+  </si>
+  <si>
+    <t>49,43</t>
+  </si>
+  <si>
+    <t>24,59</t>
+  </si>
+  <si>
+    <t>0,4</t>
+  </si>
+  <si>
+    <t>9,56</t>
+  </si>
+  <si>
+    <t>34,58</t>
+  </si>
+  <si>
+    <t>84,01</t>
+  </si>
+  <si>
+    <t>58,56</t>
+  </si>
+  <si>
+    <t>20,26</t>
+  </si>
+  <si>
+    <t>0,53</t>
+  </si>
+  <si>
+    <t>8,88</t>
+  </si>
+  <si>
+    <t>29,96</t>
+  </si>
+  <si>
+    <t>88,52</t>
+  </si>
+  <si>
+    <t>46,02</t>
+  </si>
+  <si>
+    <t>0,47</t>
+  </si>
+  <si>
+    <t>7,95</t>
+  </si>
+  <si>
+    <t>34,99</t>
+  </si>
+  <si>
+    <t>81,01</t>
+  </si>
+  <si>
+    <t>38,47</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>15,16</t>
+  </si>
+  <si>
+    <t>32,65</t>
+  </si>
+  <si>
+    <t>71,13</t>
+  </si>
+  <si>
+    <t>51,01</t>
+  </si>
+  <si>
+    <t>23,22</t>
+  </si>
+  <si>
+    <t>8,36</t>
+  </si>
+  <si>
+    <t>37,18</t>
+  </si>
+  <si>
+    <t>88,2</t>
+  </si>
+  <si>
+    <t>51,34</t>
+  </si>
+  <si>
+    <t>22,63</t>
+  </si>
+  <si>
+    <t>10,63</t>
+  </si>
+  <si>
+    <t>33,28</t>
+  </si>
+  <si>
+    <t>84,62</t>
+  </si>
+  <si>
+    <t>49,2</t>
+  </si>
+  <si>
+    <t>20,52</t>
+  </si>
+  <si>
+    <t>0,22</t>
+  </si>
+  <si>
+    <t>17,44</t>
+  </si>
+  <si>
+    <t>38,59</t>
+  </si>
+  <si>
+    <t>87,79</t>
+  </si>
+  <si>
+    <t>49,28</t>
+  </si>
+  <si>
+    <t>23,34</t>
+  </si>
+  <si>
+    <t>8,42</t>
+  </si>
+  <si>
+    <t>39,31</t>
+  </si>
+  <si>
+    <t>88,6</t>
+  </si>
+  <si>
+    <t>45,12</t>
+  </si>
+  <si>
+    <t>27,45</t>
+  </si>
+  <si>
+    <t>0,52</t>
+  </si>
+  <si>
+    <t>4,9</t>
+  </si>
+  <si>
+    <t>28,29</t>
+  </si>
+  <si>
+    <t>73,41</t>
+  </si>
+  <si>
+    <t>53,2</t>
+  </si>
+  <si>
+    <t>28,17</t>
+  </si>
+  <si>
+    <t>0,75</t>
+  </si>
+  <si>
+    <t>6,84</t>
+  </si>
+  <si>
+    <t>23,65</t>
+  </si>
+  <si>
+    <t>76,85</t>
+  </si>
+  <si>
+    <t>48,85</t>
+  </si>
+  <si>
+    <t>30,27</t>
+  </si>
+  <si>
+    <t>0,61</t>
+  </si>
+  <si>
+    <t>6,08</t>
+  </si>
+  <si>
+    <t>27,6</t>
+  </si>
+  <si>
+    <t>76,45</t>
+  </si>
+  <si>
+    <t>47,07</t>
+  </si>
+  <si>
+    <t>30,16</t>
+  </si>
+  <si>
+    <t>0,71</t>
+  </si>
+  <si>
+    <t>12,03</t>
+  </si>
+  <si>
+    <t>28,08</t>
+  </si>
+  <si>
+    <t>75,15</t>
+  </si>
+  <si>
+    <t>57,94</t>
+  </si>
+  <si>
+    <t>24,31</t>
+  </si>
+  <si>
+    <t>0,57</t>
+  </si>
+  <si>
+    <t>7,62</t>
+  </si>
+  <si>
+    <t>32,42</t>
+  </si>
+  <si>
+    <t>90,36</t>
+  </si>
+  <si>
+    <t>54,53</t>
+  </si>
+  <si>
+    <t>29,41</t>
+  </si>
+  <si>
+    <t>0,45</t>
+  </si>
+  <si>
+    <t>4,86</t>
+  </si>
+  <si>
+    <t>26,77</t>
+  </si>
+  <si>
+    <t>81,3</t>
+  </si>
+  <si>
+    <t>24,07</t>
+  </si>
+  <si>
+    <t>30,73</t>
+  </si>
+  <si>
+    <t>0,85</t>
+  </si>
+  <si>
+    <t>14,75</t>
+  </si>
+  <si>
+    <t>321,93</t>
+  </si>
+  <si>
+    <t>346</t>
+  </si>
+  <si>
+    <t>46,5</t>
+  </si>
+  <si>
+    <t>2,45</t>
+  </si>
+  <si>
+    <t>3,11</t>
+  </si>
+  <si>
+    <t>37,42</t>
+  </si>
+  <si>
+    <t>83,91</t>
+  </si>
+  <si>
+    <t>Persentase Kolom 4 9</t>
+  </si>
+  <si>
+    <t>PROGRES PENDATAAN - KESELURUHAN USAHA</t>
+  </si>
+  <si>
+    <t>Total Prelist Usaha dan Usaha Keluarga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USAHA BKU </t>
+  </si>
+  <si>
+    <t>USAHA DALAM KELUARGA</t>
+  </si>
+  <si>
+    <t>Total Usaha</t>
+  </si>
+  <si>
+    <t>Persentase Total Usaha</t>
+  </si>
+  <si>
+    <t>Subtotal</t>
+  </si>
+  <si>
+    <t>Persentase Subtotal</t>
+  </si>
+  <si>
+    <t>Ditemukan​</t>
+  </si>
+  <si>
+    <t>Persentase Ditemukan​</t>
+  </si>
+  <si>
+    <t>Baru​</t>
+  </si>
+  <si>
+    <t>Persentase Baru​</t>
+  </si>
+  <si>
+    <t>Subtotal​</t>
+  </si>
+  <si>
+    <t>Persentase Subtotal​</t>
+  </si>
+  <si>
+    <t>12,17</t>
+  </si>
+  <si>
+    <t>69,49</t>
+  </si>
+  <si>
+    <t>83,05</t>
+  </si>
+  <si>
+    <t>9,24</t>
+  </si>
+  <si>
+    <t>65,64</t>
+  </si>
+  <si>
+    <t>6,57</t>
+  </si>
+  <si>
+    <t>55,58</t>
+  </si>
+  <si>
+    <t>11,97</t>
+  </si>
+  <si>
+    <t>71,33</t>
+  </si>
+  <si>
+    <t>11,3</t>
+  </si>
+  <si>
+    <t>71,28</t>
+  </si>
+  <si>
+    <t>7,84</t>
+  </si>
+  <si>
+    <t>65,37</t>
+  </si>
+  <si>
+    <t>6,39</t>
+  </si>
+  <si>
+    <t>72,32</t>
   </si>
   <si>
     <t>21,86</t>
   </si>
   <si>
-    <t>127,85</t>
-  </si>
-  <si>
-    <t>22,68</t>
-  </si>
-  <si>
-    <t>25,05</t>
-  </si>
-  <si>
-    <t>107,91</t>
-  </si>
-  <si>
-    <t>28,78</t>
-  </si>
-  <si>
-    <t>85,33</t>
-  </si>
-  <si>
-    <t>19,33</t>
-  </si>
-  <si>
-    <t>20,21</t>
-  </si>
-  <si>
-    <t>137,14</t>
-  </si>
-  <si>
-    <t>14,73</t>
-  </si>
-  <si>
-    <t>21,4</t>
-  </si>
-  <si>
-    <t>113,73</t>
-  </si>
-  <si>
-    <t>7,2</t>
-  </si>
-  <si>
-    <t>48,98</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>39,39</t>
-  </si>
-  <si>
-    <t>65,84</t>
-  </si>
-  <si>
-    <t>131,25</t>
-  </si>
-  <si>
-    <t>155,56</t>
-  </si>
-  <si>
-    <t>65,05</t>
-  </si>
-  <si>
-    <t>114,81</t>
-  </si>
-  <si>
-    <t>36,84</t>
-  </si>
-  <si>
-    <t>63,27</t>
-  </si>
-  <si>
-    <t>113,04</t>
-  </si>
-  <si>
-    <t>56,06</t>
-  </si>
-  <si>
-    <t>92,3</t>
-  </si>
-  <si>
-    <t>55,96</t>
-  </si>
-  <si>
-    <t>65,2</t>
-  </si>
-  <si>
-    <t>10,03</t>
-  </si>
-  <si>
-    <t>19,03</t>
-  </si>
-  <si>
-    <t>122,5</t>
-  </si>
-  <si>
-    <t>46,35</t>
-  </si>
-  <si>
-    <t>43,21</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha (UB/UM/UMK)</t>
-  </si>
-  <si>
-    <t>Jumlah prelist usaha yang berhasil didata (keberadaan ditemukan, baru, pindah dapat ditelusuri) berdasarkan skala usaha, untuk usaha baru didekati dengan omzet sebagai berikut: UB (lebih dari 50 Milyar), UM (15-50 Milyar), UMK - Kecil (2-15 Milyar), UMK - Mikro (0-2 Milyar).</t>
-  </si>
-  <si>
-    <t>Tidak Dapat Diklasifikasikan (Kolom 10)</t>
-  </si>
-  <si>
-    <t>Usaha baru dengan nilai omzet/pendapatan kosong sehingga tidak dapat diklasifikasikan skala usahanya, misalnya usaha unit pembantu/penunjang.</t>
-  </si>
-  <si>
-    <t>Persentase Jumlah UB</t>
-  </si>
-  <si>
-    <t>Persentase hasil bagi jumlah UB yang berhasil didata dengan jumlah prelist UB (kolom 3).</t>
-  </si>
-  <si>
-    <t>Persentase Jumlah UM</t>
-  </si>
-  <si>
-    <t>Persentase hasil bagi jumlah UM yang berhasil didata dengan jumlah prelist UM (kolom 4).</t>
-  </si>
-  <si>
-    <t>Persentase Jumlah UMK</t>
-  </si>
-  <si>
-    <t>Persentase hasil bagi jumlah UMK yang berhasil didata dengan jumlah prelist UMK (kolom 5).</t>
-  </si>
-  <si>
-    <t>PROGRES PENDATAAN - USAHA KELUARGA</t>
-  </si>
-  <si>
-    <t>Jumlah Prelist Usaha Keluarga (ST2023 + UMKM)</t>
-  </si>
-  <si>
-    <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha dalam Keluarga (Ditemukan + Baru)</t>
-  </si>
-  <si>
-    <t>Persentase Usaha dalam Keluarga (Ditemukan + Baru)</t>
-  </si>
-  <si>
-    <t>49,43</t>
-  </si>
-  <si>
-    <t>24,59</t>
-  </si>
-  <si>
-    <t>0,4</t>
-  </si>
-  <si>
-    <t>9,56</t>
-  </si>
-  <si>
-    <t>34,58</t>
-  </si>
-  <si>
-    <t>84,01</t>
-  </si>
-  <si>
-    <t>58,56</t>
-  </si>
-  <si>
-    <t>20,26</t>
-  </si>
-  <si>
-    <t>0,53</t>
-  </si>
-  <si>
-    <t>8,88</t>
-  </si>
-  <si>
-    <t>29,96</t>
-  </si>
-  <si>
-    <t>88,52</t>
-  </si>
-  <si>
-    <t>46,02</t>
-  </si>
-  <si>
-    <t>25,51</t>
-  </si>
-  <si>
-    <t>0,47</t>
-  </si>
-  <si>
-    <t>7,95</t>
-  </si>
-  <si>
-    <t>34,99</t>
-  </si>
-  <si>
-    <t>81,01</t>
-  </si>
-  <si>
-    <t>38,47</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>15,16</t>
-  </si>
-  <si>
-    <t>32,65</t>
-  </si>
-  <si>
-    <t>71,13</t>
-  </si>
-  <si>
-    <t>51,01</t>
-  </si>
-  <si>
-    <t>23,22</t>
-  </si>
-  <si>
-    <t>8,36</t>
-  </si>
-  <si>
-    <t>37,18</t>
-  </si>
-  <si>
-    <t>88,2</t>
-  </si>
-  <si>
-    <t>51,34</t>
-  </si>
-  <si>
-    <t>22,63</t>
-  </si>
-  <si>
-    <t>10,63</t>
-  </si>
-  <si>
-    <t>33,28</t>
-  </si>
-  <si>
-    <t>84,62</t>
-  </si>
-  <si>
-    <t>49,2</t>
-  </si>
-  <si>
-    <t>20,52</t>
-  </si>
-  <si>
-    <t>0,22</t>
-  </si>
-  <si>
-    <t>17,44</t>
-  </si>
-  <si>
-    <t>38,59</t>
-  </si>
-  <si>
-    <t>87,79</t>
-  </si>
-  <si>
-    <t>49,28</t>
-  </si>
-  <si>
-    <t>23,34</t>
-  </si>
-  <si>
-    <t>8,42</t>
-  </si>
-  <si>
-    <t>39,31</t>
-  </si>
-  <si>
-    <t>88,6</t>
-  </si>
-  <si>
-    <t>45,12</t>
-  </si>
-  <si>
-    <t>27,45</t>
-  </si>
-  <si>
-    <t>0,52</t>
-  </si>
-  <si>
-    <t>4,9</t>
-  </si>
-  <si>
-    <t>28,29</t>
-  </si>
-  <si>
-    <t>73,41</t>
-  </si>
-  <si>
-    <t>53,2</t>
-  </si>
-  <si>
-    <t>28,17</t>
-  </si>
-  <si>
-    <t>0,75</t>
-  </si>
-  <si>
-    <t>6,84</t>
-  </si>
-  <si>
-    <t>23,65</t>
-  </si>
-  <si>
-    <t>76,85</t>
-  </si>
-  <si>
-    <t>48,85</t>
-  </si>
-  <si>
-    <t>30,27</t>
-  </si>
-  <si>
-    <t>0,61</t>
-  </si>
-  <si>
-    <t>6,08</t>
-  </si>
-  <si>
-    <t>27,6</t>
-  </si>
-  <si>
-    <t>76,45</t>
-  </si>
-  <si>
-    <t>47,07</t>
-  </si>
-  <si>
-    <t>30,16</t>
-  </si>
-  <si>
-    <t>0,71</t>
-  </si>
-  <si>
-    <t>12,03</t>
-  </si>
-  <si>
-    <t>28,08</t>
-  </si>
-  <si>
-    <t>75,15</t>
-  </si>
-  <si>
-    <t>57,94</t>
-  </si>
-  <si>
-    <t>24,31</t>
-  </si>
-  <si>
-    <t>0,57</t>
-  </si>
-  <si>
-    <t>7,62</t>
-  </si>
-  <si>
-    <t>32,42</t>
-  </si>
-  <si>
-    <t>90,36</t>
-  </si>
-  <si>
-    <t>54,53</t>
-  </si>
-  <si>
-    <t>29,41</t>
-  </si>
-  <si>
-    <t>0,45</t>
-  </si>
-  <si>
-    <t>4,86</t>
-  </si>
-  <si>
-    <t>26,77</t>
-  </si>
-  <si>
-    <t>81,3</t>
-  </si>
-  <si>
-    <t>24,07</t>
-  </si>
-  <si>
-    <t>30,73</t>
-  </si>
-  <si>
-    <t>0,85</t>
-  </si>
-  <si>
-    <t>14,75</t>
-  </si>
-  <si>
-    <t>321,93</t>
-  </si>
-  <si>
-    <t>346</t>
-  </si>
-  <si>
-    <t>46,5</t>
-  </si>
-  <si>
-    <t>2,45</t>
-  </si>
-  <si>
-    <t>3,11</t>
-  </si>
-  <si>
-    <t>37,42</t>
-  </si>
-  <si>
-    <t>83,91</t>
-  </si>
-  <si>
-    <t>Persentase Kolom 4 9</t>
-  </si>
-  <si>
-    <t>PROGRES PENDATAAN - KESELURUHAN USAHA</t>
-  </si>
-  <si>
-    <t>Total Prelist Usaha dan Usaha Keluarga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USAHA BKU </t>
-  </si>
-  <si>
-    <t>USAHA DALAM KELUARGA</t>
-  </si>
-  <si>
-    <t>Total Usaha</t>
-  </si>
-  <si>
-    <t>Persentase Total Usaha</t>
-  </si>
-  <si>
-    <t>Subtotal</t>
-  </si>
-  <si>
-    <t>Persentase Subtotal</t>
-  </si>
-  <si>
-    <t>Ditemukan​</t>
-  </si>
-  <si>
-    <t>Persentase Ditemukan​</t>
-  </si>
-  <si>
-    <t>Baru​</t>
-  </si>
-  <si>
-    <t>Persentase Baru​</t>
-  </si>
-  <si>
-    <t>Subtotal​</t>
-  </si>
-  <si>
-    <t>Persentase Subtotal​</t>
-  </si>
-  <si>
-    <t>12,17</t>
-  </si>
-  <si>
-    <t>69,49</t>
-  </si>
-  <si>
-    <t>83,05</t>
-  </si>
-  <si>
-    <t>9,24</t>
-  </si>
-  <si>
-    <t>65,64</t>
-  </si>
-  <si>
-    <t>6,57</t>
-  </si>
-  <si>
-    <t>55,58</t>
-  </si>
-  <si>
-    <t>11,97</t>
-  </si>
-  <si>
-    <t>71,33</t>
-  </si>
-  <si>
-    <t>11,3</t>
-  </si>
-  <si>
-    <t>71,28</t>
-  </si>
-  <si>
-    <t>7,84</t>
-  </si>
-  <si>
-    <t>65,37</t>
-  </si>
-  <si>
-    <t>6,39</t>
-  </si>
-  <si>
-    <t>72,32</t>
-  </si>
-  <si>
     <t>69,77</t>
   </si>
   <si>
@@ -1767,9 +1818,6 @@
   </si>
   <si>
     <t>6,62</t>
-  </si>
-  <si>
-    <t>66,35</t>
   </si>
   <si>
     <t>4,57</t>
@@ -2728,13 +2776,13 @@
         <v>839468</v>
       </c>
       <c r="E7" s="6">
-        <v>3976831</v>
+        <v>3997214</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>34</v>
       </c>
       <c r="G7" s="6">
-        <v>2420504</v>
+        <v>2432893</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>35</v>
@@ -2772,13 +2820,13 @@
         <v>25106</v>
       </c>
       <c r="E8" s="9">
-        <v>122242</v>
+        <v>122268</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>39</v>
       </c>
       <c r="G8" s="9">
-        <v>83191</v>
+        <v>83200</v>
       </c>
       <c r="H8" s="10" t="s">
         <v>40</v>
@@ -2816,13 +2864,13 @@
         <v>59255</v>
       </c>
       <c r="E9" s="9">
-        <v>260856</v>
+        <v>262180</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>44</v>
       </c>
       <c r="G9" s="9">
-        <v>165046</v>
+        <v>165898</v>
       </c>
       <c r="H9" s="10" t="s">
         <v>45</v>
@@ -2860,13 +2908,13 @@
         <v>125729</v>
       </c>
       <c r="E10" s="9">
-        <v>490393</v>
+        <v>494508</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>49</v>
       </c>
       <c r="G10" s="9">
-        <v>281740</v>
+        <v>284085</v>
       </c>
       <c r="H10" s="10" t="s">
         <v>50</v>
@@ -2904,13 +2952,13 @@
         <v>95638</v>
       </c>
       <c r="E11" s="9">
-        <v>533213</v>
+        <v>535432</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>54</v>
       </c>
       <c r="G11" s="9">
-        <v>330239</v>
+        <v>331592</v>
       </c>
       <c r="H11" s="10" t="s">
         <v>55</v>
@@ -2948,13 +2996,13 @@
         <v>116963</v>
       </c>
       <c r="E12" s="9">
-        <v>639761</v>
+        <v>643492</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>59</v>
       </c>
       <c r="G12" s="9">
-        <v>396348</v>
+        <v>398720</v>
       </c>
       <c r="H12" s="10" t="s">
         <v>60</v>
@@ -2992,13 +3040,13 @@
         <v>54935</v>
       </c>
       <c r="E13" s="9">
-        <v>307447</v>
+        <v>308612</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>64</v>
       </c>
       <c r="G13" s="9">
-        <v>177145</v>
+        <v>177973</v>
       </c>
       <c r="H13" s="10" t="s">
         <v>65</v>
@@ -3036,13 +3084,13 @@
         <v>49142</v>
       </c>
       <c r="E14" s="9">
-        <v>217564</v>
+        <v>219168</v>
       </c>
       <c r="F14" s="10" t="s">
         <v>69</v>
       </c>
       <c r="G14" s="9">
-        <v>132010</v>
+        <v>132997</v>
       </c>
       <c r="H14" s="10" t="s">
         <v>70</v>
@@ -3080,13 +3128,13 @@
         <v>41586</v>
       </c>
       <c r="E15" s="9">
-        <v>181401</v>
+        <v>182352</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>74</v>
       </c>
       <c r="G15" s="9">
-        <v>109444</v>
+        <v>110092</v>
       </c>
       <c r="H15" s="10" t="s">
         <v>75</v>
@@ -3124,13 +3172,13 @@
         <v>46834</v>
       </c>
       <c r="E16" s="9">
-        <v>212882</v>
+        <v>213580</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>79</v>
       </c>
       <c r="G16" s="9">
-        <v>144563</v>
+        <v>145012</v>
       </c>
       <c r="H16" s="10" t="s">
         <v>80</v>
@@ -3168,13 +3216,13 @@
         <v>35200</v>
       </c>
       <c r="E17" s="9">
-        <v>180475</v>
+        <v>181680</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>84</v>
       </c>
       <c r="G17" s="9">
-        <v>128112</v>
+        <v>128946</v>
       </c>
       <c r="H17" s="10" t="s">
         <v>85</v>
@@ -3212,13 +3260,13 @@
         <v>26927</v>
       </c>
       <c r="E18" s="9">
-        <v>114585</v>
+        <v>114592</v>
       </c>
       <c r="F18" s="10" t="s">
         <v>89</v>
       </c>
       <c r="G18" s="9">
-        <v>75133</v>
+        <v>75139</v>
       </c>
       <c r="H18" s="10" t="s">
         <v>90</v>
@@ -3256,13 +3304,13 @@
         <v>30983</v>
       </c>
       <c r="E19" s="9">
-        <v>141209</v>
+        <v>141641</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>94</v>
       </c>
       <c r="G19" s="9">
-        <v>95580</v>
+        <v>95846</v>
       </c>
       <c r="H19" s="10" t="s">
         <v>95</v>
@@ -3300,13 +3348,13 @@
         <v>14394</v>
       </c>
       <c r="E20" s="9">
-        <v>61661</v>
+        <v>61831</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>99</v>
       </c>
       <c r="G20" s="9">
-        <v>44647</v>
+        <v>44765</v>
       </c>
       <c r="H20" s="10" t="s">
         <v>100</v>
@@ -3344,13 +3392,13 @@
         <v>101136</v>
       </c>
       <c r="E21" s="9">
-        <v>435686</v>
+        <v>438051</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>104</v>
       </c>
       <c r="G21" s="9">
-        <v>209857</v>
+        <v>210952</v>
       </c>
       <c r="H21" s="10" t="s">
         <v>105</v>
@@ -3388,13 +3436,13 @@
         <v>15640</v>
       </c>
       <c r="E22" s="9">
-        <v>77456</v>
+        <v>77827</v>
       </c>
       <c r="F22" s="10" t="s">
         <v>109</v>
       </c>
       <c r="G22" s="9">
-        <v>47449</v>
+        <v>47676</v>
       </c>
       <c r="H22" s="10" t="s">
         <v>110</v>
@@ -3432,13 +3480,13 @@
         <v>839468</v>
       </c>
       <c r="E23" s="12">
-        <v>3976831</v>
+        <v>3997214</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>34</v>
       </c>
       <c r="G23" s="12">
-        <v>2420504</v>
+        <v>2432893</v>
       </c>
       <c r="H23" s="13" t="s">
         <v>35</v>
@@ -4187,7 +4235,7 @@
         <v>192</v>
       </c>
       <c r="AH8" s="6">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI8" s="7" t="s">
         <v>193</v>
@@ -4562,10 +4610,10 @@
         <v>192</v>
       </c>
       <c r="AH11" s="9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI11" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AJ11" s="9">
         <v>2967</v>
@@ -6187,7 +6235,7 @@
         <v>192</v>
       </c>
       <c r="AH24" s="12">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI24" s="13" t="s">
         <v>193</v>
@@ -6562,31 +6610,31 @@
         <v>760553</v>
       </c>
       <c r="G7" s="6">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>353</v>
       </c>
       <c r="I7" s="6">
-        <v>1178</v>
+        <v>1196</v>
       </c>
       <c r="J7" s="7" t="s">
         <v>354</v>
       </c>
       <c r="K7" s="6">
-        <v>212201</v>
+        <v>214516</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>293</v>
+        <v>355</v>
       </c>
       <c r="M7" s="6">
         <v>1087</v>
       </c>
       <c r="N7" s="6">
-        <v>215799</v>
+        <v>218133</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>202</v>
+        <v>356</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6609,31 +6657,31 @@
         <v>11927</v>
       </c>
       <c r="G8" s="9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="I8" s="9">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K8" s="9">
-        <v>4139</v>
+        <v>4148</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="M8" s="9">
         <v>12</v>
       </c>
       <c r="N8" s="9">
-        <v>4238</v>
+        <v>4250</v>
       </c>
       <c r="O8" s="10" t="s">
-        <v>212</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6659,28 +6707,28 @@
         <v>67</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="I9" s="9">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="K9" s="9">
-        <v>11151</v>
+        <v>11283</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="M9" s="9">
         <v>71</v>
       </c>
       <c r="N9" s="9">
-        <v>11305</v>
+        <v>11438</v>
       </c>
       <c r="O9" s="10" t="s">
-        <v>222</v>
+        <v>364</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6703,31 +6751,31 @@
         <v>93539</v>
       </c>
       <c r="G10" s="9">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="I10" s="9">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="K10" s="9">
-        <v>20204</v>
+        <v>20599</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="M10" s="9">
         <v>111</v>
       </c>
       <c r="N10" s="9">
-        <v>20573</v>
+        <v>20970</v>
       </c>
       <c r="O10" s="10" t="s">
-        <v>231</v>
+        <v>368</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6753,28 +6801,28 @@
         <v>101</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I11" s="9">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="K11" s="9">
-        <v>31724</v>
+        <v>32046</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="M11" s="9">
         <v>191</v>
       </c>
       <c r="N11" s="9">
-        <v>32104</v>
+        <v>32427</v>
       </c>
       <c r="O11" s="10" t="s">
-        <v>239</v>
+        <v>372</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6797,31 +6845,31 @@
         <v>131144</v>
       </c>
       <c r="G12" s="9">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="I12" s="9">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>312</v>
+        <v>374</v>
       </c>
       <c r="K12" s="9">
-        <v>37452</v>
+        <v>37958</v>
       </c>
       <c r="L12" s="10" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="M12" s="9">
         <v>182</v>
       </c>
       <c r="N12" s="9">
-        <v>37937</v>
+        <v>38447</v>
       </c>
       <c r="O12" s="10" t="s">
-        <v>247</v>
+        <v>376</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6844,31 +6892,31 @@
         <v>63919</v>
       </c>
       <c r="G13" s="9">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="I13" s="9">
         <v>75</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="K13" s="9">
-        <v>12826</v>
+        <v>12903</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="M13" s="9">
         <v>47</v>
       </c>
       <c r="N13" s="9">
-        <v>13012</v>
+        <v>13090</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>256</v>
+        <v>380</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6894,28 +6942,28 @@
         <v>48</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="I14" s="9">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="K14" s="9">
-        <v>8811</v>
+        <v>9006</v>
       </c>
       <c r="L14" s="10" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="M14" s="9">
         <v>58</v>
       </c>
       <c r="N14" s="9">
-        <v>8936</v>
+        <v>9133</v>
       </c>
       <c r="O14" s="10" t="s">
-        <v>265</v>
+        <v>384</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6941,28 +6989,28 @@
         <v>58</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="I15" s="9">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="K15" s="9">
-        <v>9353</v>
+        <v>9460</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="M15" s="9">
         <v>15</v>
       </c>
       <c r="N15" s="9">
-        <v>9452</v>
+        <v>9560</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>274</v>
+        <v>388</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6988,28 +7036,28 @@
         <v>55</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="I16" s="9">
         <v>52</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="K16" s="9">
-        <v>11981</v>
+        <v>12046</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="M16" s="9">
         <v>45</v>
       </c>
       <c r="N16" s="9">
-        <v>12133</v>
+        <v>12198</v>
       </c>
       <c r="O16" s="10" t="s">
-        <v>283</v>
+        <v>392</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -7035,28 +7083,28 @@
         <v>42</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="I17" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="K17" s="9">
-        <v>14347</v>
+        <v>14509</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="M17" s="9">
         <v>83</v>
       </c>
       <c r="N17" s="9">
-        <v>14486</v>
+        <v>14647</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>291</v>
+        <v>396</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -7079,31 +7127,31 @@
         <v>11092</v>
       </c>
       <c r="G18" s="9">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="I18" s="9">
         <v>21</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="K18" s="9">
-        <v>6965</v>
+        <v>6970</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="M18" s="9">
         <v>13</v>
       </c>
       <c r="N18" s="9">
-        <v>7030</v>
+        <v>7034</v>
       </c>
       <c r="O18" s="10" t="s">
-        <v>300</v>
+        <v>400</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -7129,28 +7177,28 @@
         <v>26</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="I19" s="9">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="K19" s="9">
-        <v>9064</v>
+        <v>9127</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="M19" s="9">
         <v>18</v>
       </c>
       <c r="N19" s="9">
-        <v>9145</v>
+        <v>9209</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>309</v>
+        <v>403</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -7176,7 +7224,7 @@
         <v>10</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="I20" s="9">
         <v>4</v>
@@ -7185,19 +7233,19 @@
         <v>192</v>
       </c>
       <c r="K20" s="9">
-        <v>3005</v>
+        <v>3042</v>
       </c>
       <c r="L20" s="10" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="M20" s="9">
         <v>0</v>
       </c>
       <c r="N20" s="9">
-        <v>3019</v>
+        <v>3056</v>
       </c>
       <c r="O20" s="10" t="s">
-        <v>318</v>
+        <v>405</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -7223,28 +7271,28 @@
         <v>444</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>391</v>
+        <v>406</v>
       </c>
       <c r="I21" s="9">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>392</v>
+        <v>407</v>
       </c>
       <c r="K21" s="9">
-        <v>23940</v>
+        <v>24114</v>
       </c>
       <c r="L21" s="10" t="s">
-        <v>393</v>
+        <v>408</v>
       </c>
       <c r="M21" s="9">
         <v>198</v>
       </c>
       <c r="N21" s="9">
-        <v>25009</v>
+        <v>25188</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>328</v>
+        <v>409</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -7270,28 +7318,28 @@
         <v>49</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="I22" s="9">
         <v>89</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>395</v>
+        <v>411</v>
       </c>
       <c r="K22" s="9">
-        <v>7239</v>
+        <v>7305</v>
       </c>
       <c r="L22" s="10" t="s">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="M22" s="9">
         <v>43</v>
       </c>
       <c r="N22" s="9">
-        <v>7420</v>
+        <v>7486</v>
       </c>
       <c r="O22" s="10" t="s">
-        <v>336</v>
+        <v>413</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -7314,31 +7362,31 @@
         <v>760553</v>
       </c>
       <c r="G23" s="12">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="H23" s="13" t="s">
         <v>353</v>
       </c>
       <c r="I23" s="12">
-        <v>1178</v>
+        <v>1196</v>
       </c>
       <c r="J23" s="13" t="s">
         <v>354</v>
       </c>
       <c r="K23" s="12">
-        <v>212201</v>
+        <v>214516</v>
       </c>
       <c r="L23" s="13" t="s">
-        <v>293</v>
+        <v>355</v>
       </c>
       <c r="M23" s="12">
         <v>1087</v>
       </c>
       <c r="N23" s="12">
-        <v>215799</v>
+        <v>218133</v>
       </c>
       <c r="O23" s="13" t="s">
-        <v>202</v>
+        <v>356</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -7362,10 +7410,10 @@
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>397</v>
+        <v>414</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>398</v>
+        <v>415</v>
       </c>
       <c r="C26" s="16"/>
       <c r="D26" s="16"/>
@@ -7383,10 +7431,10 @@
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
-        <v>399</v>
+        <v>416</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>400</v>
+        <v>417</v>
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
@@ -7404,10 +7452,10 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
-        <v>401</v>
+        <v>418</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>402</v>
+        <v>419</v>
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="16"/>
@@ -7425,10 +7473,10 @@
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>403</v>
+        <v>420</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>404</v>
+        <v>421</v>
       </c>
       <c r="C29" s="16"/>
       <c r="D29" s="16"/>
@@ -7446,10 +7494,10 @@
     </row>
     <row r="30" ht="24" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
-        <v>405</v>
+        <v>422</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
@@ -7511,7 +7559,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>407</v>
+        <v>424</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7559,10 +7607,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>409</v>
+        <v>426</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -7576,10 +7624,10 @@
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3" t="s">
-        <v>410</v>
+        <v>427</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>411</v>
+        <v>428</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7692,31 +7740,31 @@
         <v>1064683</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>412</v>
+        <v>429</v>
       </c>
       <c r="F7" s="6">
         <v>529618</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>413</v>
+        <v>430</v>
       </c>
       <c r="H7" s="6">
         <v>8662</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>414</v>
+        <v>431</v>
       </c>
       <c r="J7" s="6">
         <v>205798</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>415</v>
+        <v>432</v>
       </c>
       <c r="L7" s="6">
         <v>744683</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>416</v>
+        <v>433</v>
       </c>
       <c r="N7" s="6">
         <v>314</v>
@@ -7728,7 +7776,7 @@
         <v>1809366</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>417</v>
+        <v>434</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7745,31 +7793,31 @@
         <v>60605</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>418</v>
+        <v>435</v>
       </c>
       <c r="F8" s="9">
         <v>20962</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>419</v>
+        <v>436</v>
       </c>
       <c r="H8" s="9">
         <v>552</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>420</v>
+        <v>437</v>
       </c>
       <c r="J8" s="9">
         <v>9187</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="L8" s="9">
         <v>31001</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>422</v>
+        <v>439</v>
       </c>
       <c r="N8" s="9">
         <v>20</v>
@@ -7781,7 +7829,7 @@
         <v>91606</v>
       </c>
       <c r="Q8" s="10" t="s">
-        <v>423</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7798,31 +7846,31 @@
         <v>79108</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>424</v>
+        <v>441</v>
       </c>
       <c r="F9" s="9">
         <v>43857</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>425</v>
+        <v>372</v>
       </c>
       <c r="H9" s="9">
         <v>803</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>426</v>
+        <v>442</v>
       </c>
       <c r="J9" s="9">
         <v>13666</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>427</v>
+        <v>443</v>
       </c>
       <c r="L9" s="9">
         <v>60138</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>428</v>
+        <v>444</v>
       </c>
       <c r="N9" s="9">
         <v>16</v>
@@ -7834,7 +7882,7 @@
         <v>139246</v>
       </c>
       <c r="Q9" s="10" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7851,13 +7899,13 @@
         <v>77714</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>430</v>
+        <v>446</v>
       </c>
       <c r="F10" s="9">
         <v>48473</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>431</v>
+        <v>447</v>
       </c>
       <c r="H10" s="9">
         <v>401</v>
@@ -7869,13 +7917,13 @@
         <v>30629</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>432</v>
+        <v>448</v>
       </c>
       <c r="L10" s="9">
         <v>65956</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>433</v>
+        <v>449</v>
       </c>
       <c r="N10" s="9">
         <v>17</v>
@@ -7887,7 +7935,7 @@
         <v>143670</v>
       </c>
       <c r="Q10" s="10" t="s">
-        <v>434</v>
+        <v>450</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7904,13 +7952,13 @@
         <v>177088</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>435</v>
+        <v>451</v>
       </c>
       <c r="F11" s="9">
         <v>80618</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>436</v>
+        <v>452</v>
       </c>
       <c r="H11" s="9">
         <v>808</v>
@@ -7922,13 +7970,13 @@
         <v>29005</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>437</v>
+        <v>453</v>
       </c>
       <c r="L11" s="9">
         <v>129081</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>438</v>
+        <v>454</v>
       </c>
       <c r="N11" s="9">
         <v>56</v>
@@ -7940,7 +7988,7 @@
         <v>306169</v>
       </c>
       <c r="Q11" s="10" t="s">
-        <v>439</v>
+        <v>455</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7957,13 +8005,13 @@
         <v>213645</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>440</v>
+        <v>456</v>
       </c>
       <c r="F12" s="9">
         <v>94151</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>441</v>
+        <v>457</v>
       </c>
       <c r="H12" s="9">
         <v>1017</v>
@@ -7975,13 +8023,13 @@
         <v>44251</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>442</v>
+        <v>458</v>
       </c>
       <c r="L12" s="9">
         <v>138508</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>443</v>
+        <v>459</v>
       </c>
       <c r="N12" s="9">
         <v>57</v>
@@ -7993,7 +8041,7 @@
         <v>352153</v>
       </c>
       <c r="Q12" s="10" t="s">
-        <v>444</v>
+        <v>460</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8010,31 +8058,31 @@
         <v>63140</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>445</v>
+        <v>461</v>
       </c>
       <c r="F13" s="9">
         <v>26336</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>446</v>
+        <v>462</v>
       </c>
       <c r="H13" s="9">
         <v>283</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>447</v>
+        <v>463</v>
       </c>
       <c r="J13" s="9">
         <v>22381</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>448</v>
+        <v>464</v>
       </c>
       <c r="L13" s="9">
         <v>49519</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>449</v>
+        <v>465</v>
       </c>
       <c r="N13" s="9">
         <v>15</v>
@@ -8046,7 +8094,7 @@
         <v>112659</v>
       </c>
       <c r="Q13" s="10" t="s">
-        <v>450</v>
+        <v>466</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8063,13 +8111,13 @@
         <v>63439</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>451</v>
+        <v>467</v>
       </c>
       <c r="F14" s="9">
         <v>30044</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>452</v>
+        <v>468</v>
       </c>
       <c r="H14" s="9">
         <v>254</v>
@@ -8081,13 +8129,13 @@
         <v>10838</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>453</v>
+        <v>469</v>
       </c>
       <c r="L14" s="9">
         <v>50605</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>454</v>
+        <v>470</v>
       </c>
       <c r="N14" s="9">
         <v>17</v>
@@ -8099,7 +8147,7 @@
         <v>114044</v>
       </c>
       <c r="Q14" s="10" t="s">
-        <v>455</v>
+        <v>471</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8116,31 +8164,31 @@
         <v>51565</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>456</v>
+        <v>472</v>
       </c>
       <c r="F15" s="9">
         <v>31367</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>457</v>
+        <v>473</v>
       </c>
       <c r="H15" s="9">
         <v>594</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>458</v>
+        <v>474</v>
       </c>
       <c r="J15" s="9">
         <v>5595</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>459</v>
+        <v>475</v>
       </c>
       <c r="L15" s="9">
         <v>32323</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>460</v>
+        <v>476</v>
       </c>
       <c r="N15" s="9">
         <v>6</v>
@@ -8152,7 +8200,7 @@
         <v>83888</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>461</v>
+        <v>477</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8169,31 +8217,31 @@
         <v>82086</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>462</v>
+        <v>478</v>
       </c>
       <c r="F16" s="9">
         <v>43476</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>463</v>
+        <v>479</v>
       </c>
       <c r="H16" s="9">
         <v>1155</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>464</v>
+        <v>480</v>
       </c>
       <c r="J16" s="9">
         <v>10560</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>465</v>
+        <v>481</v>
       </c>
       <c r="L16" s="9">
         <v>36496</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>466</v>
+        <v>482</v>
       </c>
       <c r="N16" s="9">
         <v>26</v>
@@ -8205,7 +8253,7 @@
         <v>118582</v>
       </c>
       <c r="Q16" s="10" t="s">
-        <v>467</v>
+        <v>483</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8222,31 +8270,31 @@
         <v>57472</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>468</v>
+        <v>484</v>
       </c>
       <c r="F17" s="9">
         <v>35612</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>469</v>
+        <v>485</v>
       </c>
       <c r="H17" s="9">
         <v>714</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>470</v>
+        <v>486</v>
       </c>
       <c r="J17" s="9">
         <v>7158</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="L17" s="9">
         <v>32468</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>472</v>
+        <v>488</v>
       </c>
       <c r="N17" s="9">
         <v>5</v>
@@ -8258,7 +8306,7 @@
         <v>89940</v>
       </c>
       <c r="Q17" s="10" t="s">
-        <v>473</v>
+        <v>489</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8275,31 +8323,31 @@
         <v>37988</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>474</v>
+        <v>490</v>
       </c>
       <c r="F18" s="9">
         <v>24344</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>475</v>
+        <v>491</v>
       </c>
       <c r="H18" s="9">
         <v>577</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>476</v>
+        <v>492</v>
       </c>
       <c r="J18" s="9">
         <v>9710</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="L18" s="9">
         <v>22661</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>478</v>
+        <v>494</v>
       </c>
       <c r="N18" s="9">
         <v>36</v>
@@ -8311,7 +8359,7 @@
         <v>60649</v>
       </c>
       <c r="Q18" s="10" t="s">
-        <v>479</v>
+        <v>495</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8328,31 +8376,31 @@
         <v>58788</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>480</v>
+        <v>496</v>
       </c>
       <c r="F19" s="9">
         <v>24661</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>481</v>
+        <v>497</v>
       </c>
       <c r="H19" s="9">
         <v>581</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>482</v>
+        <v>498</v>
       </c>
       <c r="J19" s="9">
         <v>7736</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>483</v>
+        <v>499</v>
       </c>
       <c r="L19" s="9">
         <v>32893</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>484</v>
+        <v>500</v>
       </c>
       <c r="N19" s="9">
         <v>13</v>
@@ -8364,7 +8412,7 @@
         <v>91681</v>
       </c>
       <c r="Q19" s="10" t="s">
-        <v>485</v>
+        <v>501</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8381,31 +8429,31 @@
         <v>27963</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>486</v>
+        <v>502</v>
       </c>
       <c r="F20" s="9">
         <v>15084</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>487</v>
+        <v>503</v>
       </c>
       <c r="H20" s="9">
         <v>233</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>488</v>
+        <v>504</v>
       </c>
       <c r="J20" s="9">
         <v>2490</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>489</v>
+        <v>505</v>
       </c>
       <c r="L20" s="9">
         <v>13727</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>490</v>
+        <v>506</v>
       </c>
       <c r="N20" s="9">
         <v>6</v>
@@ -8417,7 +8465,7 @@
         <v>41690</v>
       </c>
       <c r="Q20" s="10" t="s">
-        <v>491</v>
+        <v>507</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8434,31 +8482,31 @@
         <v>3021</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>492</v>
+        <v>508</v>
       </c>
       <c r="F21" s="9">
         <v>3857</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>493</v>
+        <v>509</v>
       </c>
       <c r="H21" s="9">
         <v>107</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>494</v>
+        <v>510</v>
       </c>
       <c r="J21" s="9">
         <v>1851</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>495</v>
+        <v>511</v>
       </c>
       <c r="L21" s="9">
         <v>40406</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>496</v>
+        <v>512</v>
       </c>
       <c r="N21" s="9">
         <v>18</v>
@@ -8470,7 +8518,7 @@
         <v>43427</v>
       </c>
       <c r="Q21" s="10" t="s">
-        <v>497</v>
+        <v>513</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8487,7 +8535,7 @@
         <v>11061</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>498</v>
+        <v>514</v>
       </c>
       <c r="F22" s="9">
         <v>6776</v>
@@ -8499,19 +8547,19 @@
         <v>583</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>499</v>
+        <v>515</v>
       </c>
       <c r="J22" s="9">
         <v>741</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>500</v>
+        <v>516</v>
       </c>
       <c r="L22" s="9">
         <v>8901</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>501</v>
+        <v>517</v>
       </c>
       <c r="N22" s="9">
         <v>6</v>
@@ -8523,7 +8571,7 @@
         <v>19962</v>
       </c>
       <c r="Q22" s="10" t="s">
-        <v>502</v>
+        <v>518</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8540,31 +8588,31 @@
         <v>1064683</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>412</v>
+        <v>429</v>
       </c>
       <c r="F23" s="12">
         <v>529618</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>413</v>
+        <v>430</v>
       </c>
       <c r="H23" s="12">
         <v>8662</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>414</v>
+        <v>431</v>
       </c>
       <c r="J23" s="12">
         <v>205798</v>
       </c>
       <c r="K23" s="13" t="s">
-        <v>415</v>
+        <v>432</v>
       </c>
       <c r="L23" s="12">
         <v>744683</v>
       </c>
       <c r="M23" s="13" t="s">
-        <v>416</v>
+        <v>433</v>
       </c>
       <c r="N23" s="12">
         <v>314</v>
@@ -8576,7 +8624,7 @@
         <v>1809366</v>
       </c>
       <c r="Q23" s="13" t="s">
-        <v>417</v>
+        <v>434</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -8602,7 +8650,7 @@
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>503</v>
+        <v>519</v>
       </c>
       <c r="B26" s="16" t="s">
         <v>340</v>
@@ -8667,7 +8715,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>504</v>
+        <v>520</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -8722,13 +8770,13 @@
         <v>124</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>505</v>
+        <v>521</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>506</v>
+        <v>522</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
@@ -8736,7 +8784,7 @@
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3" t="s">
-        <v>507</v>
+        <v>523</v>
       </c>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -8744,10 +8792,10 @@
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
       <c r="R4" s="3" t="s">
-        <v>508</v>
+        <v>524</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>509</v>
+        <v>525</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8769,28 +8817,28 @@
         <v>155</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>510</v>
+        <v>526</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>511</v>
+        <v>527</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>512</v>
+        <v>528</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>513</v>
+        <v>529</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>514</v>
+        <v>530</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>515</v>
+        <v>531</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>516</v>
+        <v>532</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>517</v>
+        <v>533</v>
       </c>
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
@@ -8874,7 +8922,7 @@
         <v>92542</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>518</v>
+        <v>534</v>
       </c>
       <c r="H7" s="6">
         <v>123257</v>
@@ -8892,25 +8940,25 @@
         <v>1064683</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>412</v>
+        <v>429</v>
       </c>
       <c r="N7" s="6">
         <v>744683</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>416</v>
+        <v>433</v>
       </c>
       <c r="P7" s="6">
         <v>1809366</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>417</v>
+        <v>434</v>
       </c>
       <c r="R7" s="6">
         <v>2025165</v>
       </c>
       <c r="S7" s="7" t="s">
-        <v>519</v>
+        <v>535</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8933,7 +8981,7 @@
         <v>2080</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>448</v>
+        <v>464</v>
       </c>
       <c r="H8" s="9">
         <v>2158</v>
@@ -8951,25 +8999,25 @@
         <v>60605</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>418</v>
+        <v>435</v>
       </c>
       <c r="N8" s="9">
         <v>31001</v>
       </c>
       <c r="O8" s="10" t="s">
-        <v>422</v>
+        <v>439</v>
       </c>
       <c r="P8" s="9">
         <v>91606</v>
       </c>
       <c r="Q8" s="10" t="s">
-        <v>423</v>
+        <v>440</v>
       </c>
       <c r="R8" s="9">
         <v>95844</v>
       </c>
       <c r="S8" s="10" t="s">
-        <v>520</v>
+        <v>536</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8992,7 +9040,7 @@
         <v>5313</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>521</v>
+        <v>537</v>
       </c>
       <c r="H9" s="9">
         <v>5992</v>
@@ -9010,25 +9058,25 @@
         <v>79108</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>424</v>
+        <v>441</v>
       </c>
       <c r="N9" s="9">
         <v>60138</v>
       </c>
       <c r="O9" s="10" t="s">
-        <v>428</v>
+        <v>444</v>
       </c>
       <c r="P9" s="9">
         <v>139246</v>
       </c>
       <c r="Q9" s="10" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
       <c r="R9" s="9">
         <v>150551</v>
       </c>
       <c r="S9" s="10" t="s">
-        <v>522</v>
+        <v>538</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9051,7 +9099,7 @@
         <v>6141</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>523</v>
+        <v>539</v>
       </c>
       <c r="H10" s="9">
         <v>14432</v>
@@ -9069,25 +9117,25 @@
         <v>77714</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>430</v>
+        <v>446</v>
       </c>
       <c r="N10" s="9">
         <v>65956</v>
       </c>
       <c r="O10" s="10" t="s">
-        <v>433</v>
+        <v>449</v>
       </c>
       <c r="P10" s="9">
         <v>143670</v>
       </c>
       <c r="Q10" s="10" t="s">
-        <v>434</v>
+        <v>450</v>
       </c>
       <c r="R10" s="9">
         <v>164243</v>
       </c>
       <c r="S10" s="10" t="s">
-        <v>524</v>
+        <v>540</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9110,7 +9158,7 @@
         <v>15218</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>525</v>
+        <v>541</v>
       </c>
       <c r="H11" s="9">
         <v>16886</v>
@@ -9128,25 +9176,25 @@
         <v>177088</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>435</v>
+        <v>451</v>
       </c>
       <c r="N11" s="9">
         <v>129081</v>
       </c>
       <c r="O11" s="10" t="s">
-        <v>438</v>
+        <v>454</v>
       </c>
       <c r="P11" s="9">
         <v>306169</v>
       </c>
       <c r="Q11" s="10" t="s">
-        <v>439</v>
+        <v>455</v>
       </c>
       <c r="R11" s="9">
         <v>338273</v>
       </c>
       <c r="S11" s="10" t="s">
-        <v>526</v>
+        <v>542</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9169,7 +9217,7 @@
         <v>14814</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>527</v>
+        <v>543</v>
       </c>
       <c r="H12" s="9">
         <v>23123</v>
@@ -9187,25 +9235,25 @@
         <v>213645</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>440</v>
+        <v>456</v>
       </c>
       <c r="N12" s="9">
         <v>138508</v>
       </c>
       <c r="O12" s="10" t="s">
-        <v>443</v>
+        <v>459</v>
       </c>
       <c r="P12" s="9">
         <v>352153</v>
       </c>
       <c r="Q12" s="10" t="s">
-        <v>444</v>
+        <v>460</v>
       </c>
       <c r="R12" s="9">
         <v>390090</v>
       </c>
       <c r="S12" s="10" t="s">
-        <v>528</v>
+        <v>544</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9228,7 +9276,7 @@
         <v>5009</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>529</v>
+        <v>545</v>
       </c>
       <c r="H13" s="9">
         <v>8003</v>
@@ -9246,25 +9294,25 @@
         <v>63140</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>445</v>
+        <v>461</v>
       </c>
       <c r="N13" s="9">
         <v>49519</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>449</v>
+        <v>465</v>
       </c>
       <c r="P13" s="9">
         <v>112659</v>
       </c>
       <c r="Q13" s="10" t="s">
-        <v>450</v>
+        <v>466</v>
       </c>
       <c r="R13" s="9">
         <v>125671</v>
       </c>
       <c r="S13" s="10" t="s">
-        <v>530</v>
+        <v>546</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9287,7 +9335,7 @@
         <v>2640</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>531</v>
+        <v>547</v>
       </c>
       <c r="H14" s="9">
         <v>6296</v>
@@ -9305,25 +9353,25 @@
         <v>63439</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>451</v>
+        <v>467</v>
       </c>
       <c r="N14" s="9">
         <v>50605</v>
       </c>
       <c r="O14" s="10" t="s">
-        <v>454</v>
+        <v>470</v>
       </c>
       <c r="P14" s="9">
         <v>114044</v>
       </c>
       <c r="Q14" s="10" t="s">
-        <v>455</v>
+        <v>471</v>
       </c>
       <c r="R14" s="9">
         <v>122980</v>
       </c>
       <c r="S14" s="10" t="s">
-        <v>532</v>
+        <v>548</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9346,7 +9394,7 @@
         <v>4264</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>363</v>
+        <v>549</v>
       </c>
       <c r="H15" s="9">
         <v>5188</v>
@@ -9364,25 +9412,25 @@
         <v>51565</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>456</v>
+        <v>472</v>
       </c>
       <c r="N15" s="9">
         <v>32323</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>460</v>
+        <v>476</v>
       </c>
       <c r="P15" s="9">
         <v>83888</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>461</v>
+        <v>477</v>
       </c>
       <c r="R15" s="9">
         <v>93340</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>533</v>
+        <v>550</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9405,7 +9453,7 @@
         <v>5867</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>534</v>
+        <v>551</v>
       </c>
       <c r="H16" s="9">
         <v>6266</v>
@@ -9423,25 +9471,25 @@
         <v>82086</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>462</v>
+        <v>478</v>
       </c>
       <c r="N16" s="9">
         <v>36496</v>
       </c>
       <c r="O16" s="10" t="s">
-        <v>466</v>
+        <v>482</v>
       </c>
       <c r="P16" s="9">
         <v>118582</v>
       </c>
       <c r="Q16" s="10" t="s">
-        <v>467</v>
+        <v>483</v>
       </c>
       <c r="R16" s="9">
         <v>130715</v>
       </c>
       <c r="S16" s="10" t="s">
-        <v>535</v>
+        <v>552</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9464,7 +9512,7 @@
         <v>8193</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>536</v>
+        <v>553</v>
       </c>
       <c r="H17" s="9">
         <v>6293</v>
@@ -9482,25 +9530,25 @@
         <v>57472</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>468</v>
+        <v>484</v>
       </c>
       <c r="N17" s="9">
         <v>32468</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>472</v>
+        <v>488</v>
       </c>
       <c r="P17" s="9">
         <v>89940</v>
       </c>
       <c r="Q17" s="10" t="s">
-        <v>473</v>
+        <v>489</v>
       </c>
       <c r="R17" s="9">
         <v>104426</v>
       </c>
       <c r="S17" s="10" t="s">
-        <v>537</v>
+        <v>554</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9523,7 +9571,7 @@
         <v>3162</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>538</v>
+        <v>555</v>
       </c>
       <c r="H18" s="9">
         <v>3868</v>
@@ -9541,25 +9589,25 @@
         <v>37988</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>474</v>
+        <v>490</v>
       </c>
       <c r="N18" s="9">
         <v>22661</v>
       </c>
       <c r="O18" s="10" t="s">
-        <v>478</v>
+        <v>494</v>
       </c>
       <c r="P18" s="9">
         <v>60649</v>
       </c>
       <c r="Q18" s="10" t="s">
-        <v>479</v>
+        <v>495</v>
       </c>
       <c r="R18" s="9">
         <v>67679</v>
       </c>
       <c r="S18" s="10" t="s">
-        <v>539</v>
+        <v>556</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9582,7 +9630,7 @@
         <v>4576</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>540</v>
+        <v>557</v>
       </c>
       <c r="H19" s="9">
         <v>4569</v>
@@ -9600,25 +9648,25 @@
         <v>58788</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>480</v>
+        <v>496</v>
       </c>
       <c r="N19" s="9">
         <v>32893</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>484</v>
+        <v>500</v>
       </c>
       <c r="P19" s="9">
         <v>91681</v>
       </c>
       <c r="Q19" s="10" t="s">
-        <v>485</v>
+        <v>501</v>
       </c>
       <c r="R19" s="9">
         <v>100826</v>
       </c>
       <c r="S19" s="10" t="s">
-        <v>541</v>
+        <v>558</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9641,7 +9689,7 @@
         <v>1233</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>542</v>
+        <v>559</v>
       </c>
       <c r="H20" s="9">
         <v>1786</v>
@@ -9659,25 +9707,25 @@
         <v>27963</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>486</v>
+        <v>502</v>
       </c>
       <c r="N20" s="9">
         <v>13727</v>
       </c>
       <c r="O20" s="10" t="s">
-        <v>490</v>
+        <v>506</v>
       </c>
       <c r="P20" s="9">
         <v>41690</v>
       </c>
       <c r="Q20" s="10" t="s">
-        <v>491</v>
+        <v>507</v>
       </c>
       <c r="R20" s="9">
         <v>44709</v>
       </c>
       <c r="S20" s="10" t="s">
-        <v>543</v>
+        <v>560</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9700,7 +9748,7 @@
         <v>10014</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>544</v>
+        <v>561</v>
       </c>
       <c r="H21" s="9">
         <v>14995</v>
@@ -9718,25 +9766,25 @@
         <v>3021</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>492</v>
+        <v>508</v>
       </c>
       <c r="N21" s="9">
         <v>40406</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>496</v>
+        <v>512</v>
       </c>
       <c r="P21" s="9">
         <v>43427</v>
       </c>
       <c r="Q21" s="10" t="s">
-        <v>497</v>
+        <v>513</v>
       </c>
       <c r="R21" s="9">
         <v>68436</v>
       </c>
       <c r="S21" s="10" t="s">
-        <v>545</v>
+        <v>562</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9759,7 +9807,7 @@
         <v>4018</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>466</v>
+        <v>482</v>
       </c>
       <c r="H22" s="9">
         <v>3402</v>
@@ -9777,25 +9825,25 @@
         <v>11061</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>498</v>
+        <v>514</v>
       </c>
       <c r="N22" s="9">
         <v>8901</v>
       </c>
       <c r="O22" s="10" t="s">
-        <v>501</v>
+        <v>517</v>
       </c>
       <c r="P22" s="9">
         <v>19962</v>
       </c>
       <c r="Q22" s="10" t="s">
-        <v>502</v>
+        <v>518</v>
       </c>
       <c r="R22" s="9">
         <v>27382</v>
       </c>
       <c r="S22" s="10" t="s">
-        <v>546</v>
+        <v>563</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9818,7 +9866,7 @@
         <v>92542</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>518</v>
+        <v>534</v>
       </c>
       <c r="H23" s="12">
         <v>123257</v>
@@ -9836,25 +9884,25 @@
         <v>1064683</v>
       </c>
       <c r="M23" s="13" t="s">
-        <v>412</v>
+        <v>429</v>
       </c>
       <c r="N23" s="12">
         <v>744683</v>
       </c>
       <c r="O23" s="13" t="s">
-        <v>416</v>
+        <v>433</v>
       </c>
       <c r="P23" s="12">
         <v>1809366</v>
       </c>
       <c r="Q23" s="13" t="s">
-        <v>417</v>
+        <v>434</v>
       </c>
       <c r="R23" s="12">
         <v>2025165</v>
       </c>
       <c r="S23" s="13" t="s">
-        <v>519</v>
+        <v>535</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
@@ -9882,10 +9930,10 @@
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>547</v>
+        <v>564</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
       <c r="C26" s="16"/>
       <c r="D26" s="16"/>
@@ -9907,10 +9955,10 @@
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
-        <v>549</v>
+        <v>566</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>550</v>
+        <v>567</v>
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
@@ -9932,10 +9980,10 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
-        <v>551</v>
+        <v>568</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>552</v>
+        <v>569</v>
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="16"/>
@@ -9957,10 +10005,10 @@
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>553</v>
+        <v>570</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>554</v>
+        <v>571</v>
       </c>
       <c r="C29" s="16"/>
       <c r="D29" s="16"/>
@@ -9982,10 +10030,10 @@
     </row>
     <row r="30" ht="24" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
-        <v>555</v>
+        <v>572</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>556</v>
+        <v>573</v>
       </c>
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
@@ -10046,7 +10094,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>557</v>
+        <v>574</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -10074,19 +10122,19 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>558</v>
+        <v>575</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>337</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>559</v>
+        <v>576</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>560</v>
+        <v>577</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>561</v>
+        <v>578</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10126,13 +10174,13 @@
         <v>215799</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>562</v>
+        <v>579</v>
       </c>
       <c r="F6" s="6">
         <v>1809366</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>563</v>
+        <v>580</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10149,13 +10197,13 @@
         <v>4238</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>564</v>
+        <v>581</v>
       </c>
       <c r="F7" s="9">
         <v>91606</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>565</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10172,13 +10220,13 @@
         <v>11305</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>566</v>
+        <v>583</v>
       </c>
       <c r="F8" s="9">
         <v>139246</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>567</v>
+        <v>584</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10195,13 +10243,13 @@
         <v>20573</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>568</v>
+        <v>585</v>
       </c>
       <c r="F9" s="9">
         <v>143670</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>569</v>
+        <v>586</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10218,13 +10266,13 @@
         <v>32104</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>570</v>
+        <v>587</v>
       </c>
       <c r="F10" s="9">
         <v>306169</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>571</v>
+        <v>588</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10241,13 +10289,13 @@
         <v>37937</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>570</v>
+        <v>587</v>
       </c>
       <c r="F11" s="9">
         <v>352153</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>572</v>
+        <v>589</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10264,13 +10312,13 @@
         <v>13012</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>573</v>
+        <v>590</v>
       </c>
       <c r="F12" s="9">
         <v>112659</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>574</v>
+        <v>591</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10287,13 +10335,13 @@
         <v>8936</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>566</v>
+        <v>583</v>
       </c>
       <c r="F13" s="9">
         <v>114044</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10310,13 +10358,13 @@
         <v>9452</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>576</v>
+        <v>593</v>
       </c>
       <c r="F14" s="9">
         <v>83888</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>577</v>
+        <v>594</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10339,7 +10387,7 @@
         <v>118582</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10356,13 +10404,13 @@
         <v>14486</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>579</v>
+        <v>596</v>
       </c>
       <c r="F16" s="9">
         <v>89940</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>580</v>
+        <v>597</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10379,13 +10427,13 @@
         <v>7030</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>568</v>
+        <v>585</v>
       </c>
       <c r="F17" s="9">
         <v>60649</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>581</v>
+        <v>598</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10402,13 +10450,13 @@
         <v>9145</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>582</v>
+        <v>599</v>
       </c>
       <c r="F18" s="9">
         <v>91681</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>583</v>
+        <v>392</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10425,13 +10473,13 @@
         <v>3019</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>584</v>
+        <v>600</v>
       </c>
       <c r="F19" s="9">
         <v>41690</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>585</v>
+        <v>601</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10448,13 +10496,13 @@
         <v>25009</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>586</v>
+        <v>602</v>
       </c>
       <c r="F20" s="9">
         <v>43427</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>587</v>
+        <v>603</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10471,13 +10519,13 @@
         <v>7420</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>588</v>
+        <v>604</v>
       </c>
       <c r="F21" s="9">
         <v>19962</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>589</v>
+        <v>605</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10494,13 +10542,13 @@
         <v>215799</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>562</v>
+        <v>579</v>
       </c>
       <c r="F22" s="12">
         <v>1809366</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>563</v>
+        <v>580</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -10516,10 +10564,10 @@
     </row>
     <row r="25" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>591</v>
+        <v>607</v>
       </c>
       <c r="C25" s="16"/>
       <c r="D25" s="16"/>
@@ -10552,7 +10600,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>592</v>
+        <v>608</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -10582,7 +10630,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>593</v>
+        <v>609</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -10594,22 +10642,22 @@
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3" t="s">
-        <v>594</v>
+        <v>610</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>595</v>
+        <v>611</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>596</v>
+        <v>612</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>597</v>
+        <v>613</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>598</v>
+        <v>614</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>599</v>
+        <v>615</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11113,7 +11161,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>600</v>
+        <v>616</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -11153,22 +11201,22 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>601</v>
+        <v>617</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>602</v>
+        <v>618</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>603</v>
+        <v>619</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>604</v>
+        <v>620</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>605</v>
+        <v>621</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
@@ -11193,16 +11241,16 @@
         <v>155</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>512</v>
+        <v>528</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>513</v>
+        <v>529</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>514</v>
+        <v>530</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>515</v>
+        <v>531</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11266,25 +11314,25 @@
         <v>1613</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>606</v>
+        <v>622</v>
       </c>
       <c r="H7" s="6">
         <v>5056</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>607</v>
+        <v>623</v>
       </c>
       <c r="J7" s="6">
         <v>992265</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>608</v>
+        <v>624</v>
       </c>
       <c r="L7" s="6">
         <v>440145</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>493</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11307,25 +11355,25 @@
         <v>20</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>609</v>
+        <v>625</v>
       </c>
       <c r="H8" s="9">
         <v>127</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>610</v>
+        <v>626</v>
       </c>
       <c r="J8" s="9">
         <v>52267</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>611</v>
+        <v>627</v>
       </c>
       <c r="L8" s="9">
         <v>23693</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>612</v>
+        <v>628</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11348,25 +11396,25 @@
         <v>131</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>613</v>
+        <v>629</v>
       </c>
       <c r="H9" s="9">
         <v>389</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>614</v>
+        <v>630</v>
       </c>
       <c r="J9" s="9">
         <v>78707</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>615</v>
+        <v>631</v>
       </c>
       <c r="L9" s="9">
         <v>34784</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>616</v>
+        <v>632</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11389,25 +11437,25 @@
         <v>215</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>617</v>
+        <v>633</v>
       </c>
       <c r="H10" s="9">
         <v>1163</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>618</v>
+        <v>634</v>
       </c>
       <c r="J10" s="9">
         <v>77240</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>619</v>
+        <v>635</v>
       </c>
       <c r="L10" s="9">
         <v>31912</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>620</v>
+        <v>636</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11430,25 +11478,25 @@
         <v>359</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>621</v>
+        <v>637</v>
       </c>
       <c r="H11" s="9">
         <v>433</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>622</v>
+        <v>638</v>
       </c>
       <c r="J11" s="9">
         <v>176076</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>623</v>
+        <v>639</v>
       </c>
       <c r="L11" s="9">
         <v>77997</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>624</v>
+        <v>640</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11471,25 +11519,25 @@
         <v>425</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>625</v>
+        <v>641</v>
       </c>
       <c r="H12" s="9">
         <v>740</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>626</v>
+        <v>642</v>
       </c>
       <c r="J12" s="9">
         <v>212946</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>627</v>
+        <v>643</v>
       </c>
       <c r="L12" s="9">
         <v>90560</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>628</v>
+        <v>644</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11512,25 +11560,25 @@
         <v>135</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>629</v>
+        <v>645</v>
       </c>
       <c r="H13" s="9">
         <v>222</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>630</v>
+        <v>646</v>
       </c>
       <c r="J13" s="9">
         <v>62912</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>631</v>
+        <v>647</v>
       </c>
       <c r="L13" s="9">
         <v>29112</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>632</v>
+        <v>648</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11553,25 +11601,25 @@
         <v>66</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>633</v>
+        <v>649</v>
       </c>
       <c r="H14" s="9">
         <v>365</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>634</v>
+        <v>650</v>
       </c>
       <c r="J14" s="9">
         <v>63124</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>635</v>
+        <v>651</v>
       </c>
       <c r="L14" s="9">
         <v>33000</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>636</v>
+        <v>652</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11594,25 +11642,25 @@
         <v>24</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>637</v>
+        <v>653</v>
       </c>
       <c r="H15" s="9">
         <v>300</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>638</v>
+        <v>654</v>
       </c>
       <c r="J15" s="9">
         <v>42736</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>639</v>
+        <v>655</v>
       </c>
       <c r="L15" s="9">
         <v>22843</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>640</v>
+        <v>656</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11635,25 +11683,25 @@
         <v>64</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>641</v>
+        <v>657</v>
       </c>
       <c r="H16" s="9">
         <v>199</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>642</v>
+        <v>658</v>
       </c>
       <c r="J16" s="9">
         <v>65998</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>643</v>
+        <v>659</v>
       </c>
       <c r="L16" s="9">
         <v>23173</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>644</v>
+        <v>660</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11676,25 +11724,25 @@
         <v>33</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>645</v>
+        <v>661</v>
       </c>
       <c r="H17" s="9">
         <v>353</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>646</v>
+        <v>662</v>
       </c>
       <c r="J17" s="9">
         <v>44089</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>647</v>
+        <v>663</v>
       </c>
       <c r="L17" s="9">
         <v>18396</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>648</v>
+        <v>664</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11717,25 +11765,25 @@
         <v>36</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>649</v>
+        <v>665</v>
       </c>
       <c r="H18" s="9">
         <v>487</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>650</v>
+        <v>666</v>
       </c>
       <c r="J18" s="9">
         <v>32990</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>651</v>
+        <v>667</v>
       </c>
       <c r="L18" s="9">
         <v>16599</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>652</v>
+        <v>668</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11758,25 +11806,25 @@
         <v>21</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>653</v>
+        <v>669</v>
       </c>
       <c r="H19" s="9">
         <v>105</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>654</v>
+        <v>670</v>
       </c>
       <c r="J19" s="9">
         <v>51034</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>655</v>
+        <v>671</v>
       </c>
       <c r="L19" s="9">
         <v>24900</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>656</v>
+        <v>672</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11799,25 +11847,25 @@
         <v>10</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>657</v>
+        <v>673</v>
       </c>
       <c r="H20" s="9">
         <v>66</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>658</v>
+        <v>674</v>
       </c>
       <c r="J20" s="9">
         <v>23682</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>659</v>
+        <v>675</v>
       </c>
       <c r="L20" s="9">
         <v>9978</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>660</v>
+        <v>676</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11840,25 +11888,25 @@
         <v>46</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>661</v>
+        <v>677</v>
       </c>
       <c r="H21" s="9">
         <v>94</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>662</v>
+        <v>678</v>
       </c>
       <c r="J21" s="9">
         <v>2869</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>663</v>
+        <v>679</v>
       </c>
       <c r="L21" s="9">
         <v>1057</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>664</v>
+        <v>680</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11881,25 +11929,25 @@
         <v>28</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>665</v>
+        <v>681</v>
       </c>
       <c r="H22" s="9">
         <v>13</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>666</v>
+        <v>682</v>
       </c>
       <c r="J22" s="9">
         <v>5595</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>532</v>
+        <v>548</v>
       </c>
       <c r="L22" s="9">
         <v>2141</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>667</v>
+        <v>683</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11922,25 +11970,25 @@
         <v>1613</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>606</v>
+        <v>622</v>
       </c>
       <c r="H23" s="12">
         <v>5056</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>607</v>
+        <v>623</v>
       </c>
       <c r="J23" s="12">
         <v>992265</v>
       </c>
       <c r="K23" s="13" t="s">
-        <v>608</v>
+        <v>624</v>
       </c>
       <c r="L23" s="12">
         <v>440145</v>
       </c>
       <c r="M23" s="13" t="s">
-        <v>493</v>
+        <v>509</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
@@ -11962,10 +12010,10 @@
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>668</v>
+        <v>684</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>669</v>
+        <v>685</v>
       </c>
       <c r="C26" s="16"/>
       <c r="D26" s="16"/>
@@ -11981,10 +12029,10 @@
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
-        <v>670</v>
+        <v>686</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>671</v>
+        <v>687</v>
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
@@ -12000,10 +12048,10 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
-        <v>672</v>
+        <v>688</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>673</v>
+        <v>689</v>
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="16"/>
@@ -12019,10 +12067,10 @@
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>674</v>
+        <v>690</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>675</v>
+        <v>691</v>
       </c>
       <c r="C29" s="16"/>
       <c r="D29" s="16"/>

--- a/data/Export_Progres_Pendataan_Kabupaten_Kota.xlsx
+++ b/data/Export_Progres_Pendataan_Kabupaten_Kota.xlsx
@@ -23,7 +23,7 @@
     <t>PROGRES PENDATAAN - PROGRES PENDATAAN</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 23 Agu 2026, 18.01 | Dicetak: 23 Agu 2026, 20.20</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 24 Agu 2026, 06.00 | Dicetak: 24 Agu 2026, 07.46</t>
   </si>
   <si>
     <t>Kode</t>
@@ -122,13 +122,13 @@
     <t>LAMPUNG</t>
   </si>
   <si>
-    <t>115,15</t>
-  </si>
-  <si>
-    <t>70,2</t>
-  </si>
-  <si>
-    <t>3,95</t>
+    <t>115,67</t>
+  </si>
+  <si>
+    <t>70,59</t>
+  </si>
+  <si>
+    <t>3,78</t>
   </si>
   <si>
     <t>1801</t>
@@ -137,13 +137,13 @@
     <t>LAMPUNG BARAT</t>
   </si>
   <si>
-    <t>125,66</t>
-  </si>
-  <si>
-    <t>85,43</t>
-  </si>
-  <si>
-    <t>1,84</t>
+    <t>125,47</t>
+  </si>
+  <si>
+    <t>85,23</t>
+  </si>
+  <si>
+    <t>2,06</t>
   </si>
   <si>
     <t>1802</t>
@@ -152,210 +152,210 @@
     <t>TANGGAMUS</t>
   </si>
   <si>
-    <t>114,48</t>
-  </si>
-  <si>
-    <t>72,49</t>
+    <t>114,98</t>
+  </si>
+  <si>
+    <t>72,84</t>
+  </si>
+  <si>
+    <t>5,81</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>LAMPUNG SELATAN</t>
+  </si>
+  <si>
+    <t>115,22</t>
+  </si>
+  <si>
+    <t>66,51</t>
+  </si>
+  <si>
+    <t>4,99</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>LAMPUNG TIMUR</t>
+  </si>
+  <si>
+    <t>110,55</t>
+  </si>
+  <si>
+    <t>68,67</t>
+  </si>
+  <si>
+    <t>3,5</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>LAMPUNG TENGAH</t>
+  </si>
+  <si>
+    <t>112,1</t>
+  </si>
+  <si>
+    <t>69,69</t>
+  </si>
+  <si>
+    <t>3,71</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>LAMPUNG UTARA</t>
+  </si>
+  <si>
+    <t>118,12</t>
+  </si>
+  <si>
+    <t>68,29</t>
+  </si>
+  <si>
+    <t>1,3</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>WAY KANAN</t>
+  </si>
+  <si>
+    <t>118,45</t>
+  </si>
+  <si>
+    <t>72,28</t>
+  </si>
+  <si>
+    <t>3,68</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG</t>
+  </si>
+  <si>
+    <t>119,23</t>
+  </si>
+  <si>
+    <t>72,33</t>
+  </si>
+  <si>
+    <t>4,79</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>PESAWARAN</t>
+  </si>
+  <si>
+    <t>126,07</t>
+  </si>
+  <si>
+    <t>85,71</t>
+  </si>
+  <si>
+    <t>2,25</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>PRINGSEWU</t>
+  </si>
+  <si>
+    <t>116,67</t>
+  </si>
+  <si>
+    <t>82,98</t>
+  </si>
+  <si>
+    <t>4,83</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>MESUJI</t>
+  </si>
+  <si>
+    <t>133,03</t>
+  </si>
+  <si>
+    <t>87,28</t>
+  </si>
+  <si>
+    <t>0,06</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG BARAT</t>
+  </si>
+  <si>
+    <t>130,09</t>
+  </si>
+  <si>
+    <t>88,17</t>
+  </si>
+  <si>
+    <t>0,12</t>
+  </si>
+  <si>
+    <t>1813</t>
+  </si>
+  <si>
+    <t>PESISIR BARAT</t>
+  </si>
+  <si>
+    <t>131,35</t>
+  </si>
+  <si>
+    <t>95,17</t>
+  </si>
+  <si>
+    <t>0,63</t>
+  </si>
+  <si>
+    <t>1871</t>
+  </si>
+  <si>
+    <t>BANDAR LAMPUNG</t>
+  </si>
+  <si>
+    <t>107,94</t>
+  </si>
+  <si>
+    <t>52,14</t>
+  </si>
+  <si>
+    <t>5,4</t>
+  </si>
+  <si>
+    <t>1872</t>
+  </si>
+  <si>
+    <t>METRO</t>
+  </si>
+  <si>
+    <t>111,46</t>
+  </si>
+  <si>
+    <t>68,5</t>
   </si>
   <si>
     <t>5,92</t>
   </si>
   <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>LAMPUNG SELATAN</t>
-  </si>
-  <si>
-    <t>114,36</t>
-  </si>
-  <si>
-    <t>65,87</t>
-  </si>
-  <si>
-    <t>5,3</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>LAMPUNG TIMUR</t>
-  </si>
-  <si>
-    <t>110,01</t>
-  </si>
-  <si>
-    <t>68,23</t>
-  </si>
-  <si>
-    <t>3,72</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>LAMPUNG TENGAH</t>
-  </si>
-  <si>
-    <t>111,54</t>
-  </si>
-  <si>
-    <t>69,26</t>
-  </si>
-  <si>
-    <t>3,92</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>LAMPUNG UTARA</t>
-  </si>
-  <si>
-    <t>117,68</t>
-  </si>
-  <si>
-    <t>67,96</t>
-  </si>
-  <si>
-    <t>1,46</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>WAY KANAN</t>
-  </si>
-  <si>
-    <t>117,86</t>
-  </si>
-  <si>
-    <t>71,78</t>
-  </si>
-  <si>
-    <t>3,85</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG</t>
-  </si>
-  <si>
-    <t>118,66</t>
-  </si>
-  <si>
-    <t>71,87</t>
-  </si>
-  <si>
-    <t>4,98</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>PESAWARAN</t>
-  </si>
-  <si>
-    <t>125,68</t>
-  </si>
-  <si>
-    <t>85,4</t>
-  </si>
-  <si>
-    <t>2,47</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>PRINGSEWU</t>
-  </si>
-  <si>
-    <t>116,02</t>
-  </si>
-  <si>
-    <t>82,45</t>
-  </si>
-  <si>
-    <t>5,16</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>MESUJI</t>
-  </si>
-  <si>
-    <t>133</t>
-  </si>
-  <si>
-    <t>87,24</t>
-  </si>
-  <si>
-    <t>0,06</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG BARAT</t>
-  </si>
-  <si>
-    <t>129,99</t>
-  </si>
-  <si>
-    <t>88,06</t>
-  </si>
-  <si>
-    <t>0,18</t>
-  </si>
-  <si>
-    <t>1813</t>
-  </si>
-  <si>
-    <t>PESISIR BARAT</t>
-  </si>
-  <si>
-    <t>131,25</t>
-  </si>
-  <si>
-    <t>95,12</t>
-  </si>
-  <si>
-    <t>0,68</t>
-  </si>
-  <si>
-    <t>1871</t>
-  </si>
-  <si>
-    <t>BANDAR LAMPUNG</t>
-  </si>
-  <si>
-    <t>107,39</t>
-  </si>
-  <si>
-    <t>51,8</t>
-  </si>
-  <si>
-    <t>5,48</t>
-  </si>
-  <si>
-    <t>1872</t>
-  </si>
-  <si>
-    <t>METRO</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>68,12</t>
-  </si>
-  <si>
-    <t>6,1</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
@@ -605,1408 +605,1408 @@
     <t>0,01</t>
   </si>
   <si>
-    <t>12,17</t>
+    <t>12,27</t>
+  </si>
+  <si>
+    <t>18,41</t>
+  </si>
+  <si>
+    <t>8,31</t>
+  </si>
+  <si>
+    <t>44,06</t>
+  </si>
+  <si>
+    <t>16,74</t>
+  </si>
+  <si>
+    <t>6,78</t>
+  </si>
+  <si>
+    <t>29,01</t>
+  </si>
+  <si>
+    <t>29,17</t>
+  </si>
+  <si>
+    <t>0,2</t>
+  </si>
+  <si>
+    <t>0,03</t>
+  </si>
+  <si>
+    <t>17,21</t>
+  </si>
+  <si>
+    <t>17,09</t>
+  </si>
+  <si>
+    <t>12,84</t>
+  </si>
+  <si>
+    <t>41,59</t>
+  </si>
+  <si>
+    <t>18,09</t>
+  </si>
+  <si>
+    <t>1,53</t>
+  </si>
+  <si>
+    <t>35,3</t>
+  </si>
+  <si>
+    <t>35,5</t>
+  </si>
+  <si>
+    <t>0,1</t>
+  </si>
+  <si>
+    <t>0,05</t>
+  </si>
+  <si>
+    <t>9,33</t>
+  </si>
+  <si>
+    <t>23,04</t>
+  </si>
+  <si>
+    <t>16,14</t>
+  </si>
+  <si>
+    <t>27,74</t>
+  </si>
+  <si>
+    <t>10,83</t>
+  </si>
+  <si>
+    <t>10,89</t>
+  </si>
+  <si>
+    <t>20,16</t>
+  </si>
+  <si>
+    <t>20,26</t>
+  </si>
+  <si>
+    <t>6,68</t>
+  </si>
+  <si>
+    <t>12,52</t>
+  </si>
+  <si>
+    <t>4,46</t>
+  </si>
+  <si>
+    <t>63,62</t>
+  </si>
+  <si>
+    <t>16,23</t>
+  </si>
+  <si>
+    <t>3,27</t>
+  </si>
+  <si>
+    <t>22,91</t>
+  </si>
+  <si>
+    <t>23,05</t>
+  </si>
+  <si>
+    <t>12,18</t>
+  </si>
+  <si>
+    <t>23,11</t>
+  </si>
+  <si>
+    <t>8,01</t>
+  </si>
+  <si>
+    <t>34,05</t>
+  </si>
+  <si>
+    <t>13,88</t>
+  </si>
+  <si>
+    <t>11,9</t>
+  </si>
+  <si>
+    <t>26,05</t>
+  </si>
+  <si>
+    <t>26,11</t>
+  </si>
+  <si>
+    <t>11,5</t>
+  </si>
+  <si>
+    <t>20,58</t>
+  </si>
+  <si>
+    <t>9,96</t>
+  </si>
+  <si>
+    <t>44,38</t>
   </si>
   <si>
     <t>18,28</t>
   </si>
   <si>
-    <t>8,27</t>
-  </si>
-  <si>
-    <t>43,98</t>
-  </si>
-  <si>
-    <t>16,53</t>
+    <t>6,47</t>
+  </si>
+  <si>
+    <t>29,77</t>
+  </si>
+  <si>
+    <t>29,87</t>
+  </si>
+  <si>
+    <t>0,08</t>
+  </si>
+  <si>
+    <t>7,88</t>
+  </si>
+  <si>
+    <t>16,09</t>
+  </si>
+  <si>
+    <t>5,54</t>
+  </si>
+  <si>
+    <t>59,05</t>
+  </si>
+  <si>
+    <t>12,74</t>
+  </si>
+  <si>
+    <t>7,96</t>
+  </si>
+  <si>
+    <t>20,63</t>
+  </si>
+  <si>
+    <t>20,71</t>
+  </si>
+  <si>
+    <t>0,09</t>
+  </si>
+  <si>
+    <t>6,53</t>
+  </si>
+  <si>
+    <t>23,28</t>
+  </si>
+  <si>
+    <t>6,65</t>
+  </si>
+  <si>
+    <t>45,27</t>
+  </si>
+  <si>
+    <t>16,15</t>
+  </si>
+  <si>
+    <t>10,36</t>
+  </si>
+  <si>
+    <t>22,68</t>
+  </si>
+  <si>
+    <t>22,77</t>
+  </si>
+  <si>
+    <t>0,25</t>
+  </si>
+  <si>
+    <t>22,2</t>
+  </si>
+  <si>
+    <t>13,14</t>
+  </si>
+  <si>
+    <t>4,95</t>
+  </si>
+  <si>
+    <t>42,13</t>
+  </si>
+  <si>
+    <t>27,23</t>
+  </si>
+  <si>
+    <t>1,01</t>
+  </si>
+  <si>
+    <t>49,43</t>
+  </si>
+  <si>
+    <t>49,67</t>
+  </si>
+  <si>
+    <t>0,26</t>
+  </si>
+  <si>
+    <t>32,07</t>
+  </si>
+  <si>
+    <t>15,05</t>
+  </si>
+  <si>
+    <t>6,12</t>
+  </si>
+  <si>
+    <t>35,39</t>
+  </si>
+  <si>
+    <t>34,69</t>
+  </si>
+  <si>
+    <t>2,09</t>
+  </si>
+  <si>
+    <t>66,76</t>
+  </si>
+  <si>
+    <t>67,02</t>
+  </si>
+  <si>
+    <t>0,14</t>
+  </si>
+  <si>
+    <t>37,88</t>
+  </si>
+  <si>
+    <t>13,96</t>
+  </si>
+  <si>
+    <t>30,02</t>
+  </si>
+  <si>
+    <t>29,25</t>
+  </si>
+  <si>
+    <t>1,71</t>
+  </si>
+  <si>
+    <t>67,12</t>
+  </si>
+  <si>
+    <t>67,26</t>
+  </si>
+  <si>
+    <t>0,24</t>
+  </si>
+  <si>
+    <t>28,31</t>
+  </si>
+  <si>
+    <t>19,41</t>
+  </si>
+  <si>
+    <t>12,05</t>
+  </si>
+  <si>
+    <t>27,9</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>0,84</t>
+  </si>
+  <si>
+    <t>63,31</t>
+  </si>
+  <si>
+    <t>63,55</t>
+  </si>
+  <si>
+    <t>0,23</t>
+  </si>
+  <si>
+    <t>46,32</t>
+  </si>
+  <si>
+    <t>19,94</t>
+  </si>
+  <si>
+    <t>5,12</t>
+  </si>
+  <si>
+    <t>19,04</t>
+  </si>
+  <si>
+    <t>46,78</t>
+  </si>
+  <si>
+    <t>1,78</t>
+  </si>
+  <si>
+    <t>93,1</t>
+  </si>
+  <si>
+    <t>93,33</t>
+  </si>
+  <si>
+    <t>0,17</t>
+  </si>
+  <si>
+    <t>22,83</t>
+  </si>
+  <si>
+    <t>18,03</t>
+  </si>
+  <si>
+    <t>7,53</t>
+  </si>
+  <si>
+    <t>38,98</t>
+  </si>
+  <si>
+    <t>1,23</t>
+  </si>
+  <si>
+    <t>56,88</t>
+  </si>
+  <si>
+    <t>57,04</t>
+  </si>
+  <si>
+    <t>0,33</t>
+  </si>
+  <si>
+    <t>0,04</t>
+  </si>
+  <si>
+    <t>7,51</t>
+  </si>
+  <si>
+    <t>15,17</t>
+  </si>
+  <si>
+    <t>7,89</t>
+  </si>
+  <si>
+    <t>49,46</t>
+  </si>
+  <si>
+    <t>11,71</t>
+  </si>
+  <si>
+    <t>5,72</t>
+  </si>
+  <si>
+    <t>19,22</t>
+  </si>
+  <si>
+    <t>19,55</t>
+  </si>
+  <si>
+    <t>23,7</t>
+  </si>
+  <si>
+    <t>20,06</t>
+  </si>
+  <si>
+    <t>19,01</t>
+  </si>
+  <si>
+    <t>21,17</t>
+  </si>
+  <si>
+    <t>20,67</t>
+  </si>
+  <si>
+    <t>1,67</t>
+  </si>
+  <si>
+    <t>44,63</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha BKU</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha yang Ditemukan dan Baru (UB + UMKM)</t>
+  </si>
+  <si>
+    <t>Persentase Kolom 4 21</t>
+  </si>
+  <si>
+    <t>Persentase hasil bagi jumlah usaha pada kolom tersebut dengan jumlah prelist usaha (kolom 3).</t>
+  </si>
+  <si>
+    <t>PROGRES PENDATAAN - SKALA USAHA</t>
+  </si>
+  <si>
+    <t>JUMLAH PRELIST</t>
+  </si>
+  <si>
+    <t>JUMLAH USAHA BKU MENURUT STATUS SKALA USAHA (UB, UM, UMK)</t>
+  </si>
+  <si>
+    <t>UB​</t>
+  </si>
+  <si>
+    <t>Persentase UB​</t>
+  </si>
+  <si>
+    <t>UM​</t>
+  </si>
+  <si>
+    <t>Persentase UM​</t>
+  </si>
+  <si>
+    <t>UMK​</t>
+  </si>
+  <si>
+    <t>Persentase UMK​</t>
+  </si>
+  <si>
+    <t>Tidak Dapat Diklasifikasikan</t>
+  </si>
+  <si>
+    <t>Total Usaha BKU</t>
+  </si>
+  <si>
+    <t>Persentase Total Usaha BKU</t>
+  </si>
+  <si>
+    <t>87,9</t>
+  </si>
+  <si>
+    <t>15,1</t>
+  </si>
+  <si>
+    <t>29,05</t>
+  </si>
+  <si>
+    <t>134,78</t>
+  </si>
+  <si>
+    <t>39,07</t>
+  </si>
+  <si>
+    <t>35,17</t>
+  </si>
+  <si>
+    <t>59,65</t>
+  </si>
+  <si>
+    <t>23,38</t>
+  </si>
+  <si>
+    <t>20,05</t>
+  </si>
+  <si>
+    <t>111,03</t>
+  </si>
+  <si>
+    <t>11,15</t>
+  </si>
+  <si>
+    <t>22,92</t>
+  </si>
+  <si>
+    <t>127,85</t>
+  </si>
+  <si>
+    <t>22,94</t>
+  </si>
+  <si>
+    <t>25,91</t>
+  </si>
+  <si>
+    <t>109,35</t>
+  </si>
+  <si>
+    <t>18,62</t>
+  </si>
+  <si>
+    <t>29,71</t>
+  </si>
+  <si>
+    <t>86,67</t>
+  </si>
+  <si>
+    <t>19,33</t>
+  </si>
+  <si>
+    <t>20,56</t>
+  </si>
+  <si>
+    <t>137,14</t>
+  </si>
+  <si>
+    <t>17,83</t>
+  </si>
+  <si>
+    <t>22,54</t>
+  </si>
+  <si>
+    <t>115,69</t>
+  </si>
+  <si>
+    <t>7,48</t>
+  </si>
+  <si>
+    <t>50,21</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>39,39</t>
+  </si>
+  <si>
+    <t>66,85</t>
+  </si>
+  <si>
+    <t>128,13</t>
+  </si>
+  <si>
+    <t>144,44</t>
+  </si>
+  <si>
+    <t>66,75</t>
+  </si>
+  <si>
+    <t>111,11</t>
+  </si>
+  <si>
+    <t>36,84</t>
+  </si>
+  <si>
+    <t>63,45</t>
+  </si>
+  <si>
+    <t>113,04</t>
+  </si>
+  <si>
+    <t>57,58</t>
+  </si>
+  <si>
+    <t>56,89</t>
+  </si>
+  <si>
+    <t>65,79</t>
+  </si>
+  <si>
+    <t>10,27</t>
+  </si>
+  <si>
+    <t>19,45</t>
+  </si>
+  <si>
+    <t>122,5</t>
+  </si>
+  <si>
+    <t>46,35</t>
+  </si>
+  <si>
+    <t>44,17</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha (UB/UM/UMK)</t>
+  </si>
+  <si>
+    <t>Jumlah prelist usaha yang berhasil didata (keberadaan ditemukan, baru, pindah dapat ditelusuri) berdasarkan skala usaha, untuk usaha baru didekati dengan omzet sebagai berikut: UB (lebih dari 50 Milyar), UM (15-50 Milyar), UMK - Kecil (2-15 Milyar), UMK - Mikro (0-2 Milyar).</t>
+  </si>
+  <si>
+    <t>Tidak Dapat Diklasifikasikan (Kolom 10)</t>
+  </si>
+  <si>
+    <t>Usaha baru dengan nilai omzet/pendapatan kosong sehingga tidak dapat diklasifikasikan skala usahanya, misalnya usaha unit pembantu/penunjang.</t>
+  </si>
+  <si>
+    <t>Persentase Jumlah UB</t>
+  </si>
+  <si>
+    <t>Persentase hasil bagi jumlah UB yang berhasil didata dengan jumlah prelist UB (kolom 3).</t>
+  </si>
+  <si>
+    <t>Persentase Jumlah UM</t>
+  </si>
+  <si>
+    <t>Persentase hasil bagi jumlah UM yang berhasil didata dengan jumlah prelist UM (kolom 4).</t>
+  </si>
+  <si>
+    <t>Persentase Jumlah UMK</t>
+  </si>
+  <si>
+    <t>Persentase hasil bagi jumlah UMK yang berhasil didata dengan jumlah prelist UMK (kolom 5).</t>
+  </si>
+  <si>
+    <t>PROGRES PENDATAAN - USAHA KELUARGA</t>
+  </si>
+  <si>
+    <t>Jumlah Prelist Usaha Keluarga (ST2023 + UMKM)</t>
+  </si>
+  <si>
+    <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha dalam Keluarga (Ditemukan + Baru)</t>
+  </si>
+  <si>
+    <t>Persentase Usaha dalam Keluarga (Ditemukan + Baru)</t>
+  </si>
+  <si>
+    <t>50,19</t>
+  </si>
+  <si>
+    <t>25,04</t>
+  </si>
+  <si>
+    <t>0,41</t>
+  </si>
+  <si>
+    <t>9,59</t>
+  </si>
+  <si>
+    <t>35,11</t>
+  </si>
+  <si>
+    <t>85,3</t>
+  </si>
+  <si>
+    <t>58,21</t>
+  </si>
+  <si>
+    <t>0,53</t>
+  </si>
+  <si>
+    <t>8,92</t>
+  </si>
+  <si>
+    <t>29,72</t>
+  </si>
+  <si>
+    <t>87,93</t>
+  </si>
+  <si>
+    <t>46,74</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>0,47</t>
+  </si>
+  <si>
+    <t>7,99</t>
+  </si>
+  <si>
+    <t>35,56</t>
+  </si>
+  <si>
+    <t>82,3</t>
+  </si>
+  <si>
+    <t>39,46</t>
+  </si>
+  <si>
+    <t>24,71</t>
+  </si>
+  <si>
+    <t>15,41</t>
+  </si>
+  <si>
+    <t>33,37</t>
+  </si>
+  <si>
+    <t>51,91</t>
+  </si>
+  <si>
+    <t>23,63</t>
+  </si>
+  <si>
+    <t>8,36</t>
+  </si>
+  <si>
+    <t>37,93</t>
+  </si>
+  <si>
+    <t>89,84</t>
+  </si>
+  <si>
+    <t>52,33</t>
+  </si>
+  <si>
+    <t>23,16</t>
+  </si>
+  <si>
+    <t>10,67</t>
+  </si>
+  <si>
+    <t>33,91</t>
+  </si>
+  <si>
+    <t>86,24</t>
+  </si>
+  <si>
+    <t>49,81</t>
+  </si>
+  <si>
+    <t>20,85</t>
+  </si>
+  <si>
+    <t>17,52</t>
+  </si>
+  <si>
+    <t>39,04</t>
+  </si>
+  <si>
+    <t>88,86</t>
+  </si>
+  <si>
+    <t>50,37</t>
+  </si>
+  <si>
+    <t>24,09</t>
+  </si>
+  <si>
+    <t>0,21</t>
+  </si>
+  <si>
+    <t>8,4</t>
+  </si>
+  <si>
+    <t>40,15</t>
+  </si>
+  <si>
+    <t>90,52</t>
+  </si>
+  <si>
+    <t>46,23</t>
+  </si>
+  <si>
+    <t>28,12</t>
+  </si>
+  <si>
+    <t>4,91</t>
+  </si>
+  <si>
+    <t>28,83</t>
+  </si>
+  <si>
+    <t>75,05</t>
+  </si>
+  <si>
+    <t>53,82</t>
+  </si>
+  <si>
+    <t>28,46</t>
+  </si>
+  <si>
+    <t>0,76</t>
   </si>
   <si>
     <t>6,74</t>
   </si>
   <si>
-    <t>28,7</t>
-  </si>
-  <si>
-    <t>28,85</t>
-  </si>
-  <si>
-    <t>0,2</t>
-  </si>
-  <si>
-    <t>0,03</t>
-  </si>
-  <si>
-    <t>17,26</t>
-  </si>
-  <si>
-    <t>17,09</t>
-  </si>
-  <si>
-    <t>12,84</t>
-  </si>
-  <si>
-    <t>41,58</t>
-  </si>
-  <si>
-    <t>18,16</t>
-  </si>
-  <si>
-    <t>1,53</t>
-  </si>
-  <si>
-    <t>35,42</t>
-  </si>
-  <si>
-    <t>35,63</t>
-  </si>
-  <si>
-    <t>0,1</t>
-  </si>
-  <si>
-    <t>0,05</t>
-  </si>
-  <si>
-    <t>9,25</t>
-  </si>
-  <si>
-    <t>22,9</t>
-  </si>
-  <si>
-    <t>16,07</t>
-  </si>
-  <si>
-    <t>27,61</t>
-  </si>
-  <si>
-    <t>10,71</t>
-  </si>
-  <si>
-    <t>10,84</t>
-  </si>
-  <si>
-    <t>19,96</t>
-  </si>
-  <si>
-    <t>20,06</t>
-  </si>
-  <si>
-    <t>0,14</t>
-  </si>
-  <si>
-    <t>6,57</t>
-  </si>
-  <si>
-    <t>12,41</t>
-  </si>
-  <si>
-    <t>4,44</t>
-  </si>
-  <si>
-    <t>63,53</t>
+    <t>23,97</t>
+  </si>
+  <si>
+    <t>77,78</t>
+  </si>
+  <si>
+    <t>49,82</t>
+  </si>
+  <si>
+    <t>30,94</t>
+  </si>
+  <si>
+    <t>0,62</t>
+  </si>
+  <si>
+    <t>6,15</t>
+  </si>
+  <si>
+    <t>28,05</t>
+  </si>
+  <si>
+    <t>77,87</t>
+  </si>
+  <si>
+    <t>47,13</t>
+  </si>
+  <si>
+    <t>30,27</t>
+  </si>
+  <si>
+    <t>0,71</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>28,1</t>
+  </si>
+  <si>
+    <t>75,23</t>
+  </si>
+  <si>
+    <t>58,18</t>
+  </si>
+  <si>
+    <t>24,48</t>
+  </si>
+  <si>
+    <t>0,58</t>
+  </si>
+  <si>
+    <t>7,64</t>
+  </si>
+  <si>
+    <t>32,53</t>
+  </si>
+  <si>
+    <t>90,71</t>
+  </si>
+  <si>
+    <t>54,64</t>
+  </si>
+  <si>
+    <t>29,52</t>
+  </si>
+  <si>
+    <t>0,46</t>
+  </si>
+  <si>
+    <t>4,86</t>
+  </si>
+  <si>
+    <t>26,85</t>
+  </si>
+  <si>
+    <t>81,49</t>
+  </si>
+  <si>
+    <t>24,44</t>
+  </si>
+  <si>
+    <t>31,38</t>
+  </si>
+  <si>
+    <t>14,89</t>
+  </si>
+  <si>
+    <t>326,34</t>
+  </si>
+  <si>
+    <t>350,78</t>
+  </si>
+  <si>
+    <t>47,03</t>
+  </si>
+  <si>
+    <t>28,73</t>
+  </si>
+  <si>
+    <t>2,5</t>
+  </si>
+  <si>
+    <t>3,14</t>
+  </si>
+  <si>
+    <t>37,89</t>
+  </si>
+  <si>
+    <t>84,92</t>
+  </si>
+  <si>
+    <t>Persentase Kolom 4 9</t>
+  </si>
+  <si>
+    <t>PROGRES PENDATAAN - KESELURUHAN USAHA</t>
+  </si>
+  <si>
+    <t>Total Prelist Usaha dan Usaha Keluarga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USAHA BKU </t>
+  </si>
+  <si>
+    <t>USAHA DALAM KELUARGA</t>
+  </si>
+  <si>
+    <t>Total Usaha</t>
+  </si>
+  <si>
+    <t>Persentase Total Usaha</t>
+  </si>
+  <si>
+    <t>Subtotal</t>
+  </si>
+  <si>
+    <t>Persentase Subtotal</t>
+  </si>
+  <si>
+    <t>Ditemukan​</t>
+  </si>
+  <si>
+    <t>Persentase Ditemukan​</t>
+  </si>
+  <si>
+    <t>Baru​</t>
+  </si>
+  <si>
+    <t>Persentase Baru​</t>
+  </si>
+  <si>
+    <t>Subtotal​</t>
+  </si>
+  <si>
+    <t>Persentase Subtotal​</t>
+  </si>
+  <si>
+    <t>12,43</t>
+  </si>
+  <si>
+    <t>70,65</t>
+  </si>
+  <si>
+    <t>17,41</t>
+  </si>
+  <si>
+    <t>82,51</t>
+  </si>
+  <si>
+    <t>9,44</t>
+  </si>
+  <si>
+    <t>6,82</t>
+  </si>
+  <si>
+    <t>57,08</t>
+  </si>
+  <si>
+    <t>12,24</t>
+  </si>
+  <si>
+    <t>72,76</t>
+  </si>
+  <si>
+    <t>11,59</t>
+  </si>
+  <si>
+    <t>72,73</t>
+  </si>
+  <si>
+    <t>7,97</t>
+  </si>
+  <si>
+    <t>66,2</t>
+  </si>
+  <si>
+    <t>6,62</t>
+  </si>
+  <si>
+    <t>74,05</t>
+  </si>
+  <si>
+    <t>22,44</t>
+  </si>
+  <si>
+    <t>71,35</t>
+  </si>
+  <si>
+    <t>32,33</t>
+  </si>
+  <si>
+    <t>76,64</t>
+  </si>
+  <si>
+    <t>38,02</t>
+  </si>
+  <si>
+    <t>76,19</t>
+  </si>
+  <si>
+    <t>28,55</t>
+  </si>
+  <si>
+    <t>73,82</t>
+  </si>
+  <si>
+    <t>46,55</t>
+  </si>
+  <si>
+    <t>90,94</t>
+  </si>
+  <si>
+    <t>22,99</t>
+  </si>
+  <si>
+    <t>79,17</t>
+  </si>
+  <si>
+    <t>7,83</t>
+  </si>
+  <si>
+    <t>48,56</t>
+  </si>
+  <si>
+    <t>23,95</t>
+  </si>
+  <si>
+    <t>68,13</t>
+  </si>
+  <si>
+    <t>Total Prelist Usaha Dan Usaha Keluarga</t>
+  </si>
+  <si>
+    <t>Jumlah Prelist Usaha Ditambah Jumlah Prelist Usaha Keluarga (ST2023 + UMKM) atau Kolom (3) + (4).</t>
+  </si>
+  <si>
+    <t>Persentase Usaha BKU Ditemukan</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha BKU Ditemukan/Pindah Dapat Ditelusuri (CAPI dan CAWI) dibagi dengan Jumlah Prelist Usaha (kolom 3).</t>
+  </si>
+  <si>
+    <t>Persentase Usaha BKU Baru</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha BKU Baru (CAPI) dibagi Jumlah Prelist Usaha (kolom 3).</t>
+  </si>
+  <si>
+    <t>Persentase Usaha Keluarga Ditemukan</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha Keluarga Ditemukan dibagi dengan Jumlah Prelist Usaha Keluarga (ST2023 + UMKM) atau Kolom (4).</t>
+  </si>
+  <si>
+    <t>Persentase Usaha Keluarga Baru</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha Keluarga Baru dibagi dengan Jumlah Prelist Usaha Keluarga (ST2023 + UMKM) atau Kolom (4).</t>
+  </si>
+  <si>
+    <t>PROGRES PENDATAAN - PROPORSI USAHA</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha (Semua Status Keberadaan Usaha)</t>
+  </si>
+  <si>
+    <t>Persentase Usaha BKU</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha dalam Keluarga</t>
+  </si>
+  <si>
+    <t>Persentase Usaha dalam Keluarga</t>
+  </si>
+  <si>
+    <t>54,8</t>
+  </si>
+  <si>
+    <t>3,15</t>
+  </si>
+  <si>
+    <t>67,7</t>
+  </si>
+  <si>
+    <t>4,64</t>
+  </si>
+  <si>
+    <t>56,39</t>
+  </si>
+  <si>
+    <t>45,19</t>
+  </si>
+  <si>
+    <t>57,78</t>
+  </si>
+  <si>
+    <t>6,14</t>
+  </si>
+  <si>
+    <t>56,24</t>
+  </si>
+  <si>
+    <t>5,8</t>
+  </si>
+  <si>
+    <t>49,93</t>
+  </si>
+  <si>
+    <t>4,73</t>
+  </si>
+  <si>
+    <t>58,52</t>
+  </si>
+  <si>
+    <t>6,66</t>
+  </si>
+  <si>
+    <t>58,92</t>
+  </si>
+  <si>
+    <t>6,21</t>
+  </si>
+  <si>
+    <t>60,54</t>
+  </si>
+  <si>
+    <t>9,21</t>
+  </si>
+  <si>
+    <t>56,77</t>
+  </si>
+  <si>
+    <t>6,46</t>
+  </si>
+  <si>
+    <t>55,68</t>
+  </si>
+  <si>
+    <t>66,3</t>
+  </si>
+  <si>
+    <t>63,13</t>
+  </si>
+  <si>
+    <t>14,99</t>
+  </si>
+  <si>
+    <t>25,81</t>
+  </si>
+  <si>
+    <t>16,41</t>
+  </si>
+  <si>
+    <t>43,74</t>
+  </si>
+  <si>
+    <t>Jumlah Usaha (Semua Status Keberadaan Usaha) Kolom 3</t>
+  </si>
+  <si>
+    <t>Jumlah seluruh usaha BKU dan Usaha Keluarga dari CAPI dan CAWI dengan semua status keberadaan.</t>
+  </si>
+  <si>
+    <t>PROGRES PENDATAAN - JARINGAN USAHA</t>
+  </si>
+  <si>
+    <t>JUMLAH USAHA BERDASARKAN JARINGAN USAHA</t>
+  </si>
+  <si>
+    <t>Tunggal</t>
+  </si>
+  <si>
+    <t>Kantor Pusat</t>
+  </si>
+  <si>
+    <t>Cabang</t>
+  </si>
+  <si>
+    <t>Perwakilan</t>
+  </si>
+  <si>
+    <t>Pabrik</t>
+  </si>
+  <si>
+    <t>Unit Pembantu</t>
+  </si>
+  <si>
+    <t>PROGRES PENDATAAN - PROPORSI PERTANIAN</t>
+  </si>
+  <si>
+    <t>Jumlah Prelist Usaha SE2026</t>
+  </si>
+  <si>
+    <t>Target Berdasarkan Data ST</t>
+  </si>
+  <si>
+    <t>Jumlah UTP Subsektor Prelist</t>
+  </si>
+  <si>
+    <t>USAHA PERTANIAN BKU</t>
+  </si>
+  <si>
+    <t>USAHA PERTANIAN DALAM KELUARGA</t>
+  </si>
+  <si>
+    <t>76,05</t>
+  </si>
+  <si>
+    <t>69,31</t>
+  </si>
+  <si>
+    <t>30,69</t>
+  </si>
+  <si>
+    <t>13,7</t>
+  </si>
+  <si>
+    <t>86,3</t>
+  </si>
+  <si>
+    <t>68,85</t>
+  </si>
+  <si>
+    <t>31,15</t>
+  </si>
+  <si>
+    <t>25,23</t>
+  </si>
+  <si>
+    <t>74,77</t>
+  </si>
+  <si>
+    <t>69,35</t>
+  </si>
+  <si>
+    <t>30,65</t>
+  </si>
+  <si>
+    <t>15,56</t>
+  </si>
+  <si>
+    <t>84,44</t>
+  </si>
+  <si>
+    <t>70,89</t>
+  </si>
+  <si>
+    <t>29,11</t>
+  </si>
+  <si>
+    <t>44,73</t>
+  </si>
+  <si>
+    <t>55,27</t>
+  </si>
+  <si>
+    <t>69,29</t>
+  </si>
+  <si>
+    <t>30,71</t>
+  </si>
+  <si>
+    <t>36,13</t>
+  </si>
+  <si>
+    <t>63,87</t>
+  </si>
+  <si>
+    <t>70,22</t>
+  </si>
+  <si>
+    <t>29,78</t>
+  </si>
+  <si>
+    <t>37,29</t>
+  </si>
+  <si>
+    <t>62,71</t>
+  </si>
+  <si>
+    <t>68,41</t>
+  </si>
+  <si>
+    <t>31,59</t>
+  </si>
+  <si>
+    <t>15,19</t>
+  </si>
+  <si>
+    <t>84,81</t>
+  </si>
+  <si>
+    <t>65,71</t>
+  </si>
+  <si>
+    <t>34,29</t>
+  </si>
+  <si>
+    <t>7,55</t>
+  </si>
+  <si>
+    <t>92,45</t>
+  </si>
+  <si>
+    <t>65,29</t>
+  </si>
+  <si>
+    <t>34,71</t>
+  </si>
+  <si>
+    <t>23,33</t>
+  </si>
+  <si>
+    <t>76,67</t>
+  </si>
+  <si>
+    <t>73,94</t>
+  </si>
+  <si>
+    <t>26,06</t>
+  </si>
+  <si>
+    <t>91,6</t>
+  </si>
+  <si>
+    <t>70,64</t>
+  </si>
+  <si>
+    <t>29,36</t>
+  </si>
+  <si>
+    <t>6,88</t>
+  </si>
+  <si>
+    <t>93,12</t>
+  </si>
+  <si>
+    <t>66,53</t>
+  </si>
+  <si>
+    <t>33,47</t>
   </si>
   <si>
     <t>15,91</t>
   </si>
   <si>
-    <t>3,25</t>
-  </si>
-  <si>
-    <t>22,48</t>
-  </si>
-  <si>
-    <t>22,62</t>
-  </si>
-  <si>
-    <t>12,05</t>
-  </si>
-  <si>
-    <t>22,93</t>
-  </si>
-  <si>
-    <t>7,98</t>
-  </si>
-  <si>
-    <t>33,96</t>
-  </si>
-  <si>
-    <t>13,58</t>
-  </si>
-  <si>
-    <t>11,82</t>
-  </si>
-  <si>
-    <t>25,63</t>
-  </si>
-  <si>
-    <t>25,69</t>
-  </si>
-  <si>
-    <t>11,38</t>
-  </si>
-  <si>
-    <t>20,38</t>
-  </si>
-  <si>
-    <t>9,9</t>
-  </si>
-  <si>
-    <t>44,38</t>
-  </si>
-  <si>
-    <t>18,04</t>
-  </si>
-  <si>
-    <t>6,45</t>
-  </si>
-  <si>
-    <t>29,42</t>
-  </si>
-  <si>
-    <t>29,52</t>
-  </si>
-  <si>
-    <t>0,08</t>
-  </si>
-  <si>
-    <t>7,83</t>
-  </si>
-  <si>
-    <t>16,01</t>
-  </si>
-  <si>
-    <t>5,54</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>12,64</t>
-  </si>
-  <si>
-    <t>7,92</t>
-  </si>
-  <si>
-    <t>20,47</t>
-  </si>
-  <si>
-    <t>20,55</t>
-  </si>
-  <si>
-    <t>0,09</t>
-  </si>
-  <si>
-    <t>6,42</t>
-  </si>
-  <si>
-    <t>23,14</t>
-  </si>
-  <si>
-    <t>6,61</t>
-  </si>
-  <si>
-    <t>45,23</t>
-  </si>
-  <si>
-    <t>15,82</t>
-  </si>
-  <si>
-    <t>10,28</t>
-  </si>
-  <si>
-    <t>22,24</t>
-  </si>
-  <si>
-    <t>22,33</t>
-  </si>
-  <si>
-    <t>0,25</t>
-  </si>
-  <si>
-    <t>22,02</t>
-  </si>
-  <si>
-    <t>13,09</t>
-  </si>
-  <si>
-    <t>4,94</t>
-  </si>
-  <si>
-    <t>42,1</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>1,01</t>
-  </si>
-  <si>
-    <t>49,02</t>
-  </si>
-  <si>
-    <t>49,26</t>
-  </si>
-  <si>
-    <t>0,26</t>
-  </si>
-  <si>
-    <t>31,92</t>
-  </si>
-  <si>
-    <t>15,01</t>
-  </si>
-  <si>
-    <t>6,07</t>
-  </si>
-  <si>
-    <t>35,48</t>
-  </si>
-  <si>
-    <t>34,38</t>
-  </si>
-  <si>
-    <t>2,08</t>
-  </si>
-  <si>
-    <t>66,29</t>
-  </si>
-  <si>
-    <t>66,55</t>
-  </si>
-  <si>
-    <t>37,57</t>
-  </si>
-  <si>
-    <t>13,9</t>
-  </si>
-  <si>
-    <t>3,65</t>
-  </si>
-  <si>
-    <t>29,87</t>
-  </si>
-  <si>
-    <t>28,98</t>
-  </si>
-  <si>
-    <t>1,69</t>
-  </si>
-  <si>
-    <t>66,69</t>
-  </si>
-  <si>
-    <t>0,24</t>
-  </si>
-  <si>
-    <t>28,25</t>
-  </si>
-  <si>
-    <t>19,41</t>
-  </si>
-  <si>
-    <t>12,04</t>
-  </si>
-  <si>
-    <t>27,9</t>
-  </si>
-  <si>
-    <t>34,96</t>
-  </si>
-  <si>
-    <t>0,86</t>
-  </si>
-  <si>
-    <t>63,22</t>
-  </si>
-  <si>
-    <t>63,46</t>
-  </si>
-  <si>
-    <t>0,23</t>
-  </si>
-  <si>
-    <t>46,26</t>
-  </si>
-  <si>
-    <t>5,12</t>
-  </si>
-  <si>
-    <t>19,04</t>
-  </si>
-  <si>
-    <t>46,61</t>
-  </si>
-  <si>
-    <t>1,79</t>
-  </si>
-  <si>
-    <t>92,88</t>
-  </si>
-  <si>
-    <t>93,11</t>
-  </si>
-  <si>
-    <t>0,17</t>
-  </si>
-  <si>
-    <t>22,79</t>
-  </si>
-  <si>
-    <t>17,94</t>
-  </si>
-  <si>
-    <t>7,53</t>
-  </si>
-  <si>
-    <t>39,05</t>
-  </si>
-  <si>
-    <t>33,9</t>
-  </si>
-  <si>
-    <t>1,23</t>
-  </si>
-  <si>
-    <t>56,69</t>
-  </si>
-  <si>
-    <t>56,86</t>
-  </si>
-  <si>
-    <t>0,33</t>
-  </si>
-  <si>
-    <t>0,04</t>
-  </si>
-  <si>
-    <t>7,43</t>
-  </si>
-  <si>
-    <t>15,05</t>
-  </si>
-  <si>
-    <t>7,8</t>
-  </si>
-  <si>
-    <t>49,33</t>
-  </si>
-  <si>
-    <t>11,6</t>
-  </si>
-  <si>
-    <t>5,69</t>
-  </si>
-  <si>
-    <t>19,36</t>
-  </si>
-  <si>
-    <t>23,59</t>
-  </si>
-  <si>
-    <t>19,94</t>
-  </si>
-  <si>
-    <t>18,97</t>
-  </si>
-  <si>
-    <t>21,1</t>
-  </si>
-  <si>
-    <t>20,42</t>
-  </si>
-  <si>
-    <t>1,67</t>
-  </si>
-  <si>
-    <t>44,01</t>
-  </si>
-  <si>
-    <t>44,26</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha BKU</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha yang Ditemukan dan Baru (UB + UMKM)</t>
-  </si>
-  <si>
-    <t>Persentase Kolom 4 21</t>
-  </si>
-  <si>
-    <t>Persentase hasil bagi jumlah usaha pada kolom tersebut dengan jumlah prelist usaha (kolom 3).</t>
-  </si>
-  <si>
-    <t>PROGRES PENDATAAN - SKALA USAHA</t>
-  </si>
-  <si>
-    <t>JUMLAH PRELIST</t>
-  </si>
-  <si>
-    <t>JUMLAH USAHA BKU MENURUT STATUS SKALA USAHA (UB, UM, UMK)</t>
-  </si>
-  <si>
-    <t>UB​</t>
-  </si>
-  <si>
-    <t>Persentase UB​</t>
-  </si>
-  <si>
-    <t>UM​</t>
-  </si>
-  <si>
-    <t>Persentase UM​</t>
-  </si>
-  <si>
-    <t>UMK​</t>
-  </si>
-  <si>
-    <t>Persentase UMK​</t>
-  </si>
-  <si>
-    <t>Tidak Dapat Diklasifikasikan</t>
-  </si>
-  <si>
-    <t>Total Usaha BKU</t>
-  </si>
-  <si>
-    <t>Persentase Total Usaha BKU</t>
-  </si>
-  <si>
-    <t>87,38</t>
-  </si>
-  <si>
-    <t>14,95</t>
-  </si>
-  <si>
-    <t>28,73</t>
-  </si>
-  <si>
-    <t>134,78</t>
-  </si>
-  <si>
-    <t>39,07</t>
-  </si>
-  <si>
-    <t>35,28</t>
-  </si>
-  <si>
-    <t>59,65</t>
-  </si>
-  <si>
-    <t>22,08</t>
-  </si>
-  <si>
-    <t>19,85</t>
-  </si>
-  <si>
-    <t>108,97</t>
-  </si>
-  <si>
-    <t>10,73</t>
-  </si>
-  <si>
-    <t>22,49</t>
-  </si>
-  <si>
-    <t>127,85</t>
-  </si>
-  <si>
-    <t>22,94</t>
-  </si>
-  <si>
-    <t>25,48</t>
-  </si>
-  <si>
-    <t>107,91</t>
-  </si>
-  <si>
-    <t>18,5</t>
-  </si>
-  <si>
-    <t>29,37</t>
-  </si>
-  <si>
-    <t>86,67</t>
-  </si>
-  <si>
-    <t>19,33</t>
-  </si>
-  <si>
-    <t>20,4</t>
-  </si>
-  <si>
-    <t>137,14</t>
-  </si>
-  <si>
-    <t>16,28</t>
-  </si>
-  <si>
-    <t>22,11</t>
-  </si>
-  <si>
-    <t>113,73</t>
-  </si>
-  <si>
-    <t>7,48</t>
-  </si>
-  <si>
-    <t>49,8</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>39,39</t>
-  </si>
-  <si>
-    <t>66,38</t>
-  </si>
-  <si>
-    <t>128,13</t>
-  </si>
-  <si>
-    <t>144,44</t>
-  </si>
-  <si>
-    <t>66,18</t>
-  </si>
-  <si>
-    <t>111,11</t>
-  </si>
-  <si>
-    <t>36,84</t>
-  </si>
-  <si>
-    <t>63,36</t>
-  </si>
-  <si>
-    <t>113,04</t>
-  </si>
-  <si>
-    <t>57,58</t>
-  </si>
-  <si>
-    <t>56,7</t>
-  </si>
-  <si>
-    <t>65,49</t>
-  </si>
-  <si>
-    <t>10,17</t>
-  </si>
-  <si>
-    <t>19,26</t>
-  </si>
-  <si>
-    <t>122,5</t>
-  </si>
-  <si>
-    <t>46,35</t>
-  </si>
-  <si>
-    <t>43,8</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha (UB/UM/UMK)</t>
-  </si>
-  <si>
-    <t>Jumlah prelist usaha yang berhasil didata (keberadaan ditemukan, baru, pindah dapat ditelusuri) berdasarkan skala usaha, untuk usaha baru didekati dengan omzet sebagai berikut: UB (lebih dari 50 Milyar), UM (15-50 Milyar), UMK - Kecil (2-15 Milyar), UMK - Mikro (0-2 Milyar).</t>
-  </si>
-  <si>
-    <t>Tidak Dapat Diklasifikasikan (Kolom 10)</t>
-  </si>
-  <si>
-    <t>Usaha baru dengan nilai omzet/pendapatan kosong sehingga tidak dapat diklasifikasikan skala usahanya, misalnya usaha unit pembantu/penunjang.</t>
-  </si>
-  <si>
-    <t>Persentase Jumlah UB</t>
-  </si>
-  <si>
-    <t>Persentase hasil bagi jumlah UB yang berhasil didata dengan jumlah prelist UB (kolom 3).</t>
-  </si>
-  <si>
-    <t>Persentase Jumlah UM</t>
-  </si>
-  <si>
-    <t>Persentase hasil bagi jumlah UM yang berhasil didata dengan jumlah prelist UM (kolom 4).</t>
-  </si>
-  <si>
-    <t>Persentase Jumlah UMK</t>
-  </si>
-  <si>
-    <t>Persentase hasil bagi jumlah UMK yang berhasil didata dengan jumlah prelist UMK (kolom 5).</t>
-  </si>
-  <si>
-    <t>PROGRES PENDATAAN - USAHA KELUARGA</t>
-  </si>
-  <si>
-    <t>Jumlah Prelist Usaha Keluarga (ST2023 + UMKM)</t>
-  </si>
-  <si>
-    <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha dalam Keluarga (Ditemukan + Baru)</t>
-  </si>
-  <si>
-    <t>Persentase Usaha dalam Keluarga (Ditemukan + Baru)</t>
-  </si>
-  <si>
-    <t>49,9</t>
-  </si>
-  <si>
-    <t>24,87</t>
-  </si>
-  <si>
-    <t>0,41</t>
-  </si>
-  <si>
-    <t>9,58</t>
-  </si>
-  <si>
-    <t>34,92</t>
-  </si>
-  <si>
-    <t>84,82</t>
-  </si>
-  <si>
-    <t>58,41</t>
-  </si>
-  <si>
-    <t>20,19</t>
-  </si>
-  <si>
-    <t>0,53</t>
-  </si>
-  <si>
-    <t>8,97</t>
-  </si>
-  <si>
-    <t>29,91</t>
-  </si>
-  <si>
-    <t>88,31</t>
-  </si>
-  <si>
-    <t>46,51</t>
-  </si>
-  <si>
-    <t>25,81</t>
-  </si>
-  <si>
-    <t>0,47</t>
-  </si>
-  <si>
-    <t>7,96</t>
-  </si>
-  <si>
-    <t>35,37</t>
-  </si>
-  <si>
-    <t>81,87</t>
-  </si>
-  <si>
-    <t>39,09</t>
-  </si>
-  <si>
-    <t>24,44</t>
-  </si>
-  <si>
-    <t>15,32</t>
-  </si>
-  <si>
-    <t>33,13</t>
-  </si>
-  <si>
-    <t>72,22</t>
-  </si>
-  <si>
-    <t>51,51</t>
-  </si>
-  <si>
-    <t>23,46</t>
-  </si>
-  <si>
-    <t>8,35</t>
-  </si>
-  <si>
-    <t>37,62</t>
-  </si>
-  <si>
-    <t>89,13</t>
-  </si>
-  <si>
-    <t>51,98</t>
-  </si>
-  <si>
-    <t>22,96</t>
-  </si>
-  <si>
-    <t>10,68</t>
-  </si>
-  <si>
-    <t>33,69</t>
-  </si>
-  <si>
-    <t>85,67</t>
-  </si>
-  <si>
-    <t>49,56</t>
-  </si>
-  <si>
-    <t>20,72</t>
-  </si>
-  <si>
-    <t>17,49</t>
-  </si>
-  <si>
-    <t>38,87</t>
-  </si>
-  <si>
-    <t>88,42</t>
-  </si>
-  <si>
-    <t>50,01</t>
-  </si>
-  <si>
-    <t>23,81</t>
-  </si>
-  <si>
-    <t>0,21</t>
-  </si>
-  <si>
-    <t>8,41</t>
-  </si>
-  <si>
-    <t>39,88</t>
-  </si>
-  <si>
-    <t>89,89</t>
-  </si>
-  <si>
-    <t>45,8</t>
-  </si>
-  <si>
-    <t>27,86</t>
-  </si>
-  <si>
-    <t>4,9</t>
-  </si>
-  <si>
-    <t>28,61</t>
-  </si>
-  <si>
-    <t>74,41</t>
-  </si>
-  <si>
-    <t>53,59</t>
-  </si>
-  <si>
-    <t>28,36</t>
-  </si>
-  <si>
-    <t>0,76</t>
-  </si>
-  <si>
-    <t>6,76</t>
-  </si>
-  <si>
-    <t>23,86</t>
-  </si>
-  <si>
-    <t>77,45</t>
-  </si>
-  <si>
-    <t>49,42</t>
-  </si>
-  <si>
-    <t>30,67</t>
-  </si>
-  <si>
-    <t>0,62</t>
-  </si>
-  <si>
-    <t>6,12</t>
-  </si>
-  <si>
-    <t>27,85</t>
-  </si>
-  <si>
-    <t>77,27</t>
-  </si>
-  <si>
-    <t>47,11</t>
-  </si>
-  <si>
-    <t>30,23</t>
-  </si>
-  <si>
-    <t>0,71</t>
-  </si>
-  <si>
-    <t>12,01</t>
-  </si>
-  <si>
-    <t>28,1</t>
-  </si>
-  <si>
-    <t>75,21</t>
-  </si>
-  <si>
-    <t>58,1</t>
-  </si>
-  <si>
-    <t>24,45</t>
-  </si>
-  <si>
-    <t>0,58</t>
-  </si>
-  <si>
-    <t>7,63</t>
-  </si>
-  <si>
-    <t>32,49</t>
-  </si>
-  <si>
-    <t>90,6</t>
-  </si>
-  <si>
-    <t>54,62</t>
-  </si>
-  <si>
-    <t>29,49</t>
-  </si>
-  <si>
-    <t>0,46</t>
-  </si>
-  <si>
-    <t>4,86</t>
-  </si>
-  <si>
-    <t>26,82</t>
-  </si>
-  <si>
-    <t>81,44</t>
-  </si>
-  <si>
-    <t>24,29</t>
-  </si>
-  <si>
-    <t>31,16</t>
-  </si>
-  <si>
-    <t>0,85</t>
-  </si>
-  <si>
-    <t>14,84</t>
-  </si>
-  <si>
-    <t>324,47</t>
-  </si>
-  <si>
-    <t>348,76</t>
-  </si>
-  <si>
-    <t>46,84</t>
-  </si>
-  <si>
-    <t>2,48</t>
-  </si>
-  <si>
-    <t>3,14</t>
-  </si>
-  <si>
-    <t>37,73</t>
-  </si>
-  <si>
-    <t>84,57</t>
-  </si>
-  <si>
-    <t>Persentase Kolom 4 9</t>
-  </si>
-  <si>
-    <t>PROGRES PENDATAAN - KESELURUHAN USAHA</t>
-  </si>
-  <si>
-    <t>Total Prelist Usaha dan Usaha Keluarga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USAHA BKU </t>
-  </si>
-  <si>
-    <t>USAHA DALAM KELUARGA</t>
-  </si>
-  <si>
-    <t>Total Usaha</t>
-  </si>
-  <si>
-    <t>Persentase Total Usaha</t>
-  </si>
-  <si>
-    <t>Subtotal</t>
-  </si>
-  <si>
-    <t>Persentase Subtotal</t>
-  </si>
-  <si>
-    <t>Ditemukan​</t>
-  </si>
-  <si>
-    <t>Persentase Ditemukan​</t>
-  </si>
-  <si>
-    <t>Baru​</t>
-  </si>
-  <si>
-    <t>Persentase Baru​</t>
-  </si>
-  <si>
-    <t>Subtotal​</t>
-  </si>
-  <si>
-    <t>Persentase Subtotal​</t>
-  </si>
-  <si>
-    <t>12,32</t>
-  </si>
-  <si>
-    <t>70,21</t>
-  </si>
-  <si>
-    <t>17,46</t>
-  </si>
-  <si>
-    <t>82,87</t>
-  </si>
-  <si>
-    <t>9,35</t>
-  </si>
-  <si>
-    <t>6,71</t>
-  </si>
-  <si>
-    <t>56,52</t>
-  </si>
-  <si>
-    <t>12,11</t>
-  </si>
-  <si>
-    <t>72,12</t>
-  </si>
-  <si>
-    <t>11,48</t>
-  </si>
-  <si>
-    <t>72,21</t>
-  </si>
-  <si>
-    <t>7,91</t>
-  </si>
-  <si>
-    <t>65,86</t>
-  </si>
-  <si>
-    <t>6,51</t>
-  </si>
-  <si>
-    <t>73,47</t>
-  </si>
-  <si>
-    <t>22,26</t>
-  </si>
-  <si>
-    <t>70,74</t>
-  </si>
-  <si>
-    <t>32,18</t>
-  </si>
-  <si>
-    <t>76,29</t>
-  </si>
-  <si>
-    <t>37,71</t>
-  </si>
-  <si>
-    <t>75,6</t>
-  </si>
-  <si>
-    <t>28,5</t>
-  </si>
-  <si>
-    <t>73,79</t>
-  </si>
-  <si>
-    <t>46,49</t>
-  </si>
-  <si>
-    <t>90,82</t>
-  </si>
-  <si>
-    <t>79,1</t>
-  </si>
-  <si>
-    <t>7,76</t>
-  </si>
-  <si>
-    <t>48,21</t>
-  </si>
-  <si>
-    <t>23,84</t>
-  </si>
-  <si>
-    <t>67,78</t>
-  </si>
-  <si>
-    <t>Total Prelist Usaha Dan Usaha Keluarga</t>
-  </si>
-  <si>
-    <t>Jumlah Prelist Usaha Ditambah Jumlah Prelist Usaha Keluarga (ST2023 + UMKM) atau Kolom (3) + (4).</t>
-  </si>
-  <si>
-    <t>Persentase Usaha BKU Ditemukan</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha BKU Ditemukan/Pindah Dapat Ditelusuri (CAPI dan CAWI) dibagi dengan Jumlah Prelist Usaha (kolom 3).</t>
-  </si>
-  <si>
-    <t>Persentase Usaha BKU Baru</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha BKU Baru (CAPI) dibagi Jumlah Prelist Usaha (kolom 3).</t>
-  </si>
-  <si>
-    <t>Persentase Usaha Keluarga Ditemukan</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha Keluarga Ditemukan dibagi dengan Jumlah Prelist Usaha Keluarga (ST2023 + UMKM) atau Kolom (4).</t>
-  </si>
-  <si>
-    <t>Persentase Usaha Keluarga Baru</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha Keluarga Baru dibagi dengan Jumlah Prelist Usaha Keluarga (ST2023 + UMKM) atau Kolom (4).</t>
-  </si>
-  <si>
-    <t>PROGRES PENDATAAN - PROPORSI USAHA</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha (Semua Status Keberadaan Usaha)</t>
-  </si>
-  <si>
-    <t>Persentase Usaha BKU</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha dalam Keluarga</t>
-  </si>
-  <si>
-    <t>Persentase Usaha dalam Keluarga</t>
-  </si>
-  <si>
-    <t>6,58</t>
-  </si>
-  <si>
-    <t>54,8</t>
-  </si>
-  <si>
-    <t>3,15</t>
-  </si>
-  <si>
-    <t>67,75</t>
-  </si>
-  <si>
-    <t>4,62</t>
-  </si>
-  <si>
-    <t>56,42</t>
-  </si>
-  <si>
-    <t>6,55</t>
-  </si>
-  <si>
-    <t>45,17</t>
-  </si>
-  <si>
-    <t>57,75</t>
-  </si>
-  <si>
-    <t>56,22</t>
-  </si>
-  <si>
-    <t>5,78</t>
-  </si>
-  <si>
-    <t>49,89</t>
-  </si>
-  <si>
-    <t>4,67</t>
-  </si>
-  <si>
-    <t>58,53</t>
-  </si>
-  <si>
-    <t>6,65</t>
-  </si>
-  <si>
-    <t>58,88</t>
-  </si>
-  <si>
-    <t>6,19</t>
-  </si>
-  <si>
-    <t>60,5</t>
-  </si>
-  <si>
-    <t>9,2</t>
-  </si>
-  <si>
-    <t>56,77</t>
-  </si>
-  <si>
-    <t>6,46</t>
-  </si>
-  <si>
-    <t>55,69</t>
-  </si>
-  <si>
-    <t>63,14</t>
-  </si>
-  <si>
-    <t>14,93</t>
-  </si>
-  <si>
-    <t>16,35</t>
-  </si>
-  <si>
-    <t>43,76</t>
-  </si>
-  <si>
-    <t>Jumlah Usaha (Semua Status Keberadaan Usaha) Kolom 3</t>
-  </si>
-  <si>
-    <t>Jumlah seluruh usaha BKU dan Usaha Keluarga dari CAPI dan CAWI dengan semua status keberadaan.</t>
-  </si>
-  <si>
-    <t>PROGRES PENDATAAN - JARINGAN USAHA</t>
-  </si>
-  <si>
-    <t>JUMLAH USAHA BERDASARKAN JARINGAN USAHA</t>
-  </si>
-  <si>
-    <t>Tunggal</t>
-  </si>
-  <si>
-    <t>Kantor Pusat</t>
-  </si>
-  <si>
-    <t>Cabang</t>
-  </si>
-  <si>
-    <t>Perwakilan</t>
-  </si>
-  <si>
-    <t>Pabrik</t>
-  </si>
-  <si>
-    <t>Unit Pembantu</t>
-  </si>
-  <si>
-    <t>PROGRES PENDATAAN - PROPORSI PERTANIAN</t>
-  </si>
-  <si>
-    <t>Jumlah Prelist Usaha SE2026</t>
-  </si>
-  <si>
-    <t>Target Berdasarkan Data ST</t>
-  </si>
-  <si>
-    <t>Jumlah UTP Subsektor Prelist</t>
-  </si>
-  <si>
-    <t>USAHA PERTANIAN BKU</t>
-  </si>
-  <si>
-    <t>USAHA PERTANIAN DALAM KELUARGA</t>
-  </si>
-  <si>
-    <t>24,03</t>
-  </si>
-  <si>
-    <t>75,97</t>
-  </si>
-  <si>
-    <t>69,29</t>
-  </si>
-  <si>
-    <t>30,71</t>
-  </si>
-  <si>
-    <t>13,61</t>
-  </si>
-  <si>
-    <t>86,39</t>
-  </si>
-  <si>
-    <t>68,79</t>
-  </si>
-  <si>
-    <t>31,21</t>
-  </si>
-  <si>
-    <t>25,43</t>
-  </si>
-  <si>
-    <t>74,57</t>
-  </si>
-  <si>
-    <t>69,34</t>
-  </si>
-  <si>
-    <t>30,66</t>
-  </si>
-  <si>
-    <t>15,52</t>
-  </si>
-  <si>
-    <t>84,48</t>
-  </si>
-  <si>
-    <t>70,82</t>
-  </si>
-  <si>
-    <t>29,18</t>
-  </si>
-  <si>
-    <t>44,93</t>
-  </si>
-  <si>
-    <t>55,07</t>
-  </si>
-  <si>
-    <t>69,3</t>
-  </si>
-  <si>
-    <t>30,7</t>
-  </si>
-  <si>
-    <t>36,29</t>
-  </si>
-  <si>
-    <t>63,71</t>
-  </si>
-  <si>
-    <t>29,79</t>
-  </si>
-  <si>
-    <t>37,22</t>
-  </si>
-  <si>
-    <t>62,78</t>
-  </si>
-  <si>
-    <t>68,4</t>
-  </si>
-  <si>
-    <t>31,6</t>
-  </si>
-  <si>
-    <t>15,21</t>
-  </si>
-  <si>
-    <t>84,79</t>
-  </si>
-  <si>
-    <t>65,69</t>
-  </si>
-  <si>
-    <t>34,31</t>
-  </si>
-  <si>
-    <t>7,62</t>
-  </si>
-  <si>
-    <t>92,38</t>
-  </si>
-  <si>
-    <t>65,26</t>
-  </si>
-  <si>
-    <t>34,74</t>
-  </si>
-  <si>
-    <t>76,14</t>
-  </si>
-  <si>
-    <t>73,96</t>
-  </si>
-  <si>
-    <t>26,04</t>
-  </si>
-  <si>
-    <t>8,42</t>
-  </si>
-  <si>
-    <t>91,58</t>
-  </si>
-  <si>
-    <t>70,62</t>
-  </si>
-  <si>
-    <t>29,38</t>
-  </si>
-  <si>
-    <t>6,88</t>
-  </si>
-  <si>
-    <t>93,12</t>
-  </si>
-  <si>
-    <t>66,53</t>
-  </si>
-  <si>
-    <t>33,47</t>
-  </si>
-  <si>
     <t>84,09</t>
   </si>
   <si>
-    <t>67,22</t>
-  </si>
-  <si>
-    <t>32,78</t>
-  </si>
-  <si>
-    <t>13,16</t>
-  </si>
-  <si>
-    <t>86,84</t>
-  </si>
-  <si>
-    <t>70,35</t>
-  </si>
-  <si>
-    <t>29,65</t>
-  </si>
-  <si>
-    <t>33,09</t>
-  </si>
-  <si>
-    <t>66,91</t>
-  </si>
-  <si>
-    <t>73,05</t>
-  </si>
-  <si>
-    <t>26,95</t>
-  </si>
-  <si>
-    <t>68,29</t>
+    <t>67,24</t>
+  </si>
+  <si>
+    <t>32,76</t>
+  </si>
+  <si>
+    <t>12,99</t>
+  </si>
+  <si>
+    <t>87,01</t>
+  </si>
+  <si>
+    <t>70,33</t>
+  </si>
+  <si>
+    <t>29,67</t>
+  </si>
+  <si>
+    <t>32,86</t>
+  </si>
+  <si>
+    <t>67,14</t>
+  </si>
+  <si>
+    <t>73,11</t>
+  </si>
+  <si>
+    <t>26,89</t>
   </si>
   <si>
     <t>31,71</t>
   </si>
   <si>
-    <t>72,32</t>
-  </si>
-  <si>
-    <t>27,68</t>
+    <t>72,31</t>
+  </si>
+  <si>
+    <t>27,69</t>
   </si>
   <si>
     <t>Persentase Usaha Pertanian BKU Ditemukan</t>
@@ -2710,37 +2710,37 @@
         <v>3491486</v>
       </c>
       <c r="D7" s="6">
-        <v>849259</v>
+        <v>851787</v>
       </c>
       <c r="E7" s="6">
-        <v>4020487</v>
+        <v>4038613</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>34</v>
       </c>
       <c r="G7" s="6">
-        <v>2450989</v>
+        <v>2464738</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>35</v>
       </c>
       <c r="I7" s="6">
-        <v>138028</v>
+        <v>131892</v>
       </c>
       <c r="J7" s="7" t="s">
         <v>36</v>
       </c>
       <c r="K7" s="6">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L7" s="6">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="M7" s="6">
-        <v>38819</v>
+        <v>37048</v>
       </c>
       <c r="N7" s="6">
-        <v>156207</v>
+        <v>149349</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -2754,22 +2754,22 @@
         <v>97072</v>
       </c>
       <c r="D8" s="9">
-        <v>25128</v>
+        <v>25137</v>
       </c>
       <c r="E8" s="9">
-        <v>121980</v>
+        <v>121799</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>39</v>
       </c>
       <c r="G8" s="9">
-        <v>82931</v>
+        <v>82736</v>
       </c>
       <c r="H8" s="10" t="s">
         <v>40</v>
       </c>
       <c r="I8" s="9">
-        <v>1788</v>
+        <v>1997</v>
       </c>
       <c r="J8" s="10" t="s">
         <v>41</v>
@@ -2784,7 +2784,7 @@
         <v>8</v>
       </c>
       <c r="N8" s="9">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -2798,22 +2798,22 @@
         <v>230431</v>
       </c>
       <c r="D9" s="9">
-        <v>59822</v>
+        <v>59975</v>
       </c>
       <c r="E9" s="9">
-        <v>263804</v>
+        <v>264958</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>44</v>
       </c>
       <c r="G9" s="9">
-        <v>167042</v>
+        <v>167847</v>
       </c>
       <c r="H9" s="10" t="s">
         <v>45</v>
       </c>
       <c r="I9" s="9">
-        <v>13651</v>
+        <v>13397</v>
       </c>
       <c r="J9" s="10" t="s">
         <v>46</v>
@@ -2825,10 +2825,10 @@
         <v>4</v>
       </c>
       <c r="M9" s="9">
-        <v>2978</v>
+        <v>2793</v>
       </c>
       <c r="N9" s="9">
-        <v>9828</v>
+        <v>9295</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -2842,22 +2842,22 @@
         <v>436273</v>
       </c>
       <c r="D10" s="9">
-        <v>128081</v>
+        <v>128685</v>
       </c>
       <c r="E10" s="9">
-        <v>498918</v>
+        <v>502692</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>49</v>
       </c>
       <c r="G10" s="9">
-        <v>287387</v>
+        <v>290162</v>
       </c>
       <c r="H10" s="10" t="s">
         <v>50</v>
       </c>
       <c r="I10" s="9">
-        <v>23125</v>
+        <v>21775</v>
       </c>
       <c r="J10" s="10" t="s">
         <v>51</v>
@@ -2866,13 +2866,13 @@
         <v>1</v>
       </c>
       <c r="L10" s="9">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="M10" s="9">
-        <v>6169</v>
+        <v>5955</v>
       </c>
       <c r="N10" s="9">
-        <v>35211</v>
+        <v>33739</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -2886,22 +2886,22 @@
         <v>489943</v>
       </c>
       <c r="D11" s="9">
-        <v>96839</v>
+        <v>97091</v>
       </c>
       <c r="E11" s="9">
-        <v>539006</v>
+        <v>541619</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>54</v>
       </c>
       <c r="G11" s="9">
-        <v>334268</v>
+        <v>336459</v>
       </c>
       <c r="H11" s="10" t="s">
         <v>55</v>
       </c>
       <c r="I11" s="9">
-        <v>18212</v>
+        <v>17167</v>
       </c>
       <c r="J11" s="10" t="s">
         <v>56</v>
@@ -2910,13 +2910,13 @@
         <v>1</v>
       </c>
       <c r="L11" s="9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M11" s="9">
-        <v>6557</v>
+        <v>6250</v>
       </c>
       <c r="N11" s="9">
-        <v>22517</v>
+        <v>21665</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -2930,22 +2930,22 @@
         <v>580719</v>
       </c>
       <c r="D12" s="9">
-        <v>118513</v>
+        <v>118853</v>
       </c>
       <c r="E12" s="9">
-        <v>647744</v>
+        <v>650957</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>59</v>
       </c>
       <c r="G12" s="9">
-        <v>402225</v>
+        <v>404699</v>
       </c>
       <c r="H12" s="10" t="s">
         <v>60</v>
       </c>
       <c r="I12" s="9">
-        <v>22789</v>
+        <v>21557</v>
       </c>
       <c r="J12" s="10" t="s">
         <v>61</v>
@@ -2954,13 +2954,13 @@
         <v>3</v>
       </c>
       <c r="L12" s="9">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="M12" s="9">
-        <v>4805</v>
+        <v>4452</v>
       </c>
       <c r="N12" s="9">
-        <v>23484</v>
+        <v>22290</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -2974,22 +2974,22 @@
         <v>263315</v>
       </c>
       <c r="D13" s="9">
-        <v>55359</v>
+        <v>55537</v>
       </c>
       <c r="E13" s="9">
-        <v>309871</v>
+        <v>311020</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>64</v>
       </c>
       <c r="G13" s="9">
-        <v>178961</v>
+        <v>179816</v>
       </c>
       <c r="H13" s="10" t="s">
         <v>65</v>
       </c>
       <c r="I13" s="9">
-        <v>3840</v>
+        <v>3428</v>
       </c>
       <c r="J13" s="10" t="s">
         <v>66</v>
@@ -3001,10 +3001,10 @@
         <v>6</v>
       </c>
       <c r="M13" s="9">
-        <v>807</v>
+        <v>695</v>
       </c>
       <c r="N13" s="9">
-        <v>3919</v>
+        <v>3504</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -3018,22 +3018,22 @@
         <v>187422</v>
       </c>
       <c r="D14" s="9">
-        <v>49994</v>
+        <v>50233</v>
       </c>
       <c r="E14" s="9">
-        <v>220902</v>
+        <v>221992</v>
       </c>
       <c r="F14" s="10" t="s">
         <v>69</v>
       </c>
       <c r="G14" s="9">
-        <v>134534</v>
+        <v>135463</v>
       </c>
       <c r="H14" s="10" t="s">
         <v>70</v>
       </c>
       <c r="I14" s="9">
-        <v>7210</v>
+        <v>6905</v>
       </c>
       <c r="J14" s="10" t="s">
         <v>71</v>
@@ -3042,13 +3042,13 @@
         <v>2</v>
       </c>
       <c r="L14" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M14" s="9">
-        <v>1563</v>
+        <v>1441</v>
       </c>
       <c r="N14" s="9">
-        <v>7650</v>
+        <v>7278</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -3062,22 +3062,22 @@
         <v>154763</v>
       </c>
       <c r="D15" s="9">
-        <v>42024</v>
+        <v>42156</v>
       </c>
       <c r="E15" s="9">
-        <v>183645</v>
+        <v>184528</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>74</v>
       </c>
       <c r="G15" s="9">
-        <v>111233</v>
+        <v>111946</v>
       </c>
       <c r="H15" s="10" t="s">
         <v>75</v>
       </c>
       <c r="I15" s="9">
-        <v>7701</v>
+        <v>7408</v>
       </c>
       <c r="J15" s="10" t="s">
         <v>76</v>
@@ -3089,10 +3089,10 @@
         <v>2</v>
       </c>
       <c r="M15" s="9">
-        <v>1006</v>
+        <v>963</v>
       </c>
       <c r="N15" s="9">
-        <v>7579</v>
+        <v>7205</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -3106,22 +3106,22 @@
         <v>170543</v>
       </c>
       <c r="D16" s="9">
-        <v>47070</v>
+        <v>47118</v>
       </c>
       <c r="E16" s="9">
-        <v>214339</v>
+        <v>215003</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>79</v>
       </c>
       <c r="G16" s="9">
-        <v>145639</v>
+        <v>146166</v>
       </c>
       <c r="H16" s="10" t="s">
         <v>80</v>
       </c>
       <c r="I16" s="9">
-        <v>4205</v>
+        <v>3830</v>
       </c>
       <c r="J16" s="10" t="s">
         <v>81</v>
@@ -3133,10 +3133,10 @@
         <v>1</v>
       </c>
       <c r="M16" s="9">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="N16" s="9">
-        <v>1365</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -3150,22 +3150,22 @@
         <v>157837</v>
       </c>
       <c r="D17" s="9">
-        <v>35713</v>
+        <v>35768</v>
       </c>
       <c r="E17" s="9">
-        <v>183128</v>
+        <v>184146</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>84</v>
       </c>
       <c r="G17" s="9">
-        <v>130131</v>
+        <v>130976</v>
       </c>
       <c r="H17" s="10" t="s">
         <v>85</v>
       </c>
       <c r="I17" s="9">
-        <v>8147</v>
+        <v>7627</v>
       </c>
       <c r="J17" s="10" t="s">
         <v>86</v>
@@ -3177,10 +3177,10 @@
         <v>0</v>
       </c>
       <c r="M17" s="9">
-        <v>896</v>
+        <v>855</v>
       </c>
       <c r="N17" s="9">
-        <v>3947</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -3194,22 +3194,22 @@
         <v>86207</v>
       </c>
       <c r="D18" s="9">
-        <v>27001</v>
+        <v>27023</v>
       </c>
       <c r="E18" s="9">
-        <v>114654</v>
+        <v>114678</v>
       </c>
       <c r="F18" s="10" t="s">
         <v>89</v>
       </c>
       <c r="G18" s="9">
-        <v>75205</v>
+        <v>75240</v>
       </c>
       <c r="H18" s="10" t="s">
         <v>90</v>
       </c>
       <c r="I18" s="9">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="J18" s="10" t="s">
         <v>91</v>
@@ -3238,22 +3238,22 @@
         <v>109078</v>
       </c>
       <c r="D19" s="9">
-        <v>31169</v>
+        <v>31188</v>
       </c>
       <c r="E19" s="9">
-        <v>141789</v>
+        <v>141901</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>94</v>
       </c>
       <c r="G19" s="9">
-        <v>96052</v>
+        <v>96176</v>
       </c>
       <c r="H19" s="10" t="s">
         <v>95</v>
       </c>
       <c r="I19" s="9">
-        <v>199</v>
+        <v>135</v>
       </c>
       <c r="J19" s="10" t="s">
         <v>96</v>
@@ -3265,10 +3265,10 @@
         <v>0</v>
       </c>
       <c r="M19" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" s="9">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -3282,22 +3282,22 @@
         <v>47152</v>
       </c>
       <c r="D20" s="9">
-        <v>14524</v>
+        <v>14539</v>
       </c>
       <c r="E20" s="9">
-        <v>61886</v>
+        <v>61933</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>99</v>
       </c>
       <c r="G20" s="9">
-        <v>44849</v>
+        <v>44876</v>
       </c>
       <c r="H20" s="10" t="s">
         <v>100</v>
       </c>
       <c r="I20" s="9">
-        <v>322</v>
+        <v>295</v>
       </c>
       <c r="J20" s="10" t="s">
         <v>101</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="M20" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N20" s="9">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -3326,37 +3326,37 @@
         <v>410238</v>
       </c>
       <c r="D21" s="9">
-        <v>102121</v>
+        <v>102529</v>
       </c>
       <c r="E21" s="9">
-        <v>440575</v>
+        <v>442817</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>104</v>
       </c>
       <c r="G21" s="9">
-        <v>212512</v>
+        <v>213885</v>
       </c>
       <c r="H21" s="10" t="s">
         <v>105</v>
       </c>
       <c r="I21" s="9">
-        <v>22484</v>
+        <v>22151</v>
       </c>
       <c r="J21" s="10" t="s">
         <v>106</v>
       </c>
       <c r="K21" s="9">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L21" s="9">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="M21" s="9">
-        <v>12797</v>
+        <v>12440</v>
       </c>
       <c r="N21" s="9">
-        <v>36599</v>
+        <v>35610</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -3370,22 +3370,22 @@
         <v>70493</v>
       </c>
       <c r="D22" s="9">
-        <v>15901</v>
+        <v>15955</v>
       </c>
       <c r="E22" s="9">
-        <v>78246</v>
+        <v>78570</v>
       </c>
       <c r="F22" s="10" t="s">
         <v>109</v>
       </c>
       <c r="G22" s="9">
-        <v>48020</v>
+        <v>48291</v>
       </c>
       <c r="H22" s="10" t="s">
         <v>110</v>
       </c>
       <c r="I22" s="9">
-        <v>4300</v>
+        <v>4170</v>
       </c>
       <c r="J22" s="10" t="s">
         <v>111</v>
@@ -3397,10 +3397,10 @@
         <v>2</v>
       </c>
       <c r="M22" s="9">
-        <v>1070</v>
+        <v>1041</v>
       </c>
       <c r="N22" s="9">
-        <v>3925</v>
+        <v>3821</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -3414,37 +3414,37 @@
         <v>3491486</v>
       </c>
       <c r="D23" s="12">
-        <v>849259</v>
+        <v>851787</v>
       </c>
       <c r="E23" s="12">
-        <v>4020487</v>
+        <v>4038613</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>34</v>
       </c>
       <c r="G23" s="12">
-        <v>2450989</v>
+        <v>2464738</v>
       </c>
       <c r="H23" s="13" t="s">
         <v>35</v>
       </c>
       <c r="I23" s="12">
-        <v>138028</v>
+        <v>131892</v>
       </c>
       <c r="J23" s="13" t="s">
         <v>36</v>
       </c>
       <c r="K23" s="12">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L23" s="12">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="M23" s="12">
-        <v>38819</v>
+        <v>37048</v>
       </c>
       <c r="N23" s="12">
-        <v>156207</v>
+        <v>149349</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
@@ -4082,7 +4082,7 @@
         <v>760553</v>
       </c>
       <c r="D8" s="6">
-        <v>1164</v>
+        <v>1168</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>191</v>
@@ -4100,7 +4100,7 @@
         <v>192</v>
       </c>
       <c r="J8" s="6">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="K8" s="7" t="s">
         <v>193</v>
@@ -4112,7 +4112,7 @@
         <v>194</v>
       </c>
       <c r="N8" s="6">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="O8" s="7" t="s">
         <v>194</v>
@@ -4130,37 +4130,37 @@
         <v>192</v>
       </c>
       <c r="T8" s="6">
-        <v>1164</v>
+        <v>1168</v>
       </c>
       <c r="U8" s="7" t="s">
         <v>191</v>
       </c>
       <c r="V8" s="6">
-        <v>92551</v>
+        <v>93348</v>
       </c>
       <c r="W8" s="7" t="s">
         <v>195</v>
       </c>
       <c r="X8" s="6">
-        <v>139024</v>
+        <v>140034</v>
       </c>
       <c r="Y8" s="7" t="s">
         <v>196</v>
       </c>
       <c r="Z8" s="6">
-        <v>62878</v>
+        <v>63216</v>
       </c>
       <c r="AA8" s="7" t="s">
         <v>197</v>
       </c>
       <c r="AB8" s="6">
-        <v>334526</v>
+        <v>335068</v>
       </c>
       <c r="AC8" s="7" t="s">
         <v>198</v>
       </c>
       <c r="AD8" s="6">
-        <v>125697</v>
+        <v>127315</v>
       </c>
       <c r="AE8" s="7" t="s">
         <v>199</v>
@@ -4172,25 +4172,25 @@
         <v>192</v>
       </c>
       <c r="AH8" s="6">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AI8" s="7" t="s">
         <v>194</v>
       </c>
       <c r="AJ8" s="6">
-        <v>51245</v>
+        <v>51535</v>
       </c>
       <c r="AK8" s="7" t="s">
         <v>200</v>
       </c>
       <c r="AL8" s="6">
-        <v>218248</v>
+        <v>220663</v>
       </c>
       <c r="AM8" s="7" t="s">
         <v>201</v>
       </c>
       <c r="AN8" s="6">
-        <v>219412</v>
+        <v>221831</v>
       </c>
       <c r="AO8" s="7" t="s">
         <v>202</v>
@@ -4261,7 +4261,7 @@
         <v>203</v>
       </c>
       <c r="V9" s="9">
-        <v>2059</v>
+        <v>2053</v>
       </c>
       <c r="W9" s="10" t="s">
         <v>205</v>
@@ -4279,13 +4279,13 @@
         <v>207</v>
       </c>
       <c r="AB9" s="9">
-        <v>4959</v>
+        <v>4960</v>
       </c>
       <c r="AC9" s="10" t="s">
         <v>208</v>
       </c>
       <c r="AD9" s="9">
-        <v>2166</v>
+        <v>2157</v>
       </c>
       <c r="AE9" s="10" t="s">
         <v>209</v>
@@ -4303,19 +4303,19 @@
         <v>192</v>
       </c>
       <c r="AJ9" s="9">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AK9" s="10" t="s">
         <v>210</v>
       </c>
       <c r="AL9" s="9">
-        <v>4225</v>
+        <v>4210</v>
       </c>
       <c r="AM9" s="10" t="s">
         <v>211</v>
       </c>
       <c r="AN9" s="9">
-        <v>4249</v>
+        <v>4234</v>
       </c>
       <c r="AO9" s="10" t="s">
         <v>212</v>
@@ -4386,31 +4386,31 @@
         <v>213</v>
       </c>
       <c r="V10" s="9">
-        <v>5316</v>
+        <v>5364</v>
       </c>
       <c r="W10" s="10" t="s">
         <v>215</v>
       </c>
       <c r="X10" s="9">
-        <v>13163</v>
+        <v>13243</v>
       </c>
       <c r="Y10" s="10" t="s">
         <v>216</v>
       </c>
       <c r="Z10" s="9">
-        <v>9235</v>
+        <v>9276</v>
       </c>
       <c r="AA10" s="10" t="s">
         <v>217</v>
       </c>
       <c r="AB10" s="9">
-        <v>15871</v>
+        <v>15946</v>
       </c>
       <c r="AC10" s="10" t="s">
         <v>218</v>
       </c>
       <c r="AD10" s="9">
-        <v>6153</v>
+        <v>6224</v>
       </c>
       <c r="AE10" s="10" t="s">
         <v>219</v>
@@ -4422,25 +4422,25 @@
         <v>192</v>
       </c>
       <c r="AH10" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI10" s="10" t="s">
         <v>194</v>
       </c>
       <c r="AJ10" s="9">
-        <v>6229</v>
+        <v>6258</v>
       </c>
       <c r="AK10" s="10" t="s">
         <v>220</v>
       </c>
       <c r="AL10" s="9">
-        <v>11469</v>
+        <v>11588</v>
       </c>
       <c r="AM10" s="10" t="s">
         <v>221</v>
       </c>
       <c r="AN10" s="9">
-        <v>11528</v>
+        <v>11647</v>
       </c>
       <c r="AO10" s="10" t="s">
         <v>222</v>
@@ -4457,10 +4457,10 @@
         <v>93539</v>
       </c>
       <c r="D11" s="9">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>223</v>
+        <v>191</v>
       </c>
       <c r="F11" s="9">
         <v>0</v>
@@ -4475,16 +4475,16 @@
         <v>192</v>
       </c>
       <c r="J11" s="9">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K11" s="10" t="s">
         <v>193</v>
       </c>
       <c r="L11" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N11" s="9">
         <v>1</v>
@@ -4505,40 +4505,40 @@
         <v>192</v>
       </c>
       <c r="T11" s="9">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="U11" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="V11" s="9">
+        <v>6246</v>
+      </c>
+      <c r="W11" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="V11" s="9">
-        <v>6147</v>
-      </c>
-      <c r="W11" s="10" t="s">
+      <c r="X11" s="9">
+        <v>11714</v>
+      </c>
+      <c r="Y11" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="X11" s="9">
-        <v>11612</v>
-      </c>
-      <c r="Y11" s="10" t="s">
+      <c r="Z11" s="9">
+        <v>4173</v>
+      </c>
+      <c r="AA11" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="Z11" s="9">
-        <v>4152</v>
-      </c>
-      <c r="AA11" s="10" t="s">
+      <c r="AB11" s="9">
+        <v>59514</v>
+      </c>
+      <c r="AC11" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="AB11" s="9">
-        <v>59426</v>
-      </c>
-      <c r="AC11" s="10" t="s">
+      <c r="AD11" s="9">
+        <v>15181</v>
+      </c>
+      <c r="AE11" s="10" t="s">
         <v>227</v>
-      </c>
-      <c r="AD11" s="9">
-        <v>14878</v>
-      </c>
-      <c r="AE11" s="10" t="s">
-        <v>228</v>
       </c>
       <c r="AF11" s="9">
         <v>1</v>
@@ -4547,28 +4547,28 @@
         <v>192</v>
       </c>
       <c r="AH11" s="9">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AI11" s="10" t="s">
         <v>193</v>
       </c>
       <c r="AJ11" s="9">
-        <v>3036</v>
+        <v>3058</v>
       </c>
       <c r="AK11" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="AL11" s="9">
+        <v>21427</v>
+      </c>
+      <c r="AM11" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="AL11" s="9">
-        <v>21025</v>
-      </c>
-      <c r="AM11" s="10" t="s">
+      <c r="AN11" s="9">
+        <v>21563</v>
+      </c>
+      <c r="AO11" s="10" t="s">
         <v>230</v>
-      </c>
-      <c r="AN11" s="9">
-        <v>21159</v>
-      </c>
-      <c r="AO11" s="10" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -4636,34 +4636,34 @@
         <v>91</v>
       </c>
       <c r="V12" s="9">
-        <v>15315</v>
+        <v>15475</v>
       </c>
       <c r="W12" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="X12" s="9">
+        <v>29376</v>
+      </c>
+      <c r="Y12" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="X12" s="9">
-        <v>29139</v>
-      </c>
-      <c r="Y12" s="10" t="s">
+      <c r="Z12" s="9">
+        <v>10185</v>
+      </c>
+      <c r="AA12" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="Z12" s="9">
-        <v>10147</v>
-      </c>
-      <c r="AA12" s="10" t="s">
+      <c r="AB12" s="9">
+        <v>43284</v>
+      </c>
+      <c r="AC12" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="AB12" s="9">
-        <v>43159</v>
-      </c>
-      <c r="AC12" s="10" t="s">
+      <c r="AD12" s="9">
+        <v>17638</v>
+      </c>
+      <c r="AE12" s="10" t="s">
         <v>235</v>
-      </c>
-      <c r="AD12" s="9">
-        <v>17261</v>
-      </c>
-      <c r="AE12" s="10" t="s">
-        <v>236</v>
       </c>
       <c r="AF12" s="9">
         <v>1</v>
@@ -4678,22 +4678,22 @@
         <v>192</v>
       </c>
       <c r="AJ12" s="9">
-        <v>15019</v>
+        <v>15122</v>
       </c>
       <c r="AK12" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="AL12" s="9">
+        <v>33113</v>
+      </c>
+      <c r="AM12" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="AL12" s="9">
-        <v>32576</v>
-      </c>
-      <c r="AM12" s="10" t="s">
+      <c r="AN12" s="9">
+        <v>33191</v>
+      </c>
+      <c r="AO12" s="10" t="s">
         <v>238</v>
-      </c>
-      <c r="AN12" s="9">
-        <v>32654</v>
-      </c>
-      <c r="AO12" s="10" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -4725,19 +4725,19 @@
         <v>192</v>
       </c>
       <c r="J13" s="9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K13" s="10" t="s">
         <v>194</v>
       </c>
       <c r="L13" s="9">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M13" s="10" t="s">
         <v>194</v>
       </c>
       <c r="N13" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O13" s="10" t="s">
         <v>192</v>
@@ -4761,34 +4761,34 @@
         <v>213</v>
       </c>
       <c r="V13" s="9">
-        <v>14924</v>
+        <v>15076</v>
       </c>
       <c r="W13" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="X13" s="9">
+        <v>26994</v>
+      </c>
+      <c r="Y13" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="X13" s="9">
-        <v>26727</v>
-      </c>
-      <c r="Y13" s="10" t="s">
+      <c r="Z13" s="9">
+        <v>13060</v>
+      </c>
+      <c r="AA13" s="10" t="s">
         <v>241</v>
-      </c>
-      <c r="Z13" s="9">
-        <v>12987</v>
-      </c>
-      <c r="AA13" s="10" t="s">
-        <v>242</v>
       </c>
       <c r="AB13" s="9">
         <v>58203</v>
       </c>
       <c r="AC13" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="AD13" s="9">
+        <v>23968</v>
+      </c>
+      <c r="AE13" s="10" t="s">
         <v>243</v>
-      </c>
-      <c r="AD13" s="9">
-        <v>23664</v>
-      </c>
-      <c r="AE13" s="10" t="s">
-        <v>244</v>
       </c>
       <c r="AF13" s="9">
         <v>1</v>
@@ -4803,22 +4803,22 @@
         <v>194</v>
       </c>
       <c r="AJ13" s="9">
-        <v>8455</v>
+        <v>8489</v>
       </c>
       <c r="AK13" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="AL13" s="9">
+        <v>39044</v>
+      </c>
+      <c r="AM13" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="AL13" s="9">
-        <v>38588</v>
-      </c>
-      <c r="AM13" s="10" t="s">
+      <c r="AN13" s="9">
+        <v>39169</v>
+      </c>
+      <c r="AO13" s="10" t="s">
         <v>246</v>
-      </c>
-      <c r="AN13" s="9">
-        <v>38713</v>
-      </c>
-      <c r="AO13" s="10" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -4835,7 +4835,7 @@
         <v>52</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F14" s="9">
         <v>0</v>
@@ -4883,37 +4883,37 @@
         <v>52</v>
       </c>
       <c r="U14" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="V14" s="9">
+        <v>5040</v>
+      </c>
+      <c r="W14" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="V14" s="9">
-        <v>5004</v>
-      </c>
-      <c r="W14" s="10" t="s">
+      <c r="X14" s="9">
+        <v>10285</v>
+      </c>
+      <c r="Y14" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="X14" s="9">
-        <v>10236</v>
-      </c>
-      <c r="Y14" s="10" t="s">
+      <c r="Z14" s="9">
+        <v>3541</v>
+      </c>
+      <c r="AA14" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="Z14" s="9">
-        <v>3538</v>
-      </c>
-      <c r="AA14" s="10" t="s">
+      <c r="AB14" s="9">
+        <v>37745</v>
+      </c>
+      <c r="AC14" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="AB14" s="9">
-        <v>37713</v>
-      </c>
-      <c r="AC14" s="10" t="s">
+      <c r="AD14" s="9">
+        <v>8144</v>
+      </c>
+      <c r="AE14" s="10" t="s">
         <v>252</v>
-      </c>
-      <c r="AD14" s="9">
-        <v>8080</v>
-      </c>
-      <c r="AE14" s="10" t="s">
-        <v>253</v>
       </c>
       <c r="AF14" s="9">
         <v>0</v>
@@ -4928,22 +4928,22 @@
         <v>194</v>
       </c>
       <c r="AJ14" s="9">
-        <v>5064</v>
+        <v>5087</v>
       </c>
       <c r="AK14" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="AL14" s="9">
+        <v>13184</v>
+      </c>
+      <c r="AM14" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="AL14" s="9">
-        <v>13084</v>
-      </c>
-      <c r="AM14" s="10" t="s">
+      <c r="AN14" s="9">
+        <v>13236</v>
+      </c>
+      <c r="AO14" s="10" t="s">
         <v>255</v>
-      </c>
-      <c r="AN14" s="9">
-        <v>13136</v>
-      </c>
-      <c r="AO14" s="10" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -4960,7 +4960,7 @@
         <v>38</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F15" s="9">
         <v>0</v>
@@ -5008,37 +5008,37 @@
         <v>38</v>
       </c>
       <c r="U15" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="V15" s="9">
+        <v>2698</v>
+      </c>
+      <c r="W15" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="V15" s="9">
-        <v>2652</v>
-      </c>
-      <c r="W15" s="10" t="s">
+      <c r="X15" s="9">
+        <v>9623</v>
+      </c>
+      <c r="Y15" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="X15" s="9">
-        <v>9565</v>
-      </c>
-      <c r="Y15" s="10" t="s">
+      <c r="Z15" s="9">
+        <v>2747</v>
+      </c>
+      <c r="AA15" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="Z15" s="9">
-        <v>2732</v>
-      </c>
-      <c r="AA15" s="10" t="s">
+      <c r="AB15" s="9">
+        <v>18711</v>
+      </c>
+      <c r="AC15" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="AB15" s="9">
-        <v>18693</v>
-      </c>
-      <c r="AC15" s="10" t="s">
+      <c r="AD15" s="9">
+        <v>6674</v>
+      </c>
+      <c r="AE15" s="10" t="s">
         <v>261</v>
-      </c>
-      <c r="AD15" s="9">
-        <v>6540</v>
-      </c>
-      <c r="AE15" s="10" t="s">
-        <v>262</v>
       </c>
       <c r="AF15" s="9">
         <v>0</v>
@@ -5053,22 +5053,22 @@
         <v>192</v>
       </c>
       <c r="AJ15" s="9">
-        <v>4250</v>
+        <v>4280</v>
       </c>
       <c r="AK15" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="AL15" s="9">
+        <v>9372</v>
+      </c>
+      <c r="AM15" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="AL15" s="9">
-        <v>9192</v>
-      </c>
-      <c r="AM15" s="10" t="s">
+      <c r="AN15" s="9">
+        <v>9410</v>
+      </c>
+      <c r="AO15" s="10" t="s">
         <v>264</v>
-      </c>
-      <c r="AN15" s="9">
-        <v>9230</v>
-      </c>
-      <c r="AO15" s="10" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -5085,7 +5085,7 @@
         <v>48</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F16" s="9">
         <v>1</v>
@@ -5133,37 +5133,37 @@
         <v>48</v>
       </c>
       <c r="U16" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="V16" s="9">
+        <v>4330</v>
+      </c>
+      <c r="W16" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="V16" s="9">
-        <v>4295</v>
-      </c>
-      <c r="W16" s="10" t="s">
+      <c r="X16" s="9">
+        <v>2563</v>
+      </c>
+      <c r="Y16" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="X16" s="9">
-        <v>2554</v>
-      </c>
-      <c r="Y16" s="10" t="s">
+      <c r="Z16" s="9">
+        <v>966</v>
+      </c>
+      <c r="AA16" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="Z16" s="9">
-        <v>963</v>
-      </c>
-      <c r="AA16" s="10" t="s">
+      <c r="AB16" s="9">
+        <v>8218</v>
+      </c>
+      <c r="AC16" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="AB16" s="9">
-        <v>8213</v>
-      </c>
-      <c r="AC16" s="10" t="s">
+      <c r="AD16" s="9">
+        <v>5312</v>
+      </c>
+      <c r="AE16" s="10" t="s">
         <v>270</v>
-      </c>
-      <c r="AD16" s="9">
-        <v>5267</v>
-      </c>
-      <c r="AE16" s="10" t="s">
-        <v>271</v>
       </c>
       <c r="AF16" s="9">
         <v>0</v>
@@ -5181,19 +5181,19 @@
         <v>197</v>
       </c>
       <c r="AK16" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="AL16" s="9">
+        <v>9642</v>
+      </c>
+      <c r="AM16" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="AL16" s="9">
-        <v>9562</v>
-      </c>
-      <c r="AM16" s="10" t="s">
+      <c r="AN16" s="9">
+        <v>9690</v>
+      </c>
+      <c r="AO16" s="10" t="s">
         <v>273</v>
-      </c>
-      <c r="AN16" s="9">
-        <v>9610</v>
-      </c>
-      <c r="AO16" s="10" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -5210,7 +5210,7 @@
         <v>48</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F17" s="9">
         <v>0</v>
@@ -5258,37 +5258,37 @@
         <v>48</v>
       </c>
       <c r="U17" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="V17" s="9">
+        <v>5896</v>
+      </c>
+      <c r="W17" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="V17" s="9">
-        <v>5868</v>
-      </c>
-      <c r="W17" s="10" t="s">
+      <c r="X17" s="9">
+        <v>2767</v>
+      </c>
+      <c r="Y17" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="X17" s="9">
-        <v>2760</v>
-      </c>
-      <c r="Y17" s="10" t="s">
+      <c r="Z17" s="9">
+        <v>1126</v>
+      </c>
+      <c r="AA17" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="Z17" s="9">
-        <v>1116</v>
-      </c>
-      <c r="AA17" s="10" t="s">
+      <c r="AB17" s="9">
+        <v>6507</v>
+      </c>
+      <c r="AC17" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="AB17" s="9">
-        <v>6523</v>
-      </c>
-      <c r="AC17" s="10" t="s">
+      <c r="AD17" s="9">
+        <v>6377</v>
+      </c>
+      <c r="AE17" s="10" t="s">
         <v>279</v>
-      </c>
-      <c r="AD17" s="9">
-        <v>6320</v>
-      </c>
-      <c r="AE17" s="10" t="s">
-        <v>280</v>
       </c>
       <c r="AF17" s="9">
         <v>0</v>
@@ -5303,22 +5303,22 @@
         <v>194</v>
       </c>
       <c r="AJ17" s="9">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AK17" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="AL17" s="9">
+        <v>12273</v>
+      </c>
+      <c r="AM17" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="AL17" s="9">
-        <v>12188</v>
-      </c>
-      <c r="AM17" s="10" t="s">
+      <c r="AN17" s="9">
+        <v>12321</v>
+      </c>
+      <c r="AO17" s="10" t="s">
         <v>282</v>
-      </c>
-      <c r="AN17" s="9">
-        <v>12236</v>
-      </c>
-      <c r="AO17" s="10" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -5335,7 +5335,7 @@
         <v>31</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>223</v>
+        <v>283</v>
       </c>
       <c r="F18" s="9">
         <v>0</v>
@@ -5383,37 +5383,37 @@
         <v>31</v>
       </c>
       <c r="U18" s="10" t="s">
-        <v>223</v>
+        <v>283</v>
       </c>
       <c r="V18" s="9">
-        <v>8301</v>
+        <v>8369</v>
       </c>
       <c r="W18" s="10" t="s">
         <v>284</v>
       </c>
       <c r="X18" s="9">
-        <v>3072</v>
+        <v>3085</v>
       </c>
       <c r="Y18" s="10" t="s">
         <v>285</v>
       </c>
       <c r="Z18" s="9">
-        <v>807</v>
+        <v>819</v>
       </c>
       <c r="AA18" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB18" s="9">
+        <v>6634</v>
+      </c>
+      <c r="AC18" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="AB18" s="9">
-        <v>6599</v>
-      </c>
-      <c r="AC18" s="10" t="s">
+      <c r="AD18" s="9">
+        <v>6462</v>
+      </c>
+      <c r="AE18" s="10" t="s">
         <v>287</v>
-      </c>
-      <c r="AD18" s="9">
-        <v>6404</v>
-      </c>
-      <c r="AE18" s="10" t="s">
-        <v>288</v>
       </c>
       <c r="AF18" s="9">
         <v>0</v>
@@ -5428,19 +5428,19 @@
         <v>192</v>
       </c>
       <c r="AJ18" s="9">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AK18" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="AL18" s="9">
+        <v>14831</v>
+      </c>
+      <c r="AM18" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="AL18" s="9">
-        <v>14705</v>
-      </c>
-      <c r="AM18" s="10" t="s">
-        <v>283</v>
-      </c>
       <c r="AN18" s="9">
-        <v>14736</v>
+        <v>14862</v>
       </c>
       <c r="AO18" s="10" t="s">
         <v>290</v>
@@ -5511,7 +5511,7 @@
         <v>291</v>
       </c>
       <c r="V19" s="9">
-        <v>3134</v>
+        <v>3140</v>
       </c>
       <c r="W19" s="10" t="s">
         <v>292</v>
@@ -5523,7 +5523,7 @@
         <v>293</v>
       </c>
       <c r="Z19" s="9">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="AA19" s="10" t="s">
         <v>294</v>
@@ -5535,7 +5535,7 @@
         <v>295</v>
       </c>
       <c r="AD19" s="9">
-        <v>3878</v>
+        <v>3882</v>
       </c>
       <c r="AE19" s="10" t="s">
         <v>296</v>
@@ -5553,19 +5553,19 @@
         <v>194</v>
       </c>
       <c r="AJ19" s="9">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="AK19" s="10" t="s">
         <v>297</v>
       </c>
       <c r="AL19" s="9">
-        <v>7012</v>
+        <v>7022</v>
       </c>
       <c r="AM19" s="10" t="s">
         <v>298</v>
       </c>
       <c r="AN19" s="9">
-        <v>7039</v>
+        <v>7049</v>
       </c>
       <c r="AO19" s="10" t="s">
         <v>299</v>
@@ -5636,34 +5636,34 @@
         <v>300</v>
       </c>
       <c r="V20" s="9">
-        <v>4584</v>
+        <v>4590</v>
       </c>
       <c r="W20" s="10" t="s">
         <v>301</v>
       </c>
       <c r="X20" s="9">
-        <v>1978</v>
+        <v>1976</v>
       </c>
       <c r="Y20" s="10" t="s">
-        <v>221</v>
+        <v>302</v>
       </c>
       <c r="Z20" s="9">
         <v>507</v>
       </c>
       <c r="AA20" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AB20" s="9">
         <v>1887</v>
       </c>
       <c r="AC20" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AD20" s="9">
-        <v>4619</v>
+        <v>4635</v>
       </c>
       <c r="AE20" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AF20" s="9">
         <v>1</v>
@@ -5678,22 +5678,22 @@
         <v>192</v>
       </c>
       <c r="AJ20" s="9">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AK20" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AL20" s="9">
-        <v>9203</v>
+        <v>9225</v>
       </c>
       <c r="AM20" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AN20" s="9">
-        <v>9226</v>
+        <v>9248</v>
       </c>
       <c r="AO20" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -5710,7 +5710,7 @@
         <v>9</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F21" s="9">
         <v>1</v>
@@ -5758,37 +5758,37 @@
         <v>9</v>
       </c>
       <c r="U21" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="V21" s="9">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="W21" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="X21" s="9">
-        <v>965</v>
+        <v>970</v>
       </c>
       <c r="Y21" s="10" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Z21" s="9">
         <v>405</v>
       </c>
       <c r="AA21" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AB21" s="9">
-        <v>2101</v>
+        <v>2097</v>
       </c>
       <c r="AC21" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AD21" s="9">
-        <v>1824</v>
+        <v>1832</v>
       </c>
       <c r="AE21" s="10" t="s">
-        <v>313</v>
+        <v>234</v>
       </c>
       <c r="AF21" s="9">
         <v>0</v>
@@ -5809,13 +5809,13 @@
         <v>314</v>
       </c>
       <c r="AL21" s="9">
-        <v>3050</v>
+        <v>3060</v>
       </c>
       <c r="AM21" s="10" t="s">
         <v>315</v>
       </c>
       <c r="AN21" s="9">
-        <v>3059</v>
+        <v>3069</v>
       </c>
       <c r="AO21" s="10" t="s">
         <v>316</v>
@@ -5832,7 +5832,7 @@
         <v>130760</v>
       </c>
       <c r="D22" s="9">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>317</v>
@@ -5880,37 +5880,37 @@
         <v>192</v>
       </c>
       <c r="T22" s="9">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="U22" s="10" t="s">
         <v>317</v>
       </c>
       <c r="V22" s="9">
-        <v>9719</v>
+        <v>9817</v>
       </c>
       <c r="W22" s="10" t="s">
         <v>319</v>
       </c>
       <c r="X22" s="9">
-        <v>19674</v>
+        <v>19840</v>
       </c>
       <c r="Y22" s="10" t="s">
         <v>320</v>
       </c>
       <c r="Z22" s="9">
-        <v>10199</v>
+        <v>10313</v>
       </c>
       <c r="AA22" s="10" t="s">
         <v>321</v>
       </c>
       <c r="AB22" s="9">
-        <v>64500</v>
+        <v>64671</v>
       </c>
       <c r="AC22" s="10" t="s">
         <v>322</v>
       </c>
       <c r="AD22" s="9">
-        <v>15174</v>
+        <v>15317</v>
       </c>
       <c r="AE22" s="10" t="s">
         <v>323</v>
@@ -5922,28 +5922,28 @@
         <v>192</v>
       </c>
       <c r="AH22" s="9">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="AI22" s="10" t="s">
         <v>204</v>
       </c>
       <c r="AJ22" s="9">
-        <v>7436</v>
+        <v>7483</v>
       </c>
       <c r="AK22" s="10" t="s">
         <v>324</v>
       </c>
       <c r="AL22" s="9">
-        <v>24893</v>
+        <v>25134</v>
       </c>
       <c r="AM22" s="10" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="AN22" s="9">
-        <v>25318</v>
+        <v>25561</v>
       </c>
       <c r="AO22" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -5960,7 +5960,7 @@
         <v>43</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
@@ -6008,37 +6008,37 @@
         <v>43</v>
       </c>
       <c r="U23" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="V23" s="9">
-        <v>4007</v>
+        <v>4026</v>
       </c>
       <c r="W23" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="X23" s="9">
-        <v>3388</v>
+        <v>3407</v>
       </c>
       <c r="Y23" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Z23" s="9">
-        <v>3222</v>
+        <v>3229</v>
       </c>
       <c r="AA23" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AB23" s="9">
-        <v>3584</v>
+        <v>3596</v>
       </c>
       <c r="AC23" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AD23" s="9">
-        <v>3469</v>
+        <v>3512</v>
       </c>
       <c r="AE23" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AF23" s="9">
         <v>0</v>
@@ -6056,16 +6056,16 @@
         <v>283</v>
       </c>
       <c r="AK23" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AL23" s="9">
-        <v>7476</v>
+        <v>7538</v>
       </c>
       <c r="AM23" s="10" t="s">
-        <v>332</v>
+        <v>242</v>
       </c>
       <c r="AN23" s="9">
-        <v>7519</v>
+        <v>7581</v>
       </c>
       <c r="AO23" s="10" t="s">
         <v>333</v>
@@ -6082,7 +6082,7 @@
         <v>760553</v>
       </c>
       <c r="D24" s="12">
-        <v>1164</v>
+        <v>1168</v>
       </c>
       <c r="E24" s="13" t="s">
         <v>191</v>
@@ -6100,7 +6100,7 @@
         <v>192</v>
       </c>
       <c r="J24" s="12">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="K24" s="13" t="s">
         <v>193</v>
@@ -6112,7 +6112,7 @@
         <v>194</v>
       </c>
       <c r="N24" s="12">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="O24" s="13" t="s">
         <v>194</v>
@@ -6130,37 +6130,37 @@
         <v>192</v>
       </c>
       <c r="T24" s="12">
-        <v>1164</v>
+        <v>1168</v>
       </c>
       <c r="U24" s="13" t="s">
         <v>191</v>
       </c>
       <c r="V24" s="12">
-        <v>92551</v>
+        <v>93348</v>
       </c>
       <c r="W24" s="13" t="s">
         <v>195</v>
       </c>
       <c r="X24" s="12">
-        <v>139024</v>
+        <v>140034</v>
       </c>
       <c r="Y24" s="13" t="s">
         <v>196</v>
       </c>
       <c r="Z24" s="12">
-        <v>62878</v>
+        <v>63216</v>
       </c>
       <c r="AA24" s="13" t="s">
         <v>197</v>
       </c>
       <c r="AB24" s="12">
-        <v>334526</v>
+        <v>335068</v>
       </c>
       <c r="AC24" s="13" t="s">
         <v>198</v>
       </c>
       <c r="AD24" s="12">
-        <v>125697</v>
+        <v>127315</v>
       </c>
       <c r="AE24" s="13" t="s">
         <v>199</v>
@@ -6172,25 +6172,25 @@
         <v>192</v>
       </c>
       <c r="AH24" s="12">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AI24" s="13" t="s">
         <v>194</v>
       </c>
       <c r="AJ24" s="12">
-        <v>51245</v>
+        <v>51535</v>
       </c>
       <c r="AK24" s="13" t="s">
         <v>200</v>
       </c>
       <c r="AL24" s="12">
-        <v>218248</v>
+        <v>220663</v>
       </c>
       <c r="AM24" s="13" t="s">
         <v>201</v>
       </c>
       <c r="AN24" s="12">
-        <v>219412</v>
+        <v>221831</v>
       </c>
       <c r="AO24" s="13" t="s">
         <v>202</v>
@@ -6547,28 +6547,28 @@
         <v>760553</v>
       </c>
       <c r="G7" s="6">
-        <v>1336</v>
+        <v>1344</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>350</v>
       </c>
       <c r="I7" s="6">
-        <v>1198</v>
+        <v>1210</v>
       </c>
       <c r="J7" s="7" t="s">
         <v>351</v>
       </c>
       <c r="K7" s="6">
-        <v>215774</v>
+        <v>218164</v>
       </c>
       <c r="L7" s="7" t="s">
         <v>352</v>
       </c>
       <c r="M7" s="6">
-        <v>1104</v>
+        <v>1113</v>
       </c>
       <c r="N7" s="6">
-        <v>219412</v>
+        <v>221831</v>
       </c>
       <c r="O7" s="7" t="s">
         <v>202</v>
@@ -6606,16 +6606,16 @@
         <v>354</v>
       </c>
       <c r="K8" s="9">
-        <v>4147</v>
+        <v>4133</v>
       </c>
       <c r="L8" s="10" t="s">
         <v>355</v>
       </c>
       <c r="M8" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N8" s="9">
-        <v>4249</v>
+        <v>4234</v>
       </c>
       <c r="O8" s="10" t="s">
         <v>212</v>
@@ -6647,22 +6647,22 @@
         <v>356</v>
       </c>
       <c r="I9" s="9">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J9" s="10" t="s">
         <v>357</v>
       </c>
       <c r="K9" s="9">
-        <v>11372</v>
+        <v>11486</v>
       </c>
       <c r="L9" s="10" t="s">
         <v>358</v>
       </c>
       <c r="M9" s="9">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="N9" s="9">
-        <v>11528</v>
+        <v>11647</v>
       </c>
       <c r="O9" s="10" t="s">
         <v>222</v>
@@ -6688,31 +6688,31 @@
         <v>93539</v>
       </c>
       <c r="G10" s="9">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H10" s="10" t="s">
         <v>359</v>
       </c>
       <c r="I10" s="9">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="J10" s="10" t="s">
         <v>360</v>
       </c>
       <c r="K10" s="9">
-        <v>20787</v>
+        <v>21185</v>
       </c>
       <c r="L10" s="10" t="s">
         <v>361</v>
       </c>
       <c r="M10" s="9">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N10" s="9">
-        <v>21159</v>
+        <v>21563</v>
       </c>
       <c r="O10" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6747,7 +6747,7 @@
         <v>363</v>
       </c>
       <c r="K11" s="9">
-        <v>32271</v>
+        <v>32808</v>
       </c>
       <c r="L11" s="10" t="s">
         <v>364</v>
@@ -6756,10 +6756,10 @@
         <v>193</v>
       </c>
       <c r="N11" s="9">
-        <v>32654</v>
+        <v>33191</v>
       </c>
       <c r="O11" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6782,31 +6782,31 @@
         <v>131144</v>
       </c>
       <c r="G12" s="9">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H12" s="10" t="s">
         <v>365</v>
       </c>
       <c r="I12" s="9">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J12" s="10" t="s">
         <v>366</v>
       </c>
       <c r="K12" s="9">
-        <v>38221</v>
+        <v>38673</v>
       </c>
       <c r="L12" s="10" t="s">
         <v>367</v>
       </c>
       <c r="M12" s="9">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N12" s="9">
-        <v>38713</v>
+        <v>39169</v>
       </c>
       <c r="O12" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6841,19 +6841,19 @@
         <v>369</v>
       </c>
       <c r="K13" s="9">
-        <v>12948</v>
+        <v>13047</v>
       </c>
       <c r="L13" s="10" t="s">
         <v>370</v>
       </c>
       <c r="M13" s="9">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N13" s="9">
-        <v>13136</v>
+        <v>13236</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6882,25 +6882,25 @@
         <v>371</v>
       </c>
       <c r="I14" s="9">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J14" s="10" t="s">
         <v>372</v>
       </c>
       <c r="K14" s="9">
-        <v>9102</v>
+        <v>9278</v>
       </c>
       <c r="L14" s="10" t="s">
         <v>373</v>
       </c>
       <c r="M14" s="9">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="N14" s="9">
-        <v>9230</v>
+        <v>9410</v>
       </c>
       <c r="O14" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6923,7 +6923,7 @@
         <v>19507</v>
       </c>
       <c r="G15" s="9">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H15" s="10" t="s">
         <v>374</v>
@@ -6935,19 +6935,19 @@
         <v>375</v>
       </c>
       <c r="K15" s="9">
-        <v>9510</v>
+        <v>9588</v>
       </c>
       <c r="L15" s="10" t="s">
         <v>376</v>
       </c>
       <c r="M15" s="9">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N15" s="9">
-        <v>9610</v>
+        <v>9690</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6982,7 +6982,7 @@
         <v>378</v>
       </c>
       <c r="K16" s="9">
-        <v>12080</v>
+        <v>12165</v>
       </c>
       <c r="L16" s="10" t="s">
         <v>379</v>
@@ -6991,10 +6991,10 @@
         <v>49</v>
       </c>
       <c r="N16" s="9">
-        <v>12236</v>
+        <v>12321</v>
       </c>
       <c r="O16" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -7029,7 +7029,7 @@
         <v>381</v>
       </c>
       <c r="K17" s="9">
-        <v>14596</v>
+        <v>14722</v>
       </c>
       <c r="L17" s="10" t="s">
         <v>382</v>
@@ -7038,7 +7038,7 @@
         <v>86</v>
       </c>
       <c r="N17" s="9">
-        <v>14736</v>
+        <v>14862</v>
       </c>
       <c r="O17" s="10" t="s">
         <v>290</v>
@@ -7076,7 +7076,7 @@
         <v>384</v>
       </c>
       <c r="K18" s="9">
-        <v>6975</v>
+        <v>6985</v>
       </c>
       <c r="L18" s="10" t="s">
         <v>385</v>
@@ -7085,7 +7085,7 @@
         <v>13</v>
       </c>
       <c r="N18" s="9">
-        <v>7039</v>
+        <v>7049</v>
       </c>
       <c r="O18" s="10" t="s">
         <v>299</v>
@@ -7123,19 +7123,19 @@
         <v>387</v>
       </c>
       <c r="K19" s="9">
-        <v>9143</v>
+        <v>9165</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M19" s="9">
         <v>19</v>
       </c>
       <c r="N19" s="9">
-        <v>9226</v>
+        <v>9248</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -7170,7 +7170,7 @@
         <v>192</v>
       </c>
       <c r="K20" s="9">
-        <v>3045</v>
+        <v>3055</v>
       </c>
       <c r="L20" s="10" t="s">
         <v>388</v>
@@ -7179,7 +7179,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="9">
-        <v>3059</v>
+        <v>3069</v>
       </c>
       <c r="O20" s="10" t="s">
         <v>316</v>
@@ -7205,31 +7205,31 @@
         <v>130760</v>
       </c>
       <c r="G21" s="9">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="H21" s="10" t="s">
         <v>389</v>
       </c>
       <c r="I21" s="9">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="J21" s="10" t="s">
         <v>390</v>
       </c>
       <c r="K21" s="9">
-        <v>24239</v>
+        <v>24474</v>
       </c>
       <c r="L21" s="10" t="s">
         <v>391</v>
       </c>
       <c r="M21" s="9">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="N21" s="9">
-        <v>25318</v>
+        <v>25561</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -7264,7 +7264,7 @@
         <v>393</v>
       </c>
       <c r="K22" s="9">
-        <v>7338</v>
+        <v>7400</v>
       </c>
       <c r="L22" s="10" t="s">
         <v>394</v>
@@ -7273,7 +7273,7 @@
         <v>43</v>
       </c>
       <c r="N22" s="9">
-        <v>7519</v>
+        <v>7581</v>
       </c>
       <c r="O22" s="10" t="s">
         <v>333</v>
@@ -7299,28 +7299,28 @@
         <v>760553</v>
       </c>
       <c r="G23" s="12">
-        <v>1336</v>
+        <v>1344</v>
       </c>
       <c r="H23" s="13" t="s">
         <v>350</v>
       </c>
       <c r="I23" s="12">
-        <v>1198</v>
+        <v>1210</v>
       </c>
       <c r="J23" s="13" t="s">
         <v>351</v>
       </c>
       <c r="K23" s="12">
-        <v>215774</v>
+        <v>218164</v>
       </c>
       <c r="L23" s="13" t="s">
         <v>352</v>
       </c>
       <c r="M23" s="12">
-        <v>1104</v>
+        <v>1113</v>
       </c>
       <c r="N23" s="12">
-        <v>219412</v>
+        <v>221831</v>
       </c>
       <c r="O23" s="13" t="s">
         <v>202</v>
@@ -7674,43 +7674,43 @@
         <v>2153713</v>
       </c>
       <c r="D7" s="6">
-        <v>1074783</v>
+        <v>1080847</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>410</v>
       </c>
       <c r="F7" s="6">
-        <v>535538</v>
+        <v>539278</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>411</v>
       </c>
       <c r="H7" s="6">
-        <v>8763</v>
+        <v>8799</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>412</v>
       </c>
       <c r="J7" s="6">
-        <v>206363</v>
+        <v>206620</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>413</v>
       </c>
       <c r="L7" s="6">
-        <v>752014</v>
+        <v>756229</v>
       </c>
       <c r="M7" s="7" t="s">
         <v>414</v>
       </c>
       <c r="N7" s="6">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="O7" s="7" t="s">
         <v>194</v>
       </c>
       <c r="P7" s="6">
-        <v>1826797</v>
+        <v>1837076</v>
       </c>
       <c r="Q7" s="7" t="s">
         <v>415</v>
@@ -7727,34 +7727,34 @@
         <v>103485</v>
       </c>
       <c r="D8" s="9">
-        <v>60443</v>
+        <v>60234</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>416</v>
       </c>
       <c r="F8" s="9">
-        <v>20895</v>
+        <v>20864</v>
       </c>
       <c r="G8" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="H8" s="9">
+        <v>544</v>
+      </c>
+      <c r="I8" s="10" t="s">
         <v>417</v>
       </c>
-      <c r="H8" s="9">
-        <v>549</v>
-      </c>
-      <c r="I8" s="10" t="s">
+      <c r="J8" s="9">
+        <v>9235</v>
+      </c>
+      <c r="K8" s="10" t="s">
         <v>418</v>
       </c>
-      <c r="J8" s="9">
-        <v>9282</v>
-      </c>
-      <c r="K8" s="10" t="s">
+      <c r="L8" s="9">
+        <v>30758</v>
+      </c>
+      <c r="M8" s="10" t="s">
         <v>419</v>
-      </c>
-      <c r="L8" s="9">
-        <v>30948</v>
-      </c>
-      <c r="M8" s="10" t="s">
-        <v>420</v>
       </c>
       <c r="N8" s="9">
         <v>20</v>
@@ -7763,10 +7763,10 @@
         <v>193</v>
       </c>
       <c r="P8" s="9">
-        <v>91391</v>
+        <v>90992</v>
       </c>
       <c r="Q8" s="10" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7780,34 +7780,34 @@
         <v>171893</v>
       </c>
       <c r="D9" s="9">
-        <v>79941</v>
+        <v>80347</v>
       </c>
       <c r="E9" s="10" t="s">
+        <v>421</v>
+      </c>
+      <c r="F9" s="9">
+        <v>44689</v>
+      </c>
+      <c r="G9" s="10" t="s">
         <v>422</v>
       </c>
-      <c r="F9" s="9">
-        <v>44362</v>
-      </c>
-      <c r="G9" s="10" t="s">
+      <c r="H9" s="9">
+        <v>815</v>
+      </c>
+      <c r="I9" s="10" t="s">
         <v>423</v>
       </c>
-      <c r="H9" s="9">
-        <v>810</v>
-      </c>
-      <c r="I9" s="10" t="s">
+      <c r="J9" s="9">
+        <v>13735</v>
+      </c>
+      <c r="K9" s="10" t="s">
         <v>424</v>
       </c>
-      <c r="J9" s="9">
-        <v>13675</v>
-      </c>
-      <c r="K9" s="10" t="s">
+      <c r="L9" s="9">
+        <v>61124</v>
+      </c>
+      <c r="M9" s="10" t="s">
         <v>425</v>
-      </c>
-      <c r="L9" s="9">
-        <v>60793</v>
-      </c>
-      <c r="M9" s="10" t="s">
-        <v>426</v>
       </c>
       <c r="N9" s="9">
         <v>16</v>
@@ -7816,10 +7816,10 @@
         <v>194</v>
       </c>
       <c r="P9" s="9">
-        <v>140734</v>
+        <v>141471</v>
       </c>
       <c r="Q9" s="10" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7833,34 +7833,34 @@
         <v>201989</v>
       </c>
       <c r="D10" s="9">
-        <v>78956</v>
+        <v>79708</v>
       </c>
       <c r="E10" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="F10" s="9">
+        <v>49910</v>
+      </c>
+      <c r="G10" s="10" t="s">
         <v>428</v>
       </c>
-      <c r="F10" s="9">
-        <v>49357</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>429</v>
-      </c>
       <c r="H10" s="9">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="I10" s="10" t="s">
         <v>203</v>
       </c>
       <c r="J10" s="9">
-        <v>30938</v>
+        <v>31130</v>
       </c>
       <c r="K10" s="10" t="s">
+        <v>429</v>
+      </c>
+      <c r="L10" s="9">
+        <v>67412</v>
+      </c>
+      <c r="M10" s="10" t="s">
         <v>430</v>
-      </c>
-      <c r="L10" s="9">
-        <v>66918</v>
-      </c>
-      <c r="M10" s="10" t="s">
-        <v>431</v>
       </c>
       <c r="N10" s="9">
         <v>18</v>
@@ -7869,10 +7869,10 @@
         <v>194</v>
       </c>
       <c r="P10" s="9">
-        <v>145874</v>
+        <v>147120</v>
       </c>
       <c r="Q10" s="10" t="s">
-        <v>432</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7886,46 +7886,46 @@
         <v>347143</v>
       </c>
       <c r="D11" s="9">
-        <v>178815</v>
+        <v>180202</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="F11" s="9">
-        <v>81426</v>
+        <v>82045</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="H11" s="9">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="I11" s="10" t="s">
         <v>300</v>
       </c>
       <c r="J11" s="9">
-        <v>28989</v>
+        <v>29028</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="L11" s="9">
-        <v>130581</v>
+        <v>131676</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="N11" s="9">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O11" s="10" t="s">
         <v>193</v>
       </c>
       <c r="P11" s="9">
-        <v>309396</v>
+        <v>311878</v>
       </c>
       <c r="Q11" s="10" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7939,34 +7939,34 @@
         <v>416134</v>
       </c>
       <c r="D12" s="9">
-        <v>216305</v>
+        <v>217762</v>
       </c>
       <c r="E12" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="F12" s="9">
+        <v>96380</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>437</v>
+      </c>
+      <c r="H12" s="9">
+        <v>1040</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="J12" s="9">
+        <v>44397</v>
+      </c>
+      <c r="K12" s="10" t="s">
         <v>438</v>
       </c>
-      <c r="F12" s="9">
-        <v>95529</v>
-      </c>
-      <c r="G12" s="10" t="s">
+      <c r="L12" s="9">
+        <v>141131</v>
+      </c>
+      <c r="M12" s="10" t="s">
         <v>439</v>
-      </c>
-      <c r="H12" s="9">
-        <v>1032</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="J12" s="9">
-        <v>44426</v>
-      </c>
-      <c r="K12" s="10" t="s">
-        <v>440</v>
-      </c>
-      <c r="L12" s="9">
-        <v>140194</v>
-      </c>
-      <c r="M12" s="10" t="s">
-        <v>441</v>
       </c>
       <c r="N12" s="9">
         <v>57</v>
@@ -7975,10 +7975,10 @@
         <v>194</v>
       </c>
       <c r="P12" s="9">
-        <v>356499</v>
+        <v>358893</v>
       </c>
       <c r="Q12" s="10" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7992,34 +7992,34 @@
         <v>128332</v>
       </c>
       <c r="D13" s="9">
-        <v>63596</v>
+        <v>63928</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="F13" s="9">
-        <v>26589</v>
+        <v>26754</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="H13" s="9">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>300</v>
       </c>
       <c r="J13" s="9">
-        <v>22446</v>
+        <v>22485</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="L13" s="9">
-        <v>49878</v>
+        <v>50107</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="N13" s="9">
         <v>15</v>
@@ -8028,10 +8028,10 @@
         <v>194</v>
       </c>
       <c r="P13" s="9">
-        <v>113474</v>
+        <v>114035</v>
       </c>
       <c r="Q13" s="10" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8045,34 +8045,34 @@
         <v>128720</v>
       </c>
       <c r="D14" s="9">
-        <v>64375</v>
+        <v>64840</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F14" s="9">
-        <v>30654</v>
+        <v>31012</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="H14" s="9">
         <v>270</v>
       </c>
       <c r="I14" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="J14" s="9">
+        <v>10814</v>
+      </c>
+      <c r="K14" s="10" t="s">
+        <v>449</v>
+      </c>
+      <c r="L14" s="9">
+        <v>51679</v>
+      </c>
+      <c r="M14" s="10" t="s">
         <v>450</v>
-      </c>
-      <c r="J14" s="9">
-        <v>10831</v>
-      </c>
-      <c r="K14" s="10" t="s">
-        <v>451</v>
-      </c>
-      <c r="L14" s="9">
-        <v>51337</v>
-      </c>
-      <c r="M14" s="10" t="s">
-        <v>452</v>
       </c>
       <c r="N14" s="9">
         <v>17</v>
@@ -8081,10 +8081,10 @@
         <v>194</v>
       </c>
       <c r="P14" s="9">
-        <v>115712</v>
+        <v>116519</v>
       </c>
       <c r="Q14" s="10" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8098,46 +8098,46 @@
         <v>114275</v>
       </c>
       <c r="D15" s="9">
-        <v>52342</v>
+        <v>52826</v>
       </c>
       <c r="E15" s="10" t="s">
+        <v>452</v>
+      </c>
+      <c r="F15" s="9">
+        <v>32136</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>453</v>
+      </c>
+      <c r="H15" s="9">
+        <v>611</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>417</v>
+      </c>
+      <c r="J15" s="9">
+        <v>5615</v>
+      </c>
+      <c r="K15" s="10" t="s">
         <v>454</v>
       </c>
-      <c r="F15" s="9">
-        <v>31835</v>
-      </c>
-      <c r="G15" s="10" t="s">
+      <c r="L15" s="9">
+        <v>32941</v>
+      </c>
+      <c r="M15" s="10" t="s">
         <v>455</v>
       </c>
-      <c r="H15" s="9">
-        <v>603</v>
-      </c>
-      <c r="I15" s="10" t="s">
-        <v>418</v>
-      </c>
-      <c r="J15" s="9">
-        <v>5598</v>
-      </c>
-      <c r="K15" s="10" t="s">
+      <c r="N15" s="9">
+        <v>4</v>
+      </c>
+      <c r="O15" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="P15" s="9">
+        <v>85767</v>
+      </c>
+      <c r="Q15" s="10" t="s">
         <v>456</v>
-      </c>
-      <c r="L15" s="9">
-        <v>32691</v>
-      </c>
-      <c r="M15" s="10" t="s">
-        <v>457</v>
-      </c>
-      <c r="N15" s="9">
-        <v>6</v>
-      </c>
-      <c r="O15" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="P15" s="9">
-        <v>85033</v>
-      </c>
-      <c r="Q15" s="10" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8151,34 +8151,34 @@
         <v>154311</v>
       </c>
       <c r="D16" s="9">
-        <v>82700</v>
+        <v>83047</v>
       </c>
       <c r="E16" s="10" t="s">
+        <v>457</v>
+      </c>
+      <c r="F16" s="9">
+        <v>43917</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>458</v>
+      </c>
+      <c r="H16" s="9">
+        <v>1178</v>
+      </c>
+      <c r="I16" s="10" t="s">
         <v>459</v>
       </c>
-      <c r="F16" s="9">
-        <v>43769</v>
-      </c>
-      <c r="G16" s="10" t="s">
+      <c r="J16" s="9">
+        <v>10408</v>
+      </c>
+      <c r="K16" s="10" t="s">
         <v>460</v>
       </c>
-      <c r="H16" s="9">
-        <v>1170</v>
-      </c>
-      <c r="I16" s="10" t="s">
+      <c r="L16" s="9">
+        <v>36982</v>
+      </c>
+      <c r="M16" s="10" t="s">
         <v>461</v>
-      </c>
-      <c r="J16" s="9">
-        <v>10433</v>
-      </c>
-      <c r="K16" s="10" t="s">
-        <v>462</v>
-      </c>
-      <c r="L16" s="9">
-        <v>36813</v>
-      </c>
-      <c r="M16" s="10" t="s">
-        <v>463</v>
       </c>
       <c r="N16" s="9">
         <v>26</v>
@@ -8187,10 +8187,10 @@
         <v>193</v>
       </c>
       <c r="P16" s="9">
-        <v>119513</v>
+        <v>120029</v>
       </c>
       <c r="Q16" s="10" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8204,34 +8204,34 @@
         <v>117647</v>
       </c>
       <c r="D17" s="9">
-        <v>58140</v>
+        <v>58612</v>
       </c>
       <c r="E17" s="10" t="s">
+        <v>463</v>
+      </c>
+      <c r="F17" s="9">
+        <v>36400</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="H17" s="9">
+        <v>735</v>
+      </c>
+      <c r="I17" s="10" t="s">
         <v>465</v>
       </c>
-      <c r="F17" s="9">
-        <v>36080</v>
-      </c>
-      <c r="G17" s="10" t="s">
+      <c r="J17" s="9">
+        <v>7233</v>
+      </c>
+      <c r="K17" s="10" t="s">
         <v>466</v>
       </c>
-      <c r="H17" s="9">
-        <v>727</v>
-      </c>
-      <c r="I17" s="10" t="s">
+      <c r="L17" s="9">
+        <v>32996</v>
+      </c>
+      <c r="M17" s="10" t="s">
         <v>467</v>
-      </c>
-      <c r="J17" s="9">
-        <v>7205</v>
-      </c>
-      <c r="K17" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="L17" s="9">
-        <v>32766</v>
-      </c>
-      <c r="M17" s="10" t="s">
-        <v>469</v>
       </c>
       <c r="N17" s="9">
         <v>5</v>
@@ -8240,10 +8240,10 @@
         <v>192</v>
       </c>
       <c r="P17" s="9">
-        <v>90906</v>
+        <v>91608</v>
       </c>
       <c r="Q17" s="10" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8257,34 +8257,34 @@
         <v>80703</v>
       </c>
       <c r="D18" s="9">
-        <v>38018</v>
+        <v>38033</v>
       </c>
       <c r="E18" s="10" t="s">
+        <v>469</v>
+      </c>
+      <c r="F18" s="9">
+        <v>24427</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>470</v>
+      </c>
+      <c r="H18" s="9">
+        <v>574</v>
+      </c>
+      <c r="I18" s="10" t="s">
         <v>471</v>
       </c>
-      <c r="F18" s="9">
-        <v>24394</v>
-      </c>
-      <c r="G18" s="10" t="s">
+      <c r="J18" s="9">
+        <v>9685</v>
+      </c>
+      <c r="K18" s="10" t="s">
         <v>472</v>
       </c>
-      <c r="H18" s="9">
-        <v>577</v>
-      </c>
-      <c r="I18" s="10" t="s">
+      <c r="L18" s="9">
+        <v>22680</v>
+      </c>
+      <c r="M18" s="10" t="s">
         <v>473</v>
-      </c>
-      <c r="J18" s="9">
-        <v>9695</v>
-      </c>
-      <c r="K18" s="10" t="s">
-        <v>474</v>
-      </c>
-      <c r="L18" s="9">
-        <v>22675</v>
-      </c>
-      <c r="M18" s="10" t="s">
-        <v>475</v>
       </c>
       <c r="N18" s="9">
         <v>36</v>
@@ -8293,10 +8293,10 @@
         <v>318</v>
       </c>
       <c r="P18" s="9">
-        <v>60693</v>
+        <v>60713</v>
       </c>
       <c r="Q18" s="10" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8310,34 +8310,34 @@
         <v>101461</v>
       </c>
       <c r="D19" s="9">
-        <v>58952</v>
+        <v>59035</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="F19" s="9">
-        <v>24808</v>
+        <v>24834</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H19" s="9">
         <v>585</v>
       </c>
       <c r="I19" s="10" t="s">
+        <v>477</v>
+      </c>
+      <c r="J19" s="9">
+        <v>7748</v>
+      </c>
+      <c r="K19" s="10" t="s">
+        <v>478</v>
+      </c>
+      <c r="L19" s="9">
+        <v>33001</v>
+      </c>
+      <c r="M19" s="10" t="s">
         <v>479</v>
-      </c>
-      <c r="J19" s="9">
-        <v>7746</v>
-      </c>
-      <c r="K19" s="10" t="s">
-        <v>480</v>
-      </c>
-      <c r="L19" s="9">
-        <v>32968</v>
-      </c>
-      <c r="M19" s="10" t="s">
-        <v>481</v>
       </c>
       <c r="N19" s="9">
         <v>13</v>
@@ -8346,10 +8346,10 @@
         <v>194</v>
       </c>
       <c r="P19" s="9">
-        <v>91920</v>
+        <v>92036</v>
       </c>
       <c r="Q19" s="10" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8363,34 +8363,34 @@
         <v>51280</v>
       </c>
       <c r="D20" s="9">
-        <v>28009</v>
+        <v>28019</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="F20" s="9">
-        <v>15122</v>
+        <v>15138</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="H20" s="9">
         <v>235</v>
       </c>
       <c r="I20" s="10" t="s">
+        <v>483</v>
+      </c>
+      <c r="J20" s="9">
+        <v>2491</v>
+      </c>
+      <c r="K20" s="10" t="s">
+        <v>484</v>
+      </c>
+      <c r="L20" s="9">
+        <v>13769</v>
+      </c>
+      <c r="M20" s="10" t="s">
         <v>485</v>
-      </c>
-      <c r="J20" s="9">
-        <v>2490</v>
-      </c>
-      <c r="K20" s="10" t="s">
-        <v>486</v>
-      </c>
-      <c r="L20" s="9">
-        <v>13752</v>
-      </c>
-      <c r="M20" s="10" t="s">
-        <v>487</v>
       </c>
       <c r="N20" s="9">
         <v>6</v>
@@ -8399,10 +8399,10 @@
         <v>194</v>
       </c>
       <c r="P20" s="9">
-        <v>41761</v>
+        <v>41788</v>
       </c>
       <c r="Q20" s="10" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8416,46 +8416,46 @@
         <v>12551</v>
       </c>
       <c r="D21" s="9">
-        <v>3049</v>
+        <v>3067</v>
       </c>
       <c r="E21" s="10" t="s">
+        <v>487</v>
+      </c>
+      <c r="F21" s="9">
+        <v>3938</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="H21" s="9">
+        <v>105</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="J21" s="9">
+        <v>1869</v>
+      </c>
+      <c r="K21" s="10" t="s">
         <v>489</v>
       </c>
-      <c r="F21" s="9">
-        <v>3911</v>
-      </c>
-      <c r="G21" s="10" t="s">
+      <c r="L21" s="9">
+        <v>40959</v>
+      </c>
+      <c r="M21" s="10" t="s">
         <v>490</v>
-      </c>
-      <c r="H21" s="9">
-        <v>107</v>
-      </c>
-      <c r="I21" s="10" t="s">
-        <v>491</v>
-      </c>
-      <c r="J21" s="9">
-        <v>1862</v>
-      </c>
-      <c r="K21" s="10" t="s">
-        <v>492</v>
-      </c>
-      <c r="L21" s="9">
-        <v>40724</v>
-      </c>
-      <c r="M21" s="10" t="s">
-        <v>493</v>
       </c>
       <c r="N21" s="9">
         <v>18</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>223</v>
+        <v>283</v>
       </c>
       <c r="P21" s="9">
-        <v>43773</v>
+        <v>44026</v>
       </c>
       <c r="Q21" s="10" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8469,34 +8469,34 @@
         <v>23789</v>
       </c>
       <c r="D22" s="9">
-        <v>11142</v>
+        <v>11187</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="F22" s="9">
-        <v>6807</v>
+        <v>6834</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>457</v>
+        <v>493</v>
       </c>
       <c r="H22" s="9">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="J22" s="9">
         <v>747</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="L22" s="9">
-        <v>8976</v>
+        <v>9014</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="N22" s="9">
         <v>6</v>
@@ -8505,10 +8505,10 @@
         <v>204</v>
       </c>
       <c r="P22" s="9">
-        <v>20118</v>
+        <v>20201</v>
       </c>
       <c r="Q22" s="10" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8522,43 +8522,43 @@
         <v>2153713</v>
       </c>
       <c r="D23" s="12">
-        <v>1074783</v>
+        <v>1080847</v>
       </c>
       <c r="E23" s="13" t="s">
         <v>410</v>
       </c>
       <c r="F23" s="12">
-        <v>535538</v>
+        <v>539278</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>411</v>
       </c>
       <c r="H23" s="12">
-        <v>8763</v>
+        <v>8799</v>
       </c>
       <c r="I23" s="13" t="s">
         <v>412</v>
       </c>
       <c r="J23" s="12">
-        <v>206363</v>
+        <v>206620</v>
       </c>
       <c r="K23" s="13" t="s">
         <v>413</v>
       </c>
       <c r="L23" s="12">
-        <v>752014</v>
+        <v>756229</v>
       </c>
       <c r="M23" s="13" t="s">
         <v>414</v>
       </c>
       <c r="N23" s="12">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="O23" s="13" t="s">
         <v>194</v>
       </c>
       <c r="P23" s="12">
-        <v>1826797</v>
+        <v>1837076</v>
       </c>
       <c r="Q23" s="13" t="s">
         <v>415</v>
@@ -8587,7 +8587,7 @@
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B26" s="16" t="s">
         <v>337</v>
@@ -8652,7 +8652,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -8710,10 +8710,10 @@
         <v>406</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
@@ -8721,7 +8721,7 @@
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -8729,10 +8729,10 @@
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
       <c r="R4" s="3" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8754,28 +8754,28 @@
         <v>155</v>
       </c>
       <c r="J5" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="L5" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="M5" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="N5" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="O5" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="N5" s="3" t="s">
+      <c r="P5" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="O5" s="3" t="s">
+      <c r="Q5" s="3" t="s">
         <v>512</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>514</v>
       </c>
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
@@ -8856,46 +8856,46 @@
         <v>2914266</v>
       </c>
       <c r="F7" s="6">
-        <v>93715</v>
+        <v>94516</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H7" s="6">
-        <v>125697</v>
+        <v>127315</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>199</v>
       </c>
       <c r="J7" s="6">
-        <v>219412</v>
+        <v>221831</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>202</v>
       </c>
       <c r="L7" s="6">
-        <v>1074783</v>
+        <v>1080847</v>
       </c>
       <c r="M7" s="7" t="s">
         <v>410</v>
       </c>
       <c r="N7" s="6">
-        <v>752014</v>
+        <v>756229</v>
       </c>
       <c r="O7" s="7" t="s">
         <v>414</v>
       </c>
       <c r="P7" s="6">
-        <v>1826797</v>
+        <v>1837076</v>
       </c>
       <c r="Q7" s="7" t="s">
         <v>415</v>
       </c>
       <c r="R7" s="6">
-        <v>2046209</v>
+        <v>2058907</v>
       </c>
       <c r="S7" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8915,46 +8915,46 @@
         <v>115412</v>
       </c>
       <c r="F8" s="9">
-        <v>2083</v>
+        <v>2077</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="H8" s="9">
-        <v>2166</v>
+        <v>2157</v>
       </c>
       <c r="I8" s="10" t="s">
         <v>209</v>
       </c>
       <c r="J8" s="9">
-        <v>4249</v>
+        <v>4234</v>
       </c>
       <c r="K8" s="10" t="s">
         <v>212</v>
       </c>
       <c r="L8" s="9">
-        <v>60443</v>
+        <v>60234</v>
       </c>
       <c r="M8" s="10" t="s">
         <v>416</v>
       </c>
       <c r="N8" s="9">
-        <v>30948</v>
+        <v>30758</v>
       </c>
       <c r="O8" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="P8" s="9">
+        <v>90992</v>
+      </c>
+      <c r="Q8" s="10" t="s">
         <v>420</v>
       </c>
-      <c r="P8" s="9">
-        <v>91391</v>
-      </c>
-      <c r="Q8" s="10" t="s">
-        <v>421</v>
-      </c>
       <c r="R8" s="9">
-        <v>95640</v>
+        <v>95226</v>
       </c>
       <c r="S8" s="10" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8974,46 +8974,46 @@
         <v>229367</v>
       </c>
       <c r="F9" s="9">
-        <v>5375</v>
+        <v>5423</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H9" s="9">
-        <v>6153</v>
+        <v>6224</v>
       </c>
       <c r="I9" s="10" t="s">
         <v>219</v>
       </c>
       <c r="J9" s="9">
-        <v>11528</v>
+        <v>11647</v>
       </c>
       <c r="K9" s="10" t="s">
         <v>222</v>
       </c>
       <c r="L9" s="9">
-        <v>79941</v>
+        <v>80347</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="N9" s="9">
-        <v>60793</v>
+        <v>61124</v>
       </c>
       <c r="O9" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="P9" s="9">
+        <v>141471</v>
+      </c>
+      <c r="Q9" s="10" t="s">
         <v>426</v>
       </c>
-      <c r="P9" s="9">
-        <v>140734</v>
-      </c>
-      <c r="Q9" s="10" t="s">
-        <v>427</v>
-      </c>
       <c r="R9" s="9">
-        <v>152262</v>
+        <v>153118</v>
       </c>
       <c r="S9" s="10" t="s">
-        <v>379</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9033,46 +9033,46 @@
         <v>295528</v>
       </c>
       <c r="F10" s="9">
-        <v>6281</v>
+        <v>6382</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="H10" s="9">
-        <v>14878</v>
+        <v>15181</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J10" s="9">
-        <v>21159</v>
+        <v>21563</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L10" s="9">
-        <v>78956</v>
+        <v>79708</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="N10" s="9">
-        <v>66918</v>
+        <v>67412</v>
       </c>
       <c r="O10" s="10" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="P10" s="9">
-        <v>145874</v>
+        <v>147120</v>
       </c>
       <c r="Q10" s="10" t="s">
-        <v>432</v>
+        <v>45</v>
       </c>
       <c r="R10" s="9">
-        <v>167033</v>
+        <v>168683</v>
       </c>
       <c r="S10" s="10" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9092,46 +9092,46 @@
         <v>474247</v>
       </c>
       <c r="F11" s="9">
-        <v>15393</v>
+        <v>15553</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="H11" s="9">
-        <v>17261</v>
+        <v>17638</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J11" s="9">
-        <v>32654</v>
+        <v>33191</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L11" s="9">
-        <v>178815</v>
+        <v>180202</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="N11" s="9">
-        <v>130581</v>
+        <v>131676</v>
       </c>
       <c r="O11" s="10" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="P11" s="9">
-        <v>309396</v>
+        <v>311878</v>
       </c>
       <c r="Q11" s="10" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="R11" s="9">
-        <v>342050</v>
+        <v>345069</v>
       </c>
       <c r="S11" s="10" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9151,46 +9151,46 @@
         <v>547278</v>
       </c>
       <c r="F12" s="9">
-        <v>15049</v>
+        <v>15201</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H12" s="9">
-        <v>23664</v>
+        <v>23968</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J12" s="9">
-        <v>38713</v>
+        <v>39169</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L12" s="9">
-        <v>216305</v>
+        <v>217762</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="N12" s="9">
-        <v>140194</v>
+        <v>141131</v>
       </c>
       <c r="O12" s="10" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="P12" s="9">
-        <v>356499</v>
+        <v>358893</v>
       </c>
       <c r="Q12" s="10" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="R12" s="9">
-        <v>395212</v>
+        <v>398062</v>
       </c>
       <c r="S12" s="10" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9210,46 +9210,46 @@
         <v>192251</v>
       </c>
       <c r="F13" s="9">
-        <v>5056</v>
+        <v>5092</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H13" s="9">
-        <v>8080</v>
+        <v>8144</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J13" s="9">
-        <v>13136</v>
+        <v>13236</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="L13" s="9">
-        <v>63596</v>
+        <v>63928</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="N13" s="9">
-        <v>49878</v>
+        <v>50107</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="P13" s="9">
-        <v>113474</v>
+        <v>114035</v>
       </c>
       <c r="Q13" s="10" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="R13" s="9">
-        <v>126610</v>
+        <v>127271</v>
       </c>
       <c r="S13" s="10" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9269,46 +9269,46 @@
         <v>170050</v>
       </c>
       <c r="F14" s="9">
-        <v>2690</v>
+        <v>2736</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="H14" s="9">
-        <v>6540</v>
+        <v>6674</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J14" s="9">
-        <v>9230</v>
+        <v>9410</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L14" s="9">
-        <v>64375</v>
+        <v>64840</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="N14" s="9">
-        <v>51337</v>
+        <v>51679</v>
       </c>
       <c r="O14" s="10" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="P14" s="9">
-        <v>115712</v>
+        <v>116519</v>
       </c>
       <c r="Q14" s="10" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="R14" s="9">
-        <v>124942</v>
+        <v>125929</v>
       </c>
       <c r="S14" s="10" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9328,46 +9328,46 @@
         <v>133782</v>
       </c>
       <c r="F15" s="9">
-        <v>4343</v>
+        <v>4378</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="H15" s="9">
-        <v>5267</v>
+        <v>5312</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J15" s="9">
-        <v>9610</v>
+        <v>9690</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="L15" s="9">
-        <v>52342</v>
+        <v>52826</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="N15" s="9">
-        <v>32691</v>
+        <v>32941</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="P15" s="9">
-        <v>85033</v>
+        <v>85767</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="R15" s="9">
-        <v>94643</v>
+        <v>95457</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9387,46 +9387,46 @@
         <v>172696</v>
       </c>
       <c r="F16" s="9">
-        <v>5916</v>
+        <v>5944</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="H16" s="9">
-        <v>6320</v>
+        <v>6377</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J16" s="9">
-        <v>12236</v>
+        <v>12321</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L16" s="9">
-        <v>82700</v>
+        <v>83047</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="N16" s="9">
-        <v>36813</v>
+        <v>36982</v>
       </c>
       <c r="O16" s="10" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="P16" s="9">
-        <v>119513</v>
+        <v>120029</v>
       </c>
       <c r="Q16" s="10" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="R16" s="9">
-        <v>131749</v>
+        <v>132350</v>
       </c>
       <c r="S16" s="10" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9446,46 +9446,46 @@
         <v>139743</v>
       </c>
       <c r="F17" s="9">
-        <v>8332</v>
+        <v>8400</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="H17" s="9">
-        <v>6404</v>
+        <v>6462</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J17" s="9">
-        <v>14736</v>
+        <v>14862</v>
       </c>
       <c r="K17" s="10" t="s">
         <v>290</v>
       </c>
       <c r="L17" s="9">
-        <v>58140</v>
+        <v>58612</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="N17" s="9">
-        <v>32766</v>
+        <v>32996</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="P17" s="9">
-        <v>90906</v>
+        <v>91608</v>
       </c>
       <c r="Q17" s="10" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="R17" s="9">
-        <v>105642</v>
+        <v>106470</v>
       </c>
       <c r="S17" s="10" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9505,46 +9505,46 @@
         <v>91795</v>
       </c>
       <c r="F18" s="9">
-        <v>3161</v>
+        <v>3167</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="H18" s="9">
-        <v>3878</v>
+        <v>3882</v>
       </c>
       <c r="I18" s="10" t="s">
         <v>296</v>
       </c>
       <c r="J18" s="9">
-        <v>7039</v>
+        <v>7049</v>
       </c>
       <c r="K18" s="10" t="s">
         <v>299</v>
       </c>
       <c r="L18" s="9">
-        <v>38018</v>
+        <v>38033</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="N18" s="9">
-        <v>22675</v>
+        <v>22680</v>
       </c>
       <c r="O18" s="10" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="P18" s="9">
-        <v>60693</v>
+        <v>60713</v>
       </c>
       <c r="Q18" s="10" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="R18" s="9">
-        <v>67732</v>
+        <v>67762</v>
       </c>
       <c r="S18" s="10" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9564,46 +9564,46 @@
         <v>111370</v>
       </c>
       <c r="F19" s="9">
-        <v>4607</v>
+        <v>4613</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="H19" s="9">
-        <v>4619</v>
+        <v>4635</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J19" s="9">
-        <v>9226</v>
+        <v>9248</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L19" s="9">
-        <v>58952</v>
+        <v>59035</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="N19" s="9">
-        <v>32968</v>
+        <v>33001</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="P19" s="9">
-        <v>91920</v>
+        <v>92036</v>
       </c>
       <c r="Q19" s="10" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="R19" s="9">
-        <v>101146</v>
+        <v>101284</v>
       </c>
       <c r="S19" s="10" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9623,46 +9623,46 @@
         <v>56660</v>
       </c>
       <c r="F20" s="9">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>439</v>
+        <v>538</v>
       </c>
       <c r="H20" s="9">
-        <v>1824</v>
+        <v>1832</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>313</v>
+        <v>234</v>
       </c>
       <c r="J20" s="9">
-        <v>3059</v>
+        <v>3069</v>
       </c>
       <c r="K20" s="10" t="s">
         <v>316</v>
       </c>
       <c r="L20" s="9">
-        <v>28009</v>
+        <v>28019</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="N20" s="9">
-        <v>13752</v>
+        <v>13769</v>
       </c>
       <c r="O20" s="10" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="P20" s="9">
-        <v>41761</v>
+        <v>41788</v>
       </c>
       <c r="Q20" s="10" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="R20" s="9">
-        <v>44820</v>
+        <v>44857</v>
       </c>
       <c r="S20" s="10" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9682,46 +9682,46 @@
         <v>143311</v>
       </c>
       <c r="F21" s="9">
-        <v>10144</v>
+        <v>10244</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H21" s="9">
-        <v>15174</v>
+        <v>15317</v>
       </c>
       <c r="I21" s="10" t="s">
         <v>323</v>
       </c>
       <c r="J21" s="9">
-        <v>25318</v>
+        <v>25561</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L21" s="9">
-        <v>3049</v>
+        <v>3067</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="N21" s="9">
-        <v>40724</v>
+        <v>40959</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="P21" s="9">
-        <v>43773</v>
+        <v>44026</v>
       </c>
       <c r="Q21" s="10" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="R21" s="9">
-        <v>69091</v>
+        <v>69587</v>
       </c>
       <c r="S21" s="10" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9741,46 +9741,46 @@
         <v>40776</v>
       </c>
       <c r="F22" s="9">
-        <v>4050</v>
+        <v>4069</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H22" s="9">
-        <v>3469</v>
+        <v>3512</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J22" s="9">
-        <v>7519</v>
+        <v>7581</v>
       </c>
       <c r="K22" s="10" t="s">
         <v>333</v>
       </c>
       <c r="L22" s="9">
-        <v>11142</v>
+        <v>11187</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="N22" s="9">
-        <v>8976</v>
+        <v>9014</v>
       </c>
       <c r="O22" s="10" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="P22" s="9">
-        <v>20118</v>
+        <v>20201</v>
       </c>
       <c r="Q22" s="10" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="R22" s="9">
-        <v>27637</v>
+        <v>27782</v>
       </c>
       <c r="S22" s="10" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9800,46 +9800,46 @@
         <v>2914266</v>
       </c>
       <c r="F23" s="12">
-        <v>93715</v>
+        <v>94516</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H23" s="12">
-        <v>125697</v>
+        <v>127315</v>
       </c>
       <c r="I23" s="13" t="s">
         <v>199</v>
       </c>
       <c r="J23" s="12">
-        <v>219412</v>
+        <v>221831</v>
       </c>
       <c r="K23" s="13" t="s">
         <v>202</v>
       </c>
       <c r="L23" s="12">
-        <v>1074783</v>
+        <v>1080847</v>
       </c>
       <c r="M23" s="13" t="s">
         <v>410</v>
       </c>
       <c r="N23" s="12">
-        <v>752014</v>
+        <v>756229</v>
       </c>
       <c r="O23" s="13" t="s">
         <v>414</v>
       </c>
       <c r="P23" s="12">
-        <v>1826797</v>
+        <v>1837076</v>
       </c>
       <c r="Q23" s="13" t="s">
         <v>415</v>
       </c>
       <c r="R23" s="12">
-        <v>2046209</v>
+        <v>2058907</v>
       </c>
       <c r="S23" s="13" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
@@ -9867,10 +9867,10 @@
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="B26" s="16" t="s">
         <v>545</v>
-      </c>
-      <c r="B26" s="16" t="s">
-        <v>546</v>
       </c>
       <c r="C26" s="16"/>
       <c r="D26" s="16"/>
@@ -9892,10 +9892,10 @@
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
+        <v>546</v>
+      </c>
+      <c r="B27" s="16" t="s">
         <v>547</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>548</v>
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
@@ -9917,10 +9917,10 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
+        <v>548</v>
+      </c>
+      <c r="B28" s="16" t="s">
         <v>549</v>
-      </c>
-      <c r="B28" s="16" t="s">
-        <v>550</v>
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="16"/>
@@ -9942,10 +9942,10 @@
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
+        <v>550</v>
+      </c>
+      <c r="B29" s="16" t="s">
         <v>551</v>
-      </c>
-      <c r="B29" s="16" t="s">
-        <v>552</v>
       </c>
       <c r="C29" s="16"/>
       <c r="D29" s="16"/>
@@ -9967,10 +9967,10 @@
     </row>
     <row r="30" ht="24" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
+        <v>552</v>
+      </c>
+      <c r="B30" s="16" t="s">
         <v>553</v>
-      </c>
-      <c r="B30" s="16" t="s">
-        <v>554</v>
       </c>
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
@@ -10031,7 +10031,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -10059,19 +10059,19 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>334</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>558</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10105,19 +10105,19 @@
         <v>33</v>
       </c>
       <c r="C6" s="6">
-        <v>3333720</v>
+        <v>3352341</v>
       </c>
       <c r="D6" s="6">
-        <v>219412</v>
+        <v>221831</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>560</v>
+        <v>526</v>
       </c>
       <c r="F6" s="6">
-        <v>1826797</v>
+        <v>1837076</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10128,19 +10128,19 @@
         <v>38</v>
       </c>
       <c r="C7" s="9">
-        <v>134900</v>
+        <v>134404</v>
       </c>
       <c r="D7" s="9">
-        <v>4249</v>
+        <v>4234</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="F7" s="9">
-        <v>91391</v>
+        <v>90992</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10151,19 +10151,19 @@
         <v>43</v>
       </c>
       <c r="C8" s="9">
-        <v>249435</v>
+        <v>250879</v>
       </c>
       <c r="D8" s="9">
-        <v>11528</v>
+        <v>11647</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="F8" s="9">
-        <v>140734</v>
+        <v>141471</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10174,19 +10174,19 @@
         <v>48</v>
       </c>
       <c r="C9" s="9">
-        <v>322951</v>
+        <v>325558</v>
       </c>
       <c r="D9" s="9">
-        <v>21159</v>
+        <v>21563</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>566</v>
+        <v>526</v>
       </c>
       <c r="F9" s="9">
-        <v>145874</v>
+        <v>147120</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10197,19 +10197,19 @@
         <v>53</v>
       </c>
       <c r="C10" s="9">
-        <v>535731</v>
+        <v>539809</v>
       </c>
       <c r="D10" s="9">
-        <v>32654</v>
+        <v>33191</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>111</v>
+        <v>466</v>
       </c>
       <c r="F10" s="9">
-        <v>309396</v>
+        <v>311878</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10220,19 +10220,19 @@
         <v>58</v>
       </c>
       <c r="C11" s="9">
-        <v>634144</v>
+        <v>638164</v>
       </c>
       <c r="D11" s="9">
-        <v>38713</v>
+        <v>39169</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>111</v>
+        <v>566</v>
       </c>
       <c r="F11" s="9">
-        <v>356499</v>
+        <v>358893</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10243,19 +10243,19 @@
         <v>63</v>
       </c>
       <c r="C12" s="9">
-        <v>227451</v>
+        <v>228402</v>
       </c>
       <c r="D12" s="9">
-        <v>13136</v>
+        <v>13236</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="F12" s="9">
-        <v>113474</v>
+        <v>114035</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10266,19 +10266,19 @@
         <v>68</v>
       </c>
       <c r="C13" s="9">
-        <v>197687</v>
+        <v>199106</v>
       </c>
       <c r="D13" s="9">
-        <v>9230</v>
+        <v>9410</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="F13" s="9">
-        <v>115712</v>
+        <v>116519</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10289,19 +10289,19 @@
         <v>73</v>
       </c>
       <c r="C14" s="9">
-        <v>144419</v>
+        <v>145576</v>
       </c>
       <c r="D14" s="9">
-        <v>9610</v>
+        <v>9690</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="F14" s="9">
-        <v>85033</v>
+        <v>85767</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10312,19 +10312,19 @@
         <v>78</v>
       </c>
       <c r="C15" s="9">
-        <v>197528</v>
+        <v>198261</v>
       </c>
       <c r="D15" s="9">
-        <v>12236</v>
+        <v>12321</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="F15" s="9">
-        <v>119513</v>
+        <v>120029</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10335,19 +10335,19 @@
         <v>83</v>
       </c>
       <c r="C16" s="9">
-        <v>160133</v>
+        <v>161377</v>
       </c>
       <c r="D16" s="9">
-        <v>14736</v>
+        <v>14862</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="F16" s="9">
-        <v>90906</v>
+        <v>91608</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10358,19 +10358,19 @@
         <v>88</v>
       </c>
       <c r="C17" s="9">
-        <v>108984</v>
+        <v>109035</v>
       </c>
       <c r="D17" s="9">
-        <v>7039</v>
+        <v>7049</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="F17" s="9">
-        <v>60693</v>
+        <v>60713</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10381,19 +10381,19 @@
         <v>93</v>
       </c>
       <c r="C18" s="9">
-        <v>138658</v>
+        <v>138822</v>
       </c>
       <c r="D18" s="9">
-        <v>9226</v>
+        <v>9248</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="F18" s="9">
-        <v>91920</v>
+        <v>92036</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>282</v>
+        <v>580</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10404,19 +10404,19 @@
         <v>98</v>
       </c>
       <c r="C19" s="9">
-        <v>66141</v>
+        <v>66196</v>
       </c>
       <c r="D19" s="9">
-        <v>3059</v>
+        <v>3069</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="F19" s="9">
-        <v>41761</v>
+        <v>41788</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10427,19 +10427,19 @@
         <v>103</v>
       </c>
       <c r="C20" s="9">
-        <v>169584</v>
+        <v>170563</v>
       </c>
       <c r="D20" s="9">
-        <v>25318</v>
+        <v>25561</v>
       </c>
       <c r="E20" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="F20" s="9">
+        <v>44026</v>
+      </c>
+      <c r="G20" s="10" t="s">
         <v>583</v>
-      </c>
-      <c r="F20" s="9">
-        <v>43773</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10450,16 +10450,16 @@
         <v>108</v>
       </c>
       <c r="C21" s="9">
-        <v>45974</v>
+        <v>46189</v>
       </c>
       <c r="D21" s="9">
-        <v>7519</v>
+        <v>7581</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>584</v>
       </c>
       <c r="F21" s="9">
-        <v>20118</v>
+        <v>20201</v>
       </c>
       <c r="G21" s="10" t="s">
         <v>585</v>
@@ -10473,19 +10473,19 @@
         <v>113</v>
       </c>
       <c r="C22" s="12">
-        <v>3333720</v>
+        <v>3352341</v>
       </c>
       <c r="D22" s="12">
-        <v>219412</v>
+        <v>221831</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>560</v>
+        <v>526</v>
       </c>
       <c r="F22" s="12">
-        <v>1826797</v>
+        <v>1837076</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -10631,22 +10631,22 @@
         <v>33</v>
       </c>
       <c r="C7" s="6">
-        <v>2036512</v>
+        <v>2049115</v>
       </c>
       <c r="D7" s="6">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="E7" s="6">
-        <v>4431</v>
+        <v>4472</v>
       </c>
       <c r="F7" s="6">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G7" s="6">
         <v>88</v>
       </c>
       <c r="H7" s="6">
-        <v>1610</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10657,22 +10657,22 @@
         <v>38</v>
       </c>
       <c r="C8" s="9">
-        <v>95490</v>
+        <v>95079</v>
       </c>
       <c r="D8" s="9">
         <v>3</v>
       </c>
       <c r="E8" s="9">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F8" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G8" s="9">
         <v>0</v>
       </c>
       <c r="H8" s="9">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10683,13 +10683,13 @@
         <v>43</v>
       </c>
       <c r="C9" s="9">
-        <v>151522</v>
+        <v>152363</v>
       </c>
       <c r="D9" s="9">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E9" s="9">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="F9" s="9">
         <v>3</v>
@@ -10698,7 +10698,7 @@
         <v>2</v>
       </c>
       <c r="H9" s="9">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10709,22 +10709,22 @@
         <v>48</v>
       </c>
       <c r="C10" s="9">
-        <v>166234</v>
+        <v>167879</v>
       </c>
       <c r="D10" s="9">
         <v>28</v>
       </c>
       <c r="E10" s="9">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="F10" s="9">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G10" s="9">
         <v>17</v>
       </c>
       <c r="H10" s="9">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10735,13 +10735,13 @@
         <v>53</v>
       </c>
       <c r="C11" s="9">
-        <v>340367</v>
+        <v>343364</v>
       </c>
       <c r="D11" s="9">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E11" s="9">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F11" s="9">
         <v>29</v>
@@ -10750,7 +10750,7 @@
         <v>14</v>
       </c>
       <c r="H11" s="9">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10761,22 +10761,22 @@
         <v>58</v>
       </c>
       <c r="C12" s="9">
-        <v>393816</v>
+        <v>396648</v>
       </c>
       <c r="D12" s="9">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E12" s="9">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="F12" s="9">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G12" s="9">
         <v>23</v>
       </c>
       <c r="H12" s="9">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10787,13 +10787,13 @@
         <v>63</v>
       </c>
       <c r="C13" s="9">
-        <v>126017</v>
+        <v>126672</v>
       </c>
       <c r="D13" s="9">
         <v>7</v>
       </c>
       <c r="E13" s="9">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F13" s="9">
         <v>9</v>
@@ -10802,7 +10802,7 @@
         <v>2</v>
       </c>
       <c r="H13" s="9">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10813,7 +10813,7 @@
         <v>68</v>
       </c>
       <c r="C14" s="9">
-        <v>124438</v>
+        <v>125419</v>
       </c>
       <c r="D14" s="9">
         <v>5</v>
@@ -10828,7 +10828,7 @@
         <v>3</v>
       </c>
       <c r="H14" s="9">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10839,7 +10839,7 @@
         <v>73</v>
       </c>
       <c r="C15" s="9">
-        <v>94392</v>
+        <v>95204</v>
       </c>
       <c r="D15" s="9">
         <v>10</v>
@@ -10854,7 +10854,7 @@
         <v>3</v>
       </c>
       <c r="H15" s="9">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10865,13 +10865,13 @@
         <v>78</v>
       </c>
       <c r="C16" s="9">
-        <v>131466</v>
+        <v>132067</v>
       </c>
       <c r="D16" s="9">
         <v>12</v>
       </c>
       <c r="E16" s="9">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F16" s="9">
         <v>2</v>
@@ -10891,13 +10891,13 @@
         <v>83</v>
       </c>
       <c r="C17" s="9">
-        <v>105226</v>
+        <v>106044</v>
       </c>
       <c r="D17" s="9">
         <v>11</v>
       </c>
       <c r="E17" s="9">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="F17" s="9">
         <v>12</v>
@@ -10906,7 +10906,7 @@
         <v>3</v>
       </c>
       <c r="H17" s="9">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10917,7 +10917,7 @@
         <v>88</v>
       </c>
       <c r="C18" s="9">
-        <v>67554</v>
+        <v>67584</v>
       </c>
       <c r="D18" s="9">
         <v>4</v>
@@ -10943,7 +10943,7 @@
         <v>93</v>
       </c>
       <c r="C19" s="9">
-        <v>100988</v>
+        <v>101126</v>
       </c>
       <c r="D19" s="9">
         <v>4</v>
@@ -10969,7 +10969,7 @@
         <v>98</v>
       </c>
       <c r="C20" s="9">
-        <v>44761</v>
+        <v>44798</v>
       </c>
       <c r="D20" s="9">
         <v>2</v>
@@ -10995,13 +10995,13 @@
         <v>103</v>
       </c>
       <c r="C21" s="9">
-        <v>67026</v>
+        <v>67508</v>
       </c>
       <c r="D21" s="9">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E21" s="9">
-        <v>1426</v>
+        <v>1436</v>
       </c>
       <c r="F21" s="9">
         <v>49</v>
@@ -11010,7 +11010,7 @@
         <v>8</v>
       </c>
       <c r="H21" s="9">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11021,7 +11021,7 @@
         <v>108</v>
       </c>
       <c r="C22" s="9">
-        <v>27215</v>
+        <v>27360</v>
       </c>
       <c r="D22" s="9">
         <v>33</v>
@@ -11047,22 +11047,22 @@
         <v>113</v>
       </c>
       <c r="C23" s="12">
-        <v>2036512</v>
+        <v>2049115</v>
       </c>
       <c r="D23" s="12">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="E23" s="12">
-        <v>4431</v>
+        <v>4472</v>
       </c>
       <c r="F23" s="12">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G23" s="12">
         <v>88</v>
       </c>
       <c r="H23" s="12">
-        <v>1610</v>
+        <v>1623</v>
       </c>
     </row>
   </sheetData>
@@ -11178,16 +11178,16 @@
         <v>155</v>
       </c>
       <c r="J5" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="L5" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="M5" s="3" t="s">
         <v>510</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>511</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11248,28 +11248,28 @@
         <v>2027897</v>
       </c>
       <c r="F7" s="6">
-        <v>1624</v>
+        <v>1633</v>
       </c>
       <c r="G7" s="7" t="s">
+        <v>542</v>
+      </c>
+      <c r="H7" s="6">
+        <v>5185</v>
+      </c>
+      <c r="I7" s="7" t="s">
         <v>602</v>
       </c>
-      <c r="H7" s="6">
-        <v>5134</v>
-      </c>
-      <c r="I7" s="7" t="s">
+      <c r="J7" s="6">
+        <v>1007647</v>
+      </c>
+      <c r="K7" s="7" t="s">
         <v>603</v>
       </c>
-      <c r="J7" s="6">
-        <v>1001883</v>
-      </c>
-      <c r="K7" s="7" t="s">
+      <c r="L7" s="6">
+        <v>446260</v>
+      </c>
+      <c r="M7" s="7" t="s">
         <v>604</v>
-      </c>
-      <c r="L7" s="6">
-        <v>444012</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11292,25 +11292,25 @@
         <v>20</v>
       </c>
       <c r="G8" s="10" t="s">
+        <v>605</v>
+      </c>
+      <c r="H8" s="9">
+        <v>126</v>
+      </c>
+      <c r="I8" s="10" t="s">
         <v>606</v>
       </c>
-      <c r="H8" s="9">
-        <v>127</v>
-      </c>
-      <c r="I8" s="10" t="s">
+      <c r="J8" s="9">
+        <v>51977</v>
+      </c>
+      <c r="K8" s="10" t="s">
         <v>607</v>
       </c>
-      <c r="J8" s="9">
-        <v>52156</v>
-      </c>
-      <c r="K8" s="10" t="s">
+      <c r="L8" s="9">
+        <v>23520</v>
+      </c>
+      <c r="M8" s="10" t="s">
         <v>608</v>
-      </c>
-      <c r="L8" s="9">
-        <v>23660</v>
-      </c>
-      <c r="M8" s="10" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11330,28 +11330,28 @@
         <v>172111</v>
       </c>
       <c r="F9" s="9">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G9" s="10" t="s">
+        <v>609</v>
+      </c>
+      <c r="H9" s="9">
+        <v>400</v>
+      </c>
+      <c r="I9" s="10" t="s">
         <v>610</v>
       </c>
-      <c r="H9" s="9">
-        <v>393</v>
-      </c>
-      <c r="I9" s="10" t="s">
+      <c r="J9" s="9">
+        <v>79946</v>
+      </c>
+      <c r="K9" s="10" t="s">
         <v>611</v>
       </c>
-      <c r="J9" s="9">
-        <v>79540</v>
-      </c>
-      <c r="K9" s="10" t="s">
+      <c r="L9" s="9">
+        <v>35335</v>
+      </c>
+      <c r="M9" s="10" t="s">
         <v>612</v>
-      </c>
-      <c r="L9" s="9">
-        <v>35169</v>
-      </c>
-      <c r="M9" s="10" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11371,28 +11371,28 @@
         <v>202453</v>
       </c>
       <c r="F10" s="9">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="G10" s="10" t="s">
+        <v>613</v>
+      </c>
+      <c r="H10" s="9">
+        <v>1205</v>
+      </c>
+      <c r="I10" s="10" t="s">
         <v>614</v>
       </c>
-      <c r="H10" s="9">
-        <v>1192</v>
-      </c>
-      <c r="I10" s="10" t="s">
+      <c r="J10" s="9">
+        <v>79229</v>
+      </c>
+      <c r="K10" s="10" t="s">
         <v>615</v>
       </c>
-      <c r="J10" s="9">
-        <v>78476</v>
-      </c>
-      <c r="K10" s="10" t="s">
+      <c r="L10" s="9">
+        <v>32538</v>
+      </c>
+      <c r="M10" s="10" t="s">
         <v>616</v>
-      </c>
-      <c r="L10" s="9">
-        <v>32338</v>
-      </c>
-      <c r="M10" s="10" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11412,28 +11412,28 @@
         <v>347651</v>
       </c>
       <c r="F11" s="9">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G11" s="10" t="s">
+        <v>617</v>
+      </c>
+      <c r="H11" s="9">
+        <v>446</v>
+      </c>
+      <c r="I11" s="10" t="s">
         <v>618</v>
       </c>
-      <c r="H11" s="9">
-        <v>440</v>
-      </c>
-      <c r="I11" s="10" t="s">
+      <c r="J11" s="9">
+        <v>179188</v>
+      </c>
+      <c r="K11" s="10" t="s">
         <v>619</v>
       </c>
-      <c r="J11" s="9">
-        <v>177805</v>
-      </c>
-      <c r="K11" s="10" t="s">
+      <c r="L11" s="9">
+        <v>79411</v>
+      </c>
+      <c r="M11" s="10" t="s">
         <v>620</v>
-      </c>
-      <c r="L11" s="9">
-        <v>78776</v>
-      </c>
-      <c r="M11" s="10" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11453,25 +11453,25 @@
         <v>416503</v>
       </c>
       <c r="F12" s="9">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="G12" s="10" t="s">
+        <v>621</v>
+      </c>
+      <c r="H12" s="9">
+        <v>762</v>
+      </c>
+      <c r="I12" s="10" t="s">
         <v>622</v>
       </c>
-      <c r="H12" s="9">
-        <v>755</v>
-      </c>
-      <c r="I12" s="10" t="s">
+      <c r="J12" s="9">
+        <v>217056</v>
+      </c>
+      <c r="K12" s="10" t="s">
         <v>623</v>
       </c>
-      <c r="J12" s="9">
-        <v>215605</v>
-      </c>
-      <c r="K12" s="10" t="s">
-        <v>516</v>
-      </c>
       <c r="L12" s="9">
-        <v>91499</v>
+        <v>92065</v>
       </c>
       <c r="M12" s="10" t="s">
         <v>624</v>
@@ -11494,25 +11494,25 @@
         <v>128482</v>
       </c>
       <c r="F13" s="9">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G13" s="10" t="s">
         <v>625</v>
       </c>
       <c r="H13" s="9">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>626</v>
       </c>
       <c r="J13" s="9">
-        <v>63369</v>
+        <v>63700</v>
       </c>
       <c r="K13" s="10" t="s">
         <v>627</v>
       </c>
       <c r="L13" s="9">
-        <v>29282</v>
+        <v>29419</v>
       </c>
       <c r="M13" s="10" t="s">
         <v>628</v>
@@ -11535,25 +11535,25 @@
         <v>128768</v>
       </c>
       <c r="F14" s="9">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G14" s="10" t="s">
         <v>629</v>
       </c>
       <c r="H14" s="9">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="I14" s="10" t="s">
         <v>630</v>
       </c>
       <c r="J14" s="9">
-        <v>64055</v>
+        <v>64521</v>
       </c>
       <c r="K14" s="10" t="s">
         <v>631</v>
       </c>
       <c r="L14" s="9">
-        <v>33463</v>
+        <v>33664</v>
       </c>
       <c r="M14" s="10" t="s">
         <v>632</v>
@@ -11582,19 +11582,19 @@
         <v>633</v>
       </c>
       <c r="H15" s="9">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="I15" s="10" t="s">
         <v>634</v>
       </c>
       <c r="J15" s="9">
-        <v>43368</v>
+        <v>43765</v>
       </c>
       <c r="K15" s="10" t="s">
         <v>635</v>
       </c>
       <c r="L15" s="9">
-        <v>23087</v>
+        <v>23270</v>
       </c>
       <c r="M15" s="10" t="s">
         <v>636</v>
@@ -11620,25 +11620,25 @@
         <v>63</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>463</v>
+        <v>637</v>
       </c>
       <c r="H16" s="9">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="J16" s="9">
-        <v>66505</v>
+        <v>66772</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="L16" s="9">
-        <v>23414</v>
+        <v>23534</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11661,22 +11661,22 @@
         <v>33</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>640</v>
+        <v>449</v>
       </c>
       <c r="H17" s="9">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="I17" s="10" t="s">
         <v>641</v>
       </c>
       <c r="J17" s="9">
-        <v>44582</v>
+        <v>44935</v>
       </c>
       <c r="K17" s="10" t="s">
         <v>642</v>
       </c>
       <c r="L17" s="9">
-        <v>18546</v>
+        <v>18675</v>
       </c>
       <c r="M17" s="10" t="s">
         <v>643</v>
@@ -11711,13 +11711,13 @@
         <v>645</v>
       </c>
       <c r="J18" s="9">
-        <v>33013</v>
+        <v>33026</v>
       </c>
       <c r="K18" s="10" t="s">
         <v>646</v>
       </c>
       <c r="L18" s="9">
-        <v>16611</v>
+        <v>16615</v>
       </c>
       <c r="M18" s="10" t="s">
         <v>647</v>
@@ -11743,25 +11743,25 @@
         <v>21</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>228</v>
+        <v>648</v>
       </c>
       <c r="H19" s="9">
         <v>111</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="J19" s="9">
-        <v>51171</v>
+        <v>51244</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="L19" s="9">
-        <v>24949</v>
+        <v>24972</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11784,25 +11784,25 @@
         <v>10</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H20" s="9">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="J20" s="9">
-        <v>23712</v>
+        <v>23720</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="L20" s="9">
-        <v>9995</v>
+        <v>10005</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11825,25 +11825,25 @@
         <v>46</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H21" s="9">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="J21" s="9">
-        <v>2897</v>
+        <v>2915</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="L21" s="9">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11866,7 +11866,7 @@
         <v>28</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>659</v>
+        <v>65</v>
       </c>
       <c r="H22" s="9">
         <v>13</v>
@@ -11875,13 +11875,13 @@
         <v>660</v>
       </c>
       <c r="J22" s="9">
-        <v>5629</v>
+        <v>5653</v>
       </c>
       <c r="K22" s="10" t="s">
         <v>661</v>
       </c>
       <c r="L22" s="9">
-        <v>2154</v>
+        <v>2165</v>
       </c>
       <c r="M22" s="10" t="s">
         <v>662</v>
@@ -11904,28 +11904,28 @@
         <v>2027897</v>
       </c>
       <c r="F23" s="12">
-        <v>1624</v>
+        <v>1633</v>
       </c>
       <c r="G23" s="13" t="s">
+        <v>542</v>
+      </c>
+      <c r="H23" s="12">
+        <v>5185</v>
+      </c>
+      <c r="I23" s="13" t="s">
         <v>602</v>
       </c>
-      <c r="H23" s="12">
-        <v>5134</v>
-      </c>
-      <c r="I23" s="13" t="s">
+      <c r="J23" s="12">
+        <v>1007647</v>
+      </c>
+      <c r="K23" s="13" t="s">
         <v>603</v>
       </c>
-      <c r="J23" s="12">
-        <v>1001883</v>
-      </c>
-      <c r="K23" s="13" t="s">
+      <c r="L23" s="12">
+        <v>446260</v>
+      </c>
+      <c r="M23" s="13" t="s">
         <v>604</v>
-      </c>
-      <c r="L23" s="12">
-        <v>444012</v>
-      </c>
-      <c r="M23" s="13" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
